--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
-  </si>
-  <si>
-    <t>25.02.202618</t>
-  </si>
-  <si>
-    <t>25.02.202619</t>
-  </si>
-  <si>
-    <t>25.02.202620</t>
-  </si>
-  <si>
-    <t>25.02.202621</t>
-  </si>
-  <si>
-    <t>25.02.202622</t>
-  </si>
-  <si>
-    <t>25.02.202623</t>
-  </si>
-  <si>
-    <t>25.02.202624</t>
-  </si>
-  <si>
-    <t>25.02.202625</t>
-  </si>
-  <si>
-    <t>25.02.202626</t>
-  </si>
-  <si>
-    <t>25.02.202627</t>
-  </si>
-  <si>
-    <t>25.02.202628</t>
-  </si>
-  <si>
-    <t>25.02.202629</t>
-  </si>
-  <si>
-    <t>25.02.202630</t>
-  </si>
-  <si>
-    <t>25.02.202631</t>
-  </si>
-  <si>
-    <t>25.02.202632</t>
-  </si>
-  <si>
-    <t>25.02.202633</t>
-  </si>
-  <si>
-    <t>25.02.202634</t>
-  </si>
-  <si>
-    <t>25.02.202635</t>
-  </si>
-  <si>
-    <t>25.02.202636</t>
-  </si>
-  <si>
-    <t>25.02.202637</t>
-  </si>
-  <si>
-    <t>25.02.202638</t>
-  </si>
-  <si>
-    <t>25.02.202639</t>
-  </si>
-  <si>
-    <t>25.02.202640</t>
-  </si>
-  <si>
-    <t>25.02.202641</t>
-  </si>
-  <si>
-    <t>25.02.202642</t>
-  </si>
-  <si>
-    <t>25.02.202643</t>
-  </si>
-  <si>
-    <t>25.02.202644</t>
-  </si>
-  <si>
-    <t>25.02.202645</t>
-  </si>
-  <si>
-    <t>25.02.202646</t>
-  </si>
-  <si>
-    <t>25.02.202647</t>
-  </si>
-  <si>
-    <t>25.02.202648</t>
-  </si>
-  <si>
-    <t>25.02.202649</t>
-  </si>
-  <si>
-    <t>25.02.202650</t>
-  </si>
-  <si>
-    <t>25.02.202651</t>
-  </si>
-  <si>
-    <t>25.02.202652</t>
-  </si>
-  <si>
-    <t>25.02.202653</t>
-  </si>
-  <si>
-    <t>25.02.202654</t>
-  </si>
-  <si>
-    <t>25.02.202655</t>
-  </si>
-  <si>
-    <t>25.02.202656</t>
-  </si>
-  <si>
-    <t>25.02.202657</t>
-  </si>
-  <si>
-    <t>25.02.202658</t>
-  </si>
-  <si>
-    <t>25.02.202659</t>
-  </si>
-  <si>
-    <t>25.02.202660</t>
-  </si>
-  <si>
-    <t>25.02.202661</t>
-  </si>
-  <si>
-    <t>25.02.202662</t>
-  </si>
-  <si>
-    <t>25.02.202663</t>
-  </si>
-  <si>
-    <t>25.02.202664</t>
-  </si>
-  <si>
-    <t>25.02.202665</t>
-  </si>
-  <si>
-    <t>25.02.202666</t>
-  </si>
-  <si>
-    <t>25.02.202667</t>
-  </si>
-  <si>
-    <t>25.02.202668</t>
-  </si>
-  <si>
-    <t>25.02.202669</t>
-  </si>
-  <si>
-    <t>25.02.202670</t>
-  </si>
-  <si>
-    <t>25.02.202671</t>
-  </si>
-  <si>
-    <t>25.02.202672</t>
-  </si>
-  <si>
-    <t>25.02.202673</t>
-  </si>
-  <si>
-    <t>25.02.202674</t>
-  </si>
-  <si>
-    <t>25.02.202675</t>
-  </si>
-  <si>
-    <t>25.02.202676</t>
-  </si>
-  <si>
-    <t>25.02.202677</t>
-  </si>
-  <si>
-    <t>25.02.202678</t>
-  </si>
-  <si>
-    <t>25.02.202679</t>
-  </si>
-  <si>
-    <t>25.02.202680</t>
-  </si>
-  <si>
-    <t>25.02.202681</t>
-  </si>
-  <si>
-    <t>25.02.202682</t>
-  </si>
-  <si>
-    <t>25.02.202683</t>
-  </si>
-  <si>
-    <t>25.02.202684</t>
-  </si>
-  <si>
-    <t>25.02.202685</t>
-  </si>
-  <si>
-    <t>25.02.202686</t>
-  </si>
-  <si>
-    <t>25.02.202687</t>
-  </si>
-  <si>
-    <t>25.02.202688</t>
-  </si>
-  <si>
-    <t>25.02.202689</t>
-  </si>
-  <si>
-    <t>25.02.202690</t>
-  </si>
-  <si>
-    <t>25.02.202691</t>
-  </si>
-  <si>
-    <t>25.02.202692</t>
-  </si>
-  <si>
-    <t>25.02.202693</t>
-  </si>
-  <si>
-    <t>25.02.202694</t>
-  </si>
-  <si>
-    <t>25.02.202695</t>
-  </si>
-  <si>
-    <t>25.02.202696</t>
-  </si>
-  <si>
-    <t>26.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20262</t>
-  </si>
-  <si>
-    <t>26.02.20263</t>
-  </si>
-  <si>
-    <t>26.02.20264</t>
-  </si>
-  <si>
-    <t>26.02.20265</t>
-  </si>
-  <si>
-    <t>26.02.20266</t>
-  </si>
-  <si>
-    <t>26.02.20267</t>
-  </si>
-  <si>
-    <t>26.02.20268</t>
-  </si>
-  <si>
-    <t>26.02.20269</t>
-  </si>
-  <si>
-    <t>26.02.202610</t>
-  </si>
-  <si>
-    <t>26.02.202611</t>
-  </si>
-  <si>
-    <t>26.02.202612</t>
-  </si>
-  <si>
-    <t>26.02.202613</t>
-  </si>
-  <si>
-    <t>26.02.202614</t>
-  </si>
-  <si>
-    <t>26.02.202615</t>
-  </si>
-  <si>
-    <t>26.02.202616</t>
-  </si>
-  <si>
-    <t>26.02.202617</t>
-  </si>
-  <si>
-    <t>26.02.202618</t>
-  </si>
-  <si>
-    <t>26.02.202619</t>
-  </si>
-  <si>
-    <t>26.02.202620</t>
-  </si>
-  <si>
-    <t>26.02.202621</t>
-  </si>
-  <si>
-    <t>26.02.202622</t>
-  </si>
-  <si>
-    <t>26.02.202623</t>
-  </si>
-  <si>
-    <t>26.02.202624</t>
-  </si>
-  <si>
-    <t>26.02.202625</t>
-  </si>
-  <si>
-    <t>26.02.202626</t>
-  </si>
-  <si>
-    <t>26.02.202627</t>
-  </si>
-  <si>
-    <t>26.02.202628</t>
-  </si>
-  <si>
-    <t>26.02.202629</t>
-  </si>
-  <si>
-    <t>26.02.202630</t>
-  </si>
-  <si>
-    <t>26.02.202631</t>
-  </si>
-  <si>
-    <t>26.02.202632</t>
-  </si>
-  <si>
-    <t>26.02.202633</t>
-  </si>
-  <si>
-    <t>26.02.202634</t>
-  </si>
-  <si>
-    <t>26.02.202635</t>
-  </si>
-  <si>
-    <t>26.02.202636</t>
-  </si>
-  <si>
-    <t>26.02.202637</t>
-  </si>
-  <si>
-    <t>26.02.202638</t>
-  </si>
-  <si>
-    <t>26.02.202639</t>
-  </si>
-  <si>
-    <t>26.02.202640</t>
-  </si>
-  <si>
-    <t>26.02.202641</t>
-  </si>
-  <si>
-    <t>26.02.202642</t>
-  </si>
-  <si>
-    <t>26.02.202643</t>
-  </si>
-  <si>
-    <t>26.02.202644</t>
-  </si>
-  <si>
-    <t>26.02.202645</t>
-  </si>
-  <si>
-    <t>26.02.202646</t>
-  </si>
-  <si>
-    <t>26.02.202647</t>
-  </si>
-  <si>
-    <t>26.02.202648</t>
-  </si>
-  <si>
-    <t>26.02.202649</t>
-  </si>
-  <si>
-    <t>26.02.202650</t>
-  </si>
-  <si>
-    <t>26.02.202651</t>
-  </si>
-  <si>
-    <t>26.02.202652</t>
-  </si>
-  <si>
-    <t>26.02.202653</t>
-  </si>
-  <si>
-    <t>26.02.202654</t>
-  </si>
-  <si>
-    <t>26.02.202655</t>
-  </si>
-  <si>
-    <t>26.02.202656</t>
-  </si>
-  <si>
-    <t>26.02.202657</t>
-  </si>
-  <si>
-    <t>26.02.202658</t>
-  </si>
-  <si>
-    <t>26.02.202659</t>
-  </si>
-  <si>
-    <t>26.02.202660</t>
-  </si>
-  <si>
-    <t>26.02.202661</t>
-  </si>
-  <si>
-    <t>26.02.202662</t>
-  </si>
-  <si>
-    <t>26.02.202663</t>
-  </si>
-  <si>
-    <t>26.02.202664</t>
-  </si>
-  <si>
-    <t>26.02.202665</t>
-  </si>
-  <si>
-    <t>26.02.202666</t>
-  </si>
-  <si>
-    <t>26.02.202667</t>
-  </si>
-  <si>
-    <t>26.02.202668</t>
-  </si>
-  <si>
-    <t>26.02.202669</t>
-  </si>
-  <si>
-    <t>26.02.202670</t>
-  </si>
-  <si>
-    <t>26.02.202671</t>
-  </si>
-  <si>
-    <t>26.02.202672</t>
-  </si>
-  <si>
-    <t>26.02.202673</t>
-  </si>
-  <si>
-    <t>26.02.202674</t>
-  </si>
-  <si>
-    <t>26.02.202675</t>
-  </si>
-  <si>
-    <t>26.02.202676</t>
-  </si>
-  <si>
-    <t>26.02.202677</t>
-  </si>
-  <si>
-    <t>26.02.202678</t>
-  </si>
-  <si>
-    <t>26.02.202679</t>
-  </si>
-  <si>
-    <t>26.02.202680</t>
-  </si>
-  <si>
-    <t>26.02.202681</t>
-  </si>
-  <si>
-    <t>26.02.202682</t>
-  </si>
-  <si>
-    <t>26.02.202683</t>
-  </si>
-  <si>
-    <t>26.02.202684</t>
-  </si>
-  <si>
-    <t>26.02.202685</t>
-  </si>
-  <si>
-    <t>26.02.202686</t>
-  </si>
-  <si>
-    <t>26.02.202687</t>
-  </si>
-  <si>
-    <t>26.02.202688</t>
-  </si>
-  <si>
-    <t>26.02.202689</t>
-  </si>
-  <si>
-    <t>26.02.202690</t>
-  </si>
-  <si>
-    <t>26.02.202691</t>
-  </si>
-  <si>
-    <t>26.02.202692</t>
-  </si>
-  <si>
-    <t>26.02.202693</t>
-  </si>
-  <si>
-    <t>26.02.202694</t>
-  </si>
-  <si>
-    <t>26.02.202695</t>
-  </si>
-  <si>
-    <t>26.02.202696</t>
+    <t>12.03.20261</t>
+  </si>
+  <si>
+    <t>12.03.20262</t>
+  </si>
+  <si>
+    <t>12.03.20263</t>
+  </si>
+  <si>
+    <t>12.03.20264</t>
+  </si>
+  <si>
+    <t>12.03.20265</t>
+  </si>
+  <si>
+    <t>12.03.20266</t>
+  </si>
+  <si>
+    <t>12.03.20267</t>
+  </si>
+  <si>
+    <t>12.03.20268</t>
+  </si>
+  <si>
+    <t>12.03.20269</t>
+  </si>
+  <si>
+    <t>12.03.202610</t>
+  </si>
+  <si>
+    <t>12.03.202611</t>
+  </si>
+  <si>
+    <t>12.03.202612</t>
+  </si>
+  <si>
+    <t>12.03.202613</t>
+  </si>
+  <si>
+    <t>12.03.202614</t>
+  </si>
+  <si>
+    <t>12.03.202615</t>
+  </si>
+  <si>
+    <t>12.03.202616</t>
+  </si>
+  <si>
+    <t>12.03.202617</t>
+  </si>
+  <si>
+    <t>12.03.202618</t>
+  </si>
+  <si>
+    <t>12.03.202619</t>
+  </si>
+  <si>
+    <t>12.03.202620</t>
+  </si>
+  <si>
+    <t>12.03.202621</t>
+  </si>
+  <si>
+    <t>12.03.202622</t>
+  </si>
+  <si>
+    <t>12.03.202623</t>
+  </si>
+  <si>
+    <t>12.03.202624</t>
+  </si>
+  <si>
+    <t>12.03.202625</t>
+  </si>
+  <si>
+    <t>12.03.202626</t>
+  </si>
+  <si>
+    <t>12.03.202627</t>
+  </si>
+  <si>
+    <t>12.03.202628</t>
+  </si>
+  <si>
+    <t>12.03.202629</t>
+  </si>
+  <si>
+    <t>12.03.202630</t>
+  </si>
+  <si>
+    <t>12.03.202631</t>
+  </si>
+  <si>
+    <t>12.03.202632</t>
+  </si>
+  <si>
+    <t>12.03.202633</t>
+  </si>
+  <si>
+    <t>12.03.202634</t>
+  </si>
+  <si>
+    <t>12.03.202635</t>
+  </si>
+  <si>
+    <t>12.03.202636</t>
+  </si>
+  <si>
+    <t>12.03.202637</t>
+  </si>
+  <si>
+    <t>12.03.202638</t>
+  </si>
+  <si>
+    <t>12.03.202639</t>
+  </si>
+  <si>
+    <t>12.03.202640</t>
+  </si>
+  <si>
+    <t>12.03.202641</t>
+  </si>
+  <si>
+    <t>12.03.202642</t>
+  </si>
+  <si>
+    <t>12.03.202643</t>
+  </si>
+  <si>
+    <t>12.03.202644</t>
+  </si>
+  <si>
+    <t>12.03.202645</t>
+  </si>
+  <si>
+    <t>12.03.202646</t>
+  </si>
+  <si>
+    <t>12.03.202647</t>
+  </si>
+  <si>
+    <t>12.03.202648</t>
+  </si>
+  <si>
+    <t>12.03.202649</t>
+  </si>
+  <si>
+    <t>12.03.202650</t>
+  </si>
+  <si>
+    <t>12.03.202651</t>
+  </si>
+  <si>
+    <t>12.03.202652</t>
+  </si>
+  <si>
+    <t>12.03.202653</t>
+  </si>
+  <si>
+    <t>12.03.202654</t>
+  </si>
+  <si>
+    <t>12.03.202655</t>
+  </si>
+  <si>
+    <t>12.03.202656</t>
+  </si>
+  <si>
+    <t>12.03.202657</t>
+  </si>
+  <si>
+    <t>12.03.202658</t>
+  </si>
+  <si>
+    <t>12.03.202659</t>
+  </si>
+  <si>
+    <t>12.03.202660</t>
+  </si>
+  <si>
+    <t>12.03.202661</t>
+  </si>
+  <si>
+    <t>12.03.202662</t>
+  </si>
+  <si>
+    <t>12.03.202663</t>
+  </si>
+  <si>
+    <t>12.03.202664</t>
+  </si>
+  <si>
+    <t>12.03.202665</t>
+  </si>
+  <si>
+    <t>12.03.202666</t>
+  </si>
+  <si>
+    <t>12.03.202667</t>
+  </si>
+  <si>
+    <t>12.03.202668</t>
+  </si>
+  <si>
+    <t>12.03.202669</t>
+  </si>
+  <si>
+    <t>12.03.202670</t>
+  </si>
+  <si>
+    <t>12.03.202671</t>
+  </si>
+  <si>
+    <t>12.03.202672</t>
+  </si>
+  <si>
+    <t>12.03.202673</t>
+  </si>
+  <si>
+    <t>12.03.202674</t>
+  </si>
+  <si>
+    <t>12.03.202675</t>
+  </si>
+  <si>
+    <t>12.03.202676</t>
+  </si>
+  <si>
+    <t>12.03.202677</t>
+  </si>
+  <si>
+    <t>12.03.202678</t>
+  </si>
+  <si>
+    <t>12.03.202679</t>
+  </si>
+  <si>
+    <t>12.03.202680</t>
+  </si>
+  <si>
+    <t>12.03.202681</t>
+  </si>
+  <si>
+    <t>12.03.202682</t>
+  </si>
+  <si>
+    <t>12.03.202683</t>
+  </si>
+  <si>
+    <t>12.03.202684</t>
+  </si>
+  <si>
+    <t>12.03.202685</t>
+  </si>
+  <si>
+    <t>12.03.202686</t>
+  </si>
+  <si>
+    <t>12.03.202687</t>
+  </si>
+  <si>
+    <t>12.03.202688</t>
+  </si>
+  <si>
+    <t>12.03.202689</t>
+  </si>
+  <si>
+    <t>12.03.202690</t>
+  </si>
+  <si>
+    <t>12.03.202691</t>
+  </si>
+  <si>
+    <t>12.03.202692</t>
+  </si>
+  <si>
+    <t>12.03.202693</t>
+  </si>
+  <si>
+    <t>12.03.202694</t>
+  </si>
+  <si>
+    <t>12.03.202695</t>
+  </si>
+  <si>
+    <t>12.03.202696</t>
+  </si>
+  <si>
+    <t>13.03.20261</t>
+  </si>
+  <si>
+    <t>13.03.20262</t>
+  </si>
+  <si>
+    <t>13.03.20263</t>
+  </si>
+  <si>
+    <t>13.03.20264</t>
+  </si>
+  <si>
+    <t>13.03.20265</t>
+  </si>
+  <si>
+    <t>13.03.20266</t>
+  </si>
+  <si>
+    <t>13.03.20267</t>
+  </si>
+  <si>
+    <t>13.03.20268</t>
+  </si>
+  <si>
+    <t>13.03.20269</t>
+  </si>
+  <si>
+    <t>13.03.202610</t>
+  </si>
+  <si>
+    <t>13.03.202611</t>
+  </si>
+  <si>
+    <t>13.03.202612</t>
+  </si>
+  <si>
+    <t>13.03.202613</t>
+  </si>
+  <si>
+    <t>13.03.202614</t>
+  </si>
+  <si>
+    <t>13.03.202615</t>
+  </si>
+  <si>
+    <t>13.03.202616</t>
+  </si>
+  <si>
+    <t>13.03.202617</t>
+  </si>
+  <si>
+    <t>13.03.202618</t>
+  </si>
+  <si>
+    <t>13.03.202619</t>
+  </si>
+  <si>
+    <t>13.03.202620</t>
+  </si>
+  <si>
+    <t>13.03.202621</t>
+  </si>
+  <si>
+    <t>13.03.202622</t>
+  </si>
+  <si>
+    <t>13.03.202623</t>
+  </si>
+  <si>
+    <t>13.03.202624</t>
+  </si>
+  <si>
+    <t>13.03.202625</t>
+  </si>
+  <si>
+    <t>13.03.202626</t>
+  </si>
+  <si>
+    <t>13.03.202627</t>
+  </si>
+  <si>
+    <t>13.03.202628</t>
+  </si>
+  <si>
+    <t>13.03.202629</t>
+  </si>
+  <si>
+    <t>13.03.202630</t>
+  </si>
+  <si>
+    <t>13.03.202631</t>
+  </si>
+  <si>
+    <t>13.03.202632</t>
+  </si>
+  <si>
+    <t>13.03.202633</t>
+  </si>
+  <si>
+    <t>13.03.202634</t>
+  </si>
+  <si>
+    <t>13.03.202635</t>
+  </si>
+  <si>
+    <t>13.03.202636</t>
+  </si>
+  <si>
+    <t>13.03.202637</t>
+  </si>
+  <si>
+    <t>13.03.202638</t>
+  </si>
+  <si>
+    <t>13.03.202639</t>
+  </si>
+  <si>
+    <t>13.03.202640</t>
+  </si>
+  <si>
+    <t>13.03.202641</t>
+  </si>
+  <si>
+    <t>13.03.202642</t>
+  </si>
+  <si>
+    <t>13.03.202643</t>
+  </si>
+  <si>
+    <t>13.03.202644</t>
+  </si>
+  <si>
+    <t>13.03.202645</t>
+  </si>
+  <si>
+    <t>13.03.202646</t>
+  </si>
+  <si>
+    <t>13.03.202647</t>
+  </si>
+  <si>
+    <t>13.03.202648</t>
+  </si>
+  <si>
+    <t>13.03.202649</t>
+  </si>
+  <si>
+    <t>13.03.202650</t>
+  </si>
+  <si>
+    <t>13.03.202651</t>
+  </si>
+  <si>
+    <t>13.03.202652</t>
+  </si>
+  <si>
+    <t>13.03.202653</t>
+  </si>
+  <si>
+    <t>13.03.202654</t>
+  </si>
+  <si>
+    <t>13.03.202655</t>
+  </si>
+  <si>
+    <t>13.03.202656</t>
+  </si>
+  <si>
+    <t>13.03.202657</t>
+  </si>
+  <si>
+    <t>13.03.202658</t>
+  </si>
+  <si>
+    <t>13.03.202659</t>
+  </si>
+  <si>
+    <t>13.03.202660</t>
+  </si>
+  <si>
+    <t>13.03.202661</t>
+  </si>
+  <si>
+    <t>13.03.202662</t>
+  </si>
+  <si>
+    <t>13.03.202663</t>
+  </si>
+  <si>
+    <t>13.03.202664</t>
+  </si>
+  <si>
+    <t>13.03.202665</t>
+  </si>
+  <si>
+    <t>13.03.202666</t>
+  </si>
+  <si>
+    <t>13.03.202667</t>
+  </si>
+  <si>
+    <t>13.03.202668</t>
+  </si>
+  <si>
+    <t>13.03.202669</t>
+  </si>
+  <si>
+    <t>13.03.202670</t>
+  </si>
+  <si>
+    <t>13.03.202671</t>
+  </si>
+  <si>
+    <t>13.03.202672</t>
+  </si>
+  <si>
+    <t>13.03.202673</t>
+  </si>
+  <si>
+    <t>13.03.202674</t>
+  </si>
+  <si>
+    <t>13.03.202675</t>
+  </si>
+  <si>
+    <t>13.03.202676</t>
+  </si>
+  <si>
+    <t>13.03.202677</t>
+  </si>
+  <si>
+    <t>13.03.202678</t>
+  </si>
+  <si>
+    <t>13.03.202679</t>
+  </si>
+  <si>
+    <t>13.03.202680</t>
+  </si>
+  <si>
+    <t>13.03.202681</t>
+  </si>
+  <si>
+    <t>13.03.202682</t>
+  </si>
+  <si>
+    <t>13.03.202683</t>
+  </si>
+  <si>
+    <t>13.03.202684</t>
+  </si>
+  <si>
+    <t>13.03.202685</t>
+  </si>
+  <si>
+    <t>13.03.202686</t>
+  </si>
+  <si>
+    <t>13.03.202687</t>
+  </si>
+  <si>
+    <t>13.03.202688</t>
+  </si>
+  <si>
+    <t>13.03.202689</t>
+  </si>
+  <si>
+    <t>13.03.202690</t>
+  </si>
+  <si>
+    <t>13.03.202691</t>
+  </si>
+  <si>
+    <t>13.03.202692</t>
+  </si>
+  <si>
+    <t>13.03.202693</t>
+  </si>
+  <si>
+    <t>13.03.202694</t>
+  </si>
+  <si>
+    <t>13.03.202695</t>
+  </si>
+  <si>
+    <t>13.03.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="B2">
-        <v>2559.989</v>
+        <v>425.812</v>
       </c>
       <c r="C2">
-        <v>2530</v>
+        <v>541</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46078.01041666666</v>
+        <v>46093.01041666666</v>
       </c>
       <c r="B3">
-        <v>2570.255</v>
+        <v>414.782</v>
       </c>
       <c r="C3">
-        <v>2360</v>
+        <v>527</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46078.02083333334</v>
+        <v>46093.02083333334</v>
       </c>
       <c r="B4">
-        <v>2573.55</v>
+        <v>399.762</v>
       </c>
       <c r="C4">
-        <v>2468</v>
+        <v>502</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46078.03125</v>
+        <v>46093.03125</v>
       </c>
       <c r="B5">
-        <v>2577.071</v>
+        <v>378.93</v>
       </c>
       <c r="C5">
-        <v>2620</v>
+        <v>463</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46078.04166666666</v>
+        <v>46093.04166666666</v>
       </c>
       <c r="B6">
-        <v>2525.663</v>
+        <v>342.091</v>
       </c>
       <c r="C6">
-        <v>2624</v>
+        <v>418</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46078.05208333334</v>
+        <v>46093.05208333334</v>
       </c>
       <c r="B7">
-        <v>2526.277</v>
+        <v>329.494</v>
       </c>
       <c r="C7">
-        <v>2581</v>
+        <v>369</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46078.0625</v>
+        <v>46093.0625</v>
       </c>
       <c r="B8">
-        <v>2521.214</v>
+        <v>316.907</v>
       </c>
       <c r="C8">
-        <v>2548</v>
+        <v>341</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46078.07291666666</v>
+        <v>46093.07291666666</v>
       </c>
       <c r="B9">
-        <v>2520.407</v>
+        <v>306.728</v>
       </c>
       <c r="C9">
-        <v>2549</v>
+        <v>305</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46078.08333333334</v>
+        <v>46093.08333333334</v>
       </c>
       <c r="B10">
-        <v>2478.733</v>
+        <v>282.994</v>
       </c>
       <c r="C10">
-        <v>2550</v>
+        <v>278</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46078.09375</v>
+        <v>46093.09375</v>
       </c>
       <c r="B11">
-        <v>2469.01</v>
+        <v>278.516</v>
       </c>
       <c r="C11">
-        <v>2528</v>
+        <v>246</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46078.10416666666</v>
+        <v>46093.10416666666</v>
       </c>
       <c r="B12">
-        <v>2467.733</v>
+        <v>266.078</v>
       </c>
       <c r="C12">
-        <v>2502</v>
+        <v>228</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46078.11458333334</v>
+        <v>46093.11458333334</v>
       </c>
       <c r="B13">
-        <v>2453.364</v>
+        <v>269.85</v>
       </c>
       <c r="C13">
-        <v>2472</v>
+        <v>214</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46078.125</v>
+        <v>46093.125</v>
       </c>
       <c r="B14">
-        <v>2427.944</v>
+        <v>254.524</v>
       </c>
       <c r="C14">
-        <v>2420</v>
+        <v>189</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46078.13541666666</v>
+        <v>46093.13541666666</v>
       </c>
       <c r="B15">
-        <v>2405.511</v>
+        <v>229.736</v>
       </c>
       <c r="C15">
-        <v>2395</v>
+        <v>162</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46078.14583333334</v>
+        <v>46093.14583333334</v>
       </c>
       <c r="B16">
-        <v>2388.579</v>
+        <v>224.866</v>
       </c>
       <c r="C16">
-        <v>2357</v>
+        <v>139</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46078.15625</v>
+        <v>46093.15625</v>
       </c>
       <c r="B17">
-        <v>2367.03</v>
+        <v>224.325</v>
       </c>
       <c r="C17">
-        <v>2365</v>
+        <v>114</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46078.16666666666</v>
+        <v>46093.16666666666</v>
       </c>
       <c r="B18">
-        <v>2342.792</v>
+        <v>217.723</v>
       </c>
       <c r="C18">
-        <v>2360</v>
+        <v>99</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46078.17708333334</v>
+        <v>46093.17708333334</v>
       </c>
       <c r="B19">
-        <v>2313.686</v>
+        <v>218.869</v>
       </c>
       <c r="C19">
-        <v>2323</v>
+        <v>87</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46078.1875</v>
+        <v>46093.1875</v>
       </c>
       <c r="B20">
-        <v>2288.143</v>
+        <v>218.68</v>
       </c>
       <c r="C20">
-        <v>2306</v>
+        <v>82</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46078.19791666666</v>
+        <v>46093.19791666666</v>
       </c>
       <c r="B21">
-        <v>2256.855</v>
+        <v>219.164</v>
       </c>
       <c r="C21">
-        <v>2309</v>
+        <v>78</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46078.20833333334</v>
+        <v>46093.20833333334</v>
       </c>
       <c r="B22">
-        <v>2173.792</v>
+        <v>221.528</v>
       </c>
       <c r="C22">
-        <v>2268</v>
+        <v>81</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46078.21875</v>
+        <v>46093.21875</v>
       </c>
       <c r="B23">
-        <v>2160.922</v>
+        <v>225.839</v>
       </c>
       <c r="C23">
-        <v>2240</v>
+        <v>90</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46078.22916666666</v>
+        <v>46093.22916666666</v>
       </c>
       <c r="B24">
-        <v>2130.323</v>
+        <v>224.354</v>
       </c>
       <c r="C24">
-        <v>2186</v>
+        <v>101</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46078.23958333334</v>
+        <v>46093.23958333334</v>
       </c>
       <c r="B25">
-        <v>2105.778</v>
+        <v>229.055</v>
       </c>
       <c r="C25">
-        <v>2092</v>
+        <v>119</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46078.25</v>
+        <v>46093.25</v>
       </c>
       <c r="B26">
-        <v>1982.5</v>
+        <v>233.619</v>
       </c>
       <c r="C26">
-        <v>1957</v>
+        <v>135</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46078.26041666666</v>
+        <v>46093.26041666666</v>
       </c>
       <c r="B27">
-        <v>1942.075</v>
+        <v>234.241</v>
       </c>
       <c r="C27">
-        <v>1896</v>
+        <v>150</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46078.27083333334</v>
+        <v>46093.27083333334</v>
       </c>
       <c r="B28">
-        <v>1916.175</v>
+        <v>238.861</v>
       </c>
       <c r="C28">
-        <v>1843</v>
+        <v>182</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46078.28125</v>
+        <v>46093.28125</v>
       </c>
       <c r="B29">
-        <v>1874.84</v>
+        <v>238.009</v>
       </c>
       <c r="C29">
-        <v>1719</v>
+        <v>205</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46078.29166666666</v>
+        <v>46093.29166666666</v>
       </c>
       <c r="B30">
-        <v>1848.737</v>
+        <v>259.396</v>
       </c>
       <c r="C30">
-        <v>1615</v>
+        <v>208</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46078.30208333334</v>
+        <v>46093.30208333334</v>
       </c>
       <c r="B31">
-        <v>1821.799</v>
+        <v>250.363</v>
       </c>
       <c r="C31">
-        <v>1462</v>
+        <v>212</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46078.3125</v>
+        <v>46093.3125</v>
       </c>
       <c r="B32">
-        <v>1780.405</v>
+        <v>245.226</v>
       </c>
       <c r="C32">
-        <v>1464</v>
+        <v>200</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46078.32291666666</v>
+        <v>46093.32291666666</v>
       </c>
       <c r="B33">
-        <v>1753.623</v>
+        <v>237.697</v>
       </c>
       <c r="C33">
-        <v>1383</v>
+        <v>193</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46078.33333333334</v>
+        <v>46093.33333333334</v>
       </c>
       <c r="B34">
-        <v>1781.775</v>
+        <v>274.314</v>
       </c>
       <c r="C34">
-        <v>1294</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46078.34375</v>
+        <v>46093.34375</v>
       </c>
       <c r="B35">
-        <v>1770.524</v>
+        <v>275.794</v>
       </c>
       <c r="C35">
-        <v>1287</v>
+        <v>187</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46078.35416666666</v>
+        <v>46093.35416666666</v>
       </c>
       <c r="B36">
-        <v>1753.791</v>
+        <v>277.914</v>
       </c>
       <c r="C36">
-        <v>1330</v>
+        <v>185</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46078.36458333334</v>
+        <v>46093.36458333334</v>
       </c>
       <c r="B37">
-        <v>1735.029</v>
+        <v>280.41</v>
       </c>
       <c r="C37">
-        <v>1255</v>
+        <v>178</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46078.375</v>
+        <v>46093.375</v>
       </c>
       <c r="B38">
-        <v>1752.146</v>
+        <v>296.944</v>
       </c>
       <c r="C38">
-        <v>1259</v>
+        <v>188</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46078.38541666666</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="B39">
-        <v>1723.509</v>
+        <v>290.656</v>
       </c>
       <c r="C39">
-        <v>1427</v>
+        <v>186</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46078.39583333334</v>
+        <v>46093.39583333334</v>
       </c>
       <c r="B40">
-        <v>1698.504</v>
+        <v>287.728</v>
       </c>
       <c r="C40">
-        <v>1488</v>
+        <v>184</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46078.40625</v>
+        <v>46093.40625</v>
       </c>
       <c r="B41">
-        <v>1671.828</v>
+        <v>281.864</v>
       </c>
       <c r="C41">
-        <v>1468</v>
+        <v>183</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46078.41666666666</v>
+        <v>46093.41666666666</v>
       </c>
       <c r="B42">
-        <v>1647.005</v>
+        <v>279.936</v>
       </c>
       <c r="C42">
-        <v>1521</v>
+        <v>184</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46078.42708333334</v>
+        <v>46093.42708333334</v>
       </c>
       <c r="B43">
-        <v>1608.865</v>
+        <v>272.327</v>
       </c>
       <c r="C43">
-        <v>1508</v>
+        <v>194</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46078.4375</v>
+        <v>46093.4375</v>
       </c>
       <c r="B44">
-        <v>1567.338</v>
+        <v>265.089</v>
       </c>
       <c r="C44">
-        <v>1450</v>
+        <v>200</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46078.44791666666</v>
+        <v>46093.44791666666</v>
       </c>
       <c r="B45">
-        <v>1527.335</v>
+        <v>258.727</v>
       </c>
       <c r="C45">
-        <v>1356</v>
+        <v>179</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46078.45833333334</v>
+        <v>46093.45833333334</v>
       </c>
       <c r="B46">
-        <v>1499.746</v>
+        <v>249.181</v>
       </c>
       <c r="C46">
-        <v>1269</v>
+        <v>164</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46078.46875</v>
+        <v>46093.46875</v>
       </c>
       <c r="B47">
-        <v>1496.729</v>
+        <v>242.288</v>
       </c>
       <c r="C47">
-        <v>1252</v>
+        <v>162</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46078.47916666666</v>
+        <v>46093.47916666666</v>
       </c>
       <c r="B48">
-        <v>1495.146</v>
+        <v>235.575</v>
       </c>
       <c r="C48">
-        <v>1156</v>
+        <v>152</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46078.48958333334</v>
+        <v>46093.48958333334</v>
       </c>
       <c r="B49">
-        <v>1494.055</v>
+        <v>228.987</v>
       </c>
       <c r="C49">
-        <v>1033</v>
+        <v>151</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46078.5</v>
+        <v>46093.5</v>
       </c>
       <c r="B50">
-        <v>1479.001</v>
+        <v>203.817</v>
       </c>
       <c r="C50">
-        <v>974</v>
+        <v>149</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46078.51041666666</v>
+        <v>46093.51041666666</v>
       </c>
       <c r="B51">
-        <v>1453.961</v>
+        <v>199.679</v>
       </c>
       <c r="C51">
-        <v>947</v>
+        <v>148</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46078.52083333334</v>
+        <v>46093.52083333334</v>
       </c>
       <c r="B52">
-        <v>1430.399</v>
+        <v>195.546</v>
       </c>
       <c r="C52">
-        <v>943</v>
+        <v>139</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46078.53125</v>
+        <v>46093.53125</v>
       </c>
       <c r="B53">
-        <v>1403.685</v>
+        <v>191.913</v>
       </c>
       <c r="C53">
-        <v>978</v>
+        <v>135</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46078.54166666666</v>
+        <v>46093.54166666666</v>
       </c>
       <c r="B54">
-        <v>1356.648</v>
+        <v>190.95</v>
       </c>
       <c r="C54">
-        <v>955</v>
+        <v>132</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46078.55208333334</v>
+        <v>46093.55208333334</v>
       </c>
       <c r="B55">
-        <v>1312.7</v>
+        <v>190.57</v>
       </c>
       <c r="C55">
-        <v>896</v>
+        <v>119</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46078.5625</v>
+        <v>46093.5625</v>
       </c>
       <c r="B56">
-        <v>1267.962</v>
+        <v>189.996</v>
       </c>
       <c r="C56">
-        <v>853</v>
+        <v>102</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46078.57291666666</v>
+        <v>46093.57291666666</v>
       </c>
       <c r="B57">
-        <v>1224.012</v>
+        <v>189.23</v>
       </c>
       <c r="C57">
-        <v>814</v>
+        <v>93</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46078.58333333334</v>
+        <v>46093.58333333334</v>
       </c>
       <c r="B58">
-        <v>1185.418</v>
+        <v>181.969</v>
       </c>
       <c r="C58">
-        <v>720</v>
+        <v>85</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46078.59375</v>
+        <v>46093.59375</v>
       </c>
       <c r="B59">
-        <v>1140.119</v>
+        <v>182.532</v>
       </c>
       <c r="C59">
-        <v>624</v>
+        <v>77</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46078.60416666666</v>
+        <v>46093.60416666666</v>
       </c>
       <c r="B60">
-        <v>1096.144</v>
+        <v>182.525</v>
       </c>
       <c r="C60">
-        <v>567</v>
+        <v>79</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46078.61458333334</v>
+        <v>46093.61458333334</v>
       </c>
       <c r="B61">
-        <v>1051.368</v>
+        <v>182.948</v>
       </c>
       <c r="C61">
-        <v>528</v>
+        <v>76</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46078.625</v>
+        <v>46093.625</v>
       </c>
       <c r="B62">
-        <v>975.427</v>
+        <v>165.061</v>
       </c>
       <c r="C62">
-        <v>486</v>
+        <v>73</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46078.63541666666</v>
+        <v>46093.63541666666</v>
       </c>
       <c r="B63">
-        <v>898.215</v>
+        <v>165.209</v>
       </c>
       <c r="C63">
-        <v>421</v>
+        <v>67</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46078.64583333334</v>
+        <v>46093.64583333334</v>
       </c>
       <c r="B64">
-        <v>819.3869999999999</v>
+        <v>165.938</v>
       </c>
       <c r="C64">
-        <v>365</v>
+        <v>57</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46078.65625</v>
+        <v>46093.65625</v>
       </c>
       <c r="B65">
-        <v>742.096</v>
+        <v>167.021</v>
       </c>
       <c r="C65">
-        <v>308</v>
+        <v>48</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46078.66666666666</v>
+        <v>46093.66666666666</v>
       </c>
       <c r="B66">
-        <v>644.263</v>
+        <v>166.775</v>
       </c>
       <c r="C66">
-        <v>272</v>
+        <v>39</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46078.67708333334</v>
+        <v>46093.67708333334</v>
       </c>
       <c r="B67">
-        <v>620.254</v>
+        <v>174.191</v>
       </c>
       <c r="C67">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46078.6875</v>
+        <v>46093.6875</v>
       </c>
       <c r="B68">
-        <v>598.1799999999999</v>
+        <v>180.916</v>
       </c>
       <c r="C68">
-        <v>256</v>
+        <v>37</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46078.69791666666</v>
+        <v>46093.69791666666</v>
       </c>
       <c r="B69">
-        <v>577.378</v>
+        <v>212.665</v>
       </c>
       <c r="C69">
-        <v>233</v>
+        <v>43</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46078.70833333334</v>
+        <v>46093.70833333334</v>
       </c>
       <c r="B70">
-        <v>570.377</v>
+        <v>198.631</v>
       </c>
       <c r="C70">
-        <v>203</v>
+        <v>51</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46078.71875</v>
+        <v>46093.71875</v>
       </c>
       <c r="B71">
-        <v>587.491</v>
+        <v>203.635</v>
       </c>
       <c r="C71">
-        <v>185</v>
+        <v>57</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46078.72916666666</v>
+        <v>46093.72916666666</v>
       </c>
       <c r="B72">
-        <v>606.092</v>
+        <v>240.822</v>
       </c>
       <c r="C72">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46078.73958333334</v>
+        <v>46093.73958333334</v>
       </c>
       <c r="B73">
-        <v>624.6849999999999</v>
+        <v>247.048</v>
       </c>
       <c r="C73">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46078.75</v>
+        <v>46093.75</v>
       </c>
       <c r="B74">
-        <v>650.668</v>
+        <v>210.878</v>
       </c>
       <c r="C74">
-        <v>167</v>
+        <v>64</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46078.76041666666</v>
+        <v>46093.76041666666</v>
       </c>
       <c r="B75">
-        <v>675.902</v>
+        <v>207.668</v>
       </c>
       <c r="C75">
-        <v>208</v>
+        <v>62</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46078.77083333334</v>
+        <v>46093.77083333334</v>
       </c>
       <c r="B76">
-        <v>699.147</v>
+        <v>236.442</v>
       </c>
       <c r="C76">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46078.78125</v>
+        <v>46093.78125</v>
       </c>
       <c r="B77">
-        <v>727.533</v>
+        <v>233.698</v>
       </c>
       <c r="C77">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46078.79166666666</v>
+        <v>46093.79166666666</v>
       </c>
       <c r="B78">
-        <v>769.095</v>
+        <v>195.701</v>
       </c>
       <c r="C78">
-        <v>269</v>
+        <v>90</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46078.80208333334</v>
+        <v>46093.80208333334</v>
       </c>
       <c r="B79">
-        <v>792.189</v>
+        <v>188.344</v>
       </c>
       <c r="C79">
-        <v>292</v>
+        <v>99</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46078.8125</v>
+        <v>46093.8125</v>
       </c>
       <c r="B80">
-        <v>814.557</v>
+        <v>181.311</v>
       </c>
       <c r="C80">
-        <v>325</v>
+        <v>102</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46078.82291666666</v>
+        <v>46093.82291666666</v>
       </c>
       <c r="B81">
-        <v>836.194</v>
+        <v>174.047</v>
       </c>
       <c r="C81">
-        <v>375</v>
+        <v>101</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46078.83333333334</v>
+        <v>46093.83333333334</v>
       </c>
       <c r="B82">
-        <v>952.164</v>
+        <v>170.446</v>
       </c>
       <c r="C82">
-        <v>362</v>
+        <v>108</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46078.84375</v>
+        <v>46093.84375</v>
       </c>
       <c r="B83">
-        <v>979.149</v>
+        <v>164.15</v>
       </c>
       <c r="C83">
-        <v>364</v>
+        <v>104</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46078.85416666666</v>
+        <v>46093.85416666666</v>
       </c>
       <c r="B84">
-        <v>1003.653</v>
+        <v>157.735</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46078.86458333334</v>
+        <v>46093.86458333334</v>
       </c>
       <c r="B85">
-        <v>1029.201</v>
+        <v>152.427</v>
       </c>
       <c r="C85">
-        <v>377</v>
+        <v>98</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46078.875</v>
+        <v>46093.875</v>
       </c>
       <c r="B86">
-        <v>1047.626</v>
+        <v>179.463</v>
       </c>
       <c r="C86">
-        <v>420</v>
+        <v>88</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46078.88541666666</v>
+        <v>46093.88541666666</v>
       </c>
       <c r="B87">
-        <v>1075.66</v>
+        <v>176.707</v>
       </c>
       <c r="C87">
-        <v>460</v>
+        <v>72</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46078.89583333334</v>
+        <v>46093.89583333334</v>
       </c>
       <c r="B88">
-        <v>1103.695</v>
+        <v>173.728</v>
       </c>
       <c r="C88">
-        <v>479</v>
+        <v>66</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46078.90625</v>
+        <v>46093.90625</v>
       </c>
       <c r="B89">
-        <v>1132.85</v>
+        <v>140.25</v>
       </c>
       <c r="C89">
-        <v>526</v>
+        <v>60</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46078.91666666666</v>
+        <v>46093.91666666666</v>
       </c>
       <c r="B90">
-        <v>1163.313</v>
+        <v>138.947</v>
       </c>
       <c r="C90">
-        <v>589</v>
+        <v>55</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46078.92708333334</v>
+        <v>46093.92708333334</v>
       </c>
       <c r="B91">
-        <v>1192.835</v>
+        <v>138.984</v>
       </c>
       <c r="C91">
-        <v>664</v>
+        <v>53</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46078.9375</v>
+        <v>46093.9375</v>
       </c>
       <c r="B92">
-        <v>1220.652</v>
+        <v>138.889</v>
       </c>
       <c r="C92">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46078.94791666666</v>
+        <v>46093.94791666666</v>
       </c>
       <c r="B93">
-        <v>1247.639</v>
+        <v>139.477</v>
       </c>
       <c r="C93">
-        <v>752</v>
+        <v>58</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
       <c r="B94">
-        <v>978.056</v>
+        <v>150.755</v>
       </c>
       <c r="C94">
-        <v>784</v>
+        <v>60</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
       <c r="B95">
-        <v>1002.797</v>
+        <v>126.042</v>
       </c>
       <c r="C95">
-        <v>819</v>
+        <v>55</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
       <c r="B96">
-        <v>1026.451</v>
+        <v>157.213</v>
       </c>
       <c r="C96">
-        <v>816</v>
+        <v>56</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
       <c r="B97">
-        <v>1022.815</v>
+        <v>133.878</v>
       </c>
       <c r="C97">
-        <v>853</v>
+        <v>61</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B98">
-        <v>920.524</v>
+        <v>182.436</v>
       </c>
       <c r="C98">
-        <v>856</v>
+        <v>69</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B99">
-        <v>931.064</v>
+        <v>186.989</v>
       </c>
       <c r="C99">
-        <v>853</v>
+        <v>81</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B100">
-        <v>945.496</v>
+        <v>190.398</v>
       </c>
       <c r="C100">
-        <v>866</v>
+        <v>94</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B101">
-        <v>949.593</v>
+        <v>193.212</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B102">
-        <v>970.5359999999999</v>
+        <v>204.769</v>
       </c>
       <c r="C102">
-        <v>833</v>
+        <v>135</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B103">
-        <v>997.542</v>
+        <v>209.053</v>
       </c>
       <c r="C103">
-        <v>812</v>
+        <v>159</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B104">
-        <v>1021.302</v>
+        <v>213.468</v>
       </c>
       <c r="C104">
-        <v>807</v>
+        <v>182</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B105">
-        <v>1046.905</v>
+        <v>218.152</v>
       </c>
       <c r="C105">
-        <v>816</v>
+        <v>206</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B106">
-        <v>1077.073</v>
+        <v>220.481</v>
       </c>
       <c r="C106">
-        <v>863</v>
+        <v>219</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B107">
-        <v>1101.532</v>
+        <v>245.32</v>
       </c>
       <c r="C107">
-        <v>882</v>
+        <v>249</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B108">
-        <v>1132.267</v>
+        <v>252.074</v>
       </c>
       <c r="C108">
-        <v>891</v>
+        <v>266</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B109">
-        <v>1156.886</v>
+        <v>259.715</v>
       </c>
       <c r="C109">
-        <v>924</v>
+        <v>291</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B110">
-        <v>1217.117</v>
+        <v>281.152</v>
       </c>
       <c r="C110">
-        <v>922</v>
+        <v>315</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B111">
-        <v>1240.529</v>
+        <v>292.399</v>
       </c>
       <c r="C111">
-        <v>974</v>
+        <v>337</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B112">
-        <v>1264.845</v>
+        <v>299.506</v>
       </c>
       <c r="C112">
-        <v>1024</v>
+        <v>346</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B113">
-        <v>1285.573</v>
+        <v>303.727</v>
       </c>
       <c r="C113">
-        <v>1084</v>
+        <v>351</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B114">
-        <v>1354.253</v>
+        <v>332.798</v>
       </c>
       <c r="C114">
-        <v>1135</v>
+        <v>361</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B115">
-        <v>1377.423</v>
+        <v>335.128</v>
       </c>
       <c r="C115">
-        <v>1183</v>
+        <v>368</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B116">
-        <v>1400.985</v>
+        <v>337.679</v>
       </c>
       <c r="C116">
-        <v>1181</v>
+        <v>383</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B117">
-        <v>1432.609</v>
+        <v>336.01</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B118">
-        <v>1502.359</v>
+        <v>353.783</v>
       </c>
       <c r="C118">
-        <v>1266</v>
+        <v>389</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B119">
-        <v>1541.065</v>
+        <v>365.636</v>
       </c>
       <c r="C119">
-        <v>1309</v>
+        <v>395</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B120">
-        <v>1588.608</v>
+        <v>367.822</v>
       </c>
       <c r="C120">
-        <v>1356</v>
+        <v>389</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B121">
-        <v>1623.904</v>
+        <v>372.627</v>
       </c>
       <c r="C121">
-        <v>1391</v>
+        <v>392</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B122">
-        <v>1640.748</v>
+        <v>350.281</v>
       </c>
       <c r="C122">
-        <v>1432</v>
+        <v>408</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B123">
-        <v>1661.487</v>
+        <v>353.634</v>
       </c>
       <c r="C123">
-        <v>1444</v>
+        <v>423</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B124">
-        <v>1686.489</v>
+        <v>352.326</v>
       </c>
       <c r="C124">
-        <v>1383</v>
+        <v>421</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B125">
-        <v>1707.676</v>
+        <v>349</v>
       </c>
       <c r="C125">
-        <v>1355</v>
+        <v>425</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B126">
-        <v>1714.817</v>
+        <v>333.488</v>
       </c>
       <c r="C126">
-        <v>1365</v>
+        <v>391</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B127">
-        <v>1709.694</v>
+        <v>315.239</v>
       </c>
       <c r="C127">
-        <v>1437</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B128">
-        <v>1720.588</v>
+        <v>311.112</v>
       </c>
       <c r="C128">
-        <v>1531</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B129">
-        <v>1715.12</v>
+        <v>296.144</v>
       </c>
       <c r="C129">
-        <v>1566</v>
+        <v>0</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B130">
-        <v>1668.335</v>
+        <v>352.736</v>
       </c>
       <c r="C130">
-        <v>1545</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B131">
-        <v>1668.126</v>
+        <v>334.458</v>
       </c>
       <c r="C131">
-        <v>1595</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B132">
-        <v>1652.964</v>
+        <v>312.659</v>
       </c>
       <c r="C132">
-        <v>1626</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B133">
-        <v>1649.883</v>
+        <v>293.556</v>
       </c>
       <c r="C133">
-        <v>1552</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B134">
-        <v>1832.228</v>
+        <v>267.896</v>
       </c>
       <c r="C134">
-        <v>1439</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B135">
-        <v>1812.022</v>
+        <v>267.081</v>
       </c>
       <c r="C135">
-        <v>1388</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B136">
-        <v>1787.707</v>
+        <v>265.93</v>
       </c>
       <c r="C136">
-        <v>1401</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B137">
-        <v>1765.237</v>
+        <v>265.037</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B138">
-        <v>1755.211</v>
+        <v>267.003</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B139">
-        <v>1722.595</v>
+        <v>273.659</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B140">
-        <v>1689.932</v>
+        <v>283.963</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B141">
-        <v>1656.253</v>
+        <v>290.565</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B142">
-        <v>1625.553</v>
+        <v>300.388</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B143">
-        <v>1618.561</v>
+        <v>307.036</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B144">
-        <v>1611.877</v>
+        <v>314.525</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B145">
-        <v>1605.209</v>
+        <v>322.696</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B146">
-        <v>1617.489</v>
+        <v>331.373</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B147">
-        <v>1624.588</v>
+        <v>342.06</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B148">
-        <v>1631.367</v>
+        <v>350.969</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B149">
-        <v>1638.768</v>
+        <v>357.787</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B150">
-        <v>1651.801</v>
+        <v>367.339</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B151">
-        <v>1659.213</v>
+        <v>374.498</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B152">
-        <v>1666.19</v>
+        <v>384.824</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B153">
-        <v>1673.011</v>
+        <v>395.169</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B154">
-        <v>1709.548</v>
+        <v>411.268</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B155">
-        <v>1708.725</v>
+        <v>419.463</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B156">
-        <v>1706.367</v>
+        <v>427.417</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B157">
-        <v>1703.002</v>
+        <v>436.416</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B158">
-        <v>1680.72</v>
+        <v>406.384</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B159">
-        <v>1645.357</v>
+        <v>419.494</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B160">
-        <v>1609.523</v>
+        <v>434.199</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B161">
-        <v>1581.221</v>
+        <v>449.864</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B162">
-        <v>1366.736</v>
+        <v>479.821</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B163">
-        <v>1310.14</v>
+        <v>504.967</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B164">
-        <v>1249.842</v>
+        <v>529.746</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B165">
-        <v>1193.69</v>
+        <v>557.847</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B166">
-        <v>1120.788</v>
+        <v>527.186</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B167">
-        <v>1093.164</v>
+        <v>560.638</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B168">
-        <v>1064.168</v>
+        <v>594.8390000000001</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B169">
-        <v>1038.52</v>
+        <v>626.718</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B170">
-        <v>1004.053</v>
+        <v>657.622</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B171">
-        <v>989.991</v>
+        <v>671.7910000000001</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B172">
-        <v>977.901</v>
+        <v>686.817</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B173">
-        <v>964.999</v>
+        <v>700.268</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B174">
-        <v>976.068</v>
+        <v>705.28</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B175">
-        <v>962.5700000000001</v>
+        <v>691.26</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B176">
-        <v>951.317</v>
+        <v>676.254</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B177">
-        <v>940.407</v>
+        <v>662.609</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B178">
-        <v>915.997</v>
+        <v>632.788</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B179">
-        <v>903.3</v>
+        <v>604.973</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B180">
-        <v>892.0599999999999</v>
+        <v>577.023</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B181">
-        <v>879.619</v>
+        <v>549.019</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B182">
-        <v>864.264</v>
+        <v>515.9349999999999</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B183">
-        <v>852.547</v>
+        <v>490.188</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B184">
-        <v>841.578</v>
+        <v>465.018</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B185">
-        <v>828.5309999999999</v>
+        <v>439.68</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B186">
-        <v>805.571</v>
+        <v>412.635</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B187">
-        <v>790.02</v>
+        <v>396.526</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B188">
-        <v>774.717</v>
+        <v>380.483</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B189">
-        <v>759.293</v>
+        <v>365.356</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.03.20261</t>
-  </si>
-  <si>
-    <t>12.03.20262</t>
-  </si>
-  <si>
-    <t>12.03.20263</t>
-  </si>
-  <si>
-    <t>12.03.20264</t>
-  </si>
-  <si>
-    <t>12.03.20265</t>
-  </si>
-  <si>
-    <t>12.03.20266</t>
-  </si>
-  <si>
-    <t>12.03.20267</t>
-  </si>
-  <si>
-    <t>12.03.20268</t>
-  </si>
-  <si>
-    <t>12.03.20269</t>
-  </si>
-  <si>
-    <t>12.03.202610</t>
-  </si>
-  <si>
-    <t>12.03.202611</t>
-  </si>
-  <si>
-    <t>12.03.202612</t>
-  </si>
-  <si>
-    <t>12.03.202613</t>
-  </si>
-  <si>
-    <t>12.03.202614</t>
-  </si>
-  <si>
-    <t>12.03.202615</t>
-  </si>
-  <si>
-    <t>12.03.202616</t>
-  </si>
-  <si>
-    <t>12.03.202617</t>
-  </si>
-  <si>
-    <t>12.03.202618</t>
-  </si>
-  <si>
-    <t>12.03.202619</t>
-  </si>
-  <si>
-    <t>12.03.202620</t>
-  </si>
-  <si>
-    <t>12.03.202621</t>
-  </si>
-  <si>
-    <t>12.03.202622</t>
-  </si>
-  <si>
-    <t>12.03.202623</t>
-  </si>
-  <si>
-    <t>12.03.202624</t>
-  </si>
-  <si>
-    <t>12.03.202625</t>
-  </si>
-  <si>
-    <t>12.03.202626</t>
-  </si>
-  <si>
-    <t>12.03.202627</t>
-  </si>
-  <si>
-    <t>12.03.202628</t>
-  </si>
-  <si>
-    <t>12.03.202629</t>
-  </si>
-  <si>
-    <t>12.03.202630</t>
-  </si>
-  <si>
-    <t>12.03.202631</t>
-  </si>
-  <si>
-    <t>12.03.202632</t>
-  </si>
-  <si>
-    <t>12.03.202633</t>
-  </si>
-  <si>
-    <t>12.03.202634</t>
-  </si>
-  <si>
-    <t>12.03.202635</t>
-  </si>
-  <si>
-    <t>12.03.202636</t>
-  </si>
-  <si>
-    <t>12.03.202637</t>
-  </si>
-  <si>
-    <t>12.03.202638</t>
-  </si>
-  <si>
-    <t>12.03.202639</t>
-  </si>
-  <si>
-    <t>12.03.202640</t>
-  </si>
-  <si>
-    <t>12.03.202641</t>
-  </si>
-  <si>
-    <t>12.03.202642</t>
-  </si>
-  <si>
-    <t>12.03.202643</t>
-  </si>
-  <si>
-    <t>12.03.202644</t>
-  </si>
-  <si>
-    <t>12.03.202645</t>
-  </si>
-  <si>
-    <t>12.03.202646</t>
-  </si>
-  <si>
-    <t>12.03.202647</t>
-  </si>
-  <si>
-    <t>12.03.202648</t>
-  </si>
-  <si>
-    <t>12.03.202649</t>
-  </si>
-  <si>
-    <t>12.03.202650</t>
-  </si>
-  <si>
-    <t>12.03.202651</t>
-  </si>
-  <si>
-    <t>12.03.202652</t>
-  </si>
-  <si>
-    <t>12.03.202653</t>
-  </si>
-  <si>
-    <t>12.03.202654</t>
-  </si>
-  <si>
-    <t>12.03.202655</t>
-  </si>
-  <si>
-    <t>12.03.202656</t>
-  </si>
-  <si>
-    <t>12.03.202657</t>
-  </si>
-  <si>
-    <t>12.03.202658</t>
-  </si>
-  <si>
-    <t>12.03.202659</t>
-  </si>
-  <si>
-    <t>12.03.202660</t>
-  </si>
-  <si>
-    <t>12.03.202661</t>
-  </si>
-  <si>
-    <t>12.03.202662</t>
-  </si>
-  <si>
-    <t>12.03.202663</t>
-  </si>
-  <si>
-    <t>12.03.202664</t>
-  </si>
-  <si>
-    <t>12.03.202665</t>
-  </si>
-  <si>
-    <t>12.03.202666</t>
-  </si>
-  <si>
-    <t>12.03.202667</t>
-  </si>
-  <si>
-    <t>12.03.202668</t>
-  </si>
-  <si>
-    <t>12.03.202669</t>
-  </si>
-  <si>
-    <t>12.03.202670</t>
-  </si>
-  <si>
-    <t>12.03.202671</t>
-  </si>
-  <si>
-    <t>12.03.202672</t>
-  </si>
-  <si>
-    <t>12.03.202673</t>
-  </si>
-  <si>
-    <t>12.03.202674</t>
-  </si>
-  <si>
-    <t>12.03.202675</t>
-  </si>
-  <si>
-    <t>12.03.202676</t>
-  </si>
-  <si>
-    <t>12.03.202677</t>
-  </si>
-  <si>
-    <t>12.03.202678</t>
-  </si>
-  <si>
-    <t>12.03.202679</t>
-  </si>
-  <si>
-    <t>12.03.202680</t>
-  </si>
-  <si>
-    <t>12.03.202681</t>
-  </si>
-  <si>
-    <t>12.03.202682</t>
-  </si>
-  <si>
-    <t>12.03.202683</t>
-  </si>
-  <si>
-    <t>12.03.202684</t>
-  </si>
-  <si>
-    <t>12.03.202685</t>
-  </si>
-  <si>
-    <t>12.03.202686</t>
-  </si>
-  <si>
-    <t>12.03.202687</t>
-  </si>
-  <si>
-    <t>12.03.202688</t>
-  </si>
-  <si>
-    <t>12.03.202689</t>
-  </si>
-  <si>
-    <t>12.03.202690</t>
-  </si>
-  <si>
-    <t>12.03.202691</t>
-  </si>
-  <si>
-    <t>12.03.202692</t>
-  </si>
-  <si>
-    <t>12.03.202693</t>
-  </si>
-  <si>
-    <t>12.03.202694</t>
-  </si>
-  <si>
-    <t>12.03.202695</t>
-  </si>
-  <si>
-    <t>12.03.202696</t>
-  </si>
-  <si>
-    <t>13.03.20261</t>
-  </si>
-  <si>
-    <t>13.03.20262</t>
-  </si>
-  <si>
-    <t>13.03.20263</t>
-  </si>
-  <si>
-    <t>13.03.20264</t>
-  </si>
-  <si>
-    <t>13.03.20265</t>
-  </si>
-  <si>
-    <t>13.03.20266</t>
-  </si>
-  <si>
-    <t>13.03.20267</t>
-  </si>
-  <si>
-    <t>13.03.20268</t>
-  </si>
-  <si>
-    <t>13.03.20269</t>
-  </si>
-  <si>
-    <t>13.03.202610</t>
-  </si>
-  <si>
-    <t>13.03.202611</t>
-  </si>
-  <si>
-    <t>13.03.202612</t>
-  </si>
-  <si>
-    <t>13.03.202613</t>
-  </si>
-  <si>
-    <t>13.03.202614</t>
-  </si>
-  <si>
-    <t>13.03.202615</t>
-  </si>
-  <si>
-    <t>13.03.202616</t>
-  </si>
-  <si>
-    <t>13.03.202617</t>
-  </si>
-  <si>
-    <t>13.03.202618</t>
-  </si>
-  <si>
-    <t>13.03.202619</t>
-  </si>
-  <si>
-    <t>13.03.202620</t>
-  </si>
-  <si>
-    <t>13.03.202621</t>
-  </si>
-  <si>
-    <t>13.03.202622</t>
-  </si>
-  <si>
-    <t>13.03.202623</t>
-  </si>
-  <si>
-    <t>13.03.202624</t>
-  </si>
-  <si>
-    <t>13.03.202625</t>
-  </si>
-  <si>
-    <t>13.03.202626</t>
-  </si>
-  <si>
-    <t>13.03.202627</t>
-  </si>
-  <si>
-    <t>13.03.202628</t>
-  </si>
-  <si>
-    <t>13.03.202629</t>
-  </si>
-  <si>
-    <t>13.03.202630</t>
-  </si>
-  <si>
-    <t>13.03.202631</t>
-  </si>
-  <si>
-    <t>13.03.202632</t>
-  </si>
-  <si>
-    <t>13.03.202633</t>
-  </si>
-  <si>
-    <t>13.03.202634</t>
-  </si>
-  <si>
-    <t>13.03.202635</t>
-  </si>
-  <si>
-    <t>13.03.202636</t>
-  </si>
-  <si>
-    <t>13.03.202637</t>
-  </si>
-  <si>
-    <t>13.03.202638</t>
-  </si>
-  <si>
-    <t>13.03.202639</t>
-  </si>
-  <si>
-    <t>13.03.202640</t>
-  </si>
-  <si>
-    <t>13.03.202641</t>
-  </si>
-  <si>
-    <t>13.03.202642</t>
-  </si>
-  <si>
-    <t>13.03.202643</t>
-  </si>
-  <si>
-    <t>13.03.202644</t>
-  </si>
-  <si>
-    <t>13.03.202645</t>
-  </si>
-  <si>
-    <t>13.03.202646</t>
-  </si>
-  <si>
-    <t>13.03.202647</t>
-  </si>
-  <si>
-    <t>13.03.202648</t>
-  </si>
-  <si>
-    <t>13.03.202649</t>
-  </si>
-  <si>
-    <t>13.03.202650</t>
-  </si>
-  <si>
-    <t>13.03.202651</t>
-  </si>
-  <si>
-    <t>13.03.202652</t>
-  </si>
-  <si>
-    <t>13.03.202653</t>
-  </si>
-  <si>
-    <t>13.03.202654</t>
-  </si>
-  <si>
-    <t>13.03.202655</t>
-  </si>
-  <si>
-    <t>13.03.202656</t>
-  </si>
-  <si>
-    <t>13.03.202657</t>
-  </si>
-  <si>
-    <t>13.03.202658</t>
-  </si>
-  <si>
-    <t>13.03.202659</t>
-  </si>
-  <si>
-    <t>13.03.202660</t>
-  </si>
-  <si>
-    <t>13.03.202661</t>
-  </si>
-  <si>
-    <t>13.03.202662</t>
-  </si>
-  <si>
-    <t>13.03.202663</t>
-  </si>
-  <si>
-    <t>13.03.202664</t>
-  </si>
-  <si>
-    <t>13.03.202665</t>
-  </si>
-  <si>
-    <t>13.03.202666</t>
-  </si>
-  <si>
-    <t>13.03.202667</t>
-  </si>
-  <si>
-    <t>13.03.202668</t>
-  </si>
-  <si>
-    <t>13.03.202669</t>
-  </si>
-  <si>
-    <t>13.03.202670</t>
-  </si>
-  <si>
-    <t>13.03.202671</t>
-  </si>
-  <si>
-    <t>13.03.202672</t>
-  </si>
-  <si>
-    <t>13.03.202673</t>
-  </si>
-  <si>
-    <t>13.03.202674</t>
-  </si>
-  <si>
-    <t>13.03.202675</t>
-  </si>
-  <si>
-    <t>13.03.202676</t>
-  </si>
-  <si>
-    <t>13.03.202677</t>
-  </si>
-  <si>
-    <t>13.03.202678</t>
-  </si>
-  <si>
-    <t>13.03.202679</t>
-  </si>
-  <si>
-    <t>13.03.202680</t>
-  </si>
-  <si>
-    <t>13.03.202681</t>
-  </si>
-  <si>
-    <t>13.03.202682</t>
-  </si>
-  <si>
-    <t>13.03.202683</t>
-  </si>
-  <si>
-    <t>13.03.202684</t>
-  </si>
-  <si>
-    <t>13.03.202685</t>
-  </si>
-  <si>
-    <t>13.03.202686</t>
-  </si>
-  <si>
-    <t>13.03.202687</t>
-  </si>
-  <si>
-    <t>13.03.202688</t>
-  </si>
-  <si>
-    <t>13.03.202689</t>
-  </si>
-  <si>
-    <t>13.03.202690</t>
-  </si>
-  <si>
-    <t>13.03.202691</t>
-  </si>
-  <si>
-    <t>13.03.202692</t>
-  </si>
-  <si>
-    <t>13.03.202693</t>
-  </si>
-  <si>
-    <t>13.03.202694</t>
-  </si>
-  <si>
-    <t>13.03.202695</t>
-  </si>
-  <si>
-    <t>13.03.202696</t>
+    <t>25.03.20261</t>
+  </si>
+  <si>
+    <t>25.03.20262</t>
+  </si>
+  <si>
+    <t>25.03.20263</t>
+  </si>
+  <si>
+    <t>25.03.20264</t>
+  </si>
+  <si>
+    <t>25.03.20265</t>
+  </si>
+  <si>
+    <t>25.03.20266</t>
+  </si>
+  <si>
+    <t>25.03.20267</t>
+  </si>
+  <si>
+    <t>25.03.20268</t>
+  </si>
+  <si>
+    <t>25.03.20269</t>
+  </si>
+  <si>
+    <t>25.03.202610</t>
+  </si>
+  <si>
+    <t>25.03.202611</t>
+  </si>
+  <si>
+    <t>25.03.202612</t>
+  </si>
+  <si>
+    <t>25.03.202613</t>
+  </si>
+  <si>
+    <t>25.03.202614</t>
+  </si>
+  <si>
+    <t>25.03.202615</t>
+  </si>
+  <si>
+    <t>25.03.202616</t>
+  </si>
+  <si>
+    <t>25.03.202617</t>
+  </si>
+  <si>
+    <t>25.03.202618</t>
+  </si>
+  <si>
+    <t>25.03.202619</t>
+  </si>
+  <si>
+    <t>25.03.202620</t>
+  </si>
+  <si>
+    <t>25.03.202621</t>
+  </si>
+  <si>
+    <t>25.03.202622</t>
+  </si>
+  <si>
+    <t>25.03.202623</t>
+  </si>
+  <si>
+    <t>25.03.202624</t>
+  </si>
+  <si>
+    <t>25.03.202625</t>
+  </si>
+  <si>
+    <t>25.03.202626</t>
+  </si>
+  <si>
+    <t>25.03.202627</t>
+  </si>
+  <si>
+    <t>25.03.202628</t>
+  </si>
+  <si>
+    <t>25.03.202629</t>
+  </si>
+  <si>
+    <t>25.03.202630</t>
+  </si>
+  <si>
+    <t>25.03.202631</t>
+  </si>
+  <si>
+    <t>25.03.202632</t>
+  </si>
+  <si>
+    <t>25.03.202633</t>
+  </si>
+  <si>
+    <t>25.03.202634</t>
+  </si>
+  <si>
+    <t>25.03.202635</t>
+  </si>
+  <si>
+    <t>25.03.202636</t>
+  </si>
+  <si>
+    <t>25.03.202637</t>
+  </si>
+  <si>
+    <t>25.03.202638</t>
+  </si>
+  <si>
+    <t>25.03.202639</t>
+  </si>
+  <si>
+    <t>25.03.202640</t>
+  </si>
+  <si>
+    <t>25.03.202641</t>
+  </si>
+  <si>
+    <t>25.03.202642</t>
+  </si>
+  <si>
+    <t>25.03.202643</t>
+  </si>
+  <si>
+    <t>25.03.202644</t>
+  </si>
+  <si>
+    <t>25.03.202645</t>
+  </si>
+  <si>
+    <t>25.03.202646</t>
+  </si>
+  <si>
+    <t>25.03.202647</t>
+  </si>
+  <si>
+    <t>25.03.202648</t>
+  </si>
+  <si>
+    <t>25.03.202649</t>
+  </si>
+  <si>
+    <t>25.03.202650</t>
+  </si>
+  <si>
+    <t>25.03.202651</t>
+  </si>
+  <si>
+    <t>25.03.202652</t>
+  </si>
+  <si>
+    <t>25.03.202653</t>
+  </si>
+  <si>
+    <t>25.03.202654</t>
+  </si>
+  <si>
+    <t>25.03.202655</t>
+  </si>
+  <si>
+    <t>25.03.202656</t>
+  </si>
+  <si>
+    <t>25.03.202657</t>
+  </si>
+  <si>
+    <t>25.03.202658</t>
+  </si>
+  <si>
+    <t>25.03.202659</t>
+  </si>
+  <si>
+    <t>25.03.202660</t>
+  </si>
+  <si>
+    <t>25.03.202661</t>
+  </si>
+  <si>
+    <t>25.03.202662</t>
+  </si>
+  <si>
+    <t>25.03.202663</t>
+  </si>
+  <si>
+    <t>25.03.202664</t>
+  </si>
+  <si>
+    <t>25.03.202665</t>
+  </si>
+  <si>
+    <t>25.03.202666</t>
+  </si>
+  <si>
+    <t>25.03.202667</t>
+  </si>
+  <si>
+    <t>25.03.202668</t>
+  </si>
+  <si>
+    <t>25.03.202669</t>
+  </si>
+  <si>
+    <t>25.03.202670</t>
+  </si>
+  <si>
+    <t>25.03.202671</t>
+  </si>
+  <si>
+    <t>25.03.202672</t>
+  </si>
+  <si>
+    <t>25.03.202673</t>
+  </si>
+  <si>
+    <t>25.03.202674</t>
+  </si>
+  <si>
+    <t>25.03.202675</t>
+  </si>
+  <si>
+    <t>25.03.202676</t>
+  </si>
+  <si>
+    <t>25.03.202677</t>
+  </si>
+  <si>
+    <t>25.03.202678</t>
+  </si>
+  <si>
+    <t>25.03.202679</t>
+  </si>
+  <si>
+    <t>25.03.202680</t>
+  </si>
+  <si>
+    <t>25.03.202681</t>
+  </si>
+  <si>
+    <t>25.03.202682</t>
+  </si>
+  <si>
+    <t>25.03.202683</t>
+  </si>
+  <si>
+    <t>25.03.202684</t>
+  </si>
+  <si>
+    <t>25.03.202685</t>
+  </si>
+  <si>
+    <t>25.03.202686</t>
+  </si>
+  <si>
+    <t>25.03.202687</t>
+  </si>
+  <si>
+    <t>25.03.202688</t>
+  </si>
+  <si>
+    <t>25.03.202689</t>
+  </si>
+  <si>
+    <t>25.03.202690</t>
+  </si>
+  <si>
+    <t>25.03.202691</t>
+  </si>
+  <si>
+    <t>25.03.202692</t>
+  </si>
+  <si>
+    <t>25.03.202693</t>
+  </si>
+  <si>
+    <t>25.03.202694</t>
+  </si>
+  <si>
+    <t>25.03.202695</t>
+  </si>
+  <si>
+    <t>25.03.202696</t>
+  </si>
+  <si>
+    <t>26.03.20261</t>
+  </si>
+  <si>
+    <t>26.03.20262</t>
+  </si>
+  <si>
+    <t>26.03.20263</t>
+  </si>
+  <si>
+    <t>26.03.20264</t>
+  </si>
+  <si>
+    <t>26.03.20265</t>
+  </si>
+  <si>
+    <t>26.03.20266</t>
+  </si>
+  <si>
+    <t>26.03.20267</t>
+  </si>
+  <si>
+    <t>26.03.20268</t>
+  </si>
+  <si>
+    <t>26.03.20269</t>
+  </si>
+  <si>
+    <t>26.03.202610</t>
+  </si>
+  <si>
+    <t>26.03.202611</t>
+  </si>
+  <si>
+    <t>26.03.202612</t>
+  </si>
+  <si>
+    <t>26.03.202613</t>
+  </si>
+  <si>
+    <t>26.03.202614</t>
+  </si>
+  <si>
+    <t>26.03.202615</t>
+  </si>
+  <si>
+    <t>26.03.202616</t>
+  </si>
+  <si>
+    <t>26.03.202617</t>
+  </si>
+  <si>
+    <t>26.03.202618</t>
+  </si>
+  <si>
+    <t>26.03.202619</t>
+  </si>
+  <si>
+    <t>26.03.202620</t>
+  </si>
+  <si>
+    <t>26.03.202621</t>
+  </si>
+  <si>
+    <t>26.03.202622</t>
+  </si>
+  <si>
+    <t>26.03.202623</t>
+  </si>
+  <si>
+    <t>26.03.202624</t>
+  </si>
+  <si>
+    <t>26.03.202625</t>
+  </si>
+  <si>
+    <t>26.03.202626</t>
+  </si>
+  <si>
+    <t>26.03.202627</t>
+  </si>
+  <si>
+    <t>26.03.202628</t>
+  </si>
+  <si>
+    <t>26.03.202629</t>
+  </si>
+  <si>
+    <t>26.03.202630</t>
+  </si>
+  <si>
+    <t>26.03.202631</t>
+  </si>
+  <si>
+    <t>26.03.202632</t>
+  </si>
+  <si>
+    <t>26.03.202633</t>
+  </si>
+  <si>
+    <t>26.03.202634</t>
+  </si>
+  <si>
+    <t>26.03.202635</t>
+  </si>
+  <si>
+    <t>26.03.202636</t>
+  </si>
+  <si>
+    <t>26.03.202637</t>
+  </si>
+  <si>
+    <t>26.03.202638</t>
+  </si>
+  <si>
+    <t>26.03.202639</t>
+  </si>
+  <si>
+    <t>26.03.202640</t>
+  </si>
+  <si>
+    <t>26.03.202641</t>
+  </si>
+  <si>
+    <t>26.03.202642</t>
+  </si>
+  <si>
+    <t>26.03.202643</t>
+  </si>
+  <si>
+    <t>26.03.202644</t>
+  </si>
+  <si>
+    <t>26.03.202645</t>
+  </si>
+  <si>
+    <t>26.03.202646</t>
+  </si>
+  <si>
+    <t>26.03.202647</t>
+  </si>
+  <si>
+    <t>26.03.202648</t>
+  </si>
+  <si>
+    <t>26.03.202649</t>
+  </si>
+  <si>
+    <t>26.03.202650</t>
+  </si>
+  <si>
+    <t>26.03.202651</t>
+  </si>
+  <si>
+    <t>26.03.202652</t>
+  </si>
+  <si>
+    <t>26.03.202653</t>
+  </si>
+  <si>
+    <t>26.03.202654</t>
+  </si>
+  <si>
+    <t>26.03.202655</t>
+  </si>
+  <si>
+    <t>26.03.202656</t>
+  </si>
+  <si>
+    <t>26.03.202657</t>
+  </si>
+  <si>
+    <t>26.03.202658</t>
+  </si>
+  <si>
+    <t>26.03.202659</t>
+  </si>
+  <si>
+    <t>26.03.202660</t>
+  </si>
+  <si>
+    <t>26.03.202661</t>
+  </si>
+  <si>
+    <t>26.03.202662</t>
+  </si>
+  <si>
+    <t>26.03.202663</t>
+  </si>
+  <si>
+    <t>26.03.202664</t>
+  </si>
+  <si>
+    <t>26.03.202665</t>
+  </si>
+  <si>
+    <t>26.03.202666</t>
+  </si>
+  <si>
+    <t>26.03.202667</t>
+  </si>
+  <si>
+    <t>26.03.202668</t>
+  </si>
+  <si>
+    <t>26.03.202669</t>
+  </si>
+  <si>
+    <t>26.03.202670</t>
+  </si>
+  <si>
+    <t>26.03.202671</t>
+  </si>
+  <si>
+    <t>26.03.202672</t>
+  </si>
+  <si>
+    <t>26.03.202673</t>
+  </si>
+  <si>
+    <t>26.03.202674</t>
+  </si>
+  <si>
+    <t>26.03.202675</t>
+  </si>
+  <si>
+    <t>26.03.202676</t>
+  </si>
+  <si>
+    <t>26.03.202677</t>
+  </si>
+  <si>
+    <t>26.03.202678</t>
+  </si>
+  <si>
+    <t>26.03.202679</t>
+  </si>
+  <si>
+    <t>26.03.202680</t>
+  </si>
+  <si>
+    <t>26.03.202681</t>
+  </si>
+  <si>
+    <t>26.03.202682</t>
+  </si>
+  <si>
+    <t>26.03.202683</t>
+  </si>
+  <si>
+    <t>26.03.202684</t>
+  </si>
+  <si>
+    <t>26.03.202685</t>
+  </si>
+  <si>
+    <t>26.03.202686</t>
+  </si>
+  <si>
+    <t>26.03.202687</t>
+  </si>
+  <si>
+    <t>26.03.202688</t>
+  </si>
+  <si>
+    <t>26.03.202689</t>
+  </si>
+  <si>
+    <t>26.03.202690</t>
+  </si>
+  <si>
+    <t>26.03.202691</t>
+  </si>
+  <si>
+    <t>26.03.202692</t>
+  </si>
+  <si>
+    <t>26.03.202693</t>
+  </si>
+  <si>
+    <t>26.03.202694</t>
+  </si>
+  <si>
+    <t>26.03.202695</t>
+  </si>
+  <si>
+    <t>26.03.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="B2">
-        <v>425.812</v>
+        <v>371.959</v>
       </c>
       <c r="C2">
-        <v>541</v>
+        <v>288</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46093.01041666666</v>
+        <v>46106.01041666666</v>
       </c>
       <c r="B3">
-        <v>414.782</v>
+        <v>382.848</v>
       </c>
       <c r="C3">
-        <v>527</v>
+        <v>313</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46093.02083333334</v>
+        <v>46106.02083333334</v>
       </c>
       <c r="B4">
-        <v>399.762</v>
+        <v>394.8</v>
       </c>
       <c r="C4">
-        <v>502</v>
+        <v>328</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46093.03125</v>
+        <v>46106.03125</v>
       </c>
       <c r="B5">
-        <v>378.93</v>
+        <v>406.635</v>
       </c>
       <c r="C5">
-        <v>463</v>
+        <v>329</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46093.04166666666</v>
+        <v>46106.04166666666</v>
       </c>
       <c r="B6">
-        <v>342.091</v>
+        <v>423.084</v>
       </c>
       <c r="C6">
-        <v>418</v>
+        <v>330</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46093.05208333334</v>
+        <v>46106.05208333334</v>
       </c>
       <c r="B7">
-        <v>329.494</v>
+        <v>436.37</v>
       </c>
       <c r="C7">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46093.0625</v>
+        <v>46106.0625</v>
       </c>
       <c r="B8">
-        <v>316.907</v>
+        <v>451.496</v>
       </c>
       <c r="C8">
-        <v>341</v>
+        <v>384</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46093.07291666666</v>
+        <v>46106.07291666666</v>
       </c>
       <c r="B9">
-        <v>306.728</v>
+        <v>470.566</v>
       </c>
       <c r="C9">
-        <v>305</v>
+        <v>402</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46093.08333333334</v>
+        <v>46106.08333333334</v>
       </c>
       <c r="B10">
-        <v>282.994</v>
+        <v>501.544</v>
       </c>
       <c r="C10">
-        <v>278</v>
+        <v>426</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46093.09375</v>
+        <v>46106.09375</v>
       </c>
       <c r="B11">
-        <v>278.516</v>
+        <v>513.963</v>
       </c>
       <c r="C11">
-        <v>246</v>
+        <v>430</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46093.10416666666</v>
+        <v>46106.10416666666</v>
       </c>
       <c r="B12">
-        <v>266.078</v>
+        <v>522.158</v>
       </c>
       <c r="C12">
-        <v>228</v>
+        <v>417</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46093.11458333334</v>
+        <v>46106.11458333334</v>
       </c>
       <c r="B13">
-        <v>269.85</v>
+        <v>535.6319999999999</v>
       </c>
       <c r="C13">
-        <v>214</v>
+        <v>411</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46093.125</v>
+        <v>46106.125</v>
       </c>
       <c r="B14">
-        <v>254.524</v>
+        <v>544.764</v>
       </c>
       <c r="C14">
-        <v>189</v>
+        <v>397</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46093.13541666666</v>
+        <v>46106.13541666666</v>
       </c>
       <c r="B15">
-        <v>229.736</v>
+        <v>545.2089999999999</v>
       </c>
       <c r="C15">
-        <v>162</v>
+        <v>387</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46093.14583333334</v>
+        <v>46106.14583333334</v>
       </c>
       <c r="B16">
-        <v>224.866</v>
+        <v>545.308</v>
       </c>
       <c r="C16">
-        <v>139</v>
+        <v>379</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46093.15625</v>
+        <v>46106.15625</v>
       </c>
       <c r="B17">
-        <v>224.325</v>
+        <v>538.776</v>
       </c>
       <c r="C17">
-        <v>114</v>
+        <v>347</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46093.16666666666</v>
+        <v>46106.16666666666</v>
       </c>
       <c r="B18">
-        <v>217.723</v>
+        <v>557.063</v>
       </c>
       <c r="C18">
-        <v>99</v>
+        <v>309</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46093.17708333334</v>
+        <v>46106.17708333334</v>
       </c>
       <c r="B19">
-        <v>218.869</v>
+        <v>549.482</v>
       </c>
       <c r="C19">
-        <v>87</v>
+        <v>272</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46093.1875</v>
+        <v>46106.1875</v>
       </c>
       <c r="B20">
-        <v>218.68</v>
+        <v>540.45</v>
       </c>
       <c r="C20">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46093.19791666666</v>
+        <v>46106.19791666666</v>
       </c>
       <c r="B21">
-        <v>219.164</v>
+        <v>534.388</v>
       </c>
       <c r="C21">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46093.20833333334</v>
+        <v>46106.20833333334</v>
       </c>
       <c r="B22">
-        <v>221.528</v>
+        <v>520.674</v>
       </c>
       <c r="C22">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46093.21875</v>
+        <v>46106.21875</v>
       </c>
       <c r="B23">
-        <v>225.839</v>
+        <v>510.737</v>
       </c>
       <c r="C23">
-        <v>90</v>
+        <v>251</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46093.22916666666</v>
+        <v>46106.22916666666</v>
       </c>
       <c r="B24">
-        <v>224.354</v>
+        <v>494.326</v>
       </c>
       <c r="C24">
-        <v>101</v>
+        <v>250</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46093.23958333334</v>
+        <v>46106.23958333334</v>
       </c>
       <c r="B25">
-        <v>229.055</v>
+        <v>497.015</v>
       </c>
       <c r="C25">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46093.25</v>
+        <v>46106.25</v>
       </c>
       <c r="B26">
-        <v>233.619</v>
+        <v>477.753</v>
       </c>
       <c r="C26">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46093.26041666666</v>
+        <v>46106.26041666666</v>
       </c>
       <c r="B27">
-        <v>234.241</v>
+        <v>432.593</v>
       </c>
       <c r="C27">
-        <v>150</v>
+        <v>261</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46093.27083333334</v>
+        <v>46106.27083333334</v>
       </c>
       <c r="B28">
-        <v>238.861</v>
+        <v>449.053</v>
       </c>
       <c r="C28">
-        <v>182</v>
+        <v>270</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46093.28125</v>
+        <v>46106.28125</v>
       </c>
       <c r="B29">
-        <v>238.009</v>
+        <v>413.12</v>
       </c>
       <c r="C29">
-        <v>205</v>
+        <v>271</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46093.29166666666</v>
+        <v>46106.29166666666</v>
       </c>
       <c r="B30">
-        <v>259.396</v>
+        <v>410.337</v>
       </c>
       <c r="C30">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46093.30208333334</v>
+        <v>46106.30208333334</v>
       </c>
       <c r="B31">
-        <v>250.363</v>
+        <v>373.811</v>
       </c>
       <c r="C31">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46093.3125</v>
+        <v>46106.3125</v>
       </c>
       <c r="B32">
-        <v>245.226</v>
+        <v>348.435</v>
       </c>
       <c r="C32">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46093.32291666666</v>
+        <v>46106.32291666666</v>
       </c>
       <c r="B33">
-        <v>237.697</v>
+        <v>313.501</v>
       </c>
       <c r="C33">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46093.33333333334</v>
+        <v>46106.33333333334</v>
       </c>
       <c r="B34">
-        <v>274.314</v>
+        <v>341.709</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46093.34375</v>
+        <v>46106.34375</v>
       </c>
       <c r="B35">
-        <v>275.794</v>
+        <v>353.628</v>
       </c>
       <c r="C35">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46093.35416666666</v>
+        <v>46106.35416666666</v>
       </c>
       <c r="B36">
-        <v>277.914</v>
+        <v>362.578</v>
       </c>
       <c r="C36">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46093.36458333334</v>
+        <v>46106.36458333334</v>
       </c>
       <c r="B37">
-        <v>280.41</v>
+        <v>369.198</v>
       </c>
       <c r="C37">
-        <v>178</v>
+        <v>254</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46093.375</v>
+        <v>46106.375</v>
       </c>
       <c r="B38">
-        <v>296.944</v>
+        <v>353.736</v>
       </c>
       <c r="C38">
-        <v>188</v>
+        <v>278</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46093.38541666666</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="B39">
-        <v>290.656</v>
+        <v>360.33</v>
       </c>
       <c r="C39">
-        <v>186</v>
+        <v>290</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46093.39583333334</v>
+        <v>46106.39583333334</v>
       </c>
       <c r="B40">
-        <v>287.728</v>
+        <v>366.873</v>
       </c>
       <c r="C40">
-        <v>184</v>
+        <v>299</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46093.40625</v>
+        <v>46106.40625</v>
       </c>
       <c r="B41">
-        <v>281.864</v>
+        <v>371.805</v>
       </c>
       <c r="C41">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46093.41666666666</v>
+        <v>46106.41666666666</v>
       </c>
       <c r="B42">
-        <v>279.936</v>
+        <v>383.04</v>
       </c>
       <c r="C42">
-        <v>184</v>
+        <v>320</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46093.42708333334</v>
+        <v>46106.42708333334</v>
       </c>
       <c r="B43">
-        <v>272.327</v>
+        <v>378.354</v>
       </c>
       <c r="C43">
-        <v>194</v>
+        <v>318</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46093.4375</v>
+        <v>46106.4375</v>
       </c>
       <c r="B44">
-        <v>265.089</v>
+        <v>374.036</v>
       </c>
       <c r="C44">
-        <v>200</v>
+        <v>302</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46093.44791666666</v>
+        <v>46106.44791666666</v>
       </c>
       <c r="B45">
-        <v>258.727</v>
+        <v>368.571</v>
       </c>
       <c r="C45">
-        <v>179</v>
+        <v>291</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46093.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="B46">
-        <v>249.181</v>
+        <v>355.303</v>
       </c>
       <c r="C46">
-        <v>164</v>
+        <v>284</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46093.46875</v>
+        <v>46106.46875</v>
       </c>
       <c r="B47">
-        <v>242.288</v>
+        <v>344.869</v>
       </c>
       <c r="C47">
-        <v>162</v>
+        <v>280</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46093.47916666666</v>
+        <v>46106.47916666666</v>
       </c>
       <c r="B48">
-        <v>235.575</v>
+        <v>335.39</v>
       </c>
       <c r="C48">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46093.48958333334</v>
+        <v>46106.48958333334</v>
       </c>
       <c r="B49">
-        <v>228.987</v>
+        <v>327.342</v>
       </c>
       <c r="C49">
-        <v>151</v>
+        <v>266</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46093.5</v>
+        <v>46106.5</v>
       </c>
       <c r="B50">
-        <v>203.817</v>
+        <v>296.039</v>
       </c>
       <c r="C50">
-        <v>149</v>
+        <v>252</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46093.51041666666</v>
+        <v>46106.51041666666</v>
       </c>
       <c r="B51">
-        <v>199.679</v>
+        <v>286.54</v>
       </c>
       <c r="C51">
-        <v>148</v>
+        <v>224</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46093.52083333334</v>
+        <v>46106.52083333334</v>
       </c>
       <c r="B52">
-        <v>195.546</v>
+        <v>276.808</v>
       </c>
       <c r="C52">
-        <v>139</v>
+        <v>223</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46093.53125</v>
+        <v>46106.53125</v>
       </c>
       <c r="B53">
-        <v>191.913</v>
+        <v>266.088</v>
       </c>
       <c r="C53">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46093.54166666666</v>
+        <v>46106.54166666666</v>
       </c>
       <c r="B54">
-        <v>190.95</v>
+        <v>243.631</v>
       </c>
       <c r="C54">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46093.55208333334</v>
+        <v>46106.55208333334</v>
       </c>
       <c r="B55">
-        <v>190.57</v>
+        <v>235.721</v>
       </c>
       <c r="C55">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46093.5625</v>
+        <v>46106.5625</v>
       </c>
       <c r="B56">
-        <v>189.996</v>
+        <v>228.031</v>
       </c>
       <c r="C56">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46093.57291666666</v>
+        <v>46106.57291666666</v>
       </c>
       <c r="B57">
-        <v>189.23</v>
+        <v>220.143</v>
       </c>
       <c r="C57">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46093.58333333334</v>
+        <v>46106.58333333334</v>
       </c>
       <c r="B58">
-        <v>181.969</v>
+        <v>184.698</v>
       </c>
       <c r="C58">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46093.59375</v>
+        <v>46106.59375</v>
       </c>
       <c r="B59">
-        <v>182.532</v>
+        <v>180.366</v>
       </c>
       <c r="C59">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46093.60416666666</v>
+        <v>46106.60416666666</v>
       </c>
       <c r="B60">
-        <v>182.525</v>
+        <v>174.606</v>
       </c>
       <c r="C60">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46093.61458333334</v>
+        <v>46106.61458333334</v>
       </c>
       <c r="B61">
-        <v>182.948</v>
+        <v>169.092</v>
       </c>
       <c r="C61">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46093.625</v>
+        <v>46106.625</v>
       </c>
       <c r="B62">
-        <v>165.061</v>
+        <v>159.543</v>
       </c>
       <c r="C62">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46093.63541666666</v>
+        <v>46106.63541666666</v>
       </c>
       <c r="B63">
-        <v>165.209</v>
+        <v>153.695</v>
       </c>
       <c r="C63">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46093.64583333334</v>
+        <v>46106.64583333334</v>
       </c>
       <c r="B64">
-        <v>165.938</v>
+        <v>147.643</v>
       </c>
       <c r="C64">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46093.65625</v>
+        <v>46106.65625</v>
       </c>
       <c r="B65">
-        <v>167.021</v>
+        <v>142.065</v>
       </c>
       <c r="C65">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46093.66666666666</v>
+        <v>46106.66666666666</v>
       </c>
       <c r="B66">
-        <v>166.775</v>
+        <v>144.703</v>
       </c>
       <c r="C66">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46093.67708333334</v>
+        <v>46106.67708333334</v>
       </c>
       <c r="B67">
-        <v>174.191</v>
+        <v>141.214</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46093.6875</v>
+        <v>46106.6875</v>
       </c>
       <c r="B68">
-        <v>180.916</v>
+        <v>135.638</v>
       </c>
       <c r="C68">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46093.69791666666</v>
+        <v>46106.69791666666</v>
       </c>
       <c r="B69">
-        <v>212.665</v>
+        <v>132.296</v>
       </c>
       <c r="C69">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46093.70833333334</v>
+        <v>46106.70833333334</v>
       </c>
       <c r="B70">
-        <v>198.631</v>
+        <v>138.121</v>
       </c>
       <c r="C70">
-        <v>51</v>
+        <v>158</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46093.71875</v>
+        <v>46106.71875</v>
       </c>
       <c r="B71">
-        <v>203.635</v>
+        <v>144.823</v>
       </c>
       <c r="C71">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46093.72916666666</v>
+        <v>46106.72916666666</v>
       </c>
       <c r="B72">
-        <v>240.822</v>
+        <v>153.288</v>
       </c>
       <c r="C72">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46093.73958333334</v>
+        <v>46106.73958333334</v>
       </c>
       <c r="B73">
-        <v>247.048</v>
+        <v>162.555</v>
       </c>
       <c r="C73">
-        <v>63</v>
+        <v>225</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46093.75</v>
+        <v>46106.75</v>
       </c>
       <c r="B74">
-        <v>210.878</v>
+        <v>183.428</v>
       </c>
       <c r="C74">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46093.76041666666</v>
+        <v>46106.76041666666</v>
       </c>
       <c r="B75">
-        <v>207.668</v>
+        <v>198.58</v>
       </c>
       <c r="C75">
-        <v>62</v>
+        <v>269</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46093.77083333334</v>
+        <v>46106.77083333334</v>
       </c>
       <c r="B76">
-        <v>236.442</v>
+        <v>213.475</v>
       </c>
       <c r="C76">
-        <v>66</v>
+        <v>271</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46093.78125</v>
+        <v>46106.78125</v>
       </c>
       <c r="B77">
-        <v>233.698</v>
+        <v>228.641</v>
       </c>
       <c r="C77">
-        <v>81</v>
+        <v>283</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46093.79166666666</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B78">
-        <v>195.701</v>
+        <v>252.652</v>
       </c>
       <c r="C78">
-        <v>90</v>
+        <v>302</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46093.80208333334</v>
+        <v>46106.80208333334</v>
       </c>
       <c r="B79">
-        <v>188.344</v>
+        <v>264.618</v>
       </c>
       <c r="C79">
-        <v>99</v>
+        <v>346</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46093.8125</v>
+        <v>46106.8125</v>
       </c>
       <c r="B80">
-        <v>181.311</v>
+        <v>277.151</v>
       </c>
       <c r="C80">
-        <v>102</v>
+        <v>389</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46093.82291666666</v>
+        <v>46106.82291666666</v>
       </c>
       <c r="B81">
-        <v>174.047</v>
+        <v>289.788</v>
       </c>
       <c r="C81">
-        <v>101</v>
+        <v>419</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46093.83333333334</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="B82">
-        <v>170.446</v>
+        <v>314.558</v>
       </c>
       <c r="C82">
-        <v>108</v>
+        <v>427</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46093.84375</v>
+        <v>46106.84375</v>
       </c>
       <c r="B83">
-        <v>164.15</v>
+        <v>321.295</v>
       </c>
       <c r="C83">
-        <v>104</v>
+        <v>419</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46093.85416666666</v>
+        <v>46106.85416666666</v>
       </c>
       <c r="B84">
-        <v>157.735</v>
+        <v>329.836</v>
       </c>
       <c r="C84">
-        <v>100</v>
+        <v>424</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46093.86458333334</v>
+        <v>46106.86458333334</v>
       </c>
       <c r="B85">
-        <v>152.427</v>
+        <v>337.043</v>
       </c>
       <c r="C85">
-        <v>98</v>
+        <v>438</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46093.875</v>
+        <v>46106.875</v>
       </c>
       <c r="B86">
-        <v>179.463</v>
+        <v>340.355</v>
       </c>
       <c r="C86">
-        <v>88</v>
+        <v>449</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46093.88541666666</v>
+        <v>46106.88541666666</v>
       </c>
       <c r="B87">
-        <v>176.707</v>
+        <v>350.127</v>
       </c>
       <c r="C87">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46093.89583333334</v>
+        <v>46106.89583333334</v>
       </c>
       <c r="B88">
-        <v>173.728</v>
+        <v>360.816</v>
       </c>
       <c r="C88">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46093.90625</v>
+        <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>140.25</v>
+        <v>371.344</v>
       </c>
       <c r="C89">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46093.91666666666</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>138.947</v>
+        <v>376.092</v>
       </c>
       <c r="C90">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46093.92708333334</v>
+        <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>138.984</v>
+        <v>381.059</v>
       </c>
       <c r="C91">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46093.9375</v>
+        <v>46106.9375</v>
       </c>
       <c r="B92">
-        <v>138.889</v>
+        <v>385.83</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46093.94791666666</v>
+        <v>46106.94791666666</v>
       </c>
       <c r="B93">
-        <v>139.477</v>
+        <v>390.789</v>
       </c>
       <c r="C93">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46093.95833333334</v>
+        <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>150.755</v>
+        <v>421.804</v>
       </c>
       <c r="C94">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46093.96875</v>
+        <v>46106.96875</v>
       </c>
       <c r="B95">
-        <v>126.042</v>
+        <v>420.4</v>
       </c>
       <c r="C95">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46093.97916666666</v>
+        <v>46106.97916666666</v>
       </c>
       <c r="B96">
-        <v>157.213</v>
+        <v>388.853</v>
       </c>
       <c r="C96">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46093.98958333334</v>
+        <v>46106.98958333334</v>
       </c>
       <c r="B97">
-        <v>133.878</v>
+        <v>387.668</v>
       </c>
       <c r="C97">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B98">
-        <v>182.436</v>
+        <v>612.924</v>
       </c>
       <c r="C98">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B99">
-        <v>186.989</v>
+        <v>604.886</v>
       </c>
       <c r="C99">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B100">
-        <v>190.398</v>
+        <v>596.915</v>
       </c>
       <c r="C100">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B101">
-        <v>193.212</v>
+        <v>588.1319999999999</v>
       </c>
       <c r="C101">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B102">
-        <v>204.769</v>
+        <v>573.1</v>
       </c>
       <c r="C102">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B103">
-        <v>209.053</v>
+        <v>558.83</v>
       </c>
       <c r="C103">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B104">
-        <v>213.468</v>
+        <v>515.771</v>
       </c>
       <c r="C104">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B105">
-        <v>218.152</v>
+        <v>500.421</v>
       </c>
       <c r="C105">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B106">
-        <v>220.481</v>
+        <v>483.99</v>
       </c>
       <c r="C106">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B107">
-        <v>245.32</v>
+        <v>475.527</v>
       </c>
       <c r="C107">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B108">
-        <v>252.074</v>
+        <v>467.288</v>
       </c>
       <c r="C108">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B109">
-        <v>259.715</v>
+        <v>474.649</v>
       </c>
       <c r="C109">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B110">
-        <v>281.152</v>
+        <v>475.584</v>
       </c>
       <c r="C110">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B111">
-        <v>292.399</v>
+        <v>436.536</v>
       </c>
       <c r="C111">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B112">
-        <v>299.506</v>
+        <v>460.419</v>
       </c>
       <c r="C112">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B113">
-        <v>303.727</v>
+        <v>451.902</v>
       </c>
       <c r="C113">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B114">
-        <v>332.798</v>
+        <v>468.267</v>
       </c>
       <c r="C114">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B115">
-        <v>335.128</v>
+        <v>458.138</v>
       </c>
       <c r="C115">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B116">
-        <v>337.679</v>
+        <v>448.863</v>
       </c>
       <c r="C116">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B117">
-        <v>336.01</v>
+        <v>440.506</v>
       </c>
       <c r="C117">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>353.783</v>
+        <v>427.736</v>
       </c>
       <c r="C118">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>365.636</v>
+        <v>428.806</v>
       </c>
       <c r="C119">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>367.822</v>
+        <v>424.886</v>
       </c>
       <c r="C120">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>372.627</v>
+        <v>421.186</v>
       </c>
       <c r="C121">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>350.281</v>
+        <v>390.986</v>
       </c>
       <c r="C122">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B123">
-        <v>353.634</v>
+        <v>387.153</v>
       </c>
       <c r="C123">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>352.326</v>
+        <v>385.34</v>
       </c>
       <c r="C124">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>349</v>
+        <v>383.057</v>
       </c>
       <c r="C125">
-        <v>425</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>333.488</v>
+        <v>396.008</v>
       </c>
       <c r="C126">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B127">
-        <v>315.239</v>
+        <v>390.956</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B128">
-        <v>311.112</v>
+        <v>385.578</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B129">
-        <v>296.144</v>
+        <v>381.935</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B130">
-        <v>352.736</v>
+        <v>398.335</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B131">
-        <v>334.458</v>
+        <v>424.336</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B132">
-        <v>312.659</v>
+        <v>450.86</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B133">
-        <v>293.556</v>
+        <v>477.957</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B134">
-        <v>267.896</v>
+        <v>527.635</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B135">
-        <v>267.081</v>
+        <v>565.8099999999999</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B136">
-        <v>265.93</v>
+        <v>605.367</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B137">
-        <v>265.037</v>
+        <v>643.782</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B138">
-        <v>267.003</v>
+        <v>686.043</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B139">
-        <v>273.659</v>
+        <v>715.658</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B140">
-        <v>283.963</v>
+        <v>746.902</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B141">
-        <v>290.565</v>
+        <v>775.378</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B142">
-        <v>300.388</v>
+        <v>803.016</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B143">
-        <v>307.036</v>
+        <v>819.1849999999999</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B144">
-        <v>314.525</v>
+        <v>836.769</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B145">
-        <v>322.696</v>
+        <v>853.852</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B146">
-        <v>331.373</v>
+        <v>846.442</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B147">
-        <v>342.06</v>
+        <v>859.053</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B148">
-        <v>350.969</v>
+        <v>871.553</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B149">
-        <v>357.787</v>
+        <v>883.837</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B150">
-        <v>367.339</v>
+        <v>915.248</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B151">
-        <v>374.498</v>
+        <v>934.417</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B152">
-        <v>384.824</v>
+        <v>950.341</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B153">
-        <v>395.169</v>
+        <v>968.828</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B154">
-        <v>411.268</v>
+        <v>974.8869999999999</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B155">
-        <v>419.463</v>
+        <v>999.831</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B156">
-        <v>427.417</v>
+        <v>1025.989</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B157">
-        <v>436.416</v>
+        <v>1050.72</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B158">
-        <v>406.384</v>
+        <v>1016.337</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B159">
-        <v>419.494</v>
+        <v>1040.03</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B160">
-        <v>434.199</v>
+        <v>1062.495</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B161">
-        <v>449.864</v>
+        <v>1085.884</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B162">
-        <v>479.821</v>
+        <v>1078.37</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B163">
-        <v>504.967</v>
+        <v>1098.622</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B164">
-        <v>529.746</v>
+        <v>1121.827</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B165">
-        <v>557.847</v>
+        <v>1143.388</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B166">
-        <v>527.186</v>
+        <v>1169.784</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B167">
-        <v>560.638</v>
+        <v>1199.123</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B168">
-        <v>594.8390000000001</v>
+        <v>1229.245</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B169">
-        <v>626.718</v>
+        <v>1259.277</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B170">
-        <v>657.622</v>
+        <v>1296.082</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B171">
-        <v>671.7910000000001</v>
+        <v>1307.346</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B172">
-        <v>686.817</v>
+        <v>1317.444</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B173">
-        <v>700.268</v>
+        <v>1327.783</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B174">
-        <v>705.28</v>
+        <v>1335.641</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B175">
-        <v>691.26</v>
+        <v>1331.747</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B176">
-        <v>676.254</v>
+        <v>1328.492</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B177">
-        <v>662.609</v>
+        <v>1325.969</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B178">
-        <v>632.788</v>
+        <v>1314.092</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B179">
-        <v>604.973</v>
+        <v>1303.502</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B180">
-        <v>577.023</v>
+        <v>1292.743</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B181">
-        <v>549.019</v>
+        <v>1281.853</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B182">
-        <v>515.9349999999999</v>
+        <v>1275.471</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B183">
-        <v>490.188</v>
+        <v>1262.754</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B184">
-        <v>465.018</v>
+        <v>1251.374</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B185">
-        <v>439.68</v>
+        <v>1239.93</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B186">
-        <v>412.635</v>
+        <v>1225.935</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B187">
-        <v>396.526</v>
+        <v>1214.907</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B188">
-        <v>380.483</v>
+        <v>1204.845</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B189">
-        <v>365.356</v>
+        <v>1194.266</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.03.20261</t>
-  </si>
-  <si>
-    <t>25.03.20262</t>
-  </si>
-  <si>
-    <t>25.03.20263</t>
-  </si>
-  <si>
-    <t>25.03.20264</t>
-  </si>
-  <si>
-    <t>25.03.20265</t>
-  </si>
-  <si>
-    <t>25.03.20266</t>
-  </si>
-  <si>
-    <t>25.03.20267</t>
-  </si>
-  <si>
-    <t>25.03.20268</t>
-  </si>
-  <si>
-    <t>25.03.20269</t>
-  </si>
-  <si>
-    <t>25.03.202610</t>
-  </si>
-  <si>
-    <t>25.03.202611</t>
-  </si>
-  <si>
-    <t>25.03.202612</t>
-  </si>
-  <si>
-    <t>25.03.202613</t>
-  </si>
-  <si>
-    <t>25.03.202614</t>
-  </si>
-  <si>
-    <t>25.03.202615</t>
-  </si>
-  <si>
-    <t>25.03.202616</t>
-  </si>
-  <si>
-    <t>25.03.202617</t>
-  </si>
-  <si>
-    <t>25.03.202618</t>
-  </si>
-  <si>
-    <t>25.03.202619</t>
-  </si>
-  <si>
-    <t>25.03.202620</t>
-  </si>
-  <si>
-    <t>25.03.202621</t>
-  </si>
-  <si>
-    <t>25.03.202622</t>
-  </si>
-  <si>
-    <t>25.03.202623</t>
-  </si>
-  <si>
-    <t>25.03.202624</t>
-  </si>
-  <si>
-    <t>25.03.202625</t>
-  </si>
-  <si>
-    <t>25.03.202626</t>
-  </si>
-  <si>
-    <t>25.03.202627</t>
-  </si>
-  <si>
-    <t>25.03.202628</t>
-  </si>
-  <si>
-    <t>25.03.202629</t>
-  </si>
-  <si>
-    <t>25.03.202630</t>
-  </si>
-  <si>
-    <t>25.03.202631</t>
-  </si>
-  <si>
-    <t>25.03.202632</t>
-  </si>
-  <si>
-    <t>25.03.202633</t>
-  </si>
-  <si>
-    <t>25.03.202634</t>
-  </si>
-  <si>
-    <t>25.03.202635</t>
-  </si>
-  <si>
-    <t>25.03.202636</t>
-  </si>
-  <si>
-    <t>25.03.202637</t>
-  </si>
-  <si>
-    <t>25.03.202638</t>
-  </si>
-  <si>
-    <t>25.03.202639</t>
-  </si>
-  <si>
-    <t>25.03.202640</t>
-  </si>
-  <si>
-    <t>25.03.202641</t>
-  </si>
-  <si>
-    <t>25.03.202642</t>
-  </si>
-  <si>
-    <t>25.03.202643</t>
-  </si>
-  <si>
-    <t>25.03.202644</t>
-  </si>
-  <si>
-    <t>25.03.202645</t>
-  </si>
-  <si>
-    <t>25.03.202646</t>
-  </si>
-  <si>
-    <t>25.03.202647</t>
-  </si>
-  <si>
-    <t>25.03.202648</t>
-  </si>
-  <si>
-    <t>25.03.202649</t>
-  </si>
-  <si>
-    <t>25.03.202650</t>
-  </si>
-  <si>
-    <t>25.03.202651</t>
-  </si>
-  <si>
-    <t>25.03.202652</t>
-  </si>
-  <si>
-    <t>25.03.202653</t>
-  </si>
-  <si>
-    <t>25.03.202654</t>
-  </si>
-  <si>
-    <t>25.03.202655</t>
-  </si>
-  <si>
-    <t>25.03.202656</t>
-  </si>
-  <si>
-    <t>25.03.202657</t>
-  </si>
-  <si>
-    <t>25.03.202658</t>
-  </si>
-  <si>
-    <t>25.03.202659</t>
-  </si>
-  <si>
-    <t>25.03.202660</t>
-  </si>
-  <si>
-    <t>25.03.202661</t>
-  </si>
-  <si>
-    <t>25.03.202662</t>
-  </si>
-  <si>
-    <t>25.03.202663</t>
-  </si>
-  <si>
-    <t>25.03.202664</t>
-  </si>
-  <si>
-    <t>25.03.202665</t>
-  </si>
-  <si>
-    <t>25.03.202666</t>
-  </si>
-  <si>
-    <t>25.03.202667</t>
-  </si>
-  <si>
-    <t>25.03.202668</t>
-  </si>
-  <si>
-    <t>25.03.202669</t>
-  </si>
-  <si>
-    <t>25.03.202670</t>
-  </si>
-  <si>
-    <t>25.03.202671</t>
-  </si>
-  <si>
-    <t>25.03.202672</t>
-  </si>
-  <si>
-    <t>25.03.202673</t>
-  </si>
-  <si>
-    <t>25.03.202674</t>
-  </si>
-  <si>
-    <t>25.03.202675</t>
-  </si>
-  <si>
-    <t>25.03.202676</t>
-  </si>
-  <si>
-    <t>25.03.202677</t>
-  </si>
-  <si>
-    <t>25.03.202678</t>
-  </si>
-  <si>
-    <t>25.03.202679</t>
-  </si>
-  <si>
-    <t>25.03.202680</t>
-  </si>
-  <si>
-    <t>25.03.202681</t>
-  </si>
-  <si>
-    <t>25.03.202682</t>
-  </si>
-  <si>
-    <t>25.03.202683</t>
-  </si>
-  <si>
-    <t>25.03.202684</t>
-  </si>
-  <si>
-    <t>25.03.202685</t>
-  </si>
-  <si>
-    <t>25.03.202686</t>
-  </si>
-  <si>
-    <t>25.03.202687</t>
-  </si>
-  <si>
-    <t>25.03.202688</t>
-  </si>
-  <si>
-    <t>25.03.202689</t>
-  </si>
-  <si>
-    <t>25.03.202690</t>
-  </si>
-  <si>
-    <t>25.03.202691</t>
-  </si>
-  <si>
-    <t>25.03.202692</t>
-  </si>
-  <si>
-    <t>25.03.202693</t>
-  </si>
-  <si>
-    <t>25.03.202694</t>
-  </si>
-  <si>
-    <t>25.03.202695</t>
-  </si>
-  <si>
-    <t>25.03.202696</t>
-  </si>
-  <si>
     <t>26.03.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>26.03.202696</t>
+  </si>
+  <si>
+    <t>27.03.20261</t>
+  </si>
+  <si>
+    <t>27.03.20262</t>
+  </si>
+  <si>
+    <t>27.03.20263</t>
+  </si>
+  <si>
+    <t>27.03.20264</t>
+  </si>
+  <si>
+    <t>27.03.20265</t>
+  </si>
+  <si>
+    <t>27.03.20266</t>
+  </si>
+  <si>
+    <t>27.03.20267</t>
+  </si>
+  <si>
+    <t>27.03.20268</t>
+  </si>
+  <si>
+    <t>27.03.20269</t>
+  </si>
+  <si>
+    <t>27.03.202610</t>
+  </si>
+  <si>
+    <t>27.03.202611</t>
+  </si>
+  <si>
+    <t>27.03.202612</t>
+  </si>
+  <si>
+    <t>27.03.202613</t>
+  </si>
+  <si>
+    <t>27.03.202614</t>
+  </si>
+  <si>
+    <t>27.03.202615</t>
+  </si>
+  <si>
+    <t>27.03.202616</t>
+  </si>
+  <si>
+    <t>27.03.202617</t>
+  </si>
+  <si>
+    <t>27.03.202618</t>
+  </si>
+  <si>
+    <t>27.03.202619</t>
+  </si>
+  <si>
+    <t>27.03.202620</t>
+  </si>
+  <si>
+    <t>27.03.202621</t>
+  </si>
+  <si>
+    <t>27.03.202622</t>
+  </si>
+  <si>
+    <t>27.03.202623</t>
+  </si>
+  <si>
+    <t>27.03.202624</t>
+  </si>
+  <si>
+    <t>27.03.202625</t>
+  </si>
+  <si>
+    <t>27.03.202626</t>
+  </si>
+  <si>
+    <t>27.03.202627</t>
+  </si>
+  <si>
+    <t>27.03.202628</t>
+  </si>
+  <si>
+    <t>27.03.202629</t>
+  </si>
+  <si>
+    <t>27.03.202630</t>
+  </si>
+  <si>
+    <t>27.03.202631</t>
+  </si>
+  <si>
+    <t>27.03.202632</t>
+  </si>
+  <si>
+    <t>27.03.202633</t>
+  </si>
+  <si>
+    <t>27.03.202634</t>
+  </si>
+  <si>
+    <t>27.03.202635</t>
+  </si>
+  <si>
+    <t>27.03.202636</t>
+  </si>
+  <si>
+    <t>27.03.202637</t>
+  </si>
+  <si>
+    <t>27.03.202638</t>
+  </si>
+  <si>
+    <t>27.03.202639</t>
+  </si>
+  <si>
+    <t>27.03.202640</t>
+  </si>
+  <si>
+    <t>27.03.202641</t>
+  </si>
+  <si>
+    <t>27.03.202642</t>
+  </si>
+  <si>
+    <t>27.03.202643</t>
+  </si>
+  <si>
+    <t>27.03.202644</t>
+  </si>
+  <si>
+    <t>27.03.202645</t>
+  </si>
+  <si>
+    <t>27.03.202646</t>
+  </si>
+  <si>
+    <t>27.03.202647</t>
+  </si>
+  <si>
+    <t>27.03.202648</t>
+  </si>
+  <si>
+    <t>27.03.202649</t>
+  </si>
+  <si>
+    <t>27.03.202650</t>
+  </si>
+  <si>
+    <t>27.03.202651</t>
+  </si>
+  <si>
+    <t>27.03.202652</t>
+  </si>
+  <si>
+    <t>27.03.202653</t>
+  </si>
+  <si>
+    <t>27.03.202654</t>
+  </si>
+  <si>
+    <t>27.03.202655</t>
+  </si>
+  <si>
+    <t>27.03.202656</t>
+  </si>
+  <si>
+    <t>27.03.202657</t>
+  </si>
+  <si>
+    <t>27.03.202658</t>
+  </si>
+  <si>
+    <t>27.03.202659</t>
+  </si>
+  <si>
+    <t>27.03.202660</t>
+  </si>
+  <si>
+    <t>27.03.202661</t>
+  </si>
+  <si>
+    <t>27.03.202662</t>
+  </si>
+  <si>
+    <t>27.03.202663</t>
+  </si>
+  <si>
+    <t>27.03.202664</t>
+  </si>
+  <si>
+    <t>27.03.202665</t>
+  </si>
+  <si>
+    <t>27.03.202666</t>
+  </si>
+  <si>
+    <t>27.03.202667</t>
+  </si>
+  <si>
+    <t>27.03.202668</t>
+  </si>
+  <si>
+    <t>27.03.202669</t>
+  </si>
+  <si>
+    <t>27.03.202670</t>
+  </si>
+  <si>
+    <t>27.03.202671</t>
+  </si>
+  <si>
+    <t>27.03.202672</t>
+  </si>
+  <si>
+    <t>27.03.202673</t>
+  </si>
+  <si>
+    <t>27.03.202674</t>
+  </si>
+  <si>
+    <t>27.03.202675</t>
+  </si>
+  <si>
+    <t>27.03.202676</t>
+  </si>
+  <si>
+    <t>27.03.202677</t>
+  </si>
+  <si>
+    <t>27.03.202678</t>
+  </si>
+  <si>
+    <t>27.03.202679</t>
+  </si>
+  <si>
+    <t>27.03.202680</t>
+  </si>
+  <si>
+    <t>27.03.202681</t>
+  </si>
+  <si>
+    <t>27.03.202682</t>
+  </si>
+  <si>
+    <t>27.03.202683</t>
+  </si>
+  <si>
+    <t>27.03.202684</t>
+  </si>
+  <si>
+    <t>27.03.202685</t>
+  </si>
+  <si>
+    <t>27.03.202686</t>
+  </si>
+  <si>
+    <t>27.03.202687</t>
+  </si>
+  <si>
+    <t>27.03.202688</t>
+  </si>
+  <si>
+    <t>27.03.202689</t>
+  </si>
+  <si>
+    <t>27.03.202690</t>
+  </si>
+  <si>
+    <t>27.03.202691</t>
+  </si>
+  <si>
+    <t>27.03.202692</t>
+  </si>
+  <si>
+    <t>27.03.202693</t>
+  </si>
+  <si>
+    <t>27.03.202694</t>
+  </si>
+  <si>
+    <t>27.03.202695</t>
+  </si>
+  <si>
+    <t>27.03.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B2">
-        <v>371.959</v>
+        <v>603.224</v>
       </c>
       <c r="C2">
-        <v>288</v>
+        <v>536</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46106.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B3">
-        <v>382.848</v>
+        <v>590.586</v>
       </c>
       <c r="C3">
-        <v>313</v>
+        <v>524</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46106.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B4">
-        <v>394.8</v>
+        <v>583.615</v>
       </c>
       <c r="C4">
-        <v>328</v>
+        <v>505</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46106.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B5">
-        <v>406.635</v>
+        <v>573.032</v>
       </c>
       <c r="C5">
-        <v>329</v>
+        <v>488</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46106.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B6">
-        <v>423.084</v>
+        <v>560</v>
       </c>
       <c r="C6">
-        <v>330</v>
+        <v>473</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46106.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B7">
-        <v>436.37</v>
+        <v>533.63</v>
       </c>
       <c r="C7">
-        <v>366</v>
+        <v>472</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46106.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B8">
-        <v>451.496</v>
+        <v>483.971</v>
       </c>
       <c r="C8">
-        <v>384</v>
+        <v>468</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46106.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B9">
-        <v>470.566</v>
+        <v>468.821</v>
       </c>
       <c r="C9">
-        <v>402</v>
+        <v>465</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46106.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B10">
-        <v>501.544</v>
+        <v>459.09</v>
       </c>
       <c r="C10">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46106.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B11">
-        <v>513.963</v>
+        <v>447.927</v>
       </c>
       <c r="C11">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46106.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B12">
-        <v>522.158</v>
+        <v>437.288</v>
       </c>
       <c r="C12">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46106.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B13">
-        <v>535.6319999999999</v>
+        <v>445.149</v>
       </c>
       <c r="C13">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46106.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B14">
-        <v>544.764</v>
+        <v>427.884</v>
       </c>
       <c r="C14">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46106.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B15">
-        <v>545.2089999999999</v>
+        <v>415.236</v>
       </c>
       <c r="C15">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46106.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B16">
-        <v>545.308</v>
+        <v>408.719</v>
       </c>
       <c r="C16">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46106.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B17">
-        <v>538.776</v>
+        <v>397.902</v>
       </c>
       <c r="C17">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46106.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B18">
-        <v>557.063</v>
+        <v>418.867</v>
       </c>
       <c r="C18">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46106.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B19">
-        <v>549.482</v>
+        <v>410.538</v>
       </c>
       <c r="C19">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46106.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B20">
-        <v>540.45</v>
+        <v>398.663</v>
       </c>
       <c r="C20">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46106.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B21">
-        <v>534.388</v>
+        <v>387.606</v>
       </c>
       <c r="C21">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46106.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B22">
-        <v>520.674</v>
+        <v>369.255</v>
       </c>
       <c r="C22">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46106.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B23">
-        <v>510.737</v>
+        <v>370.93</v>
       </c>
       <c r="C23">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46106.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B24">
-        <v>494.326</v>
+        <v>370.782</v>
       </c>
       <c r="C24">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46106.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B25">
-        <v>497.015</v>
+        <v>370.212</v>
       </c>
       <c r="C25">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46106.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B26">
-        <v>477.753</v>
+        <v>375.166</v>
       </c>
       <c r="C26">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46106.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B27">
-        <v>432.593</v>
+        <v>372.733</v>
       </c>
       <c r="C27">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46106.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B28">
-        <v>449.053</v>
+        <v>371.644</v>
       </c>
       <c r="C28">
-        <v>270</v>
+        <v>187</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46106.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B29">
-        <v>413.12</v>
+        <v>370.701</v>
       </c>
       <c r="C29">
-        <v>271</v>
+        <v>169</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46106.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B30">
-        <v>410.337</v>
+        <v>410.748</v>
       </c>
       <c r="C30">
-        <v>254</v>
+        <v>150</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46106.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B31">
-        <v>373.811</v>
+        <v>405.728</v>
       </c>
       <c r="C31">
-        <v>241</v>
+        <v>145</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46106.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B32">
-        <v>348.435</v>
+        <v>397.41</v>
       </c>
       <c r="C32">
-        <v>220</v>
+        <v>123</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46106.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B33">
-        <v>313.501</v>
+        <v>395.359</v>
       </c>
       <c r="C33">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46106.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B34">
-        <v>341.709</v>
+        <v>407.632</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46106.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B35">
-        <v>353.628</v>
+        <v>424.403</v>
       </c>
       <c r="C35">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46106.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B36">
-        <v>362.578</v>
+        <v>450.027</v>
       </c>
       <c r="C36">
-        <v>227</v>
+        <v>154</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46106.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B37">
-        <v>369.198</v>
+        <v>477.074</v>
       </c>
       <c r="C37">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46106.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B38">
-        <v>353.736</v>
+        <v>502.935</v>
       </c>
       <c r="C38">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46106.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B39">
-        <v>360.33</v>
+        <v>541.11</v>
       </c>
       <c r="C39">
-        <v>290</v>
+        <v>398</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46106.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B40">
-        <v>366.873</v>
+        <v>580.667</v>
       </c>
       <c r="C40">
-        <v>299</v>
+        <v>493</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46106.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B41">
-        <v>371.805</v>
+        <v>619.082</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46106.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B42">
-        <v>383.04</v>
+        <v>688.043</v>
       </c>
       <c r="C42">
-        <v>320</v>
+        <v>638</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46106.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B43">
-        <v>378.354</v>
+        <v>717.658</v>
       </c>
       <c r="C43">
-        <v>318</v>
+        <v>699</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46106.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B44">
-        <v>374.036</v>
+        <v>748.902</v>
       </c>
       <c r="C44">
-        <v>302</v>
+        <v>737</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46106.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B45">
-        <v>368.571</v>
+        <v>777.378</v>
       </c>
       <c r="C45">
-        <v>291</v>
+        <v>759</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46106.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B46">
-        <v>355.303</v>
+        <v>806.216</v>
       </c>
       <c r="C46">
-        <v>284</v>
+        <v>800</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46106.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B47">
-        <v>344.869</v>
+        <v>822.385</v>
       </c>
       <c r="C47">
-        <v>280</v>
+        <v>805</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46106.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B48">
-        <v>335.39</v>
+        <v>839.9690000000001</v>
       </c>
       <c r="C48">
-        <v>269</v>
+        <v>832</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46106.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B49">
-        <v>327.342</v>
+        <v>857.052</v>
       </c>
       <c r="C49">
-        <v>266</v>
+        <v>812</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46106.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B50">
-        <v>296.039</v>
+        <v>848.842</v>
       </c>
       <c r="C50">
-        <v>252</v>
+        <v>808</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46106.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B51">
-        <v>286.54</v>
+        <v>861.453</v>
       </c>
       <c r="C51">
-        <v>224</v>
+        <v>788</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46106.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B52">
-        <v>276.808</v>
+        <v>873.953</v>
       </c>
       <c r="C52">
-        <v>223</v>
+        <v>781</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46106.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B53">
-        <v>266.088</v>
+        <v>886.237</v>
       </c>
       <c r="C53">
-        <v>207</v>
+        <v>756</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46106.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B54">
-        <v>243.631</v>
+        <v>921.248</v>
       </c>
       <c r="C54">
-        <v>186</v>
+        <v>757</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46106.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B55">
-        <v>235.721</v>
+        <v>940.417</v>
       </c>
       <c r="C55">
-        <v>173</v>
+        <v>768</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46106.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B56">
-        <v>228.031</v>
+        <v>956.341</v>
       </c>
       <c r="C56">
-        <v>167</v>
+        <v>767</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46106.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B57">
-        <v>220.143</v>
+        <v>974.828</v>
       </c>
       <c r="C57">
-        <v>145</v>
+        <v>788</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46106.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B58">
-        <v>184.698</v>
+        <v>980.787</v>
       </c>
       <c r="C58">
-        <v>138</v>
+        <v>793</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46106.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B59">
-        <v>180.366</v>
+        <v>1005.731</v>
       </c>
       <c r="C59">
-        <v>136</v>
+        <v>822</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46106.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B60">
-        <v>174.606</v>
+        <v>1031.889</v>
       </c>
       <c r="C60">
-        <v>128</v>
+        <v>830</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46106.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B61">
-        <v>169.092</v>
+        <v>1056.62</v>
       </c>
       <c r="C61">
-        <v>126</v>
+        <v>837</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46106.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B62">
-        <v>159.543</v>
+        <v>1016.337</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>830</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46106.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B63">
-        <v>153.695</v>
+        <v>1040.03</v>
       </c>
       <c r="C63">
-        <v>137</v>
+        <v>857</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46106.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B64">
-        <v>147.643</v>
+        <v>1062.495</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46106.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B65">
-        <v>142.065</v>
+        <v>1085.884</v>
       </c>
       <c r="C65">
-        <v>129</v>
+        <v>865</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46106.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B66">
-        <v>144.703</v>
+        <v>1078.37</v>
       </c>
       <c r="C66">
-        <v>123</v>
+        <v>922</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46106.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B67">
-        <v>141.214</v>
+        <v>1098.622</v>
       </c>
       <c r="C67">
-        <v>116</v>
+        <v>987</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46106.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B68">
-        <v>135.638</v>
+        <v>1121.827</v>
       </c>
       <c r="C68">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46106.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B69">
-        <v>132.296</v>
+        <v>1143.388</v>
       </c>
       <c r="C69">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46106.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B70">
-        <v>138.121</v>
+        <v>1170.084</v>
       </c>
       <c r="C70">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46106.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B71">
-        <v>144.823</v>
+        <v>1199.423</v>
       </c>
       <c r="C71">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46106.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B72">
-        <v>153.288</v>
+        <v>1229.545</v>
       </c>
       <c r="C72">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46106.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B73">
-        <v>162.555</v>
+        <v>1259.577</v>
       </c>
       <c r="C73">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46106.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B74">
-        <v>183.428</v>
+        <v>1296.082</v>
       </c>
       <c r="C74">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46106.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B75">
-        <v>198.58</v>
+        <v>1307.346</v>
       </c>
       <c r="C75">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46106.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B76">
-        <v>213.475</v>
+        <v>1317.444</v>
       </c>
       <c r="C76">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46106.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B77">
-        <v>228.641</v>
+        <v>1327.783</v>
       </c>
       <c r="C77">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46106.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B78">
-        <v>252.652</v>
+        <v>1335.641</v>
       </c>
       <c r="C78">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46106.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B79">
-        <v>264.618</v>
+        <v>1331.747</v>
       </c>
       <c r="C79">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46106.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B80">
-        <v>277.151</v>
+        <v>1328.492</v>
       </c>
       <c r="C80">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46106.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B81">
-        <v>289.788</v>
+        <v>1325.969</v>
       </c>
       <c r="C81">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46106.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B82">
-        <v>314.558</v>
+        <v>1314.092</v>
       </c>
       <c r="C82">
-        <v>427</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46106.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B83">
-        <v>321.295</v>
+        <v>1303.502</v>
       </c>
       <c r="C83">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46106.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B84">
-        <v>329.836</v>
+        <v>1292.743</v>
       </c>
       <c r="C84">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46106.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B85">
-        <v>337.043</v>
+        <v>1281.853</v>
       </c>
       <c r="C85">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46106.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B86">
-        <v>340.355</v>
+        <v>1275.471</v>
       </c>
       <c r="C86">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46106.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B87">
-        <v>350.127</v>
+        <v>1262.754</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46106.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B88">
-        <v>360.816</v>
+        <v>1251.374</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46106.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B89">
-        <v>371.344</v>
+        <v>1239.93</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46106.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B90">
-        <v>376.092</v>
+        <v>1225.935</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2501,10 +2501,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46106.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B91">
-        <v>381.059</v>
+        <v>1214.907</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46106.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B92">
-        <v>385.83</v>
+        <v>1204.845</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46106.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B93">
-        <v>390.789</v>
+        <v>1194.266</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46106.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B94">
-        <v>421.804</v>
+        <v>1174.411</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46106.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B95">
-        <v>420.4</v>
+        <v>1157.848</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46106.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B96">
-        <v>388.853</v>
+        <v>1142.16</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46106.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B97">
-        <v>387.668</v>
+        <v>1126.168</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B98">
-        <v>612.924</v>
+        <v>1016.396</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46107.01041666666</v>
+        <v>46108.01041666666</v>
       </c>
       <c r="B99">
-        <v>604.886</v>
+        <v>998.72</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46107.02083333334</v>
+        <v>46108.02083333334</v>
       </c>
       <c r="B100">
-        <v>596.915</v>
+        <v>980.487</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2671,10 +2671,10 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46107.03125</v>
+        <v>46108.03125</v>
       </c>
       <c r="B101">
-        <v>588.1319999999999</v>
+        <v>962.099</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46107.04166666666</v>
+        <v>46108.04166666666</v>
       </c>
       <c r="B102">
-        <v>573.1</v>
+        <v>940.331</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46107.05208333334</v>
+        <v>46108.05208333334</v>
       </c>
       <c r="B103">
-        <v>558.83</v>
+        <v>933.647</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46107.0625</v>
+        <v>46108.0625</v>
       </c>
       <c r="B104">
-        <v>515.771</v>
+        <v>928.147</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46107.07291666666</v>
+        <v>46108.07291666666</v>
       </c>
       <c r="B105">
-        <v>500.421</v>
+        <v>922.9829999999999</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46107.08333333334</v>
+        <v>46108.08333333334</v>
       </c>
       <c r="B106">
-        <v>483.99</v>
+        <v>914.4059999999999</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46107.09375</v>
+        <v>46108.09375</v>
       </c>
       <c r="B107">
-        <v>475.527</v>
+        <v>906.4589999999999</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46107.10416666666</v>
+        <v>46108.10416666666</v>
       </c>
       <c r="B108">
-        <v>467.288</v>
+        <v>897.6</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46107.11458333334</v>
+        <v>46108.11458333334</v>
       </c>
       <c r="B109">
-        <v>474.649</v>
+        <v>889.276</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46107.125</v>
+        <v>46108.125</v>
       </c>
       <c r="B110">
-        <v>475.584</v>
+        <v>883.321</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46107.13541666666</v>
+        <v>46108.13541666666</v>
       </c>
       <c r="B111">
-        <v>436.536</v>
+        <v>883.217</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46107.14583333334</v>
+        <v>46108.14583333334</v>
       </c>
       <c r="B112">
-        <v>460.419</v>
+        <v>882.655</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46107.15625</v>
+        <v>46108.15625</v>
       </c>
       <c r="B113">
-        <v>451.902</v>
+        <v>884.51</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46107.16666666666</v>
+        <v>46108.16666666666</v>
       </c>
       <c r="B114">
-        <v>468.267</v>
+        <v>915.755</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46107.17708333334</v>
+        <v>46108.17708333334</v>
       </c>
       <c r="B115">
-        <v>458.138</v>
+        <v>925.0170000000001</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46107.1875</v>
+        <v>46108.1875</v>
       </c>
       <c r="B116">
-        <v>448.863</v>
+        <v>935.505</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46107.19791666666</v>
+        <v>46108.19791666666</v>
       </c>
       <c r="B117">
-        <v>440.506</v>
+        <v>945.02</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46107.20833333334</v>
+        <v>46108.20833333334</v>
       </c>
       <c r="B118">
-        <v>427.736</v>
+        <v>960.133</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46107.21875</v>
+        <v>46108.21875</v>
       </c>
       <c r="B119">
-        <v>428.806</v>
+        <v>973.886</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46107.22916666666</v>
+        <v>46108.22916666666</v>
       </c>
       <c r="B120">
-        <v>424.886</v>
+        <v>987.67</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3011,10 +3011,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46107.23958333334</v>
+        <v>46108.23958333334</v>
       </c>
       <c r="B121">
-        <v>421.186</v>
+        <v>1000.842</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46107.25</v>
+        <v>46108.25</v>
       </c>
       <c r="B122">
-        <v>390.986</v>
+        <v>1017.68</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46107.26041666666</v>
+        <v>46108.26041666666</v>
       </c>
       <c r="B123">
-        <v>387.153</v>
+        <v>1034.912</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46107.27083333334</v>
+        <v>46108.27083333334</v>
       </c>
       <c r="B124">
-        <v>385.34</v>
+        <v>1047.495</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46107.28125</v>
+        <v>46108.28125</v>
       </c>
       <c r="B125">
-        <v>383.057</v>
+        <v>1066.943</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -3096,10 +3096,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46107.29166666666</v>
+        <v>46108.29166666666</v>
       </c>
       <c r="B126">
-        <v>396.008</v>
+        <v>1100.773</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46107.30208333334</v>
+        <v>46108.30208333334</v>
       </c>
       <c r="B127">
-        <v>390.956</v>
+        <v>1126.003</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46107.3125</v>
+        <v>46108.3125</v>
       </c>
       <c r="B128">
-        <v>385.578</v>
+        <v>1149.723</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46107.32291666666</v>
+        <v>46108.32291666666</v>
       </c>
       <c r="B129">
-        <v>381.935</v>
+        <v>1176.014</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46107.33333333334</v>
+        <v>46108.33333333334</v>
       </c>
       <c r="B130">
-        <v>398.335</v>
+        <v>1181.385</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46107.34375</v>
+        <v>46108.34375</v>
       </c>
       <c r="B131">
-        <v>424.336</v>
+        <v>1199.655</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46107.35416666666</v>
+        <v>46108.35416666666</v>
       </c>
       <c r="B132">
-        <v>450.86</v>
+        <v>1219.439</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46107.36458333334</v>
+        <v>46108.36458333334</v>
       </c>
       <c r="B133">
-        <v>477.957</v>
+        <v>1236.568</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46107.375</v>
+        <v>46108.375</v>
       </c>
       <c r="B134">
-        <v>527.635</v>
+        <v>1375.716</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46107.38541666666</v>
+        <v>46108.38541666666</v>
       </c>
       <c r="B135">
-        <v>565.8099999999999</v>
+        <v>1389.339</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46107.39583333334</v>
+        <v>46108.39583333334</v>
       </c>
       <c r="B136">
-        <v>605.367</v>
+        <v>1402.547</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46107.40625</v>
+        <v>46108.40625</v>
       </c>
       <c r="B137">
-        <v>643.782</v>
+        <v>1416.079</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46107.41666666666</v>
+        <v>46108.41666666666</v>
       </c>
       <c r="B138">
-        <v>686.043</v>
+        <v>1507.287</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46107.42708333334</v>
+        <v>46108.42708333334</v>
       </c>
       <c r="B139">
-        <v>715.658</v>
+        <v>1515.984</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46107.4375</v>
+        <v>46108.4375</v>
       </c>
       <c r="B140">
-        <v>746.902</v>
+        <v>1523.82</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46107.44791666666</v>
+        <v>46108.44791666666</v>
       </c>
       <c r="B141">
-        <v>775.378</v>
+        <v>1533.2</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46107.45833333334</v>
+        <v>46108.45833333334</v>
       </c>
       <c r="B142">
-        <v>803.016</v>
+        <v>1547.758</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46107.46875</v>
+        <v>46108.46875</v>
       </c>
       <c r="B143">
-        <v>819.1849999999999</v>
+        <v>1558.586</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46107.47916666666</v>
+        <v>46108.47916666666</v>
       </c>
       <c r="B144">
-        <v>836.769</v>
+        <v>1570.279</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46107.48958333334</v>
+        <v>46108.48958333334</v>
       </c>
       <c r="B145">
-        <v>853.852</v>
+        <v>1582.034</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46107.5</v>
+        <v>46108.5</v>
       </c>
       <c r="B146">
-        <v>846.442</v>
+        <v>1561.704</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46107.51041666666</v>
+        <v>46108.51041666666</v>
       </c>
       <c r="B147">
-        <v>859.053</v>
+        <v>1579.949</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46107.52083333334</v>
+        <v>46108.52083333334</v>
       </c>
       <c r="B148">
-        <v>871.553</v>
+        <v>1597.993</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46107.53125</v>
+        <v>46108.53125</v>
       </c>
       <c r="B149">
-        <v>883.837</v>
+        <v>1617.352</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46107.54166666666</v>
+        <v>46108.54166666666</v>
       </c>
       <c r="B150">
-        <v>915.248</v>
+        <v>1579.449</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46107.55208333334</v>
+        <v>46108.55208333334</v>
       </c>
       <c r="B151">
-        <v>934.417</v>
+        <v>1604.255</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46107.5625</v>
+        <v>46108.5625</v>
       </c>
       <c r="B152">
-        <v>950.341</v>
+        <v>1625.84</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46107.57291666666</v>
+        <v>46108.57291666666</v>
       </c>
       <c r="B153">
-        <v>968.828</v>
+        <v>1651.096</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46107.58333333334</v>
+        <v>46108.58333333334</v>
       </c>
       <c r="B154">
-        <v>974.8869999999999</v>
+        <v>1575.59</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46107.59375</v>
+        <v>46108.59375</v>
       </c>
       <c r="B155">
-        <v>999.831</v>
+        <v>1600.074</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46107.60416666666</v>
+        <v>46108.60416666666</v>
       </c>
       <c r="B156">
-        <v>1025.989</v>
+        <v>1622.606</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46107.61458333334</v>
+        <v>46108.61458333334</v>
       </c>
       <c r="B157">
-        <v>1050.72</v>
+        <v>1647.792</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46107.625</v>
+        <v>46108.625</v>
       </c>
       <c r="B158">
-        <v>1016.337</v>
+        <v>1691.042</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46107.63541666666</v>
+        <v>46108.63541666666</v>
       </c>
       <c r="B159">
-        <v>1040.03</v>
+        <v>1707.793</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46107.64583333334</v>
+        <v>46108.64583333334</v>
       </c>
       <c r="B160">
-        <v>1062.495</v>
+        <v>1721.416</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46107.65625</v>
+        <v>46108.65625</v>
       </c>
       <c r="B161">
-        <v>1085.884</v>
+        <v>1737.038</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46107.66666666666</v>
+        <v>46108.66666666666</v>
       </c>
       <c r="B162">
-        <v>1078.37</v>
+        <v>1702.702</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46107.67708333334</v>
+        <v>46108.67708333334</v>
       </c>
       <c r="B163">
-        <v>1098.622</v>
+        <v>1697.743</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46107.6875</v>
+        <v>46108.6875</v>
       </c>
       <c r="B164">
-        <v>1121.827</v>
+        <v>1702.46</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46107.69791666666</v>
+        <v>46108.69791666666</v>
       </c>
       <c r="B165">
-        <v>1143.388</v>
+        <v>1698.749</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46107.70833333334</v>
+        <v>46108.70833333334</v>
       </c>
       <c r="B166">
-        <v>1169.784</v>
+        <v>1692.219</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46107.71875</v>
+        <v>46108.71875</v>
       </c>
       <c r="B167">
-        <v>1199.123</v>
+        <v>1684.263</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46107.72916666666</v>
+        <v>46108.72916666666</v>
       </c>
       <c r="B168">
-        <v>1229.245</v>
+        <v>1682.341</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46107.73958333334</v>
+        <v>46108.73958333334</v>
       </c>
       <c r="B169">
-        <v>1259.277</v>
+        <v>1672.744</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46107.75</v>
+        <v>46108.75</v>
       </c>
       <c r="B170">
-        <v>1296.082</v>
+        <v>1654.802</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46107.76041666666</v>
+        <v>46108.76041666666</v>
       </c>
       <c r="B171">
-        <v>1307.346</v>
+        <v>1641.173</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46107.77083333334</v>
+        <v>46108.77083333334</v>
       </c>
       <c r="B172">
-        <v>1317.444</v>
+        <v>1627.922</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46107.78125</v>
+        <v>46108.78125</v>
       </c>
       <c r="B173">
-        <v>1327.783</v>
+        <v>1614.12</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46107.79166666666</v>
+        <v>46108.79166666666</v>
       </c>
       <c r="B174">
-        <v>1335.641</v>
+        <v>1615.434</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46107.80208333334</v>
+        <v>46108.80208333334</v>
       </c>
       <c r="B175">
-        <v>1331.747</v>
+        <v>1606.372</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46107.8125</v>
+        <v>46108.8125</v>
       </c>
       <c r="B176">
-        <v>1328.492</v>
+        <v>1599.104</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46107.82291666666</v>
+        <v>46108.82291666666</v>
       </c>
       <c r="B177">
-        <v>1325.969</v>
+        <v>1591.135</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46107.83333333334</v>
+        <v>46108.83333333334</v>
       </c>
       <c r="B178">
-        <v>1314.092</v>
+        <v>1587.419</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46107.84375</v>
+        <v>46108.84375</v>
       </c>
       <c r="B179">
-        <v>1303.502</v>
+        <v>1584.608</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46107.85416666666</v>
+        <v>46108.85416666666</v>
       </c>
       <c r="B180">
-        <v>1292.743</v>
+        <v>1581.542</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46107.86458333334</v>
+        <v>46108.86458333334</v>
       </c>
       <c r="B181">
-        <v>1281.853</v>
+        <v>1578.763</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46107.875</v>
+        <v>46108.875</v>
       </c>
       <c r="B182">
-        <v>1275.471</v>
+        <v>1563.951</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46107.88541666666</v>
+        <v>46108.88541666666</v>
       </c>
       <c r="B183">
-        <v>1262.754</v>
+        <v>1549.546</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46107.89583333334</v>
+        <v>46108.89583333334</v>
       </c>
       <c r="B184">
-        <v>1251.374</v>
+        <v>1535.407</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46107.90625</v>
+        <v>46108.90625</v>
       </c>
       <c r="B185">
-        <v>1239.93</v>
+        <v>1520.646</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46107.91666666666</v>
+        <v>46108.91666666666</v>
       </c>
       <c r="B186">
-        <v>1225.935</v>
+        <v>1503.614</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46107.92708333334</v>
+        <v>46108.92708333334</v>
       </c>
       <c r="B187">
-        <v>1214.907</v>
+        <v>1483.037</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46107.9375</v>
+        <v>46108.9375</v>
       </c>
       <c r="B188">
-        <v>1204.845</v>
+        <v>1463.039</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46107.94791666666</v>
+        <v>46108.94791666666</v>
       </c>
       <c r="B189">
-        <v>1194.266</v>
+        <v>1440.538</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46107.95833333334</v>
+        <v>46108.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46107.96875</v>
+        <v>46108.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46107.97916666666</v>
+        <v>46108.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46107.98958333334</v>
+        <v>46108.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.04.20261</t>
-  </si>
-  <si>
-    <t>09.04.20262</t>
-  </si>
-  <si>
-    <t>09.04.20263</t>
-  </si>
-  <si>
-    <t>09.04.20264</t>
-  </si>
-  <si>
-    <t>09.04.20265</t>
-  </si>
-  <si>
-    <t>09.04.20266</t>
-  </si>
-  <si>
-    <t>09.04.20267</t>
-  </si>
-  <si>
-    <t>09.04.20268</t>
-  </si>
-  <si>
-    <t>09.04.20269</t>
-  </si>
-  <si>
-    <t>09.04.202610</t>
-  </si>
-  <si>
-    <t>09.04.202611</t>
-  </si>
-  <si>
-    <t>09.04.202612</t>
-  </si>
-  <si>
-    <t>09.04.202613</t>
-  </si>
-  <si>
-    <t>09.04.202614</t>
-  </si>
-  <si>
-    <t>09.04.202615</t>
-  </si>
-  <si>
-    <t>09.04.202616</t>
-  </si>
-  <si>
-    <t>09.04.202617</t>
-  </si>
-  <si>
-    <t>09.04.202618</t>
-  </si>
-  <si>
-    <t>09.04.202619</t>
-  </si>
-  <si>
-    <t>09.04.202620</t>
-  </si>
-  <si>
-    <t>09.04.202621</t>
-  </si>
-  <si>
-    <t>09.04.202622</t>
-  </si>
-  <si>
-    <t>09.04.202623</t>
-  </si>
-  <si>
-    <t>09.04.202624</t>
-  </si>
-  <si>
-    <t>09.04.202625</t>
-  </si>
-  <si>
-    <t>09.04.202626</t>
-  </si>
-  <si>
-    <t>09.04.202627</t>
-  </si>
-  <si>
-    <t>09.04.202628</t>
-  </si>
-  <si>
-    <t>09.04.202629</t>
-  </si>
-  <si>
-    <t>09.04.202630</t>
-  </si>
-  <si>
-    <t>09.04.202631</t>
-  </si>
-  <si>
-    <t>09.04.202632</t>
-  </si>
-  <si>
-    <t>09.04.202633</t>
-  </si>
-  <si>
-    <t>09.04.202634</t>
-  </si>
-  <si>
-    <t>09.04.202635</t>
-  </si>
-  <si>
-    <t>09.04.202636</t>
-  </si>
-  <si>
-    <t>09.04.202637</t>
-  </si>
-  <si>
-    <t>09.04.202638</t>
-  </si>
-  <si>
-    <t>09.04.202639</t>
-  </si>
-  <si>
-    <t>09.04.202640</t>
-  </si>
-  <si>
-    <t>09.04.202641</t>
-  </si>
-  <si>
-    <t>09.04.202642</t>
-  </si>
-  <si>
-    <t>09.04.202643</t>
-  </si>
-  <si>
-    <t>09.04.202644</t>
-  </si>
-  <si>
-    <t>09.04.202645</t>
-  </si>
-  <si>
-    <t>09.04.202646</t>
-  </si>
-  <si>
-    <t>09.04.202647</t>
-  </si>
-  <si>
-    <t>09.04.202648</t>
-  </si>
-  <si>
-    <t>09.04.202649</t>
-  </si>
-  <si>
-    <t>09.04.202650</t>
-  </si>
-  <si>
-    <t>09.04.202651</t>
-  </si>
-  <si>
-    <t>09.04.202652</t>
-  </si>
-  <si>
-    <t>09.04.202653</t>
-  </si>
-  <si>
-    <t>09.04.202654</t>
-  </si>
-  <si>
-    <t>09.04.202655</t>
-  </si>
-  <si>
-    <t>09.04.202656</t>
-  </si>
-  <si>
-    <t>09.04.202657</t>
-  </si>
-  <si>
-    <t>09.04.202658</t>
-  </si>
-  <si>
-    <t>09.04.202659</t>
-  </si>
-  <si>
-    <t>09.04.202660</t>
-  </si>
-  <si>
-    <t>09.04.202661</t>
-  </si>
-  <si>
-    <t>09.04.202662</t>
-  </si>
-  <si>
-    <t>09.04.202663</t>
-  </si>
-  <si>
-    <t>09.04.202664</t>
-  </si>
-  <si>
-    <t>09.04.202665</t>
-  </si>
-  <si>
-    <t>09.04.202666</t>
-  </si>
-  <si>
-    <t>09.04.202667</t>
-  </si>
-  <si>
-    <t>09.04.202668</t>
-  </si>
-  <si>
-    <t>09.04.202669</t>
-  </si>
-  <si>
-    <t>09.04.202670</t>
-  </si>
-  <si>
-    <t>09.04.202671</t>
-  </si>
-  <si>
-    <t>09.04.202672</t>
-  </si>
-  <si>
-    <t>09.04.202673</t>
-  </si>
-  <si>
-    <t>09.04.202674</t>
-  </si>
-  <si>
-    <t>09.04.202675</t>
-  </si>
-  <si>
-    <t>09.04.202676</t>
-  </si>
-  <si>
-    <t>09.04.202677</t>
-  </si>
-  <si>
-    <t>09.04.202678</t>
-  </si>
-  <si>
-    <t>09.04.202679</t>
-  </si>
-  <si>
-    <t>09.04.202680</t>
-  </si>
-  <si>
-    <t>09.04.202681</t>
-  </si>
-  <si>
-    <t>09.04.202682</t>
-  </si>
-  <si>
-    <t>09.04.202683</t>
-  </si>
-  <si>
-    <t>09.04.202684</t>
-  </si>
-  <si>
-    <t>09.04.202685</t>
-  </si>
-  <si>
-    <t>09.04.202686</t>
-  </si>
-  <si>
-    <t>09.04.202687</t>
-  </si>
-  <si>
-    <t>09.04.202688</t>
-  </si>
-  <si>
-    <t>09.04.202689</t>
-  </si>
-  <si>
-    <t>09.04.202690</t>
-  </si>
-  <si>
-    <t>09.04.202691</t>
-  </si>
-  <si>
-    <t>09.04.202692</t>
-  </si>
-  <si>
-    <t>09.04.202693</t>
-  </si>
-  <si>
-    <t>09.04.202694</t>
-  </si>
-  <si>
-    <t>09.04.202695</t>
-  </si>
-  <si>
-    <t>09.04.202696</t>
-  </si>
-  <si>
-    <t>10.04.20261</t>
-  </si>
-  <si>
-    <t>10.04.20262</t>
-  </si>
-  <si>
-    <t>10.04.20263</t>
-  </si>
-  <si>
-    <t>10.04.20264</t>
-  </si>
-  <si>
-    <t>10.04.20265</t>
-  </si>
-  <si>
-    <t>10.04.20266</t>
-  </si>
-  <si>
-    <t>10.04.20267</t>
-  </si>
-  <si>
-    <t>10.04.20268</t>
-  </si>
-  <si>
-    <t>10.04.20269</t>
-  </si>
-  <si>
-    <t>10.04.202610</t>
-  </si>
-  <si>
-    <t>10.04.202611</t>
-  </si>
-  <si>
-    <t>10.04.202612</t>
-  </si>
-  <si>
-    <t>10.04.202613</t>
-  </si>
-  <si>
-    <t>10.04.202614</t>
-  </si>
-  <si>
-    <t>10.04.202615</t>
-  </si>
-  <si>
-    <t>10.04.202616</t>
-  </si>
-  <si>
-    <t>10.04.202617</t>
-  </si>
-  <si>
-    <t>10.04.202618</t>
-  </si>
-  <si>
-    <t>10.04.202619</t>
-  </si>
-  <si>
-    <t>10.04.202620</t>
-  </si>
-  <si>
-    <t>10.04.202621</t>
-  </si>
-  <si>
-    <t>10.04.202622</t>
-  </si>
-  <si>
-    <t>10.04.202623</t>
-  </si>
-  <si>
-    <t>10.04.202624</t>
-  </si>
-  <si>
-    <t>10.04.202625</t>
-  </si>
-  <si>
-    <t>10.04.202626</t>
-  </si>
-  <si>
-    <t>10.04.202627</t>
-  </si>
-  <si>
-    <t>10.04.202628</t>
-  </si>
-  <si>
-    <t>10.04.202629</t>
-  </si>
-  <si>
-    <t>10.04.202630</t>
-  </si>
-  <si>
-    <t>10.04.202631</t>
-  </si>
-  <si>
-    <t>10.04.202632</t>
-  </si>
-  <si>
-    <t>10.04.202633</t>
-  </si>
-  <si>
-    <t>10.04.202634</t>
-  </si>
-  <si>
-    <t>10.04.202635</t>
-  </si>
-  <si>
-    <t>10.04.202636</t>
-  </si>
-  <si>
-    <t>10.04.202637</t>
-  </si>
-  <si>
-    <t>10.04.202638</t>
-  </si>
-  <si>
-    <t>10.04.202639</t>
-  </si>
-  <si>
-    <t>10.04.202640</t>
-  </si>
-  <si>
-    <t>10.04.202641</t>
-  </si>
-  <si>
-    <t>10.04.202642</t>
-  </si>
-  <si>
-    <t>10.04.202643</t>
-  </si>
-  <si>
-    <t>10.04.202644</t>
-  </si>
-  <si>
-    <t>10.04.202645</t>
-  </si>
-  <si>
-    <t>10.04.202646</t>
-  </si>
-  <si>
-    <t>10.04.202647</t>
-  </si>
-  <si>
-    <t>10.04.202648</t>
-  </si>
-  <si>
-    <t>10.04.202649</t>
-  </si>
-  <si>
-    <t>10.04.202650</t>
-  </si>
-  <si>
-    <t>10.04.202651</t>
-  </si>
-  <si>
-    <t>10.04.202652</t>
-  </si>
-  <si>
-    <t>10.04.202653</t>
-  </si>
-  <si>
-    <t>10.04.202654</t>
-  </si>
-  <si>
-    <t>10.04.202655</t>
-  </si>
-  <si>
-    <t>10.04.202656</t>
-  </si>
-  <si>
-    <t>10.04.202657</t>
-  </si>
-  <si>
-    <t>10.04.202658</t>
-  </si>
-  <si>
-    <t>10.04.202659</t>
-  </si>
-  <si>
-    <t>10.04.202660</t>
-  </si>
-  <si>
-    <t>10.04.202661</t>
-  </si>
-  <si>
-    <t>10.04.202662</t>
-  </si>
-  <si>
-    <t>10.04.202663</t>
-  </si>
-  <si>
-    <t>10.04.202664</t>
-  </si>
-  <si>
-    <t>10.04.202665</t>
-  </si>
-  <si>
-    <t>10.04.202666</t>
-  </si>
-  <si>
-    <t>10.04.202667</t>
-  </si>
-  <si>
-    <t>10.04.202668</t>
-  </si>
-  <si>
-    <t>10.04.202669</t>
-  </si>
-  <si>
-    <t>10.04.202670</t>
-  </si>
-  <si>
-    <t>10.04.202671</t>
-  </si>
-  <si>
-    <t>10.04.202672</t>
-  </si>
-  <si>
-    <t>10.04.202673</t>
-  </si>
-  <si>
-    <t>10.04.202674</t>
-  </si>
-  <si>
-    <t>10.04.202675</t>
-  </si>
-  <si>
-    <t>10.04.202676</t>
-  </si>
-  <si>
-    <t>10.04.202677</t>
-  </si>
-  <si>
-    <t>10.04.202678</t>
-  </si>
-  <si>
-    <t>10.04.202679</t>
-  </si>
-  <si>
-    <t>10.04.202680</t>
-  </si>
-  <si>
-    <t>10.04.202681</t>
-  </si>
-  <si>
-    <t>10.04.202682</t>
-  </si>
-  <si>
-    <t>10.04.202683</t>
-  </si>
-  <si>
-    <t>10.04.202684</t>
-  </si>
-  <si>
-    <t>10.04.202685</t>
-  </si>
-  <si>
-    <t>10.04.202686</t>
-  </si>
-  <si>
-    <t>10.04.202687</t>
-  </si>
-  <si>
-    <t>10.04.202688</t>
-  </si>
-  <si>
-    <t>10.04.202689</t>
-  </si>
-  <si>
-    <t>10.04.202690</t>
-  </si>
-  <si>
-    <t>10.04.202691</t>
-  </si>
-  <si>
-    <t>10.04.202692</t>
-  </si>
-  <si>
-    <t>10.04.202693</t>
-  </si>
-  <si>
-    <t>10.04.202694</t>
-  </si>
-  <si>
-    <t>10.04.202695</t>
-  </si>
-  <si>
-    <t>10.04.202696</t>
+    <t>16.04.20261</t>
+  </si>
+  <si>
+    <t>16.04.20262</t>
+  </si>
+  <si>
+    <t>16.04.20263</t>
+  </si>
+  <si>
+    <t>16.04.20264</t>
+  </si>
+  <si>
+    <t>16.04.20265</t>
+  </si>
+  <si>
+    <t>16.04.20266</t>
+  </si>
+  <si>
+    <t>16.04.20267</t>
+  </si>
+  <si>
+    <t>16.04.20268</t>
+  </si>
+  <si>
+    <t>16.04.20269</t>
+  </si>
+  <si>
+    <t>16.04.202610</t>
+  </si>
+  <si>
+    <t>16.04.202611</t>
+  </si>
+  <si>
+    <t>16.04.202612</t>
+  </si>
+  <si>
+    <t>16.04.202613</t>
+  </si>
+  <si>
+    <t>16.04.202614</t>
+  </si>
+  <si>
+    <t>16.04.202615</t>
+  </si>
+  <si>
+    <t>16.04.202616</t>
+  </si>
+  <si>
+    <t>16.04.202617</t>
+  </si>
+  <si>
+    <t>16.04.202618</t>
+  </si>
+  <si>
+    <t>16.04.202619</t>
+  </si>
+  <si>
+    <t>16.04.202620</t>
+  </si>
+  <si>
+    <t>16.04.202621</t>
+  </si>
+  <si>
+    <t>16.04.202622</t>
+  </si>
+  <si>
+    <t>16.04.202623</t>
+  </si>
+  <si>
+    <t>16.04.202624</t>
+  </si>
+  <si>
+    <t>16.04.202625</t>
+  </si>
+  <si>
+    <t>16.04.202626</t>
+  </si>
+  <si>
+    <t>16.04.202627</t>
+  </si>
+  <si>
+    <t>16.04.202628</t>
+  </si>
+  <si>
+    <t>16.04.202629</t>
+  </si>
+  <si>
+    <t>16.04.202630</t>
+  </si>
+  <si>
+    <t>16.04.202631</t>
+  </si>
+  <si>
+    <t>16.04.202632</t>
+  </si>
+  <si>
+    <t>16.04.202633</t>
+  </si>
+  <si>
+    <t>16.04.202634</t>
+  </si>
+  <si>
+    <t>16.04.202635</t>
+  </si>
+  <si>
+    <t>16.04.202636</t>
+  </si>
+  <si>
+    <t>16.04.202637</t>
+  </si>
+  <si>
+    <t>16.04.202638</t>
+  </si>
+  <si>
+    <t>16.04.202639</t>
+  </si>
+  <si>
+    <t>16.04.202640</t>
+  </si>
+  <si>
+    <t>16.04.202641</t>
+  </si>
+  <si>
+    <t>16.04.202642</t>
+  </si>
+  <si>
+    <t>16.04.202643</t>
+  </si>
+  <si>
+    <t>16.04.202644</t>
+  </si>
+  <si>
+    <t>16.04.202645</t>
+  </si>
+  <si>
+    <t>16.04.202646</t>
+  </si>
+  <si>
+    <t>16.04.202647</t>
+  </si>
+  <si>
+    <t>16.04.202648</t>
+  </si>
+  <si>
+    <t>16.04.202649</t>
+  </si>
+  <si>
+    <t>16.04.202650</t>
+  </si>
+  <si>
+    <t>16.04.202651</t>
+  </si>
+  <si>
+    <t>16.04.202652</t>
+  </si>
+  <si>
+    <t>16.04.202653</t>
+  </si>
+  <si>
+    <t>16.04.202654</t>
+  </si>
+  <si>
+    <t>16.04.202655</t>
+  </si>
+  <si>
+    <t>16.04.202656</t>
+  </si>
+  <si>
+    <t>16.04.202657</t>
+  </si>
+  <si>
+    <t>16.04.202658</t>
+  </si>
+  <si>
+    <t>16.04.202659</t>
+  </si>
+  <si>
+    <t>16.04.202660</t>
+  </si>
+  <si>
+    <t>16.04.202661</t>
+  </si>
+  <si>
+    <t>16.04.202662</t>
+  </si>
+  <si>
+    <t>16.04.202663</t>
+  </si>
+  <si>
+    <t>16.04.202664</t>
+  </si>
+  <si>
+    <t>16.04.202665</t>
+  </si>
+  <si>
+    <t>16.04.202666</t>
+  </si>
+  <si>
+    <t>16.04.202667</t>
+  </si>
+  <si>
+    <t>16.04.202668</t>
+  </si>
+  <si>
+    <t>16.04.202669</t>
+  </si>
+  <si>
+    <t>16.04.202670</t>
+  </si>
+  <si>
+    <t>16.04.202671</t>
+  </si>
+  <si>
+    <t>16.04.202672</t>
+  </si>
+  <si>
+    <t>16.04.202673</t>
+  </si>
+  <si>
+    <t>16.04.202674</t>
+  </si>
+  <si>
+    <t>16.04.202675</t>
+  </si>
+  <si>
+    <t>16.04.202676</t>
+  </si>
+  <si>
+    <t>16.04.202677</t>
+  </si>
+  <si>
+    <t>16.04.202678</t>
+  </si>
+  <si>
+    <t>16.04.202679</t>
+  </si>
+  <si>
+    <t>16.04.202680</t>
+  </si>
+  <si>
+    <t>16.04.202681</t>
+  </si>
+  <si>
+    <t>16.04.202682</t>
+  </si>
+  <si>
+    <t>16.04.202683</t>
+  </si>
+  <si>
+    <t>16.04.202684</t>
+  </si>
+  <si>
+    <t>16.04.202685</t>
+  </si>
+  <si>
+    <t>16.04.202686</t>
+  </si>
+  <si>
+    <t>16.04.202687</t>
+  </si>
+  <si>
+    <t>16.04.202688</t>
+  </si>
+  <si>
+    <t>16.04.202689</t>
+  </si>
+  <si>
+    <t>16.04.202690</t>
+  </si>
+  <si>
+    <t>16.04.202691</t>
+  </si>
+  <si>
+    <t>16.04.202692</t>
+  </si>
+  <si>
+    <t>16.04.202693</t>
+  </si>
+  <si>
+    <t>16.04.202694</t>
+  </si>
+  <si>
+    <t>16.04.202695</t>
+  </si>
+  <si>
+    <t>16.04.202696</t>
+  </si>
+  <si>
+    <t>17.04.20261</t>
+  </si>
+  <si>
+    <t>17.04.20262</t>
+  </si>
+  <si>
+    <t>17.04.20263</t>
+  </si>
+  <si>
+    <t>17.04.20264</t>
+  </si>
+  <si>
+    <t>17.04.20265</t>
+  </si>
+  <si>
+    <t>17.04.20266</t>
+  </si>
+  <si>
+    <t>17.04.20267</t>
+  </si>
+  <si>
+    <t>17.04.20268</t>
+  </si>
+  <si>
+    <t>17.04.20269</t>
+  </si>
+  <si>
+    <t>17.04.202610</t>
+  </si>
+  <si>
+    <t>17.04.202611</t>
+  </si>
+  <si>
+    <t>17.04.202612</t>
+  </si>
+  <si>
+    <t>17.04.202613</t>
+  </si>
+  <si>
+    <t>17.04.202614</t>
+  </si>
+  <si>
+    <t>17.04.202615</t>
+  </si>
+  <si>
+    <t>17.04.202616</t>
+  </si>
+  <si>
+    <t>17.04.202617</t>
+  </si>
+  <si>
+    <t>17.04.202618</t>
+  </si>
+  <si>
+    <t>17.04.202619</t>
+  </si>
+  <si>
+    <t>17.04.202620</t>
+  </si>
+  <si>
+    <t>17.04.202621</t>
+  </si>
+  <si>
+    <t>17.04.202622</t>
+  </si>
+  <si>
+    <t>17.04.202623</t>
+  </si>
+  <si>
+    <t>17.04.202624</t>
+  </si>
+  <si>
+    <t>17.04.202625</t>
+  </si>
+  <si>
+    <t>17.04.202626</t>
+  </si>
+  <si>
+    <t>17.04.202627</t>
+  </si>
+  <si>
+    <t>17.04.202628</t>
+  </si>
+  <si>
+    <t>17.04.202629</t>
+  </si>
+  <si>
+    <t>17.04.202630</t>
+  </si>
+  <si>
+    <t>17.04.202631</t>
+  </si>
+  <si>
+    <t>17.04.202632</t>
+  </si>
+  <si>
+    <t>17.04.202633</t>
+  </si>
+  <si>
+    <t>17.04.202634</t>
+  </si>
+  <si>
+    <t>17.04.202635</t>
+  </si>
+  <si>
+    <t>17.04.202636</t>
+  </si>
+  <si>
+    <t>17.04.202637</t>
+  </si>
+  <si>
+    <t>17.04.202638</t>
+  </si>
+  <si>
+    <t>17.04.202639</t>
+  </si>
+  <si>
+    <t>17.04.202640</t>
+  </si>
+  <si>
+    <t>17.04.202641</t>
+  </si>
+  <si>
+    <t>17.04.202642</t>
+  </si>
+  <si>
+    <t>17.04.202643</t>
+  </si>
+  <si>
+    <t>17.04.202644</t>
+  </si>
+  <si>
+    <t>17.04.202645</t>
+  </si>
+  <si>
+    <t>17.04.202646</t>
+  </si>
+  <si>
+    <t>17.04.202647</t>
+  </si>
+  <si>
+    <t>17.04.202648</t>
+  </si>
+  <si>
+    <t>17.04.202649</t>
+  </si>
+  <si>
+    <t>17.04.202650</t>
+  </si>
+  <si>
+    <t>17.04.202651</t>
+  </si>
+  <si>
+    <t>17.04.202652</t>
+  </si>
+  <si>
+    <t>17.04.202653</t>
+  </si>
+  <si>
+    <t>17.04.202654</t>
+  </si>
+  <si>
+    <t>17.04.202655</t>
+  </si>
+  <si>
+    <t>17.04.202656</t>
+  </si>
+  <si>
+    <t>17.04.202657</t>
+  </si>
+  <si>
+    <t>17.04.202658</t>
+  </si>
+  <si>
+    <t>17.04.202659</t>
+  </si>
+  <si>
+    <t>17.04.202660</t>
+  </si>
+  <si>
+    <t>17.04.202661</t>
+  </si>
+  <si>
+    <t>17.04.202662</t>
+  </si>
+  <si>
+    <t>17.04.202663</t>
+  </si>
+  <si>
+    <t>17.04.202664</t>
+  </si>
+  <si>
+    <t>17.04.202665</t>
+  </si>
+  <si>
+    <t>17.04.202666</t>
+  </si>
+  <si>
+    <t>17.04.202667</t>
+  </si>
+  <si>
+    <t>17.04.202668</t>
+  </si>
+  <si>
+    <t>17.04.202669</t>
+  </si>
+  <si>
+    <t>17.04.202670</t>
+  </si>
+  <si>
+    <t>17.04.202671</t>
+  </si>
+  <si>
+    <t>17.04.202672</t>
+  </si>
+  <si>
+    <t>17.04.202673</t>
+  </si>
+  <si>
+    <t>17.04.202674</t>
+  </si>
+  <si>
+    <t>17.04.202675</t>
+  </si>
+  <si>
+    <t>17.04.202676</t>
+  </si>
+  <si>
+    <t>17.04.202677</t>
+  </si>
+  <si>
+    <t>17.04.202678</t>
+  </si>
+  <si>
+    <t>17.04.202679</t>
+  </si>
+  <si>
+    <t>17.04.202680</t>
+  </si>
+  <si>
+    <t>17.04.202681</t>
+  </si>
+  <si>
+    <t>17.04.202682</t>
+  </si>
+  <si>
+    <t>17.04.202683</t>
+  </si>
+  <si>
+    <t>17.04.202684</t>
+  </si>
+  <si>
+    <t>17.04.202685</t>
+  </si>
+  <si>
+    <t>17.04.202686</t>
+  </si>
+  <si>
+    <t>17.04.202687</t>
+  </si>
+  <si>
+    <t>17.04.202688</t>
+  </si>
+  <si>
+    <t>17.04.202689</t>
+  </si>
+  <si>
+    <t>17.04.202690</t>
+  </si>
+  <si>
+    <t>17.04.202691</t>
+  </si>
+  <si>
+    <t>17.04.202692</t>
+  </si>
+  <si>
+    <t>17.04.202693</t>
+  </si>
+  <si>
+    <t>17.04.202694</t>
+  </si>
+  <si>
+    <t>17.04.202695</t>
+  </si>
+  <si>
+    <t>17.04.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="B2">
-        <v>904.039</v>
+        <v>592.54</v>
       </c>
       <c r="C2">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46128.01041666666</v>
       </c>
       <c r="B3">
-        <v>903.504</v>
+        <v>568.7140000000001</v>
       </c>
       <c r="C3">
-        <v>787</v>
+        <v>667</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46128.02083333334</v>
       </c>
       <c r="B4">
-        <v>903.285</v>
+        <v>549.0650000000001</v>
       </c>
       <c r="C4">
-        <v>886</v>
+        <v>641</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46128.03125</v>
       </c>
       <c r="B5">
-        <v>900.282</v>
+        <v>527.902</v>
       </c>
       <c r="C5">
-        <v>1012</v>
+        <v>612</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46128.04166666666</v>
       </c>
       <c r="B6">
-        <v>879.8869999999999</v>
+        <v>490.559</v>
       </c>
       <c r="C6">
-        <v>998</v>
+        <v>594</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46128.05208333334</v>
       </c>
       <c r="B7">
-        <v>863.421</v>
+        <v>465.157</v>
       </c>
       <c r="C7">
-        <v>940</v>
+        <v>566</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46128.0625</v>
       </c>
       <c r="B8">
-        <v>850.204</v>
+        <v>447.718</v>
       </c>
       <c r="C8">
-        <v>921</v>
+        <v>556</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46128.07291666666</v>
       </c>
       <c r="B9">
-        <v>847.136</v>
+        <v>432.307</v>
       </c>
       <c r="C9">
-        <v>908</v>
+        <v>532</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46128.08333333334</v>
       </c>
       <c r="B10">
-        <v>852.676</v>
+        <v>402.808</v>
       </c>
       <c r="C10">
-        <v>895</v>
+        <v>511</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46128.09375</v>
       </c>
       <c r="B11">
-        <v>854.657</v>
+        <v>392.081</v>
       </c>
       <c r="C11">
-        <v>896</v>
+        <v>503</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46128.10416666666</v>
       </c>
       <c r="B12">
-        <v>847.989</v>
+        <v>378.85</v>
       </c>
       <c r="C12">
-        <v>899</v>
+        <v>496</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46128.11458333334</v>
       </c>
       <c r="B13">
-        <v>835.1</v>
+        <v>368.192</v>
       </c>
       <c r="C13">
-        <v>886</v>
+        <v>467</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46128.125</v>
       </c>
       <c r="B14">
-        <v>835.202</v>
+        <v>348.022</v>
       </c>
       <c r="C14">
-        <v>870</v>
+        <v>421</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46128.13541666666</v>
       </c>
       <c r="B15">
-        <v>830.59</v>
+        <v>340.524</v>
       </c>
       <c r="C15">
-        <v>837</v>
+        <v>385</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46128.14583333334</v>
       </c>
       <c r="B16">
-        <v>817.865</v>
+        <v>334.011</v>
       </c>
       <c r="C16">
-        <v>855</v>
+        <v>361</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46128.15625</v>
       </c>
       <c r="B17">
-        <v>799.353</v>
+        <v>321.79</v>
       </c>
       <c r="C17">
-        <v>856</v>
+        <v>338</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46128.16666666666</v>
       </c>
       <c r="B18">
-        <v>791.196</v>
+        <v>327.048</v>
       </c>
       <c r="C18">
-        <v>851</v>
+        <v>337</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46128.17708333334</v>
       </c>
       <c r="B19">
-        <v>777.6180000000001</v>
+        <v>317.894</v>
       </c>
       <c r="C19">
-        <v>833</v>
+        <v>325</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46128.1875</v>
       </c>
       <c r="B20">
-        <v>763.972</v>
+        <v>309.743</v>
       </c>
       <c r="C20">
-        <v>841</v>
+        <v>314</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46128.19791666666</v>
       </c>
       <c r="B21">
-        <v>750.107</v>
+        <v>301.832</v>
       </c>
       <c r="C21">
-        <v>867</v>
+        <v>305</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46128.20833333334</v>
       </c>
       <c r="B22">
-        <v>734.673</v>
+        <v>269.475</v>
       </c>
       <c r="C22">
-        <v>881</v>
+        <v>295</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46128.21875</v>
       </c>
       <c r="B23">
-        <v>730.487</v>
+        <v>290.431</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46128.22916666666</v>
       </c>
       <c r="B24">
-        <v>721.407</v>
+        <v>285.438</v>
       </c>
       <c r="C24">
-        <v>906</v>
+        <v>266</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46128.23958333334</v>
       </c>
       <c r="B25">
-        <v>714.399</v>
+        <v>282.303</v>
       </c>
       <c r="C25">
-        <v>885</v>
+        <v>276</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46128.25</v>
       </c>
       <c r="B26">
-        <v>704.393</v>
+        <v>269.953</v>
       </c>
       <c r="C26">
-        <v>872</v>
+        <v>292</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46128.26041666666</v>
       </c>
       <c r="B27">
-        <v>699.775</v>
+        <v>271.191</v>
       </c>
       <c r="C27">
-        <v>837</v>
+        <v>301</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46128.27083333334</v>
       </c>
       <c r="B28">
-        <v>704.554</v>
+        <v>269.5</v>
       </c>
       <c r="C28">
-        <v>778</v>
+        <v>311</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46128.28125</v>
       </c>
       <c r="B29">
-        <v>747.604</v>
+        <v>272.141</v>
       </c>
       <c r="C29">
-        <v>750</v>
+        <v>318</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46128.29166666666</v>
       </c>
       <c r="B30">
-        <v>746.63</v>
+        <v>268.449</v>
       </c>
       <c r="C30">
-        <v>703</v>
+        <v>319</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46128.30208333334</v>
       </c>
       <c r="B31">
-        <v>746.7859999999999</v>
+        <v>263.221</v>
       </c>
       <c r="C31">
-        <v>684</v>
+        <v>289</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46128.3125</v>
       </c>
       <c r="B32">
-        <v>743.4109999999999</v>
+        <v>252.759</v>
       </c>
       <c r="C32">
-        <v>654</v>
+        <v>254</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46128.32291666666</v>
       </c>
       <c r="B33">
-        <v>742.184</v>
+        <v>247.16</v>
       </c>
       <c r="C33">
-        <v>649</v>
+        <v>219</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="B34">
-        <v>801.313</v>
+        <v>271.059</v>
       </c>
       <c r="C34">
-        <v>781</v>
+        <v>183</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46128.34375</v>
       </c>
       <c r="B35">
-        <v>825.9109999999999</v>
+        <v>263.113</v>
       </c>
       <c r="C35">
-        <v>886</v>
+        <v>157</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46128.35416666666</v>
       </c>
       <c r="B36">
-        <v>854.364</v>
+        <v>244.604</v>
       </c>
       <c r="C36">
-        <v>908</v>
+        <v>153</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46128.36458333334</v>
       </c>
       <c r="B37">
-        <v>883.586</v>
+        <v>235.746</v>
       </c>
       <c r="C37">
-        <v>894</v>
+        <v>146</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46128.375</v>
       </c>
       <c r="B38">
-        <v>862.452</v>
+        <v>232.409</v>
       </c>
       <c r="C38">
-        <v>903</v>
+        <v>140</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46128.38541666666</v>
       </c>
       <c r="B39">
-        <v>887.158</v>
+        <v>238.527</v>
       </c>
       <c r="C39">
-        <v>889</v>
+        <v>134</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46128.39583333334</v>
       </c>
       <c r="B40">
-        <v>909.361</v>
+        <v>244.997</v>
       </c>
       <c r="C40">
-        <v>857</v>
+        <v>120</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46128.40625</v>
       </c>
       <c r="B41">
-        <v>934.838</v>
+        <v>252.147</v>
       </c>
       <c r="C41">
-        <v>838</v>
+        <v>115</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46128.41666666666</v>
       </c>
       <c r="B42">
-        <v>967.367</v>
+        <v>259.223</v>
       </c>
       <c r="C42">
-        <v>830</v>
+        <v>121</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46128.42708333334</v>
       </c>
       <c r="B43">
-        <v>963.377</v>
+        <v>268.202</v>
       </c>
       <c r="C43">
-        <v>800</v>
+        <v>130</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46128.4375</v>
       </c>
       <c r="B44">
-        <v>959.202</v>
+        <v>277.339</v>
       </c>
       <c r="C44">
-        <v>846</v>
+        <v>153</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46128.44791666666</v>
       </c>
       <c r="B45">
-        <v>954.076</v>
+        <v>286.445</v>
       </c>
       <c r="C45">
-        <v>856</v>
+        <v>172</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46128.45833333334</v>
       </c>
       <c r="B46">
-        <v>938.278</v>
+        <v>310.287</v>
       </c>
       <c r="C46">
-        <v>834</v>
+        <v>181</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46128.46875</v>
       </c>
       <c r="B47">
-        <v>921.982</v>
+        <v>320.25</v>
       </c>
       <c r="C47">
-        <v>837</v>
+        <v>192</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46128.47916666666</v>
       </c>
       <c r="B48">
-        <v>790.853</v>
+        <v>331.64</v>
       </c>
       <c r="C48">
-        <v>829</v>
+        <v>193</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46128.48958333334</v>
       </c>
       <c r="B49">
-        <v>739.509</v>
+        <v>343.052</v>
       </c>
       <c r="C49">
-        <v>719</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46128.5</v>
       </c>
       <c r="B50">
-        <v>757.347</v>
+        <v>330.465</v>
       </c>
       <c r="C50">
-        <v>745</v>
+        <v>185</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46128.51041666666</v>
       </c>
       <c r="B51">
-        <v>744.4349999999999</v>
+        <v>341.567</v>
       </c>
       <c r="C51">
-        <v>748</v>
+        <v>182</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46128.52083333334</v>
       </c>
       <c r="B52">
-        <v>640.794</v>
+        <v>352.632</v>
       </c>
       <c r="C52">
-        <v>722</v>
+        <v>184</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46128.53125</v>
       </c>
       <c r="B53">
-        <v>632.516</v>
+        <v>364.514</v>
       </c>
       <c r="C53">
-        <v>719</v>
+        <v>183</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46128.54166666666</v>
       </c>
       <c r="B54">
-        <v>666.3339999999999</v>
+        <v>374.336</v>
       </c>
       <c r="C54">
-        <v>741</v>
+        <v>185</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="B55">
-        <v>643.196</v>
+        <v>384.999</v>
       </c>
       <c r="C55">
-        <v>812</v>
+        <v>182</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46128.5625</v>
       </c>
       <c r="B56">
-        <v>677.492</v>
+        <v>395.258</v>
       </c>
       <c r="C56">
-        <v>821</v>
+        <v>196</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46128.57291666666</v>
       </c>
       <c r="B57">
-        <v>665.856</v>
+        <v>406.279</v>
       </c>
       <c r="C57">
-        <v>680</v>
+        <v>212</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46128.58333333334</v>
       </c>
       <c r="B58">
-        <v>703.524</v>
+        <v>420.211</v>
       </c>
       <c r="C58">
-        <v>779</v>
+        <v>228</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46128.59375</v>
       </c>
       <c r="B59">
-        <v>689.998</v>
+        <v>430.595</v>
       </c>
       <c r="C59">
-        <v>838</v>
+        <v>247</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46128.60416666666</v>
       </c>
       <c r="B60">
-        <v>686.009</v>
+        <v>440.127</v>
       </c>
       <c r="C60">
-        <v>871</v>
+        <v>261</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46128.61458333334</v>
       </c>
       <c r="B61">
-        <v>667.913</v>
+        <v>450.147</v>
       </c>
       <c r="C61">
-        <v>900</v>
+        <v>284</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46128.625</v>
       </c>
       <c r="B62">
-        <v>593.9829999999999</v>
+        <v>466.494</v>
       </c>
       <c r="C62">
-        <v>864</v>
+        <v>319</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46128.63541666666</v>
       </c>
       <c r="B63">
-        <v>593.0170000000001</v>
+        <v>476.9</v>
       </c>
       <c r="C63">
-        <v>769</v>
+        <v>349</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46128.64583333334</v>
       </c>
       <c r="B64">
-        <v>593.782</v>
+        <v>488.48</v>
       </c>
       <c r="C64">
-        <v>695</v>
+        <v>396</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46128.65625</v>
       </c>
       <c r="B65">
-        <v>589.175</v>
+        <v>499.268</v>
       </c>
       <c r="C65">
-        <v>722</v>
+        <v>447</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46128.66666666666</v>
       </c>
       <c r="B66">
-        <v>555.545</v>
+        <v>459.538</v>
       </c>
       <c r="C66">
-        <v>729</v>
+        <v>464</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46128.67708333334</v>
       </c>
       <c r="B67">
-        <v>534.986</v>
+        <v>467.344</v>
       </c>
       <c r="C67">
-        <v>782</v>
+        <v>490</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46128.6875</v>
       </c>
       <c r="B68">
-        <v>513.468</v>
+        <v>474.564</v>
       </c>
       <c r="C68">
-        <v>583</v>
+        <v>517</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46128.69791666666</v>
       </c>
       <c r="B69">
-        <v>493.734</v>
+        <v>482.431</v>
       </c>
       <c r="C69">
-        <v>456</v>
+        <v>548</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46128.70833333334</v>
       </c>
       <c r="B70">
-        <v>462.611</v>
+        <v>488.425</v>
       </c>
       <c r="C70">
-        <v>421</v>
+        <v>567</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46128.71875</v>
       </c>
       <c r="B71">
-        <v>438.23</v>
+        <v>495.54</v>
       </c>
       <c r="C71">
-        <v>382</v>
+        <v>587</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46128.72916666666</v>
       </c>
       <c r="B72">
-        <v>414.199</v>
+        <v>503.11</v>
       </c>
       <c r="C72">
-        <v>406</v>
+        <v>611</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46128.73958333334</v>
       </c>
       <c r="B73">
-        <v>391.126</v>
+        <v>512.556</v>
       </c>
       <c r="C73">
-        <v>435</v>
+        <v>631</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46128.75</v>
       </c>
       <c r="B74">
-        <v>370.873</v>
+        <v>528.972</v>
       </c>
       <c r="C74">
-        <v>445</v>
+        <v>644</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46128.76041666666</v>
       </c>
       <c r="B75">
-        <v>365.884</v>
+        <v>546.249</v>
       </c>
       <c r="C75">
-        <v>511</v>
+        <v>654</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46128.77083333334</v>
       </c>
       <c r="B76">
-        <v>361.08</v>
+        <v>560.875</v>
       </c>
       <c r="C76">
-        <v>505</v>
+        <v>680</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46128.78125</v>
       </c>
       <c r="B77">
-        <v>356.411</v>
+        <v>572.953</v>
       </c>
       <c r="C77">
-        <v>483</v>
+        <v>683</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46128.79166666666</v>
       </c>
       <c r="B78">
-        <v>352.057</v>
+        <v>592.843</v>
       </c>
       <c r="C78">
-        <v>463</v>
+        <v>669</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46128.80208333334</v>
       </c>
       <c r="B79">
-        <v>355.704</v>
+        <v>605.588</v>
       </c>
       <c r="C79">
-        <v>450</v>
+        <v>692</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46128.8125</v>
       </c>
       <c r="B80">
-        <v>360.467</v>
+        <v>618.4349999999999</v>
       </c>
       <c r="C80">
-        <v>485</v>
+        <v>702</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46128.82291666666</v>
       </c>
       <c r="B81">
-        <v>365.156</v>
+        <v>640.071</v>
       </c>
       <c r="C81">
-        <v>534</v>
+        <v>745</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46128.83333333334</v>
       </c>
       <c r="B82">
-        <v>376.996</v>
+        <v>654.652</v>
       </c>
       <c r="C82">
-        <v>564</v>
+        <v>751</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46128.84375</v>
       </c>
       <c r="B83">
-        <v>379.432</v>
+        <v>648.175</v>
       </c>
       <c r="C83">
-        <v>572</v>
+        <v>737</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46128.85416666666</v>
       </c>
       <c r="B84">
-        <v>381.469</v>
+        <v>650.3339999999999</v>
       </c>
       <c r="C84">
-        <v>585</v>
+        <v>750</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46128.86458333334</v>
       </c>
       <c r="B85">
-        <v>384.292</v>
+        <v>651.987</v>
       </c>
       <c r="C85">
-        <v>604</v>
+        <v>730</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46128.875</v>
       </c>
       <c r="B86">
-        <v>388.708</v>
+        <v>655.191</v>
       </c>
       <c r="C86">
-        <v>653</v>
+        <v>713</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46128.88541666666</v>
       </c>
       <c r="B87">
-        <v>398.483</v>
+        <v>639.574</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46128.89583333334</v>
       </c>
       <c r="B88">
-        <v>408.455</v>
+        <v>642.812</v>
       </c>
       <c r="C88">
-        <v>713</v>
+        <v>670</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46128.90625</v>
       </c>
       <c r="B89">
-        <v>419.264</v>
+        <v>626.904</v>
       </c>
       <c r="C89">
-        <v>735</v>
+        <v>675</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46128.91666666666</v>
       </c>
       <c r="B90">
-        <v>443.684</v>
+        <v>608.9109999999999</v>
       </c>
       <c r="C90">
-        <v>779</v>
+        <v>688</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46128.92708333334</v>
       </c>
       <c r="B91">
-        <v>459.404</v>
+        <v>590.879</v>
       </c>
       <c r="C91">
-        <v>787</v>
+        <v>660</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46128.9375</v>
       </c>
       <c r="B92">
-        <v>475.842</v>
+        <v>574.389</v>
       </c>
       <c r="C92">
-        <v>795</v>
+        <v>621</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46128.94791666666</v>
       </c>
       <c r="B93">
-        <v>490.812</v>
+        <v>557.12</v>
       </c>
       <c r="C93">
-        <v>778</v>
+        <v>561</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46128.95833333334</v>
       </c>
       <c r="B94">
-        <v>577.088</v>
+        <v>577.4930000000001</v>
       </c>
       <c r="C94">
-        <v>828</v>
+        <v>536</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46128.96875</v>
       </c>
       <c r="B95">
-        <v>592.715</v>
+        <v>557.9589999999999</v>
       </c>
       <c r="C95">
-        <v>839</v>
+        <v>532</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46128.97916666666</v>
       </c>
       <c r="B96">
-        <v>607.8440000000001</v>
+        <v>541.802</v>
       </c>
       <c r="C96">
-        <v>861</v>
+        <v>511</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46128.98958333334</v>
       </c>
       <c r="B97">
-        <v>621.5890000000001</v>
+        <v>516.087</v>
       </c>
       <c r="C97">
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="B98">
-        <v>610.15</v>
+        <v>492.289</v>
       </c>
       <c r="C98">
-        <v>915</v>
+        <v>442</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46122.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B99">
-        <v>624.881</v>
+        <v>470.433</v>
       </c>
       <c r="C99">
-        <v>887</v>
+        <v>413</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46122.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B100">
-        <v>629.535</v>
+        <v>450.249</v>
       </c>
       <c r="C100">
-        <v>875</v>
+        <v>373</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46122.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B101">
-        <v>641.432</v>
+        <v>424.939</v>
       </c>
       <c r="C101">
-        <v>850</v>
+        <v>362</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46122.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B102">
-        <v>644.551</v>
+        <v>384.318</v>
       </c>
       <c r="C102">
-        <v>828</v>
+        <v>357</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46122.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B103">
-        <v>653.672</v>
+        <v>366.312</v>
       </c>
       <c r="C103">
-        <v>845</v>
+        <v>358</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46122.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B104">
-        <v>662.116</v>
+        <v>345.968</v>
       </c>
       <c r="C104">
-        <v>898</v>
+        <v>348</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46122.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B105">
-        <v>663.824</v>
+        <v>327.101</v>
       </c>
       <c r="C105">
-        <v>956</v>
+        <v>336</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46122.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B106">
-        <v>671.386</v>
+        <v>299.321</v>
       </c>
       <c r="C106">
-        <v>1013</v>
+        <v>313</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46122.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B107">
-        <v>682.599</v>
+        <v>283.355</v>
       </c>
       <c r="C107">
-        <v>1035</v>
+        <v>290</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46122.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B108">
-        <v>698.974</v>
+        <v>273.912</v>
       </c>
       <c r="C108">
-        <v>1031</v>
+        <v>297</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46122.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B109">
-        <v>711.982</v>
+        <v>265.646</v>
       </c>
       <c r="C109">
-        <v>1050</v>
+        <v>284</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46122.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B110">
-        <v>735.777</v>
+        <v>255.408</v>
       </c>
       <c r="C110">
-        <v>1046</v>
+        <v>260</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46122.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B111">
-        <v>739.3440000000001</v>
+        <v>248.314</v>
       </c>
       <c r="C111">
-        <v>1068</v>
+        <v>242</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46122.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B112">
-        <v>746.215</v>
+        <v>239.166</v>
       </c>
       <c r="C112">
-        <v>1047</v>
+        <v>219</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46122.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B113">
-        <v>798.527</v>
+        <v>232.88</v>
       </c>
       <c r="C113">
-        <v>1067</v>
+        <v>202</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46122.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B114">
-        <v>819.769</v>
+        <v>241.677</v>
       </c>
       <c r="C114">
-        <v>1072</v>
+        <v>201</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46122.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B115">
-        <v>821.691</v>
+        <v>232.256</v>
       </c>
       <c r="C115">
-        <v>1063</v>
+        <v>198</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46122.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B116">
-        <v>825.071</v>
+        <v>224.945</v>
       </c>
       <c r="C116">
-        <v>1050</v>
+        <v>190</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46122.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B117">
-        <v>835.143</v>
+        <v>218.791</v>
       </c>
       <c r="C117">
-        <v>1034</v>
+        <v>194</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46122.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B118">
-        <v>796.947</v>
+        <v>197.97</v>
       </c>
       <c r="C118">
-        <v>986</v>
+        <v>198</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46122.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B119">
-        <v>823.806</v>
+        <v>189.546</v>
       </c>
       <c r="C119">
-        <v>936</v>
+        <v>190</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46122.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B120">
-        <v>816.269</v>
+        <v>212.254</v>
       </c>
       <c r="C120">
-        <v>912</v>
+        <v>189</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46122.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B121">
-        <v>807.489</v>
+        <v>208.106</v>
       </c>
       <c r="C121">
-        <v>915</v>
+        <v>193</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46122.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B122">
-        <v>794.961</v>
+        <v>203.017</v>
       </c>
       <c r="C122">
-        <v>876</v>
+        <v>173</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46122.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B123">
-        <v>784.756</v>
+        <v>199.185</v>
       </c>
       <c r="C123">
-        <v>825</v>
+        <v>143</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46122.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B124">
-        <v>779.461</v>
+        <v>194.304</v>
       </c>
       <c r="C124">
-        <v>780</v>
+        <v>136</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46122.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B125">
-        <v>769.4450000000001</v>
+        <v>190.044</v>
       </c>
       <c r="C125">
-        <v>737</v>
+        <v>139</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46122.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B126">
-        <v>748.9400000000001</v>
+        <v>174.644</v>
       </c>
       <c r="C126">
-        <v>675</v>
+        <v>133</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46122.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B127">
-        <v>723.814</v>
+        <v>168.972</v>
       </c>
       <c r="C127">
-        <v>605</v>
+        <v>105</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46122.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B128">
-        <v>715.508</v>
+        <v>157.268</v>
       </c>
       <c r="C128">
-        <v>600</v>
+        <v>72</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46122.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B129">
-        <v>696.314</v>
+        <v>149.267</v>
       </c>
       <c r="C129">
-        <v>588</v>
+        <v>53</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46122.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B130">
-        <v>786.958</v>
+        <v>128.096</v>
       </c>
       <c r="C130">
-        <v>575</v>
+        <v>52</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46122.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B131">
-        <v>783.22</v>
+        <v>119.716</v>
       </c>
       <c r="C131">
-        <v>577</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46122.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B132">
-        <v>774.575</v>
+        <v>108.219</v>
       </c>
       <c r="C132">
-        <v>582</v>
+        <v>57</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46122.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B133">
-        <v>771.88</v>
+        <v>101.987</v>
       </c>
       <c r="C133">
-        <v>600</v>
+        <v>67</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46122.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B134">
-        <v>818.318</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C134">
-        <v>654</v>
+        <v>72</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46122.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B135">
-        <v>815.2569999999999</v>
+        <v>101.639</v>
       </c>
       <c r="C135">
-        <v>690</v>
+        <v>73</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46122.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B136">
-        <v>811.625</v>
+        <v>106.323</v>
       </c>
       <c r="C136">
-        <v>669</v>
+        <v>85</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46122.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B137">
-        <v>806.9109999999999</v>
+        <v>111.178</v>
       </c>
       <c r="C137">
-        <v>647</v>
+        <v>97</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46122.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B138">
-        <v>789.808</v>
+        <v>122.041</v>
       </c>
       <c r="C138">
-        <v>639</v>
+        <v>91</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46122.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B139">
-        <v>776.229</v>
+        <v>127.32</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46122.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B140">
-        <v>762.419</v>
+        <v>132.758</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46122.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B141">
-        <v>749.939</v>
+        <v>137.693</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46122.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B142">
-        <v>734.466</v>
+        <v>147.869</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46122.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B143">
-        <v>724.052</v>
+        <v>151.088</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3402,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46122.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B144">
-        <v>715.009</v>
+        <v>154.678</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46122.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B145">
-        <v>706.077</v>
+        <v>159.297</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46122.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B146">
-        <v>696.101</v>
+        <v>149.505</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46122.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B147">
-        <v>686.051</v>
+        <v>152.66</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46122.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B148">
-        <v>676.202</v>
+        <v>156.874</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46122.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B149">
-        <v>667.763</v>
+        <v>159.964</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46122.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B150">
-        <v>654.615</v>
+        <v>163.73</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46122.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B151">
-        <v>642.753</v>
+        <v>168.04</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46122.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B152">
-        <v>630.938</v>
+        <v>171.965</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46122.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B153">
-        <v>619.136</v>
+        <v>175.952</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46122.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B154">
-        <v>576.921</v>
+        <v>172.821</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46122.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B155">
-        <v>574.298</v>
+        <v>177.526</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46122.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B156">
-        <v>571.647</v>
+        <v>182.393</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46122.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B157">
-        <v>568.478</v>
+        <v>186.972</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46122.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B158">
-        <v>541.198</v>
+        <v>193.94</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46122.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B159">
-        <v>530.201</v>
+        <v>201.676</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46122.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B160">
-        <v>518.152</v>
+        <v>208.28</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46122.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B161">
-        <v>508.394</v>
+        <v>214.292</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46122.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B162">
-        <v>393.268</v>
+        <v>219.51</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46122.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B163">
-        <v>378.454</v>
+        <v>224.067</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46122.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B164">
-        <v>359.609</v>
+        <v>227.76</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46122.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B165">
-        <v>344.562</v>
+        <v>230.483</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46122.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B166">
-        <v>303.006</v>
+        <v>229.954</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46122.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B167">
-        <v>281.344</v>
+        <v>233.124</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46122.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B168">
-        <v>254.269</v>
+        <v>235.809</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46122.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B169">
-        <v>234.469</v>
+        <v>239.164</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46122.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B170">
-        <v>209.761</v>
+        <v>248.793</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46122.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B171">
-        <v>199.401</v>
+        <v>250.9</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46122.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B172">
-        <v>189.484</v>
+        <v>252.83</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46122.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B173">
-        <v>180.056</v>
+        <v>255.55</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46122.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B174">
-        <v>172.67</v>
+        <v>250.756</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46122.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B175">
-        <v>165.115</v>
+        <v>247.006</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46122.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B176">
-        <v>159.205</v>
+        <v>242.379</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46122.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B177">
-        <v>178.059</v>
+        <v>236.831</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46122.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B178">
-        <v>167.388</v>
+        <v>227.465</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46122.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B179">
-        <v>162.01</v>
+        <v>221.904</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46122.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B180">
-        <v>131.837</v>
+        <v>215.489</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46122.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B181">
-        <v>126.57</v>
+        <v>208.289</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46122.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B182">
-        <v>139.718</v>
+        <v>197.694</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46122.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B183">
-        <v>109.887</v>
+        <v>195.738</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46122.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B184">
-        <v>106.752</v>
+        <v>193.064</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46122.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B185">
-        <v>104.218</v>
+        <v>190.67</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46122.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B186">
-        <v>103.374</v>
+        <v>190.547</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46122.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B187">
-        <v>103.201</v>
+        <v>200.607</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46122.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B188">
-        <v>103.158</v>
+        <v>211.629</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46122.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B189">
-        <v>102.906</v>
+        <v>223.221</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46122.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46122.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46122.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46122.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>16.04.20261</t>
-  </si>
-  <si>
-    <t>16.04.20262</t>
-  </si>
-  <si>
-    <t>16.04.20263</t>
-  </si>
-  <si>
-    <t>16.04.20264</t>
-  </si>
-  <si>
-    <t>16.04.20265</t>
-  </si>
-  <si>
-    <t>16.04.20266</t>
-  </si>
-  <si>
-    <t>16.04.20267</t>
-  </si>
-  <si>
-    <t>16.04.20268</t>
-  </si>
-  <si>
-    <t>16.04.20269</t>
-  </si>
-  <si>
-    <t>16.04.202610</t>
-  </si>
-  <si>
-    <t>16.04.202611</t>
-  </si>
-  <si>
-    <t>16.04.202612</t>
-  </si>
-  <si>
-    <t>16.04.202613</t>
-  </si>
-  <si>
-    <t>16.04.202614</t>
-  </si>
-  <si>
-    <t>16.04.202615</t>
-  </si>
-  <si>
-    <t>16.04.202616</t>
-  </si>
-  <si>
-    <t>16.04.202617</t>
-  </si>
-  <si>
-    <t>16.04.202618</t>
-  </si>
-  <si>
-    <t>16.04.202619</t>
-  </si>
-  <si>
-    <t>16.04.202620</t>
-  </si>
-  <si>
-    <t>16.04.202621</t>
-  </si>
-  <si>
-    <t>16.04.202622</t>
-  </si>
-  <si>
-    <t>16.04.202623</t>
-  </si>
-  <si>
-    <t>16.04.202624</t>
-  </si>
-  <si>
-    <t>16.04.202625</t>
-  </si>
-  <si>
-    <t>16.04.202626</t>
-  </si>
-  <si>
-    <t>16.04.202627</t>
-  </si>
-  <si>
-    <t>16.04.202628</t>
-  </si>
-  <si>
-    <t>16.04.202629</t>
-  </si>
-  <si>
-    <t>16.04.202630</t>
-  </si>
-  <si>
-    <t>16.04.202631</t>
-  </si>
-  <si>
-    <t>16.04.202632</t>
-  </si>
-  <si>
-    <t>16.04.202633</t>
-  </si>
-  <si>
-    <t>16.04.202634</t>
-  </si>
-  <si>
-    <t>16.04.202635</t>
-  </si>
-  <si>
-    <t>16.04.202636</t>
-  </si>
-  <si>
-    <t>16.04.202637</t>
-  </si>
-  <si>
-    <t>16.04.202638</t>
-  </si>
-  <si>
-    <t>16.04.202639</t>
-  </si>
-  <si>
-    <t>16.04.202640</t>
-  </si>
-  <si>
-    <t>16.04.202641</t>
-  </si>
-  <si>
-    <t>16.04.202642</t>
-  </si>
-  <si>
-    <t>16.04.202643</t>
-  </si>
-  <si>
-    <t>16.04.202644</t>
-  </si>
-  <si>
-    <t>16.04.202645</t>
-  </si>
-  <si>
-    <t>16.04.202646</t>
-  </si>
-  <si>
-    <t>16.04.202647</t>
-  </si>
-  <si>
-    <t>16.04.202648</t>
-  </si>
-  <si>
-    <t>16.04.202649</t>
-  </si>
-  <si>
-    <t>16.04.202650</t>
-  </si>
-  <si>
-    <t>16.04.202651</t>
-  </si>
-  <si>
-    <t>16.04.202652</t>
-  </si>
-  <si>
-    <t>16.04.202653</t>
-  </si>
-  <si>
-    <t>16.04.202654</t>
-  </si>
-  <si>
-    <t>16.04.202655</t>
-  </si>
-  <si>
-    <t>16.04.202656</t>
-  </si>
-  <si>
-    <t>16.04.202657</t>
-  </si>
-  <si>
-    <t>16.04.202658</t>
-  </si>
-  <si>
-    <t>16.04.202659</t>
-  </si>
-  <si>
-    <t>16.04.202660</t>
-  </si>
-  <si>
-    <t>16.04.202661</t>
-  </si>
-  <si>
-    <t>16.04.202662</t>
-  </si>
-  <si>
-    <t>16.04.202663</t>
-  </si>
-  <si>
-    <t>16.04.202664</t>
-  </si>
-  <si>
-    <t>16.04.202665</t>
-  </si>
-  <si>
-    <t>16.04.202666</t>
-  </si>
-  <si>
-    <t>16.04.202667</t>
-  </si>
-  <si>
-    <t>16.04.202668</t>
-  </si>
-  <si>
-    <t>16.04.202669</t>
-  </si>
-  <si>
-    <t>16.04.202670</t>
-  </si>
-  <si>
-    <t>16.04.202671</t>
-  </si>
-  <si>
-    <t>16.04.202672</t>
-  </si>
-  <si>
-    <t>16.04.202673</t>
-  </si>
-  <si>
-    <t>16.04.202674</t>
-  </si>
-  <si>
-    <t>16.04.202675</t>
-  </si>
-  <si>
-    <t>16.04.202676</t>
-  </si>
-  <si>
-    <t>16.04.202677</t>
-  </si>
-  <si>
-    <t>16.04.202678</t>
-  </si>
-  <si>
-    <t>16.04.202679</t>
-  </si>
-  <si>
-    <t>16.04.202680</t>
-  </si>
-  <si>
-    <t>16.04.202681</t>
-  </si>
-  <si>
-    <t>16.04.202682</t>
-  </si>
-  <si>
-    <t>16.04.202683</t>
-  </si>
-  <si>
-    <t>16.04.202684</t>
-  </si>
-  <si>
-    <t>16.04.202685</t>
-  </si>
-  <si>
-    <t>16.04.202686</t>
-  </si>
-  <si>
-    <t>16.04.202687</t>
-  </si>
-  <si>
-    <t>16.04.202688</t>
-  </si>
-  <si>
-    <t>16.04.202689</t>
-  </si>
-  <si>
-    <t>16.04.202690</t>
-  </si>
-  <si>
-    <t>16.04.202691</t>
-  </si>
-  <si>
-    <t>16.04.202692</t>
-  </si>
-  <si>
-    <t>16.04.202693</t>
-  </si>
-  <si>
-    <t>16.04.202694</t>
-  </si>
-  <si>
-    <t>16.04.202695</t>
-  </si>
-  <si>
-    <t>16.04.202696</t>
-  </si>
-  <si>
     <t>17.04.20261</t>
   </si>
   <si>
@@ -605,6 +317,870 @@
   </si>
   <si>
     <t>17.04.202696</t>
+  </si>
+  <si>
+    <t>18.04.20261</t>
+  </si>
+  <si>
+    <t>18.04.20262</t>
+  </si>
+  <si>
+    <t>18.04.20263</t>
+  </si>
+  <si>
+    <t>18.04.20264</t>
+  </si>
+  <si>
+    <t>18.04.20265</t>
+  </si>
+  <si>
+    <t>18.04.20266</t>
+  </si>
+  <si>
+    <t>18.04.20267</t>
+  </si>
+  <si>
+    <t>18.04.20268</t>
+  </si>
+  <si>
+    <t>18.04.20269</t>
+  </si>
+  <si>
+    <t>18.04.202610</t>
+  </si>
+  <si>
+    <t>18.04.202611</t>
+  </si>
+  <si>
+    <t>18.04.202612</t>
+  </si>
+  <si>
+    <t>18.04.202613</t>
+  </si>
+  <si>
+    <t>18.04.202614</t>
+  </si>
+  <si>
+    <t>18.04.202615</t>
+  </si>
+  <si>
+    <t>18.04.202616</t>
+  </si>
+  <si>
+    <t>18.04.202617</t>
+  </si>
+  <si>
+    <t>18.04.202618</t>
+  </si>
+  <si>
+    <t>18.04.202619</t>
+  </si>
+  <si>
+    <t>18.04.202620</t>
+  </si>
+  <si>
+    <t>18.04.202621</t>
+  </si>
+  <si>
+    <t>18.04.202622</t>
+  </si>
+  <si>
+    <t>18.04.202623</t>
+  </si>
+  <si>
+    <t>18.04.202624</t>
+  </si>
+  <si>
+    <t>18.04.202625</t>
+  </si>
+  <si>
+    <t>18.04.202626</t>
+  </si>
+  <si>
+    <t>18.04.202627</t>
+  </si>
+  <si>
+    <t>18.04.202628</t>
+  </si>
+  <si>
+    <t>18.04.202629</t>
+  </si>
+  <si>
+    <t>18.04.202630</t>
+  </si>
+  <si>
+    <t>18.04.202631</t>
+  </si>
+  <si>
+    <t>18.04.202632</t>
+  </si>
+  <si>
+    <t>18.04.202633</t>
+  </si>
+  <si>
+    <t>18.04.202634</t>
+  </si>
+  <si>
+    <t>18.04.202635</t>
+  </si>
+  <si>
+    <t>18.04.202636</t>
+  </si>
+  <si>
+    <t>18.04.202637</t>
+  </si>
+  <si>
+    <t>18.04.202638</t>
+  </si>
+  <si>
+    <t>18.04.202639</t>
+  </si>
+  <si>
+    <t>18.04.202640</t>
+  </si>
+  <si>
+    <t>18.04.202641</t>
+  </si>
+  <si>
+    <t>18.04.202642</t>
+  </si>
+  <si>
+    <t>18.04.202643</t>
+  </si>
+  <si>
+    <t>18.04.202644</t>
+  </si>
+  <si>
+    <t>18.04.202645</t>
+  </si>
+  <si>
+    <t>18.04.202646</t>
+  </si>
+  <si>
+    <t>18.04.202647</t>
+  </si>
+  <si>
+    <t>18.04.202648</t>
+  </si>
+  <si>
+    <t>18.04.202649</t>
+  </si>
+  <si>
+    <t>18.04.202650</t>
+  </si>
+  <si>
+    <t>18.04.202651</t>
+  </si>
+  <si>
+    <t>18.04.202652</t>
+  </si>
+  <si>
+    <t>18.04.202653</t>
+  </si>
+  <si>
+    <t>18.04.202654</t>
+  </si>
+  <si>
+    <t>18.04.202655</t>
+  </si>
+  <si>
+    <t>18.04.202656</t>
+  </si>
+  <si>
+    <t>18.04.202657</t>
+  </si>
+  <si>
+    <t>18.04.202658</t>
+  </si>
+  <si>
+    <t>18.04.202659</t>
+  </si>
+  <si>
+    <t>18.04.202660</t>
+  </si>
+  <si>
+    <t>18.04.202661</t>
+  </si>
+  <si>
+    <t>18.04.202662</t>
+  </si>
+  <si>
+    <t>18.04.202663</t>
+  </si>
+  <si>
+    <t>18.04.202664</t>
+  </si>
+  <si>
+    <t>18.04.202665</t>
+  </si>
+  <si>
+    <t>18.04.202666</t>
+  </si>
+  <si>
+    <t>18.04.202667</t>
+  </si>
+  <si>
+    <t>18.04.202668</t>
+  </si>
+  <si>
+    <t>18.04.202669</t>
+  </si>
+  <si>
+    <t>18.04.202670</t>
+  </si>
+  <si>
+    <t>18.04.202671</t>
+  </si>
+  <si>
+    <t>18.04.202672</t>
+  </si>
+  <si>
+    <t>18.04.202673</t>
+  </si>
+  <si>
+    <t>18.04.202674</t>
+  </si>
+  <si>
+    <t>18.04.202675</t>
+  </si>
+  <si>
+    <t>18.04.202676</t>
+  </si>
+  <si>
+    <t>18.04.202677</t>
+  </si>
+  <si>
+    <t>18.04.202678</t>
+  </si>
+  <si>
+    <t>18.04.202679</t>
+  </si>
+  <si>
+    <t>18.04.202680</t>
+  </si>
+  <si>
+    <t>18.04.202681</t>
+  </si>
+  <si>
+    <t>18.04.202682</t>
+  </si>
+  <si>
+    <t>18.04.202683</t>
+  </si>
+  <si>
+    <t>18.04.202684</t>
+  </si>
+  <si>
+    <t>18.04.202685</t>
+  </si>
+  <si>
+    <t>18.04.202686</t>
+  </si>
+  <si>
+    <t>18.04.202687</t>
+  </si>
+  <si>
+    <t>18.04.202688</t>
+  </si>
+  <si>
+    <t>18.04.202689</t>
+  </si>
+  <si>
+    <t>18.04.202690</t>
+  </si>
+  <si>
+    <t>18.04.202691</t>
+  </si>
+  <si>
+    <t>18.04.202692</t>
+  </si>
+  <si>
+    <t>18.04.202693</t>
+  </si>
+  <si>
+    <t>18.04.202694</t>
+  </si>
+  <si>
+    <t>18.04.202695</t>
+  </si>
+  <si>
+    <t>18.04.202696</t>
+  </si>
+  <si>
+    <t>19.04.20261</t>
+  </si>
+  <si>
+    <t>19.04.20262</t>
+  </si>
+  <si>
+    <t>19.04.20263</t>
+  </si>
+  <si>
+    <t>19.04.20264</t>
+  </si>
+  <si>
+    <t>19.04.20265</t>
+  </si>
+  <si>
+    <t>19.04.20266</t>
+  </si>
+  <si>
+    <t>19.04.20267</t>
+  </si>
+  <si>
+    <t>19.04.20268</t>
+  </si>
+  <si>
+    <t>19.04.20269</t>
+  </si>
+  <si>
+    <t>19.04.202610</t>
+  </si>
+  <si>
+    <t>19.04.202611</t>
+  </si>
+  <si>
+    <t>19.04.202612</t>
+  </si>
+  <si>
+    <t>19.04.202613</t>
+  </si>
+  <si>
+    <t>19.04.202614</t>
+  </si>
+  <si>
+    <t>19.04.202615</t>
+  </si>
+  <si>
+    <t>19.04.202616</t>
+  </si>
+  <si>
+    <t>19.04.202617</t>
+  </si>
+  <si>
+    <t>19.04.202618</t>
+  </si>
+  <si>
+    <t>19.04.202619</t>
+  </si>
+  <si>
+    <t>19.04.202620</t>
+  </si>
+  <si>
+    <t>19.04.202621</t>
+  </si>
+  <si>
+    <t>19.04.202622</t>
+  </si>
+  <si>
+    <t>19.04.202623</t>
+  </si>
+  <si>
+    <t>19.04.202624</t>
+  </si>
+  <si>
+    <t>19.04.202625</t>
+  </si>
+  <si>
+    <t>19.04.202626</t>
+  </si>
+  <si>
+    <t>19.04.202627</t>
+  </si>
+  <si>
+    <t>19.04.202628</t>
+  </si>
+  <si>
+    <t>19.04.202629</t>
+  </si>
+  <si>
+    <t>19.04.202630</t>
+  </si>
+  <si>
+    <t>19.04.202631</t>
+  </si>
+  <si>
+    <t>19.04.202632</t>
+  </si>
+  <si>
+    <t>19.04.202633</t>
+  </si>
+  <si>
+    <t>19.04.202634</t>
+  </si>
+  <si>
+    <t>19.04.202635</t>
+  </si>
+  <si>
+    <t>19.04.202636</t>
+  </si>
+  <si>
+    <t>19.04.202637</t>
+  </si>
+  <si>
+    <t>19.04.202638</t>
+  </si>
+  <si>
+    <t>19.04.202639</t>
+  </si>
+  <si>
+    <t>19.04.202640</t>
+  </si>
+  <si>
+    <t>19.04.202641</t>
+  </si>
+  <si>
+    <t>19.04.202642</t>
+  </si>
+  <si>
+    <t>19.04.202643</t>
+  </si>
+  <si>
+    <t>19.04.202644</t>
+  </si>
+  <si>
+    <t>19.04.202645</t>
+  </si>
+  <si>
+    <t>19.04.202646</t>
+  </si>
+  <si>
+    <t>19.04.202647</t>
+  </si>
+  <si>
+    <t>19.04.202648</t>
+  </si>
+  <si>
+    <t>19.04.202649</t>
+  </si>
+  <si>
+    <t>19.04.202650</t>
+  </si>
+  <si>
+    <t>19.04.202651</t>
+  </si>
+  <si>
+    <t>19.04.202652</t>
+  </si>
+  <si>
+    <t>19.04.202653</t>
+  </si>
+  <si>
+    <t>19.04.202654</t>
+  </si>
+  <si>
+    <t>19.04.202655</t>
+  </si>
+  <si>
+    <t>19.04.202656</t>
+  </si>
+  <si>
+    <t>19.04.202657</t>
+  </si>
+  <si>
+    <t>19.04.202658</t>
+  </si>
+  <si>
+    <t>19.04.202659</t>
+  </si>
+  <si>
+    <t>19.04.202660</t>
+  </si>
+  <si>
+    <t>19.04.202661</t>
+  </si>
+  <si>
+    <t>19.04.202662</t>
+  </si>
+  <si>
+    <t>19.04.202663</t>
+  </si>
+  <si>
+    <t>19.04.202664</t>
+  </si>
+  <si>
+    <t>19.04.202665</t>
+  </si>
+  <si>
+    <t>19.04.202666</t>
+  </si>
+  <si>
+    <t>19.04.202667</t>
+  </si>
+  <si>
+    <t>19.04.202668</t>
+  </si>
+  <si>
+    <t>19.04.202669</t>
+  </si>
+  <si>
+    <t>19.04.202670</t>
+  </si>
+  <si>
+    <t>19.04.202671</t>
+  </si>
+  <si>
+    <t>19.04.202672</t>
+  </si>
+  <si>
+    <t>19.04.202673</t>
+  </si>
+  <si>
+    <t>19.04.202674</t>
+  </si>
+  <si>
+    <t>19.04.202675</t>
+  </si>
+  <si>
+    <t>19.04.202676</t>
+  </si>
+  <si>
+    <t>19.04.202677</t>
+  </si>
+  <si>
+    <t>19.04.202678</t>
+  </si>
+  <si>
+    <t>19.04.202679</t>
+  </si>
+  <si>
+    <t>19.04.202680</t>
+  </si>
+  <si>
+    <t>19.04.202681</t>
+  </si>
+  <si>
+    <t>19.04.202682</t>
+  </si>
+  <si>
+    <t>19.04.202683</t>
+  </si>
+  <si>
+    <t>19.04.202684</t>
+  </si>
+  <si>
+    <t>19.04.202685</t>
+  </si>
+  <si>
+    <t>19.04.202686</t>
+  </si>
+  <si>
+    <t>19.04.202687</t>
+  </si>
+  <si>
+    <t>19.04.202688</t>
+  </si>
+  <si>
+    <t>19.04.202689</t>
+  </si>
+  <si>
+    <t>19.04.202690</t>
+  </si>
+  <si>
+    <t>19.04.202691</t>
+  </si>
+  <si>
+    <t>19.04.202692</t>
+  </si>
+  <si>
+    <t>19.04.202693</t>
+  </si>
+  <si>
+    <t>19.04.202694</t>
+  </si>
+  <si>
+    <t>19.04.202695</t>
+  </si>
+  <si>
+    <t>19.04.202696</t>
+  </si>
+  <si>
+    <t>20.04.20261</t>
+  </si>
+  <si>
+    <t>20.04.20262</t>
+  </si>
+  <si>
+    <t>20.04.20263</t>
+  </si>
+  <si>
+    <t>20.04.20264</t>
+  </si>
+  <si>
+    <t>20.04.20265</t>
+  </si>
+  <si>
+    <t>20.04.20266</t>
+  </si>
+  <si>
+    <t>20.04.20267</t>
+  </si>
+  <si>
+    <t>20.04.20268</t>
+  </si>
+  <si>
+    <t>20.04.20269</t>
+  </si>
+  <si>
+    <t>20.04.202610</t>
+  </si>
+  <si>
+    <t>20.04.202611</t>
+  </si>
+  <si>
+    <t>20.04.202612</t>
+  </si>
+  <si>
+    <t>20.04.202613</t>
+  </si>
+  <si>
+    <t>20.04.202614</t>
+  </si>
+  <si>
+    <t>20.04.202615</t>
+  </si>
+  <si>
+    <t>20.04.202616</t>
+  </si>
+  <si>
+    <t>20.04.202617</t>
+  </si>
+  <si>
+    <t>20.04.202618</t>
+  </si>
+  <si>
+    <t>20.04.202619</t>
+  </si>
+  <si>
+    <t>20.04.202620</t>
+  </si>
+  <si>
+    <t>20.04.202621</t>
+  </si>
+  <si>
+    <t>20.04.202622</t>
+  </si>
+  <si>
+    <t>20.04.202623</t>
+  </si>
+  <si>
+    <t>20.04.202624</t>
+  </si>
+  <si>
+    <t>20.04.202625</t>
+  </si>
+  <si>
+    <t>20.04.202626</t>
+  </si>
+  <si>
+    <t>20.04.202627</t>
+  </si>
+  <si>
+    <t>20.04.202628</t>
+  </si>
+  <si>
+    <t>20.04.202629</t>
+  </si>
+  <si>
+    <t>20.04.202630</t>
+  </si>
+  <si>
+    <t>20.04.202631</t>
+  </si>
+  <si>
+    <t>20.04.202632</t>
+  </si>
+  <si>
+    <t>20.04.202633</t>
+  </si>
+  <si>
+    <t>20.04.202634</t>
+  </si>
+  <si>
+    <t>20.04.202635</t>
+  </si>
+  <si>
+    <t>20.04.202636</t>
+  </si>
+  <si>
+    <t>20.04.202637</t>
+  </si>
+  <si>
+    <t>20.04.202638</t>
+  </si>
+  <si>
+    <t>20.04.202639</t>
+  </si>
+  <si>
+    <t>20.04.202640</t>
+  </si>
+  <si>
+    <t>20.04.202641</t>
+  </si>
+  <si>
+    <t>20.04.202642</t>
+  </si>
+  <si>
+    <t>20.04.202643</t>
+  </si>
+  <si>
+    <t>20.04.202644</t>
+  </si>
+  <si>
+    <t>20.04.202645</t>
+  </si>
+  <si>
+    <t>20.04.202646</t>
+  </si>
+  <si>
+    <t>20.04.202647</t>
+  </si>
+  <si>
+    <t>20.04.202648</t>
+  </si>
+  <si>
+    <t>20.04.202649</t>
+  </si>
+  <si>
+    <t>20.04.202650</t>
+  </si>
+  <si>
+    <t>20.04.202651</t>
+  </si>
+  <si>
+    <t>20.04.202652</t>
+  </si>
+  <si>
+    <t>20.04.202653</t>
+  </si>
+  <si>
+    <t>20.04.202654</t>
+  </si>
+  <si>
+    <t>20.04.202655</t>
+  </si>
+  <si>
+    <t>20.04.202656</t>
+  </si>
+  <si>
+    <t>20.04.202657</t>
+  </si>
+  <si>
+    <t>20.04.202658</t>
+  </si>
+  <si>
+    <t>20.04.202659</t>
+  </si>
+  <si>
+    <t>20.04.202660</t>
+  </si>
+  <si>
+    <t>20.04.202661</t>
+  </si>
+  <si>
+    <t>20.04.202662</t>
+  </si>
+  <si>
+    <t>20.04.202663</t>
+  </si>
+  <si>
+    <t>20.04.202664</t>
+  </si>
+  <si>
+    <t>20.04.202665</t>
+  </si>
+  <si>
+    <t>20.04.202666</t>
+  </si>
+  <si>
+    <t>20.04.202667</t>
+  </si>
+  <si>
+    <t>20.04.202668</t>
+  </si>
+  <si>
+    <t>20.04.202669</t>
+  </si>
+  <si>
+    <t>20.04.202670</t>
+  </si>
+  <si>
+    <t>20.04.202671</t>
+  </si>
+  <si>
+    <t>20.04.202672</t>
+  </si>
+  <si>
+    <t>20.04.202673</t>
+  </si>
+  <si>
+    <t>20.04.202674</t>
+  </si>
+  <si>
+    <t>20.04.202675</t>
+  </si>
+  <si>
+    <t>20.04.202676</t>
+  </si>
+  <si>
+    <t>20.04.202677</t>
+  </si>
+  <si>
+    <t>20.04.202678</t>
+  </si>
+  <si>
+    <t>20.04.202679</t>
+  </si>
+  <si>
+    <t>20.04.202680</t>
+  </si>
+  <si>
+    <t>20.04.202681</t>
+  </si>
+  <si>
+    <t>20.04.202682</t>
+  </si>
+  <si>
+    <t>20.04.202683</t>
+  </si>
+  <si>
+    <t>20.04.202684</t>
+  </si>
+  <si>
+    <t>20.04.202685</t>
+  </si>
+  <si>
+    <t>20.04.202686</t>
+  </si>
+  <si>
+    <t>20.04.202687</t>
+  </si>
+  <si>
+    <t>20.04.202688</t>
+  </si>
+  <si>
+    <t>20.04.202689</t>
+  </si>
+  <si>
+    <t>20.04.202690</t>
+  </si>
+  <si>
+    <t>20.04.202691</t>
+  </si>
+  <si>
+    <t>20.04.202692</t>
+  </si>
+  <si>
+    <t>20.04.202693</t>
+  </si>
+  <si>
+    <t>20.04.202694</t>
+  </si>
+  <si>
+    <t>20.04.202695</t>
+  </si>
+  <si>
+    <t>20.04.202696</t>
   </si>
 </sst>
 </file>
@@ -966,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -988,13 +1564,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B2">
-        <v>592.54</v>
+        <v>492.289</v>
       </c>
       <c r="C2">
-        <v>685</v>
+        <v>442</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1581,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46128.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
-        <v>568.7140000000001</v>
+        <v>470.433</v>
       </c>
       <c r="C3">
-        <v>667</v>
+        <v>413</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1598,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46128.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
-        <v>549.0650000000001</v>
+        <v>450.249</v>
       </c>
       <c r="C4">
-        <v>641</v>
+        <v>373</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1615,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46128.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
-        <v>527.902</v>
+        <v>424.939</v>
       </c>
       <c r="C5">
-        <v>612</v>
+        <v>362</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1632,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46128.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
-        <v>490.559</v>
+        <v>384.318</v>
       </c>
       <c r="C6">
-        <v>594</v>
+        <v>357</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1649,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46128.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
-        <v>465.157</v>
+        <v>366.312</v>
       </c>
       <c r="C7">
-        <v>566</v>
+        <v>358</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1666,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46128.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
-        <v>447.718</v>
+        <v>345.968</v>
       </c>
       <c r="C8">
-        <v>556</v>
+        <v>348</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1683,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46128.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
-        <v>432.307</v>
+        <v>327.101</v>
       </c>
       <c r="C9">
-        <v>532</v>
+        <v>336</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1700,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46128.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
-        <v>402.808</v>
+        <v>299.321</v>
       </c>
       <c r="C10">
-        <v>511</v>
+        <v>313</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1717,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46128.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
-        <v>392.081</v>
+        <v>283.355</v>
       </c>
       <c r="C11">
-        <v>503</v>
+        <v>290</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1734,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46128.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
-        <v>378.85</v>
+        <v>273.912</v>
       </c>
       <c r="C12">
-        <v>496</v>
+        <v>297</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1751,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46128.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
-        <v>368.192</v>
+        <v>265.646</v>
       </c>
       <c r="C13">
-        <v>467</v>
+        <v>284</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1768,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46128.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
-        <v>348.022</v>
+        <v>255.408</v>
       </c>
       <c r="C14">
-        <v>421</v>
+        <v>260</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1785,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46128.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
-        <v>340.524</v>
+        <v>248.314</v>
       </c>
       <c r="C15">
-        <v>385</v>
+        <v>242</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1802,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46128.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
-        <v>334.011</v>
+        <v>239.166</v>
       </c>
       <c r="C16">
-        <v>361</v>
+        <v>219</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1819,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46128.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
-        <v>321.79</v>
+        <v>232.88</v>
       </c>
       <c r="C17">
-        <v>338</v>
+        <v>202</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1836,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46128.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>327.048</v>
+        <v>241.677</v>
       </c>
       <c r="C18">
-        <v>337</v>
+        <v>201</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1853,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46128.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
-        <v>317.894</v>
+        <v>232.256</v>
       </c>
       <c r="C19">
-        <v>325</v>
+        <v>198</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1870,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46128.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
-        <v>309.743</v>
+        <v>224.945</v>
       </c>
       <c r="C20">
-        <v>314</v>
+        <v>190</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1887,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46128.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>301.832</v>
+        <v>218.791</v>
       </c>
       <c r="C21">
-        <v>305</v>
+        <v>194</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1904,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46128.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
-        <v>269.475</v>
+        <v>197.97</v>
       </c>
       <c r="C22">
-        <v>295</v>
+        <v>198</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1921,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46128.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>290.431</v>
+        <v>189.546</v>
       </c>
       <c r="C23">
-        <v>287</v>
+        <v>190</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1938,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46128.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>285.438</v>
+        <v>212.254</v>
       </c>
       <c r="C24">
-        <v>266</v>
+        <v>189</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1955,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46128.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>282.303</v>
+        <v>208.106</v>
       </c>
       <c r="C25">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1972,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46128.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>269.953</v>
+        <v>203.017</v>
       </c>
       <c r="C26">
-        <v>292</v>
+        <v>173</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1989,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46128.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>271.191</v>
+        <v>199.185</v>
       </c>
       <c r="C27">
-        <v>301</v>
+        <v>143</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +2006,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46128.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>269.5</v>
+        <v>194.304</v>
       </c>
       <c r="C28">
-        <v>311</v>
+        <v>136</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +2023,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46128.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>272.141</v>
+        <v>190.044</v>
       </c>
       <c r="C29">
-        <v>318</v>
+        <v>139</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +2040,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46128.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
-        <v>268.449</v>
+        <v>174.644</v>
       </c>
       <c r="C30">
-        <v>319</v>
+        <v>133</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +2057,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46128.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
-        <v>263.221</v>
+        <v>168.972</v>
       </c>
       <c r="C31">
-        <v>289</v>
+        <v>105</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +2074,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46128.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
-        <v>252.759</v>
+        <v>157.268</v>
       </c>
       <c r="C32">
-        <v>254</v>
+        <v>72</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +2091,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46128.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
-        <v>247.16</v>
+        <v>149.267</v>
       </c>
       <c r="C33">
-        <v>219</v>
+        <v>53</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +2108,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46128.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>271.059</v>
+        <v>128.096</v>
       </c>
       <c r="C34">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +2125,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46128.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>263.113</v>
+        <v>119.716</v>
       </c>
       <c r="C35">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +2142,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46128.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
-        <v>244.604</v>
+        <v>108.219</v>
       </c>
       <c r="C36">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +2159,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46128.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
-        <v>235.746</v>
+        <v>101.987</v>
       </c>
       <c r="C37">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +2176,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46128.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>232.409</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="C38">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +2193,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46128.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>238.527</v>
+        <v>101.639</v>
       </c>
       <c r="C39">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +2210,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46128.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
-        <v>244.997</v>
+        <v>106.323</v>
       </c>
       <c r="C40">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +2227,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46128.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
-        <v>252.147</v>
+        <v>111.178</v>
       </c>
       <c r="C41">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +2244,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46128.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>259.223</v>
+        <v>122.041</v>
       </c>
       <c r="C42">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +2261,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46128.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>268.202</v>
+        <v>127.32</v>
       </c>
       <c r="C43">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +2278,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46128.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>277.339</v>
+        <v>132.758</v>
       </c>
       <c r="C44">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +2295,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46128.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
-        <v>286.445</v>
+        <v>137.693</v>
       </c>
       <c r="C45">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +2312,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46128.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
-        <v>310.287</v>
+        <v>147.869</v>
       </c>
       <c r="C46">
-        <v>181</v>
+        <v>71</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +2329,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46128.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>320.25</v>
+        <v>151.088</v>
       </c>
       <c r="C47">
-        <v>192</v>
+        <v>66</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +2346,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46128.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>331.64</v>
+        <v>154.678</v>
       </c>
       <c r="C48">
-        <v>193</v>
+        <v>62</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,10 +2363,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46128.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
-        <v>343.052</v>
+        <v>159.297</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1804,13 +2380,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46128.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
-        <v>330.465</v>
+        <v>149.505</v>
       </c>
       <c r="C50">
-        <v>185</v>
+        <v>64</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +2397,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46128.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>341.567</v>
+        <v>152.66</v>
       </c>
       <c r="C51">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +2414,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46128.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>352.632</v>
+        <v>156.874</v>
       </c>
       <c r="C52">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +2431,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46128.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
-        <v>364.514</v>
+        <v>159.964</v>
       </c>
       <c r="C53">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +2448,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46128.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B54">
-        <v>374.336</v>
+        <v>163.73</v>
       </c>
       <c r="C54">
-        <v>185</v>
+        <v>39</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +2465,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46128.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B55">
-        <v>384.999</v>
+        <v>168.04</v>
       </c>
       <c r="C55">
-        <v>182</v>
+        <v>38</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +2482,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46128.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B56">
-        <v>395.258</v>
+        <v>171.965</v>
       </c>
       <c r="C56">
-        <v>196</v>
+        <v>34</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +2499,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46128.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B57">
-        <v>406.279</v>
+        <v>175.952</v>
       </c>
       <c r="C57">
-        <v>212</v>
+        <v>32</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +2516,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46128.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B58">
-        <v>420.211</v>
+        <v>172.821</v>
       </c>
       <c r="C58">
-        <v>228</v>
+        <v>31</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +2533,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46128.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B59">
-        <v>430.595</v>
+        <v>177.526</v>
       </c>
       <c r="C59">
-        <v>247</v>
+        <v>27</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +2550,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46128.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B60">
-        <v>440.127</v>
+        <v>182.393</v>
       </c>
       <c r="C60">
-        <v>261</v>
+        <v>23</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +2567,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46128.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B61">
-        <v>450.147</v>
+        <v>186.972</v>
       </c>
       <c r="C61">
-        <v>284</v>
+        <v>33</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2584,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46128.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B62">
-        <v>466.494</v>
+        <v>193.94</v>
       </c>
       <c r="C62">
-        <v>319</v>
+        <v>40</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2601,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46128.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B63">
-        <v>476.9</v>
+        <v>201.676</v>
       </c>
       <c r="C63">
-        <v>349</v>
+        <v>50</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2618,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46128.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B64">
-        <v>488.48</v>
+        <v>208.28</v>
       </c>
       <c r="C64">
-        <v>396</v>
+        <v>57</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2635,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46128.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B65">
-        <v>499.268</v>
+        <v>214.292</v>
       </c>
       <c r="C65">
-        <v>447</v>
+        <v>67</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2652,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46128.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B66">
-        <v>459.538</v>
+        <v>219.51</v>
       </c>
       <c r="C66">
-        <v>464</v>
+        <v>86</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2669,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46128.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B67">
-        <v>467.344</v>
+        <v>224.067</v>
       </c>
       <c r="C67">
-        <v>490</v>
+        <v>106</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2686,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46128.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B68">
-        <v>474.564</v>
+        <v>227.76</v>
       </c>
       <c r="C68">
-        <v>517</v>
+        <v>122</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2703,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46128.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B69">
-        <v>482.431</v>
+        <v>230.483</v>
       </c>
       <c r="C69">
-        <v>548</v>
+        <v>147</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2720,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46128.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B70">
-        <v>488.425</v>
+        <v>229.954</v>
       </c>
       <c r="C70">
-        <v>567</v>
+        <v>161</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2737,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46128.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B71">
-        <v>495.54</v>
+        <v>233.124</v>
       </c>
       <c r="C71">
-        <v>587</v>
+        <v>165</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2754,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46128.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B72">
-        <v>503.11</v>
+        <v>235.809</v>
       </c>
       <c r="C72">
-        <v>611</v>
+        <v>184</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2771,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46128.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B73">
-        <v>512.556</v>
+        <v>239.164</v>
       </c>
       <c r="C73">
-        <v>631</v>
+        <v>216</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2788,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46128.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B74">
-        <v>528.972</v>
+        <v>248.793</v>
       </c>
       <c r="C74">
-        <v>644</v>
+        <v>250</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2805,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46128.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B75">
-        <v>546.249</v>
+        <v>250.9</v>
       </c>
       <c r="C75">
-        <v>654</v>
+        <v>294</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2822,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46128.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B76">
-        <v>560.875</v>
+        <v>252.83</v>
       </c>
       <c r="C76">
-        <v>680</v>
+        <v>308</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2839,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46128.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B77">
-        <v>572.953</v>
+        <v>255.55</v>
       </c>
       <c r="C77">
-        <v>683</v>
+        <v>298</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2856,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46128.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B78">
-        <v>592.843</v>
+        <v>250.756</v>
       </c>
       <c r="C78">
-        <v>669</v>
+        <v>306</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2873,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46128.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B79">
-        <v>605.588</v>
+        <v>247.006</v>
       </c>
       <c r="C79">
-        <v>692</v>
+        <v>274</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2890,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46128.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B80">
-        <v>618.4349999999999</v>
+        <v>242.379</v>
       </c>
       <c r="C80">
-        <v>702</v>
+        <v>248</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2907,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46128.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B81">
-        <v>640.071</v>
+        <v>236.831</v>
       </c>
       <c r="C81">
-        <v>745</v>
+        <v>223</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2924,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46128.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B82">
-        <v>654.652</v>
+        <v>227.465</v>
       </c>
       <c r="C82">
-        <v>751</v>
+        <v>179</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2941,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46128.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B83">
-        <v>648.175</v>
+        <v>221.904</v>
       </c>
       <c r="C83">
-        <v>737</v>
+        <v>142</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2958,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46128.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B84">
-        <v>650.3339999999999</v>
+        <v>215.489</v>
       </c>
       <c r="C84">
-        <v>750</v>
+        <v>127</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2975,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46128.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B85">
-        <v>651.987</v>
+        <v>208.289</v>
       </c>
       <c r="C85">
-        <v>730</v>
+        <v>123</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2992,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46128.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B86">
-        <v>655.191</v>
+        <v>197.694</v>
       </c>
       <c r="C86">
-        <v>713</v>
+        <v>115</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +3009,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46128.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B87">
-        <v>639.574</v>
+        <v>195.738</v>
       </c>
       <c r="C87">
-        <v>698</v>
+        <v>114</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +3026,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46128.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B88">
-        <v>642.812</v>
+        <v>193.064</v>
       </c>
       <c r="C88">
-        <v>670</v>
+        <v>113</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +3043,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46128.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B89">
-        <v>626.904</v>
+        <v>190.67</v>
       </c>
       <c r="C89">
-        <v>675</v>
+        <v>114</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +3060,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46128.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B90">
-        <v>608.9109999999999</v>
+        <v>190.547</v>
       </c>
       <c r="C90">
-        <v>688</v>
+        <v>120</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +3077,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46128.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B91">
-        <v>590.879</v>
+        <v>200.607</v>
       </c>
       <c r="C91">
-        <v>660</v>
+        <v>124</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +3094,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46128.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B92">
-        <v>574.389</v>
+        <v>211.629</v>
       </c>
       <c r="C92">
-        <v>621</v>
+        <v>138</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +3111,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46128.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B93">
-        <v>557.12</v>
+        <v>223.221</v>
       </c>
       <c r="C93">
-        <v>561</v>
+        <v>165</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +3128,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46128.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B94">
-        <v>577.4930000000001</v>
+        <v>343.378</v>
       </c>
       <c r="C94">
-        <v>536</v>
+        <v>205</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +3145,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46128.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B95">
-        <v>557.9589999999999</v>
+        <v>365.025</v>
       </c>
       <c r="C95">
-        <v>532</v>
+        <v>256</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +3162,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46128.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B96">
-        <v>541.802</v>
+        <v>391.148</v>
       </c>
       <c r="C96">
-        <v>511</v>
+        <v>338</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +3179,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46128.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B97">
-        <v>516.087</v>
+        <v>417.707</v>
       </c>
       <c r="C97">
-        <v>480</v>
+        <v>395</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +3196,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B98">
-        <v>492.289</v>
+        <v>529.785</v>
       </c>
       <c r="C98">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +3213,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46129.01041666666</v>
+        <v>46130.01041666666</v>
       </c>
       <c r="B99">
-        <v>470.433</v>
+        <v>570.852</v>
       </c>
       <c r="C99">
-        <v>413</v>
+        <v>523</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +3230,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46129.02083333334</v>
+        <v>46130.02083333334</v>
       </c>
       <c r="B100">
-        <v>450.249</v>
+        <v>610.544</v>
       </c>
       <c r="C100">
-        <v>373</v>
+        <v>570</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +3247,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46129.03125</v>
+        <v>46130.03125</v>
       </c>
       <c r="B101">
-        <v>424.939</v>
+        <v>653.384</v>
       </c>
       <c r="C101">
-        <v>362</v>
+        <v>636</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +3264,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46129.04166666666</v>
+        <v>46130.04166666666</v>
       </c>
       <c r="B102">
-        <v>384.318</v>
+        <v>726.135</v>
       </c>
       <c r="C102">
-        <v>357</v>
+        <v>666</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +3281,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46129.05208333334</v>
+        <v>46130.05208333334</v>
       </c>
       <c r="B103">
-        <v>366.312</v>
+        <v>765.408</v>
       </c>
       <c r="C103">
-        <v>358</v>
+        <v>717</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +3298,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46129.0625</v>
+        <v>46130.0625</v>
       </c>
       <c r="B104">
-        <v>345.968</v>
+        <v>807.5</v>
       </c>
       <c r="C104">
-        <v>348</v>
+        <v>819</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +3315,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46129.07291666666</v>
+        <v>46130.07291666666</v>
       </c>
       <c r="B105">
-        <v>327.101</v>
+        <v>851.753</v>
       </c>
       <c r="C105">
-        <v>336</v>
+        <v>916</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +3332,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46129.08333333334</v>
+        <v>46130.08333333334</v>
       </c>
       <c r="B106">
-        <v>299.321</v>
+        <v>905.143</v>
       </c>
       <c r="C106">
-        <v>313</v>
+        <v>981</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +3349,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46129.09375</v>
+        <v>46130.09375</v>
       </c>
       <c r="B107">
-        <v>283.355</v>
+        <v>929.683</v>
       </c>
       <c r="C107">
-        <v>290</v>
+        <v>1040</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +3366,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46129.10416666666</v>
+        <v>46130.10416666666</v>
       </c>
       <c r="B108">
-        <v>273.912</v>
+        <v>955.653</v>
       </c>
       <c r="C108">
-        <v>297</v>
+        <v>1078</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +3383,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46129.11458333334</v>
+        <v>46130.11458333334</v>
       </c>
       <c r="B109">
-        <v>265.646</v>
+        <v>997.188</v>
       </c>
       <c r="C109">
-        <v>284</v>
+        <v>1133</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +3400,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46129.125</v>
+        <v>46130.125</v>
       </c>
       <c r="B110">
-        <v>255.408</v>
+        <v>1075.567</v>
       </c>
       <c r="C110">
-        <v>260</v>
+        <v>1205</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +3417,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46129.13541666666</v>
+        <v>46130.13541666666</v>
       </c>
       <c r="B111">
-        <v>248.314</v>
+        <v>1101.991</v>
       </c>
       <c r="C111">
-        <v>242</v>
+        <v>1200</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +3434,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46129.14583333334</v>
+        <v>46130.14583333334</v>
       </c>
       <c r="B112">
-        <v>239.166</v>
+        <v>1130.733</v>
       </c>
       <c r="C112">
-        <v>219</v>
+        <v>1181</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +3451,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46129.15625</v>
+        <v>46130.15625</v>
       </c>
       <c r="B113">
-        <v>232.88</v>
+        <v>1162.317</v>
       </c>
       <c r="C113">
-        <v>202</v>
+        <v>1210</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +3468,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46129.16666666666</v>
+        <v>46130.16666666666</v>
       </c>
       <c r="B114">
-        <v>241.677</v>
+        <v>1237.075</v>
       </c>
       <c r="C114">
-        <v>201</v>
+        <v>1209</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +3485,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46129.17708333334</v>
+        <v>46130.17708333334</v>
       </c>
       <c r="B115">
-        <v>232.256</v>
+        <v>1284.013</v>
       </c>
       <c r="C115">
-        <v>198</v>
+        <v>1182</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +3502,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46129.1875</v>
+        <v>46130.1875</v>
       </c>
       <c r="B116">
-        <v>224.945</v>
+        <v>1307.813</v>
       </c>
       <c r="C116">
-        <v>190</v>
+        <v>1138</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +3519,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46129.19791666666</v>
+        <v>46130.19791666666</v>
       </c>
       <c r="B117">
-        <v>218.791</v>
+        <v>1349.779</v>
       </c>
       <c r="C117">
-        <v>194</v>
+        <v>1094</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +3536,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46129.20833333334</v>
+        <v>46130.20833333334</v>
       </c>
       <c r="B118">
-        <v>197.97</v>
+        <v>1377.421</v>
       </c>
       <c r="C118">
-        <v>198</v>
+        <v>1047</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +3553,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46129.21875</v>
+        <v>46130.21875</v>
       </c>
       <c r="B119">
-        <v>189.546</v>
+        <v>1415.568</v>
       </c>
       <c r="C119">
-        <v>190</v>
+        <v>1029</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +3570,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46129.22916666666</v>
+        <v>46130.22916666666</v>
       </c>
       <c r="B120">
-        <v>212.254</v>
+        <v>1444.679</v>
       </c>
       <c r="C120">
-        <v>189</v>
+        <v>1013</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3587,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46129.23958333334</v>
+        <v>46130.23958333334</v>
       </c>
       <c r="B121">
-        <v>208.106</v>
+        <v>1474.413</v>
       </c>
       <c r="C121">
-        <v>193</v>
+        <v>996</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3604,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46129.25</v>
+        <v>46130.25</v>
       </c>
       <c r="B122">
-        <v>203.017</v>
+        <v>1486.771</v>
       </c>
       <c r="C122">
-        <v>173</v>
+        <v>959</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3621,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46129.26041666666</v>
+        <v>46130.26041666666</v>
       </c>
       <c r="B123">
-        <v>199.185</v>
+        <v>1526.34</v>
       </c>
       <c r="C123">
-        <v>143</v>
+        <v>947</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3638,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46129.27083333334</v>
+        <v>46130.27083333334</v>
       </c>
       <c r="B124">
-        <v>194.304</v>
+        <v>1582.393</v>
       </c>
       <c r="C124">
-        <v>136</v>
+        <v>957</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3655,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46129.28125</v>
+        <v>46130.28125</v>
       </c>
       <c r="B125">
-        <v>190.044</v>
+        <v>1650.876</v>
       </c>
       <c r="C125">
-        <v>139</v>
+        <v>927</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3672,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46129.29166666666</v>
+        <v>46130.29166666666</v>
       </c>
       <c r="B126">
-        <v>174.644</v>
+        <v>1659.45</v>
       </c>
       <c r="C126">
-        <v>133</v>
+        <v>888</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3689,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46129.30208333334</v>
+        <v>46130.30208333334</v>
       </c>
       <c r="B127">
-        <v>168.972</v>
+        <v>1722.237</v>
       </c>
       <c r="C127">
-        <v>105</v>
+        <v>906</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3706,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46129.3125</v>
+        <v>46130.3125</v>
       </c>
       <c r="B128">
-        <v>157.268</v>
+        <v>1791.208</v>
       </c>
       <c r="C128">
-        <v>72</v>
+        <v>971</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3723,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46129.32291666666</v>
+        <v>46130.32291666666</v>
       </c>
       <c r="B129">
-        <v>149.267</v>
+        <v>1845.953</v>
       </c>
       <c r="C129">
-        <v>53</v>
+        <v>1069</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3740,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46129.33333333334</v>
+        <v>46130.33333333334</v>
       </c>
       <c r="B130">
-        <v>128.096</v>
+        <v>2108.153</v>
       </c>
       <c r="C130">
-        <v>52</v>
+        <v>1264</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3757,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46129.34375</v>
+        <v>46130.34375</v>
       </c>
       <c r="B131">
-        <v>119.716</v>
+        <v>2140.865</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>1370</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3774,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46129.35416666666</v>
+        <v>46130.35416666666</v>
       </c>
       <c r="B132">
-        <v>108.219</v>
+        <v>2242.251</v>
       </c>
       <c r="C132">
-        <v>57</v>
+        <v>1408</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3791,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46129.36458333334</v>
+        <v>46130.36458333334</v>
       </c>
       <c r="B133">
-        <v>101.987</v>
+        <v>2298.931</v>
       </c>
       <c r="C133">
-        <v>67</v>
+        <v>1430</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3808,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46129.375</v>
+        <v>46130.375</v>
       </c>
       <c r="B134">
-        <v>99.98999999999999</v>
+        <v>2409.024</v>
       </c>
       <c r="C134">
-        <v>72</v>
+        <v>1564</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3825,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46129.38541666666</v>
+        <v>46130.38541666666</v>
       </c>
       <c r="B135">
-        <v>101.639</v>
+        <v>2424.114</v>
       </c>
       <c r="C135">
-        <v>73</v>
+        <v>1704</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3842,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46129.39583333334</v>
+        <v>46130.39583333334</v>
       </c>
       <c r="B136">
-        <v>106.323</v>
+        <v>2417.108</v>
       </c>
       <c r="C136">
-        <v>85</v>
+        <v>1891</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3859,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46129.40625</v>
+        <v>46130.40625</v>
       </c>
       <c r="B137">
-        <v>111.178</v>
+        <v>2309.986</v>
       </c>
       <c r="C137">
-        <v>97</v>
+        <v>1981</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3876,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46129.41666666666</v>
+        <v>46130.41666666666</v>
       </c>
       <c r="B138">
-        <v>122.041</v>
+        <v>2332.214</v>
       </c>
       <c r="C138">
-        <v>91</v>
+        <v>2077</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3893,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46129.42708333334</v>
+        <v>46130.42708333334</v>
       </c>
       <c r="B139">
-        <v>127.32</v>
+        <v>2151.305</v>
       </c>
       <c r="C139">
-        <v>78</v>
+        <v>2015</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3910,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46129.4375</v>
+        <v>46130.4375</v>
       </c>
       <c r="B140">
-        <v>132.758</v>
+        <v>2089.519</v>
       </c>
       <c r="C140">
-        <v>65</v>
+        <v>1922</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3927,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46129.44791666666</v>
+        <v>46130.44791666666</v>
       </c>
       <c r="B141">
-        <v>137.693</v>
+        <v>2077.467</v>
       </c>
       <c r="C141">
-        <v>68</v>
+        <v>1937</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3944,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46129.45833333334</v>
+        <v>46130.45833333334</v>
       </c>
       <c r="B142">
-        <v>147.869</v>
+        <v>2049.904</v>
       </c>
       <c r="C142">
-        <v>71</v>
+        <v>1924</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3961,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46129.46875</v>
+        <v>46130.46875</v>
       </c>
       <c r="B143">
-        <v>151.088</v>
+        <v>2034.055</v>
       </c>
       <c r="C143">
-        <v>66</v>
+        <v>1926</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3978,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46129.47916666666</v>
+        <v>46130.47916666666</v>
       </c>
       <c r="B144">
-        <v>154.678</v>
+        <v>2017.273</v>
       </c>
       <c r="C144">
-        <v>62</v>
+        <v>1902</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3995,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46129.48958333334</v>
+        <v>46130.48958333334</v>
       </c>
       <c r="B145">
-        <v>159.297</v>
+        <v>1676.594</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1813</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +4012,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46129.5</v>
+        <v>46130.5</v>
       </c>
       <c r="B146">
-        <v>149.505</v>
+        <v>1988.412</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1908</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +4029,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46129.51041666666</v>
+        <v>46130.51041666666</v>
       </c>
       <c r="B147">
-        <v>152.66</v>
+        <v>1842.593</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1913</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +4046,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46129.52083333334</v>
+        <v>46130.52083333334</v>
       </c>
       <c r="B148">
-        <v>156.874</v>
+        <v>1660.43</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1798</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,13 +4063,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46129.53125</v>
+        <v>46130.53125</v>
       </c>
       <c r="B149">
-        <v>159.964</v>
+        <v>1659.245</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1604</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3504,13 +4080,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46129.54166666666</v>
+        <v>46130.54166666666</v>
       </c>
       <c r="B150">
-        <v>163.73</v>
+        <v>1666.784</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1635</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3521,13 +4097,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46129.55208333334</v>
+        <v>46130.55208333334</v>
       </c>
       <c r="B151">
-        <v>168.04</v>
+        <v>1673.94</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>1636</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3538,13 +4114,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46129.5625</v>
+        <v>46130.5625</v>
       </c>
       <c r="B152">
-        <v>171.965</v>
+        <v>1680.633</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>1655</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3555,13 +4131,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46129.57291666666</v>
+        <v>46130.57291666666</v>
       </c>
       <c r="B153">
-        <v>175.952</v>
+        <v>1698.02</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>1707</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3572,13 +4148,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46129.58333333334</v>
+        <v>46130.58333333334</v>
       </c>
       <c r="B154">
-        <v>172.821</v>
+        <v>2043.324</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>1769</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3589,13 +4165,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46129.59375</v>
+        <v>46130.59375</v>
       </c>
       <c r="B155">
-        <v>177.526</v>
+        <v>2051.406</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>1897</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3606,13 +4182,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46129.60416666666</v>
+        <v>46130.60416666666</v>
       </c>
       <c r="B156">
-        <v>182.393</v>
+        <v>2060.342</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>1883</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3623,13 +4199,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46129.61458333334</v>
+        <v>46130.61458333334</v>
       </c>
       <c r="B157">
-        <v>186.972</v>
+        <v>2068.887</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1892</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3640,13 +4216,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46129.625</v>
+        <v>46130.625</v>
       </c>
       <c r="B158">
-        <v>193.94</v>
+        <v>2070.77</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>1881</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3657,13 +4233,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46129.63541666666</v>
+        <v>46130.63541666666</v>
       </c>
       <c r="B159">
-        <v>201.676</v>
+        <v>2064.142</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>1856</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3674,13 +4250,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46129.64583333334</v>
+        <v>46130.64583333334</v>
       </c>
       <c r="B160">
-        <v>208.28</v>
+        <v>2234.001</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>1924</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3691,13 +4267,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46129.65625</v>
+        <v>46130.65625</v>
       </c>
       <c r="B161">
-        <v>214.292</v>
+        <v>2223.781</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>1922</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3708,13 +4284,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46129.66666666666</v>
+        <v>46130.66666666666</v>
       </c>
       <c r="B162">
-        <v>219.51</v>
+        <v>2190.137</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>1907</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3725,13 +4301,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46129.67708333334</v>
+        <v>46130.67708333334</v>
       </c>
       <c r="B163">
-        <v>224.067</v>
+        <v>2162.475</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>1914</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3742,13 +4318,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46129.6875</v>
+        <v>46130.6875</v>
       </c>
       <c r="B164">
-        <v>227.76</v>
+        <v>2250.746</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>1901</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3759,13 +4335,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46129.69791666666</v>
+        <v>46130.69791666666</v>
       </c>
       <c r="B165">
-        <v>230.483</v>
+        <v>2218.488</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>1842</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3776,13 +4352,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46129.70833333334</v>
+        <v>46130.70833333334</v>
       </c>
       <c r="B166">
-        <v>229.954</v>
+        <v>1890.398</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>1733</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3793,13 +4369,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46129.71875</v>
+        <v>46130.71875</v>
       </c>
       <c r="B167">
-        <v>233.124</v>
+        <v>1924.197</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>1719</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3810,13 +4386,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46129.72916666666</v>
+        <v>46130.72916666666</v>
       </c>
       <c r="B168">
-        <v>235.809</v>
+        <v>1846.972</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1641</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3827,13 +4403,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46129.73958333334</v>
+        <v>46130.73958333334</v>
       </c>
       <c r="B169">
-        <v>239.164</v>
+        <v>1770.815</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1554</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3844,13 +4420,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46129.75</v>
+        <v>46130.75</v>
       </c>
       <c r="B170">
-        <v>248.793</v>
+        <v>1638.026</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1454</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3861,13 +4437,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46129.76041666666</v>
+        <v>46130.76041666666</v>
       </c>
       <c r="B171">
-        <v>250.9</v>
+        <v>1566.99</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1322</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3878,13 +4454,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46129.77083333334</v>
+        <v>46130.77083333334</v>
       </c>
       <c r="B172">
-        <v>252.83</v>
+        <v>1498.16</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1232</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3895,13 +4471,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46129.78125</v>
+        <v>46130.78125</v>
       </c>
       <c r="B173">
-        <v>255.55</v>
+        <v>1434.239</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1112</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3912,13 +4488,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46129.79166666666</v>
+        <v>46130.79166666666</v>
       </c>
       <c r="B174">
-        <v>250.756</v>
+        <v>1375.609</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3929,13 +4505,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46129.80208333334</v>
+        <v>46130.80208333334</v>
       </c>
       <c r="B175">
-        <v>247.006</v>
+        <v>1355.564</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3946,13 +4522,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46129.8125</v>
+        <v>46130.8125</v>
       </c>
       <c r="B176">
-        <v>242.379</v>
+        <v>1334.755</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>949</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3963,13 +4539,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46129.82291666666</v>
+        <v>46130.82291666666</v>
       </c>
       <c r="B177">
-        <v>236.831</v>
+        <v>1314.068</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>928</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3980,13 +4556,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46129.83333333334</v>
+        <v>46130.83333333334</v>
       </c>
       <c r="B178">
-        <v>227.465</v>
+        <v>1291.203</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>831</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3997,13 +4573,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46129.84375</v>
+        <v>46130.84375</v>
       </c>
       <c r="B179">
-        <v>221.904</v>
+        <v>1283.017</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4014,13 +4590,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46129.85416666666</v>
+        <v>46130.85416666666</v>
       </c>
       <c r="B180">
-        <v>215.489</v>
+        <v>1276.502</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4031,13 +4607,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46129.86458333334</v>
+        <v>46130.86458333334</v>
       </c>
       <c r="B181">
-        <v>208.289</v>
+        <v>1271.114</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4048,13 +4624,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46129.875</v>
+        <v>46130.875</v>
       </c>
       <c r="B182">
-        <v>197.694</v>
+        <v>1282.469</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4065,13 +4641,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46129.88541666666</v>
+        <v>46130.88541666666</v>
       </c>
       <c r="B183">
-        <v>195.738</v>
+        <v>1297.494</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4082,13 +4658,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46129.89583333334</v>
+        <v>46130.89583333334</v>
       </c>
       <c r="B184">
-        <v>193.064</v>
+        <v>1310.221</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4099,13 +4675,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46129.90625</v>
+        <v>46130.90625</v>
       </c>
       <c r="B185">
-        <v>190.67</v>
+        <v>1324.524</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>913</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4116,13 +4692,13 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46129.91666666666</v>
+        <v>46130.91666666666</v>
       </c>
       <c r="B186">
-        <v>190.547</v>
+        <v>1337.16</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4133,10 +4709,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46129.92708333334</v>
+        <v>46130.92708333334</v>
       </c>
       <c r="B187">
-        <v>200.607</v>
+        <v>1354.833</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,13 +4726,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46129.9375</v>
+        <v>46130.9375</v>
       </c>
       <c r="B188">
-        <v>211.629</v>
+        <v>1372.719</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4167,13 +4743,13 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46129.94791666666</v>
+        <v>46130.94791666666</v>
       </c>
       <c r="B189">
-        <v>223.221</v>
+        <v>1390.503</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4184,13 +4760,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46129.95833333334</v>
+        <v>46130.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>1220.116</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4201,13 +4777,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46129.96875</v>
+        <v>46130.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>1226.178</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>1021</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4218,13 +4794,13 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46129.97916666666</v>
+        <v>46130.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>1234.053</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="D192">
         <v>95</v>
@@ -4235,19 +4811,3283 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46129.98958333334</v>
+        <v>46130.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>1241.802</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="D193">
         <v>96</v>
       </c>
       <c r="E193" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B194">
+        <v>1169.676</v>
+      </c>
+      <c r="C194">
+        <v>986</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46131.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>1180.243</v>
+      </c>
+      <c r="C195">
+        <v>976</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46131.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>1190.252</v>
+      </c>
+      <c r="C196">
+        <v>963</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46131.03125</v>
+      </c>
+      <c r="B197">
+        <v>1201.41</v>
+      </c>
+      <c r="C197">
+        <v>956</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46131.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>1196.33</v>
+      </c>
+      <c r="C198">
+        <v>1019</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46131.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>1190.311</v>
+      </c>
+      <c r="C199">
+        <v>1066</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46131.0625</v>
+      </c>
+      <c r="B200">
+        <v>1192.647</v>
+      </c>
+      <c r="C200">
+        <v>1080</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46131.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>1190.538</v>
+      </c>
+      <c r="C201">
+        <v>1104</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46131.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>1178.978</v>
+      </c>
+      <c r="C202">
+        <v>1092</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46131.09375</v>
+      </c>
+      <c r="B203">
+        <v>1167.284</v>
+      </c>
+      <c r="C203">
+        <v>1069</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46131.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1155.243</v>
+      </c>
+      <c r="C204">
+        <v>1030</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46131.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>1143.207</v>
+      </c>
+      <c r="C205">
+        <v>990</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46131.125</v>
+      </c>
+      <c r="B206">
+        <v>1147.915</v>
+      </c>
+      <c r="C206">
+        <v>998</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46131.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>1129.526</v>
+      </c>
+      <c r="C207">
+        <v>1018</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46131.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>1108.038</v>
+      </c>
+      <c r="C208">
+        <v>1014</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46131.15625</v>
+      </c>
+      <c r="B209">
+        <v>1089.298</v>
+      </c>
+      <c r="C209">
+        <v>977</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46131.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>1126.598</v>
+      </c>
+      <c r="C210">
+        <v>937</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46131.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>1107.493</v>
+      </c>
+      <c r="C211">
+        <v>927</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46131.1875</v>
+      </c>
+      <c r="B212">
+        <v>1083.276</v>
+      </c>
+      <c r="C212">
+        <v>881</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46131.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>1069.347</v>
+      </c>
+      <c r="C213">
+        <v>805</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46131.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>1045.626</v>
+      </c>
+      <c r="C214">
+        <v>765</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46131.21875</v>
+      </c>
+      <c r="B215">
+        <v>1023.332</v>
+      </c>
+      <c r="C215">
+        <v>736</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46131.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>1007.428</v>
+      </c>
+      <c r="C216">
+        <v>698</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46131.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>984.678</v>
+      </c>
+      <c r="C217">
+        <v>693</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46131.25</v>
+      </c>
+      <c r="B218">
+        <v>925.977</v>
+      </c>
+      <c r="C218">
+        <v>713</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46131.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>890.424</v>
+      </c>
+      <c r="C219">
+        <v>694</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46131.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>830.8200000000001</v>
+      </c>
+      <c r="C220">
+        <v>619</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46131.28125</v>
+      </c>
+      <c r="B221">
+        <v>814.599</v>
+      </c>
+      <c r="C221">
+        <v>529</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46131.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>770.852</v>
+      </c>
+      <c r="C222">
+        <v>416</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46131.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>723.367</v>
+      </c>
+      <c r="C223">
+        <v>310</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46131.3125</v>
+      </c>
+      <c r="B224">
+        <v>682.3049999999999</v>
+      </c>
+      <c r="C224">
+        <v>280</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46131.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>602.287</v>
+      </c>
+      <c r="C225">
+        <v>251</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46131.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>732.91</v>
+      </c>
+      <c r="C226">
+        <v>261</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46131.34375</v>
+      </c>
+      <c r="B227">
+        <v>729.974</v>
+      </c>
+      <c r="C227">
+        <v>275</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46131.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>754.167</v>
+      </c>
+      <c r="C228">
+        <v>313</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46131.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>718.804</v>
+      </c>
+      <c r="C229">
+        <v>357</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46131.375</v>
+      </c>
+      <c r="B230">
+        <v>825.703</v>
+      </c>
+      <c r="C230">
+        <v>369</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46131.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>848.15</v>
+      </c>
+      <c r="C231">
+        <v>370</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46131.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>870.859</v>
+      </c>
+      <c r="C232">
+        <v>378</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46131.40625</v>
+      </c>
+      <c r="B233">
+        <v>887.747</v>
+      </c>
+      <c r="C233">
+        <v>396</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46131.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>916.473</v>
+      </c>
+      <c r="C234">
+        <v>417</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46131.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>904.079</v>
+      </c>
+      <c r="C235">
+        <v>440</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46131.4375</v>
+      </c>
+      <c r="B236">
+        <v>874.062</v>
+      </c>
+      <c r="C236">
+        <v>453</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46131.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>883.7619999999999</v>
+      </c>
+      <c r="C237">
+        <v>479</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46131.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>883.41</v>
+      </c>
+      <c r="C238">
+        <v>488</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46131.46875</v>
+      </c>
+      <c r="B239">
+        <v>875.812</v>
+      </c>
+      <c r="C239">
+        <v>486</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46131.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>868.4640000000001</v>
+      </c>
+      <c r="C240">
+        <v>503</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46131.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>859.782</v>
+      </c>
+      <c r="C241">
+        <v>531</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46131.5</v>
+      </c>
+      <c r="B242">
+        <v>875.513</v>
+      </c>
+      <c r="C242">
+        <v>519</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46131.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>849.862</v>
+      </c>
+      <c r="C243">
+        <v>491</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46131.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>815.297</v>
+      </c>
+      <c r="C244">
+        <v>472</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46131.53125</v>
+      </c>
+      <c r="B245">
+        <v>775.421</v>
+      </c>
+      <c r="C245">
+        <v>436</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46131.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>744.938</v>
+      </c>
+      <c r="C246">
+        <v>386</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46131.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>713.4299999999999</v>
+      </c>
+      <c r="C247">
+        <v>346</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46131.5625</v>
+      </c>
+      <c r="B248">
+        <v>689.654</v>
+      </c>
+      <c r="C248">
+        <v>312</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46131.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>665.063</v>
+      </c>
+      <c r="C249">
+        <v>305</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46131.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>627.833</v>
+      </c>
+      <c r="C250">
+        <v>273</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46131.59375</v>
+      </c>
+      <c r="B251">
+        <v>603.347</v>
+      </c>
+      <c r="C251">
+        <v>253</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46131.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>576.759</v>
+      </c>
+      <c r="C252">
+        <v>240</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46131.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>510.813</v>
+      </c>
+      <c r="C253">
+        <v>221</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46131.625</v>
+      </c>
+      <c r="B254">
+        <v>512.925</v>
+      </c>
+      <c r="C254">
+        <v>178</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46131.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>490.265</v>
+      </c>
+      <c r="C255">
+        <v>157</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46131.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>466.123</v>
+      </c>
+      <c r="C256">
+        <v>132</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46131.65625</v>
+      </c>
+      <c r="B257">
+        <v>443.968</v>
+      </c>
+      <c r="C257">
+        <v>103</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46131.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>351.338</v>
+      </c>
+      <c r="C258">
+        <v>100</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46131.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>332.933</v>
+      </c>
+      <c r="C259">
+        <v>78</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46131.6875</v>
+      </c>
+      <c r="B260">
+        <v>328.827</v>
+      </c>
+      <c r="C260">
+        <v>40</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46131.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>303.89</v>
+      </c>
+      <c r="C261">
+        <v>12</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46131.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>261.964</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46131.71875</v>
+      </c>
+      <c r="B263">
+        <v>240.489</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46131.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>220.157</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46131.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>199.687</v>
+      </c>
+      <c r="C265">
+        <v>10</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46131.75</v>
+      </c>
+      <c r="B266">
+        <v>176.871</v>
+      </c>
+      <c r="C266">
+        <v>12</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46131.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>168.316</v>
+      </c>
+      <c r="C267">
+        <v>15</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46131.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>160.782</v>
+      </c>
+      <c r="C268">
+        <v>27</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46131.78125</v>
+      </c>
+      <c r="B269">
+        <v>153.164</v>
+      </c>
+      <c r="C269">
+        <v>38</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46131.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>143.983</v>
+      </c>
+      <c r="C270">
+        <v>87</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46131.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>141.746</v>
+      </c>
+      <c r="C271">
+        <v>157</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46131.8125</v>
+      </c>
+      <c r="B272">
+        <v>139.459</v>
+      </c>
+      <c r="C272">
+        <v>223</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46131.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>137.38</v>
+      </c>
+      <c r="C273">
+        <v>279</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46131.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>135.694</v>
+      </c>
+      <c r="C274">
+        <v>323</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46131.84375</v>
+      </c>
+      <c r="B275">
+        <v>135.714</v>
+      </c>
+      <c r="C275">
+        <v>347</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46131.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>136.119</v>
+      </c>
+      <c r="C276">
+        <v>371</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46131.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>136.408</v>
+      </c>
+      <c r="C277">
+        <v>388</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46131.875</v>
+      </c>
+      <c r="B278">
+        <v>139.603</v>
+      </c>
+      <c r="C278">
+        <v>437</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46131.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>143.028</v>
+      </c>
+      <c r="C279">
+        <v>471</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46131.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>147.152</v>
+      </c>
+      <c r="C280">
+        <v>453</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46131.90625</v>
+      </c>
+      <c r="B281">
+        <v>150.673</v>
+      </c>
+      <c r="C281">
+        <v>462</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46131.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>157.978</v>
+      </c>
+      <c r="C282">
+        <v>442</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46131.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>163.78</v>
+      </c>
+      <c r="C283">
+        <v>455</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46131.9375</v>
+      </c>
+      <c r="B284">
+        <v>168.71</v>
+      </c>
+      <c r="C284">
+        <v>482</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46131.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>175.004</v>
+      </c>
+      <c r="C285">
+        <v>493</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46131.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>325.268</v>
+      </c>
+      <c r="C286">
+        <v>505</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46131.96875</v>
+      </c>
+      <c r="B287">
+        <v>330.097</v>
+      </c>
+      <c r="C287">
+        <v>537</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46131.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>343.178</v>
+      </c>
+      <c r="C288">
+        <v>538</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46131.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>351.274</v>
+      </c>
+      <c r="C289">
+        <v>525</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B290">
+        <v>432.708</v>
+      </c>
+      <c r="C290">
+        <v>538</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46132.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>441.809</v>
+      </c>
+      <c r="C291">
+        <v>537</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46132.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>452.109</v>
+      </c>
+      <c r="C292">
+        <v>531</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46132.03125</v>
+      </c>
+      <c r="B293">
+        <v>448.302</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46132.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>465.917</v>
+      </c>
+      <c r="C294">
+        <v>557</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46132.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>472.364</v>
+      </c>
+      <c r="C295">
+        <v>577</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46132.0625</v>
+      </c>
+      <c r="B296">
+        <v>462.461</v>
+      </c>
+      <c r="C296">
+        <v>561</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46132.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>445.559</v>
+      </c>
+      <c r="C297">
+        <v>516</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46132.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>466.258</v>
+      </c>
+      <c r="C298">
+        <v>514</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46132.09375</v>
+      </c>
+      <c r="B299">
+        <v>450.039</v>
+      </c>
+      <c r="C299">
+        <v>495</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46132.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>479.346</v>
+      </c>
+      <c r="C300">
+        <v>501</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46132.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>478.487</v>
+      </c>
+      <c r="C301">
+        <v>493</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46132.125</v>
+      </c>
+      <c r="B302">
+        <v>510.454</v>
+      </c>
+      <c r="C302">
+        <v>515</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46132.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>504.502</v>
+      </c>
+      <c r="C303">
+        <v>533</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46132.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>529.279</v>
+      </c>
+      <c r="C304">
+        <v>547</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46132.15625</v>
+      </c>
+      <c r="B305">
+        <v>533.029</v>
+      </c>
+      <c r="C305">
+        <v>543</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46132.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>553.497</v>
+      </c>
+      <c r="C306">
+        <v>544</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46132.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>558.114</v>
+      </c>
+      <c r="C307">
+        <v>547</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46132.1875</v>
+      </c>
+      <c r="B308">
+        <v>557.848</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46132.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>559.373</v>
+      </c>
+      <c r="C309">
+        <v>535</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46132.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>558.3390000000001</v>
+      </c>
+      <c r="C310">
+        <v>526</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46132.21875</v>
+      </c>
+      <c r="B311">
+        <v>556.898</v>
+      </c>
+      <c r="C311">
+        <v>522</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46132.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>590.338</v>
+      </c>
+      <c r="C312">
+        <v>512</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46132.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>592.871</v>
+      </c>
+      <c r="C313">
+        <v>501</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46132.25</v>
+      </c>
+      <c r="B314">
+        <v>561.0700000000001</v>
+      </c>
+      <c r="C314">
+        <v>496</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46132.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>568.5</v>
+      </c>
+      <c r="C315">
+        <v>508</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46132.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>555.579</v>
+      </c>
+      <c r="C316">
+        <v>513</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46132.28125</v>
+      </c>
+      <c r="B317">
+        <v>556.778</v>
+      </c>
+      <c r="C317">
+        <v>484</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46132.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>529.5700000000001</v>
+      </c>
+      <c r="C318">
+        <v>460</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46132.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>524.929</v>
+      </c>
+      <c r="C319">
+        <v>437</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46132.3125</v>
+      </c>
+      <c r="B320">
+        <v>498.782</v>
+      </c>
+      <c r="C320">
+        <v>404</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46132.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>481.623</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46132.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>474.739</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46132.34375</v>
+      </c>
+      <c r="B323">
+        <v>469.586</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46132.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>455.636</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46132.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>449.774</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46132.375</v>
+      </c>
+      <c r="B326">
+        <v>528.0549999999999</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46132.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>578.211</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46132.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>628.5700000000001</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46132.40625</v>
+      </c>
+      <c r="B329">
+        <v>680.249</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46132.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>765.114</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46132.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>823.2329999999999</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46132.4375</v>
+      </c>
+      <c r="B332">
+        <v>881.218</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46132.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>926.2809999999999</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46132.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>988.7910000000001</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46132.46875</v>
+      </c>
+      <c r="B335">
+        <v>1029.472</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46132.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>1070.07</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46132.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>1112.707</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46132.5</v>
+      </c>
+      <c r="B338">
+        <v>1158.154</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46132.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>1202.716</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46132.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>1247.382</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46132.53125</v>
+      </c>
+      <c r="B341">
+        <v>1291.131</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46132.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>1325.232</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46132.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>1355.936</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46132.5625</v>
+      </c>
+      <c r="B344">
+        <v>1386.313</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46132.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>1415.796</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46132.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>1460.35</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46132.59375</v>
+      </c>
+      <c r="B347">
+        <v>1471.689</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46132.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>1482.595</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46132.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>1492.8</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46132.625</v>
+      </c>
+      <c r="B350">
+        <v>1533.11</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46132.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>1539.277</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46132.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>1544.006</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46132.65625</v>
+      </c>
+      <c r="B353">
+        <v>1550.109</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46132.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>1438.04</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46132.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>1450.791</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46132.6875</v>
+      </c>
+      <c r="B356">
+        <v>1466.04</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46132.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>1491.632</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46132.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>1494.439</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46132.71875</v>
+      </c>
+      <c r="B359">
+        <v>1514.649</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46132.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>1543.387</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46132.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>1562.521</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46132.75</v>
+      </c>
+      <c r="B362">
+        <v>1550.375</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46132.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>1494.685</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46132.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>1439.056</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46132.78125</v>
+      </c>
+      <c r="B365">
+        <v>1385.868</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46132.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>1297.875</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46132.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>1237.708</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46132.8125</v>
+      </c>
+      <c r="B368">
+        <v>1178.866</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46132.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>1119.838</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46132.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>1058.792</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46132.84375</v>
+      </c>
+      <c r="B371">
+        <v>1038.445</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46132.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>1020.379</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46132.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>1004.859</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46132.875</v>
+      </c>
+      <c r="B374">
+        <v>979.351</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46132.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>966.115</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46132.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>955.16</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46132.90625</v>
+      </c>
+      <c r="B377">
+        <v>943.016</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46132.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>923.506</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46132.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>907.62</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46132.9375</v>
+      </c>
+      <c r="B380">
+        <v>892.739</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46132.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>880.611</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46132.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46132.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46132.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46132.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.04.20261</t>
-  </si>
-  <si>
-    <t>20.04.20262</t>
-  </si>
-  <si>
-    <t>20.04.20263</t>
-  </si>
-  <si>
-    <t>20.04.20264</t>
-  </si>
-  <si>
-    <t>20.04.20265</t>
-  </si>
-  <si>
-    <t>20.04.20266</t>
-  </si>
-  <si>
-    <t>20.04.20267</t>
-  </si>
-  <si>
-    <t>20.04.20268</t>
-  </si>
-  <si>
-    <t>20.04.20269</t>
-  </si>
-  <si>
-    <t>20.04.202610</t>
-  </si>
-  <si>
-    <t>20.04.202611</t>
-  </si>
-  <si>
-    <t>20.04.202612</t>
-  </si>
-  <si>
-    <t>20.04.202613</t>
-  </si>
-  <si>
-    <t>20.04.202614</t>
-  </si>
-  <si>
-    <t>20.04.202615</t>
-  </si>
-  <si>
-    <t>20.04.202616</t>
-  </si>
-  <si>
-    <t>20.04.202617</t>
-  </si>
-  <si>
-    <t>20.04.202618</t>
-  </si>
-  <si>
-    <t>20.04.202619</t>
-  </si>
-  <si>
-    <t>20.04.202620</t>
-  </si>
-  <si>
-    <t>20.04.202621</t>
-  </si>
-  <si>
-    <t>20.04.202622</t>
-  </si>
-  <si>
-    <t>20.04.202623</t>
-  </si>
-  <si>
-    <t>20.04.202624</t>
-  </si>
-  <si>
-    <t>20.04.202625</t>
-  </si>
-  <si>
-    <t>20.04.202626</t>
-  </si>
-  <si>
-    <t>20.04.202627</t>
-  </si>
-  <si>
-    <t>20.04.202628</t>
-  </si>
-  <si>
-    <t>20.04.202629</t>
-  </si>
-  <si>
-    <t>20.04.202630</t>
-  </si>
-  <si>
-    <t>20.04.202631</t>
-  </si>
-  <si>
-    <t>20.04.202632</t>
-  </si>
-  <si>
-    <t>20.04.202633</t>
-  </si>
-  <si>
-    <t>20.04.202634</t>
-  </si>
-  <si>
-    <t>20.04.202635</t>
-  </si>
-  <si>
-    <t>20.04.202636</t>
-  </si>
-  <si>
-    <t>20.04.202637</t>
-  </si>
-  <si>
-    <t>20.04.202638</t>
-  </si>
-  <si>
-    <t>20.04.202639</t>
-  </si>
-  <si>
-    <t>20.04.202640</t>
-  </si>
-  <si>
-    <t>20.04.202641</t>
-  </si>
-  <si>
-    <t>20.04.202642</t>
-  </si>
-  <si>
-    <t>20.04.202643</t>
-  </si>
-  <si>
-    <t>20.04.202644</t>
-  </si>
-  <si>
-    <t>20.04.202645</t>
-  </si>
-  <si>
-    <t>20.04.202646</t>
-  </si>
-  <si>
-    <t>20.04.202647</t>
-  </si>
-  <si>
-    <t>20.04.202648</t>
-  </si>
-  <si>
-    <t>20.04.202649</t>
-  </si>
-  <si>
-    <t>20.04.202650</t>
-  </si>
-  <si>
-    <t>20.04.202651</t>
-  </si>
-  <si>
-    <t>20.04.202652</t>
-  </si>
-  <si>
-    <t>20.04.202653</t>
-  </si>
-  <si>
-    <t>20.04.202654</t>
-  </si>
-  <si>
-    <t>20.04.202655</t>
-  </si>
-  <si>
-    <t>20.04.202656</t>
-  </si>
-  <si>
-    <t>20.04.202657</t>
-  </si>
-  <si>
-    <t>20.04.202658</t>
-  </si>
-  <si>
-    <t>20.04.202659</t>
-  </si>
-  <si>
-    <t>20.04.202660</t>
-  </si>
-  <si>
-    <t>20.04.202661</t>
-  </si>
-  <si>
-    <t>20.04.202662</t>
-  </si>
-  <si>
-    <t>20.04.202663</t>
-  </si>
-  <si>
-    <t>20.04.202664</t>
-  </si>
-  <si>
-    <t>20.04.202665</t>
-  </si>
-  <si>
-    <t>20.04.202666</t>
-  </si>
-  <si>
-    <t>20.04.202667</t>
-  </si>
-  <si>
-    <t>20.04.202668</t>
-  </si>
-  <si>
-    <t>20.04.202669</t>
-  </si>
-  <si>
-    <t>20.04.202670</t>
-  </si>
-  <si>
-    <t>20.04.202671</t>
-  </si>
-  <si>
-    <t>20.04.202672</t>
-  </si>
-  <si>
-    <t>20.04.202673</t>
-  </si>
-  <si>
-    <t>20.04.202674</t>
-  </si>
-  <si>
-    <t>20.04.202675</t>
-  </si>
-  <si>
-    <t>20.04.202676</t>
-  </si>
-  <si>
-    <t>20.04.202677</t>
-  </si>
-  <si>
-    <t>20.04.202678</t>
-  </si>
-  <si>
-    <t>20.04.202679</t>
-  </si>
-  <si>
-    <t>20.04.202680</t>
-  </si>
-  <si>
-    <t>20.04.202681</t>
-  </si>
-  <si>
-    <t>20.04.202682</t>
-  </si>
-  <si>
-    <t>20.04.202683</t>
-  </si>
-  <si>
-    <t>20.04.202684</t>
-  </si>
-  <si>
-    <t>20.04.202685</t>
-  </si>
-  <si>
-    <t>20.04.202686</t>
-  </si>
-  <si>
-    <t>20.04.202687</t>
-  </si>
-  <si>
-    <t>20.04.202688</t>
-  </si>
-  <si>
-    <t>20.04.202689</t>
-  </si>
-  <si>
-    <t>20.04.202690</t>
-  </si>
-  <si>
-    <t>20.04.202691</t>
-  </si>
-  <si>
-    <t>20.04.202692</t>
-  </si>
-  <si>
-    <t>20.04.202693</t>
-  </si>
-  <si>
-    <t>20.04.202694</t>
-  </si>
-  <si>
-    <t>20.04.202695</t>
-  </si>
-  <si>
-    <t>20.04.202696</t>
-  </si>
-  <si>
     <t>21.04.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>21.04.202696</t>
+  </si>
+  <si>
+    <t>22.04.20261</t>
+  </si>
+  <si>
+    <t>22.04.20262</t>
+  </si>
+  <si>
+    <t>22.04.20263</t>
+  </si>
+  <si>
+    <t>22.04.20264</t>
+  </si>
+  <si>
+    <t>22.04.20265</t>
+  </si>
+  <si>
+    <t>22.04.20266</t>
+  </si>
+  <si>
+    <t>22.04.20267</t>
+  </si>
+  <si>
+    <t>22.04.20268</t>
+  </si>
+  <si>
+    <t>22.04.20269</t>
+  </si>
+  <si>
+    <t>22.04.202610</t>
+  </si>
+  <si>
+    <t>22.04.202611</t>
+  </si>
+  <si>
+    <t>22.04.202612</t>
+  </si>
+  <si>
+    <t>22.04.202613</t>
+  </si>
+  <si>
+    <t>22.04.202614</t>
+  </si>
+  <si>
+    <t>22.04.202615</t>
+  </si>
+  <si>
+    <t>22.04.202616</t>
+  </si>
+  <si>
+    <t>22.04.202617</t>
+  </si>
+  <si>
+    <t>22.04.202618</t>
+  </si>
+  <si>
+    <t>22.04.202619</t>
+  </si>
+  <si>
+    <t>22.04.202620</t>
+  </si>
+  <si>
+    <t>22.04.202621</t>
+  </si>
+  <si>
+    <t>22.04.202622</t>
+  </si>
+  <si>
+    <t>22.04.202623</t>
+  </si>
+  <si>
+    <t>22.04.202624</t>
+  </si>
+  <si>
+    <t>22.04.202625</t>
+  </si>
+  <si>
+    <t>22.04.202626</t>
+  </si>
+  <si>
+    <t>22.04.202627</t>
+  </si>
+  <si>
+    <t>22.04.202628</t>
+  </si>
+  <si>
+    <t>22.04.202629</t>
+  </si>
+  <si>
+    <t>22.04.202630</t>
+  </si>
+  <si>
+    <t>22.04.202631</t>
+  </si>
+  <si>
+    <t>22.04.202632</t>
+  </si>
+  <si>
+    <t>22.04.202633</t>
+  </si>
+  <si>
+    <t>22.04.202634</t>
+  </si>
+  <si>
+    <t>22.04.202635</t>
+  </si>
+  <si>
+    <t>22.04.202636</t>
+  </si>
+  <si>
+    <t>22.04.202637</t>
+  </si>
+  <si>
+    <t>22.04.202638</t>
+  </si>
+  <si>
+    <t>22.04.202639</t>
+  </si>
+  <si>
+    <t>22.04.202640</t>
+  </si>
+  <si>
+    <t>22.04.202641</t>
+  </si>
+  <si>
+    <t>22.04.202642</t>
+  </si>
+  <si>
+    <t>22.04.202643</t>
+  </si>
+  <si>
+    <t>22.04.202644</t>
+  </si>
+  <si>
+    <t>22.04.202645</t>
+  </si>
+  <si>
+    <t>22.04.202646</t>
+  </si>
+  <si>
+    <t>22.04.202647</t>
+  </si>
+  <si>
+    <t>22.04.202648</t>
+  </si>
+  <si>
+    <t>22.04.202649</t>
+  </si>
+  <si>
+    <t>22.04.202650</t>
+  </si>
+  <si>
+    <t>22.04.202651</t>
+  </si>
+  <si>
+    <t>22.04.202652</t>
+  </si>
+  <si>
+    <t>22.04.202653</t>
+  </si>
+  <si>
+    <t>22.04.202654</t>
+  </si>
+  <si>
+    <t>22.04.202655</t>
+  </si>
+  <si>
+    <t>22.04.202656</t>
+  </si>
+  <si>
+    <t>22.04.202657</t>
+  </si>
+  <si>
+    <t>22.04.202658</t>
+  </si>
+  <si>
+    <t>22.04.202659</t>
+  </si>
+  <si>
+    <t>22.04.202660</t>
+  </si>
+  <si>
+    <t>22.04.202661</t>
+  </si>
+  <si>
+    <t>22.04.202662</t>
+  </si>
+  <si>
+    <t>22.04.202663</t>
+  </si>
+  <si>
+    <t>22.04.202664</t>
+  </si>
+  <si>
+    <t>22.04.202665</t>
+  </si>
+  <si>
+    <t>22.04.202666</t>
+  </si>
+  <si>
+    <t>22.04.202667</t>
+  </si>
+  <si>
+    <t>22.04.202668</t>
+  </si>
+  <si>
+    <t>22.04.202669</t>
+  </si>
+  <si>
+    <t>22.04.202670</t>
+  </si>
+  <si>
+    <t>22.04.202671</t>
+  </si>
+  <si>
+    <t>22.04.202672</t>
+  </si>
+  <si>
+    <t>22.04.202673</t>
+  </si>
+  <si>
+    <t>22.04.202674</t>
+  </si>
+  <si>
+    <t>22.04.202675</t>
+  </si>
+  <si>
+    <t>22.04.202676</t>
+  </si>
+  <si>
+    <t>22.04.202677</t>
+  </si>
+  <si>
+    <t>22.04.202678</t>
+  </si>
+  <si>
+    <t>22.04.202679</t>
+  </si>
+  <si>
+    <t>22.04.202680</t>
+  </si>
+  <si>
+    <t>22.04.202681</t>
+  </si>
+  <si>
+    <t>22.04.202682</t>
+  </si>
+  <si>
+    <t>22.04.202683</t>
+  </si>
+  <si>
+    <t>22.04.202684</t>
+  </si>
+  <si>
+    <t>22.04.202685</t>
+  </si>
+  <si>
+    <t>22.04.202686</t>
+  </si>
+  <si>
+    <t>22.04.202687</t>
+  </si>
+  <si>
+    <t>22.04.202688</t>
+  </si>
+  <si>
+    <t>22.04.202689</t>
+  </si>
+  <si>
+    <t>22.04.202690</t>
+  </si>
+  <si>
+    <t>22.04.202691</t>
+  </si>
+  <si>
+    <t>22.04.202692</t>
+  </si>
+  <si>
+    <t>22.04.202693</t>
+  </si>
+  <si>
+    <t>22.04.202694</t>
+  </si>
+  <si>
+    <t>22.04.202695</t>
+  </si>
+  <si>
+    <t>22.04.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
-        <v>432.708</v>
+        <v>861.976</v>
       </c>
       <c r="C2">
-        <v>538</v>
+        <v>1008</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
-        <v>441.809</v>
+        <v>898.958</v>
       </c>
       <c r="C3">
-        <v>537</v>
+        <v>1104</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
-        <v>452.109</v>
+        <v>928.774</v>
       </c>
       <c r="C4">
-        <v>531</v>
+        <v>1214</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
-        <v>448.302</v>
+        <v>948.021</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1296</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
-        <v>465.917</v>
+        <v>1077.874</v>
       </c>
       <c r="C6">
-        <v>557</v>
+        <v>1491</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
-        <v>472.364</v>
+        <v>1133.461</v>
       </c>
       <c r="C7">
-        <v>577</v>
+        <v>1563</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
-        <v>462.461</v>
+        <v>1182.254</v>
       </c>
       <c r="C8">
-        <v>561</v>
+        <v>1666</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
-        <v>445.559</v>
+        <v>1216.081</v>
       </c>
       <c r="C9">
-        <v>516</v>
+        <v>1575</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
-        <v>466.258</v>
+        <v>1274.183</v>
       </c>
       <c r="C10">
-        <v>514</v>
+        <v>1585</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
-        <v>450.039</v>
+        <v>1324.831</v>
       </c>
       <c r="C11">
-        <v>495</v>
+        <v>1602</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
-        <v>479.346</v>
+        <v>1348.891</v>
       </c>
       <c r="C12">
-        <v>501</v>
+        <v>1627</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
-        <v>478.487</v>
+        <v>1376.946</v>
       </c>
       <c r="C13">
-        <v>493</v>
+        <v>1545</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
-        <v>510.454</v>
+        <v>1404.427</v>
       </c>
       <c r="C14">
-        <v>515</v>
+        <v>1575</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
-        <v>504.502</v>
+        <v>1414.548</v>
       </c>
       <c r="C15">
-        <v>533</v>
+        <v>1541</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
-        <v>529.279</v>
+        <v>1430.951</v>
       </c>
       <c r="C16">
-        <v>547</v>
+        <v>1573</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
-        <v>533.029</v>
+        <v>1447.523</v>
       </c>
       <c r="C17">
-        <v>543</v>
+        <v>1630</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>553.497</v>
+        <v>1484.44</v>
       </c>
       <c r="C18">
-        <v>544</v>
+        <v>1659</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
-        <v>558.114</v>
+        <v>1503.468</v>
       </c>
       <c r="C19">
-        <v>547</v>
+        <v>1647</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
-        <v>557.848</v>
+        <v>1522.836</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1607</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>559.373</v>
+        <v>1544.936</v>
       </c>
       <c r="C21">
-        <v>535</v>
+        <v>1646</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>558.3390000000001</v>
+        <v>1507.048</v>
       </c>
       <c r="C22">
-        <v>526</v>
+        <v>1641</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>556.898</v>
+        <v>1529.185</v>
       </c>
       <c r="C23">
-        <v>522</v>
+        <v>1618</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>590.338</v>
+        <v>1547.264</v>
       </c>
       <c r="C24">
-        <v>512</v>
+        <v>1641</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>592.871</v>
+        <v>1567.177</v>
       </c>
       <c r="C25">
-        <v>501</v>
+        <v>1650</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>561.0700000000001</v>
+        <v>1548.791</v>
       </c>
       <c r="C26">
-        <v>496</v>
+        <v>1655</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>568.5</v>
+        <v>1528.274</v>
       </c>
       <c r="C27">
-        <v>508</v>
+        <v>1685</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>555.579</v>
+        <v>1514.297</v>
       </c>
       <c r="C28">
-        <v>513</v>
+        <v>1629</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>556.778</v>
+        <v>1508.218</v>
       </c>
       <c r="C29">
-        <v>484</v>
+        <v>1538</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>529.5700000000001</v>
+        <v>1450.05</v>
       </c>
       <c r="C30">
-        <v>460</v>
+        <v>1499</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>524.929</v>
+        <v>1428.46</v>
       </c>
       <c r="C31">
-        <v>437</v>
+        <v>1454</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>498.782</v>
+        <v>1402.589</v>
       </c>
       <c r="C32">
-        <v>404</v>
+        <v>1379</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>481.623</v>
+        <v>1371.67</v>
       </c>
       <c r="C33">
-        <v>384</v>
+        <v>1288</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>474.739</v>
+        <v>1398.347</v>
       </c>
       <c r="C34">
-        <v>371</v>
+        <v>1274</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
-        <v>469.586</v>
+        <v>1360.717</v>
       </c>
       <c r="C35">
-        <v>350</v>
+        <v>1191</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
-        <v>455.636</v>
+        <v>1335.17</v>
       </c>
       <c r="C36">
-        <v>357</v>
+        <v>1116</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
-        <v>449.774</v>
+        <v>1296.393</v>
       </c>
       <c r="C37">
-        <v>382</v>
+        <v>1055</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
-        <v>528.0549999999999</v>
+        <v>1226.429</v>
       </c>
       <c r="C38">
-        <v>448</v>
+        <v>984</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
-        <v>578.211</v>
+        <v>1196.936</v>
       </c>
       <c r="C39">
-        <v>494</v>
+        <v>885</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
-        <v>628.5700000000001</v>
+        <v>1167.024</v>
       </c>
       <c r="C40">
-        <v>549</v>
+        <v>772</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
-        <v>680.249</v>
+        <v>1137.75</v>
       </c>
       <c r="C41">
-        <v>615</v>
+        <v>716</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>765.114</v>
+        <v>1080.848</v>
       </c>
       <c r="C42">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>823.2329999999999</v>
+        <v>1055.565</v>
       </c>
       <c r="C43">
-        <v>771</v>
+        <v>645</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>881.218</v>
+        <v>1028.35</v>
       </c>
       <c r="C44">
-        <v>867</v>
+        <v>601</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>926.2809999999999</v>
+        <v>992.583</v>
       </c>
       <c r="C45">
-        <v>946</v>
+        <v>543</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
-        <v>988.7910000000001</v>
+        <v>962.218</v>
       </c>
       <c r="C46">
-        <v>1048</v>
+        <v>516</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
-        <v>1029.472</v>
+        <v>926.774</v>
       </c>
       <c r="C47">
-        <v>1133</v>
+        <v>504</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
-        <v>1070.07</v>
+        <v>903.449</v>
       </c>
       <c r="C48">
-        <v>1250</v>
+        <v>521</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>1112.707</v>
+        <v>879.111</v>
       </c>
       <c r="C49">
-        <v>1295</v>
+        <v>514</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>1158.154</v>
+        <v>854.42</v>
       </c>
       <c r="C50">
-        <v>1417</v>
+        <v>509</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>1202.716</v>
+        <v>826.579</v>
       </c>
       <c r="C51">
-        <v>1324</v>
+        <v>484</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
-        <v>1247.382</v>
+        <v>795.973</v>
       </c>
       <c r="C52">
-        <v>1343</v>
+        <v>444</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>1291.131</v>
+        <v>768.671</v>
       </c>
       <c r="C53">
-        <v>1316</v>
+        <v>414</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>1325.232</v>
+        <v>737.912</v>
       </c>
       <c r="C54">
-        <v>1587</v>
+        <v>406</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>1355.936</v>
+        <v>716.249</v>
       </c>
       <c r="C55">
-        <v>1788</v>
+        <v>407</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>1386.313</v>
+        <v>694.509</v>
       </c>
       <c r="C56">
-        <v>1829</v>
+        <v>384</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>1415.796</v>
+        <v>673.726</v>
       </c>
       <c r="C57">
-        <v>1561</v>
+        <v>358</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>1460.35</v>
+        <v>652.4400000000001</v>
       </c>
       <c r="C58">
-        <v>1541</v>
+        <v>323</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>1471.689</v>
+        <v>628.48</v>
       </c>
       <c r="C59">
-        <v>1610</v>
+        <v>306</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>1482.595</v>
+        <v>603.484</v>
       </c>
       <c r="C60">
-        <v>1906</v>
+        <v>289</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>1492.8</v>
+        <v>577.245</v>
       </c>
       <c r="C61">
-        <v>1967</v>
+        <v>270</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>1533.11</v>
+        <v>479.83</v>
       </c>
       <c r="C62">
-        <v>2047</v>
+        <v>256</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>1539.277</v>
+        <v>465.959</v>
       </c>
       <c r="C63">
-        <v>1809</v>
+        <v>242</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>1544.006</v>
+        <v>447.618</v>
       </c>
       <c r="C64">
-        <v>2050</v>
+        <v>247</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>1550.109</v>
+        <v>438.696</v>
       </c>
       <c r="C65">
-        <v>2159</v>
+        <v>227</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>1438.04</v>
+        <v>384.676</v>
       </c>
       <c r="C66">
-        <v>2129</v>
+        <v>199</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>1450.791</v>
+        <v>380.195</v>
       </c>
       <c r="C67">
-        <v>2047</v>
+        <v>189</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>1466.04</v>
+        <v>372.484</v>
       </c>
       <c r="C68">
-        <v>2051</v>
+        <v>162</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>1491.632</v>
+        <v>368.806</v>
       </c>
       <c r="C69">
-        <v>2014</v>
+        <v>144</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>1494.439</v>
+        <v>359.26</v>
       </c>
       <c r="C70">
-        <v>1935</v>
+        <v>142</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>1514.649</v>
+        <v>344.714</v>
       </c>
       <c r="C71">
-        <v>1946</v>
+        <v>135</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>1543.387</v>
+        <v>330.445</v>
       </c>
       <c r="C72">
-        <v>2024</v>
+        <v>143</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>1562.521</v>
+        <v>316.297</v>
       </c>
       <c r="C73">
-        <v>2120</v>
+        <v>123</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>1550.375</v>
+        <v>289.643</v>
       </c>
       <c r="C74">
-        <v>2084</v>
+        <v>102</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>1494.685</v>
+        <v>280.347</v>
       </c>
       <c r="C75">
-        <v>2113</v>
+        <v>100</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>1439.056</v>
+        <v>272.872</v>
       </c>
       <c r="C76">
-        <v>2007</v>
+        <v>88</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>1385.868</v>
+        <v>266.022</v>
       </c>
       <c r="C77">
-        <v>2002</v>
+        <v>78</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>1297.875</v>
+        <v>257.366</v>
       </c>
       <c r="C78">
-        <v>1989</v>
+        <v>62</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
-        <v>1237.708</v>
+        <v>257.522</v>
       </c>
       <c r="C79">
-        <v>1911</v>
+        <v>57</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
-        <v>1178.866</v>
+        <v>257.86</v>
       </c>
       <c r="C80">
-        <v>1686</v>
+        <v>66</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
-        <v>1119.838</v>
+        <v>282.689</v>
       </c>
       <c r="C81">
-        <v>1444</v>
+        <v>79</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
-        <v>1058.792</v>
+        <v>253.54</v>
       </c>
       <c r="C82">
-        <v>1216</v>
+        <v>109</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
-        <v>1038.445</v>
+        <v>250.577</v>
       </c>
       <c r="C83">
-        <v>1056</v>
+        <v>128</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
-        <v>1020.379</v>
+        <v>248.198</v>
       </c>
       <c r="C84">
-        <v>978</v>
+        <v>148</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
-        <v>1004.859</v>
+        <v>245.698</v>
       </c>
       <c r="C85">
-        <v>886</v>
+        <v>165</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
-        <v>979.351</v>
+        <v>241.75</v>
       </c>
       <c r="C86">
-        <v>894</v>
+        <v>166</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
-        <v>966.115</v>
+        <v>241.722</v>
       </c>
       <c r="C87">
-        <v>892</v>
+        <v>148</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
-        <v>955.16</v>
+        <v>242.544</v>
       </c>
       <c r="C88">
-        <v>950</v>
+        <v>129</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
-        <v>943.016</v>
+        <v>242.781</v>
       </c>
       <c r="C89">
-        <v>953</v>
+        <v>115</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
-        <v>923.506</v>
+        <v>244.823</v>
       </c>
       <c r="C90">
-        <v>933</v>
+        <v>102</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
-        <v>907.62</v>
+        <v>244.969</v>
       </c>
       <c r="C91">
-        <v>886</v>
+        <v>103</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
-        <v>892.739</v>
+        <v>245.517</v>
       </c>
       <c r="C92">
-        <v>840</v>
+        <v>102</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
-        <v>880.611</v>
+        <v>246.372</v>
       </c>
       <c r="C93">
-        <v>829</v>
+        <v>100</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
-        <v>883.4450000000001</v>
+        <v>191.294</v>
       </c>
       <c r="C94">
-        <v>793</v>
+        <v>103</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
-        <v>913.206</v>
+        <v>187.847</v>
       </c>
       <c r="C95">
-        <v>782</v>
+        <v>105</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
-        <v>934.176</v>
+        <v>191.819</v>
       </c>
       <c r="C96">
-        <v>812</v>
+        <v>109</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B97">
-        <v>956.794</v>
+        <v>191.992</v>
       </c>
       <c r="C97">
-        <v>853</v>
+        <v>113</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B98">
-        <v>861.976</v>
+        <v>158.174</v>
       </c>
       <c r="C98">
-        <v>1008</v>
+        <v>117</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46133.01041666666</v>
+        <v>46134.01041666666</v>
       </c>
       <c r="B99">
-        <v>898.958</v>
+        <v>155.872</v>
       </c>
       <c r="C99">
-        <v>1104</v>
+        <v>116</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46133.02083333334</v>
+        <v>46134.02083333334</v>
       </c>
       <c r="B100">
-        <v>928.774</v>
+        <v>153.695</v>
       </c>
       <c r="C100">
-        <v>1214</v>
+        <v>105</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46133.03125</v>
+        <v>46134.03125</v>
       </c>
       <c r="B101">
-        <v>948.021</v>
+        <v>151.473</v>
       </c>
       <c r="C101">
-        <v>1296</v>
+        <v>93</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46133.04166666666</v>
+        <v>46134.04166666666</v>
       </c>
       <c r="B102">
-        <v>1077.874</v>
+        <v>160.64</v>
       </c>
       <c r="C102">
-        <v>1491</v>
+        <v>81</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46133.05208333334</v>
+        <v>46134.05208333334</v>
       </c>
       <c r="B103">
-        <v>1133.461</v>
+        <v>160.307</v>
       </c>
       <c r="C103">
-        <v>1563</v>
+        <v>73</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46133.0625</v>
+        <v>46134.0625</v>
       </c>
       <c r="B104">
-        <v>1182.254</v>
+        <v>159.694</v>
       </c>
       <c r="C104">
-        <v>1666</v>
+        <v>75</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46133.07291666666</v>
+        <v>46134.07291666666</v>
       </c>
       <c r="B105">
-        <v>1216.081</v>
+        <v>164.316</v>
       </c>
       <c r="C105">
-        <v>1575</v>
+        <v>65</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46133.08333333334</v>
+        <v>46134.08333333334</v>
       </c>
       <c r="B106">
-        <v>1274.183</v>
+        <v>151.49</v>
       </c>
       <c r="C106">
-        <v>1585</v>
+        <v>63</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46133.09375</v>
+        <v>46134.09375</v>
       </c>
       <c r="B107">
-        <v>1324.831</v>
+        <v>148.96</v>
       </c>
       <c r="C107">
-        <v>1602</v>
+        <v>67</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46133.10416666666</v>
+        <v>46134.10416666666</v>
       </c>
       <c r="B108">
-        <v>1348.891</v>
+        <v>146.664</v>
       </c>
       <c r="C108">
-        <v>1627</v>
+        <v>65</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46133.11458333334</v>
+        <v>46134.11458333334</v>
       </c>
       <c r="B109">
-        <v>1376.946</v>
+        <v>144.892</v>
       </c>
       <c r="C109">
-        <v>1545</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46133.125</v>
+        <v>46134.125</v>
       </c>
       <c r="B110">
-        <v>1404.427</v>
+        <v>138.836</v>
       </c>
       <c r="C110">
-        <v>1575</v>
+        <v>62</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46133.13541666666</v>
+        <v>46134.13541666666</v>
       </c>
       <c r="B111">
-        <v>1414.548</v>
+        <v>139.182</v>
       </c>
       <c r="C111">
-        <v>1541</v>
+        <v>53</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46133.14583333334</v>
+        <v>46134.14583333334</v>
       </c>
       <c r="B112">
-        <v>1430.951</v>
+        <v>134.931</v>
       </c>
       <c r="C112">
-        <v>1573</v>
+        <v>49</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46133.15625</v>
+        <v>46134.15625</v>
       </c>
       <c r="B113">
-        <v>1447.523</v>
+        <v>133.371</v>
       </c>
       <c r="C113">
-        <v>1630</v>
+        <v>57</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46133.16666666666</v>
+        <v>46134.16666666666</v>
       </c>
       <c r="B114">
-        <v>1484.44</v>
+        <v>130.362</v>
       </c>
       <c r="C114">
-        <v>1659</v>
+        <v>79</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46133.17708333334</v>
+        <v>46134.17708333334</v>
       </c>
       <c r="B115">
-        <v>1503.468</v>
+        <v>129.74</v>
       </c>
       <c r="C115">
-        <v>1647</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46133.1875</v>
+        <v>46134.1875</v>
       </c>
       <c r="B116">
-        <v>1522.836</v>
+        <v>128.585</v>
       </c>
       <c r="C116">
-        <v>1607</v>
+        <v>67</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46133.19791666666</v>
+        <v>46134.19791666666</v>
       </c>
       <c r="B117">
-        <v>1544.936</v>
+        <v>128.406</v>
       </c>
       <c r="C117">
-        <v>1646</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46133.20833333334</v>
+        <v>46134.20833333334</v>
       </c>
       <c r="B118">
-        <v>1507.048</v>
+        <v>126.483</v>
       </c>
       <c r="C118">
-        <v>1641</v>
+        <v>73</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46133.21875</v>
+        <v>46134.21875</v>
       </c>
       <c r="B119">
-        <v>1529.185</v>
+        <v>130.537</v>
       </c>
       <c r="C119">
-        <v>1618</v>
+        <v>66</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46133.22916666666</v>
+        <v>46134.22916666666</v>
       </c>
       <c r="B120">
-        <v>1547.264</v>
+        <v>127.264</v>
       </c>
       <c r="C120">
-        <v>1641</v>
+        <v>74</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46133.23958333334</v>
+        <v>46134.23958333334</v>
       </c>
       <c r="B121">
-        <v>1567.177</v>
+        <v>126.524</v>
       </c>
       <c r="C121">
-        <v>1650</v>
+        <v>79</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46133.25</v>
+        <v>46134.25</v>
       </c>
       <c r="B122">
-        <v>1548.791</v>
+        <v>126.459</v>
       </c>
       <c r="C122">
-        <v>1655</v>
+        <v>83</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46133.26041666666</v>
+        <v>46134.26041666666</v>
       </c>
       <c r="B123">
-        <v>1528.274</v>
+        <v>124.088</v>
       </c>
       <c r="C123">
-        <v>1685</v>
+        <v>94</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46133.27083333334</v>
+        <v>46134.27083333334</v>
       </c>
       <c r="B124">
-        <v>1514.297</v>
+        <v>122.142</v>
       </c>
       <c r="C124">
-        <v>1629</v>
+        <v>87</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46133.28125</v>
+        <v>46134.28125</v>
       </c>
       <c r="B125">
-        <v>1508.218</v>
+        <v>122.967</v>
       </c>
       <c r="C125">
-        <v>1538</v>
+        <v>68</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46133.29166666666</v>
+        <v>46134.29166666666</v>
       </c>
       <c r="B126">
-        <v>1450.05</v>
+        <v>114.014</v>
       </c>
       <c r="C126">
-        <v>1499</v>
+        <v>60</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46133.30208333334</v>
+        <v>46134.30208333334</v>
       </c>
       <c r="B127">
-        <v>1428.46</v>
+        <v>104.521</v>
       </c>
       <c r="C127">
-        <v>1454</v>
+        <v>48</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46133.3125</v>
+        <v>46134.3125</v>
       </c>
       <c r="B128">
-        <v>1402.589</v>
+        <v>105.309</v>
       </c>
       <c r="C128">
-        <v>1379</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46133.32291666666</v>
+        <v>46134.32291666666</v>
       </c>
       <c r="B129">
-        <v>1371.67</v>
+        <v>102.014</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46133.33333333334</v>
+        <v>46134.33333333334</v>
       </c>
       <c r="B130">
-        <v>1398.347</v>
+        <v>101.664</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46133.34375</v>
+        <v>46134.34375</v>
       </c>
       <c r="B131">
-        <v>1360.717</v>
+        <v>103.078</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46133.35416666666</v>
+        <v>46134.35416666666</v>
       </c>
       <c r="B132">
-        <v>1335.17</v>
+        <v>106.413</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46133.36458333334</v>
+        <v>46134.36458333334</v>
       </c>
       <c r="B133">
-        <v>1296.393</v>
+        <v>107.525</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46133.375</v>
+        <v>46134.375</v>
       </c>
       <c r="B134">
-        <v>1226.429</v>
+        <v>117.023</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46133.38541666666</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="B135">
-        <v>1196.936</v>
+        <v>117.767</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46133.39583333334</v>
+        <v>46134.39583333334</v>
       </c>
       <c r="B136">
-        <v>1167.024</v>
+        <v>120.02</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46133.40625</v>
+        <v>46134.40625</v>
       </c>
       <c r="B137">
-        <v>1137.75</v>
+        <v>122.091</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46133.41666666666</v>
+        <v>46134.41666666666</v>
       </c>
       <c r="B138">
-        <v>1080.848</v>
+        <v>132.836</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46133.42708333334</v>
+        <v>46134.42708333334</v>
       </c>
       <c r="B139">
-        <v>1055.565</v>
+        <v>136.99</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46133.4375</v>
+        <v>46134.4375</v>
       </c>
       <c r="B140">
-        <v>1028.35</v>
+        <v>142.054</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46133.44791666666</v>
+        <v>46134.44791666666</v>
       </c>
       <c r="B141">
-        <v>992.583</v>
+        <v>146.909</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46133.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="B142">
-        <v>962.218</v>
+        <v>157.659</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46133.46875</v>
+        <v>46134.46875</v>
       </c>
       <c r="B143">
-        <v>926.774</v>
+        <v>161.587</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46133.47916666666</v>
+        <v>46134.47916666666</v>
       </c>
       <c r="B144">
-        <v>903.449</v>
+        <v>166.04</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46133.48958333334</v>
+        <v>46134.48958333334</v>
       </c>
       <c r="B145">
-        <v>879.111</v>
+        <v>171.034</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46133.5</v>
+        <v>46134.5</v>
       </c>
       <c r="B146">
-        <v>854.42</v>
+        <v>177.005</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46133.51041666666</v>
+        <v>46134.51041666666</v>
       </c>
       <c r="B147">
-        <v>826.579</v>
+        <v>183.822</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46133.52083333334</v>
+        <v>46134.52083333334</v>
       </c>
       <c r="B148">
-        <v>795.973</v>
+        <v>190.732</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46133.53125</v>
+        <v>46134.53125</v>
       </c>
       <c r="B149">
-        <v>768.671</v>
+        <v>198.5</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46133.54166666666</v>
+        <v>46134.54166666666</v>
       </c>
       <c r="B150">
-        <v>737.912</v>
+        <v>207.101</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46133.55208333334</v>
+        <v>46134.55208333334</v>
       </c>
       <c r="B151">
-        <v>716.249</v>
+        <v>211.85</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46133.5625</v>
+        <v>46134.5625</v>
       </c>
       <c r="B152">
-        <v>694.509</v>
+        <v>215.998</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46133.57291666666</v>
+        <v>46134.57291666666</v>
       </c>
       <c r="B153">
-        <v>673.726</v>
+        <v>220.702</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46133.58333333334</v>
+        <v>46134.58333333334</v>
       </c>
       <c r="B154">
-        <v>652.4400000000001</v>
+        <v>209.954</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46133.59375</v>
+        <v>46134.59375</v>
       </c>
       <c r="B155">
-        <v>628.48</v>
+        <v>212.789</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46133.60416666666</v>
+        <v>46134.60416666666</v>
       </c>
       <c r="B156">
-        <v>603.484</v>
+        <v>215.351</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46133.61458333334</v>
+        <v>46134.61458333334</v>
       </c>
       <c r="B157">
-        <v>577.245</v>
+        <v>218.587</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46133.625</v>
+        <v>46134.625</v>
       </c>
       <c r="B158">
-        <v>479.83</v>
+        <v>216.018</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46133.63541666666</v>
+        <v>46134.63541666666</v>
       </c>
       <c r="B159">
-        <v>465.959</v>
+        <v>217.418</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46133.64583333334</v>
+        <v>46134.64583333334</v>
       </c>
       <c r="B160">
-        <v>447.618</v>
+        <v>218.832</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46133.65625</v>
+        <v>46134.65625</v>
       </c>
       <c r="B161">
-        <v>438.696</v>
+        <v>220.038</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46133.66666666666</v>
+        <v>46134.66666666666</v>
       </c>
       <c r="B162">
-        <v>384.676</v>
+        <v>202.203</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46133.67708333334</v>
+        <v>46134.67708333334</v>
       </c>
       <c r="B163">
-        <v>380.195</v>
+        <v>202.076</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46133.6875</v>
+        <v>46134.6875</v>
       </c>
       <c r="B164">
-        <v>372.484</v>
+        <v>202.339</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46133.69791666666</v>
+        <v>46134.69791666666</v>
       </c>
       <c r="B165">
-        <v>368.806</v>
+        <v>202.629</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46133.70833333334</v>
+        <v>46134.70833333334</v>
       </c>
       <c r="B166">
-        <v>359.26</v>
+        <v>204.068</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46133.71875</v>
+        <v>46134.71875</v>
       </c>
       <c r="B167">
-        <v>344.714</v>
+        <v>201.438</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46133.72916666666</v>
+        <v>46134.72916666666</v>
       </c>
       <c r="B168">
-        <v>330.445</v>
+        <v>197.952</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46133.73958333334</v>
+        <v>46134.73958333334</v>
       </c>
       <c r="B169">
-        <v>316.297</v>
+        <v>194.897</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46133.75</v>
+        <v>46134.75</v>
       </c>
       <c r="B170">
-        <v>289.643</v>
+        <v>186.38</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46133.76041666666</v>
+        <v>46134.76041666666</v>
       </c>
       <c r="B171">
-        <v>280.347</v>
+        <v>183.014</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46133.77083333334</v>
+        <v>46134.77083333334</v>
       </c>
       <c r="B172">
-        <v>272.872</v>
+        <v>182.938</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46133.78125</v>
+        <v>46134.78125</v>
       </c>
       <c r="B173">
-        <v>266.022</v>
+        <v>180.603</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46133.79166666666</v>
+        <v>46134.79166666666</v>
       </c>
       <c r="B174">
-        <v>257.366</v>
+        <v>179.394</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46133.80208333334</v>
+        <v>46134.80208333334</v>
       </c>
       <c r="B175">
-        <v>257.522</v>
+        <v>178.479</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46133.8125</v>
+        <v>46134.8125</v>
       </c>
       <c r="B176">
-        <v>257.86</v>
+        <v>177.533</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46133.82291666666</v>
+        <v>46134.82291666666</v>
       </c>
       <c r="B177">
-        <v>282.689</v>
+        <v>204.031</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46133.83333333334</v>
+        <v>46134.83333333334</v>
       </c>
       <c r="B178">
-        <v>253.54</v>
+        <v>204.143</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46133.84375</v>
+        <v>46134.84375</v>
       </c>
       <c r="B179">
-        <v>250.577</v>
+        <v>183.175</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46133.85416666666</v>
+        <v>46134.85416666666</v>
       </c>
       <c r="B180">
-        <v>248.198</v>
+        <v>174.296</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46133.86458333334</v>
+        <v>46134.86458333334</v>
       </c>
       <c r="B181">
-        <v>245.698</v>
+        <v>172.46</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46133.875</v>
+        <v>46134.875</v>
       </c>
       <c r="B182">
-        <v>241.75</v>
+        <v>203.364</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46133.88541666666</v>
+        <v>46134.88541666666</v>
       </c>
       <c r="B183">
-        <v>241.722</v>
+        <v>181.195</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46133.89583333334</v>
+        <v>46134.89583333334</v>
       </c>
       <c r="B184">
-        <v>242.544</v>
+        <v>186.171</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46133.90625</v>
+        <v>46134.90625</v>
       </c>
       <c r="B185">
-        <v>242.781</v>
+        <v>191.384</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46133.91666666666</v>
+        <v>46134.91666666666</v>
       </c>
       <c r="B186">
-        <v>244.823</v>
+        <v>193.589</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46133.92708333334</v>
+        <v>46134.92708333334</v>
       </c>
       <c r="B187">
-        <v>244.969</v>
+        <v>201.694</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46133.9375</v>
+        <v>46134.9375</v>
       </c>
       <c r="B188">
-        <v>245.517</v>
+        <v>209.729</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46133.94791666666</v>
+        <v>46134.94791666666</v>
       </c>
       <c r="B189">
-        <v>246.372</v>
+        <v>218.427</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46133.95833333334</v>
+        <v>46134.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46133.96875</v>
+        <v>46134.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46133.97916666666</v>
+        <v>46134.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46133.98958333334</v>
+        <v>46134.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,580 +31,1156 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.04.20261</t>
-  </si>
-  <si>
-    <t>21.04.20262</t>
-  </si>
-  <si>
-    <t>21.04.20263</t>
-  </si>
-  <si>
-    <t>21.04.20264</t>
-  </si>
-  <si>
-    <t>21.04.20265</t>
-  </si>
-  <si>
-    <t>21.04.20266</t>
-  </si>
-  <si>
-    <t>21.04.20267</t>
-  </si>
-  <si>
-    <t>21.04.20268</t>
-  </si>
-  <si>
-    <t>21.04.20269</t>
-  </si>
-  <si>
-    <t>21.04.202610</t>
-  </si>
-  <si>
-    <t>21.04.202611</t>
-  </si>
-  <si>
-    <t>21.04.202612</t>
-  </si>
-  <si>
-    <t>21.04.202613</t>
-  </si>
-  <si>
-    <t>21.04.202614</t>
-  </si>
-  <si>
-    <t>21.04.202615</t>
-  </si>
-  <si>
-    <t>21.04.202616</t>
-  </si>
-  <si>
-    <t>21.04.202617</t>
-  </si>
-  <si>
-    <t>21.04.202618</t>
-  </si>
-  <si>
-    <t>21.04.202619</t>
-  </si>
-  <si>
-    <t>21.04.202620</t>
-  </si>
-  <si>
-    <t>21.04.202621</t>
-  </si>
-  <si>
-    <t>21.04.202622</t>
-  </si>
-  <si>
-    <t>21.04.202623</t>
-  </si>
-  <si>
-    <t>21.04.202624</t>
-  </si>
-  <si>
-    <t>21.04.202625</t>
-  </si>
-  <si>
-    <t>21.04.202626</t>
-  </si>
-  <si>
-    <t>21.04.202627</t>
-  </si>
-  <si>
-    <t>21.04.202628</t>
-  </si>
-  <si>
-    <t>21.04.202629</t>
-  </si>
-  <si>
-    <t>21.04.202630</t>
-  </si>
-  <si>
-    <t>21.04.202631</t>
-  </si>
-  <si>
-    <t>21.04.202632</t>
-  </si>
-  <si>
-    <t>21.04.202633</t>
-  </si>
-  <si>
-    <t>21.04.202634</t>
-  </si>
-  <si>
-    <t>21.04.202635</t>
-  </si>
-  <si>
-    <t>21.04.202636</t>
-  </si>
-  <si>
-    <t>21.04.202637</t>
-  </si>
-  <si>
-    <t>21.04.202638</t>
-  </si>
-  <si>
-    <t>21.04.202639</t>
-  </si>
-  <si>
-    <t>21.04.202640</t>
-  </si>
-  <si>
-    <t>21.04.202641</t>
-  </si>
-  <si>
-    <t>21.04.202642</t>
-  </si>
-  <si>
-    <t>21.04.202643</t>
-  </si>
-  <si>
-    <t>21.04.202644</t>
-  </si>
-  <si>
-    <t>21.04.202645</t>
-  </si>
-  <si>
-    <t>21.04.202646</t>
-  </si>
-  <si>
-    <t>21.04.202647</t>
-  </si>
-  <si>
-    <t>21.04.202648</t>
-  </si>
-  <si>
-    <t>21.04.202649</t>
-  </si>
-  <si>
-    <t>21.04.202650</t>
-  </si>
-  <si>
-    <t>21.04.202651</t>
-  </si>
-  <si>
-    <t>21.04.202652</t>
-  </si>
-  <si>
-    <t>21.04.202653</t>
-  </si>
-  <si>
-    <t>21.04.202654</t>
-  </si>
-  <si>
-    <t>21.04.202655</t>
-  </si>
-  <si>
-    <t>21.04.202656</t>
-  </si>
-  <si>
-    <t>21.04.202657</t>
-  </si>
-  <si>
-    <t>21.04.202658</t>
-  </si>
-  <si>
-    <t>21.04.202659</t>
-  </si>
-  <si>
-    <t>21.04.202660</t>
-  </si>
-  <si>
-    <t>21.04.202661</t>
-  </si>
-  <si>
-    <t>21.04.202662</t>
-  </si>
-  <si>
-    <t>21.04.202663</t>
-  </si>
-  <si>
-    <t>21.04.202664</t>
-  </si>
-  <si>
-    <t>21.04.202665</t>
-  </si>
-  <si>
-    <t>21.04.202666</t>
-  </si>
-  <si>
-    <t>21.04.202667</t>
-  </si>
-  <si>
-    <t>21.04.202668</t>
-  </si>
-  <si>
-    <t>21.04.202669</t>
-  </si>
-  <si>
-    <t>21.04.202670</t>
-  </si>
-  <si>
-    <t>21.04.202671</t>
-  </si>
-  <si>
-    <t>21.04.202672</t>
-  </si>
-  <si>
-    <t>21.04.202673</t>
-  </si>
-  <si>
-    <t>21.04.202674</t>
-  </si>
-  <si>
-    <t>21.04.202675</t>
-  </si>
-  <si>
-    <t>21.04.202676</t>
-  </si>
-  <si>
-    <t>21.04.202677</t>
-  </si>
-  <si>
-    <t>21.04.202678</t>
-  </si>
-  <si>
-    <t>21.04.202679</t>
-  </si>
-  <si>
-    <t>21.04.202680</t>
-  </si>
-  <si>
-    <t>21.04.202681</t>
-  </si>
-  <si>
-    <t>21.04.202682</t>
-  </si>
-  <si>
-    <t>21.04.202683</t>
-  </si>
-  <si>
-    <t>21.04.202684</t>
-  </si>
-  <si>
-    <t>21.04.202685</t>
-  </si>
-  <si>
-    <t>21.04.202686</t>
-  </si>
-  <si>
-    <t>21.04.202687</t>
-  </si>
-  <si>
-    <t>21.04.202688</t>
-  </si>
-  <si>
-    <t>21.04.202689</t>
-  </si>
-  <si>
-    <t>21.04.202690</t>
-  </si>
-  <si>
-    <t>21.04.202691</t>
-  </si>
-  <si>
-    <t>21.04.202692</t>
-  </si>
-  <si>
-    <t>21.04.202693</t>
-  </si>
-  <si>
-    <t>21.04.202694</t>
-  </si>
-  <si>
-    <t>21.04.202695</t>
-  </si>
-  <si>
-    <t>21.04.202696</t>
-  </si>
-  <si>
-    <t>22.04.20261</t>
-  </si>
-  <si>
-    <t>22.04.20262</t>
-  </si>
-  <si>
-    <t>22.04.20263</t>
-  </si>
-  <si>
-    <t>22.04.20264</t>
-  </si>
-  <si>
-    <t>22.04.20265</t>
-  </si>
-  <si>
-    <t>22.04.20266</t>
-  </si>
-  <si>
-    <t>22.04.20267</t>
-  </si>
-  <si>
-    <t>22.04.20268</t>
-  </si>
-  <si>
-    <t>22.04.20269</t>
-  </si>
-  <si>
-    <t>22.04.202610</t>
-  </si>
-  <si>
-    <t>22.04.202611</t>
-  </si>
-  <si>
-    <t>22.04.202612</t>
-  </si>
-  <si>
-    <t>22.04.202613</t>
-  </si>
-  <si>
-    <t>22.04.202614</t>
-  </si>
-  <si>
-    <t>22.04.202615</t>
-  </si>
-  <si>
-    <t>22.04.202616</t>
-  </si>
-  <si>
-    <t>22.04.202617</t>
-  </si>
-  <si>
-    <t>22.04.202618</t>
-  </si>
-  <si>
-    <t>22.04.202619</t>
-  </si>
-  <si>
-    <t>22.04.202620</t>
-  </si>
-  <si>
-    <t>22.04.202621</t>
-  </si>
-  <si>
-    <t>22.04.202622</t>
-  </si>
-  <si>
-    <t>22.04.202623</t>
-  </si>
-  <si>
-    <t>22.04.202624</t>
-  </si>
-  <si>
-    <t>22.04.202625</t>
-  </si>
-  <si>
-    <t>22.04.202626</t>
-  </si>
-  <si>
-    <t>22.04.202627</t>
-  </si>
-  <si>
-    <t>22.04.202628</t>
-  </si>
-  <si>
-    <t>22.04.202629</t>
-  </si>
-  <si>
-    <t>22.04.202630</t>
-  </si>
-  <si>
-    <t>22.04.202631</t>
-  </si>
-  <si>
-    <t>22.04.202632</t>
-  </si>
-  <si>
-    <t>22.04.202633</t>
-  </si>
-  <si>
-    <t>22.04.202634</t>
-  </si>
-  <si>
-    <t>22.04.202635</t>
-  </si>
-  <si>
-    <t>22.04.202636</t>
-  </si>
-  <si>
-    <t>22.04.202637</t>
-  </si>
-  <si>
-    <t>22.04.202638</t>
-  </si>
-  <si>
-    <t>22.04.202639</t>
-  </si>
-  <si>
-    <t>22.04.202640</t>
-  </si>
-  <si>
-    <t>22.04.202641</t>
-  </si>
-  <si>
-    <t>22.04.202642</t>
-  </si>
-  <si>
-    <t>22.04.202643</t>
-  </si>
-  <si>
-    <t>22.04.202644</t>
-  </si>
-  <si>
-    <t>22.04.202645</t>
-  </si>
-  <si>
-    <t>22.04.202646</t>
-  </si>
-  <si>
-    <t>22.04.202647</t>
-  </si>
-  <si>
-    <t>22.04.202648</t>
-  </si>
-  <si>
-    <t>22.04.202649</t>
-  </si>
-  <si>
-    <t>22.04.202650</t>
-  </si>
-  <si>
-    <t>22.04.202651</t>
-  </si>
-  <si>
-    <t>22.04.202652</t>
-  </si>
-  <si>
-    <t>22.04.202653</t>
-  </si>
-  <si>
-    <t>22.04.202654</t>
-  </si>
-  <si>
-    <t>22.04.202655</t>
-  </si>
-  <si>
-    <t>22.04.202656</t>
-  </si>
-  <si>
-    <t>22.04.202657</t>
-  </si>
-  <si>
-    <t>22.04.202658</t>
-  </si>
-  <si>
-    <t>22.04.202659</t>
-  </si>
-  <si>
-    <t>22.04.202660</t>
-  </si>
-  <si>
-    <t>22.04.202661</t>
-  </si>
-  <si>
-    <t>22.04.202662</t>
-  </si>
-  <si>
-    <t>22.04.202663</t>
-  </si>
-  <si>
-    <t>22.04.202664</t>
-  </si>
-  <si>
-    <t>22.04.202665</t>
-  </si>
-  <si>
-    <t>22.04.202666</t>
-  </si>
-  <si>
-    <t>22.04.202667</t>
-  </si>
-  <si>
-    <t>22.04.202668</t>
-  </si>
-  <si>
-    <t>22.04.202669</t>
-  </si>
-  <si>
-    <t>22.04.202670</t>
-  </si>
-  <si>
-    <t>22.04.202671</t>
-  </si>
-  <si>
-    <t>22.04.202672</t>
-  </si>
-  <si>
-    <t>22.04.202673</t>
-  </si>
-  <si>
-    <t>22.04.202674</t>
-  </si>
-  <si>
-    <t>22.04.202675</t>
-  </si>
-  <si>
-    <t>22.04.202676</t>
-  </si>
-  <si>
-    <t>22.04.202677</t>
-  </si>
-  <si>
-    <t>22.04.202678</t>
-  </si>
-  <si>
-    <t>22.04.202679</t>
-  </si>
-  <si>
-    <t>22.04.202680</t>
-  </si>
-  <si>
-    <t>22.04.202681</t>
-  </si>
-  <si>
-    <t>22.04.202682</t>
-  </si>
-  <si>
-    <t>22.04.202683</t>
-  </si>
-  <si>
-    <t>22.04.202684</t>
-  </si>
-  <si>
-    <t>22.04.202685</t>
-  </si>
-  <si>
-    <t>22.04.202686</t>
-  </si>
-  <si>
-    <t>22.04.202687</t>
-  </si>
-  <si>
-    <t>22.04.202688</t>
-  </si>
-  <si>
-    <t>22.04.202689</t>
-  </si>
-  <si>
-    <t>22.04.202690</t>
-  </si>
-  <si>
-    <t>22.04.202691</t>
-  </si>
-  <si>
-    <t>22.04.202692</t>
-  </si>
-  <si>
-    <t>22.04.202693</t>
-  </si>
-  <si>
-    <t>22.04.202694</t>
-  </si>
-  <si>
-    <t>22.04.202695</t>
-  </si>
-  <si>
-    <t>22.04.202696</t>
+    <t>24.04.20261</t>
+  </si>
+  <si>
+    <t>24.04.20262</t>
+  </si>
+  <si>
+    <t>24.04.20263</t>
+  </si>
+  <si>
+    <t>24.04.20264</t>
+  </si>
+  <si>
+    <t>24.04.20265</t>
+  </si>
+  <si>
+    <t>24.04.20266</t>
+  </si>
+  <si>
+    <t>24.04.20267</t>
+  </si>
+  <si>
+    <t>24.04.20268</t>
+  </si>
+  <si>
+    <t>24.04.20269</t>
+  </si>
+  <si>
+    <t>24.04.202610</t>
+  </si>
+  <si>
+    <t>24.04.202611</t>
+  </si>
+  <si>
+    <t>24.04.202612</t>
+  </si>
+  <si>
+    <t>24.04.202613</t>
+  </si>
+  <si>
+    <t>24.04.202614</t>
+  </si>
+  <si>
+    <t>24.04.202615</t>
+  </si>
+  <si>
+    <t>24.04.202616</t>
+  </si>
+  <si>
+    <t>24.04.202617</t>
+  </si>
+  <si>
+    <t>24.04.202618</t>
+  </si>
+  <si>
+    <t>24.04.202619</t>
+  </si>
+  <si>
+    <t>24.04.202620</t>
+  </si>
+  <si>
+    <t>24.04.202621</t>
+  </si>
+  <si>
+    <t>24.04.202622</t>
+  </si>
+  <si>
+    <t>24.04.202623</t>
+  </si>
+  <si>
+    <t>24.04.202624</t>
+  </si>
+  <si>
+    <t>24.04.202625</t>
+  </si>
+  <si>
+    <t>24.04.202626</t>
+  </si>
+  <si>
+    <t>24.04.202627</t>
+  </si>
+  <si>
+    <t>24.04.202628</t>
+  </si>
+  <si>
+    <t>24.04.202629</t>
+  </si>
+  <si>
+    <t>24.04.202630</t>
+  </si>
+  <si>
+    <t>24.04.202631</t>
+  </si>
+  <si>
+    <t>24.04.202632</t>
+  </si>
+  <si>
+    <t>24.04.202633</t>
+  </si>
+  <si>
+    <t>24.04.202634</t>
+  </si>
+  <si>
+    <t>24.04.202635</t>
+  </si>
+  <si>
+    <t>24.04.202636</t>
+  </si>
+  <si>
+    <t>24.04.202637</t>
+  </si>
+  <si>
+    <t>24.04.202638</t>
+  </si>
+  <si>
+    <t>24.04.202639</t>
+  </si>
+  <si>
+    <t>24.04.202640</t>
+  </si>
+  <si>
+    <t>24.04.202641</t>
+  </si>
+  <si>
+    <t>24.04.202642</t>
+  </si>
+  <si>
+    <t>24.04.202643</t>
+  </si>
+  <si>
+    <t>24.04.202644</t>
+  </si>
+  <si>
+    <t>24.04.202645</t>
+  </si>
+  <si>
+    <t>24.04.202646</t>
+  </si>
+  <si>
+    <t>24.04.202647</t>
+  </si>
+  <si>
+    <t>24.04.202648</t>
+  </si>
+  <si>
+    <t>24.04.202649</t>
+  </si>
+  <si>
+    <t>24.04.202650</t>
+  </si>
+  <si>
+    <t>24.04.202651</t>
+  </si>
+  <si>
+    <t>24.04.202652</t>
+  </si>
+  <si>
+    <t>24.04.202653</t>
+  </si>
+  <si>
+    <t>24.04.202654</t>
+  </si>
+  <si>
+    <t>24.04.202655</t>
+  </si>
+  <si>
+    <t>24.04.202656</t>
+  </si>
+  <si>
+    <t>24.04.202657</t>
+  </si>
+  <si>
+    <t>24.04.202658</t>
+  </si>
+  <si>
+    <t>24.04.202659</t>
+  </si>
+  <si>
+    <t>24.04.202660</t>
+  </si>
+  <si>
+    <t>24.04.202661</t>
+  </si>
+  <si>
+    <t>24.04.202662</t>
+  </si>
+  <si>
+    <t>24.04.202663</t>
+  </si>
+  <si>
+    <t>24.04.202664</t>
+  </si>
+  <si>
+    <t>24.04.202665</t>
+  </si>
+  <si>
+    <t>24.04.202666</t>
+  </si>
+  <si>
+    <t>24.04.202667</t>
+  </si>
+  <si>
+    <t>24.04.202668</t>
+  </si>
+  <si>
+    <t>24.04.202669</t>
+  </si>
+  <si>
+    <t>24.04.202670</t>
+  </si>
+  <si>
+    <t>24.04.202671</t>
+  </si>
+  <si>
+    <t>24.04.202672</t>
+  </si>
+  <si>
+    <t>24.04.202673</t>
+  </si>
+  <si>
+    <t>24.04.202674</t>
+  </si>
+  <si>
+    <t>24.04.202675</t>
+  </si>
+  <si>
+    <t>24.04.202676</t>
+  </si>
+  <si>
+    <t>24.04.202677</t>
+  </si>
+  <si>
+    <t>24.04.202678</t>
+  </si>
+  <si>
+    <t>24.04.202679</t>
+  </si>
+  <si>
+    <t>24.04.202680</t>
+  </si>
+  <si>
+    <t>24.04.202681</t>
+  </si>
+  <si>
+    <t>24.04.202682</t>
+  </si>
+  <si>
+    <t>24.04.202683</t>
+  </si>
+  <si>
+    <t>24.04.202684</t>
+  </si>
+  <si>
+    <t>24.04.202685</t>
+  </si>
+  <si>
+    <t>24.04.202686</t>
+  </si>
+  <si>
+    <t>24.04.202687</t>
+  </si>
+  <si>
+    <t>24.04.202688</t>
+  </si>
+  <si>
+    <t>24.04.202689</t>
+  </si>
+  <si>
+    <t>24.04.202690</t>
+  </si>
+  <si>
+    <t>24.04.202691</t>
+  </si>
+  <si>
+    <t>24.04.202692</t>
+  </si>
+  <si>
+    <t>24.04.202693</t>
+  </si>
+  <si>
+    <t>24.04.202694</t>
+  </si>
+  <si>
+    <t>24.04.202695</t>
+  </si>
+  <si>
+    <t>24.04.202696</t>
+  </si>
+  <si>
+    <t>25.04.20261</t>
+  </si>
+  <si>
+    <t>25.04.20262</t>
+  </si>
+  <si>
+    <t>25.04.20263</t>
+  </si>
+  <si>
+    <t>25.04.20264</t>
+  </si>
+  <si>
+    <t>25.04.20265</t>
+  </si>
+  <si>
+    <t>25.04.20266</t>
+  </si>
+  <si>
+    <t>25.04.20267</t>
+  </si>
+  <si>
+    <t>25.04.20268</t>
+  </si>
+  <si>
+    <t>25.04.20269</t>
+  </si>
+  <si>
+    <t>25.04.202610</t>
+  </si>
+  <si>
+    <t>25.04.202611</t>
+  </si>
+  <si>
+    <t>25.04.202612</t>
+  </si>
+  <si>
+    <t>25.04.202613</t>
+  </si>
+  <si>
+    <t>25.04.202614</t>
+  </si>
+  <si>
+    <t>25.04.202615</t>
+  </si>
+  <si>
+    <t>25.04.202616</t>
+  </si>
+  <si>
+    <t>25.04.202617</t>
+  </si>
+  <si>
+    <t>25.04.202618</t>
+  </si>
+  <si>
+    <t>25.04.202619</t>
+  </si>
+  <si>
+    <t>25.04.202620</t>
+  </si>
+  <si>
+    <t>25.04.202621</t>
+  </si>
+  <si>
+    <t>25.04.202622</t>
+  </si>
+  <si>
+    <t>25.04.202623</t>
+  </si>
+  <si>
+    <t>25.04.202624</t>
+  </si>
+  <si>
+    <t>25.04.202625</t>
+  </si>
+  <si>
+    <t>25.04.202626</t>
+  </si>
+  <si>
+    <t>25.04.202627</t>
+  </si>
+  <si>
+    <t>25.04.202628</t>
+  </si>
+  <si>
+    <t>25.04.202629</t>
+  </si>
+  <si>
+    <t>25.04.202630</t>
+  </si>
+  <si>
+    <t>25.04.202631</t>
+  </si>
+  <si>
+    <t>25.04.202632</t>
+  </si>
+  <si>
+    <t>25.04.202633</t>
+  </si>
+  <si>
+    <t>25.04.202634</t>
+  </si>
+  <si>
+    <t>25.04.202635</t>
+  </si>
+  <si>
+    <t>25.04.202636</t>
+  </si>
+  <si>
+    <t>25.04.202637</t>
+  </si>
+  <si>
+    <t>25.04.202638</t>
+  </si>
+  <si>
+    <t>25.04.202639</t>
+  </si>
+  <si>
+    <t>25.04.202640</t>
+  </si>
+  <si>
+    <t>25.04.202641</t>
+  </si>
+  <si>
+    <t>25.04.202642</t>
+  </si>
+  <si>
+    <t>25.04.202643</t>
+  </si>
+  <si>
+    <t>25.04.202644</t>
+  </si>
+  <si>
+    <t>25.04.202645</t>
+  </si>
+  <si>
+    <t>25.04.202646</t>
+  </si>
+  <si>
+    <t>25.04.202647</t>
+  </si>
+  <si>
+    <t>25.04.202648</t>
+  </si>
+  <si>
+    <t>25.04.202649</t>
+  </si>
+  <si>
+    <t>25.04.202650</t>
+  </si>
+  <si>
+    <t>25.04.202651</t>
+  </si>
+  <si>
+    <t>25.04.202652</t>
+  </si>
+  <si>
+    <t>25.04.202653</t>
+  </si>
+  <si>
+    <t>25.04.202654</t>
+  </si>
+  <si>
+    <t>25.04.202655</t>
+  </si>
+  <si>
+    <t>25.04.202656</t>
+  </si>
+  <si>
+    <t>25.04.202657</t>
+  </si>
+  <si>
+    <t>25.04.202658</t>
+  </si>
+  <si>
+    <t>25.04.202659</t>
+  </si>
+  <si>
+    <t>25.04.202660</t>
+  </si>
+  <si>
+    <t>25.04.202661</t>
+  </si>
+  <si>
+    <t>25.04.202662</t>
+  </si>
+  <si>
+    <t>25.04.202663</t>
+  </si>
+  <si>
+    <t>25.04.202664</t>
+  </si>
+  <si>
+    <t>25.04.202665</t>
+  </si>
+  <si>
+    <t>25.04.202666</t>
+  </si>
+  <si>
+    <t>25.04.202667</t>
+  </si>
+  <si>
+    <t>25.04.202668</t>
+  </si>
+  <si>
+    <t>25.04.202669</t>
+  </si>
+  <si>
+    <t>25.04.202670</t>
+  </si>
+  <si>
+    <t>25.04.202671</t>
+  </si>
+  <si>
+    <t>25.04.202672</t>
+  </si>
+  <si>
+    <t>25.04.202673</t>
+  </si>
+  <si>
+    <t>25.04.202674</t>
+  </si>
+  <si>
+    <t>25.04.202675</t>
+  </si>
+  <si>
+    <t>25.04.202676</t>
+  </si>
+  <si>
+    <t>25.04.202677</t>
+  </si>
+  <si>
+    <t>25.04.202678</t>
+  </si>
+  <si>
+    <t>25.04.202679</t>
+  </si>
+  <si>
+    <t>25.04.202680</t>
+  </si>
+  <si>
+    <t>25.04.202681</t>
+  </si>
+  <si>
+    <t>25.04.202682</t>
+  </si>
+  <si>
+    <t>25.04.202683</t>
+  </si>
+  <si>
+    <t>25.04.202684</t>
+  </si>
+  <si>
+    <t>25.04.202685</t>
+  </si>
+  <si>
+    <t>25.04.202686</t>
+  </si>
+  <si>
+    <t>25.04.202687</t>
+  </si>
+  <si>
+    <t>25.04.202688</t>
+  </si>
+  <si>
+    <t>25.04.202689</t>
+  </si>
+  <si>
+    <t>25.04.202690</t>
+  </si>
+  <si>
+    <t>25.04.202691</t>
+  </si>
+  <si>
+    <t>25.04.202692</t>
+  </si>
+  <si>
+    <t>25.04.202693</t>
+  </si>
+  <si>
+    <t>25.04.202694</t>
+  </si>
+  <si>
+    <t>25.04.202695</t>
+  </si>
+  <si>
+    <t>25.04.202696</t>
+  </si>
+  <si>
+    <t>26.04.20261</t>
+  </si>
+  <si>
+    <t>26.04.20262</t>
+  </si>
+  <si>
+    <t>26.04.20263</t>
+  </si>
+  <si>
+    <t>26.04.20264</t>
+  </si>
+  <si>
+    <t>26.04.20265</t>
+  </si>
+  <si>
+    <t>26.04.20266</t>
+  </si>
+  <si>
+    <t>26.04.20267</t>
+  </si>
+  <si>
+    <t>26.04.20268</t>
+  </si>
+  <si>
+    <t>26.04.20269</t>
+  </si>
+  <si>
+    <t>26.04.202610</t>
+  </si>
+  <si>
+    <t>26.04.202611</t>
+  </si>
+  <si>
+    <t>26.04.202612</t>
+  </si>
+  <si>
+    <t>26.04.202613</t>
+  </si>
+  <si>
+    <t>26.04.202614</t>
+  </si>
+  <si>
+    <t>26.04.202615</t>
+  </si>
+  <si>
+    <t>26.04.202616</t>
+  </si>
+  <si>
+    <t>26.04.202617</t>
+  </si>
+  <si>
+    <t>26.04.202618</t>
+  </si>
+  <si>
+    <t>26.04.202619</t>
+  </si>
+  <si>
+    <t>26.04.202620</t>
+  </si>
+  <si>
+    <t>26.04.202621</t>
+  </si>
+  <si>
+    <t>26.04.202622</t>
+  </si>
+  <si>
+    <t>26.04.202623</t>
+  </si>
+  <si>
+    <t>26.04.202624</t>
+  </si>
+  <si>
+    <t>26.04.202625</t>
+  </si>
+  <si>
+    <t>26.04.202626</t>
+  </si>
+  <si>
+    <t>26.04.202627</t>
+  </si>
+  <si>
+    <t>26.04.202628</t>
+  </si>
+  <si>
+    <t>26.04.202629</t>
+  </si>
+  <si>
+    <t>26.04.202630</t>
+  </si>
+  <si>
+    <t>26.04.202631</t>
+  </si>
+  <si>
+    <t>26.04.202632</t>
+  </si>
+  <si>
+    <t>26.04.202633</t>
+  </si>
+  <si>
+    <t>26.04.202634</t>
+  </si>
+  <si>
+    <t>26.04.202635</t>
+  </si>
+  <si>
+    <t>26.04.202636</t>
+  </si>
+  <si>
+    <t>26.04.202637</t>
+  </si>
+  <si>
+    <t>26.04.202638</t>
+  </si>
+  <si>
+    <t>26.04.202639</t>
+  </si>
+  <si>
+    <t>26.04.202640</t>
+  </si>
+  <si>
+    <t>26.04.202641</t>
+  </si>
+  <si>
+    <t>26.04.202642</t>
+  </si>
+  <si>
+    <t>26.04.202643</t>
+  </si>
+  <si>
+    <t>26.04.202644</t>
+  </si>
+  <si>
+    <t>26.04.202645</t>
+  </si>
+  <si>
+    <t>26.04.202646</t>
+  </si>
+  <si>
+    <t>26.04.202647</t>
+  </si>
+  <si>
+    <t>26.04.202648</t>
+  </si>
+  <si>
+    <t>26.04.202649</t>
+  </si>
+  <si>
+    <t>26.04.202650</t>
+  </si>
+  <si>
+    <t>26.04.202651</t>
+  </si>
+  <si>
+    <t>26.04.202652</t>
+  </si>
+  <si>
+    <t>26.04.202653</t>
+  </si>
+  <si>
+    <t>26.04.202654</t>
+  </si>
+  <si>
+    <t>26.04.202655</t>
+  </si>
+  <si>
+    <t>26.04.202656</t>
+  </si>
+  <si>
+    <t>26.04.202657</t>
+  </si>
+  <si>
+    <t>26.04.202658</t>
+  </si>
+  <si>
+    <t>26.04.202659</t>
+  </si>
+  <si>
+    <t>26.04.202660</t>
+  </si>
+  <si>
+    <t>26.04.202661</t>
+  </si>
+  <si>
+    <t>26.04.202662</t>
+  </si>
+  <si>
+    <t>26.04.202663</t>
+  </si>
+  <si>
+    <t>26.04.202664</t>
+  </si>
+  <si>
+    <t>26.04.202665</t>
+  </si>
+  <si>
+    <t>26.04.202666</t>
+  </si>
+  <si>
+    <t>26.04.202667</t>
+  </si>
+  <si>
+    <t>26.04.202668</t>
+  </si>
+  <si>
+    <t>26.04.202669</t>
+  </si>
+  <si>
+    <t>26.04.202670</t>
+  </si>
+  <si>
+    <t>26.04.202671</t>
+  </si>
+  <si>
+    <t>26.04.202672</t>
+  </si>
+  <si>
+    <t>26.04.202673</t>
+  </si>
+  <si>
+    <t>26.04.202674</t>
+  </si>
+  <si>
+    <t>26.04.202675</t>
+  </si>
+  <si>
+    <t>26.04.202676</t>
+  </si>
+  <si>
+    <t>26.04.202677</t>
+  </si>
+  <si>
+    <t>26.04.202678</t>
+  </si>
+  <si>
+    <t>26.04.202679</t>
+  </si>
+  <si>
+    <t>26.04.202680</t>
+  </si>
+  <si>
+    <t>26.04.202681</t>
+  </si>
+  <si>
+    <t>26.04.202682</t>
+  </si>
+  <si>
+    <t>26.04.202683</t>
+  </si>
+  <si>
+    <t>26.04.202684</t>
+  </si>
+  <si>
+    <t>26.04.202685</t>
+  </si>
+  <si>
+    <t>26.04.202686</t>
+  </si>
+  <si>
+    <t>26.04.202687</t>
+  </si>
+  <si>
+    <t>26.04.202688</t>
+  </si>
+  <si>
+    <t>26.04.202689</t>
+  </si>
+  <si>
+    <t>26.04.202690</t>
+  </si>
+  <si>
+    <t>26.04.202691</t>
+  </si>
+  <si>
+    <t>26.04.202692</t>
+  </si>
+  <si>
+    <t>26.04.202693</t>
+  </si>
+  <si>
+    <t>26.04.202694</t>
+  </si>
+  <si>
+    <t>26.04.202695</t>
+  </si>
+  <si>
+    <t>26.04.202696</t>
+  </si>
+  <si>
+    <t>27.04.20261</t>
+  </si>
+  <si>
+    <t>27.04.20262</t>
+  </si>
+  <si>
+    <t>27.04.20263</t>
+  </si>
+  <si>
+    <t>27.04.20264</t>
+  </si>
+  <si>
+    <t>27.04.20265</t>
+  </si>
+  <si>
+    <t>27.04.20266</t>
+  </si>
+  <si>
+    <t>27.04.20267</t>
+  </si>
+  <si>
+    <t>27.04.20268</t>
+  </si>
+  <si>
+    <t>27.04.20269</t>
+  </si>
+  <si>
+    <t>27.04.202610</t>
+  </si>
+  <si>
+    <t>27.04.202611</t>
+  </si>
+  <si>
+    <t>27.04.202612</t>
+  </si>
+  <si>
+    <t>27.04.202613</t>
+  </si>
+  <si>
+    <t>27.04.202614</t>
+  </si>
+  <si>
+    <t>27.04.202615</t>
+  </si>
+  <si>
+    <t>27.04.202616</t>
+  </si>
+  <si>
+    <t>27.04.202617</t>
+  </si>
+  <si>
+    <t>27.04.202618</t>
+  </si>
+  <si>
+    <t>27.04.202619</t>
+  </si>
+  <si>
+    <t>27.04.202620</t>
+  </si>
+  <si>
+    <t>27.04.202621</t>
+  </si>
+  <si>
+    <t>27.04.202622</t>
+  </si>
+  <si>
+    <t>27.04.202623</t>
+  </si>
+  <si>
+    <t>27.04.202624</t>
+  </si>
+  <si>
+    <t>27.04.202625</t>
+  </si>
+  <si>
+    <t>27.04.202626</t>
+  </si>
+  <si>
+    <t>27.04.202627</t>
+  </si>
+  <si>
+    <t>27.04.202628</t>
+  </si>
+  <si>
+    <t>27.04.202629</t>
+  </si>
+  <si>
+    <t>27.04.202630</t>
+  </si>
+  <si>
+    <t>27.04.202631</t>
+  </si>
+  <si>
+    <t>27.04.202632</t>
+  </si>
+  <si>
+    <t>27.04.202633</t>
+  </si>
+  <si>
+    <t>27.04.202634</t>
+  </si>
+  <si>
+    <t>27.04.202635</t>
+  </si>
+  <si>
+    <t>27.04.202636</t>
+  </si>
+  <si>
+    <t>27.04.202637</t>
+  </si>
+  <si>
+    <t>27.04.202638</t>
+  </si>
+  <si>
+    <t>27.04.202639</t>
+  </si>
+  <si>
+    <t>27.04.202640</t>
+  </si>
+  <si>
+    <t>27.04.202641</t>
+  </si>
+  <si>
+    <t>27.04.202642</t>
+  </si>
+  <si>
+    <t>27.04.202643</t>
+  </si>
+  <si>
+    <t>27.04.202644</t>
+  </si>
+  <si>
+    <t>27.04.202645</t>
+  </si>
+  <si>
+    <t>27.04.202646</t>
+  </si>
+  <si>
+    <t>27.04.202647</t>
+  </si>
+  <si>
+    <t>27.04.202648</t>
+  </si>
+  <si>
+    <t>27.04.202649</t>
+  </si>
+  <si>
+    <t>27.04.202650</t>
+  </si>
+  <si>
+    <t>27.04.202651</t>
+  </si>
+  <si>
+    <t>27.04.202652</t>
+  </si>
+  <si>
+    <t>27.04.202653</t>
+  </si>
+  <si>
+    <t>27.04.202654</t>
+  </si>
+  <si>
+    <t>27.04.202655</t>
+  </si>
+  <si>
+    <t>27.04.202656</t>
+  </si>
+  <si>
+    <t>27.04.202657</t>
+  </si>
+  <si>
+    <t>27.04.202658</t>
+  </si>
+  <si>
+    <t>27.04.202659</t>
+  </si>
+  <si>
+    <t>27.04.202660</t>
+  </si>
+  <si>
+    <t>27.04.202661</t>
+  </si>
+  <si>
+    <t>27.04.202662</t>
+  </si>
+  <si>
+    <t>27.04.202663</t>
+  </si>
+  <si>
+    <t>27.04.202664</t>
+  </si>
+  <si>
+    <t>27.04.202665</t>
+  </si>
+  <si>
+    <t>27.04.202666</t>
+  </si>
+  <si>
+    <t>27.04.202667</t>
+  </si>
+  <si>
+    <t>27.04.202668</t>
+  </si>
+  <si>
+    <t>27.04.202669</t>
+  </si>
+  <si>
+    <t>27.04.202670</t>
+  </si>
+  <si>
+    <t>27.04.202671</t>
+  </si>
+  <si>
+    <t>27.04.202672</t>
+  </si>
+  <si>
+    <t>27.04.202673</t>
+  </si>
+  <si>
+    <t>27.04.202674</t>
+  </si>
+  <si>
+    <t>27.04.202675</t>
+  </si>
+  <si>
+    <t>27.04.202676</t>
+  </si>
+  <si>
+    <t>27.04.202677</t>
+  </si>
+  <si>
+    <t>27.04.202678</t>
+  </si>
+  <si>
+    <t>27.04.202679</t>
+  </si>
+  <si>
+    <t>27.04.202680</t>
+  </si>
+  <si>
+    <t>27.04.202681</t>
+  </si>
+  <si>
+    <t>27.04.202682</t>
+  </si>
+  <si>
+    <t>27.04.202683</t>
+  </si>
+  <si>
+    <t>27.04.202684</t>
+  </si>
+  <si>
+    <t>27.04.202685</t>
+  </si>
+  <si>
+    <t>27.04.202686</t>
+  </si>
+  <si>
+    <t>27.04.202687</t>
+  </si>
+  <si>
+    <t>27.04.202688</t>
+  </si>
+  <si>
+    <t>27.04.202689</t>
+  </si>
+  <si>
+    <t>27.04.202690</t>
+  </si>
+  <si>
+    <t>27.04.202691</t>
+  </si>
+  <si>
+    <t>27.04.202692</t>
+  </si>
+  <si>
+    <t>27.04.202693</t>
+  </si>
+  <si>
+    <t>27.04.202694</t>
+  </si>
+  <si>
+    <t>27.04.202695</t>
+  </si>
+  <si>
+    <t>27.04.202696</t>
   </si>
 </sst>
 </file>
@@ -966,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -988,13 +1564,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B2">
-        <v>861.976</v>
+        <v>665.026</v>
       </c>
       <c r="C2">
-        <v>1008</v>
+        <v>139</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1581,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46136.01041666666</v>
       </c>
       <c r="B3">
-        <v>898.958</v>
+        <v>647.7190000000001</v>
       </c>
       <c r="C3">
-        <v>1104</v>
+        <v>148</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1598,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46136.02083333334</v>
       </c>
       <c r="B4">
-        <v>928.774</v>
+        <v>631.566</v>
       </c>
       <c r="C4">
-        <v>1214</v>
+        <v>154</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1615,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46136.03125</v>
       </c>
       <c r="B5">
-        <v>948.021</v>
+        <v>615.604</v>
       </c>
       <c r="C5">
-        <v>1296</v>
+        <v>168</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1632,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46136.04166666666</v>
       </c>
       <c r="B6">
-        <v>1077.874</v>
+        <v>578.424</v>
       </c>
       <c r="C6">
-        <v>1491</v>
+        <v>172</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1649,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46136.05208333334</v>
       </c>
       <c r="B7">
-        <v>1133.461</v>
+        <v>563.504</v>
       </c>
       <c r="C7">
-        <v>1563</v>
+        <v>183</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1666,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46136.0625</v>
       </c>
       <c r="B8">
-        <v>1182.254</v>
+        <v>548.254</v>
       </c>
       <c r="C8">
-        <v>1666</v>
+        <v>195</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1683,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46136.07291666666</v>
       </c>
       <c r="B9">
-        <v>1216.081</v>
+        <v>534.623</v>
       </c>
       <c r="C9">
-        <v>1575</v>
+        <v>230</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1700,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46136.08333333334</v>
       </c>
       <c r="B10">
-        <v>1274.183</v>
+        <v>529.165</v>
       </c>
       <c r="C10">
-        <v>1585</v>
+        <v>259</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1717,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46136.09375</v>
       </c>
       <c r="B11">
-        <v>1324.831</v>
+        <v>516.585</v>
       </c>
       <c r="C11">
-        <v>1602</v>
+        <v>279</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1734,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46136.10416666666</v>
       </c>
       <c r="B12">
-        <v>1348.891</v>
+        <v>507.853</v>
       </c>
       <c r="C12">
-        <v>1627</v>
+        <v>312</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1751,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46136.11458333334</v>
       </c>
       <c r="B13">
-        <v>1376.946</v>
+        <v>495.969</v>
       </c>
       <c r="C13">
-        <v>1545</v>
+        <v>345</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1768,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46136.125</v>
       </c>
       <c r="B14">
-        <v>1404.427</v>
+        <v>504.263</v>
       </c>
       <c r="C14">
-        <v>1575</v>
+        <v>371</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1785,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46136.13541666666</v>
       </c>
       <c r="B15">
-        <v>1414.548</v>
+        <v>492.011</v>
       </c>
       <c r="C15">
-        <v>1541</v>
+        <v>366</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1802,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46136.14583333334</v>
       </c>
       <c r="B16">
-        <v>1430.951</v>
+        <v>480.752</v>
       </c>
       <c r="C16">
-        <v>1573</v>
+        <v>351</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1819,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46136.15625</v>
       </c>
       <c r="B17">
-        <v>1447.523</v>
+        <v>473.638</v>
       </c>
       <c r="C17">
-        <v>1630</v>
+        <v>348</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1836,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46136.16666666666</v>
       </c>
       <c r="B18">
-        <v>1484.44</v>
+        <v>471.748</v>
       </c>
       <c r="C18">
-        <v>1659</v>
+        <v>366</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1853,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46136.17708333334</v>
       </c>
       <c r="B19">
-        <v>1503.468</v>
+        <v>469.261</v>
       </c>
       <c r="C19">
-        <v>1647</v>
+        <v>388</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1870,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46136.1875</v>
       </c>
       <c r="B20">
-        <v>1522.836</v>
+        <v>466.18</v>
       </c>
       <c r="C20">
-        <v>1607</v>
+        <v>412</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1887,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46136.19791666666</v>
       </c>
       <c r="B21">
-        <v>1544.936</v>
+        <v>460.671</v>
       </c>
       <c r="C21">
-        <v>1646</v>
+        <v>431</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1904,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46136.20833333334</v>
       </c>
       <c r="B22">
-        <v>1507.048</v>
+        <v>466.689</v>
       </c>
       <c r="C22">
-        <v>1641</v>
+        <v>433</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1921,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46136.21875</v>
       </c>
       <c r="B23">
-        <v>1529.185</v>
+        <v>466.945</v>
       </c>
       <c r="C23">
-        <v>1618</v>
+        <v>432</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1938,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46136.22916666666</v>
       </c>
       <c r="B24">
-        <v>1547.264</v>
+        <v>466.497</v>
       </c>
       <c r="C24">
-        <v>1641</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1955,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46136.23958333334</v>
       </c>
       <c r="B25">
-        <v>1567.177</v>
+        <v>471.485</v>
       </c>
       <c r="C25">
-        <v>1650</v>
+        <v>428</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1972,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46136.25</v>
       </c>
       <c r="B26">
-        <v>1548.791</v>
+        <v>485.641</v>
       </c>
       <c r="C26">
-        <v>1655</v>
+        <v>445</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1989,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46136.26041666666</v>
       </c>
       <c r="B27">
-        <v>1528.274</v>
+        <v>475.86</v>
       </c>
       <c r="C27">
-        <v>1685</v>
+        <v>449</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +2006,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46136.27083333334</v>
       </c>
       <c r="B28">
-        <v>1514.297</v>
+        <v>469.402</v>
       </c>
       <c r="C28">
-        <v>1629</v>
+        <v>429</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +2023,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46136.28125</v>
       </c>
       <c r="B29">
-        <v>1508.218</v>
+        <v>465.477</v>
       </c>
       <c r="C29">
-        <v>1538</v>
+        <v>427</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +2040,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46136.29166666666</v>
       </c>
       <c r="B30">
-        <v>1450.05</v>
+        <v>469.386</v>
       </c>
       <c r="C30">
-        <v>1499</v>
+        <v>399</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +2057,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46136.30208333334</v>
       </c>
       <c r="B31">
-        <v>1428.46</v>
+        <v>445.8</v>
       </c>
       <c r="C31">
-        <v>1454</v>
+        <v>353</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +2074,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46136.3125</v>
       </c>
       <c r="B32">
-        <v>1402.589</v>
+        <v>431.971</v>
       </c>
       <c r="C32">
-        <v>1379</v>
+        <v>320</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +2091,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46136.32291666666</v>
       </c>
       <c r="B33">
-        <v>1371.67</v>
+        <v>417.947</v>
       </c>
       <c r="C33">
-        <v>1288</v>
+        <v>298</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +2108,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46136.33333333334</v>
       </c>
       <c r="B34">
-        <v>1398.347</v>
+        <v>424.317</v>
       </c>
       <c r="C34">
-        <v>1274</v>
+        <v>305</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +2125,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46136.34375</v>
       </c>
       <c r="B35">
-        <v>1360.717</v>
+        <v>426.389</v>
       </c>
       <c r="C35">
-        <v>1191</v>
+        <v>322</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +2142,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46136.35416666666</v>
       </c>
       <c r="B36">
-        <v>1335.17</v>
+        <v>418.195</v>
       </c>
       <c r="C36">
-        <v>1116</v>
+        <v>354</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +2159,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46136.36458333334</v>
       </c>
       <c r="B37">
-        <v>1296.393</v>
+        <v>417.811</v>
       </c>
       <c r="C37">
-        <v>1055</v>
+        <v>359</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +2176,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46136.375</v>
       </c>
       <c r="B38">
-        <v>1226.429</v>
+        <v>446.498</v>
       </c>
       <c r="C38">
-        <v>984</v>
+        <v>347</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +2193,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="B39">
-        <v>1196.936</v>
+        <v>452.56</v>
       </c>
       <c r="C39">
-        <v>885</v>
+        <v>336</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +2210,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46136.39583333334</v>
       </c>
       <c r="B40">
-        <v>1167.024</v>
+        <v>459.42</v>
       </c>
       <c r="C40">
-        <v>772</v>
+        <v>344</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +2227,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46136.40625</v>
       </c>
       <c r="B41">
-        <v>1137.75</v>
+        <v>466.569</v>
       </c>
       <c r="C41">
-        <v>716</v>
+        <v>336</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +2244,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46136.41666666666</v>
       </c>
       <c r="B42">
-        <v>1080.848</v>
+        <v>483.508</v>
       </c>
       <c r="C42">
-        <v>678</v>
+        <v>312</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +2261,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46136.42708333334</v>
       </c>
       <c r="B43">
-        <v>1055.565</v>
+        <v>492.752</v>
       </c>
       <c r="C43">
-        <v>645</v>
+        <v>288</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +2278,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46133.4375</v>
+        <v>46136.4375</v>
       </c>
       <c r="B44">
-        <v>1028.35</v>
+        <v>501.86</v>
       </c>
       <c r="C44">
-        <v>601</v>
+        <v>257</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +2295,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46133.44791666666</v>
+        <v>46136.44791666666</v>
       </c>
       <c r="B45">
-        <v>992.583</v>
+        <v>460.841</v>
       </c>
       <c r="C45">
-        <v>543</v>
+        <v>233</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +2312,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46133.45833333334</v>
+        <v>46136.45833333334</v>
       </c>
       <c r="B46">
-        <v>962.218</v>
+        <v>542.029</v>
       </c>
       <c r="C46">
-        <v>516</v>
+        <v>250</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +2329,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46133.46875</v>
+        <v>46136.46875</v>
       </c>
       <c r="B47">
-        <v>926.774</v>
+        <v>516.511</v>
       </c>
       <c r="C47">
-        <v>504</v>
+        <v>202</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +2346,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46133.47916666666</v>
+        <v>46136.47916666666</v>
       </c>
       <c r="B48">
-        <v>903.449</v>
+        <v>541.527</v>
       </c>
       <c r="C48">
-        <v>521</v>
+        <v>199</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +2363,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46133.48958333334</v>
+        <v>46136.48958333334</v>
       </c>
       <c r="B49">
-        <v>879.111</v>
+        <v>566.624</v>
       </c>
       <c r="C49">
-        <v>514</v>
+        <v>179</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +2380,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46133.5</v>
+        <v>46136.5</v>
       </c>
       <c r="B50">
-        <v>854.42</v>
+        <v>598.731</v>
       </c>
       <c r="C50">
-        <v>509</v>
+        <v>164</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +2397,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46133.51041666666</v>
+        <v>46136.51041666666</v>
       </c>
       <c r="B51">
-        <v>826.579</v>
+        <v>523.9640000000001</v>
       </c>
       <c r="C51">
-        <v>484</v>
+        <v>177</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +2414,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46133.52083333334</v>
+        <v>46136.52083333334</v>
       </c>
       <c r="B52">
-        <v>795.973</v>
+        <v>538.585</v>
       </c>
       <c r="C52">
-        <v>444</v>
+        <v>208</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +2431,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46133.53125</v>
+        <v>46136.53125</v>
       </c>
       <c r="B53">
-        <v>768.671</v>
+        <v>440.167</v>
       </c>
       <c r="C53">
-        <v>414</v>
+        <v>204</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +2448,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46133.54166666666</v>
+        <v>46136.54166666666</v>
       </c>
       <c r="B54">
-        <v>737.912</v>
+        <v>447.021</v>
       </c>
       <c r="C54">
-        <v>406</v>
+        <v>226</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +2465,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46133.55208333334</v>
+        <v>46136.55208333334</v>
       </c>
       <c r="B55">
-        <v>716.249</v>
+        <v>451.579</v>
       </c>
       <c r="C55">
-        <v>407</v>
+        <v>252</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +2482,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46133.5625</v>
+        <v>46136.5625</v>
       </c>
       <c r="B56">
-        <v>694.509</v>
+        <v>455.338</v>
       </c>
       <c r="C56">
-        <v>384</v>
+        <v>320</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +2499,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46133.57291666666</v>
+        <v>46136.57291666666</v>
       </c>
       <c r="B57">
-        <v>673.726</v>
+        <v>461.401</v>
       </c>
       <c r="C57">
-        <v>358</v>
+        <v>291</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +2516,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46133.58333333334</v>
+        <v>46136.58333333334</v>
       </c>
       <c r="B58">
-        <v>652.4400000000001</v>
+        <v>464.729</v>
       </c>
       <c r="C58">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +2533,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46133.59375</v>
+        <v>46136.59375</v>
       </c>
       <c r="B59">
-        <v>628.48</v>
+        <v>465.924</v>
       </c>
       <c r="C59">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +2550,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46133.60416666666</v>
+        <v>46136.60416666666</v>
       </c>
       <c r="B60">
-        <v>603.484</v>
+        <v>503.601</v>
       </c>
       <c r="C60">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +2567,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46133.61458333334</v>
+        <v>46136.61458333334</v>
       </c>
       <c r="B61">
-        <v>577.245</v>
+        <v>467.234</v>
       </c>
       <c r="C61">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2584,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46133.625</v>
+        <v>46136.625</v>
       </c>
       <c r="B62">
-        <v>479.83</v>
+        <v>456.455</v>
       </c>
       <c r="C62">
-        <v>256</v>
+        <v>298</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2601,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46133.63541666666</v>
+        <v>46136.63541666666</v>
       </c>
       <c r="B63">
-        <v>465.959</v>
+        <v>453.542</v>
       </c>
       <c r="C63">
-        <v>242</v>
+        <v>312</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2618,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46133.64583333334</v>
+        <v>46136.64583333334</v>
       </c>
       <c r="B64">
-        <v>447.618</v>
+        <v>450.577</v>
       </c>
       <c r="C64">
-        <v>247</v>
+        <v>301</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2635,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46133.65625</v>
+        <v>46136.65625</v>
       </c>
       <c r="B65">
-        <v>438.696</v>
+        <v>543.198</v>
       </c>
       <c r="C65">
-        <v>227</v>
+        <v>397</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2652,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46133.66666666666</v>
+        <v>46136.66666666666</v>
       </c>
       <c r="B66">
-        <v>384.676</v>
+        <v>469.206</v>
       </c>
       <c r="C66">
-        <v>199</v>
+        <v>428</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2669,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46133.67708333334</v>
+        <v>46136.67708333334</v>
       </c>
       <c r="B67">
-        <v>380.195</v>
+        <v>460.646</v>
       </c>
       <c r="C67">
-        <v>189</v>
+        <v>435</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2686,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46133.6875</v>
+        <v>46136.6875</v>
       </c>
       <c r="B68">
-        <v>372.484</v>
+        <v>496.325</v>
       </c>
       <c r="C68">
-        <v>162</v>
+        <v>431</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2703,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46133.69791666666</v>
+        <v>46136.69791666666</v>
       </c>
       <c r="B69">
-        <v>368.806</v>
+        <v>486.365</v>
       </c>
       <c r="C69">
-        <v>144</v>
+        <v>421</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2720,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46133.70833333334</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="B70">
-        <v>359.26</v>
+        <v>480.644</v>
       </c>
       <c r="C70">
-        <v>142</v>
+        <v>393</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2737,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46133.71875</v>
+        <v>46136.71875</v>
       </c>
       <c r="B71">
-        <v>344.714</v>
+        <v>504.856</v>
       </c>
       <c r="C71">
-        <v>135</v>
+        <v>426</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2754,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46133.72916666666</v>
+        <v>46136.72916666666</v>
       </c>
       <c r="B72">
-        <v>330.445</v>
+        <v>500.726</v>
       </c>
       <c r="C72">
-        <v>143</v>
+        <v>476</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2771,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46133.73958333334</v>
+        <v>46136.73958333334</v>
       </c>
       <c r="B73">
-        <v>316.297</v>
+        <v>498.086</v>
       </c>
       <c r="C73">
-        <v>123</v>
+        <v>455</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2788,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46133.75</v>
+        <v>46136.75</v>
       </c>
       <c r="B74">
-        <v>289.643</v>
+        <v>496.562</v>
       </c>
       <c r="C74">
-        <v>102</v>
+        <v>431</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2805,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46133.76041666666</v>
+        <v>46136.76041666666</v>
       </c>
       <c r="B75">
-        <v>280.347</v>
+        <v>505.952</v>
       </c>
       <c r="C75">
-        <v>100</v>
+        <v>405</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2822,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46133.77083333334</v>
+        <v>46136.77083333334</v>
       </c>
       <c r="B76">
-        <v>272.872</v>
+        <v>516.424</v>
       </c>
       <c r="C76">
-        <v>88</v>
+        <v>387</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2839,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46133.78125</v>
+        <v>46136.78125</v>
       </c>
       <c r="B77">
-        <v>266.022</v>
+        <v>528.675</v>
       </c>
       <c r="C77">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2856,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46133.79166666666</v>
+        <v>46136.79166666666</v>
       </c>
       <c r="B78">
-        <v>257.366</v>
+        <v>554.681</v>
       </c>
       <c r="C78">
-        <v>62</v>
+        <v>399</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2873,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46133.80208333334</v>
+        <v>46136.80208333334</v>
       </c>
       <c r="B79">
-        <v>257.522</v>
+        <v>569.019</v>
       </c>
       <c r="C79">
-        <v>57</v>
+        <v>442</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2890,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46133.8125</v>
+        <v>46136.8125</v>
       </c>
       <c r="B80">
-        <v>257.86</v>
+        <v>584.817</v>
       </c>
       <c r="C80">
-        <v>66</v>
+        <v>464</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2907,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46133.82291666666</v>
+        <v>46136.82291666666</v>
       </c>
       <c r="B81">
-        <v>282.689</v>
+        <v>606.749</v>
       </c>
       <c r="C81">
-        <v>79</v>
+        <v>530</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2924,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46133.83333333334</v>
+        <v>46136.83333333334</v>
       </c>
       <c r="B82">
-        <v>253.54</v>
+        <v>652.603</v>
       </c>
       <c r="C82">
-        <v>109</v>
+        <v>562</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2941,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46133.84375</v>
+        <v>46136.84375</v>
       </c>
       <c r="B83">
-        <v>250.577</v>
+        <v>664.03</v>
       </c>
       <c r="C83">
-        <v>128</v>
+        <v>584</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2958,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46133.85416666666</v>
+        <v>46136.85416666666</v>
       </c>
       <c r="B84">
-        <v>248.198</v>
+        <v>681.05</v>
       </c>
       <c r="C84">
-        <v>148</v>
+        <v>623</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2975,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46133.86458333334</v>
+        <v>46136.86458333334</v>
       </c>
       <c r="B85">
-        <v>245.698</v>
+        <v>698.918</v>
       </c>
       <c r="C85">
-        <v>165</v>
+        <v>673</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2992,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46133.875</v>
+        <v>46136.875</v>
       </c>
       <c r="B86">
-        <v>241.75</v>
+        <v>726.809</v>
       </c>
       <c r="C86">
-        <v>166</v>
+        <v>777</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +3009,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46133.88541666666</v>
+        <v>46136.88541666666</v>
       </c>
       <c r="B87">
-        <v>241.722</v>
+        <v>740.963</v>
       </c>
       <c r="C87">
-        <v>148</v>
+        <v>828</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +3026,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46133.89583333334</v>
+        <v>46136.89583333334</v>
       </c>
       <c r="B88">
-        <v>242.544</v>
+        <v>753.851</v>
       </c>
       <c r="C88">
-        <v>129</v>
+        <v>809</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +3043,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46133.90625</v>
+        <v>46136.90625</v>
       </c>
       <c r="B89">
-        <v>242.781</v>
+        <v>766.2329999999999</v>
       </c>
       <c r="C89">
-        <v>115</v>
+        <v>785</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +3060,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46133.91666666666</v>
+        <v>46136.91666666666</v>
       </c>
       <c r="B90">
-        <v>244.823</v>
+        <v>778.633</v>
       </c>
       <c r="C90">
-        <v>102</v>
+        <v>839</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +3077,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46133.92708333334</v>
+        <v>46136.92708333334</v>
       </c>
       <c r="B91">
-        <v>244.969</v>
+        <v>784.284</v>
       </c>
       <c r="C91">
-        <v>103</v>
+        <v>927</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +3094,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46133.9375</v>
+        <v>46136.9375</v>
       </c>
       <c r="B92">
-        <v>245.517</v>
+        <v>791.021</v>
       </c>
       <c r="C92">
-        <v>102</v>
+        <v>966</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +3111,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46133.94791666666</v>
+        <v>46136.94791666666</v>
       </c>
       <c r="B93">
-        <v>246.372</v>
+        <v>797.1900000000001</v>
       </c>
       <c r="C93">
-        <v>100</v>
+        <v>1047</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +3128,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46133.95833333334</v>
+        <v>46136.95833333334</v>
       </c>
       <c r="B94">
-        <v>191.294</v>
+        <v>904.681</v>
       </c>
       <c r="C94">
-        <v>103</v>
+        <v>992</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +3145,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46133.96875</v>
+        <v>46136.96875</v>
       </c>
       <c r="B95">
-        <v>187.847</v>
+        <v>887.894</v>
       </c>
       <c r="C95">
-        <v>105</v>
+        <v>978</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +3162,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46133.97916666666</v>
+        <v>46136.97916666666</v>
       </c>
       <c r="B96">
-        <v>191.819</v>
+        <v>879.894</v>
       </c>
       <c r="C96">
-        <v>109</v>
+        <v>957</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +3179,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46133.98958333334</v>
+        <v>46136.98958333334</v>
       </c>
       <c r="B97">
-        <v>191.992</v>
+        <v>874.231</v>
       </c>
       <c r="C97">
-        <v>113</v>
+        <v>928</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +3196,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B98">
-        <v>158.174</v>
+        <v>894.958</v>
       </c>
       <c r="C98">
-        <v>117</v>
+        <v>911</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +3213,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46134.01041666666</v>
+        <v>46137.01041666666</v>
       </c>
       <c r="B99">
-        <v>155.872</v>
+        <v>861.502</v>
       </c>
       <c r="C99">
-        <v>116</v>
+        <v>877</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +3230,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46134.02083333334</v>
+        <v>46137.02083333334</v>
       </c>
       <c r="B100">
-        <v>153.695</v>
+        <v>828.576</v>
       </c>
       <c r="C100">
-        <v>105</v>
+        <v>820</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +3247,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46134.03125</v>
+        <v>46137.03125</v>
       </c>
       <c r="B101">
-        <v>151.473</v>
+        <v>799.489</v>
       </c>
       <c r="C101">
-        <v>93</v>
+        <v>769</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +3264,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46134.04166666666</v>
+        <v>46137.04166666666</v>
       </c>
       <c r="B102">
-        <v>160.64</v>
+        <v>768.277</v>
       </c>
       <c r="C102">
-        <v>81</v>
+        <v>718</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +3281,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46134.05208333334</v>
+        <v>46137.05208333334</v>
       </c>
       <c r="B103">
-        <v>160.307</v>
+        <v>733.153</v>
       </c>
       <c r="C103">
-        <v>73</v>
+        <v>671</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +3298,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46134.0625</v>
+        <v>46137.0625</v>
       </c>
       <c r="B104">
-        <v>159.694</v>
+        <v>701.039</v>
       </c>
       <c r="C104">
-        <v>75</v>
+        <v>639</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +3315,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46134.07291666666</v>
+        <v>46137.07291666666</v>
       </c>
       <c r="B105">
-        <v>164.316</v>
+        <v>664.437</v>
       </c>
       <c r="C105">
-        <v>65</v>
+        <v>609</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +3332,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46134.08333333334</v>
+        <v>46137.08333333334</v>
       </c>
       <c r="B106">
-        <v>151.49</v>
+        <v>632.496</v>
       </c>
       <c r="C106">
-        <v>63</v>
+        <v>575</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +3349,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46134.09375</v>
+        <v>46137.09375</v>
       </c>
       <c r="B107">
-        <v>148.96</v>
+        <v>596.213</v>
       </c>
       <c r="C107">
-        <v>67</v>
+        <v>551</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +3366,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46134.10416666666</v>
+        <v>46137.10416666666</v>
       </c>
       <c r="B108">
-        <v>146.664</v>
+        <v>551.927</v>
       </c>
       <c r="C108">
-        <v>65</v>
+        <v>504</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +3383,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46134.11458333334</v>
+        <v>46137.11458333334</v>
       </c>
       <c r="B109">
-        <v>144.892</v>
+        <v>515.8440000000001</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +3400,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46134.125</v>
+        <v>46137.125</v>
       </c>
       <c r="B110">
-        <v>138.836</v>
+        <v>439.281</v>
       </c>
       <c r="C110">
-        <v>62</v>
+        <v>423</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +3417,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46134.13541666666</v>
+        <v>46137.13541666666</v>
       </c>
       <c r="B111">
-        <v>139.182</v>
+        <v>406.419</v>
       </c>
       <c r="C111">
-        <v>53</v>
+        <v>381</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +3434,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46134.14583333334</v>
+        <v>46137.14583333334</v>
       </c>
       <c r="B112">
-        <v>134.931</v>
+        <v>384.79</v>
       </c>
       <c r="C112">
-        <v>49</v>
+        <v>334</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +3451,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46134.15625</v>
+        <v>46137.15625</v>
       </c>
       <c r="B113">
-        <v>133.371</v>
+        <v>357.211</v>
       </c>
       <c r="C113">
-        <v>57</v>
+        <v>301</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +3468,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46134.16666666666</v>
+        <v>46137.16666666666</v>
       </c>
       <c r="B114">
-        <v>130.362</v>
+        <v>298.728</v>
       </c>
       <c r="C114">
-        <v>79</v>
+        <v>305</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +3485,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46134.17708333334</v>
+        <v>46137.17708333334</v>
       </c>
       <c r="B115">
-        <v>129.74</v>
+        <v>282.631</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +3502,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46134.1875</v>
+        <v>46137.1875</v>
       </c>
       <c r="B116">
-        <v>128.585</v>
+        <v>253.707</v>
       </c>
       <c r="C116">
-        <v>67</v>
+        <v>259</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +3519,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46134.19791666666</v>
+        <v>46137.19791666666</v>
       </c>
       <c r="B117">
-        <v>128.406</v>
+        <v>228.193</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +3536,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46134.20833333334</v>
+        <v>46137.20833333334</v>
       </c>
       <c r="B118">
-        <v>126.483</v>
+        <v>192.296</v>
       </c>
       <c r="C118">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +3553,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46134.21875</v>
+        <v>46137.21875</v>
       </c>
       <c r="B119">
-        <v>130.537</v>
+        <v>176.877</v>
       </c>
       <c r="C119">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +3570,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46134.22916666666</v>
+        <v>46137.22916666666</v>
       </c>
       <c r="B120">
-        <v>127.264</v>
+        <v>163.805</v>
       </c>
       <c r="C120">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3587,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46134.23958333334</v>
+        <v>46137.23958333334</v>
       </c>
       <c r="B121">
-        <v>126.524</v>
+        <v>147.917</v>
       </c>
       <c r="C121">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3604,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46134.25</v>
+        <v>46137.25</v>
       </c>
       <c r="B122">
-        <v>126.459</v>
+        <v>135.523</v>
       </c>
       <c r="C122">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3621,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46134.26041666666</v>
+        <v>46137.26041666666</v>
       </c>
       <c r="B123">
-        <v>124.088</v>
+        <v>137.01</v>
       </c>
       <c r="C123">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3638,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46134.27083333334</v>
+        <v>46137.27083333334</v>
       </c>
       <c r="B124">
-        <v>122.142</v>
+        <v>137.106</v>
       </c>
       <c r="C124">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3655,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46134.28125</v>
+        <v>46137.28125</v>
       </c>
       <c r="B125">
-        <v>122.967</v>
+        <v>137.833</v>
       </c>
       <c r="C125">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3672,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46134.29166666666</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="B126">
-        <v>114.014</v>
+        <v>125.111</v>
       </c>
       <c r="C126">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3689,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46134.30208333334</v>
+        <v>46137.30208333334</v>
       </c>
       <c r="B127">
-        <v>104.521</v>
+        <v>123.434</v>
       </c>
       <c r="C127">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3706,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46134.3125</v>
+        <v>46137.3125</v>
       </c>
       <c r="B128">
-        <v>105.309</v>
+        <v>123.116</v>
       </c>
       <c r="C128">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3723,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46134.32291666666</v>
+        <v>46137.32291666666</v>
       </c>
       <c r="B129">
-        <v>102.014</v>
+        <v>110.638</v>
       </c>
       <c r="C129">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3740,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46134.33333333334</v>
+        <v>46137.33333333334</v>
       </c>
       <c r="B130">
-        <v>101.664</v>
+        <v>101.337</v>
       </c>
       <c r="C130">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,10 +3757,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46134.34375</v>
+        <v>46137.34375</v>
       </c>
       <c r="B131">
-        <v>103.078</v>
+        <v>110.893</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3198,10 +3774,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46134.35416666666</v>
+        <v>46137.35416666666</v>
       </c>
       <c r="B132">
-        <v>106.413</v>
+        <v>113.816</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3215,10 +3791,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46134.36458333334</v>
+        <v>46137.36458333334</v>
       </c>
       <c r="B133">
-        <v>107.525</v>
+        <v>113.22</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3808,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46134.375</v>
+        <v>46137.375</v>
       </c>
       <c r="B134">
-        <v>117.023</v>
+        <v>133.018</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,13 +3825,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46134.38541666666</v>
+        <v>46137.38541666666</v>
       </c>
       <c r="B135">
-        <v>117.767</v>
+        <v>139.85</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3842,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46134.39583333334</v>
+        <v>46137.39583333334</v>
       </c>
       <c r="B136">
-        <v>120.02</v>
+        <v>136.823</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3859,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46134.40625</v>
+        <v>46137.40625</v>
       </c>
       <c r="B137">
-        <v>122.091</v>
+        <v>138.594</v>
       </c>
       <c r="C137">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3876,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46134.41666666666</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="B138">
-        <v>132.836</v>
+        <v>143.699</v>
       </c>
       <c r="C138">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3893,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46134.42708333334</v>
+        <v>46137.42708333334</v>
       </c>
       <c r="B139">
-        <v>136.99</v>
+        <v>154.929</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3910,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46134.4375</v>
+        <v>46137.4375</v>
       </c>
       <c r="B140">
-        <v>142.054</v>
+        <v>164.356</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3927,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46134.44791666666</v>
+        <v>46137.44791666666</v>
       </c>
       <c r="B141">
-        <v>146.909</v>
+        <v>169.318</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3944,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46134.45833333334</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="B142">
-        <v>157.659</v>
+        <v>169.172</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3961,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46134.46875</v>
+        <v>46137.46875</v>
       </c>
       <c r="B143">
-        <v>161.587</v>
+        <v>161.277</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3978,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46134.47916666666</v>
+        <v>46137.47916666666</v>
       </c>
       <c r="B144">
-        <v>166.04</v>
+        <v>173.77</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3995,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46134.48958333334</v>
+        <v>46137.48958333334</v>
       </c>
       <c r="B145">
-        <v>171.034</v>
+        <v>186.886</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +4012,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46134.5</v>
+        <v>46137.5</v>
       </c>
       <c r="B146">
-        <v>177.005</v>
+        <v>209.142</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +4029,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46134.51041666666</v>
+        <v>46137.51041666666</v>
       </c>
       <c r="B147">
-        <v>183.822</v>
+        <v>224.887</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +4046,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46134.52083333334</v>
+        <v>46137.52083333334</v>
       </c>
       <c r="B148">
-        <v>190.732</v>
+        <v>241.566</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,13 +4063,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46134.53125</v>
+        <v>46137.53125</v>
       </c>
       <c r="B149">
-        <v>198.5</v>
+        <v>254.442</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3504,13 +4080,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46134.54166666666</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="B150">
-        <v>207.101</v>
+        <v>258.456</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3521,13 +4097,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46134.55208333334</v>
+        <v>46137.55208333334</v>
       </c>
       <c r="B151">
-        <v>211.85</v>
+        <v>269.765</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3538,13 +4114,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46134.5625</v>
+        <v>46137.5625</v>
       </c>
       <c r="B152">
-        <v>215.998</v>
+        <v>281.351</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3555,13 +4131,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46134.57291666666</v>
+        <v>46137.57291666666</v>
       </c>
       <c r="B153">
-        <v>220.702</v>
+        <v>293.08</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3572,13 +4148,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46134.58333333334</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="B154">
-        <v>209.954</v>
+        <v>310.441</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3589,13 +4165,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46134.59375</v>
+        <v>46137.59375</v>
       </c>
       <c r="B155">
-        <v>212.789</v>
+        <v>324.051</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3606,13 +4182,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46134.60416666666</v>
+        <v>46137.60416666666</v>
       </c>
       <c r="B156">
-        <v>215.351</v>
+        <v>334.96</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3623,13 +4199,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46134.61458333334</v>
+        <v>46137.61458333334</v>
       </c>
       <c r="B157">
-        <v>218.587</v>
+        <v>344.445</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3640,13 +4216,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46134.625</v>
+        <v>46137.625</v>
       </c>
       <c r="B158">
-        <v>216.018</v>
+        <v>354.722</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3657,13 +4233,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46134.63541666666</v>
+        <v>46137.63541666666</v>
       </c>
       <c r="B159">
-        <v>217.418</v>
+        <v>365.8</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3674,13 +4250,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46134.64583333334</v>
+        <v>46137.64583333334</v>
       </c>
       <c r="B160">
-        <v>218.832</v>
+        <v>376.637</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3691,13 +4267,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46134.65625</v>
+        <v>46137.65625</v>
       </c>
       <c r="B161">
-        <v>220.038</v>
+        <v>388.006</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3708,13 +4284,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46134.66666666666</v>
+        <v>46137.66666666666</v>
       </c>
       <c r="B162">
-        <v>202.203</v>
+        <v>420.016</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3725,13 +4301,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46134.67708333334</v>
+        <v>46137.67708333334</v>
       </c>
       <c r="B163">
-        <v>202.076</v>
+        <v>473.213</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3742,13 +4318,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46134.6875</v>
+        <v>46137.6875</v>
       </c>
       <c r="B164">
-        <v>202.339</v>
+        <v>559.336</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3759,13 +4335,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46134.69791666666</v>
+        <v>46137.69791666666</v>
       </c>
       <c r="B165">
-        <v>202.629</v>
+        <v>637.91</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3776,13 +4352,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46134.70833333334</v>
+        <v>46137.70833333334</v>
       </c>
       <c r="B166">
-        <v>204.068</v>
+        <v>562.899</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3793,13 +4369,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46134.71875</v>
+        <v>46137.71875</v>
       </c>
       <c r="B167">
-        <v>201.438</v>
+        <v>586.375</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3810,13 +4386,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46134.72916666666</v>
+        <v>46137.72916666666</v>
       </c>
       <c r="B168">
-        <v>197.952</v>
+        <v>626.359</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3827,13 +4403,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46134.73958333334</v>
+        <v>46137.73958333334</v>
       </c>
       <c r="B169">
-        <v>194.897</v>
+        <v>644.191</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3844,13 +4420,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46134.75</v>
+        <v>46137.75</v>
       </c>
       <c r="B170">
-        <v>186.38</v>
+        <v>685.5410000000001</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3861,13 +4437,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46134.76041666666</v>
+        <v>46137.76041666666</v>
       </c>
       <c r="B171">
-        <v>183.014</v>
+        <v>718.276</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3878,13 +4454,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46134.77083333334</v>
+        <v>46137.77083333334</v>
       </c>
       <c r="B172">
-        <v>182.938</v>
+        <v>756.663</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3895,13 +4471,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46134.78125</v>
+        <v>46137.78125</v>
       </c>
       <c r="B173">
-        <v>180.603</v>
+        <v>791.7430000000001</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3912,13 +4488,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46134.79166666666</v>
+        <v>46137.79166666666</v>
       </c>
       <c r="B174">
-        <v>179.394</v>
+        <v>848.917</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3929,13 +4505,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46134.80208333334</v>
+        <v>46137.80208333334</v>
       </c>
       <c r="B175">
-        <v>178.479</v>
+        <v>881.832</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3946,13 +4522,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46134.8125</v>
+        <v>46137.8125</v>
       </c>
       <c r="B176">
-        <v>177.533</v>
+        <v>913.321</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3963,13 +4539,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46134.82291666666</v>
+        <v>46137.82291666666</v>
       </c>
       <c r="B177">
-        <v>204.031</v>
+        <v>943.285</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3980,13 +4556,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46134.83333333334</v>
+        <v>46137.83333333334</v>
       </c>
       <c r="B178">
-        <v>204.143</v>
+        <v>993.975</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>813</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3997,13 +4573,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46134.84375</v>
+        <v>46137.84375</v>
       </c>
       <c r="B179">
-        <v>183.175</v>
+        <v>993.648</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4014,13 +4590,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46134.85416666666</v>
+        <v>46137.85416666666</v>
       </c>
       <c r="B180">
-        <v>174.296</v>
+        <v>992.079</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4031,13 +4607,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46134.86458333334</v>
+        <v>46137.86458333334</v>
       </c>
       <c r="B181">
-        <v>172.46</v>
+        <v>990.756</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>878</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4048,13 +4624,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46134.875</v>
+        <v>46137.875</v>
       </c>
       <c r="B182">
-        <v>203.364</v>
+        <v>985.55</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4065,13 +4641,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46134.88541666666</v>
+        <v>46137.88541666666</v>
       </c>
       <c r="B183">
-        <v>181.195</v>
+        <v>973.5549999999999</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>944</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4082,13 +4658,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46134.89583333334</v>
+        <v>46137.89583333334</v>
       </c>
       <c r="B184">
-        <v>186.171</v>
+        <v>960.324</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4099,13 +4675,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46134.90625</v>
+        <v>46137.90625</v>
       </c>
       <c r="B185">
-        <v>191.384</v>
+        <v>949.183</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>899</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4116,13 +4692,13 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46134.91666666666</v>
+        <v>46137.91666666666</v>
       </c>
       <c r="B186">
-        <v>193.589</v>
+        <v>926.7809999999999</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4133,13 +4709,13 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46134.92708333334</v>
+        <v>46137.92708333334</v>
       </c>
       <c r="B187">
-        <v>201.694</v>
+        <v>904.496</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4150,13 +4726,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46134.9375</v>
+        <v>46137.9375</v>
       </c>
       <c r="B188">
-        <v>209.729</v>
+        <v>881.772</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>718</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4167,13 +4743,13 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46134.94791666666</v>
+        <v>46137.94791666666</v>
       </c>
       <c r="B189">
-        <v>218.427</v>
+        <v>859.764</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4184,13 +4760,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46134.95833333334</v>
+        <v>46137.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>753.063</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>620</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4201,13 +4777,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46134.96875</v>
+        <v>46137.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>737.824</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4218,13 +4794,13 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46134.97916666666</v>
+        <v>46137.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>722.258</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="D192">
         <v>95</v>
@@ -4235,19 +4811,3283 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46134.98958333334</v>
+        <v>46137.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>701.105</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="D193">
         <v>96</v>
       </c>
       <c r="E193" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B194">
+        <v>679.077</v>
+      </c>
+      <c r="C194">
+        <v>562</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46138.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>679.8920000000001</v>
+      </c>
+      <c r="C195">
+        <v>564</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46138.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>683.215</v>
+      </c>
+      <c r="C196">
+        <v>561</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46138.03125</v>
+      </c>
+      <c r="B197">
+        <v>686.477</v>
+      </c>
+      <c r="C197">
+        <v>556</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46138.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>681.207</v>
+      </c>
+      <c r="C198">
+        <v>574</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46138.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>691.852</v>
+      </c>
+      <c r="C199">
+        <v>564</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46138.0625</v>
+      </c>
+      <c r="B200">
+        <v>703.054</v>
+      </c>
+      <c r="C200">
+        <v>568</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46138.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>704.143</v>
+      </c>
+      <c r="C201">
+        <v>583</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46138.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>738.193</v>
+      </c>
+      <c r="C202">
+        <v>577</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46138.09375</v>
+      </c>
+      <c r="B203">
+        <v>759.51</v>
+      </c>
+      <c r="C203">
+        <v>615</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46138.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>776.71</v>
+      </c>
+      <c r="C204">
+        <v>650</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46138.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>801.628</v>
+      </c>
+      <c r="C205">
+        <v>659</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46138.125</v>
+      </c>
+      <c r="B206">
+        <v>846.979</v>
+      </c>
+      <c r="C206">
+        <v>688</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46138.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>872.068</v>
+      </c>
+      <c r="C207">
+        <v>738</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46138.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>896.723</v>
+      </c>
+      <c r="C208">
+        <v>782</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46138.15625</v>
+      </c>
+      <c r="B209">
+        <v>922.851</v>
+      </c>
+      <c r="C209">
+        <v>835</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46138.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>957.765</v>
+      </c>
+      <c r="C210">
+        <v>897</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46138.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>974.252</v>
+      </c>
+      <c r="C211">
+        <v>976</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46138.1875</v>
+      </c>
+      <c r="B212">
+        <v>997.658</v>
+      </c>
+      <c r="C212">
+        <v>1028</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46138.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>1013.143</v>
+      </c>
+      <c r="C213">
+        <v>1045</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46138.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>1051.839</v>
+      </c>
+      <c r="C214">
+        <v>1047</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46138.21875</v>
+      </c>
+      <c r="B215">
+        <v>1066.182</v>
+      </c>
+      <c r="C215">
+        <v>1042</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46138.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>1077.389</v>
+      </c>
+      <c r="C216">
+        <v>1032</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46138.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>1097.017</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46138.25</v>
+      </c>
+      <c r="B218">
+        <v>1126.35</v>
+      </c>
+      <c r="C218">
+        <v>1083</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46138.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>1137.599</v>
+      </c>
+      <c r="C219">
+        <v>1102</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46138.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>1152.179</v>
+      </c>
+      <c r="C220">
+        <v>1095</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46138.28125</v>
+      </c>
+      <c r="B221">
+        <v>1169.778</v>
+      </c>
+      <c r="C221">
+        <v>1141</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46138.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>1167.542</v>
+      </c>
+      <c r="C222">
+        <v>1129</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46138.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>1158.329</v>
+      </c>
+      <c r="C223">
+        <v>1090</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46138.3125</v>
+      </c>
+      <c r="B224">
+        <v>1145.047</v>
+      </c>
+      <c r="C224">
+        <v>1010</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46138.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>1096.348</v>
+      </c>
+      <c r="C225">
+        <v>903</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46138.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1187.799</v>
+      </c>
+      <c r="C226">
+        <v>827</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46138.34375</v>
+      </c>
+      <c r="B227">
+        <v>1219.093</v>
+      </c>
+      <c r="C227">
+        <v>797</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46138.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1225.523</v>
+      </c>
+      <c r="C228">
+        <v>750</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46138.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1221.876</v>
+      </c>
+      <c r="C229">
+        <v>723</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46138.375</v>
+      </c>
+      <c r="B230">
+        <v>1379.733</v>
+      </c>
+      <c r="C230">
+        <v>797</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46138.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1441.319</v>
+      </c>
+      <c r="C231">
+        <v>937</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46138.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1227.881</v>
+      </c>
+      <c r="C232">
+        <v>1016</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46138.40625</v>
+      </c>
+      <c r="B233">
+        <v>1223.048</v>
+      </c>
+      <c r="C233">
+        <v>1032</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>1241.714</v>
+      </c>
+      <c r="C234">
+        <v>1114</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46138.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>1078.108</v>
+      </c>
+      <c r="C235">
+        <v>1073</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46138.4375</v>
+      </c>
+      <c r="B236">
+        <v>852.902</v>
+      </c>
+      <c r="C236">
+        <v>932</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46138.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>874.325</v>
+      </c>
+      <c r="C237">
+        <v>847</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46138.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>905.0119999999999</v>
+      </c>
+      <c r="C238">
+        <v>812</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46138.46875</v>
+      </c>
+      <c r="B239">
+        <v>919.202</v>
+      </c>
+      <c r="C239">
+        <v>821</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46138.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>931.4160000000001</v>
+      </c>
+      <c r="C240">
+        <v>851</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46138.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>947.217</v>
+      </c>
+      <c r="C241">
+        <v>892</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46138.5</v>
+      </c>
+      <c r="B242">
+        <v>962.061</v>
+      </c>
+      <c r="C242">
+        <v>910</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46138.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>969.905</v>
+      </c>
+      <c r="C243">
+        <v>911</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46138.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>978.307</v>
+      </c>
+      <c r="C244">
+        <v>897</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46138.53125</v>
+      </c>
+      <c r="B245">
+        <v>988.672</v>
+      </c>
+      <c r="C245">
+        <v>817</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46138.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>1003.281</v>
+      </c>
+      <c r="C246">
+        <v>780</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46138.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1000.856</v>
+      </c>
+      <c r="C247">
+        <v>732</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46138.5625</v>
+      </c>
+      <c r="B248">
+        <v>1009.593</v>
+      </c>
+      <c r="C248">
+        <v>709</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46138.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1012.919</v>
+      </c>
+      <c r="C249">
+        <v>646</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46138.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1021.172</v>
+      </c>
+      <c r="C250">
+        <v>565</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46138.59375</v>
+      </c>
+      <c r="B251">
+        <v>1023.028</v>
+      </c>
+      <c r="C251">
+        <v>583</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46138.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>1025.93</v>
+      </c>
+      <c r="C252">
+        <v>594</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46138.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1027.749</v>
+      </c>
+      <c r="C253">
+        <v>604</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46138.625</v>
+      </c>
+      <c r="B254">
+        <v>1029.85</v>
+      </c>
+      <c r="C254">
+        <v>662</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46138.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1035.589</v>
+      </c>
+      <c r="C255">
+        <v>653</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46138.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1036.599</v>
+      </c>
+      <c r="C256">
+        <v>664</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46138.65625</v>
+      </c>
+      <c r="B257">
+        <v>1040.893</v>
+      </c>
+      <c r="C257">
+        <v>883</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46138.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1220.396</v>
+      </c>
+      <c r="C258">
+        <v>1297</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46138.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1042.527</v>
+      </c>
+      <c r="C259">
+        <v>1286</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46138.6875</v>
+      </c>
+      <c r="B260">
+        <v>1559.126</v>
+      </c>
+      <c r="C260">
+        <v>1834</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46138.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>1928.731</v>
+      </c>
+      <c r="C261">
+        <v>2169</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46138.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>1923.238</v>
+      </c>
+      <c r="C262">
+        <v>2121</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46138.71875</v>
+      </c>
+      <c r="B263">
+        <v>1955.798</v>
+      </c>
+      <c r="C263">
+        <v>1916</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46138.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>2207.081</v>
+      </c>
+      <c r="C264">
+        <v>1934</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46138.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>2362.118</v>
+      </c>
+      <c r="C265">
+        <v>2324</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46138.75</v>
+      </c>
+      <c r="B266">
+        <v>2408.725</v>
+      </c>
+      <c r="C266">
+        <v>2439</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46138.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>2450.189</v>
+      </c>
+      <c r="C267">
+        <v>2440</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46138.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>2491.995</v>
+      </c>
+      <c r="C268">
+        <v>2463</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46138.78125</v>
+      </c>
+      <c r="B269">
+        <v>2532.701</v>
+      </c>
+      <c r="C269">
+        <v>2471</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46138.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>2542.035</v>
+      </c>
+      <c r="C270">
+        <v>2499</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46138.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>2533.284</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46138.8125</v>
+      </c>
+      <c r="B272">
+        <v>2521.214</v>
+      </c>
+      <c r="C272">
+        <v>2506</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46138.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>2507.363</v>
+      </c>
+      <c r="C273">
+        <v>2478</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46138.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>2459.435</v>
+      </c>
+      <c r="C274">
+        <v>2414</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46138.84375</v>
+      </c>
+      <c r="B275">
+        <v>2411.843</v>
+      </c>
+      <c r="C275">
+        <v>2318</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46138.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>2364.718</v>
+      </c>
+      <c r="C276">
+        <v>2245</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46138.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>2317.1</v>
+      </c>
+      <c r="C277">
+        <v>2129</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46138.875</v>
+      </c>
+      <c r="B278">
+        <v>2237.605</v>
+      </c>
+      <c r="C278">
+        <v>2001</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46138.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>2172.581</v>
+      </c>
+      <c r="C279">
+        <v>1834</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46138.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>2107.458</v>
+      </c>
+      <c r="C280">
+        <v>1723</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46138.90625</v>
+      </c>
+      <c r="B281">
+        <v>2041.33</v>
+      </c>
+      <c r="C281">
+        <v>1639</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46138.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>1932.647</v>
+      </c>
+      <c r="C282">
+        <v>1496</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46138.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>1848.702</v>
+      </c>
+      <c r="C283">
+        <v>1356</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46138.9375</v>
+      </c>
+      <c r="B284">
+        <v>1763.583</v>
+      </c>
+      <c r="C284">
+        <v>1235</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46138.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>1679.444</v>
+      </c>
+      <c r="C285">
+        <v>1136</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46138.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>1591.089</v>
+      </c>
+      <c r="C286">
+        <v>1078</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46138.96875</v>
+      </c>
+      <c r="B287">
+        <v>1504.473</v>
+      </c>
+      <c r="C287">
+        <v>1055</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46138.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>1414.221</v>
+      </c>
+      <c r="C288">
+        <v>1083</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46138.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>1330.862</v>
+      </c>
+      <c r="C289">
+        <v>1127</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B290">
+        <v>1098.587</v>
+      </c>
+      <c r="C290">
+        <v>1192</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46139.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>1049.537</v>
+      </c>
+      <c r="C291">
+        <v>1173</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46139.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>996.675</v>
+      </c>
+      <c r="C292">
+        <v>1145</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46139.03125</v>
+      </c>
+      <c r="B293">
+        <v>995.662</v>
+      </c>
+      <c r="C293">
+        <v>1095</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46139.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>924.468</v>
+      </c>
+      <c r="C294">
+        <v>1103</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46139.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>913.903</v>
+      </c>
+      <c r="C295">
+        <v>1158</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46139.0625</v>
+      </c>
+      <c r="B296">
+        <v>902.963</v>
+      </c>
+      <c r="C296">
+        <v>1046</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46139.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>874.16</v>
+      </c>
+      <c r="C297">
+        <v>1036</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>838.809</v>
+      </c>
+      <c r="C298">
+        <v>1146</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46139.09375</v>
+      </c>
+      <c r="B299">
+        <v>826.361</v>
+      </c>
+      <c r="C299">
+        <v>1148</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46139.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>812.409</v>
+      </c>
+      <c r="C300">
+        <v>1019</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46139.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>790.47</v>
+      </c>
+      <c r="C301">
+        <v>989</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46139.125</v>
+      </c>
+      <c r="B302">
+        <v>760.476</v>
+      </c>
+      <c r="C302">
+        <v>946</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46139.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>769.836</v>
+      </c>
+      <c r="C303">
+        <v>931</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46139.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>759.821</v>
+      </c>
+      <c r="C304">
+        <v>976</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46139.15625</v>
+      </c>
+      <c r="B305">
+        <v>725.421</v>
+      </c>
+      <c r="C305">
+        <v>909</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46139.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>670.1420000000001</v>
+      </c>
+      <c r="C306">
+        <v>764</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46139.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>649.968</v>
+      </c>
+      <c r="C307">
+        <v>701</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46139.1875</v>
+      </c>
+      <c r="B308">
+        <v>624.922</v>
+      </c>
+      <c r="C308">
+        <v>624</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46139.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>611.199</v>
+      </c>
+      <c r="C309">
+        <v>591</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46139.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>560.783</v>
+      </c>
+      <c r="C310">
+        <v>517</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46139.21875</v>
+      </c>
+      <c r="B311">
+        <v>528.7569999999999</v>
+      </c>
+      <c r="C311">
+        <v>528</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46139.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>500.799</v>
+      </c>
+      <c r="C312">
+        <v>497</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46139.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>466.528</v>
+      </c>
+      <c r="C313">
+        <v>453</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46139.25</v>
+      </c>
+      <c r="B314">
+        <v>385.067</v>
+      </c>
+      <c r="C314">
+        <v>384</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46139.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>364.182</v>
+      </c>
+      <c r="C315">
+        <v>332</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46139.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>351.931</v>
+      </c>
+      <c r="C316">
+        <v>281</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46139.28125</v>
+      </c>
+      <c r="B317">
+        <v>333.269</v>
+      </c>
+      <c r="C317">
+        <v>248</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46139.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>306.711</v>
+      </c>
+      <c r="C318">
+        <v>210</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46139.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>314.599</v>
+      </c>
+      <c r="C319">
+        <v>194</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46139.3125</v>
+      </c>
+      <c r="B320">
+        <v>312.717</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46139.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>302.537</v>
+      </c>
+      <c r="C321">
+        <v>195</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46139.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>329.192</v>
+      </c>
+      <c r="C322">
+        <v>224</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46139.34375</v>
+      </c>
+      <c r="B323">
+        <v>322.348</v>
+      </c>
+      <c r="C323">
+        <v>214</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46139.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>321.427</v>
+      </c>
+      <c r="C324">
+        <v>199</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46139.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>316.179</v>
+      </c>
+      <c r="C325">
+        <v>173</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46139.375</v>
+      </c>
+      <c r="B326">
+        <v>322.345</v>
+      </c>
+      <c r="C326">
+        <v>137</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46139.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>306.786</v>
+      </c>
+      <c r="C327">
+        <v>118</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46139.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>290.984</v>
+      </c>
+      <c r="C328">
+        <v>114</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46139.40625</v>
+      </c>
+      <c r="B329">
+        <v>275.459</v>
+      </c>
+      <c r="C329">
+        <v>116</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46139.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>277.774</v>
+      </c>
+      <c r="C330">
+        <v>117</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46139.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>266.334</v>
+      </c>
+      <c r="C331">
+        <v>111</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46139.4375</v>
+      </c>
+      <c r="B332">
+        <v>255.004</v>
+      </c>
+      <c r="C332">
+        <v>105</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46139.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>244.57</v>
+      </c>
+      <c r="C333">
+        <v>95</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46139.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>199.082</v>
+      </c>
+      <c r="C334">
+        <v>72</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46139.46875</v>
+      </c>
+      <c r="B335">
+        <v>181.206</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46139.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>169.225</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46139.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>164.601</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46139.5</v>
+      </c>
+      <c r="B338">
+        <v>171.219</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46139.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>173</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46139.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>174.979</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46139.53125</v>
+      </c>
+      <c r="B341">
+        <v>176.989</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46139.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>183.538</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46139.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>189.984</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46139.5625</v>
+      </c>
+      <c r="B344">
+        <v>195.538</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46139.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>202.743</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46139.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>218.684</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46139.59375</v>
+      </c>
+      <c r="B347">
+        <v>245.462</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46139.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>271.293</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46139.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>297.991</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46139.625</v>
+      </c>
+      <c r="B350">
+        <v>294.546</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46139.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>324.271</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46139.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>355.158</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46139.65625</v>
+      </c>
+      <c r="B353">
+        <v>408.287</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46139.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>435.06</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46139.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>473.326</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46139.6875</v>
+      </c>
+      <c r="B356">
+        <v>509.229</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46139.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>544.872</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46139.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>549.2140000000001</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46139.71875</v>
+      </c>
+      <c r="B359">
+        <v>590.837</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46139.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>634.539</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46139.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>678.954</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46139.75</v>
+      </c>
+      <c r="B362">
+        <v>751.826</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46139.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>810.625</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46139.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>871.121</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46139.78125</v>
+      </c>
+      <c r="B365">
+        <v>931.152</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46139.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>1014.763</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46139.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>1076.04</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46139.8125</v>
+      </c>
+      <c r="B368">
+        <v>1140.012</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46139.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>1200.132</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46139.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>1271.342</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46139.84375</v>
+      </c>
+      <c r="B371">
+        <v>1292.747</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46139.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>1311.048</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46139.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>1331.301</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46139.875</v>
+      </c>
+      <c r="B374">
+        <v>1345.363</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46139.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>1340.855</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46139.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>1338.817</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46139.90625</v>
+      </c>
+      <c r="B377">
+        <v>1336.875</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46139.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>1321.734</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46139.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>1307.586</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46139.9375</v>
+      </c>
+      <c r="B380">
+        <v>1294</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46139.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>1278.48</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46139.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46139.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46139.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46139.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,1156 +31,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>24.04.20261</t>
-  </si>
-  <si>
-    <t>24.04.20262</t>
-  </si>
-  <si>
-    <t>24.04.20263</t>
-  </si>
-  <si>
-    <t>24.04.20264</t>
-  </si>
-  <si>
-    <t>24.04.20265</t>
-  </si>
-  <si>
-    <t>24.04.20266</t>
-  </si>
-  <si>
-    <t>24.04.20267</t>
-  </si>
-  <si>
-    <t>24.04.20268</t>
-  </si>
-  <si>
-    <t>24.04.20269</t>
-  </si>
-  <si>
-    <t>24.04.202610</t>
-  </si>
-  <si>
-    <t>24.04.202611</t>
-  </si>
-  <si>
-    <t>24.04.202612</t>
-  </si>
-  <si>
-    <t>24.04.202613</t>
-  </si>
-  <si>
-    <t>24.04.202614</t>
-  </si>
-  <si>
-    <t>24.04.202615</t>
-  </si>
-  <si>
-    <t>24.04.202616</t>
-  </si>
-  <si>
-    <t>24.04.202617</t>
-  </si>
-  <si>
-    <t>24.04.202618</t>
-  </si>
-  <si>
-    <t>24.04.202619</t>
-  </si>
-  <si>
-    <t>24.04.202620</t>
-  </si>
-  <si>
-    <t>24.04.202621</t>
-  </si>
-  <si>
-    <t>24.04.202622</t>
-  </si>
-  <si>
-    <t>24.04.202623</t>
-  </si>
-  <si>
-    <t>24.04.202624</t>
-  </si>
-  <si>
-    <t>24.04.202625</t>
-  </si>
-  <si>
-    <t>24.04.202626</t>
-  </si>
-  <si>
-    <t>24.04.202627</t>
-  </si>
-  <si>
-    <t>24.04.202628</t>
-  </si>
-  <si>
-    <t>24.04.202629</t>
-  </si>
-  <si>
-    <t>24.04.202630</t>
-  </si>
-  <si>
-    <t>24.04.202631</t>
-  </si>
-  <si>
-    <t>24.04.202632</t>
-  </si>
-  <si>
-    <t>24.04.202633</t>
-  </si>
-  <si>
-    <t>24.04.202634</t>
-  </si>
-  <si>
-    <t>24.04.202635</t>
-  </si>
-  <si>
-    <t>24.04.202636</t>
-  </si>
-  <si>
-    <t>24.04.202637</t>
-  </si>
-  <si>
-    <t>24.04.202638</t>
-  </si>
-  <si>
-    <t>24.04.202639</t>
-  </si>
-  <si>
-    <t>24.04.202640</t>
-  </si>
-  <si>
-    <t>24.04.202641</t>
-  </si>
-  <si>
-    <t>24.04.202642</t>
-  </si>
-  <si>
-    <t>24.04.202643</t>
-  </si>
-  <si>
-    <t>24.04.202644</t>
-  </si>
-  <si>
-    <t>24.04.202645</t>
-  </si>
-  <si>
-    <t>24.04.202646</t>
-  </si>
-  <si>
-    <t>24.04.202647</t>
-  </si>
-  <si>
-    <t>24.04.202648</t>
-  </si>
-  <si>
-    <t>24.04.202649</t>
-  </si>
-  <si>
-    <t>24.04.202650</t>
-  </si>
-  <si>
-    <t>24.04.202651</t>
-  </si>
-  <si>
-    <t>24.04.202652</t>
-  </si>
-  <si>
-    <t>24.04.202653</t>
-  </si>
-  <si>
-    <t>24.04.202654</t>
-  </si>
-  <si>
-    <t>24.04.202655</t>
-  </si>
-  <si>
-    <t>24.04.202656</t>
-  </si>
-  <si>
-    <t>24.04.202657</t>
-  </si>
-  <si>
-    <t>24.04.202658</t>
-  </si>
-  <si>
-    <t>24.04.202659</t>
-  </si>
-  <si>
-    <t>24.04.202660</t>
-  </si>
-  <si>
-    <t>24.04.202661</t>
-  </si>
-  <si>
-    <t>24.04.202662</t>
-  </si>
-  <si>
-    <t>24.04.202663</t>
-  </si>
-  <si>
-    <t>24.04.202664</t>
-  </si>
-  <si>
-    <t>24.04.202665</t>
-  </si>
-  <si>
-    <t>24.04.202666</t>
-  </si>
-  <si>
-    <t>24.04.202667</t>
-  </si>
-  <si>
-    <t>24.04.202668</t>
-  </si>
-  <si>
-    <t>24.04.202669</t>
-  </si>
-  <si>
-    <t>24.04.202670</t>
-  </si>
-  <si>
-    <t>24.04.202671</t>
-  </si>
-  <si>
-    <t>24.04.202672</t>
-  </si>
-  <si>
-    <t>24.04.202673</t>
-  </si>
-  <si>
-    <t>24.04.202674</t>
-  </si>
-  <si>
-    <t>24.04.202675</t>
-  </si>
-  <si>
-    <t>24.04.202676</t>
-  </si>
-  <si>
-    <t>24.04.202677</t>
-  </si>
-  <si>
-    <t>24.04.202678</t>
-  </si>
-  <si>
-    <t>24.04.202679</t>
-  </si>
-  <si>
-    <t>24.04.202680</t>
-  </si>
-  <si>
-    <t>24.04.202681</t>
-  </si>
-  <si>
-    <t>24.04.202682</t>
-  </si>
-  <si>
-    <t>24.04.202683</t>
-  </si>
-  <si>
-    <t>24.04.202684</t>
-  </si>
-  <si>
-    <t>24.04.202685</t>
-  </si>
-  <si>
-    <t>24.04.202686</t>
-  </si>
-  <si>
-    <t>24.04.202687</t>
-  </si>
-  <si>
-    <t>24.04.202688</t>
-  </si>
-  <si>
-    <t>24.04.202689</t>
-  </si>
-  <si>
-    <t>24.04.202690</t>
-  </si>
-  <si>
-    <t>24.04.202691</t>
-  </si>
-  <si>
-    <t>24.04.202692</t>
-  </si>
-  <si>
-    <t>24.04.202693</t>
-  </si>
-  <si>
-    <t>24.04.202694</t>
-  </si>
-  <si>
-    <t>24.04.202695</t>
-  </si>
-  <si>
-    <t>24.04.202696</t>
-  </si>
-  <si>
-    <t>25.04.20261</t>
-  </si>
-  <si>
-    <t>25.04.20262</t>
-  </si>
-  <si>
-    <t>25.04.20263</t>
-  </si>
-  <si>
-    <t>25.04.20264</t>
-  </si>
-  <si>
-    <t>25.04.20265</t>
-  </si>
-  <si>
-    <t>25.04.20266</t>
-  </si>
-  <si>
-    <t>25.04.20267</t>
-  </si>
-  <si>
-    <t>25.04.20268</t>
-  </si>
-  <si>
-    <t>25.04.20269</t>
-  </si>
-  <si>
-    <t>25.04.202610</t>
-  </si>
-  <si>
-    <t>25.04.202611</t>
-  </si>
-  <si>
-    <t>25.04.202612</t>
-  </si>
-  <si>
-    <t>25.04.202613</t>
-  </si>
-  <si>
-    <t>25.04.202614</t>
-  </si>
-  <si>
-    <t>25.04.202615</t>
-  </si>
-  <si>
-    <t>25.04.202616</t>
-  </si>
-  <si>
-    <t>25.04.202617</t>
-  </si>
-  <si>
-    <t>25.04.202618</t>
-  </si>
-  <si>
-    <t>25.04.202619</t>
-  </si>
-  <si>
-    <t>25.04.202620</t>
-  </si>
-  <si>
-    <t>25.04.202621</t>
-  </si>
-  <si>
-    <t>25.04.202622</t>
-  </si>
-  <si>
-    <t>25.04.202623</t>
-  </si>
-  <si>
-    <t>25.04.202624</t>
-  </si>
-  <si>
-    <t>25.04.202625</t>
-  </si>
-  <si>
-    <t>25.04.202626</t>
-  </si>
-  <si>
-    <t>25.04.202627</t>
-  </si>
-  <si>
-    <t>25.04.202628</t>
-  </si>
-  <si>
-    <t>25.04.202629</t>
-  </si>
-  <si>
-    <t>25.04.202630</t>
-  </si>
-  <si>
-    <t>25.04.202631</t>
-  </si>
-  <si>
-    <t>25.04.202632</t>
-  </si>
-  <si>
-    <t>25.04.202633</t>
-  </si>
-  <si>
-    <t>25.04.202634</t>
-  </si>
-  <si>
-    <t>25.04.202635</t>
-  </si>
-  <si>
-    <t>25.04.202636</t>
-  </si>
-  <si>
-    <t>25.04.202637</t>
-  </si>
-  <si>
-    <t>25.04.202638</t>
-  </si>
-  <si>
-    <t>25.04.202639</t>
-  </si>
-  <si>
-    <t>25.04.202640</t>
-  </si>
-  <si>
-    <t>25.04.202641</t>
-  </si>
-  <si>
-    <t>25.04.202642</t>
-  </si>
-  <si>
-    <t>25.04.202643</t>
-  </si>
-  <si>
-    <t>25.04.202644</t>
-  </si>
-  <si>
-    <t>25.04.202645</t>
-  </si>
-  <si>
-    <t>25.04.202646</t>
-  </si>
-  <si>
-    <t>25.04.202647</t>
-  </si>
-  <si>
-    <t>25.04.202648</t>
-  </si>
-  <si>
-    <t>25.04.202649</t>
-  </si>
-  <si>
-    <t>25.04.202650</t>
-  </si>
-  <si>
-    <t>25.04.202651</t>
-  </si>
-  <si>
-    <t>25.04.202652</t>
-  </si>
-  <si>
-    <t>25.04.202653</t>
-  </si>
-  <si>
-    <t>25.04.202654</t>
-  </si>
-  <si>
-    <t>25.04.202655</t>
-  </si>
-  <si>
-    <t>25.04.202656</t>
-  </si>
-  <si>
-    <t>25.04.202657</t>
-  </si>
-  <si>
-    <t>25.04.202658</t>
-  </si>
-  <si>
-    <t>25.04.202659</t>
-  </si>
-  <si>
-    <t>25.04.202660</t>
-  </si>
-  <si>
-    <t>25.04.202661</t>
-  </si>
-  <si>
-    <t>25.04.202662</t>
-  </si>
-  <si>
-    <t>25.04.202663</t>
-  </si>
-  <si>
-    <t>25.04.202664</t>
-  </si>
-  <si>
-    <t>25.04.202665</t>
-  </si>
-  <si>
-    <t>25.04.202666</t>
-  </si>
-  <si>
-    <t>25.04.202667</t>
-  </si>
-  <si>
-    <t>25.04.202668</t>
-  </si>
-  <si>
-    <t>25.04.202669</t>
-  </si>
-  <si>
-    <t>25.04.202670</t>
-  </si>
-  <si>
-    <t>25.04.202671</t>
-  </si>
-  <si>
-    <t>25.04.202672</t>
-  </si>
-  <si>
-    <t>25.04.202673</t>
-  </si>
-  <si>
-    <t>25.04.202674</t>
-  </si>
-  <si>
-    <t>25.04.202675</t>
-  </si>
-  <si>
-    <t>25.04.202676</t>
-  </si>
-  <si>
-    <t>25.04.202677</t>
-  </si>
-  <si>
-    <t>25.04.202678</t>
-  </si>
-  <si>
-    <t>25.04.202679</t>
-  </si>
-  <si>
-    <t>25.04.202680</t>
-  </si>
-  <si>
-    <t>25.04.202681</t>
-  </si>
-  <si>
-    <t>25.04.202682</t>
-  </si>
-  <si>
-    <t>25.04.202683</t>
-  </si>
-  <si>
-    <t>25.04.202684</t>
-  </si>
-  <si>
-    <t>25.04.202685</t>
-  </si>
-  <si>
-    <t>25.04.202686</t>
-  </si>
-  <si>
-    <t>25.04.202687</t>
-  </si>
-  <si>
-    <t>25.04.202688</t>
-  </si>
-  <si>
-    <t>25.04.202689</t>
-  </si>
-  <si>
-    <t>25.04.202690</t>
-  </si>
-  <si>
-    <t>25.04.202691</t>
-  </si>
-  <si>
-    <t>25.04.202692</t>
-  </si>
-  <si>
-    <t>25.04.202693</t>
-  </si>
-  <si>
-    <t>25.04.202694</t>
-  </si>
-  <si>
-    <t>25.04.202695</t>
-  </si>
-  <si>
-    <t>25.04.202696</t>
-  </si>
-  <si>
-    <t>26.04.20261</t>
-  </si>
-  <si>
-    <t>26.04.20262</t>
-  </si>
-  <si>
-    <t>26.04.20263</t>
-  </si>
-  <si>
-    <t>26.04.20264</t>
-  </si>
-  <si>
-    <t>26.04.20265</t>
-  </si>
-  <si>
-    <t>26.04.20266</t>
-  </si>
-  <si>
-    <t>26.04.20267</t>
-  </si>
-  <si>
-    <t>26.04.20268</t>
-  </si>
-  <si>
-    <t>26.04.20269</t>
-  </si>
-  <si>
-    <t>26.04.202610</t>
-  </si>
-  <si>
-    <t>26.04.202611</t>
-  </si>
-  <si>
-    <t>26.04.202612</t>
-  </si>
-  <si>
-    <t>26.04.202613</t>
-  </si>
-  <si>
-    <t>26.04.202614</t>
-  </si>
-  <si>
-    <t>26.04.202615</t>
-  </si>
-  <si>
-    <t>26.04.202616</t>
-  </si>
-  <si>
-    <t>26.04.202617</t>
-  </si>
-  <si>
-    <t>26.04.202618</t>
-  </si>
-  <si>
-    <t>26.04.202619</t>
-  </si>
-  <si>
-    <t>26.04.202620</t>
-  </si>
-  <si>
-    <t>26.04.202621</t>
-  </si>
-  <si>
-    <t>26.04.202622</t>
-  </si>
-  <si>
-    <t>26.04.202623</t>
-  </si>
-  <si>
-    <t>26.04.202624</t>
-  </si>
-  <si>
-    <t>26.04.202625</t>
-  </si>
-  <si>
-    <t>26.04.202626</t>
-  </si>
-  <si>
-    <t>26.04.202627</t>
-  </si>
-  <si>
-    <t>26.04.202628</t>
-  </si>
-  <si>
-    <t>26.04.202629</t>
-  </si>
-  <si>
-    <t>26.04.202630</t>
-  </si>
-  <si>
-    <t>26.04.202631</t>
-  </si>
-  <si>
-    <t>26.04.202632</t>
-  </si>
-  <si>
-    <t>26.04.202633</t>
-  </si>
-  <si>
-    <t>26.04.202634</t>
-  </si>
-  <si>
-    <t>26.04.202635</t>
-  </si>
-  <si>
-    <t>26.04.202636</t>
-  </si>
-  <si>
-    <t>26.04.202637</t>
-  </si>
-  <si>
-    <t>26.04.202638</t>
-  </si>
-  <si>
-    <t>26.04.202639</t>
-  </si>
-  <si>
-    <t>26.04.202640</t>
-  </si>
-  <si>
-    <t>26.04.202641</t>
-  </si>
-  <si>
-    <t>26.04.202642</t>
-  </si>
-  <si>
-    <t>26.04.202643</t>
-  </si>
-  <si>
-    <t>26.04.202644</t>
-  </si>
-  <si>
-    <t>26.04.202645</t>
-  </si>
-  <si>
-    <t>26.04.202646</t>
-  </si>
-  <si>
-    <t>26.04.202647</t>
-  </si>
-  <si>
-    <t>26.04.202648</t>
-  </si>
-  <si>
-    <t>26.04.202649</t>
-  </si>
-  <si>
-    <t>26.04.202650</t>
-  </si>
-  <si>
-    <t>26.04.202651</t>
-  </si>
-  <si>
-    <t>26.04.202652</t>
-  </si>
-  <si>
-    <t>26.04.202653</t>
-  </si>
-  <si>
-    <t>26.04.202654</t>
-  </si>
-  <si>
-    <t>26.04.202655</t>
-  </si>
-  <si>
-    <t>26.04.202656</t>
-  </si>
-  <si>
-    <t>26.04.202657</t>
-  </si>
-  <si>
-    <t>26.04.202658</t>
-  </si>
-  <si>
-    <t>26.04.202659</t>
-  </si>
-  <si>
-    <t>26.04.202660</t>
-  </si>
-  <si>
-    <t>26.04.202661</t>
-  </si>
-  <si>
-    <t>26.04.202662</t>
-  </si>
-  <si>
-    <t>26.04.202663</t>
-  </si>
-  <si>
-    <t>26.04.202664</t>
-  </si>
-  <si>
-    <t>26.04.202665</t>
-  </si>
-  <si>
-    <t>26.04.202666</t>
-  </si>
-  <si>
-    <t>26.04.202667</t>
-  </si>
-  <si>
-    <t>26.04.202668</t>
-  </si>
-  <si>
-    <t>26.04.202669</t>
-  </si>
-  <si>
-    <t>26.04.202670</t>
-  </si>
-  <si>
-    <t>26.04.202671</t>
-  </si>
-  <si>
-    <t>26.04.202672</t>
-  </si>
-  <si>
-    <t>26.04.202673</t>
-  </si>
-  <si>
-    <t>26.04.202674</t>
-  </si>
-  <si>
-    <t>26.04.202675</t>
-  </si>
-  <si>
-    <t>26.04.202676</t>
-  </si>
-  <si>
-    <t>26.04.202677</t>
-  </si>
-  <si>
-    <t>26.04.202678</t>
-  </si>
-  <si>
-    <t>26.04.202679</t>
-  </si>
-  <si>
-    <t>26.04.202680</t>
-  </si>
-  <si>
-    <t>26.04.202681</t>
-  </si>
-  <si>
-    <t>26.04.202682</t>
-  </si>
-  <si>
-    <t>26.04.202683</t>
-  </si>
-  <si>
-    <t>26.04.202684</t>
-  </si>
-  <si>
-    <t>26.04.202685</t>
-  </si>
-  <si>
-    <t>26.04.202686</t>
-  </si>
-  <si>
-    <t>26.04.202687</t>
-  </si>
-  <si>
-    <t>26.04.202688</t>
-  </si>
-  <si>
-    <t>26.04.202689</t>
-  </si>
-  <si>
-    <t>26.04.202690</t>
-  </si>
-  <si>
-    <t>26.04.202691</t>
-  </si>
-  <si>
-    <t>26.04.202692</t>
-  </si>
-  <si>
-    <t>26.04.202693</t>
-  </si>
-  <si>
-    <t>26.04.202694</t>
-  </si>
-  <si>
-    <t>26.04.202695</t>
-  </si>
-  <si>
-    <t>26.04.202696</t>
-  </si>
-  <si>
-    <t>27.04.20261</t>
-  </si>
-  <si>
-    <t>27.04.20262</t>
-  </si>
-  <si>
-    <t>27.04.20263</t>
-  </si>
-  <si>
-    <t>27.04.20264</t>
-  </si>
-  <si>
-    <t>27.04.20265</t>
-  </si>
-  <si>
-    <t>27.04.20266</t>
-  </si>
-  <si>
-    <t>27.04.20267</t>
-  </si>
-  <si>
-    <t>27.04.20268</t>
-  </si>
-  <si>
-    <t>27.04.20269</t>
-  </si>
-  <si>
-    <t>27.04.202610</t>
-  </si>
-  <si>
-    <t>27.04.202611</t>
-  </si>
-  <si>
-    <t>27.04.202612</t>
-  </si>
-  <si>
-    <t>27.04.202613</t>
-  </si>
-  <si>
-    <t>27.04.202614</t>
-  </si>
-  <si>
-    <t>27.04.202615</t>
-  </si>
-  <si>
-    <t>27.04.202616</t>
-  </si>
-  <si>
-    <t>27.04.202617</t>
-  </si>
-  <si>
-    <t>27.04.202618</t>
-  </si>
-  <si>
-    <t>27.04.202619</t>
-  </si>
-  <si>
-    <t>27.04.202620</t>
-  </si>
-  <si>
-    <t>27.04.202621</t>
-  </si>
-  <si>
-    <t>27.04.202622</t>
-  </si>
-  <si>
-    <t>27.04.202623</t>
-  </si>
-  <si>
-    <t>27.04.202624</t>
-  </si>
-  <si>
-    <t>27.04.202625</t>
-  </si>
-  <si>
-    <t>27.04.202626</t>
-  </si>
-  <si>
-    <t>27.04.202627</t>
-  </si>
-  <si>
-    <t>27.04.202628</t>
-  </si>
-  <si>
-    <t>27.04.202629</t>
-  </si>
-  <si>
-    <t>27.04.202630</t>
-  </si>
-  <si>
-    <t>27.04.202631</t>
-  </si>
-  <si>
-    <t>27.04.202632</t>
-  </si>
-  <si>
-    <t>27.04.202633</t>
-  </si>
-  <si>
-    <t>27.04.202634</t>
-  </si>
-  <si>
-    <t>27.04.202635</t>
-  </si>
-  <si>
-    <t>27.04.202636</t>
-  </si>
-  <si>
-    <t>27.04.202637</t>
-  </si>
-  <si>
-    <t>27.04.202638</t>
-  </si>
-  <si>
-    <t>27.04.202639</t>
-  </si>
-  <si>
-    <t>27.04.202640</t>
-  </si>
-  <si>
-    <t>27.04.202641</t>
-  </si>
-  <si>
-    <t>27.04.202642</t>
-  </si>
-  <si>
-    <t>27.04.202643</t>
-  </si>
-  <si>
-    <t>27.04.202644</t>
-  </si>
-  <si>
-    <t>27.04.202645</t>
-  </si>
-  <si>
-    <t>27.04.202646</t>
-  </si>
-  <si>
-    <t>27.04.202647</t>
-  </si>
-  <si>
-    <t>27.04.202648</t>
-  </si>
-  <si>
-    <t>27.04.202649</t>
-  </si>
-  <si>
-    <t>27.04.202650</t>
-  </si>
-  <si>
-    <t>27.04.202651</t>
-  </si>
-  <si>
-    <t>27.04.202652</t>
-  </si>
-  <si>
-    <t>27.04.202653</t>
-  </si>
-  <si>
-    <t>27.04.202654</t>
-  </si>
-  <si>
-    <t>27.04.202655</t>
-  </si>
-  <si>
-    <t>27.04.202656</t>
-  </si>
-  <si>
-    <t>27.04.202657</t>
-  </si>
-  <si>
-    <t>27.04.202658</t>
-  </si>
-  <si>
-    <t>27.04.202659</t>
-  </si>
-  <si>
-    <t>27.04.202660</t>
-  </si>
-  <si>
-    <t>27.04.202661</t>
-  </si>
-  <si>
-    <t>27.04.202662</t>
-  </si>
-  <si>
-    <t>27.04.202663</t>
-  </si>
-  <si>
-    <t>27.04.202664</t>
-  </si>
-  <si>
-    <t>27.04.202665</t>
-  </si>
-  <si>
-    <t>27.04.202666</t>
-  </si>
-  <si>
-    <t>27.04.202667</t>
-  </si>
-  <si>
-    <t>27.04.202668</t>
-  </si>
-  <si>
-    <t>27.04.202669</t>
-  </si>
-  <si>
-    <t>27.04.202670</t>
-  </si>
-  <si>
-    <t>27.04.202671</t>
-  </si>
-  <si>
-    <t>27.04.202672</t>
-  </si>
-  <si>
-    <t>27.04.202673</t>
-  </si>
-  <si>
-    <t>27.04.202674</t>
-  </si>
-  <si>
-    <t>27.04.202675</t>
-  </si>
-  <si>
-    <t>27.04.202676</t>
-  </si>
-  <si>
-    <t>27.04.202677</t>
-  </si>
-  <si>
-    <t>27.04.202678</t>
-  </si>
-  <si>
-    <t>27.04.202679</t>
-  </si>
-  <si>
-    <t>27.04.202680</t>
-  </si>
-  <si>
-    <t>27.04.202681</t>
-  </si>
-  <si>
-    <t>27.04.202682</t>
-  </si>
-  <si>
-    <t>27.04.202683</t>
-  </si>
-  <si>
-    <t>27.04.202684</t>
-  </si>
-  <si>
-    <t>27.04.202685</t>
-  </si>
-  <si>
-    <t>27.04.202686</t>
-  </si>
-  <si>
-    <t>27.04.202687</t>
-  </si>
-  <si>
-    <t>27.04.202688</t>
-  </si>
-  <si>
-    <t>27.04.202689</t>
-  </si>
-  <si>
-    <t>27.04.202690</t>
-  </si>
-  <si>
-    <t>27.04.202691</t>
-  </si>
-  <si>
-    <t>27.04.202692</t>
-  </si>
-  <si>
-    <t>27.04.202693</t>
-  </si>
-  <si>
-    <t>27.04.202694</t>
-  </si>
-  <si>
-    <t>27.04.202695</t>
-  </si>
-  <si>
-    <t>27.04.202696</t>
+    <t>28.04.20261</t>
+  </si>
+  <si>
+    <t>28.04.20262</t>
+  </si>
+  <si>
+    <t>28.04.20263</t>
+  </si>
+  <si>
+    <t>28.04.20264</t>
+  </si>
+  <si>
+    <t>28.04.20265</t>
+  </si>
+  <si>
+    <t>28.04.20266</t>
+  </si>
+  <si>
+    <t>28.04.20267</t>
+  </si>
+  <si>
+    <t>28.04.20268</t>
+  </si>
+  <si>
+    <t>28.04.20269</t>
+  </si>
+  <si>
+    <t>28.04.202610</t>
+  </si>
+  <si>
+    <t>28.04.202611</t>
+  </si>
+  <si>
+    <t>28.04.202612</t>
+  </si>
+  <si>
+    <t>28.04.202613</t>
+  </si>
+  <si>
+    <t>28.04.202614</t>
+  </si>
+  <si>
+    <t>28.04.202615</t>
+  </si>
+  <si>
+    <t>28.04.202616</t>
+  </si>
+  <si>
+    <t>28.04.202617</t>
+  </si>
+  <si>
+    <t>28.04.202618</t>
+  </si>
+  <si>
+    <t>28.04.202619</t>
+  </si>
+  <si>
+    <t>28.04.202620</t>
+  </si>
+  <si>
+    <t>28.04.202621</t>
+  </si>
+  <si>
+    <t>28.04.202622</t>
+  </si>
+  <si>
+    <t>28.04.202623</t>
+  </si>
+  <si>
+    <t>28.04.202624</t>
+  </si>
+  <si>
+    <t>28.04.202625</t>
+  </si>
+  <si>
+    <t>28.04.202626</t>
+  </si>
+  <si>
+    <t>28.04.202627</t>
+  </si>
+  <si>
+    <t>28.04.202628</t>
+  </si>
+  <si>
+    <t>28.04.202629</t>
+  </si>
+  <si>
+    <t>28.04.202630</t>
+  </si>
+  <si>
+    <t>28.04.202631</t>
+  </si>
+  <si>
+    <t>28.04.202632</t>
+  </si>
+  <si>
+    <t>28.04.202633</t>
+  </si>
+  <si>
+    <t>28.04.202634</t>
+  </si>
+  <si>
+    <t>28.04.202635</t>
+  </si>
+  <si>
+    <t>28.04.202636</t>
+  </si>
+  <si>
+    <t>28.04.202637</t>
+  </si>
+  <si>
+    <t>28.04.202638</t>
+  </si>
+  <si>
+    <t>28.04.202639</t>
+  </si>
+  <si>
+    <t>28.04.202640</t>
+  </si>
+  <si>
+    <t>28.04.202641</t>
+  </si>
+  <si>
+    <t>28.04.202642</t>
+  </si>
+  <si>
+    <t>28.04.202643</t>
+  </si>
+  <si>
+    <t>28.04.202644</t>
+  </si>
+  <si>
+    <t>28.04.202645</t>
+  </si>
+  <si>
+    <t>28.04.202646</t>
+  </si>
+  <si>
+    <t>28.04.202647</t>
+  </si>
+  <si>
+    <t>28.04.202648</t>
+  </si>
+  <si>
+    <t>28.04.202649</t>
+  </si>
+  <si>
+    <t>28.04.202650</t>
+  </si>
+  <si>
+    <t>28.04.202651</t>
+  </si>
+  <si>
+    <t>28.04.202652</t>
+  </si>
+  <si>
+    <t>28.04.202653</t>
+  </si>
+  <si>
+    <t>28.04.202654</t>
+  </si>
+  <si>
+    <t>28.04.202655</t>
+  </si>
+  <si>
+    <t>28.04.202656</t>
+  </si>
+  <si>
+    <t>28.04.202657</t>
+  </si>
+  <si>
+    <t>28.04.202658</t>
+  </si>
+  <si>
+    <t>28.04.202659</t>
+  </si>
+  <si>
+    <t>28.04.202660</t>
+  </si>
+  <si>
+    <t>28.04.202661</t>
+  </si>
+  <si>
+    <t>28.04.202662</t>
+  </si>
+  <si>
+    <t>28.04.202663</t>
+  </si>
+  <si>
+    <t>28.04.202664</t>
+  </si>
+  <si>
+    <t>28.04.202665</t>
+  </si>
+  <si>
+    <t>28.04.202666</t>
+  </si>
+  <si>
+    <t>28.04.202667</t>
+  </si>
+  <si>
+    <t>28.04.202668</t>
+  </si>
+  <si>
+    <t>28.04.202669</t>
+  </si>
+  <si>
+    <t>28.04.202670</t>
+  </si>
+  <si>
+    <t>28.04.202671</t>
+  </si>
+  <si>
+    <t>28.04.202672</t>
+  </si>
+  <si>
+    <t>28.04.202673</t>
+  </si>
+  <si>
+    <t>28.04.202674</t>
+  </si>
+  <si>
+    <t>28.04.202675</t>
+  </si>
+  <si>
+    <t>28.04.202676</t>
+  </si>
+  <si>
+    <t>28.04.202677</t>
+  </si>
+  <si>
+    <t>28.04.202678</t>
+  </si>
+  <si>
+    <t>28.04.202679</t>
+  </si>
+  <si>
+    <t>28.04.202680</t>
+  </si>
+  <si>
+    <t>28.04.202681</t>
+  </si>
+  <si>
+    <t>28.04.202682</t>
+  </si>
+  <si>
+    <t>28.04.202683</t>
+  </si>
+  <si>
+    <t>28.04.202684</t>
+  </si>
+  <si>
+    <t>28.04.202685</t>
+  </si>
+  <si>
+    <t>28.04.202686</t>
+  </si>
+  <si>
+    <t>28.04.202687</t>
+  </si>
+  <si>
+    <t>28.04.202688</t>
+  </si>
+  <si>
+    <t>28.04.202689</t>
+  </si>
+  <si>
+    <t>28.04.202690</t>
+  </si>
+  <si>
+    <t>28.04.202691</t>
+  </si>
+  <si>
+    <t>28.04.202692</t>
+  </si>
+  <si>
+    <t>28.04.202693</t>
+  </si>
+  <si>
+    <t>28.04.202694</t>
+  </si>
+  <si>
+    <t>28.04.202695</t>
+  </si>
+  <si>
+    <t>28.04.202696</t>
+  </si>
+  <si>
+    <t>29.04.20261</t>
+  </si>
+  <si>
+    <t>29.04.20262</t>
+  </si>
+  <si>
+    <t>29.04.20263</t>
+  </si>
+  <si>
+    <t>29.04.20264</t>
+  </si>
+  <si>
+    <t>29.04.20265</t>
+  </si>
+  <si>
+    <t>29.04.20266</t>
+  </si>
+  <si>
+    <t>29.04.20267</t>
+  </si>
+  <si>
+    <t>29.04.20268</t>
+  </si>
+  <si>
+    <t>29.04.20269</t>
+  </si>
+  <si>
+    <t>29.04.202610</t>
+  </si>
+  <si>
+    <t>29.04.202611</t>
+  </si>
+  <si>
+    <t>29.04.202612</t>
+  </si>
+  <si>
+    <t>29.04.202613</t>
+  </si>
+  <si>
+    <t>29.04.202614</t>
+  </si>
+  <si>
+    <t>29.04.202615</t>
+  </si>
+  <si>
+    <t>29.04.202616</t>
+  </si>
+  <si>
+    <t>29.04.202617</t>
+  </si>
+  <si>
+    <t>29.04.202618</t>
+  </si>
+  <si>
+    <t>29.04.202619</t>
+  </si>
+  <si>
+    <t>29.04.202620</t>
+  </si>
+  <si>
+    <t>29.04.202621</t>
+  </si>
+  <si>
+    <t>29.04.202622</t>
+  </si>
+  <si>
+    <t>29.04.202623</t>
+  </si>
+  <si>
+    <t>29.04.202624</t>
+  </si>
+  <si>
+    <t>29.04.202625</t>
+  </si>
+  <si>
+    <t>29.04.202626</t>
+  </si>
+  <si>
+    <t>29.04.202627</t>
+  </si>
+  <si>
+    <t>29.04.202628</t>
+  </si>
+  <si>
+    <t>29.04.202629</t>
+  </si>
+  <si>
+    <t>29.04.202630</t>
+  </si>
+  <si>
+    <t>29.04.202631</t>
+  </si>
+  <si>
+    <t>29.04.202632</t>
+  </si>
+  <si>
+    <t>29.04.202633</t>
+  </si>
+  <si>
+    <t>29.04.202634</t>
+  </si>
+  <si>
+    <t>29.04.202635</t>
+  </si>
+  <si>
+    <t>29.04.202636</t>
+  </si>
+  <si>
+    <t>29.04.202637</t>
+  </si>
+  <si>
+    <t>29.04.202638</t>
+  </si>
+  <si>
+    <t>29.04.202639</t>
+  </si>
+  <si>
+    <t>29.04.202640</t>
+  </si>
+  <si>
+    <t>29.04.202641</t>
+  </si>
+  <si>
+    <t>29.04.202642</t>
+  </si>
+  <si>
+    <t>29.04.202643</t>
+  </si>
+  <si>
+    <t>29.04.202644</t>
+  </si>
+  <si>
+    <t>29.04.202645</t>
+  </si>
+  <si>
+    <t>29.04.202646</t>
+  </si>
+  <si>
+    <t>29.04.202647</t>
+  </si>
+  <si>
+    <t>29.04.202648</t>
+  </si>
+  <si>
+    <t>29.04.202649</t>
+  </si>
+  <si>
+    <t>29.04.202650</t>
+  </si>
+  <si>
+    <t>29.04.202651</t>
+  </si>
+  <si>
+    <t>29.04.202652</t>
+  </si>
+  <si>
+    <t>29.04.202653</t>
+  </si>
+  <si>
+    <t>29.04.202654</t>
+  </si>
+  <si>
+    <t>29.04.202655</t>
+  </si>
+  <si>
+    <t>29.04.202656</t>
+  </si>
+  <si>
+    <t>29.04.202657</t>
+  </si>
+  <si>
+    <t>29.04.202658</t>
+  </si>
+  <si>
+    <t>29.04.202659</t>
+  </si>
+  <si>
+    <t>29.04.202660</t>
+  </si>
+  <si>
+    <t>29.04.202661</t>
+  </si>
+  <si>
+    <t>29.04.202662</t>
+  </si>
+  <si>
+    <t>29.04.202663</t>
+  </si>
+  <si>
+    <t>29.04.202664</t>
+  </si>
+  <si>
+    <t>29.04.202665</t>
+  </si>
+  <si>
+    <t>29.04.202666</t>
+  </si>
+  <si>
+    <t>29.04.202667</t>
+  </si>
+  <si>
+    <t>29.04.202668</t>
+  </si>
+  <si>
+    <t>29.04.202669</t>
+  </si>
+  <si>
+    <t>29.04.202670</t>
+  </si>
+  <si>
+    <t>29.04.202671</t>
+  </si>
+  <si>
+    <t>29.04.202672</t>
+  </si>
+  <si>
+    <t>29.04.202673</t>
+  </si>
+  <si>
+    <t>29.04.202674</t>
+  </si>
+  <si>
+    <t>29.04.202675</t>
+  </si>
+  <si>
+    <t>29.04.202676</t>
+  </si>
+  <si>
+    <t>29.04.202677</t>
+  </si>
+  <si>
+    <t>29.04.202678</t>
+  </si>
+  <si>
+    <t>29.04.202679</t>
+  </si>
+  <si>
+    <t>29.04.202680</t>
+  </si>
+  <si>
+    <t>29.04.202681</t>
+  </si>
+  <si>
+    <t>29.04.202682</t>
+  </si>
+  <si>
+    <t>29.04.202683</t>
+  </si>
+  <si>
+    <t>29.04.202684</t>
+  </si>
+  <si>
+    <t>29.04.202685</t>
+  </si>
+  <si>
+    <t>29.04.202686</t>
+  </si>
+  <si>
+    <t>29.04.202687</t>
+  </si>
+  <si>
+    <t>29.04.202688</t>
+  </si>
+  <si>
+    <t>29.04.202689</t>
+  </si>
+  <si>
+    <t>29.04.202690</t>
+  </si>
+  <si>
+    <t>29.04.202691</t>
+  </si>
+  <si>
+    <t>29.04.202692</t>
+  </si>
+  <si>
+    <t>29.04.202693</t>
+  </si>
+  <si>
+    <t>29.04.202694</t>
+  </si>
+  <si>
+    <t>29.04.202695</t>
+  </si>
+  <si>
+    <t>29.04.202696</t>
+  </si>
+  <si>
+    <t>30.04.20261</t>
+  </si>
+  <si>
+    <t>30.04.20262</t>
+  </si>
+  <si>
+    <t>30.04.20263</t>
+  </si>
+  <si>
+    <t>30.04.20264</t>
+  </si>
+  <si>
+    <t>30.04.20265</t>
+  </si>
+  <si>
+    <t>30.04.20266</t>
+  </si>
+  <si>
+    <t>30.04.20267</t>
+  </si>
+  <si>
+    <t>30.04.20268</t>
+  </si>
+  <si>
+    <t>30.04.20269</t>
+  </si>
+  <si>
+    <t>30.04.202610</t>
+  </si>
+  <si>
+    <t>30.04.202611</t>
+  </si>
+  <si>
+    <t>30.04.202612</t>
+  </si>
+  <si>
+    <t>30.04.202613</t>
+  </si>
+  <si>
+    <t>30.04.202614</t>
+  </si>
+  <si>
+    <t>30.04.202615</t>
+  </si>
+  <si>
+    <t>30.04.202616</t>
+  </si>
+  <si>
+    <t>30.04.202617</t>
+  </si>
+  <si>
+    <t>30.04.202618</t>
+  </si>
+  <si>
+    <t>30.04.202619</t>
+  </si>
+  <si>
+    <t>30.04.202620</t>
+  </si>
+  <si>
+    <t>30.04.202621</t>
+  </si>
+  <si>
+    <t>30.04.202622</t>
+  </si>
+  <si>
+    <t>30.04.202623</t>
+  </si>
+  <si>
+    <t>30.04.202624</t>
+  </si>
+  <si>
+    <t>30.04.202625</t>
+  </si>
+  <si>
+    <t>30.04.202626</t>
+  </si>
+  <si>
+    <t>30.04.202627</t>
+  </si>
+  <si>
+    <t>30.04.202628</t>
+  </si>
+  <si>
+    <t>30.04.202629</t>
+  </si>
+  <si>
+    <t>30.04.202630</t>
+  </si>
+  <si>
+    <t>30.04.202631</t>
+  </si>
+  <si>
+    <t>30.04.202632</t>
+  </si>
+  <si>
+    <t>30.04.202633</t>
+  </si>
+  <si>
+    <t>30.04.202634</t>
+  </si>
+  <si>
+    <t>30.04.202635</t>
+  </si>
+  <si>
+    <t>30.04.202636</t>
+  </si>
+  <si>
+    <t>30.04.202637</t>
+  </si>
+  <si>
+    <t>30.04.202638</t>
+  </si>
+  <si>
+    <t>30.04.202639</t>
+  </si>
+  <si>
+    <t>30.04.202640</t>
+  </si>
+  <si>
+    <t>30.04.202641</t>
+  </si>
+  <si>
+    <t>30.04.202642</t>
+  </si>
+  <si>
+    <t>30.04.202643</t>
+  </si>
+  <si>
+    <t>30.04.202644</t>
+  </si>
+  <si>
+    <t>30.04.202645</t>
+  </si>
+  <si>
+    <t>30.04.202646</t>
+  </si>
+  <si>
+    <t>30.04.202647</t>
+  </si>
+  <si>
+    <t>30.04.202648</t>
+  </si>
+  <si>
+    <t>30.04.202649</t>
+  </si>
+  <si>
+    <t>30.04.202650</t>
+  </si>
+  <si>
+    <t>30.04.202651</t>
+  </si>
+  <si>
+    <t>30.04.202652</t>
+  </si>
+  <si>
+    <t>30.04.202653</t>
+  </si>
+  <si>
+    <t>30.04.202654</t>
+  </si>
+  <si>
+    <t>30.04.202655</t>
+  </si>
+  <si>
+    <t>30.04.202656</t>
+  </si>
+  <si>
+    <t>30.04.202657</t>
+  </si>
+  <si>
+    <t>30.04.202658</t>
+  </si>
+  <si>
+    <t>30.04.202659</t>
+  </si>
+  <si>
+    <t>30.04.202660</t>
+  </si>
+  <si>
+    <t>30.04.202661</t>
+  </si>
+  <si>
+    <t>30.04.202662</t>
+  </si>
+  <si>
+    <t>30.04.202663</t>
+  </si>
+  <si>
+    <t>30.04.202664</t>
+  </si>
+  <si>
+    <t>30.04.202665</t>
+  </si>
+  <si>
+    <t>30.04.202666</t>
+  </si>
+  <si>
+    <t>30.04.202667</t>
+  </si>
+  <si>
+    <t>30.04.202668</t>
+  </si>
+  <si>
+    <t>30.04.202669</t>
+  </si>
+  <si>
+    <t>30.04.202670</t>
+  </si>
+  <si>
+    <t>30.04.202671</t>
+  </si>
+  <si>
+    <t>30.04.202672</t>
+  </si>
+  <si>
+    <t>30.04.202673</t>
+  </si>
+  <si>
+    <t>30.04.202674</t>
+  </si>
+  <si>
+    <t>30.04.202675</t>
+  </si>
+  <si>
+    <t>30.04.202676</t>
+  </si>
+  <si>
+    <t>30.04.202677</t>
+  </si>
+  <si>
+    <t>30.04.202678</t>
+  </si>
+  <si>
+    <t>30.04.202679</t>
+  </si>
+  <si>
+    <t>30.04.202680</t>
+  </si>
+  <si>
+    <t>30.04.202681</t>
+  </si>
+  <si>
+    <t>30.04.202682</t>
+  </si>
+  <si>
+    <t>30.04.202683</t>
+  </si>
+  <si>
+    <t>30.04.202684</t>
+  </si>
+  <si>
+    <t>30.04.202685</t>
+  </si>
+  <si>
+    <t>30.04.202686</t>
+  </si>
+  <si>
+    <t>30.04.202687</t>
+  </si>
+  <si>
+    <t>30.04.202688</t>
+  </si>
+  <si>
+    <t>30.04.202689</t>
+  </si>
+  <si>
+    <t>30.04.202690</t>
+  </si>
+  <si>
+    <t>30.04.202691</t>
+  </si>
+  <si>
+    <t>30.04.202692</t>
+  </si>
+  <si>
+    <t>30.04.202693</t>
+  </si>
+  <si>
+    <t>30.04.202694</t>
+  </si>
+  <si>
+    <t>30.04.202695</t>
+  </si>
+  <si>
+    <t>30.04.202696</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E385"/>
+  <dimension ref="A1:E289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1564,13 +1276,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B2">
-        <v>665.026</v>
+        <v>1270.767</v>
       </c>
       <c r="C2">
-        <v>139</v>
+        <v>1494</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1581,13 +1293,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46136.01041666666</v>
+        <v>46140.01041666666</v>
       </c>
       <c r="B3">
-        <v>647.7190000000001</v>
+        <v>1252.175</v>
       </c>
       <c r="C3">
-        <v>148</v>
+        <v>1475</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1598,13 +1310,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46136.02083333334</v>
+        <v>46140.02083333334</v>
       </c>
       <c r="B4">
-        <v>631.566</v>
+        <v>1243.357</v>
       </c>
       <c r="C4">
-        <v>154</v>
+        <v>1376</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1615,13 +1327,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46136.03125</v>
+        <v>46140.03125</v>
       </c>
       <c r="B5">
-        <v>615.604</v>
+        <v>1219.203</v>
       </c>
       <c r="C5">
-        <v>168</v>
+        <v>1393</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1632,13 +1344,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46136.04166666666</v>
+        <v>46140.04166666666</v>
       </c>
       <c r="B6">
-        <v>578.424</v>
+        <v>1184.954</v>
       </c>
       <c r="C6">
-        <v>172</v>
+        <v>1360</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1649,13 +1361,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46136.05208333334</v>
+        <v>46140.05208333334</v>
       </c>
       <c r="B7">
-        <v>563.504</v>
+        <v>1156.669</v>
       </c>
       <c r="C7">
-        <v>183</v>
+        <v>1329</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1666,13 +1378,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46136.0625</v>
+        <v>46140.0625</v>
       </c>
       <c r="B8">
-        <v>548.254</v>
+        <v>1133.874</v>
       </c>
       <c r="C8">
-        <v>195</v>
+        <v>1342</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1683,13 +1395,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46136.07291666666</v>
+        <v>46140.07291666666</v>
       </c>
       <c r="B9">
-        <v>534.623</v>
+        <v>1094.568</v>
       </c>
       <c r="C9">
-        <v>230</v>
+        <v>1320</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1700,13 +1412,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46136.08333333334</v>
+        <v>46140.08333333334</v>
       </c>
       <c r="B10">
-        <v>529.165</v>
+        <v>1032.122</v>
       </c>
       <c r="C10">
-        <v>259</v>
+        <v>1302</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1717,13 +1429,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46136.09375</v>
+        <v>46140.09375</v>
       </c>
       <c r="B11">
-        <v>516.585</v>
+        <v>1014.116</v>
       </c>
       <c r="C11">
-        <v>279</v>
+        <v>1277</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1734,13 +1446,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46136.10416666666</v>
+        <v>46140.10416666666</v>
       </c>
       <c r="B12">
-        <v>507.853</v>
+        <v>1007.059</v>
       </c>
       <c r="C12">
-        <v>312</v>
+        <v>1222</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1751,13 +1463,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46136.11458333334</v>
+        <v>46140.11458333334</v>
       </c>
       <c r="B13">
-        <v>495.969</v>
+        <v>974.268</v>
       </c>
       <c r="C13">
-        <v>345</v>
+        <v>1178</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1768,13 +1480,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46136.125</v>
+        <v>46140.125</v>
       </c>
       <c r="B14">
-        <v>504.263</v>
+        <v>968.976</v>
       </c>
       <c r="C14">
-        <v>371</v>
+        <v>1137</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1785,13 +1497,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46136.13541666666</v>
+        <v>46140.13541666666</v>
       </c>
       <c r="B15">
-        <v>492.011</v>
+        <v>941.582</v>
       </c>
       <c r="C15">
-        <v>366</v>
+        <v>1089</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1802,13 +1514,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46136.14583333334</v>
+        <v>46140.14583333334</v>
       </c>
       <c r="B16">
-        <v>480.752</v>
+        <v>920.5549999999999</v>
       </c>
       <c r="C16">
-        <v>351</v>
+        <v>1036</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1819,13 +1531,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46136.15625</v>
+        <v>46140.15625</v>
       </c>
       <c r="B17">
-        <v>473.638</v>
+        <v>897.37</v>
       </c>
       <c r="C17">
-        <v>348</v>
+        <v>988</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1836,13 +1548,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46136.16666666666</v>
+        <v>46140.16666666666</v>
       </c>
       <c r="B18">
-        <v>471.748</v>
+        <v>876.832</v>
       </c>
       <c r="C18">
-        <v>366</v>
+        <v>974</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1853,13 +1565,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46136.17708333334</v>
+        <v>46140.17708333334</v>
       </c>
       <c r="B19">
-        <v>469.261</v>
+        <v>844.365</v>
       </c>
       <c r="C19">
-        <v>388</v>
+        <v>940</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1870,13 +1582,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46136.1875</v>
+        <v>46140.1875</v>
       </c>
       <c r="B20">
-        <v>466.18</v>
+        <v>807.5650000000001</v>
       </c>
       <c r="C20">
-        <v>412</v>
+        <v>883</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1887,13 +1599,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46136.19791666666</v>
+        <v>46140.19791666666</v>
       </c>
       <c r="B21">
-        <v>460.671</v>
+        <v>780.474</v>
       </c>
       <c r="C21">
-        <v>431</v>
+        <v>848</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1904,13 +1616,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46136.20833333334</v>
+        <v>46140.20833333334</v>
       </c>
       <c r="B22">
-        <v>466.689</v>
+        <v>757.066</v>
       </c>
       <c r="C22">
-        <v>433</v>
+        <v>827</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1921,13 +1633,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46136.21875</v>
+        <v>46140.21875</v>
       </c>
       <c r="B23">
-        <v>466.945</v>
+        <v>720.212</v>
       </c>
       <c r="C23">
-        <v>432</v>
+        <v>814</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1938,13 +1650,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46136.22916666666</v>
+        <v>46140.22916666666</v>
       </c>
       <c r="B24">
-        <v>466.497</v>
+        <v>690.349</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>807</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1955,13 +1667,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46136.23958333334</v>
+        <v>46140.23958333334</v>
       </c>
       <c r="B25">
-        <v>471.485</v>
+        <v>658.62</v>
       </c>
       <c r="C25">
-        <v>428</v>
+        <v>798</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1972,13 +1684,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46136.25</v>
+        <v>46140.25</v>
       </c>
       <c r="B26">
-        <v>485.641</v>
+        <v>626.619</v>
       </c>
       <c r="C26">
-        <v>445</v>
+        <v>771</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1989,13 +1701,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46136.26041666666</v>
+        <v>46140.26041666666</v>
       </c>
       <c r="B27">
-        <v>475.86</v>
+        <v>592.035</v>
       </c>
       <c r="C27">
-        <v>449</v>
+        <v>740</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -2006,13 +1718,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46136.27083333334</v>
+        <v>46140.27083333334</v>
       </c>
       <c r="B28">
-        <v>469.402</v>
+        <v>560.535</v>
       </c>
       <c r="C28">
-        <v>429</v>
+        <v>695</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -2023,13 +1735,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46136.28125</v>
+        <v>46140.28125</v>
       </c>
       <c r="B29">
-        <v>465.477</v>
+        <v>537.501</v>
       </c>
       <c r="C29">
-        <v>427</v>
+        <v>631</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -2040,13 +1752,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46136.29166666666</v>
+        <v>46140.29166666666</v>
       </c>
       <c r="B30">
-        <v>469.386</v>
+        <v>511.299</v>
       </c>
       <c r="C30">
-        <v>399</v>
+        <v>542</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -2057,13 +1769,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46136.30208333334</v>
+        <v>46140.30208333334</v>
       </c>
       <c r="B31">
-        <v>445.8</v>
+        <v>472.693</v>
       </c>
       <c r="C31">
-        <v>353</v>
+        <v>457</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -2074,13 +1786,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46136.3125</v>
+        <v>46140.3125</v>
       </c>
       <c r="B32">
-        <v>431.971</v>
+        <v>437.198</v>
       </c>
       <c r="C32">
-        <v>320</v>
+        <v>406</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -2091,13 +1803,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46136.32291666666</v>
+        <v>46140.32291666666</v>
       </c>
       <c r="B33">
-        <v>417.947</v>
+        <v>403.051</v>
       </c>
       <c r="C33">
-        <v>298</v>
+        <v>392</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -2108,13 +1820,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46136.33333333334</v>
+        <v>46140.33333333334</v>
       </c>
       <c r="B34">
-        <v>424.317</v>
+        <v>420.481</v>
       </c>
       <c r="C34">
-        <v>305</v>
+        <v>370</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -2125,13 +1837,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46136.34375</v>
+        <v>46140.34375</v>
       </c>
       <c r="B35">
-        <v>426.389</v>
+        <v>425.709</v>
       </c>
       <c r="C35">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -2142,13 +1854,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46136.35416666666</v>
+        <v>46140.35416666666</v>
       </c>
       <c r="B36">
-        <v>418.195</v>
+        <v>432.047</v>
       </c>
       <c r="C36">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -2159,13 +1871,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46136.36458333334</v>
+        <v>46140.36458333334</v>
       </c>
       <c r="B37">
-        <v>417.811</v>
+        <v>438.316</v>
       </c>
       <c r="C37">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -2176,13 +1888,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46136.375</v>
+        <v>46140.375</v>
       </c>
       <c r="B38">
-        <v>446.498</v>
+        <v>444.116</v>
       </c>
       <c r="C38">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -2193,13 +1905,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46136.38541666666</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="B39">
-        <v>452.56</v>
+        <v>462.96</v>
       </c>
       <c r="C39">
-        <v>336</v>
+        <v>378</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -2210,13 +1922,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46136.39583333334</v>
+        <v>46140.39583333334</v>
       </c>
       <c r="B40">
-        <v>459.42</v>
+        <v>480.088</v>
       </c>
       <c r="C40">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -2227,13 +1939,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46136.40625</v>
+        <v>46140.40625</v>
       </c>
       <c r="B41">
-        <v>466.569</v>
+        <v>473.522</v>
       </c>
       <c r="C41">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -2244,13 +1956,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46136.41666666666</v>
+        <v>46140.41666666666</v>
       </c>
       <c r="B42">
-        <v>483.508</v>
+        <v>484.77</v>
       </c>
       <c r="C42">
-        <v>312</v>
+        <v>381</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -2261,13 +1973,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46136.42708333334</v>
+        <v>46140.42708333334</v>
       </c>
       <c r="B43">
-        <v>492.752</v>
+        <v>495.258</v>
       </c>
       <c r="C43">
-        <v>288</v>
+        <v>372</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -2278,13 +1990,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46136.4375</v>
+        <v>46140.4375</v>
       </c>
       <c r="B44">
-        <v>501.86</v>
+        <v>504.924</v>
       </c>
       <c r="C44">
-        <v>257</v>
+        <v>345</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -2295,13 +2007,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46136.44791666666</v>
+        <v>46140.44791666666</v>
       </c>
       <c r="B45">
-        <v>460.841</v>
+        <v>488.467</v>
       </c>
       <c r="C45">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2312,13 +2024,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46136.45833333334</v>
+        <v>46140.45833333334</v>
       </c>
       <c r="B46">
-        <v>542.029</v>
+        <v>525.664</v>
       </c>
       <c r="C46">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2329,13 +2041,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46136.46875</v>
+        <v>46140.46875</v>
       </c>
       <c r="B47">
-        <v>516.511</v>
+        <v>540.508</v>
       </c>
       <c r="C47">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2346,13 +2058,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46136.47916666666</v>
+        <v>46140.47916666666</v>
       </c>
       <c r="B48">
-        <v>541.527</v>
+        <v>555.289</v>
       </c>
       <c r="C48">
-        <v>199</v>
+        <v>316</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2363,13 +2075,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46136.48958333334</v>
+        <v>46140.48958333334</v>
       </c>
       <c r="B49">
-        <v>566.624</v>
+        <v>569.922</v>
       </c>
       <c r="C49">
-        <v>179</v>
+        <v>325</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2380,13 +2092,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46136.5</v>
+        <v>46140.5</v>
       </c>
       <c r="B50">
-        <v>598.731</v>
+        <v>595.285</v>
       </c>
       <c r="C50">
-        <v>164</v>
+        <v>332</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2397,13 +2109,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46136.51041666666</v>
+        <v>46140.51041666666</v>
       </c>
       <c r="B51">
-        <v>523.9640000000001</v>
+        <v>608.415</v>
       </c>
       <c r="C51">
-        <v>177</v>
+        <v>350</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2414,13 +2126,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46136.52083333334</v>
+        <v>46140.52083333334</v>
       </c>
       <c r="B52">
-        <v>538.585</v>
+        <v>620.948</v>
       </c>
       <c r="C52">
-        <v>208</v>
+        <v>348</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2431,13 +2143,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46136.53125</v>
+        <v>46140.53125</v>
       </c>
       <c r="B53">
-        <v>440.167</v>
+        <v>634.0940000000001</v>
       </c>
       <c r="C53">
-        <v>204</v>
+        <v>329</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2448,13 +2160,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46136.54166666666</v>
+        <v>46140.54166666666</v>
       </c>
       <c r="B54">
-        <v>447.021</v>
+        <v>642.139</v>
       </c>
       <c r="C54">
-        <v>226</v>
+        <v>336</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2465,13 +2177,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46136.55208333334</v>
+        <v>46140.55208333334</v>
       </c>
       <c r="B55">
-        <v>451.579</v>
+        <v>648.282</v>
       </c>
       <c r="C55">
-        <v>252</v>
+        <v>358</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2482,13 +2194,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46136.5625</v>
+        <v>46140.5625</v>
       </c>
       <c r="B56">
-        <v>455.338</v>
+        <v>653.936</v>
       </c>
       <c r="C56">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2499,13 +2211,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46136.57291666666</v>
+        <v>46140.57291666666</v>
       </c>
       <c r="B57">
-        <v>461.401</v>
+        <v>672.5069999999999</v>
       </c>
       <c r="C57">
-        <v>291</v>
+        <v>392</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2516,13 +2228,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46136.58333333334</v>
+        <v>46140.58333333334</v>
       </c>
       <c r="B58">
-        <v>464.729</v>
+        <v>672.6609999999999</v>
       </c>
       <c r="C58">
-        <v>309</v>
+        <v>425</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2533,13 +2245,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46136.59375</v>
+        <v>46140.59375</v>
       </c>
       <c r="B59">
-        <v>465.924</v>
+        <v>692.461</v>
       </c>
       <c r="C59">
-        <v>296</v>
+        <v>440</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2550,13 +2262,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46136.60416666666</v>
+        <v>46140.60416666666</v>
       </c>
       <c r="B60">
-        <v>503.601</v>
+        <v>711.9589999999999</v>
       </c>
       <c r="C60">
-        <v>297</v>
+        <v>459</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2567,13 +2279,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46136.61458333334</v>
+        <v>46140.61458333334</v>
       </c>
       <c r="B61">
-        <v>467.234</v>
+        <v>731.011</v>
       </c>
       <c r="C61">
-        <v>276</v>
+        <v>467</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2584,13 +2296,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46136.625</v>
+        <v>46140.625</v>
       </c>
       <c r="B62">
-        <v>456.455</v>
+        <v>756.898</v>
       </c>
       <c r="C62">
-        <v>298</v>
+        <v>489</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2601,13 +2313,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46136.63541666666</v>
+        <v>46140.63541666666</v>
       </c>
       <c r="B63">
-        <v>453.542</v>
+        <v>783.296</v>
       </c>
       <c r="C63">
-        <v>312</v>
+        <v>537</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2618,13 +2330,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46136.64583333334</v>
+        <v>46140.64583333334</v>
       </c>
       <c r="B64">
-        <v>450.577</v>
+        <v>810.365</v>
       </c>
       <c r="C64">
-        <v>301</v>
+        <v>579</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2635,13 +2347,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46136.65625</v>
+        <v>46140.65625</v>
       </c>
       <c r="B65">
-        <v>543.198</v>
+        <v>837.025</v>
       </c>
       <c r="C65">
-        <v>397</v>
+        <v>629</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2652,13 +2364,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46136.66666666666</v>
+        <v>46140.66666666666</v>
       </c>
       <c r="B66">
-        <v>469.206</v>
+        <v>858.855</v>
       </c>
       <c r="C66">
-        <v>428</v>
+        <v>671</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2669,13 +2381,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46136.67708333334</v>
+        <v>46140.67708333334</v>
       </c>
       <c r="B67">
-        <v>460.646</v>
+        <v>894.855</v>
       </c>
       <c r="C67">
-        <v>435</v>
+        <v>749</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2686,13 +2398,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46136.6875</v>
+        <v>46140.6875</v>
       </c>
       <c r="B68">
-        <v>496.325</v>
+        <v>962.076</v>
       </c>
       <c r="C68">
-        <v>431</v>
+        <v>821</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2703,13 +2415,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46136.69791666666</v>
+        <v>46140.69791666666</v>
       </c>
       <c r="B69">
-        <v>486.365</v>
+        <v>998.465</v>
       </c>
       <c r="C69">
-        <v>421</v>
+        <v>875</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2720,13 +2432,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46136.70833333334</v>
+        <v>46140.70833333334</v>
       </c>
       <c r="B70">
-        <v>480.644</v>
+        <v>933.609</v>
       </c>
       <c r="C70">
-        <v>393</v>
+        <v>885</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2737,13 +2449,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46136.71875</v>
+        <v>46140.71875</v>
       </c>
       <c r="B71">
-        <v>504.856</v>
+        <v>954.96</v>
       </c>
       <c r="C71">
-        <v>426</v>
+        <v>870</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2754,13 +2466,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46136.72916666666</v>
+        <v>46140.72916666666</v>
       </c>
       <c r="B72">
-        <v>500.726</v>
+        <v>977.203</v>
       </c>
       <c r="C72">
-        <v>476</v>
+        <v>875</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2771,13 +2483,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46136.73958333334</v>
+        <v>46140.73958333334</v>
       </c>
       <c r="B73">
-        <v>498.086</v>
+        <v>1003.257</v>
       </c>
       <c r="C73">
-        <v>455</v>
+        <v>898</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2788,13 +2500,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46136.75</v>
+        <v>46140.75</v>
       </c>
       <c r="B74">
-        <v>496.562</v>
+        <v>997.271</v>
       </c>
       <c r="C74">
-        <v>431</v>
+        <v>923</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2805,13 +2517,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46136.76041666666</v>
+        <v>46140.76041666666</v>
       </c>
       <c r="B75">
-        <v>505.952</v>
+        <v>997.668</v>
       </c>
       <c r="C75">
-        <v>405</v>
+        <v>941</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2822,13 +2534,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46136.77083333334</v>
+        <v>46140.77083333334</v>
       </c>
       <c r="B76">
-        <v>516.424</v>
+        <v>998.407</v>
       </c>
       <c r="C76">
-        <v>387</v>
+        <v>942</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2839,13 +2551,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46136.78125</v>
+        <v>46140.78125</v>
       </c>
       <c r="B77">
-        <v>528.675</v>
+        <v>1001.131</v>
       </c>
       <c r="C77">
-        <v>377</v>
+        <v>931</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2856,13 +2568,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46136.79166666666</v>
+        <v>46140.79166666666</v>
       </c>
       <c r="B78">
-        <v>554.681</v>
+        <v>988.856</v>
       </c>
       <c r="C78">
-        <v>399</v>
+        <v>961</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2873,13 +2585,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46136.80208333334</v>
+        <v>46140.80208333334</v>
       </c>
       <c r="B79">
-        <v>569.019</v>
+        <v>984.095</v>
       </c>
       <c r="C79">
-        <v>442</v>
+        <v>974</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2890,13 +2602,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46136.8125</v>
+        <v>46140.8125</v>
       </c>
       <c r="B80">
-        <v>584.817</v>
+        <v>980.83</v>
       </c>
       <c r="C80">
-        <v>464</v>
+        <v>949</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2907,13 +2619,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46136.82291666666</v>
+        <v>46140.82291666666</v>
       </c>
       <c r="B81">
-        <v>606.749</v>
+        <v>978.266</v>
       </c>
       <c r="C81">
-        <v>530</v>
+        <v>951</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2924,13 +2636,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46136.83333333334</v>
+        <v>46140.83333333334</v>
       </c>
       <c r="B82">
-        <v>652.603</v>
+        <v>954.473</v>
       </c>
       <c r="C82">
-        <v>562</v>
+        <v>954</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2941,13 +2653,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46136.84375</v>
+        <v>46140.84375</v>
       </c>
       <c r="B83">
-        <v>664.03</v>
+        <v>929.12</v>
       </c>
       <c r="C83">
-        <v>584</v>
+        <v>950</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2958,13 +2670,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46136.85416666666</v>
+        <v>46140.85416666666</v>
       </c>
       <c r="B84">
-        <v>681.05</v>
+        <v>909.0549999999999</v>
       </c>
       <c r="C84">
-        <v>623</v>
+        <v>959</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2975,13 +2687,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46136.86458333334</v>
+        <v>46140.86458333334</v>
       </c>
       <c r="B85">
-        <v>698.918</v>
+        <v>885.792</v>
       </c>
       <c r="C85">
-        <v>673</v>
+        <v>946</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2992,13 +2704,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46136.875</v>
+        <v>46140.875</v>
       </c>
       <c r="B86">
-        <v>726.809</v>
+        <v>852.3150000000001</v>
       </c>
       <c r="C86">
-        <v>777</v>
+        <v>928</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -3009,13 +2721,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46136.88541666666</v>
+        <v>46140.88541666666</v>
       </c>
       <c r="B87">
-        <v>740.963</v>
+        <v>827.341</v>
       </c>
       <c r="C87">
-        <v>828</v>
+        <v>893</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -3026,13 +2738,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46136.89583333334</v>
+        <v>46140.89583333334</v>
       </c>
       <c r="B88">
-        <v>753.851</v>
+        <v>802.425</v>
       </c>
       <c r="C88">
-        <v>809</v>
+        <v>834</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -3043,13 +2755,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46136.90625</v>
+        <v>46140.90625</v>
       </c>
       <c r="B89">
-        <v>766.2329999999999</v>
+        <v>778.785</v>
       </c>
       <c r="C89">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -3060,13 +2772,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46136.91666666666</v>
+        <v>46140.91666666666</v>
       </c>
       <c r="B90">
-        <v>778.633</v>
+        <v>748.401</v>
       </c>
       <c r="C90">
-        <v>839</v>
+        <v>707</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -3077,13 +2789,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46136.92708333334</v>
+        <v>46140.92708333334</v>
       </c>
       <c r="B91">
-        <v>784.284</v>
+        <v>727.739</v>
       </c>
       <c r="C91">
-        <v>927</v>
+        <v>673</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -3094,13 +2806,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46136.9375</v>
+        <v>46140.9375</v>
       </c>
       <c r="B92">
-        <v>791.021</v>
+        <v>707.723</v>
       </c>
       <c r="C92">
-        <v>966</v>
+        <v>649</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -3111,13 +2823,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46136.94791666666</v>
+        <v>46140.94791666666</v>
       </c>
       <c r="B93">
-        <v>797.1900000000001</v>
+        <v>686.889</v>
       </c>
       <c r="C93">
-        <v>1047</v>
+        <v>627</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -3128,13 +2840,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46136.95833333334</v>
+        <v>46140.95833333334</v>
       </c>
       <c r="B94">
-        <v>904.681</v>
+        <v>623.862</v>
       </c>
       <c r="C94">
-        <v>992</v>
+        <v>595</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -3145,13 +2857,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46136.96875</v>
+        <v>46140.96875</v>
       </c>
       <c r="B95">
-        <v>887.894</v>
+        <v>599.125</v>
       </c>
       <c r="C95">
-        <v>978</v>
+        <v>557</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -3162,13 +2874,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46136.97916666666</v>
+        <v>46140.97916666666</v>
       </c>
       <c r="B96">
-        <v>879.894</v>
+        <v>577.424</v>
       </c>
       <c r="C96">
-        <v>957</v>
+        <v>539</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -3179,13 +2891,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46136.98958333334</v>
+        <v>46140.98958333334</v>
       </c>
       <c r="B97">
-        <v>874.231</v>
+        <v>564.722</v>
       </c>
       <c r="C97">
-        <v>928</v>
+        <v>507</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -3196,13 +2908,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="B98">
-        <v>894.958</v>
+        <v>519.583</v>
       </c>
       <c r="C98">
-        <v>911</v>
+        <v>448</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3213,13 +2925,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46137.01041666666</v>
+        <v>46141.01041666666</v>
       </c>
       <c r="B99">
-        <v>861.502</v>
+        <v>504.68</v>
       </c>
       <c r="C99">
-        <v>877</v>
+        <v>408</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -3230,13 +2942,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46137.02083333334</v>
+        <v>46141.02083333334</v>
       </c>
       <c r="B100">
-        <v>828.576</v>
+        <v>485.484</v>
       </c>
       <c r="C100">
-        <v>820</v>
+        <v>372</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -3247,13 +2959,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46137.03125</v>
+        <v>46141.03125</v>
       </c>
       <c r="B101">
-        <v>799.489</v>
+        <v>467.114</v>
       </c>
       <c r="C101">
-        <v>769</v>
+        <v>361</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -3264,13 +2976,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46137.04166666666</v>
+        <v>46141.04166666666</v>
       </c>
       <c r="B102">
-        <v>768.277</v>
+        <v>435.739</v>
       </c>
       <c r="C102">
-        <v>718</v>
+        <v>332</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -3281,13 +2993,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46137.05208333334</v>
+        <v>46141.05208333334</v>
       </c>
       <c r="B103">
-        <v>733.153</v>
+        <v>417.841</v>
       </c>
       <c r="C103">
-        <v>671</v>
+        <v>325</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -3298,13 +3010,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46137.0625</v>
+        <v>46141.0625</v>
       </c>
       <c r="B104">
-        <v>701.039</v>
+        <v>397.748</v>
       </c>
       <c r="C104">
-        <v>639</v>
+        <v>339</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -3315,13 +3027,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46137.07291666666</v>
+        <v>46141.07291666666</v>
       </c>
       <c r="B105">
-        <v>664.437</v>
+        <v>379.447</v>
       </c>
       <c r="C105">
-        <v>609</v>
+        <v>334</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -3332,13 +3044,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46137.08333333334</v>
+        <v>46141.08333333334</v>
       </c>
       <c r="B106">
-        <v>632.496</v>
+        <v>356.681</v>
       </c>
       <c r="C106">
-        <v>575</v>
+        <v>305</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -3349,13 +3061,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46137.09375</v>
+        <v>46141.09375</v>
       </c>
       <c r="B107">
-        <v>596.213</v>
+        <v>339.795</v>
       </c>
       <c r="C107">
-        <v>551</v>
+        <v>247</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -3366,13 +3078,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46137.10416666666</v>
+        <v>46141.10416666666</v>
       </c>
       <c r="B108">
-        <v>551.927</v>
+        <v>323.738</v>
       </c>
       <c r="C108">
-        <v>504</v>
+        <v>201</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -3383,13 +3095,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46137.11458333334</v>
+        <v>46141.11458333334</v>
       </c>
       <c r="B109">
-        <v>515.8440000000001</v>
+        <v>308.664</v>
       </c>
       <c r="C109">
-        <v>461</v>
+        <v>184</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -3400,13 +3112,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46137.125</v>
+        <v>46141.125</v>
       </c>
       <c r="B110">
-        <v>439.281</v>
+        <v>298.263</v>
       </c>
       <c r="C110">
-        <v>423</v>
+        <v>172</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -3417,13 +3129,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46137.13541666666</v>
+        <v>46141.13541666666</v>
       </c>
       <c r="B111">
-        <v>406.419</v>
+        <v>291.526</v>
       </c>
       <c r="C111">
-        <v>381</v>
+        <v>168</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -3434,13 +3146,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46137.14583333334</v>
+        <v>46141.14583333334</v>
       </c>
       <c r="B112">
-        <v>384.79</v>
+        <v>285.145</v>
       </c>
       <c r="C112">
-        <v>334</v>
+        <v>166</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -3451,13 +3163,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46137.15625</v>
+        <v>46141.15625</v>
       </c>
       <c r="B113">
-        <v>357.211</v>
+        <v>272.793</v>
       </c>
       <c r="C113">
-        <v>301</v>
+        <v>161</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -3468,13 +3180,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46137.16666666666</v>
+        <v>46141.16666666666</v>
       </c>
       <c r="B114">
-        <v>298.728</v>
+        <v>262.379</v>
       </c>
       <c r="C114">
-        <v>305</v>
+        <v>171</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3485,13 +3197,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46137.17708333334</v>
+        <v>46141.17708333334</v>
       </c>
       <c r="B115">
-        <v>282.631</v>
+        <v>267.568</v>
       </c>
       <c r="C115">
-        <v>285</v>
+        <v>180</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3502,13 +3214,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46137.1875</v>
+        <v>46141.1875</v>
       </c>
       <c r="B116">
-        <v>253.707</v>
+        <v>266.997</v>
       </c>
       <c r="C116">
-        <v>259</v>
+        <v>170</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -3519,13 +3231,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46137.19791666666</v>
+        <v>46141.19791666666</v>
       </c>
       <c r="B117">
-        <v>228.193</v>
+        <v>265.784</v>
       </c>
       <c r="C117">
-        <v>229</v>
+        <v>158</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3536,13 +3248,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46137.20833333334</v>
+        <v>46141.20833333334</v>
       </c>
       <c r="B118">
-        <v>192.296</v>
+        <v>259.815</v>
       </c>
       <c r="C118">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3553,13 +3265,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46137.21875</v>
+        <v>46141.21875</v>
       </c>
       <c r="B119">
-        <v>176.877</v>
+        <v>263.032</v>
       </c>
       <c r="C119">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3570,13 +3282,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46137.22916666666</v>
+        <v>46141.22916666666</v>
       </c>
       <c r="B120">
-        <v>163.805</v>
+        <v>264.538</v>
       </c>
       <c r="C120">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3587,13 +3299,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46137.23958333334</v>
+        <v>46141.23958333334</v>
       </c>
       <c r="B121">
-        <v>147.917</v>
+        <v>268.175</v>
       </c>
       <c r="C121">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3604,13 +3316,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46137.25</v>
+        <v>46141.25</v>
       </c>
       <c r="B122">
-        <v>135.523</v>
+        <v>267.464</v>
       </c>
       <c r="C122">
-        <v>74</v>
+        <v>199</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3621,13 +3333,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46137.26041666666</v>
+        <v>46141.26041666666</v>
       </c>
       <c r="B123">
-        <v>137.01</v>
+        <v>266.108</v>
       </c>
       <c r="C123">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3638,13 +3350,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46137.27083333334</v>
+        <v>46141.27083333334</v>
       </c>
       <c r="B124">
-        <v>137.106</v>
+        <v>274.297</v>
       </c>
       <c r="C124">
-        <v>33</v>
+        <v>170</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3655,13 +3367,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46137.28125</v>
+        <v>46141.28125</v>
       </c>
       <c r="B125">
-        <v>137.833</v>
+        <v>282.184</v>
       </c>
       <c r="C125">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3672,13 +3384,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46137.29166666666</v>
+        <v>46141.29166666666</v>
       </c>
       <c r="B126">
-        <v>125.111</v>
+        <v>295.651</v>
       </c>
       <c r="C126">
-        <v>5</v>
+        <v>143</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3689,13 +3401,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46137.30208333334</v>
+        <v>46141.30208333334</v>
       </c>
       <c r="B127">
-        <v>123.434</v>
+        <v>292.798</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3706,13 +3418,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46137.3125</v>
+        <v>46141.3125</v>
       </c>
       <c r="B128">
-        <v>123.116</v>
+        <v>286.728</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3723,13 +3435,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46137.32291666666</v>
+        <v>46141.32291666666</v>
       </c>
       <c r="B129">
-        <v>110.638</v>
+        <v>277.51</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3740,13 +3452,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46137.33333333334</v>
+        <v>46141.33333333334</v>
       </c>
       <c r="B130">
-        <v>101.337</v>
+        <v>323.265</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3757,13 +3469,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46137.34375</v>
+        <v>46141.34375</v>
       </c>
       <c r="B131">
-        <v>110.893</v>
+        <v>324.217</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3774,13 +3486,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46137.35416666666</v>
+        <v>46141.35416666666</v>
       </c>
       <c r="B132">
-        <v>113.816</v>
+        <v>329.726</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3791,13 +3503,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46137.36458333334</v>
+        <v>46141.36458333334</v>
       </c>
       <c r="B133">
-        <v>113.22</v>
+        <v>330.432</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3808,13 +3520,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46137.375</v>
+        <v>46141.375</v>
       </c>
       <c r="B134">
-        <v>133.018</v>
+        <v>343.325</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3825,13 +3537,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46137.38541666666</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="B135">
-        <v>139.85</v>
+        <v>353.008</v>
       </c>
       <c r="C135">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3842,13 +3554,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46137.39583333334</v>
+        <v>46141.39583333334</v>
       </c>
       <c r="B136">
-        <v>136.823</v>
+        <v>362.508</v>
       </c>
       <c r="C136">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3859,13 +3571,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46137.40625</v>
+        <v>46141.40625</v>
       </c>
       <c r="B137">
-        <v>138.594</v>
+        <v>374.271</v>
       </c>
       <c r="C137">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3876,13 +3588,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46137.41666666666</v>
+        <v>46141.41666666666</v>
       </c>
       <c r="B138">
-        <v>143.699</v>
+        <v>386.541</v>
       </c>
       <c r="C138">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3893,13 +3605,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46137.42708333334</v>
+        <v>46141.42708333334</v>
       </c>
       <c r="B139">
-        <v>154.929</v>
+        <v>396.382</v>
       </c>
       <c r="C139">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3910,13 +3622,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46137.4375</v>
+        <v>46141.4375</v>
       </c>
       <c r="B140">
-        <v>164.356</v>
+        <v>405.672</v>
       </c>
       <c r="C140">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3927,13 +3639,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46137.44791666666</v>
+        <v>46141.44791666666</v>
       </c>
       <c r="B141">
-        <v>169.318</v>
+        <v>414.995</v>
       </c>
       <c r="C141">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3944,13 +3656,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46137.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="B142">
-        <v>169.172</v>
+        <v>406.167</v>
       </c>
       <c r="C142">
-        <v>65</v>
+        <v>173</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3961,13 +3673,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46137.46875</v>
+        <v>46141.46875</v>
       </c>
       <c r="B143">
-        <v>161.277</v>
+        <v>417.166</v>
       </c>
       <c r="C143">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3978,13 +3690,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46137.47916666666</v>
+        <v>46141.47916666666</v>
       </c>
       <c r="B144">
-        <v>173.77</v>
+        <v>428.775</v>
       </c>
       <c r="C144">
-        <v>52</v>
+        <v>262</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3995,13 +3707,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46137.48958333334</v>
+        <v>46141.48958333334</v>
       </c>
       <c r="B145">
-        <v>186.886</v>
+        <v>439.906</v>
       </c>
       <c r="C145">
-        <v>50</v>
+        <v>275</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -4012,13 +3724,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46137.5</v>
+        <v>46141.5</v>
       </c>
       <c r="B146">
-        <v>209.142</v>
+        <v>458.335</v>
       </c>
       <c r="C146">
-        <v>55</v>
+        <v>254</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -4029,13 +3741,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46137.51041666666</v>
+        <v>46141.51041666666</v>
       </c>
       <c r="B147">
-        <v>224.887</v>
+        <v>473.635</v>
       </c>
       <c r="C147">
-        <v>61</v>
+        <v>267</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -4046,13 +3758,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46137.52083333334</v>
+        <v>46141.52083333334</v>
       </c>
       <c r="B148">
-        <v>241.566</v>
+        <v>490.088</v>
       </c>
       <c r="C148">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -4063,13 +3775,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46137.53125</v>
+        <v>46141.53125</v>
       </c>
       <c r="B149">
-        <v>254.442</v>
+        <v>506.022</v>
       </c>
       <c r="C149">
-        <v>101</v>
+        <v>303</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -4080,13 +3792,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46137.54166666666</v>
+        <v>46141.54166666666</v>
       </c>
       <c r="B150">
-        <v>258.456</v>
+        <v>530.439</v>
       </c>
       <c r="C150">
-        <v>128</v>
+        <v>338</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -4097,13 +3809,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46137.55208333334</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="B151">
-        <v>269.765</v>
+        <v>559.462</v>
       </c>
       <c r="C151">
-        <v>151</v>
+        <v>376</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -4114,13 +3826,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46137.5625</v>
+        <v>46141.5625</v>
       </c>
       <c r="B152">
-        <v>281.351</v>
+        <v>589.021</v>
       </c>
       <c r="C152">
-        <v>180</v>
+        <v>571</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -4131,13 +3843,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46137.57291666666</v>
+        <v>46141.57291666666</v>
       </c>
       <c r="B153">
-        <v>293.08</v>
+        <v>618.462</v>
       </c>
       <c r="C153">
-        <v>211</v>
+        <v>610</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -4148,13 +3860,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46137.58333333334</v>
+        <v>46141.58333333334</v>
       </c>
       <c r="B154">
-        <v>310.441</v>
+        <v>669.425</v>
       </c>
       <c r="C154">
-        <v>228</v>
+        <v>724</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -4165,13 +3877,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46137.59375</v>
+        <v>46141.59375</v>
       </c>
       <c r="B155">
-        <v>324.051</v>
+        <v>695.582</v>
       </c>
       <c r="C155">
-        <v>247</v>
+        <v>729</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -4182,13 +3894,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46137.60416666666</v>
+        <v>46141.60416666666</v>
       </c>
       <c r="B156">
-        <v>334.96</v>
+        <v>720.357</v>
       </c>
       <c r="C156">
-        <v>229</v>
+        <v>780</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -4199,13 +3911,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46137.61458333334</v>
+        <v>46141.61458333334</v>
       </c>
       <c r="B157">
-        <v>344.445</v>
+        <v>748.28</v>
       </c>
       <c r="C157">
-        <v>254</v>
+        <v>839</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -4216,13 +3928,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46137.625</v>
+        <v>46141.625</v>
       </c>
       <c r="B158">
-        <v>354.722</v>
+        <v>777.725</v>
       </c>
       <c r="C158">
-        <v>272</v>
+        <v>868</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -4233,13 +3945,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46137.63541666666</v>
+        <v>46141.63541666666</v>
       </c>
       <c r="B159">
-        <v>365.8</v>
+        <v>795.747</v>
       </c>
       <c r="C159">
-        <v>297</v>
+        <v>903</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -4250,13 +3962,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46137.64583333334</v>
+        <v>46141.64583333334</v>
       </c>
       <c r="B160">
-        <v>376.637</v>
+        <v>813.443</v>
       </c>
       <c r="C160">
-        <v>326</v>
+        <v>910</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -4267,13 +3979,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46137.65625</v>
+        <v>46141.65625</v>
       </c>
       <c r="B161">
-        <v>388.006</v>
+        <v>830.962</v>
       </c>
       <c r="C161">
-        <v>352</v>
+        <v>928</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -4284,13 +3996,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46137.66666666666</v>
+        <v>46141.66666666666</v>
       </c>
       <c r="B162">
-        <v>420.016</v>
+        <v>821.8099999999999</v>
       </c>
       <c r="C162">
-        <v>394</v>
+        <v>996</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -4301,13 +4013,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46137.67708333334</v>
+        <v>46141.67708333334</v>
       </c>
       <c r="B163">
-        <v>473.213</v>
+        <v>831.864</v>
       </c>
       <c r="C163">
-        <v>412</v>
+        <v>1023</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -4318,13 +4030,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46137.6875</v>
+        <v>46141.6875</v>
       </c>
       <c r="B164">
-        <v>559.336</v>
+        <v>841.284</v>
       </c>
       <c r="C164">
-        <v>527</v>
+        <v>1006</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -4335,13 +4047,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46137.69791666666</v>
+        <v>46141.69791666666</v>
       </c>
       <c r="B165">
-        <v>637.91</v>
+        <v>849.897</v>
       </c>
       <c r="C165">
-        <v>624</v>
+        <v>967</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -4352,13 +4064,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46137.70833333334</v>
+        <v>46141.70833333334</v>
       </c>
       <c r="B166">
-        <v>562.899</v>
+        <v>760.847</v>
       </c>
       <c r="C166">
-        <v>589</v>
+        <v>885</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -4369,13 +4081,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46137.71875</v>
+        <v>46141.71875</v>
       </c>
       <c r="B167">
-        <v>586.375</v>
+        <v>754.633</v>
       </c>
       <c r="C167">
-        <v>596</v>
+        <v>817</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -4386,13 +4098,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46137.72916666666</v>
+        <v>46141.72916666666</v>
       </c>
       <c r="B168">
-        <v>626.359</v>
+        <v>749.009</v>
       </c>
       <c r="C168">
-        <v>612</v>
+        <v>841</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -4403,13 +4115,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46137.73958333334</v>
+        <v>46141.73958333334</v>
       </c>
       <c r="B169">
-        <v>644.191</v>
+        <v>743.52</v>
       </c>
       <c r="C169">
-        <v>608</v>
+        <v>795</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -4420,13 +4132,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46137.75</v>
+        <v>46141.75</v>
       </c>
       <c r="B170">
-        <v>685.5410000000001</v>
+        <v>738.33</v>
       </c>
       <c r="C170">
-        <v>612</v>
+        <v>743</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -4437,13 +4149,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46137.76041666666</v>
+        <v>46141.76041666666</v>
       </c>
       <c r="B171">
-        <v>718.276</v>
+        <v>737.772</v>
       </c>
       <c r="C171">
-        <v>626</v>
+        <v>750</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -4454,13 +4166,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46137.77083333334</v>
+        <v>46141.77083333334</v>
       </c>
       <c r="B172">
-        <v>756.663</v>
+        <v>736.492</v>
       </c>
       <c r="C172">
-        <v>638</v>
+        <v>781</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4471,13 +4183,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46137.78125</v>
+        <v>46141.78125</v>
       </c>
       <c r="B173">
-        <v>791.7430000000001</v>
+        <v>735.7140000000001</v>
       </c>
       <c r="C173">
-        <v>649</v>
+        <v>793</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4488,13 +4200,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46137.79166666666</v>
+        <v>46141.79166666666</v>
       </c>
       <c r="B174">
-        <v>848.917</v>
+        <v>732.727</v>
       </c>
       <c r="C174">
-        <v>673</v>
+        <v>771</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4505,13 +4217,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46137.80208333334</v>
+        <v>46141.80208333334</v>
       </c>
       <c r="B175">
-        <v>881.832</v>
+        <v>733.014</v>
       </c>
       <c r="C175">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -4522,13 +4234,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46137.8125</v>
+        <v>46141.8125</v>
       </c>
       <c r="B176">
-        <v>913.321</v>
+        <v>733.753</v>
       </c>
       <c r="C176">
-        <v>767</v>
+        <v>668</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -4539,13 +4251,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46137.82291666666</v>
+        <v>46141.82291666666</v>
       </c>
       <c r="B177">
-        <v>943.285</v>
+        <v>734.694</v>
       </c>
       <c r="C177">
-        <v>790</v>
+        <v>604</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -4556,13 +4268,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46137.83333333334</v>
+        <v>46141.83333333334</v>
       </c>
       <c r="B178">
-        <v>993.975</v>
+        <v>724.697</v>
       </c>
       <c r="C178">
-        <v>813</v>
+        <v>629</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -4573,13 +4285,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46137.84375</v>
+        <v>46141.84375</v>
       </c>
       <c r="B179">
-        <v>993.648</v>
+        <v>702.802</v>
       </c>
       <c r="C179">
-        <v>843</v>
+        <v>679</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4590,13 +4302,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46137.85416666666</v>
+        <v>46141.85416666666</v>
       </c>
       <c r="B180">
-        <v>992.079</v>
+        <v>681.704</v>
       </c>
       <c r="C180">
-        <v>855</v>
+        <v>775</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4607,13 +4319,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46137.86458333334</v>
+        <v>46141.86458333334</v>
       </c>
       <c r="B181">
-        <v>990.756</v>
+        <v>660.646</v>
       </c>
       <c r="C181">
-        <v>878</v>
+        <v>856</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4624,13 +4336,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46137.875</v>
+        <v>46141.875</v>
       </c>
       <c r="B182">
-        <v>985.55</v>
+        <v>638.54</v>
       </c>
       <c r="C182">
-        <v>929</v>
+        <v>828</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4641,13 +4353,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46137.88541666666</v>
+        <v>46141.88541666666</v>
       </c>
       <c r="B183">
-        <v>973.5549999999999</v>
+        <v>626.155</v>
       </c>
       <c r="C183">
-        <v>944</v>
+        <v>755</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4658,13 +4370,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46137.89583333334</v>
+        <v>46141.89583333334</v>
       </c>
       <c r="B184">
-        <v>960.324</v>
+        <v>612.587</v>
       </c>
       <c r="C184">
-        <v>931</v>
+        <v>726</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4675,13 +4387,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46137.90625</v>
+        <v>46141.90625</v>
       </c>
       <c r="B185">
-        <v>949.183</v>
+        <v>598.783</v>
       </c>
       <c r="C185">
-        <v>899</v>
+        <v>721</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4692,13 +4404,13 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46137.91666666666</v>
+        <v>46141.91666666666</v>
       </c>
       <c r="B186">
-        <v>926.7809999999999</v>
+        <v>586.925</v>
       </c>
       <c r="C186">
-        <v>834</v>
+        <v>740</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4709,13 +4421,13 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46137.92708333334</v>
+        <v>46141.92708333334</v>
       </c>
       <c r="B187">
-        <v>904.496</v>
+        <v>577.496</v>
       </c>
       <c r="C187">
-        <v>772</v>
+        <v>737</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4726,13 +4438,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46137.9375</v>
+        <v>46141.9375</v>
       </c>
       <c r="B188">
-        <v>881.772</v>
+        <v>570.268</v>
       </c>
       <c r="C188">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4743,13 +4455,13 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46137.94791666666</v>
+        <v>46141.94791666666</v>
       </c>
       <c r="B189">
-        <v>859.764</v>
+        <v>562.154</v>
       </c>
       <c r="C189">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4760,13 +4472,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46137.95833333334</v>
+        <v>46141.95833333334</v>
       </c>
       <c r="B190">
-        <v>753.063</v>
+        <v>616.958</v>
       </c>
       <c r="C190">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4777,13 +4489,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46137.96875</v>
+        <v>46141.96875</v>
       </c>
       <c r="B191">
-        <v>737.824</v>
+        <v>626.409</v>
       </c>
       <c r="C191">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4794,13 +4506,13 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46137.97916666666</v>
+        <v>46141.97916666666</v>
       </c>
       <c r="B192">
-        <v>722.258</v>
+        <v>625.082</v>
       </c>
       <c r="C192">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="D192">
         <v>95</v>
@@ -4811,13 +4523,13 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46137.98958333334</v>
+        <v>46141.98958333334</v>
       </c>
       <c r="B193">
-        <v>701.105</v>
+        <v>622.006</v>
       </c>
       <c r="C193">
-        <v>577</v>
+        <v>609</v>
       </c>
       <c r="D193">
         <v>96</v>
@@ -4828,13 +4540,13 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B194">
-        <v>679.077</v>
+        <v>648.849</v>
       </c>
       <c r="C194">
-        <v>562</v>
+        <v>636</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4845,13 +4557,13 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46138.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B195">
-        <v>679.8920000000001</v>
+        <v>652.102</v>
       </c>
       <c r="C195">
-        <v>564</v>
+        <v>638</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -4862,13 +4574,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46138.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B196">
-        <v>683.215</v>
+        <v>652.4349999999999</v>
       </c>
       <c r="C196">
-        <v>561</v>
+        <v>625</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -4879,13 +4591,13 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46138.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B197">
-        <v>686.477</v>
+        <v>657.736</v>
       </c>
       <c r="C197">
-        <v>556</v>
+        <v>616</v>
       </c>
       <c r="D197">
         <v>4</v>
@@ -4896,13 +4608,13 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46138.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B198">
-        <v>681.207</v>
+        <v>634.076</v>
       </c>
       <c r="C198">
-        <v>574</v>
+        <v>613</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -4913,13 +4625,13 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46138.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B199">
-        <v>691.852</v>
+        <v>645.49</v>
       </c>
       <c r="C199">
-        <v>564</v>
+        <v>604</v>
       </c>
       <c r="D199">
         <v>6</v>
@@ -4930,13 +4642,13 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46138.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B200">
-        <v>703.054</v>
+        <v>659.099</v>
       </c>
       <c r="C200">
-        <v>568</v>
+        <v>613</v>
       </c>
       <c r="D200">
         <v>7</v>
@@ -4947,13 +4659,13 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46138.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B201">
-        <v>704.143</v>
+        <v>675.169</v>
       </c>
       <c r="C201">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="D201">
         <v>8</v>
@@ -4964,13 +4676,13 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46138.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B202">
-        <v>738.193</v>
+        <v>684.753</v>
       </c>
       <c r="C202">
-        <v>577</v>
+        <v>612</v>
       </c>
       <c r="D202">
         <v>9</v>
@@ -4981,13 +4693,13 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46138.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B203">
-        <v>759.51</v>
+        <v>698.7910000000001</v>
       </c>
       <c r="C203">
-        <v>615</v>
+        <v>579</v>
       </c>
       <c r="D203">
         <v>10</v>
@@ -4998,13 +4710,13 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46138.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B204">
-        <v>776.71</v>
+        <v>712.357</v>
       </c>
       <c r="C204">
-        <v>650</v>
+        <v>582</v>
       </c>
       <c r="D204">
         <v>11</v>
@@ -5015,13 +4727,13 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46138.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B205">
-        <v>801.628</v>
+        <v>729.8819999999999</v>
       </c>
       <c r="C205">
-        <v>659</v>
+        <v>572</v>
       </c>
       <c r="D205">
         <v>12</v>
@@ -5032,13 +4744,13 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46138.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B206">
-        <v>846.979</v>
+        <v>753.501</v>
       </c>
       <c r="C206">
-        <v>688</v>
+        <v>544</v>
       </c>
       <c r="D206">
         <v>13</v>
@@ -5049,13 +4761,13 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46138.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B207">
-        <v>872.068</v>
+        <v>774.6660000000001</v>
       </c>
       <c r="C207">
-        <v>738</v>
+        <v>532</v>
       </c>
       <c r="D207">
         <v>14</v>
@@ -5066,13 +4778,13 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46138.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B208">
-        <v>896.723</v>
+        <v>790.66</v>
       </c>
       <c r="C208">
-        <v>782</v>
+        <v>521</v>
       </c>
       <c r="D208">
         <v>15</v>
@@ -5083,13 +4795,13 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46138.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B209">
-        <v>922.851</v>
+        <v>815.938</v>
       </c>
       <c r="C209">
-        <v>835</v>
+        <v>511</v>
       </c>
       <c r="D209">
         <v>16</v>
@@ -5100,13 +4812,13 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46138.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B210">
-        <v>957.765</v>
+        <v>848.564</v>
       </c>
       <c r="C210">
-        <v>897</v>
+        <v>538</v>
       </c>
       <c r="D210">
         <v>17</v>
@@ -5117,13 +4829,13 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46138.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B211">
-        <v>974.252</v>
+        <v>868.607</v>
       </c>
       <c r="C211">
-        <v>976</v>
+        <v>563</v>
       </c>
       <c r="D211">
         <v>18</v>
@@ -5134,13 +4846,13 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46138.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B212">
-        <v>997.658</v>
+        <v>891.778</v>
       </c>
       <c r="C212">
-        <v>1028</v>
+        <v>592</v>
       </c>
       <c r="D212">
         <v>19</v>
@@ -5151,13 +4863,13 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46138.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B213">
-        <v>1013.143</v>
+        <v>910.2329999999999</v>
       </c>
       <c r="C213">
-        <v>1045</v>
+        <v>606</v>
       </c>
       <c r="D213">
         <v>20</v>
@@ -5168,13 +4880,13 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46138.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B214">
-        <v>1051.839</v>
+        <v>971.033</v>
       </c>
       <c r="C214">
-        <v>1047</v>
+        <v>623</v>
       </c>
       <c r="D214">
         <v>21</v>
@@ -5185,13 +4897,13 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46138.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B215">
-        <v>1066.182</v>
+        <v>996.926</v>
       </c>
       <c r="C215">
-        <v>1042</v>
+        <v>627</v>
       </c>
       <c r="D215">
         <v>22</v>
@@ -5202,13 +4914,13 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46138.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B216">
-        <v>1077.389</v>
+        <v>1022.417</v>
       </c>
       <c r="C216">
-        <v>1032</v>
+        <v>641</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -5219,13 +4931,13 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46138.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B217">
-        <v>1097.017</v>
+        <v>1045.328</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="D217">
         <v>24</v>
@@ -5236,13 +4948,13 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46138.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B218">
-        <v>1126.35</v>
+        <v>1119.208</v>
       </c>
       <c r="C218">
-        <v>1083</v>
+        <v>672</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -5253,13 +4965,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46138.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B219">
-        <v>1137.599</v>
+        <v>1142.173</v>
       </c>
       <c r="C219">
-        <v>1102</v>
+        <v>686</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -5270,13 +4982,13 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46138.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B220">
-        <v>1152.179</v>
+        <v>1160.553</v>
       </c>
       <c r="C220">
-        <v>1095</v>
+        <v>713</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -5287,13 +4999,13 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46138.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B221">
-        <v>1169.778</v>
+        <v>1164.352</v>
       </c>
       <c r="C221">
-        <v>1141</v>
+        <v>723</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -5304,13 +5016,13 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46138.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B222">
-        <v>1167.542</v>
+        <v>1215.261</v>
       </c>
       <c r="C222">
-        <v>1129</v>
+        <v>710</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -5321,13 +5033,13 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46138.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B223">
-        <v>1158.329</v>
+        <v>1213.192</v>
       </c>
       <c r="C223">
-        <v>1090</v>
+        <v>683</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -5338,13 +5050,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46138.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B224">
-        <v>1145.047</v>
+        <v>1210.118</v>
       </c>
       <c r="C224">
-        <v>1010</v>
+        <v>628</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -5355,13 +5067,13 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46138.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B225">
-        <v>1096.348</v>
+        <v>1220.582</v>
       </c>
       <c r="C225">
-        <v>903</v>
+        <v>605</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -5372,13 +5084,13 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46138.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B226">
-        <v>1187.799</v>
+        <v>1116.184</v>
       </c>
       <c r="C226">
-        <v>827</v>
+        <v>609</v>
       </c>
       <c r="D226">
         <v>33</v>
@@ -5389,13 +5101,13 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46138.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B227">
-        <v>1219.093</v>
+        <v>1119.482</v>
       </c>
       <c r="C227">
-        <v>797</v>
+        <v>626</v>
       </c>
       <c r="D227">
         <v>34</v>
@@ -5406,13 +5118,13 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46138.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B228">
-        <v>1225.523</v>
+        <v>1134.834</v>
       </c>
       <c r="C228">
-        <v>750</v>
+        <v>677</v>
       </c>
       <c r="D228">
         <v>35</v>
@@ -5423,13 +5135,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46138.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B229">
-        <v>1221.876</v>
+        <v>1142.694</v>
       </c>
       <c r="C229">
-        <v>723</v>
+        <v>767</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -5440,13 +5152,13 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46138.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B230">
-        <v>1379.733</v>
+        <v>1318.648</v>
       </c>
       <c r="C230">
-        <v>797</v>
+        <v>867</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -5457,13 +5169,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46138.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B231">
-        <v>1441.319</v>
+        <v>1331.289</v>
       </c>
       <c r="C231">
-        <v>937</v>
+        <v>975</v>
       </c>
       <c r="D231">
         <v>38</v>
@@ -5474,13 +5186,13 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46138.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B232">
-        <v>1227.881</v>
+        <v>1343.271</v>
       </c>
       <c r="C232">
-        <v>1016</v>
+        <v>1142</v>
       </c>
       <c r="D232">
         <v>39</v>
@@ -5491,13 +5203,13 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46138.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B233">
-        <v>1223.048</v>
+        <v>1318.529</v>
       </c>
       <c r="C233">
-        <v>1032</v>
+        <v>1198</v>
       </c>
       <c r="D233">
         <v>40</v>
@@ -5508,13 +5220,13 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46138.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B234">
-        <v>1241.714</v>
+        <v>1369.836</v>
       </c>
       <c r="C234">
-        <v>1114</v>
+        <v>1279</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5525,13 +5237,13 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46138.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B235">
-        <v>1078.108</v>
+        <v>1345.14</v>
       </c>
       <c r="C235">
-        <v>1073</v>
+        <v>1396</v>
       </c>
       <c r="D235">
         <v>42</v>
@@ -5542,13 +5254,13 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46138.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B236">
-        <v>852.902</v>
+        <v>1387.805</v>
       </c>
       <c r="C236">
-        <v>932</v>
+        <v>1409</v>
       </c>
       <c r="D236">
         <v>43</v>
@@ -5559,13 +5271,13 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46138.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B237">
-        <v>874.325</v>
+        <v>1416.536</v>
       </c>
       <c r="C237">
-        <v>847</v>
+        <v>1402</v>
       </c>
       <c r="D237">
         <v>44</v>
@@ -5576,13 +5288,13 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46138.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B238">
-        <v>905.0119999999999</v>
+        <v>1494.563</v>
       </c>
       <c r="C238">
-        <v>812</v>
+        <v>1470</v>
       </c>
       <c r="D238">
         <v>45</v>
@@ -5593,13 +5305,13 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46138.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B239">
-        <v>919.202</v>
+        <v>1513.067</v>
       </c>
       <c r="C239">
-        <v>821</v>
+        <v>0</v>
       </c>
       <c r="D239">
         <v>46</v>
@@ -5610,13 +5322,13 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46138.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B240">
-        <v>931.4160000000001</v>
+        <v>1535.332</v>
       </c>
       <c r="C240">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="D240">
         <v>47</v>
@@ -5627,13 +5339,13 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46138.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B241">
-        <v>947.217</v>
+        <v>1553.759</v>
       </c>
       <c r="C241">
-        <v>892</v>
+        <v>0</v>
       </c>
       <c r="D241">
         <v>48</v>
@@ -5644,13 +5356,13 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46138.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B242">
-        <v>962.061</v>
+        <v>1585.976</v>
       </c>
       <c r="C242">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="D242">
         <v>49</v>
@@ -5661,13 +5373,13 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46138.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B243">
-        <v>969.905</v>
+        <v>1610.747</v>
       </c>
       <c r="C243">
-        <v>911</v>
+        <v>0</v>
       </c>
       <c r="D243">
         <v>50</v>
@@ -5678,13 +5390,13 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46138.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B244">
-        <v>978.307</v>
+        <v>1587.508</v>
       </c>
       <c r="C244">
-        <v>897</v>
+        <v>0</v>
       </c>
       <c r="D244">
         <v>51</v>
@@ -5695,13 +5407,13 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46138.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B245">
-        <v>988.672</v>
+        <v>1609.954</v>
       </c>
       <c r="C245">
-        <v>817</v>
+        <v>0</v>
       </c>
       <c r="D245">
         <v>52</v>
@@ -5712,13 +5424,13 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46138.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B246">
-        <v>1003.281</v>
+        <v>1615.319</v>
       </c>
       <c r="C246">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="D246">
         <v>53</v>
@@ -5729,13 +5441,13 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46138.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B247">
-        <v>1000.856</v>
+        <v>1623.051</v>
       </c>
       <c r="C247">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="D247">
         <v>54</v>
@@ -5746,13 +5458,13 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46138.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B248">
-        <v>1009.593</v>
+        <v>1629.591</v>
       </c>
       <c r="C248">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="D248">
         <v>55</v>
@@ -5763,13 +5475,13 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46138.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B249">
-        <v>1012.919</v>
+        <v>1690.212</v>
       </c>
       <c r="C249">
-        <v>646</v>
+        <v>0</v>
       </c>
       <c r="D249">
         <v>56</v>
@@ -5780,13 +5492,13 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46138.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B250">
-        <v>1021.172</v>
+        <v>1691.257</v>
       </c>
       <c r="C250">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="D250">
         <v>57</v>
@@ -5797,13 +5509,13 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46138.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B251">
-        <v>1023.028</v>
+        <v>1684.456</v>
       </c>
       <c r="C251">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="D251">
         <v>58</v>
@@ -5814,13 +5526,13 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46138.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B252">
-        <v>1025.93</v>
+        <v>1730.248</v>
       </c>
       <c r="C252">
-        <v>594</v>
+        <v>0</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -5831,13 +5543,13 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46138.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B253">
-        <v>1027.749</v>
+        <v>1667.491</v>
       </c>
       <c r="C253">
-        <v>604</v>
+        <v>0</v>
       </c>
       <c r="D253">
         <v>60</v>
@@ -5848,13 +5560,13 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46138.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B254">
-        <v>1029.85</v>
+        <v>1651.491</v>
       </c>
       <c r="C254">
-        <v>662</v>
+        <v>0</v>
       </c>
       <c r="D254">
         <v>61</v>
@@ -5865,13 +5577,13 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46138.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B255">
-        <v>1035.589</v>
+        <v>1639.549</v>
       </c>
       <c r="C255">
-        <v>653</v>
+        <v>0</v>
       </c>
       <c r="D255">
         <v>62</v>
@@ -5882,13 +5594,13 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46138.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B256">
-        <v>1036.599</v>
+        <v>1678.808</v>
       </c>
       <c r="C256">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="D256">
         <v>63</v>
@@ -5899,13 +5611,13 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46138.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B257">
-        <v>1040.893</v>
+        <v>1664.533</v>
       </c>
       <c r="C257">
-        <v>883</v>
+        <v>0</v>
       </c>
       <c r="D257">
         <v>64</v>
@@ -5916,13 +5628,13 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46138.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B258">
-        <v>1220.396</v>
+        <v>1596.839</v>
       </c>
       <c r="C258">
-        <v>1297</v>
+        <v>0</v>
       </c>
       <c r="D258">
         <v>65</v>
@@ -5933,13 +5645,13 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46138.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B259">
-        <v>1042.527</v>
+        <v>1561.902</v>
       </c>
       <c r="C259">
-        <v>1286</v>
+        <v>0</v>
       </c>
       <c r="D259">
         <v>66</v>
@@ -5950,13 +5662,13 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46138.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B260">
-        <v>1559.126</v>
+        <v>1523.067</v>
       </c>
       <c r="C260">
-        <v>1834</v>
+        <v>0</v>
       </c>
       <c r="D260">
         <v>67</v>
@@ -5967,13 +5679,13 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46138.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B261">
-        <v>1928.731</v>
+        <v>1481.622</v>
       </c>
       <c r="C261">
-        <v>2169</v>
+        <v>0</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -5984,13 +5696,13 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46138.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B262">
-        <v>1923.238</v>
+        <v>1202.378</v>
       </c>
       <c r="C262">
-        <v>2121</v>
+        <v>0</v>
       </c>
       <c r="D262">
         <v>69</v>
@@ -6001,13 +5713,13 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46138.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B263">
-        <v>1955.798</v>
+        <v>1140.683</v>
       </c>
       <c r="C263">
-        <v>1916</v>
+        <v>0</v>
       </c>
       <c r="D263">
         <v>70</v>
@@ -6018,13 +5730,13 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46138.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B264">
-        <v>2207.081</v>
+        <v>1082.644</v>
       </c>
       <c r="C264">
-        <v>1934</v>
+        <v>0</v>
       </c>
       <c r="D264">
         <v>71</v>
@@ -6035,13 +5747,13 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46138.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B265">
-        <v>2362.118</v>
+        <v>1026.684</v>
       </c>
       <c r="C265">
-        <v>2324</v>
+        <v>0</v>
       </c>
       <c r="D265">
         <v>72</v>
@@ -6052,13 +5764,13 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46138.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B266">
-        <v>2408.725</v>
+        <v>934.331</v>
       </c>
       <c r="C266">
-        <v>2439</v>
+        <v>0</v>
       </c>
       <c r="D266">
         <v>73</v>
@@ -6069,13 +5781,13 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46138.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B267">
-        <v>2450.189</v>
+        <v>873.372</v>
       </c>
       <c r="C267">
-        <v>2440</v>
+        <v>0</v>
       </c>
       <c r="D267">
         <v>74</v>
@@ -6086,13 +5798,13 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46138.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B268">
-        <v>2491.995</v>
+        <v>814.657</v>
       </c>
       <c r="C268">
-        <v>2463</v>
+        <v>0</v>
       </c>
       <c r="D268">
         <v>75</v>
@@ -6103,13 +5815,13 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46138.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B269">
-        <v>2532.701</v>
+        <v>755.008</v>
       </c>
       <c r="C269">
-        <v>2471</v>
+        <v>0</v>
       </c>
       <c r="D269">
         <v>76</v>
@@ -6120,13 +5832,13 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46138.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B270">
-        <v>2542.035</v>
+        <v>684.558</v>
       </c>
       <c r="C270">
-        <v>2499</v>
+        <v>0</v>
       </c>
       <c r="D270">
         <v>77</v>
@@ -6137,10 +5849,10 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46138.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B271">
-        <v>2533.284</v>
+        <v>645.986</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -6154,13 +5866,13 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46138.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B272">
-        <v>2521.214</v>
+        <v>608.806</v>
       </c>
       <c r="C272">
-        <v>2506</v>
+        <v>0</v>
       </c>
       <c r="D272">
         <v>79</v>
@@ -6171,13 +5883,13 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46138.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B273">
-        <v>2507.363</v>
+        <v>571.515</v>
       </c>
       <c r="C273">
-        <v>2478</v>
+        <v>0</v>
       </c>
       <c r="D273">
         <v>80</v>
@@ -6188,13 +5900,13 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46138.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B274">
-        <v>2459.435</v>
+        <v>515.564</v>
       </c>
       <c r="C274">
-        <v>2414</v>
+        <v>0</v>
       </c>
       <c r="D274">
         <v>81</v>
@@ -6205,13 +5917,13 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46138.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B275">
-        <v>2411.843</v>
+        <v>494.889</v>
       </c>
       <c r="C275">
-        <v>2318</v>
+        <v>0</v>
       </c>
       <c r="D275">
         <v>82</v>
@@ -6222,13 +5934,13 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46138.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B276">
-        <v>2364.718</v>
+        <v>474.77</v>
       </c>
       <c r="C276">
-        <v>2245</v>
+        <v>0</v>
       </c>
       <c r="D276">
         <v>83</v>
@@ -6239,13 +5951,13 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46138.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B277">
-        <v>2317.1</v>
+        <v>454.56</v>
       </c>
       <c r="C277">
-        <v>2129</v>
+        <v>0</v>
       </c>
       <c r="D277">
         <v>84</v>
@@ -6256,13 +5968,13 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46138.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B278">
-        <v>2237.605</v>
+        <v>448.509</v>
       </c>
       <c r="C278">
-        <v>2001</v>
+        <v>0</v>
       </c>
       <c r="D278">
         <v>85</v>
@@ -6273,13 +5985,13 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46138.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B279">
-        <v>2172.581</v>
+        <v>445.173</v>
       </c>
       <c r="C279">
-        <v>1834</v>
+        <v>0</v>
       </c>
       <c r="D279">
         <v>86</v>
@@ -6290,13 +6002,13 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46138.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B280">
-        <v>2107.458</v>
+        <v>442.81</v>
       </c>
       <c r="C280">
-        <v>1723</v>
+        <v>0</v>
       </c>
       <c r="D280">
         <v>87</v>
@@ -6307,13 +6019,13 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46138.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B281">
-        <v>2041.33</v>
+        <v>429.088</v>
       </c>
       <c r="C281">
-        <v>1639</v>
+        <v>0</v>
       </c>
       <c r="D281">
         <v>88</v>
@@ -6324,13 +6036,13 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46138.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B282">
-        <v>1932.647</v>
+        <v>448.858</v>
       </c>
       <c r="C282">
-        <v>1496</v>
+        <v>0</v>
       </c>
       <c r="D282">
         <v>89</v>
@@ -6341,13 +6053,13 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46138.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B283">
-        <v>1848.702</v>
+        <v>469.044</v>
       </c>
       <c r="C283">
-        <v>1356</v>
+        <v>0</v>
       </c>
       <c r="D283">
         <v>90</v>
@@ -6358,13 +6070,13 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46138.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B284">
-        <v>1763.583</v>
+        <v>489.697</v>
       </c>
       <c r="C284">
-        <v>1235</v>
+        <v>0</v>
       </c>
       <c r="D284">
         <v>91</v>
@@ -6375,13 +6087,13 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46138.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B285">
-        <v>1679.444</v>
+        <v>509.745</v>
       </c>
       <c r="C285">
-        <v>1136</v>
+        <v>0</v>
       </c>
       <c r="D285">
         <v>92</v>
@@ -6392,13 +6104,13 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="2">
-        <v>46138.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B286">
-        <v>1591.089</v>
+        <v>0</v>
       </c>
       <c r="C286">
-        <v>1078</v>
+        <v>0</v>
       </c>
       <c r="D286">
         <v>93</v>
@@ -6409,13 +6121,13 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="2">
-        <v>46138.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B287">
-        <v>1504.473</v>
+        <v>0</v>
       </c>
       <c r="C287">
-        <v>1055</v>
+        <v>0</v>
       </c>
       <c r="D287">
         <v>94</v>
@@ -6426,13 +6138,13 @@
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="2">
-        <v>46138.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B288">
-        <v>1414.221</v>
+        <v>0</v>
       </c>
       <c r="C288">
-        <v>1083</v>
+        <v>0</v>
       </c>
       <c r="D288">
         <v>95</v>
@@ -6443,1651 +6155,19 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="2">
-        <v>46138.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B289">
-        <v>1330.862</v>
+        <v>0</v>
       </c>
       <c r="C289">
-        <v>1127</v>
+        <v>0</v>
       </c>
       <c r="D289">
         <v>96</v>
       </c>
       <c r="E289" t="s">
         <v>292</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5">
-      <c r="A290" s="2">
-        <v>46139</v>
-      </c>
-      <c r="B290">
-        <v>1098.587</v>
-      </c>
-      <c r="C290">
-        <v>1192</v>
-      </c>
-      <c r="D290">
-        <v>1</v>
-      </c>
-      <c r="E290" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5">
-      <c r="A291" s="2">
-        <v>46139.01041666666</v>
-      </c>
-      <c r="B291">
-        <v>1049.537</v>
-      </c>
-      <c r="C291">
-        <v>1173</v>
-      </c>
-      <c r="D291">
-        <v>2</v>
-      </c>
-      <c r="E291" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5">
-      <c r="A292" s="2">
-        <v>46139.02083333334</v>
-      </c>
-      <c r="B292">
-        <v>996.675</v>
-      </c>
-      <c r="C292">
-        <v>1145</v>
-      </c>
-      <c r="D292">
-        <v>3</v>
-      </c>
-      <c r="E292" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5">
-      <c r="A293" s="2">
-        <v>46139.03125</v>
-      </c>
-      <c r="B293">
-        <v>995.662</v>
-      </c>
-      <c r="C293">
-        <v>1095</v>
-      </c>
-      <c r="D293">
-        <v>4</v>
-      </c>
-      <c r="E293" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5">
-      <c r="A294" s="2">
-        <v>46139.04166666666</v>
-      </c>
-      <c r="B294">
-        <v>924.468</v>
-      </c>
-      <c r="C294">
-        <v>1103</v>
-      </c>
-      <c r="D294">
-        <v>5</v>
-      </c>
-      <c r="E294" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5">
-      <c r="A295" s="2">
-        <v>46139.05208333334</v>
-      </c>
-      <c r="B295">
-        <v>913.903</v>
-      </c>
-      <c r="C295">
-        <v>1158</v>
-      </c>
-      <c r="D295">
-        <v>6</v>
-      </c>
-      <c r="E295" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5">
-      <c r="A296" s="2">
-        <v>46139.0625</v>
-      </c>
-      <c r="B296">
-        <v>902.963</v>
-      </c>
-      <c r="C296">
-        <v>1046</v>
-      </c>
-      <c r="D296">
-        <v>7</v>
-      </c>
-      <c r="E296" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5">
-      <c r="A297" s="2">
-        <v>46139.07291666666</v>
-      </c>
-      <c r="B297">
-        <v>874.16</v>
-      </c>
-      <c r="C297">
-        <v>1036</v>
-      </c>
-      <c r="D297">
-        <v>8</v>
-      </c>
-      <c r="E297" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5">
-      <c r="A298" s="2">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="B298">
-        <v>838.809</v>
-      </c>
-      <c r="C298">
-        <v>1146</v>
-      </c>
-      <c r="D298">
-        <v>9</v>
-      </c>
-      <c r="E298" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5">
-      <c r="A299" s="2">
-        <v>46139.09375</v>
-      </c>
-      <c r="B299">
-        <v>826.361</v>
-      </c>
-      <c r="C299">
-        <v>1148</v>
-      </c>
-      <c r="D299">
-        <v>10</v>
-      </c>
-      <c r="E299" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5">
-      <c r="A300" s="2">
-        <v>46139.10416666666</v>
-      </c>
-      <c r="B300">
-        <v>812.409</v>
-      </c>
-      <c r="C300">
-        <v>1019</v>
-      </c>
-      <c r="D300">
-        <v>11</v>
-      </c>
-      <c r="E300" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5">
-      <c r="A301" s="2">
-        <v>46139.11458333334</v>
-      </c>
-      <c r="B301">
-        <v>790.47</v>
-      </c>
-      <c r="C301">
-        <v>989</v>
-      </c>
-      <c r="D301">
-        <v>12</v>
-      </c>
-      <c r="E301" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5">
-      <c r="A302" s="2">
-        <v>46139.125</v>
-      </c>
-      <c r="B302">
-        <v>760.476</v>
-      </c>
-      <c r="C302">
-        <v>946</v>
-      </c>
-      <c r="D302">
-        <v>13</v>
-      </c>
-      <c r="E302" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5">
-      <c r="A303" s="2">
-        <v>46139.13541666666</v>
-      </c>
-      <c r="B303">
-        <v>769.836</v>
-      </c>
-      <c r="C303">
-        <v>931</v>
-      </c>
-      <c r="D303">
-        <v>14</v>
-      </c>
-      <c r="E303" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5">
-      <c r="A304" s="2">
-        <v>46139.14583333334</v>
-      </c>
-      <c r="B304">
-        <v>759.821</v>
-      </c>
-      <c r="C304">
-        <v>976</v>
-      </c>
-      <c r="D304">
-        <v>15</v>
-      </c>
-      <c r="E304" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5">
-      <c r="A305" s="2">
-        <v>46139.15625</v>
-      </c>
-      <c r="B305">
-        <v>725.421</v>
-      </c>
-      <c r="C305">
-        <v>909</v>
-      </c>
-      <c r="D305">
-        <v>16</v>
-      </c>
-      <c r="E305" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5">
-      <c r="A306" s="2">
-        <v>46139.16666666666</v>
-      </c>
-      <c r="B306">
-        <v>670.1420000000001</v>
-      </c>
-      <c r="C306">
-        <v>764</v>
-      </c>
-      <c r="D306">
-        <v>17</v>
-      </c>
-      <c r="E306" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5">
-      <c r="A307" s="2">
-        <v>46139.17708333334</v>
-      </c>
-      <c r="B307">
-        <v>649.968</v>
-      </c>
-      <c r="C307">
-        <v>701</v>
-      </c>
-      <c r="D307">
-        <v>18</v>
-      </c>
-      <c r="E307" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5">
-      <c r="A308" s="2">
-        <v>46139.1875</v>
-      </c>
-      <c r="B308">
-        <v>624.922</v>
-      </c>
-      <c r="C308">
-        <v>624</v>
-      </c>
-      <c r="D308">
-        <v>19</v>
-      </c>
-      <c r="E308" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5">
-      <c r="A309" s="2">
-        <v>46139.19791666666</v>
-      </c>
-      <c r="B309">
-        <v>611.199</v>
-      </c>
-      <c r="C309">
-        <v>591</v>
-      </c>
-      <c r="D309">
-        <v>20</v>
-      </c>
-      <c r="E309" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5">
-      <c r="A310" s="2">
-        <v>46139.20833333334</v>
-      </c>
-      <c r="B310">
-        <v>560.783</v>
-      </c>
-      <c r="C310">
-        <v>517</v>
-      </c>
-      <c r="D310">
-        <v>21</v>
-      </c>
-      <c r="E310" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5">
-      <c r="A311" s="2">
-        <v>46139.21875</v>
-      </c>
-      <c r="B311">
-        <v>528.7569999999999</v>
-      </c>
-      <c r="C311">
-        <v>528</v>
-      </c>
-      <c r="D311">
-        <v>22</v>
-      </c>
-      <c r="E311" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5">
-      <c r="A312" s="2">
-        <v>46139.22916666666</v>
-      </c>
-      <c r="B312">
-        <v>500.799</v>
-      </c>
-      <c r="C312">
-        <v>497</v>
-      </c>
-      <c r="D312">
-        <v>23</v>
-      </c>
-      <c r="E312" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5">
-      <c r="A313" s="2">
-        <v>46139.23958333334</v>
-      </c>
-      <c r="B313">
-        <v>466.528</v>
-      </c>
-      <c r="C313">
-        <v>453</v>
-      </c>
-      <c r="D313">
-        <v>24</v>
-      </c>
-      <c r="E313" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5">
-      <c r="A314" s="2">
-        <v>46139.25</v>
-      </c>
-      <c r="B314">
-        <v>385.067</v>
-      </c>
-      <c r="C314">
-        <v>384</v>
-      </c>
-      <c r="D314">
-        <v>25</v>
-      </c>
-      <c r="E314" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5">
-      <c r="A315" s="2">
-        <v>46139.26041666666</v>
-      </c>
-      <c r="B315">
-        <v>364.182</v>
-      </c>
-      <c r="C315">
-        <v>332</v>
-      </c>
-      <c r="D315">
-        <v>26</v>
-      </c>
-      <c r="E315" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5">
-      <c r="A316" s="2">
-        <v>46139.27083333334</v>
-      </c>
-      <c r="B316">
-        <v>351.931</v>
-      </c>
-      <c r="C316">
-        <v>281</v>
-      </c>
-      <c r="D316">
-        <v>27</v>
-      </c>
-      <c r="E316" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5">
-      <c r="A317" s="2">
-        <v>46139.28125</v>
-      </c>
-      <c r="B317">
-        <v>333.269</v>
-      </c>
-      <c r="C317">
-        <v>248</v>
-      </c>
-      <c r="D317">
-        <v>28</v>
-      </c>
-      <c r="E317" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5">
-      <c r="A318" s="2">
-        <v>46139.29166666666</v>
-      </c>
-      <c r="B318">
-        <v>306.711</v>
-      </c>
-      <c r="C318">
-        <v>210</v>
-      </c>
-      <c r="D318">
-        <v>29</v>
-      </c>
-      <c r="E318" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5">
-      <c r="A319" s="2">
-        <v>46139.30208333334</v>
-      </c>
-      <c r="B319">
-        <v>314.599</v>
-      </c>
-      <c r="C319">
-        <v>194</v>
-      </c>
-      <c r="D319">
-        <v>30</v>
-      </c>
-      <c r="E319" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5">
-      <c r="A320" s="2">
-        <v>46139.3125</v>
-      </c>
-      <c r="B320">
-        <v>312.717</v>
-      </c>
-      <c r="C320">
-        <v>0</v>
-      </c>
-      <c r="D320">
-        <v>31</v>
-      </c>
-      <c r="E320" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5">
-      <c r="A321" s="2">
-        <v>46139.32291666666</v>
-      </c>
-      <c r="B321">
-        <v>302.537</v>
-      </c>
-      <c r="C321">
-        <v>195</v>
-      </c>
-      <c r="D321">
-        <v>32</v>
-      </c>
-      <c r="E321" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5">
-      <c r="A322" s="2">
-        <v>46139.33333333334</v>
-      </c>
-      <c r="B322">
-        <v>329.192</v>
-      </c>
-      <c r="C322">
-        <v>224</v>
-      </c>
-      <c r="D322">
-        <v>33</v>
-      </c>
-      <c r="E322" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
-      <c r="A323" s="2">
-        <v>46139.34375</v>
-      </c>
-      <c r="B323">
-        <v>322.348</v>
-      </c>
-      <c r="C323">
-        <v>214</v>
-      </c>
-      <c r="D323">
-        <v>34</v>
-      </c>
-      <c r="E323" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5">
-      <c r="A324" s="2">
-        <v>46139.35416666666</v>
-      </c>
-      <c r="B324">
-        <v>321.427</v>
-      </c>
-      <c r="C324">
-        <v>199</v>
-      </c>
-      <c r="D324">
-        <v>35</v>
-      </c>
-      <c r="E324" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5">
-      <c r="A325" s="2">
-        <v>46139.36458333334</v>
-      </c>
-      <c r="B325">
-        <v>316.179</v>
-      </c>
-      <c r="C325">
-        <v>173</v>
-      </c>
-      <c r="D325">
-        <v>36</v>
-      </c>
-      <c r="E325" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5">
-      <c r="A326" s="2">
-        <v>46139.375</v>
-      </c>
-      <c r="B326">
-        <v>322.345</v>
-      </c>
-      <c r="C326">
-        <v>137</v>
-      </c>
-      <c r="D326">
-        <v>37</v>
-      </c>
-      <c r="E326" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5">
-      <c r="A327" s="2">
-        <v>46139.38541666666</v>
-      </c>
-      <c r="B327">
-        <v>306.786</v>
-      </c>
-      <c r="C327">
-        <v>118</v>
-      </c>
-      <c r="D327">
-        <v>38</v>
-      </c>
-      <c r="E327" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5">
-      <c r="A328" s="2">
-        <v>46139.39583333334</v>
-      </c>
-      <c r="B328">
-        <v>290.984</v>
-      </c>
-      <c r="C328">
-        <v>114</v>
-      </c>
-      <c r="D328">
-        <v>39</v>
-      </c>
-      <c r="E328" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5">
-      <c r="A329" s="2">
-        <v>46139.40625</v>
-      </c>
-      <c r="B329">
-        <v>275.459</v>
-      </c>
-      <c r="C329">
-        <v>116</v>
-      </c>
-      <c r="D329">
-        <v>40</v>
-      </c>
-      <c r="E329" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5">
-      <c r="A330" s="2">
-        <v>46139.41666666666</v>
-      </c>
-      <c r="B330">
-        <v>277.774</v>
-      </c>
-      <c r="C330">
-        <v>117</v>
-      </c>
-      <c r="D330">
-        <v>41</v>
-      </c>
-      <c r="E330" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5">
-      <c r="A331" s="2">
-        <v>46139.42708333334</v>
-      </c>
-      <c r="B331">
-        <v>266.334</v>
-      </c>
-      <c r="C331">
-        <v>111</v>
-      </c>
-      <c r="D331">
-        <v>42</v>
-      </c>
-      <c r="E331" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5">
-      <c r="A332" s="2">
-        <v>46139.4375</v>
-      </c>
-      <c r="B332">
-        <v>255.004</v>
-      </c>
-      <c r="C332">
-        <v>105</v>
-      </c>
-      <c r="D332">
-        <v>43</v>
-      </c>
-      <c r="E332" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5">
-      <c r="A333" s="2">
-        <v>46139.44791666666</v>
-      </c>
-      <c r="B333">
-        <v>244.57</v>
-      </c>
-      <c r="C333">
-        <v>95</v>
-      </c>
-      <c r="D333">
-        <v>44</v>
-      </c>
-      <c r="E333" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5">
-      <c r="A334" s="2">
-        <v>46139.45833333334</v>
-      </c>
-      <c r="B334">
-        <v>199.082</v>
-      </c>
-      <c r="C334">
-        <v>72</v>
-      </c>
-      <c r="D334">
-        <v>45</v>
-      </c>
-      <c r="E334" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5">
-      <c r="A335" s="2">
-        <v>46139.46875</v>
-      </c>
-      <c r="B335">
-        <v>181.206</v>
-      </c>
-      <c r="C335">
-        <v>0</v>
-      </c>
-      <c r="D335">
-        <v>46</v>
-      </c>
-      <c r="E335" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5">
-      <c r="A336" s="2">
-        <v>46139.47916666666</v>
-      </c>
-      <c r="B336">
-        <v>169.225</v>
-      </c>
-      <c r="C336">
-        <v>0</v>
-      </c>
-      <c r="D336">
-        <v>47</v>
-      </c>
-      <c r="E336" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5">
-      <c r="A337" s="2">
-        <v>46139.48958333334</v>
-      </c>
-      <c r="B337">
-        <v>164.601</v>
-      </c>
-      <c r="C337">
-        <v>0</v>
-      </c>
-      <c r="D337">
-        <v>48</v>
-      </c>
-      <c r="E337" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5">
-      <c r="A338" s="2">
-        <v>46139.5</v>
-      </c>
-      <c r="B338">
-        <v>171.219</v>
-      </c>
-      <c r="C338">
-        <v>0</v>
-      </c>
-      <c r="D338">
-        <v>49</v>
-      </c>
-      <c r="E338" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5">
-      <c r="A339" s="2">
-        <v>46139.51041666666</v>
-      </c>
-      <c r="B339">
-        <v>173</v>
-      </c>
-      <c r="C339">
-        <v>0</v>
-      </c>
-      <c r="D339">
-        <v>50</v>
-      </c>
-      <c r="E339" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5">
-      <c r="A340" s="2">
-        <v>46139.52083333334</v>
-      </c>
-      <c r="B340">
-        <v>174.979</v>
-      </c>
-      <c r="C340">
-        <v>0</v>
-      </c>
-      <c r="D340">
-        <v>51</v>
-      </c>
-      <c r="E340" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5">
-      <c r="A341" s="2">
-        <v>46139.53125</v>
-      </c>
-      <c r="B341">
-        <v>176.989</v>
-      </c>
-      <c r="C341">
-        <v>0</v>
-      </c>
-      <c r="D341">
-        <v>52</v>
-      </c>
-      <c r="E341" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5">
-      <c r="A342" s="2">
-        <v>46139.54166666666</v>
-      </c>
-      <c r="B342">
-        <v>183.538</v>
-      </c>
-      <c r="C342">
-        <v>0</v>
-      </c>
-      <c r="D342">
-        <v>53</v>
-      </c>
-      <c r="E342" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5">
-      <c r="A343" s="2">
-        <v>46139.55208333334</v>
-      </c>
-      <c r="B343">
-        <v>189.984</v>
-      </c>
-      <c r="C343">
-        <v>0</v>
-      </c>
-      <c r="D343">
-        <v>54</v>
-      </c>
-      <c r="E343" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5">
-      <c r="A344" s="2">
-        <v>46139.5625</v>
-      </c>
-      <c r="B344">
-        <v>195.538</v>
-      </c>
-      <c r="C344">
-        <v>0</v>
-      </c>
-      <c r="D344">
-        <v>55</v>
-      </c>
-      <c r="E344" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5">
-      <c r="A345" s="2">
-        <v>46139.57291666666</v>
-      </c>
-      <c r="B345">
-        <v>202.743</v>
-      </c>
-      <c r="C345">
-        <v>0</v>
-      </c>
-      <c r="D345">
-        <v>56</v>
-      </c>
-      <c r="E345" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5">
-      <c r="A346" s="2">
-        <v>46139.58333333334</v>
-      </c>
-      <c r="B346">
-        <v>218.684</v>
-      </c>
-      <c r="C346">
-        <v>0</v>
-      </c>
-      <c r="D346">
-        <v>57</v>
-      </c>
-      <c r="E346" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5">
-      <c r="A347" s="2">
-        <v>46139.59375</v>
-      </c>
-      <c r="B347">
-        <v>245.462</v>
-      </c>
-      <c r="C347">
-        <v>0</v>
-      </c>
-      <c r="D347">
-        <v>58</v>
-      </c>
-      <c r="E347" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5">
-      <c r="A348" s="2">
-        <v>46139.60416666666</v>
-      </c>
-      <c r="B348">
-        <v>271.293</v>
-      </c>
-      <c r="C348">
-        <v>0</v>
-      </c>
-      <c r="D348">
-        <v>59</v>
-      </c>
-      <c r="E348" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5">
-      <c r="A349" s="2">
-        <v>46139.61458333334</v>
-      </c>
-      <c r="B349">
-        <v>297.991</v>
-      </c>
-      <c r="C349">
-        <v>0</v>
-      </c>
-      <c r="D349">
-        <v>60</v>
-      </c>
-      <c r="E349" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5">
-      <c r="A350" s="2">
-        <v>46139.625</v>
-      </c>
-      <c r="B350">
-        <v>294.546</v>
-      </c>
-      <c r="C350">
-        <v>0</v>
-      </c>
-      <c r="D350">
-        <v>61</v>
-      </c>
-      <c r="E350" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5">
-      <c r="A351" s="2">
-        <v>46139.63541666666</v>
-      </c>
-      <c r="B351">
-        <v>324.271</v>
-      </c>
-      <c r="C351">
-        <v>0</v>
-      </c>
-      <c r="D351">
-        <v>62</v>
-      </c>
-      <c r="E351" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5">
-      <c r="A352" s="2">
-        <v>46139.64583333334</v>
-      </c>
-      <c r="B352">
-        <v>355.158</v>
-      </c>
-      <c r="C352">
-        <v>0</v>
-      </c>
-      <c r="D352">
-        <v>63</v>
-      </c>
-      <c r="E352" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5">
-      <c r="A353" s="2">
-        <v>46139.65625</v>
-      </c>
-      <c r="B353">
-        <v>408.287</v>
-      </c>
-      <c r="C353">
-        <v>0</v>
-      </c>
-      <c r="D353">
-        <v>64</v>
-      </c>
-      <c r="E353" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5">
-      <c r="A354" s="2">
-        <v>46139.66666666666</v>
-      </c>
-      <c r="B354">
-        <v>435.06</v>
-      </c>
-      <c r="C354">
-        <v>0</v>
-      </c>
-      <c r="D354">
-        <v>65</v>
-      </c>
-      <c r="E354" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5">
-      <c r="A355" s="2">
-        <v>46139.67708333334</v>
-      </c>
-      <c r="B355">
-        <v>473.326</v>
-      </c>
-      <c r="C355">
-        <v>0</v>
-      </c>
-      <c r="D355">
-        <v>66</v>
-      </c>
-      <c r="E355" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5">
-      <c r="A356" s="2">
-        <v>46139.6875</v>
-      </c>
-      <c r="B356">
-        <v>509.229</v>
-      </c>
-      <c r="C356">
-        <v>0</v>
-      </c>
-      <c r="D356">
-        <v>67</v>
-      </c>
-      <c r="E356" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5">
-      <c r="A357" s="2">
-        <v>46139.69791666666</v>
-      </c>
-      <c r="B357">
-        <v>544.872</v>
-      </c>
-      <c r="C357">
-        <v>0</v>
-      </c>
-      <c r="D357">
-        <v>68</v>
-      </c>
-      <c r="E357" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5">
-      <c r="A358" s="2">
-        <v>46139.70833333334</v>
-      </c>
-      <c r="B358">
-        <v>549.2140000000001</v>
-      </c>
-      <c r="C358">
-        <v>0</v>
-      </c>
-      <c r="D358">
-        <v>69</v>
-      </c>
-      <c r="E358" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5">
-      <c r="A359" s="2">
-        <v>46139.71875</v>
-      </c>
-      <c r="B359">
-        <v>590.837</v>
-      </c>
-      <c r="C359">
-        <v>0</v>
-      </c>
-      <c r="D359">
-        <v>70</v>
-      </c>
-      <c r="E359" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5">
-      <c r="A360" s="2">
-        <v>46139.72916666666</v>
-      </c>
-      <c r="B360">
-        <v>634.539</v>
-      </c>
-      <c r="C360">
-        <v>0</v>
-      </c>
-      <c r="D360">
-        <v>71</v>
-      </c>
-      <c r="E360" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5">
-      <c r="A361" s="2">
-        <v>46139.73958333334</v>
-      </c>
-      <c r="B361">
-        <v>678.954</v>
-      </c>
-      <c r="C361">
-        <v>0</v>
-      </c>
-      <c r="D361">
-        <v>72</v>
-      </c>
-      <c r="E361" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5">
-      <c r="A362" s="2">
-        <v>46139.75</v>
-      </c>
-      <c r="B362">
-        <v>751.826</v>
-      </c>
-      <c r="C362">
-        <v>0</v>
-      </c>
-      <c r="D362">
-        <v>73</v>
-      </c>
-      <c r="E362" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5">
-      <c r="A363" s="2">
-        <v>46139.76041666666</v>
-      </c>
-      <c r="B363">
-        <v>810.625</v>
-      </c>
-      <c r="C363">
-        <v>0</v>
-      </c>
-      <c r="D363">
-        <v>74</v>
-      </c>
-      <c r="E363" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5">
-      <c r="A364" s="2">
-        <v>46139.77083333334</v>
-      </c>
-      <c r="B364">
-        <v>871.121</v>
-      </c>
-      <c r="C364">
-        <v>0</v>
-      </c>
-      <c r="D364">
-        <v>75</v>
-      </c>
-      <c r="E364" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5">
-      <c r="A365" s="2">
-        <v>46139.78125</v>
-      </c>
-      <c r="B365">
-        <v>931.152</v>
-      </c>
-      <c r="C365">
-        <v>0</v>
-      </c>
-      <c r="D365">
-        <v>76</v>
-      </c>
-      <c r="E365" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5">
-      <c r="A366" s="2">
-        <v>46139.79166666666</v>
-      </c>
-      <c r="B366">
-        <v>1014.763</v>
-      </c>
-      <c r="C366">
-        <v>0</v>
-      </c>
-      <c r="D366">
-        <v>77</v>
-      </c>
-      <c r="E366" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5">
-      <c r="A367" s="2">
-        <v>46139.80208333334</v>
-      </c>
-      <c r="B367">
-        <v>1076.04</v>
-      </c>
-      <c r="C367">
-        <v>0</v>
-      </c>
-      <c r="D367">
-        <v>78</v>
-      </c>
-      <c r="E367" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5">
-      <c r="A368" s="2">
-        <v>46139.8125</v>
-      </c>
-      <c r="B368">
-        <v>1140.012</v>
-      </c>
-      <c r="C368">
-        <v>0</v>
-      </c>
-      <c r="D368">
-        <v>79</v>
-      </c>
-      <c r="E368" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5">
-      <c r="A369" s="2">
-        <v>46139.82291666666</v>
-      </c>
-      <c r="B369">
-        <v>1200.132</v>
-      </c>
-      <c r="C369">
-        <v>0</v>
-      </c>
-      <c r="D369">
-        <v>80</v>
-      </c>
-      <c r="E369" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5">
-      <c r="A370" s="2">
-        <v>46139.83333333334</v>
-      </c>
-      <c r="B370">
-        <v>1271.342</v>
-      </c>
-      <c r="C370">
-        <v>0</v>
-      </c>
-      <c r="D370">
-        <v>81</v>
-      </c>
-      <c r="E370" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5">
-      <c r="A371" s="2">
-        <v>46139.84375</v>
-      </c>
-      <c r="B371">
-        <v>1292.747</v>
-      </c>
-      <c r="C371">
-        <v>0</v>
-      </c>
-      <c r="D371">
-        <v>82</v>
-      </c>
-      <c r="E371" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5">
-      <c r="A372" s="2">
-        <v>46139.85416666666</v>
-      </c>
-      <c r="B372">
-        <v>1311.048</v>
-      </c>
-      <c r="C372">
-        <v>0</v>
-      </c>
-      <c r="D372">
-        <v>83</v>
-      </c>
-      <c r="E372" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5">
-      <c r="A373" s="2">
-        <v>46139.86458333334</v>
-      </c>
-      <c r="B373">
-        <v>1331.301</v>
-      </c>
-      <c r="C373">
-        <v>0</v>
-      </c>
-      <c r="D373">
-        <v>84</v>
-      </c>
-      <c r="E373" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5">
-      <c r="A374" s="2">
-        <v>46139.875</v>
-      </c>
-      <c r="B374">
-        <v>1345.363</v>
-      </c>
-      <c r="C374">
-        <v>0</v>
-      </c>
-      <c r="D374">
-        <v>85</v>
-      </c>
-      <c r="E374" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5">
-      <c r="A375" s="2">
-        <v>46139.88541666666</v>
-      </c>
-      <c r="B375">
-        <v>1340.855</v>
-      </c>
-      <c r="C375">
-        <v>0</v>
-      </c>
-      <c r="D375">
-        <v>86</v>
-      </c>
-      <c r="E375" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5">
-      <c r="A376" s="2">
-        <v>46139.89583333334</v>
-      </c>
-      <c r="B376">
-        <v>1338.817</v>
-      </c>
-      <c r="C376">
-        <v>0</v>
-      </c>
-      <c r="D376">
-        <v>87</v>
-      </c>
-      <c r="E376" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5">
-      <c r="A377" s="2">
-        <v>46139.90625</v>
-      </c>
-      <c r="B377">
-        <v>1336.875</v>
-      </c>
-      <c r="C377">
-        <v>0</v>
-      </c>
-      <c r="D377">
-        <v>88</v>
-      </c>
-      <c r="E377" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5">
-      <c r="A378" s="2">
-        <v>46139.91666666666</v>
-      </c>
-      <c r="B378">
-        <v>1321.734</v>
-      </c>
-      <c r="C378">
-        <v>0</v>
-      </c>
-      <c r="D378">
-        <v>89</v>
-      </c>
-      <c r="E378" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5">
-      <c r="A379" s="2">
-        <v>46139.92708333334</v>
-      </c>
-      <c r="B379">
-        <v>1307.586</v>
-      </c>
-      <c r="C379">
-        <v>0</v>
-      </c>
-      <c r="D379">
-        <v>90</v>
-      </c>
-      <c r="E379" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5">
-      <c r="A380" s="2">
-        <v>46139.9375</v>
-      </c>
-      <c r="B380">
-        <v>1294</v>
-      </c>
-      <c r="C380">
-        <v>0</v>
-      </c>
-      <c r="D380">
-        <v>91</v>
-      </c>
-      <c r="E380" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5">
-      <c r="A381" s="2">
-        <v>46139.94791666666</v>
-      </c>
-      <c r="B381">
-        <v>1278.48</v>
-      </c>
-      <c r="C381">
-        <v>0</v>
-      </c>
-      <c r="D381">
-        <v>92</v>
-      </c>
-      <c r="E381" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5">
-      <c r="A382" s="2">
-        <v>46139.95833333334</v>
-      </c>
-      <c r="B382">
-        <v>0</v>
-      </c>
-      <c r="C382">
-        <v>0</v>
-      </c>
-      <c r="D382">
-        <v>93</v>
-      </c>
-      <c r="E382" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5">
-      <c r="A383" s="2">
-        <v>46139.96875</v>
-      </c>
-      <c r="B383">
-        <v>0</v>
-      </c>
-      <c r="C383">
-        <v>0</v>
-      </c>
-      <c r="D383">
-        <v>94</v>
-      </c>
-      <c r="E383" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5">
-      <c r="A384" s="2">
-        <v>46139.97916666666</v>
-      </c>
-      <c r="B384">
-        <v>0</v>
-      </c>
-      <c r="C384">
-        <v>0</v>
-      </c>
-      <c r="D384">
-        <v>95</v>
-      </c>
-      <c r="E384" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5">
-      <c r="A385" s="2">
-        <v>46139.98958333334</v>
-      </c>
-      <c r="B385">
-        <v>0</v>
-      </c>
-      <c r="C385">
-        <v>0</v>
-      </c>
-      <c r="D385">
-        <v>96</v>
-      </c>
-      <c r="E385" t="s">
-        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,582 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.04.20261</t>
-  </si>
-  <si>
-    <t>28.04.20262</t>
-  </si>
-  <si>
-    <t>28.04.20263</t>
-  </si>
-  <si>
-    <t>28.04.20264</t>
-  </si>
-  <si>
-    <t>28.04.20265</t>
-  </si>
-  <si>
-    <t>28.04.20266</t>
-  </si>
-  <si>
-    <t>28.04.20267</t>
-  </si>
-  <si>
-    <t>28.04.20268</t>
-  </si>
-  <si>
-    <t>28.04.20269</t>
-  </si>
-  <si>
-    <t>28.04.202610</t>
-  </si>
-  <si>
-    <t>28.04.202611</t>
-  </si>
-  <si>
-    <t>28.04.202612</t>
-  </si>
-  <si>
-    <t>28.04.202613</t>
-  </si>
-  <si>
-    <t>28.04.202614</t>
-  </si>
-  <si>
-    <t>28.04.202615</t>
-  </si>
-  <si>
-    <t>28.04.202616</t>
-  </si>
-  <si>
-    <t>28.04.202617</t>
-  </si>
-  <si>
-    <t>28.04.202618</t>
-  </si>
-  <si>
-    <t>28.04.202619</t>
-  </si>
-  <si>
-    <t>28.04.202620</t>
-  </si>
-  <si>
-    <t>28.04.202621</t>
-  </si>
-  <si>
-    <t>28.04.202622</t>
-  </si>
-  <si>
-    <t>28.04.202623</t>
-  </si>
-  <si>
-    <t>28.04.202624</t>
-  </si>
-  <si>
-    <t>28.04.202625</t>
-  </si>
-  <si>
-    <t>28.04.202626</t>
-  </si>
-  <si>
-    <t>28.04.202627</t>
-  </si>
-  <si>
-    <t>28.04.202628</t>
-  </si>
-  <si>
-    <t>28.04.202629</t>
-  </si>
-  <si>
-    <t>28.04.202630</t>
-  </si>
-  <si>
-    <t>28.04.202631</t>
-  </si>
-  <si>
-    <t>28.04.202632</t>
-  </si>
-  <si>
-    <t>28.04.202633</t>
-  </si>
-  <si>
-    <t>28.04.202634</t>
-  </si>
-  <si>
-    <t>28.04.202635</t>
-  </si>
-  <si>
-    <t>28.04.202636</t>
-  </si>
-  <si>
-    <t>28.04.202637</t>
-  </si>
-  <si>
-    <t>28.04.202638</t>
-  </si>
-  <si>
-    <t>28.04.202639</t>
-  </si>
-  <si>
-    <t>28.04.202640</t>
-  </si>
-  <si>
-    <t>28.04.202641</t>
-  </si>
-  <si>
-    <t>28.04.202642</t>
-  </si>
-  <si>
-    <t>28.04.202643</t>
-  </si>
-  <si>
-    <t>28.04.202644</t>
-  </si>
-  <si>
-    <t>28.04.202645</t>
-  </si>
-  <si>
-    <t>28.04.202646</t>
-  </si>
-  <si>
-    <t>28.04.202647</t>
-  </si>
-  <si>
-    <t>28.04.202648</t>
-  </si>
-  <si>
-    <t>28.04.202649</t>
-  </si>
-  <si>
-    <t>28.04.202650</t>
-  </si>
-  <si>
-    <t>28.04.202651</t>
-  </si>
-  <si>
-    <t>28.04.202652</t>
-  </si>
-  <si>
-    <t>28.04.202653</t>
-  </si>
-  <si>
-    <t>28.04.202654</t>
-  </si>
-  <si>
-    <t>28.04.202655</t>
-  </si>
-  <si>
-    <t>28.04.202656</t>
-  </si>
-  <si>
-    <t>28.04.202657</t>
-  </si>
-  <si>
-    <t>28.04.202658</t>
-  </si>
-  <si>
-    <t>28.04.202659</t>
-  </si>
-  <si>
-    <t>28.04.202660</t>
-  </si>
-  <si>
-    <t>28.04.202661</t>
-  </si>
-  <si>
-    <t>28.04.202662</t>
-  </si>
-  <si>
-    <t>28.04.202663</t>
-  </si>
-  <si>
-    <t>28.04.202664</t>
-  </si>
-  <si>
-    <t>28.04.202665</t>
-  </si>
-  <si>
-    <t>28.04.202666</t>
-  </si>
-  <si>
-    <t>28.04.202667</t>
-  </si>
-  <si>
-    <t>28.04.202668</t>
-  </si>
-  <si>
-    <t>28.04.202669</t>
-  </si>
-  <si>
-    <t>28.04.202670</t>
-  </si>
-  <si>
-    <t>28.04.202671</t>
-  </si>
-  <si>
-    <t>28.04.202672</t>
-  </si>
-  <si>
-    <t>28.04.202673</t>
-  </si>
-  <si>
-    <t>28.04.202674</t>
-  </si>
-  <si>
-    <t>28.04.202675</t>
-  </si>
-  <si>
-    <t>28.04.202676</t>
-  </si>
-  <si>
-    <t>28.04.202677</t>
-  </si>
-  <si>
-    <t>28.04.202678</t>
-  </si>
-  <si>
-    <t>28.04.202679</t>
-  </si>
-  <si>
-    <t>28.04.202680</t>
-  </si>
-  <si>
-    <t>28.04.202681</t>
-  </si>
-  <si>
-    <t>28.04.202682</t>
-  </si>
-  <si>
-    <t>28.04.202683</t>
-  </si>
-  <si>
-    <t>28.04.202684</t>
-  </si>
-  <si>
-    <t>28.04.202685</t>
-  </si>
-  <si>
-    <t>28.04.202686</t>
-  </si>
-  <si>
-    <t>28.04.202687</t>
-  </si>
-  <si>
-    <t>28.04.202688</t>
-  </si>
-  <si>
-    <t>28.04.202689</t>
-  </si>
-  <si>
-    <t>28.04.202690</t>
-  </si>
-  <si>
-    <t>28.04.202691</t>
-  </si>
-  <si>
-    <t>28.04.202692</t>
-  </si>
-  <si>
-    <t>28.04.202693</t>
-  </si>
-  <si>
-    <t>28.04.202694</t>
-  </si>
-  <si>
-    <t>28.04.202695</t>
-  </si>
-  <si>
-    <t>28.04.202696</t>
-  </si>
-  <si>
-    <t>29.04.20261</t>
-  </si>
-  <si>
-    <t>29.04.20262</t>
-  </si>
-  <si>
-    <t>29.04.20263</t>
-  </si>
-  <si>
-    <t>29.04.20264</t>
-  </si>
-  <si>
-    <t>29.04.20265</t>
-  </si>
-  <si>
-    <t>29.04.20266</t>
-  </si>
-  <si>
-    <t>29.04.20267</t>
-  </si>
-  <si>
-    <t>29.04.20268</t>
-  </si>
-  <si>
-    <t>29.04.20269</t>
-  </si>
-  <si>
-    <t>29.04.202610</t>
-  </si>
-  <si>
-    <t>29.04.202611</t>
-  </si>
-  <si>
-    <t>29.04.202612</t>
-  </si>
-  <si>
-    <t>29.04.202613</t>
-  </si>
-  <si>
-    <t>29.04.202614</t>
-  </si>
-  <si>
-    <t>29.04.202615</t>
-  </si>
-  <si>
-    <t>29.04.202616</t>
-  </si>
-  <si>
-    <t>29.04.202617</t>
-  </si>
-  <si>
-    <t>29.04.202618</t>
-  </si>
-  <si>
-    <t>29.04.202619</t>
-  </si>
-  <si>
-    <t>29.04.202620</t>
-  </si>
-  <si>
-    <t>29.04.202621</t>
-  </si>
-  <si>
-    <t>29.04.202622</t>
-  </si>
-  <si>
-    <t>29.04.202623</t>
-  </si>
-  <si>
-    <t>29.04.202624</t>
-  </si>
-  <si>
-    <t>29.04.202625</t>
-  </si>
-  <si>
-    <t>29.04.202626</t>
-  </si>
-  <si>
-    <t>29.04.202627</t>
-  </si>
-  <si>
-    <t>29.04.202628</t>
-  </si>
-  <si>
-    <t>29.04.202629</t>
-  </si>
-  <si>
-    <t>29.04.202630</t>
-  </si>
-  <si>
-    <t>29.04.202631</t>
-  </si>
-  <si>
-    <t>29.04.202632</t>
-  </si>
-  <si>
-    <t>29.04.202633</t>
-  </si>
-  <si>
-    <t>29.04.202634</t>
-  </si>
-  <si>
-    <t>29.04.202635</t>
-  </si>
-  <si>
-    <t>29.04.202636</t>
-  </si>
-  <si>
-    <t>29.04.202637</t>
-  </si>
-  <si>
-    <t>29.04.202638</t>
-  </si>
-  <si>
-    <t>29.04.202639</t>
-  </si>
-  <si>
-    <t>29.04.202640</t>
-  </si>
-  <si>
-    <t>29.04.202641</t>
-  </si>
-  <si>
-    <t>29.04.202642</t>
-  </si>
-  <si>
-    <t>29.04.202643</t>
-  </si>
-  <si>
-    <t>29.04.202644</t>
-  </si>
-  <si>
-    <t>29.04.202645</t>
-  </si>
-  <si>
-    <t>29.04.202646</t>
-  </si>
-  <si>
-    <t>29.04.202647</t>
-  </si>
-  <si>
-    <t>29.04.202648</t>
-  </si>
-  <si>
-    <t>29.04.202649</t>
-  </si>
-  <si>
-    <t>29.04.202650</t>
-  </si>
-  <si>
-    <t>29.04.202651</t>
-  </si>
-  <si>
-    <t>29.04.202652</t>
-  </si>
-  <si>
-    <t>29.04.202653</t>
-  </si>
-  <si>
-    <t>29.04.202654</t>
-  </si>
-  <si>
-    <t>29.04.202655</t>
-  </si>
-  <si>
-    <t>29.04.202656</t>
-  </si>
-  <si>
-    <t>29.04.202657</t>
-  </si>
-  <si>
-    <t>29.04.202658</t>
-  </si>
-  <si>
-    <t>29.04.202659</t>
-  </si>
-  <si>
-    <t>29.04.202660</t>
-  </si>
-  <si>
-    <t>29.04.202661</t>
-  </si>
-  <si>
-    <t>29.04.202662</t>
-  </si>
-  <si>
-    <t>29.04.202663</t>
-  </si>
-  <si>
-    <t>29.04.202664</t>
-  </si>
-  <si>
-    <t>29.04.202665</t>
-  </si>
-  <si>
-    <t>29.04.202666</t>
-  </si>
-  <si>
-    <t>29.04.202667</t>
-  </si>
-  <si>
-    <t>29.04.202668</t>
-  </si>
-  <si>
-    <t>29.04.202669</t>
-  </si>
-  <si>
-    <t>29.04.202670</t>
-  </si>
-  <si>
-    <t>29.04.202671</t>
-  </si>
-  <si>
-    <t>29.04.202672</t>
-  </si>
-  <si>
-    <t>29.04.202673</t>
-  </si>
-  <si>
-    <t>29.04.202674</t>
-  </si>
-  <si>
-    <t>29.04.202675</t>
-  </si>
-  <si>
-    <t>29.04.202676</t>
-  </si>
-  <si>
-    <t>29.04.202677</t>
-  </si>
-  <si>
-    <t>29.04.202678</t>
-  </si>
-  <si>
-    <t>29.04.202679</t>
-  </si>
-  <si>
-    <t>29.04.202680</t>
-  </si>
-  <si>
-    <t>29.04.202681</t>
-  </si>
-  <si>
-    <t>29.04.202682</t>
-  </si>
-  <si>
-    <t>29.04.202683</t>
-  </si>
-  <si>
-    <t>29.04.202684</t>
-  </si>
-  <si>
-    <t>29.04.202685</t>
-  </si>
-  <si>
-    <t>29.04.202686</t>
-  </si>
-  <si>
-    <t>29.04.202687</t>
-  </si>
-  <si>
-    <t>29.04.202688</t>
-  </si>
-  <si>
-    <t>29.04.202689</t>
-  </si>
-  <si>
-    <t>29.04.202690</t>
-  </si>
-  <si>
-    <t>29.04.202691</t>
-  </si>
-  <si>
-    <t>29.04.202692</t>
-  </si>
-  <si>
-    <t>29.04.202693</t>
-  </si>
-  <si>
-    <t>29.04.202694</t>
-  </si>
-  <si>
-    <t>29.04.202695</t>
-  </si>
-  <si>
-    <t>29.04.202696</t>
-  </si>
-  <si>
     <t>30.04.20261</t>
   </si>
   <si>
@@ -893,6 +317,1158 @@
   </si>
   <si>
     <t>30.04.202696</t>
+  </si>
+  <si>
+    <t>01.05.20261</t>
+  </si>
+  <si>
+    <t>01.05.20262</t>
+  </si>
+  <si>
+    <t>01.05.20263</t>
+  </si>
+  <si>
+    <t>01.05.20264</t>
+  </si>
+  <si>
+    <t>01.05.20265</t>
+  </si>
+  <si>
+    <t>01.05.20266</t>
+  </si>
+  <si>
+    <t>01.05.20267</t>
+  </si>
+  <si>
+    <t>01.05.20268</t>
+  </si>
+  <si>
+    <t>01.05.20269</t>
+  </si>
+  <si>
+    <t>01.05.202610</t>
+  </si>
+  <si>
+    <t>01.05.202611</t>
+  </si>
+  <si>
+    <t>01.05.202612</t>
+  </si>
+  <si>
+    <t>01.05.202613</t>
+  </si>
+  <si>
+    <t>01.05.202614</t>
+  </si>
+  <si>
+    <t>01.05.202615</t>
+  </si>
+  <si>
+    <t>01.05.202616</t>
+  </si>
+  <si>
+    <t>01.05.202617</t>
+  </si>
+  <si>
+    <t>01.05.202618</t>
+  </si>
+  <si>
+    <t>01.05.202619</t>
+  </si>
+  <si>
+    <t>01.05.202620</t>
+  </si>
+  <si>
+    <t>01.05.202621</t>
+  </si>
+  <si>
+    <t>01.05.202622</t>
+  </si>
+  <si>
+    <t>01.05.202623</t>
+  </si>
+  <si>
+    <t>01.05.202624</t>
+  </si>
+  <si>
+    <t>01.05.202625</t>
+  </si>
+  <si>
+    <t>01.05.202626</t>
+  </si>
+  <si>
+    <t>01.05.202627</t>
+  </si>
+  <si>
+    <t>01.05.202628</t>
+  </si>
+  <si>
+    <t>01.05.202629</t>
+  </si>
+  <si>
+    <t>01.05.202630</t>
+  </si>
+  <si>
+    <t>01.05.202631</t>
+  </si>
+  <si>
+    <t>01.05.202632</t>
+  </si>
+  <si>
+    <t>01.05.202633</t>
+  </si>
+  <si>
+    <t>01.05.202634</t>
+  </si>
+  <si>
+    <t>01.05.202635</t>
+  </si>
+  <si>
+    <t>01.05.202636</t>
+  </si>
+  <si>
+    <t>01.05.202637</t>
+  </si>
+  <si>
+    <t>01.05.202638</t>
+  </si>
+  <si>
+    <t>01.05.202639</t>
+  </si>
+  <si>
+    <t>01.05.202640</t>
+  </si>
+  <si>
+    <t>01.05.202641</t>
+  </si>
+  <si>
+    <t>01.05.202642</t>
+  </si>
+  <si>
+    <t>01.05.202643</t>
+  </si>
+  <si>
+    <t>01.05.202644</t>
+  </si>
+  <si>
+    <t>01.05.202645</t>
+  </si>
+  <si>
+    <t>01.05.202646</t>
+  </si>
+  <si>
+    <t>01.05.202647</t>
+  </si>
+  <si>
+    <t>01.05.202648</t>
+  </si>
+  <si>
+    <t>01.05.202649</t>
+  </si>
+  <si>
+    <t>01.05.202650</t>
+  </si>
+  <si>
+    <t>01.05.202651</t>
+  </si>
+  <si>
+    <t>01.05.202652</t>
+  </si>
+  <si>
+    <t>01.05.202653</t>
+  </si>
+  <si>
+    <t>01.05.202654</t>
+  </si>
+  <si>
+    <t>01.05.202655</t>
+  </si>
+  <si>
+    <t>01.05.202656</t>
+  </si>
+  <si>
+    <t>01.05.202657</t>
+  </si>
+  <si>
+    <t>01.05.202658</t>
+  </si>
+  <si>
+    <t>01.05.202659</t>
+  </si>
+  <si>
+    <t>01.05.202660</t>
+  </si>
+  <si>
+    <t>01.05.202661</t>
+  </si>
+  <si>
+    <t>01.05.202662</t>
+  </si>
+  <si>
+    <t>01.05.202663</t>
+  </si>
+  <si>
+    <t>01.05.202664</t>
+  </si>
+  <si>
+    <t>01.05.202665</t>
+  </si>
+  <si>
+    <t>01.05.202666</t>
+  </si>
+  <si>
+    <t>01.05.202667</t>
+  </si>
+  <si>
+    <t>01.05.202668</t>
+  </si>
+  <si>
+    <t>01.05.202669</t>
+  </si>
+  <si>
+    <t>01.05.202670</t>
+  </si>
+  <si>
+    <t>01.05.202671</t>
+  </si>
+  <si>
+    <t>01.05.202672</t>
+  </si>
+  <si>
+    <t>01.05.202673</t>
+  </si>
+  <si>
+    <t>01.05.202674</t>
+  </si>
+  <si>
+    <t>01.05.202675</t>
+  </si>
+  <si>
+    <t>01.05.202676</t>
+  </si>
+  <si>
+    <t>01.05.202677</t>
+  </si>
+  <si>
+    <t>01.05.202678</t>
+  </si>
+  <si>
+    <t>01.05.202679</t>
+  </si>
+  <si>
+    <t>01.05.202680</t>
+  </si>
+  <si>
+    <t>01.05.202681</t>
+  </si>
+  <si>
+    <t>01.05.202682</t>
+  </si>
+  <si>
+    <t>01.05.202683</t>
+  </si>
+  <si>
+    <t>01.05.202684</t>
+  </si>
+  <si>
+    <t>01.05.202685</t>
+  </si>
+  <si>
+    <t>01.05.202686</t>
+  </si>
+  <si>
+    <t>01.05.202687</t>
+  </si>
+  <si>
+    <t>01.05.202688</t>
+  </si>
+  <si>
+    <t>01.05.202689</t>
+  </si>
+  <si>
+    <t>01.05.202690</t>
+  </si>
+  <si>
+    <t>01.05.202691</t>
+  </si>
+  <si>
+    <t>01.05.202692</t>
+  </si>
+  <si>
+    <t>01.05.202693</t>
+  </si>
+  <si>
+    <t>01.05.202694</t>
+  </si>
+  <si>
+    <t>01.05.202695</t>
+  </si>
+  <si>
+    <t>01.05.202696</t>
+  </si>
+  <si>
+    <t>02.05.20261</t>
+  </si>
+  <si>
+    <t>02.05.20262</t>
+  </si>
+  <si>
+    <t>02.05.20263</t>
+  </si>
+  <si>
+    <t>02.05.20264</t>
+  </si>
+  <si>
+    <t>02.05.20265</t>
+  </si>
+  <si>
+    <t>02.05.20266</t>
+  </si>
+  <si>
+    <t>02.05.20267</t>
+  </si>
+  <si>
+    <t>02.05.20268</t>
+  </si>
+  <si>
+    <t>02.05.20269</t>
+  </si>
+  <si>
+    <t>02.05.202610</t>
+  </si>
+  <si>
+    <t>02.05.202611</t>
+  </si>
+  <si>
+    <t>02.05.202612</t>
+  </si>
+  <si>
+    <t>02.05.202613</t>
+  </si>
+  <si>
+    <t>02.05.202614</t>
+  </si>
+  <si>
+    <t>02.05.202615</t>
+  </si>
+  <si>
+    <t>02.05.202616</t>
+  </si>
+  <si>
+    <t>02.05.202617</t>
+  </si>
+  <si>
+    <t>02.05.202618</t>
+  </si>
+  <si>
+    <t>02.05.202619</t>
+  </si>
+  <si>
+    <t>02.05.202620</t>
+  </si>
+  <si>
+    <t>02.05.202621</t>
+  </si>
+  <si>
+    <t>02.05.202622</t>
+  </si>
+  <si>
+    <t>02.05.202623</t>
+  </si>
+  <si>
+    <t>02.05.202624</t>
+  </si>
+  <si>
+    <t>02.05.202625</t>
+  </si>
+  <si>
+    <t>02.05.202626</t>
+  </si>
+  <si>
+    <t>02.05.202627</t>
+  </si>
+  <si>
+    <t>02.05.202628</t>
+  </si>
+  <si>
+    <t>02.05.202629</t>
+  </si>
+  <si>
+    <t>02.05.202630</t>
+  </si>
+  <si>
+    <t>02.05.202631</t>
+  </si>
+  <si>
+    <t>02.05.202632</t>
+  </si>
+  <si>
+    <t>02.05.202633</t>
+  </si>
+  <si>
+    <t>02.05.202634</t>
+  </si>
+  <si>
+    <t>02.05.202635</t>
+  </si>
+  <si>
+    <t>02.05.202636</t>
+  </si>
+  <si>
+    <t>02.05.202637</t>
+  </si>
+  <si>
+    <t>02.05.202638</t>
+  </si>
+  <si>
+    <t>02.05.202639</t>
+  </si>
+  <si>
+    <t>02.05.202640</t>
+  </si>
+  <si>
+    <t>02.05.202641</t>
+  </si>
+  <si>
+    <t>02.05.202642</t>
+  </si>
+  <si>
+    <t>02.05.202643</t>
+  </si>
+  <si>
+    <t>02.05.202644</t>
+  </si>
+  <si>
+    <t>02.05.202645</t>
+  </si>
+  <si>
+    <t>02.05.202646</t>
+  </si>
+  <si>
+    <t>02.05.202647</t>
+  </si>
+  <si>
+    <t>02.05.202648</t>
+  </si>
+  <si>
+    <t>02.05.202649</t>
+  </si>
+  <si>
+    <t>02.05.202650</t>
+  </si>
+  <si>
+    <t>02.05.202651</t>
+  </si>
+  <si>
+    <t>02.05.202652</t>
+  </si>
+  <si>
+    <t>02.05.202653</t>
+  </si>
+  <si>
+    <t>02.05.202654</t>
+  </si>
+  <si>
+    <t>02.05.202655</t>
+  </si>
+  <si>
+    <t>02.05.202656</t>
+  </si>
+  <si>
+    <t>02.05.202657</t>
+  </si>
+  <si>
+    <t>02.05.202658</t>
+  </si>
+  <si>
+    <t>02.05.202659</t>
+  </si>
+  <si>
+    <t>02.05.202660</t>
+  </si>
+  <si>
+    <t>02.05.202661</t>
+  </si>
+  <si>
+    <t>02.05.202662</t>
+  </si>
+  <si>
+    <t>02.05.202663</t>
+  </si>
+  <si>
+    <t>02.05.202664</t>
+  </si>
+  <si>
+    <t>02.05.202665</t>
+  </si>
+  <si>
+    <t>02.05.202666</t>
+  </si>
+  <si>
+    <t>02.05.202667</t>
+  </si>
+  <si>
+    <t>02.05.202668</t>
+  </si>
+  <si>
+    <t>02.05.202669</t>
+  </si>
+  <si>
+    <t>02.05.202670</t>
+  </si>
+  <si>
+    <t>02.05.202671</t>
+  </si>
+  <si>
+    <t>02.05.202672</t>
+  </si>
+  <si>
+    <t>02.05.202673</t>
+  </si>
+  <si>
+    <t>02.05.202674</t>
+  </si>
+  <si>
+    <t>02.05.202675</t>
+  </si>
+  <si>
+    <t>02.05.202676</t>
+  </si>
+  <si>
+    <t>02.05.202677</t>
+  </si>
+  <si>
+    <t>02.05.202678</t>
+  </si>
+  <si>
+    <t>02.05.202679</t>
+  </si>
+  <si>
+    <t>02.05.202680</t>
+  </si>
+  <si>
+    <t>02.05.202681</t>
+  </si>
+  <si>
+    <t>02.05.202682</t>
+  </si>
+  <si>
+    <t>02.05.202683</t>
+  </si>
+  <si>
+    <t>02.05.202684</t>
+  </si>
+  <si>
+    <t>02.05.202685</t>
+  </si>
+  <si>
+    <t>02.05.202686</t>
+  </si>
+  <si>
+    <t>02.05.202687</t>
+  </si>
+  <si>
+    <t>02.05.202688</t>
+  </si>
+  <si>
+    <t>02.05.202689</t>
+  </si>
+  <si>
+    <t>02.05.202690</t>
+  </si>
+  <si>
+    <t>02.05.202691</t>
+  </si>
+  <si>
+    <t>02.05.202692</t>
+  </si>
+  <si>
+    <t>02.05.202693</t>
+  </si>
+  <si>
+    <t>02.05.202694</t>
+  </si>
+  <si>
+    <t>02.05.202695</t>
+  </si>
+  <si>
+    <t>02.05.202696</t>
+  </si>
+  <si>
+    <t>03.05.20261</t>
+  </si>
+  <si>
+    <t>03.05.20262</t>
+  </si>
+  <si>
+    <t>03.05.20263</t>
+  </si>
+  <si>
+    <t>03.05.20264</t>
+  </si>
+  <si>
+    <t>03.05.20265</t>
+  </si>
+  <si>
+    <t>03.05.20266</t>
+  </si>
+  <si>
+    <t>03.05.20267</t>
+  </si>
+  <si>
+    <t>03.05.20268</t>
+  </si>
+  <si>
+    <t>03.05.20269</t>
+  </si>
+  <si>
+    <t>03.05.202610</t>
+  </si>
+  <si>
+    <t>03.05.202611</t>
+  </si>
+  <si>
+    <t>03.05.202612</t>
+  </si>
+  <si>
+    <t>03.05.202613</t>
+  </si>
+  <si>
+    <t>03.05.202614</t>
+  </si>
+  <si>
+    <t>03.05.202615</t>
+  </si>
+  <si>
+    <t>03.05.202616</t>
+  </si>
+  <si>
+    <t>03.05.202617</t>
+  </si>
+  <si>
+    <t>03.05.202618</t>
+  </si>
+  <si>
+    <t>03.05.202619</t>
+  </si>
+  <si>
+    <t>03.05.202620</t>
+  </si>
+  <si>
+    <t>03.05.202621</t>
+  </si>
+  <si>
+    <t>03.05.202622</t>
+  </si>
+  <si>
+    <t>03.05.202623</t>
+  </si>
+  <si>
+    <t>03.05.202624</t>
+  </si>
+  <si>
+    <t>03.05.202625</t>
+  </si>
+  <si>
+    <t>03.05.202626</t>
+  </si>
+  <si>
+    <t>03.05.202627</t>
+  </si>
+  <si>
+    <t>03.05.202628</t>
+  </si>
+  <si>
+    <t>03.05.202629</t>
+  </si>
+  <si>
+    <t>03.05.202630</t>
+  </si>
+  <si>
+    <t>03.05.202631</t>
+  </si>
+  <si>
+    <t>03.05.202632</t>
+  </si>
+  <si>
+    <t>03.05.202633</t>
+  </si>
+  <si>
+    <t>03.05.202634</t>
+  </si>
+  <si>
+    <t>03.05.202635</t>
+  </si>
+  <si>
+    <t>03.05.202636</t>
+  </si>
+  <si>
+    <t>03.05.202637</t>
+  </si>
+  <si>
+    <t>03.05.202638</t>
+  </si>
+  <si>
+    <t>03.05.202639</t>
+  </si>
+  <si>
+    <t>03.05.202640</t>
+  </si>
+  <si>
+    <t>03.05.202641</t>
+  </si>
+  <si>
+    <t>03.05.202642</t>
+  </si>
+  <si>
+    <t>03.05.202643</t>
+  </si>
+  <si>
+    <t>03.05.202644</t>
+  </si>
+  <si>
+    <t>03.05.202645</t>
+  </si>
+  <si>
+    <t>03.05.202646</t>
+  </si>
+  <si>
+    <t>03.05.202647</t>
+  </si>
+  <si>
+    <t>03.05.202648</t>
+  </si>
+  <si>
+    <t>03.05.202649</t>
+  </si>
+  <si>
+    <t>03.05.202650</t>
+  </si>
+  <si>
+    <t>03.05.202651</t>
+  </si>
+  <si>
+    <t>03.05.202652</t>
+  </si>
+  <si>
+    <t>03.05.202653</t>
+  </si>
+  <si>
+    <t>03.05.202654</t>
+  </si>
+  <si>
+    <t>03.05.202655</t>
+  </si>
+  <si>
+    <t>03.05.202656</t>
+  </si>
+  <si>
+    <t>03.05.202657</t>
+  </si>
+  <si>
+    <t>03.05.202658</t>
+  </si>
+  <si>
+    <t>03.05.202659</t>
+  </si>
+  <si>
+    <t>03.05.202660</t>
+  </si>
+  <si>
+    <t>03.05.202661</t>
+  </si>
+  <si>
+    <t>03.05.202662</t>
+  </si>
+  <si>
+    <t>03.05.202663</t>
+  </si>
+  <si>
+    <t>03.05.202664</t>
+  </si>
+  <si>
+    <t>03.05.202665</t>
+  </si>
+  <si>
+    <t>03.05.202666</t>
+  </si>
+  <si>
+    <t>03.05.202667</t>
+  </si>
+  <si>
+    <t>03.05.202668</t>
+  </si>
+  <si>
+    <t>03.05.202669</t>
+  </si>
+  <si>
+    <t>03.05.202670</t>
+  </si>
+  <si>
+    <t>03.05.202671</t>
+  </si>
+  <si>
+    <t>03.05.202672</t>
+  </si>
+  <si>
+    <t>03.05.202673</t>
+  </si>
+  <si>
+    <t>03.05.202674</t>
+  </si>
+  <si>
+    <t>03.05.202675</t>
+  </si>
+  <si>
+    <t>03.05.202676</t>
+  </si>
+  <si>
+    <t>03.05.202677</t>
+  </si>
+  <si>
+    <t>03.05.202678</t>
+  </si>
+  <si>
+    <t>03.05.202679</t>
+  </si>
+  <si>
+    <t>03.05.202680</t>
+  </si>
+  <si>
+    <t>03.05.202681</t>
+  </si>
+  <si>
+    <t>03.05.202682</t>
+  </si>
+  <si>
+    <t>03.05.202683</t>
+  </si>
+  <si>
+    <t>03.05.202684</t>
+  </si>
+  <si>
+    <t>03.05.202685</t>
+  </si>
+  <si>
+    <t>03.05.202686</t>
+  </si>
+  <si>
+    <t>03.05.202687</t>
+  </si>
+  <si>
+    <t>03.05.202688</t>
+  </si>
+  <si>
+    <t>03.05.202689</t>
+  </si>
+  <si>
+    <t>03.05.202690</t>
+  </si>
+  <si>
+    <t>03.05.202691</t>
+  </si>
+  <si>
+    <t>03.05.202692</t>
+  </si>
+  <si>
+    <t>03.05.202693</t>
+  </si>
+  <si>
+    <t>03.05.202694</t>
+  </si>
+  <si>
+    <t>03.05.202695</t>
+  </si>
+  <si>
+    <t>03.05.202696</t>
+  </si>
+  <si>
+    <t>04.05.20261</t>
+  </si>
+  <si>
+    <t>04.05.20262</t>
+  </si>
+  <si>
+    <t>04.05.20263</t>
+  </si>
+  <si>
+    <t>04.05.20264</t>
+  </si>
+  <si>
+    <t>04.05.20265</t>
+  </si>
+  <si>
+    <t>04.05.20266</t>
+  </si>
+  <si>
+    <t>04.05.20267</t>
+  </si>
+  <si>
+    <t>04.05.20268</t>
+  </si>
+  <si>
+    <t>04.05.20269</t>
+  </si>
+  <si>
+    <t>04.05.202610</t>
+  </si>
+  <si>
+    <t>04.05.202611</t>
+  </si>
+  <si>
+    <t>04.05.202612</t>
+  </si>
+  <si>
+    <t>04.05.202613</t>
+  </si>
+  <si>
+    <t>04.05.202614</t>
+  </si>
+  <si>
+    <t>04.05.202615</t>
+  </si>
+  <si>
+    <t>04.05.202616</t>
+  </si>
+  <si>
+    <t>04.05.202617</t>
+  </si>
+  <si>
+    <t>04.05.202618</t>
+  </si>
+  <si>
+    <t>04.05.202619</t>
+  </si>
+  <si>
+    <t>04.05.202620</t>
+  </si>
+  <si>
+    <t>04.05.202621</t>
+  </si>
+  <si>
+    <t>04.05.202622</t>
+  </si>
+  <si>
+    <t>04.05.202623</t>
+  </si>
+  <si>
+    <t>04.05.202624</t>
+  </si>
+  <si>
+    <t>04.05.202625</t>
+  </si>
+  <si>
+    <t>04.05.202626</t>
+  </si>
+  <si>
+    <t>04.05.202627</t>
+  </si>
+  <si>
+    <t>04.05.202628</t>
+  </si>
+  <si>
+    <t>04.05.202629</t>
+  </si>
+  <si>
+    <t>04.05.202630</t>
+  </si>
+  <si>
+    <t>04.05.202631</t>
+  </si>
+  <si>
+    <t>04.05.202632</t>
+  </si>
+  <si>
+    <t>04.05.202633</t>
+  </si>
+  <si>
+    <t>04.05.202634</t>
+  </si>
+  <si>
+    <t>04.05.202635</t>
+  </si>
+  <si>
+    <t>04.05.202636</t>
+  </si>
+  <si>
+    <t>04.05.202637</t>
+  </si>
+  <si>
+    <t>04.05.202638</t>
+  </si>
+  <si>
+    <t>04.05.202639</t>
+  </si>
+  <si>
+    <t>04.05.202640</t>
+  </si>
+  <si>
+    <t>04.05.202641</t>
+  </si>
+  <si>
+    <t>04.05.202642</t>
+  </si>
+  <si>
+    <t>04.05.202643</t>
+  </si>
+  <si>
+    <t>04.05.202644</t>
+  </si>
+  <si>
+    <t>04.05.202645</t>
+  </si>
+  <si>
+    <t>04.05.202646</t>
+  </si>
+  <si>
+    <t>04.05.202647</t>
+  </si>
+  <si>
+    <t>04.05.202648</t>
+  </si>
+  <si>
+    <t>04.05.202649</t>
+  </si>
+  <si>
+    <t>04.05.202650</t>
+  </si>
+  <si>
+    <t>04.05.202651</t>
+  </si>
+  <si>
+    <t>04.05.202652</t>
+  </si>
+  <si>
+    <t>04.05.202653</t>
+  </si>
+  <si>
+    <t>04.05.202654</t>
+  </si>
+  <si>
+    <t>04.05.202655</t>
+  </si>
+  <si>
+    <t>04.05.202656</t>
+  </si>
+  <si>
+    <t>04.05.202657</t>
+  </si>
+  <si>
+    <t>04.05.202658</t>
+  </si>
+  <si>
+    <t>04.05.202659</t>
+  </si>
+  <si>
+    <t>04.05.202660</t>
+  </si>
+  <si>
+    <t>04.05.202661</t>
+  </si>
+  <si>
+    <t>04.05.202662</t>
+  </si>
+  <si>
+    <t>04.05.202663</t>
+  </si>
+  <si>
+    <t>04.05.202664</t>
+  </si>
+  <si>
+    <t>04.05.202665</t>
+  </si>
+  <si>
+    <t>04.05.202666</t>
+  </si>
+  <si>
+    <t>04.05.202667</t>
+  </si>
+  <si>
+    <t>04.05.202668</t>
+  </si>
+  <si>
+    <t>04.05.202669</t>
+  </si>
+  <si>
+    <t>04.05.202670</t>
+  </si>
+  <si>
+    <t>04.05.202671</t>
+  </si>
+  <si>
+    <t>04.05.202672</t>
+  </si>
+  <si>
+    <t>04.05.202673</t>
+  </si>
+  <si>
+    <t>04.05.202674</t>
+  </si>
+  <si>
+    <t>04.05.202675</t>
+  </si>
+  <si>
+    <t>04.05.202676</t>
+  </si>
+  <si>
+    <t>04.05.202677</t>
+  </si>
+  <si>
+    <t>04.05.202678</t>
+  </si>
+  <si>
+    <t>04.05.202679</t>
+  </si>
+  <si>
+    <t>04.05.202680</t>
+  </si>
+  <si>
+    <t>04.05.202681</t>
+  </si>
+  <si>
+    <t>04.05.202682</t>
+  </si>
+  <si>
+    <t>04.05.202683</t>
+  </si>
+  <si>
+    <t>04.05.202684</t>
+  </si>
+  <si>
+    <t>04.05.202685</t>
+  </si>
+  <si>
+    <t>04.05.202686</t>
+  </si>
+  <si>
+    <t>04.05.202687</t>
+  </si>
+  <si>
+    <t>04.05.202688</t>
+  </si>
+  <si>
+    <t>04.05.202689</t>
+  </si>
+  <si>
+    <t>04.05.202690</t>
+  </si>
+  <si>
+    <t>04.05.202691</t>
+  </si>
+  <si>
+    <t>04.05.202692</t>
+  </si>
+  <si>
+    <t>04.05.202693</t>
+  </si>
+  <si>
+    <t>04.05.202694</t>
+  </si>
+  <si>
+    <t>04.05.202695</t>
+  </si>
+  <si>
+    <t>04.05.202696</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E289"/>
+  <dimension ref="A1:E481"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1276,13 +1852,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B2">
-        <v>1270.767</v>
+        <v>648.849</v>
       </c>
       <c r="C2">
-        <v>1494</v>
+        <v>636</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1293,13 +1869,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46140.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B3">
-        <v>1252.175</v>
+        <v>652.102</v>
       </c>
       <c r="C3">
-        <v>1475</v>
+        <v>638</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1310,13 +1886,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46140.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B4">
-        <v>1243.357</v>
+        <v>652.4349999999999</v>
       </c>
       <c r="C4">
-        <v>1376</v>
+        <v>625</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1327,13 +1903,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46140.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B5">
-        <v>1219.203</v>
+        <v>657.736</v>
       </c>
       <c r="C5">
-        <v>1393</v>
+        <v>616</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1344,13 +1920,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46140.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B6">
-        <v>1184.954</v>
+        <v>634.076</v>
       </c>
       <c r="C6">
-        <v>1360</v>
+        <v>613</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1361,13 +1937,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46140.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B7">
-        <v>1156.669</v>
+        <v>645.49</v>
       </c>
       <c r="C7">
-        <v>1329</v>
+        <v>604</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1378,13 +1954,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46140.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B8">
-        <v>1133.874</v>
+        <v>659.099</v>
       </c>
       <c r="C8">
-        <v>1342</v>
+        <v>613</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1395,13 +1971,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46140.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B9">
-        <v>1094.568</v>
+        <v>675.169</v>
       </c>
       <c r="C9">
-        <v>1320</v>
+        <v>628</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1412,13 +1988,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46140.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B10">
-        <v>1032.122</v>
+        <v>684.753</v>
       </c>
       <c r="C10">
-        <v>1302</v>
+        <v>612</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1429,13 +2005,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46140.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B11">
-        <v>1014.116</v>
+        <v>698.7910000000001</v>
       </c>
       <c r="C11">
-        <v>1277</v>
+        <v>579</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1446,13 +2022,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46140.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B12">
-        <v>1007.059</v>
+        <v>712.357</v>
       </c>
       <c r="C12">
-        <v>1222</v>
+        <v>582</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1463,13 +2039,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46140.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B13">
-        <v>974.268</v>
+        <v>729.8819999999999</v>
       </c>
       <c r="C13">
-        <v>1178</v>
+        <v>572</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1480,13 +2056,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46140.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B14">
-        <v>968.976</v>
+        <v>753.501</v>
       </c>
       <c r="C14">
-        <v>1137</v>
+        <v>544</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1497,13 +2073,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46140.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B15">
-        <v>941.582</v>
+        <v>774.6660000000001</v>
       </c>
       <c r="C15">
-        <v>1089</v>
+        <v>532</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1514,13 +2090,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46140.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B16">
-        <v>920.5549999999999</v>
+        <v>790.66</v>
       </c>
       <c r="C16">
-        <v>1036</v>
+        <v>521</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1531,13 +2107,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46140.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B17">
-        <v>897.37</v>
+        <v>815.938</v>
       </c>
       <c r="C17">
-        <v>988</v>
+        <v>511</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1548,13 +2124,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46140.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B18">
-        <v>876.832</v>
+        <v>848.564</v>
       </c>
       <c r="C18">
-        <v>974</v>
+        <v>538</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1565,13 +2141,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46140.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B19">
-        <v>844.365</v>
+        <v>868.607</v>
       </c>
       <c r="C19">
-        <v>940</v>
+        <v>563</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1582,13 +2158,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46140.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B20">
-        <v>807.5650000000001</v>
+        <v>891.778</v>
       </c>
       <c r="C20">
-        <v>883</v>
+        <v>592</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1599,13 +2175,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46140.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B21">
-        <v>780.474</v>
+        <v>910.2329999999999</v>
       </c>
       <c r="C21">
-        <v>848</v>
+        <v>606</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1616,13 +2192,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46140.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B22">
-        <v>757.066</v>
+        <v>971.033</v>
       </c>
       <c r="C22">
-        <v>827</v>
+        <v>623</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1633,13 +2209,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46140.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B23">
-        <v>720.212</v>
+        <v>996.926</v>
       </c>
       <c r="C23">
-        <v>814</v>
+        <v>627</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1650,13 +2226,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46140.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B24">
-        <v>690.349</v>
+        <v>1022.417</v>
       </c>
       <c r="C24">
-        <v>807</v>
+        <v>641</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1667,13 +2243,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46140.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B25">
-        <v>658.62</v>
+        <v>1045.328</v>
       </c>
       <c r="C25">
-        <v>798</v>
+        <v>674</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1684,13 +2260,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46140.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B26">
-        <v>626.619</v>
+        <v>1119.208</v>
       </c>
       <c r="C26">
-        <v>771</v>
+        <v>672</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1701,13 +2277,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46140.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B27">
-        <v>592.035</v>
+        <v>1142.173</v>
       </c>
       <c r="C27">
-        <v>740</v>
+        <v>686</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1718,13 +2294,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46140.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B28">
-        <v>560.535</v>
+        <v>1160.553</v>
       </c>
       <c r="C28">
-        <v>695</v>
+        <v>713</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1735,13 +2311,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46140.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B29">
-        <v>537.501</v>
+        <v>1164.352</v>
       </c>
       <c r="C29">
-        <v>631</v>
+        <v>723</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1752,13 +2328,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46140.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B30">
-        <v>511.299</v>
+        <v>1215.261</v>
       </c>
       <c r="C30">
-        <v>542</v>
+        <v>710</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1769,13 +2345,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46140.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B31">
-        <v>472.693</v>
+        <v>1213.192</v>
       </c>
       <c r="C31">
-        <v>457</v>
+        <v>683</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1786,13 +2362,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46140.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B32">
-        <v>437.198</v>
+        <v>1210.118</v>
       </c>
       <c r="C32">
-        <v>406</v>
+        <v>628</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1803,13 +2379,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46140.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B33">
-        <v>403.051</v>
+        <v>1220.582</v>
       </c>
       <c r="C33">
-        <v>392</v>
+        <v>605</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1820,13 +2396,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46140.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B34">
-        <v>420.481</v>
+        <v>1116.184</v>
       </c>
       <c r="C34">
-        <v>370</v>
+        <v>609</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1837,13 +2413,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46140.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B35">
-        <v>425.709</v>
+        <v>1119.482</v>
       </c>
       <c r="C35">
-        <v>373</v>
+        <v>626</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1854,13 +2430,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46140.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B36">
-        <v>432.047</v>
+        <v>1134.834</v>
       </c>
       <c r="C36">
-        <v>374</v>
+        <v>677</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1871,13 +2447,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46140.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B37">
-        <v>438.316</v>
+        <v>1142.694</v>
       </c>
       <c r="C37">
-        <v>383</v>
+        <v>767</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1888,13 +2464,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46140.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B38">
-        <v>444.116</v>
+        <v>1318.648</v>
       </c>
       <c r="C38">
-        <v>374</v>
+        <v>867</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1905,13 +2481,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46140.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B39">
-        <v>462.96</v>
+        <v>1331.289</v>
       </c>
       <c r="C39">
-        <v>378</v>
+        <v>975</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1922,13 +2498,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46140.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B40">
-        <v>480.088</v>
+        <v>1343.271</v>
       </c>
       <c r="C40">
-        <v>398</v>
+        <v>1142</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1939,13 +2515,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46140.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B41">
-        <v>473.522</v>
+        <v>1318.529</v>
       </c>
       <c r="C41">
-        <v>380</v>
+        <v>1198</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1956,13 +2532,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46140.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B42">
-        <v>484.77</v>
+        <v>1369.836</v>
       </c>
       <c r="C42">
-        <v>381</v>
+        <v>1279</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1973,13 +2549,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46140.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B43">
-        <v>495.258</v>
+        <v>1345.14</v>
       </c>
       <c r="C43">
-        <v>372</v>
+        <v>1396</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1990,13 +2566,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46140.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B44">
-        <v>504.924</v>
+        <v>1387.805</v>
       </c>
       <c r="C44">
-        <v>345</v>
+        <v>1409</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -2007,13 +2583,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46140.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B45">
-        <v>488.467</v>
+        <v>1416.536</v>
       </c>
       <c r="C45">
-        <v>319</v>
+        <v>1402</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -2024,13 +2600,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46140.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B46">
-        <v>525.664</v>
+        <v>1494.563</v>
       </c>
       <c r="C46">
-        <v>312</v>
+        <v>1470</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -2041,13 +2617,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46140.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B47">
-        <v>540.508</v>
+        <v>1513.067</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -2058,13 +2634,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46140.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B48">
-        <v>555.289</v>
+        <v>1535.332</v>
       </c>
       <c r="C48">
-        <v>316</v>
+        <v>1608</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -2075,13 +2651,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46140.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B49">
-        <v>569.922</v>
+        <v>1553.759</v>
       </c>
       <c r="C49">
-        <v>325</v>
+        <v>1646</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -2092,13 +2668,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46140.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B50">
-        <v>595.285</v>
+        <v>1585.976</v>
       </c>
       <c r="C50">
-        <v>332</v>
+        <v>1683</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -2109,13 +2685,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46140.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B51">
-        <v>608.415</v>
+        <v>1610.747</v>
       </c>
       <c r="C51">
-        <v>350</v>
+        <v>1688</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -2126,13 +2702,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46140.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B52">
-        <v>620.948</v>
+        <v>1587.508</v>
       </c>
       <c r="C52">
-        <v>348</v>
+        <v>1645</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -2143,13 +2719,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46140.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B53">
-        <v>634.0940000000001</v>
+        <v>1609.954</v>
       </c>
       <c r="C53">
-        <v>329</v>
+        <v>1657</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2160,13 +2736,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46140.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B54">
-        <v>642.139</v>
+        <v>1615.319</v>
       </c>
       <c r="C54">
-        <v>336</v>
+        <v>1670</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -2177,13 +2753,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46140.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B55">
-        <v>648.282</v>
+        <v>1623.051</v>
       </c>
       <c r="C55">
-        <v>358</v>
+        <v>1635</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -2194,13 +2770,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46140.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B56">
-        <v>653.936</v>
+        <v>1629.591</v>
       </c>
       <c r="C56">
-        <v>380</v>
+        <v>1564</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -2211,13 +2787,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46140.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B57">
-        <v>672.5069999999999</v>
+        <v>1690.212</v>
       </c>
       <c r="C57">
-        <v>392</v>
+        <v>1562</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -2228,13 +2804,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46140.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B58">
-        <v>672.6609999999999</v>
+        <v>1691.257</v>
       </c>
       <c r="C58">
-        <v>425</v>
+        <v>1502</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -2245,13 +2821,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46140.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B59">
-        <v>692.461</v>
+        <v>1684.456</v>
       </c>
       <c r="C59">
-        <v>440</v>
+        <v>1538</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -2262,13 +2838,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46140.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B60">
-        <v>711.9589999999999</v>
+        <v>1730.248</v>
       </c>
       <c r="C60">
-        <v>459</v>
+        <v>1546</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -2279,13 +2855,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46140.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B61">
-        <v>731.011</v>
+        <v>1667.491</v>
       </c>
       <c r="C61">
-        <v>467</v>
+        <v>1584</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2296,13 +2872,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46140.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B62">
-        <v>756.898</v>
+        <v>1651.491</v>
       </c>
       <c r="C62">
-        <v>489</v>
+        <v>1597</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2313,13 +2889,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46140.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B63">
-        <v>783.296</v>
+        <v>1639.549</v>
       </c>
       <c r="C63">
-        <v>537</v>
+        <v>1639</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2330,13 +2906,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46140.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B64">
-        <v>810.365</v>
+        <v>1678.808</v>
       </c>
       <c r="C64">
-        <v>579</v>
+        <v>1602</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2347,13 +2923,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46140.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B65">
-        <v>837.025</v>
+        <v>1664.533</v>
       </c>
       <c r="C65">
-        <v>629</v>
+        <v>1522</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2364,13 +2940,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46140.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B66">
-        <v>858.855</v>
+        <v>1596.839</v>
       </c>
       <c r="C66">
-        <v>671</v>
+        <v>1364</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2381,13 +2957,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46140.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B67">
-        <v>894.855</v>
+        <v>1561.902</v>
       </c>
       <c r="C67">
-        <v>749</v>
+        <v>1350</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2398,13 +2974,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46140.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B68">
-        <v>962.076</v>
+        <v>1523.067</v>
       </c>
       <c r="C68">
-        <v>821</v>
+        <v>1341</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2415,13 +2991,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46140.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B69">
-        <v>998.465</v>
+        <v>1481.622</v>
       </c>
       <c r="C69">
-        <v>875</v>
+        <v>1367</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2432,13 +3008,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46140.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B70">
-        <v>933.609</v>
+        <v>1202.378</v>
       </c>
       <c r="C70">
-        <v>885</v>
+        <v>1294</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2449,13 +3025,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46140.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B71">
-        <v>954.96</v>
+        <v>1140.683</v>
       </c>
       <c r="C71">
-        <v>870</v>
+        <v>1184</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2466,13 +3042,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46140.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B72">
-        <v>977.203</v>
+        <v>1082.644</v>
       </c>
       <c r="C72">
-        <v>875</v>
+        <v>1087</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2483,13 +3059,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46140.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B73">
-        <v>1003.257</v>
+        <v>1026.684</v>
       </c>
       <c r="C73">
-        <v>898</v>
+        <v>1003</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2500,13 +3076,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46140.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B74">
-        <v>997.271</v>
+        <v>934.331</v>
       </c>
       <c r="C74">
-        <v>923</v>
+        <v>1033</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2517,13 +3093,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46140.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B75">
-        <v>997.668</v>
+        <v>873.372</v>
       </c>
       <c r="C75">
-        <v>941</v>
+        <v>1101</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2534,13 +3110,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46140.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B76">
-        <v>998.407</v>
+        <v>814.657</v>
       </c>
       <c r="C76">
-        <v>942</v>
+        <v>1135</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2551,13 +3127,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46140.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B77">
-        <v>1001.131</v>
+        <v>755.008</v>
       </c>
       <c r="C77">
-        <v>931</v>
+        <v>1056</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2568,13 +3144,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46140.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B78">
-        <v>988.856</v>
+        <v>684.558</v>
       </c>
       <c r="C78">
-        <v>961</v>
+        <v>1081</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2585,13 +3161,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46140.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B79">
-        <v>984.095</v>
+        <v>645.986</v>
       </c>
       <c r="C79">
-        <v>974</v>
+        <v>1019</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2602,13 +3178,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46140.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B80">
-        <v>980.83</v>
+        <v>608.806</v>
       </c>
       <c r="C80">
-        <v>949</v>
+        <v>920</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2619,13 +3195,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46140.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B81">
-        <v>978.266</v>
+        <v>571.515</v>
       </c>
       <c r="C81">
-        <v>951</v>
+        <v>883</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2636,13 +3212,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46140.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B82">
-        <v>954.473</v>
+        <v>515.564</v>
       </c>
       <c r="C82">
-        <v>954</v>
+        <v>937</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2653,13 +3229,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46140.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B83">
-        <v>929.12</v>
+        <v>494.889</v>
       </c>
       <c r="C83">
-        <v>950</v>
+        <v>902</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2670,13 +3246,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46140.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B84">
-        <v>909.0549999999999</v>
+        <v>474.77</v>
       </c>
       <c r="C84">
-        <v>959</v>
+        <v>850</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2687,13 +3263,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46140.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B85">
-        <v>885.792</v>
+        <v>454.56</v>
       </c>
       <c r="C85">
-        <v>946</v>
+        <v>811</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2704,13 +3280,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46140.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B86">
-        <v>852.3150000000001</v>
+        <v>448.509</v>
       </c>
       <c r="C86">
-        <v>928</v>
+        <v>730</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2721,13 +3297,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46140.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B87">
-        <v>827.341</v>
+        <v>445.173</v>
       </c>
       <c r="C87">
-        <v>893</v>
+        <v>754</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2738,13 +3314,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46140.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B88">
-        <v>802.425</v>
+        <v>442.81</v>
       </c>
       <c r="C88">
-        <v>834</v>
+        <v>800</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2755,13 +3331,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46140.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B89">
-        <v>778.785</v>
+        <v>429.088</v>
       </c>
       <c r="C89">
-        <v>770</v>
+        <v>807</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2772,13 +3348,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46140.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B90">
-        <v>748.401</v>
+        <v>448.858</v>
       </c>
       <c r="C90">
-        <v>707</v>
+        <v>770</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2789,13 +3365,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46140.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B91">
-        <v>727.739</v>
+        <v>469.044</v>
       </c>
       <c r="C91">
-        <v>673</v>
+        <v>744</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2806,13 +3382,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46140.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B92">
-        <v>707.723</v>
+        <v>489.697</v>
       </c>
       <c r="C92">
-        <v>649</v>
+        <v>739</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2823,13 +3399,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46140.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B93">
-        <v>686.889</v>
+        <v>509.745</v>
       </c>
       <c r="C93">
-        <v>627</v>
+        <v>732</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2840,13 +3416,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46140.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B94">
-        <v>623.862</v>
+        <v>620.296</v>
       </c>
       <c r="C94">
-        <v>595</v>
+        <v>690</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2857,13 +3433,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46140.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B95">
-        <v>599.125</v>
+        <v>646.274</v>
       </c>
       <c r="C95">
-        <v>557</v>
+        <v>688</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2874,13 +3450,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46140.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B96">
-        <v>577.424</v>
+        <v>674.098</v>
       </c>
       <c r="C96">
-        <v>539</v>
+        <v>643</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2891,13 +3467,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46140.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B97">
-        <v>564.722</v>
+        <v>711.963</v>
       </c>
       <c r="C97">
-        <v>507</v>
+        <v>594</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2908,13 +3484,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B98">
-        <v>519.583</v>
+        <v>683.3049999999999</v>
       </c>
       <c r="C98">
-        <v>448</v>
+        <v>555</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2925,13 +3501,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46141.01041666666</v>
+        <v>46143.01041666666</v>
       </c>
       <c r="B99">
-        <v>504.68</v>
+        <v>717.756</v>
       </c>
       <c r="C99">
-        <v>408</v>
+        <v>517</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2942,13 +3518,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46141.02083333334</v>
+        <v>46143.02083333334</v>
       </c>
       <c r="B100">
-        <v>485.484</v>
+        <v>724.659</v>
       </c>
       <c r="C100">
-        <v>372</v>
+        <v>506</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2959,13 +3535,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46141.03125</v>
+        <v>46143.03125</v>
       </c>
       <c r="B101">
-        <v>467.114</v>
+        <v>753.575</v>
       </c>
       <c r="C101">
-        <v>361</v>
+        <v>508</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2976,13 +3552,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46141.04166666666</v>
+        <v>46143.04166666666</v>
       </c>
       <c r="B102">
-        <v>435.739</v>
+        <v>720.975</v>
       </c>
       <c r="C102">
-        <v>332</v>
+        <v>509</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2993,13 +3569,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46141.05208333334</v>
+        <v>46143.05208333334</v>
       </c>
       <c r="B103">
-        <v>417.841</v>
+        <v>762.245</v>
       </c>
       <c r="C103">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -3010,13 +3586,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46141.0625</v>
+        <v>46143.0625</v>
       </c>
       <c r="B104">
-        <v>397.748</v>
+        <v>801.967</v>
       </c>
       <c r="C104">
-        <v>339</v>
+        <v>483</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -3027,13 +3603,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46141.07291666666</v>
+        <v>46143.07291666666</v>
       </c>
       <c r="B105">
-        <v>379.447</v>
+        <v>837.1130000000001</v>
       </c>
       <c r="C105">
-        <v>334</v>
+        <v>460</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -3044,13 +3620,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46141.08333333334</v>
+        <v>46143.08333333334</v>
       </c>
       <c r="B106">
-        <v>356.681</v>
+        <v>865.758</v>
       </c>
       <c r="C106">
-        <v>305</v>
+        <v>550</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -3061,13 +3637,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46141.09375</v>
+        <v>46143.09375</v>
       </c>
       <c r="B107">
-        <v>339.795</v>
+        <v>891.655</v>
       </c>
       <c r="C107">
-        <v>247</v>
+        <v>584</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -3078,13 +3654,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46141.10416666666</v>
+        <v>46143.10416666666</v>
       </c>
       <c r="B108">
-        <v>323.738</v>
+        <v>911.322</v>
       </c>
       <c r="C108">
-        <v>201</v>
+        <v>579</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -3095,13 +3671,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46141.11458333334</v>
+        <v>46143.11458333334</v>
       </c>
       <c r="B109">
-        <v>308.664</v>
+        <v>945.908</v>
       </c>
       <c r="C109">
-        <v>184</v>
+        <v>665</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -3112,13 +3688,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46141.125</v>
+        <v>46143.125</v>
       </c>
       <c r="B110">
-        <v>298.263</v>
+        <v>982.28</v>
       </c>
       <c r="C110">
-        <v>172</v>
+        <v>723</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -3129,13 +3705,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46141.13541666666</v>
+        <v>46143.13541666666</v>
       </c>
       <c r="B111">
-        <v>291.526</v>
+        <v>1008.866</v>
       </c>
       <c r="C111">
-        <v>168</v>
+        <v>737</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -3146,13 +3722,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46141.14583333334</v>
+        <v>46143.14583333334</v>
       </c>
       <c r="B112">
-        <v>285.145</v>
+        <v>1022.053</v>
       </c>
       <c r="C112">
-        <v>166</v>
+        <v>745</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -3163,13 +3739,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46141.15625</v>
+        <v>46143.15625</v>
       </c>
       <c r="B113">
-        <v>272.793</v>
+        <v>1020.753</v>
       </c>
       <c r="C113">
-        <v>161</v>
+        <v>789</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -3180,13 +3756,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46141.16666666666</v>
+        <v>46143.16666666666</v>
       </c>
       <c r="B114">
-        <v>262.379</v>
+        <v>1060.467</v>
       </c>
       <c r="C114">
-        <v>171</v>
+        <v>857</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -3197,13 +3773,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46141.17708333334</v>
+        <v>46143.17708333334</v>
       </c>
       <c r="B115">
-        <v>267.568</v>
+        <v>1069.186</v>
       </c>
       <c r="C115">
-        <v>180</v>
+        <v>905</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -3214,13 +3790,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46141.1875</v>
+        <v>46143.1875</v>
       </c>
       <c r="B116">
-        <v>266.997</v>
+        <v>1078.844</v>
       </c>
       <c r="C116">
-        <v>170</v>
+        <v>965</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -3231,13 +3807,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46141.19791666666</v>
+        <v>46143.19791666666</v>
       </c>
       <c r="B117">
-        <v>265.784</v>
+        <v>1091.105</v>
       </c>
       <c r="C117">
-        <v>158</v>
+        <v>1015</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -3248,13 +3824,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46141.20833333334</v>
+        <v>46143.20833333334</v>
       </c>
       <c r="B118">
-        <v>259.815</v>
+        <v>1084.399</v>
       </c>
       <c r="C118">
-        <v>155</v>
+        <v>1038</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -3265,13 +3841,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46141.21875</v>
+        <v>46143.21875</v>
       </c>
       <c r="B119">
-        <v>263.032</v>
+        <v>1095.429</v>
       </c>
       <c r="C119">
-        <v>160</v>
+        <v>1076</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -3282,13 +3858,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46141.22916666666</v>
+        <v>46143.22916666666</v>
       </c>
       <c r="B120">
-        <v>264.538</v>
+        <v>1108.271</v>
       </c>
       <c r="C120">
-        <v>166</v>
+        <v>1097</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3299,13 +3875,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46141.23958333334</v>
+        <v>46143.23958333334</v>
       </c>
       <c r="B121">
-        <v>268.175</v>
+        <v>1124.863</v>
       </c>
       <c r="C121">
-        <v>176</v>
+        <v>1140</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3316,13 +3892,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46141.25</v>
+        <v>46143.25</v>
       </c>
       <c r="B122">
-        <v>267.464</v>
+        <v>1139.243</v>
       </c>
       <c r="C122">
-        <v>199</v>
+        <v>1146</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3333,13 +3909,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46141.26041666666</v>
+        <v>46143.26041666666</v>
       </c>
       <c r="B123">
-        <v>266.108</v>
+        <v>1101.629</v>
       </c>
       <c r="C123">
-        <v>186</v>
+        <v>1123</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3350,13 +3926,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46141.27083333334</v>
+        <v>46143.27083333334</v>
       </c>
       <c r="B124">
-        <v>274.297</v>
+        <v>1062.74</v>
       </c>
       <c r="C124">
-        <v>170</v>
+        <v>1047</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3367,13 +3943,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46141.28125</v>
+        <v>46143.28125</v>
       </c>
       <c r="B125">
-        <v>282.184</v>
+        <v>1031.901</v>
       </c>
       <c r="C125">
-        <v>165</v>
+        <v>957</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3384,13 +3960,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46141.29166666666</v>
+        <v>46143.29166666666</v>
       </c>
       <c r="B126">
-        <v>295.651</v>
+        <v>1015.103</v>
       </c>
       <c r="C126">
-        <v>143</v>
+        <v>885</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3401,13 +3977,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46141.30208333334</v>
+        <v>46143.30208333334</v>
       </c>
       <c r="B127">
-        <v>292.798</v>
+        <v>967.873</v>
       </c>
       <c r="C127">
-        <v>129</v>
+        <v>828</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3418,13 +3994,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46141.3125</v>
+        <v>46143.3125</v>
       </c>
       <c r="B128">
-        <v>286.728</v>
+        <v>922.192</v>
       </c>
       <c r="C128">
-        <v>108</v>
+        <v>806</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3435,13 +4011,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46141.32291666666</v>
+        <v>46143.32291666666</v>
       </c>
       <c r="B129">
-        <v>277.51</v>
+        <v>876.627</v>
       </c>
       <c r="C129">
-        <v>99</v>
+        <v>787</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3452,13 +4028,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46141.33333333334</v>
+        <v>46143.33333333334</v>
       </c>
       <c r="B130">
-        <v>323.265</v>
+        <v>915.421</v>
       </c>
       <c r="C130">
-        <v>80</v>
+        <v>798</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3469,13 +4045,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46141.34375</v>
+        <v>46143.34375</v>
       </c>
       <c r="B131">
-        <v>324.217</v>
+        <v>931.564</v>
       </c>
       <c r="C131">
-        <v>70</v>
+        <v>814</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3486,13 +4062,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46141.35416666666</v>
+        <v>46143.35416666666</v>
       </c>
       <c r="B132">
-        <v>329.726</v>
+        <v>952.314</v>
       </c>
       <c r="C132">
-        <v>76</v>
+        <v>868</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3503,13 +4079,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46141.36458333334</v>
+        <v>46143.36458333334</v>
       </c>
       <c r="B133">
-        <v>330.432</v>
+        <v>927.207</v>
       </c>
       <c r="C133">
-        <v>63</v>
+        <v>936</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3520,13 +4096,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46141.375</v>
+        <v>46143.375</v>
       </c>
       <c r="B134">
-        <v>343.325</v>
+        <v>1041.113</v>
       </c>
       <c r="C134">
-        <v>90</v>
+        <v>1059</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3537,13 +4113,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46141.38541666666</v>
+        <v>46143.38541666666</v>
       </c>
       <c r="B135">
-        <v>353.008</v>
+        <v>958.112</v>
       </c>
       <c r="C135">
-        <v>126</v>
+        <v>1035</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3554,13 +4130,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46141.39583333334</v>
+        <v>46143.39583333334</v>
       </c>
       <c r="B136">
-        <v>362.508</v>
+        <v>965.4299999999999</v>
       </c>
       <c r="C136">
-        <v>161</v>
+        <v>929</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3571,13 +4147,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46141.40625</v>
+        <v>46143.40625</v>
       </c>
       <c r="B137">
-        <v>374.271</v>
+        <v>968.65</v>
       </c>
       <c r="C137">
-        <v>166</v>
+        <v>904</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3588,13 +4164,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46141.41666666666</v>
+        <v>46143.41666666666</v>
       </c>
       <c r="B138">
-        <v>386.541</v>
+        <v>955.673</v>
       </c>
       <c r="C138">
-        <v>172</v>
+        <v>842</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3605,13 +4181,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46141.42708333334</v>
+        <v>46143.42708333334</v>
       </c>
       <c r="B139">
-        <v>396.382</v>
+        <v>932.078</v>
       </c>
       <c r="C139">
-        <v>158</v>
+        <v>774</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3622,13 +4198,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46141.4375</v>
+        <v>46143.4375</v>
       </c>
       <c r="B140">
-        <v>405.672</v>
+        <v>934.643</v>
       </c>
       <c r="C140">
-        <v>145</v>
+        <v>758</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3639,13 +4215,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46141.44791666666</v>
+        <v>46143.44791666666</v>
       </c>
       <c r="B141">
-        <v>414.995</v>
+        <v>922.645</v>
       </c>
       <c r="C141">
-        <v>171</v>
+        <v>685</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3656,13 +4232,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46141.45833333334</v>
+        <v>46143.45833333334</v>
       </c>
       <c r="B142">
-        <v>406.167</v>
+        <v>956.525</v>
       </c>
       <c r="C142">
-        <v>173</v>
+        <v>666</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3673,13 +4249,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46141.46875</v>
+        <v>46143.46875</v>
       </c>
       <c r="B143">
-        <v>417.166</v>
+        <v>937.03</v>
       </c>
       <c r="C143">
-        <v>220</v>
+        <v>636</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3690,13 +4266,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46141.47916666666</v>
+        <v>46143.47916666666</v>
       </c>
       <c r="B144">
-        <v>428.775</v>
+        <v>900.221</v>
       </c>
       <c r="C144">
-        <v>262</v>
+        <v>600</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3707,13 +4283,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46141.48958333334</v>
+        <v>46143.48958333334</v>
       </c>
       <c r="B145">
-        <v>439.906</v>
+        <v>899.5599999999999</v>
       </c>
       <c r="C145">
-        <v>275</v>
+        <v>606</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3724,13 +4300,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46141.5</v>
+        <v>46143.5</v>
       </c>
       <c r="B146">
-        <v>458.335</v>
+        <v>845.384</v>
       </c>
       <c r="C146">
-        <v>254</v>
+        <v>580</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3741,13 +4317,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46141.51041666666</v>
+        <v>46143.51041666666</v>
       </c>
       <c r="B147">
-        <v>473.635</v>
+        <v>832.093</v>
       </c>
       <c r="C147">
-        <v>267</v>
+        <v>579</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3758,13 +4334,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46141.52083333334</v>
+        <v>46143.52083333334</v>
       </c>
       <c r="B148">
-        <v>490.088</v>
+        <v>818.312</v>
       </c>
       <c r="C148">
-        <v>277</v>
+        <v>588</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3775,13 +4351,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46141.53125</v>
+        <v>46143.53125</v>
       </c>
       <c r="B149">
-        <v>506.022</v>
+        <v>804.1</v>
       </c>
       <c r="C149">
-        <v>303</v>
+        <v>596</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3792,13 +4368,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46141.54166666666</v>
+        <v>46143.54166666666</v>
       </c>
       <c r="B150">
-        <v>530.439</v>
+        <v>780.01</v>
       </c>
       <c r="C150">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3809,13 +4385,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46141.55208333334</v>
+        <v>46143.55208333334</v>
       </c>
       <c r="B151">
-        <v>559.462</v>
+        <v>767.635</v>
       </c>
       <c r="C151">
-        <v>376</v>
+        <v>550</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3826,13 +4402,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46141.5625</v>
+        <v>46143.5625</v>
       </c>
       <c r="B152">
-        <v>589.021</v>
+        <v>753.577</v>
       </c>
       <c r="C152">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3843,13 +4419,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46141.57291666666</v>
+        <v>46143.57291666666</v>
       </c>
       <c r="B153">
-        <v>618.462</v>
+        <v>738.374</v>
       </c>
       <c r="C153">
-        <v>610</v>
+        <v>516</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3860,13 +4436,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46141.58333333334</v>
+        <v>46143.58333333334</v>
       </c>
       <c r="B154">
-        <v>669.425</v>
+        <v>720.302</v>
       </c>
       <c r="C154">
-        <v>724</v>
+        <v>537</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3877,13 +4453,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46141.59375</v>
+        <v>46143.59375</v>
       </c>
       <c r="B155">
-        <v>695.582</v>
+        <v>710.277</v>
       </c>
       <c r="C155">
-        <v>729</v>
+        <v>520</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3894,13 +4470,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46141.60416666666</v>
+        <v>46143.60416666666</v>
       </c>
       <c r="B156">
-        <v>720.357</v>
+        <v>671.27</v>
       </c>
       <c r="C156">
-        <v>780</v>
+        <v>490</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3911,13 +4487,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46141.61458333334</v>
+        <v>46143.61458333334</v>
       </c>
       <c r="B157">
-        <v>748.28</v>
+        <v>672.854</v>
       </c>
       <c r="C157">
-        <v>839</v>
+        <v>475</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3928,13 +4504,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46141.625</v>
+        <v>46143.625</v>
       </c>
       <c r="B158">
-        <v>777.725</v>
+        <v>588.428</v>
       </c>
       <c r="C158">
-        <v>868</v>
+        <v>463</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3945,13 +4521,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46141.63541666666</v>
+        <v>46143.63541666666</v>
       </c>
       <c r="B159">
-        <v>795.747</v>
+        <v>591.874</v>
       </c>
       <c r="C159">
-        <v>903</v>
+        <v>410</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3962,13 +4538,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46141.64583333334</v>
+        <v>46143.64583333334</v>
       </c>
       <c r="B160">
-        <v>813.443</v>
+        <v>593.619</v>
       </c>
       <c r="C160">
-        <v>910</v>
+        <v>403</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3979,13 +4555,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46141.65625</v>
+        <v>46143.65625</v>
       </c>
       <c r="B161">
-        <v>830.962</v>
+        <v>591.163</v>
       </c>
       <c r="C161">
-        <v>928</v>
+        <v>415</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3996,13 +4572,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46141.66666666666</v>
+        <v>46143.66666666666</v>
       </c>
       <c r="B162">
-        <v>821.8099999999999</v>
+        <v>551.272</v>
       </c>
       <c r="C162">
-        <v>996</v>
+        <v>388</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -4013,13 +4589,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46141.67708333334</v>
+        <v>46143.67708333334</v>
       </c>
       <c r="B163">
-        <v>831.864</v>
+        <v>547.053</v>
       </c>
       <c r="C163">
-        <v>1023</v>
+        <v>341</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -4030,13 +4606,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46141.6875</v>
+        <v>46143.6875</v>
       </c>
       <c r="B164">
-        <v>841.284</v>
+        <v>541.573</v>
       </c>
       <c r="C164">
-        <v>1006</v>
+        <v>324</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -4047,13 +4623,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46141.69791666666</v>
+        <v>46143.69791666666</v>
       </c>
       <c r="B165">
-        <v>849.897</v>
+        <v>530.4880000000001</v>
       </c>
       <c r="C165">
-        <v>967</v>
+        <v>305</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -4064,13 +4640,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46141.70833333334</v>
+        <v>46143.70833333334</v>
       </c>
       <c r="B166">
-        <v>760.847</v>
+        <v>504.906</v>
       </c>
       <c r="C166">
-        <v>885</v>
+        <v>258</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -4081,13 +4657,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46141.71875</v>
+        <v>46143.71875</v>
       </c>
       <c r="B167">
-        <v>754.633</v>
+        <v>506.403</v>
       </c>
       <c r="C167">
-        <v>817</v>
+        <v>228</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -4098,13 +4674,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46141.72916666666</v>
+        <v>46143.72916666666</v>
       </c>
       <c r="B168">
-        <v>749.009</v>
+        <v>484.381</v>
       </c>
       <c r="C168">
-        <v>841</v>
+        <v>197</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -4115,13 +4691,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46141.73958333334</v>
+        <v>46143.73958333334</v>
       </c>
       <c r="B169">
-        <v>743.52</v>
+        <v>462.408</v>
       </c>
       <c r="C169">
-        <v>795</v>
+        <v>165</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -4132,13 +4708,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46141.75</v>
+        <v>46143.75</v>
       </c>
       <c r="B170">
-        <v>738.33</v>
+        <v>427.033</v>
       </c>
       <c r="C170">
-        <v>743</v>
+        <v>131</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -4149,13 +4725,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46141.76041666666</v>
+        <v>46143.76041666666</v>
       </c>
       <c r="B171">
-        <v>737.772</v>
+        <v>404.17</v>
       </c>
       <c r="C171">
-        <v>750</v>
+        <v>81</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -4166,13 +4742,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46141.77083333334</v>
+        <v>46143.77083333334</v>
       </c>
       <c r="B172">
-        <v>736.492</v>
+        <v>382.445</v>
       </c>
       <c r="C172">
-        <v>781</v>
+        <v>50</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -4183,13 +4759,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46141.78125</v>
+        <v>46143.78125</v>
       </c>
       <c r="B173">
-        <v>735.7140000000001</v>
+        <v>368.771</v>
       </c>
       <c r="C173">
-        <v>793</v>
+        <v>35</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -4200,13 +4776,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46141.79166666666</v>
+        <v>46143.79166666666</v>
       </c>
       <c r="B174">
-        <v>732.727</v>
+        <v>289.828</v>
       </c>
       <c r="C174">
-        <v>771</v>
+        <v>34</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -4217,13 +4793,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46141.80208333334</v>
+        <v>46143.80208333334</v>
       </c>
       <c r="B175">
-        <v>733.014</v>
+        <v>281.31</v>
       </c>
       <c r="C175">
-        <v>713</v>
+        <v>24</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -4234,13 +4810,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46141.8125</v>
+        <v>46143.8125</v>
       </c>
       <c r="B176">
-        <v>733.753</v>
+        <v>273.654</v>
       </c>
       <c r="C176">
-        <v>668</v>
+        <v>17</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -4251,13 +4827,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46141.82291666666</v>
+        <v>46143.82291666666</v>
       </c>
       <c r="B177">
-        <v>734.694</v>
+        <v>284.958</v>
       </c>
       <c r="C177">
-        <v>604</v>
+        <v>10</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -4268,13 +4844,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46141.83333333334</v>
+        <v>46143.83333333334</v>
       </c>
       <c r="B178">
-        <v>724.697</v>
+        <v>277.277</v>
       </c>
       <c r="C178">
-        <v>629</v>
+        <v>5</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -4285,13 +4861,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46141.84375</v>
+        <v>46143.84375</v>
       </c>
       <c r="B179">
-        <v>702.802</v>
+        <v>290.884</v>
       </c>
       <c r="C179">
-        <v>679</v>
+        <v>10</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4302,13 +4878,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46141.85416666666</v>
+        <v>46143.85416666666</v>
       </c>
       <c r="B180">
-        <v>681.704</v>
+        <v>284.935</v>
       </c>
       <c r="C180">
-        <v>775</v>
+        <v>1</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4319,13 +4895,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46141.86458333334</v>
+        <v>46143.86458333334</v>
       </c>
       <c r="B181">
-        <v>660.646</v>
+        <v>258.461</v>
       </c>
       <c r="C181">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4336,13 +4912,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46141.875</v>
+        <v>46143.875</v>
       </c>
       <c r="B182">
-        <v>638.54</v>
+        <v>271.312</v>
       </c>
       <c r="C182">
-        <v>828</v>
+        <v>0</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4353,13 +4929,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46141.88541666666</v>
+        <v>46143.88541666666</v>
       </c>
       <c r="B183">
-        <v>626.155</v>
+        <v>266.864</v>
       </c>
       <c r="C183">
-        <v>755</v>
+        <v>17</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4370,13 +4946,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46141.89583333334</v>
+        <v>46143.89583333334</v>
       </c>
       <c r="B184">
-        <v>612.587</v>
+        <v>255.233</v>
       </c>
       <c r="C184">
-        <v>726</v>
+        <v>26</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4387,13 +4963,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46141.90625</v>
+        <v>46143.90625</v>
       </c>
       <c r="B185">
-        <v>598.783</v>
+        <v>235.564</v>
       </c>
       <c r="C185">
-        <v>721</v>
+        <v>12</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4404,13 +4980,13 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46141.91666666666</v>
+        <v>46143.91666666666</v>
       </c>
       <c r="B186">
-        <v>586.925</v>
+        <v>225.077</v>
       </c>
       <c r="C186">
-        <v>740</v>
+        <v>14</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4421,13 +4997,13 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46141.92708333334</v>
+        <v>46143.92708333334</v>
       </c>
       <c r="B187">
-        <v>577.496</v>
+        <v>223.096</v>
       </c>
       <c r="C187">
-        <v>737</v>
+        <v>16</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4438,13 +5014,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46141.9375</v>
+        <v>46143.9375</v>
       </c>
       <c r="B188">
-        <v>570.268</v>
+        <v>221.719</v>
       </c>
       <c r="C188">
-        <v>713</v>
+        <v>9</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4455,13 +5031,13 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46141.94791666666</v>
+        <v>46143.94791666666</v>
       </c>
       <c r="B189">
-        <v>562.154</v>
+        <v>219.533</v>
       </c>
       <c r="C189">
-        <v>678</v>
+        <v>3</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4472,13 +5048,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46141.95833333334</v>
+        <v>46143.95833333334</v>
       </c>
       <c r="B190">
-        <v>616.958</v>
+        <v>200.448</v>
       </c>
       <c r="C190">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4489,13 +5065,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46141.96875</v>
+        <v>46143.96875</v>
       </c>
       <c r="B191">
-        <v>626.409</v>
+        <v>203.89</v>
       </c>
       <c r="C191">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4506,13 +5082,13 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46141.97916666666</v>
+        <v>46143.97916666666</v>
       </c>
       <c r="B192">
-        <v>625.082</v>
+        <v>198.773</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D192">
         <v>95</v>
@@ -4523,13 +5099,13 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46141.98958333334</v>
+        <v>46143.98958333334</v>
       </c>
       <c r="B193">
-        <v>622.006</v>
+        <v>191.299</v>
       </c>
       <c r="C193">
-        <v>609</v>
+        <v>8</v>
       </c>
       <c r="D193">
         <v>96</v>
@@ -4540,13 +5116,13 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="B194">
-        <v>648.849</v>
+        <v>175.891</v>
       </c>
       <c r="C194">
-        <v>636</v>
+        <v>13</v>
       </c>
       <c r="D194">
         <v>1</v>
@@ -4557,13 +5133,13 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46142.01041666666</v>
+        <v>46144.01041666666</v>
       </c>
       <c r="B195">
-        <v>652.102</v>
+        <v>178.385</v>
       </c>
       <c r="C195">
-        <v>638</v>
+        <v>23</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -4574,13 +5150,13 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46142.02083333334</v>
+        <v>46144.02083333334</v>
       </c>
       <c r="B196">
-        <v>652.4349999999999</v>
+        <v>178.006</v>
       </c>
       <c r="C196">
-        <v>625</v>
+        <v>34</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -4591,13 +5167,13 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46142.03125</v>
+        <v>46144.03125</v>
       </c>
       <c r="B197">
-        <v>657.736</v>
+        <v>179.661</v>
       </c>
       <c r="C197">
-        <v>616</v>
+        <v>49</v>
       </c>
       <c r="D197">
         <v>4</v>
@@ -4608,13 +5184,13 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46142.04166666666</v>
+        <v>46144.04166666666</v>
       </c>
       <c r="B198">
-        <v>634.076</v>
+        <v>180.041</v>
       </c>
       <c r="C198">
-        <v>613</v>
+        <v>70</v>
       </c>
       <c r="D198">
         <v>5</v>
@@ -4625,13 +5201,13 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46142.05208333334</v>
+        <v>46144.05208333334</v>
       </c>
       <c r="B199">
-        <v>645.49</v>
+        <v>188.54</v>
       </c>
       <c r="C199">
-        <v>604</v>
+        <v>92</v>
       </c>
       <c r="D199">
         <v>6</v>
@@ -4642,13 +5218,13 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46142.0625</v>
+        <v>46144.0625</v>
       </c>
       <c r="B200">
-        <v>659.099</v>
+        <v>197.437</v>
       </c>
       <c r="C200">
-        <v>613</v>
+        <v>100</v>
       </c>
       <c r="D200">
         <v>7</v>
@@ -4659,13 +5235,13 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46142.07291666666</v>
+        <v>46144.07291666666</v>
       </c>
       <c r="B201">
-        <v>675.169</v>
+        <v>210.534</v>
       </c>
       <c r="C201">
-        <v>628</v>
+        <v>107</v>
       </c>
       <c r="D201">
         <v>8</v>
@@ -4676,13 +5252,13 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46142.08333333334</v>
+        <v>46144.08333333334</v>
       </c>
       <c r="B202">
-        <v>684.753</v>
+        <v>244.048</v>
       </c>
       <c r="C202">
-        <v>612</v>
+        <v>116</v>
       </c>
       <c r="D202">
         <v>9</v>
@@ -4693,13 +5269,13 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46142.09375</v>
+        <v>46144.09375</v>
       </c>
       <c r="B203">
-        <v>698.7910000000001</v>
+        <v>266.242</v>
       </c>
       <c r="C203">
-        <v>579</v>
+        <v>106</v>
       </c>
       <c r="D203">
         <v>10</v>
@@ -4710,13 +5286,13 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46142.10416666666</v>
+        <v>46144.10416666666</v>
       </c>
       <c r="B204">
-        <v>712.357</v>
+        <v>285.742</v>
       </c>
       <c r="C204">
-        <v>582</v>
+        <v>103</v>
       </c>
       <c r="D204">
         <v>11</v>
@@ -4727,13 +5303,13 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46142.11458333334</v>
+        <v>46144.11458333334</v>
       </c>
       <c r="B205">
-        <v>729.8819999999999</v>
+        <v>305.258</v>
       </c>
       <c r="C205">
-        <v>572</v>
+        <v>107</v>
       </c>
       <c r="D205">
         <v>12</v>
@@ -4744,13 +5320,13 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46142.125</v>
+        <v>46144.125</v>
       </c>
       <c r="B206">
-        <v>753.501</v>
+        <v>339.096</v>
       </c>
       <c r="C206">
-        <v>544</v>
+        <v>108</v>
       </c>
       <c r="D206">
         <v>13</v>
@@ -4761,13 +5337,13 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46142.13541666666</v>
+        <v>46144.13541666666</v>
       </c>
       <c r="B207">
-        <v>774.6660000000001</v>
+        <v>361.566</v>
       </c>
       <c r="C207">
-        <v>532</v>
+        <v>130</v>
       </c>
       <c r="D207">
         <v>14</v>
@@ -4778,13 +5354,13 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46142.14583333334</v>
+        <v>46144.14583333334</v>
       </c>
       <c r="B208">
-        <v>790.66</v>
+        <v>372.807</v>
       </c>
       <c r="C208">
-        <v>521</v>
+        <v>189</v>
       </c>
       <c r="D208">
         <v>15</v>
@@ -4795,13 +5371,13 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46142.15625</v>
+        <v>46144.15625</v>
       </c>
       <c r="B209">
-        <v>815.938</v>
+        <v>385.906</v>
       </c>
       <c r="C209">
-        <v>511</v>
+        <v>230</v>
       </c>
       <c r="D209">
         <v>16</v>
@@ -4812,13 +5388,13 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46142.16666666666</v>
+        <v>46144.16666666666</v>
       </c>
       <c r="B210">
-        <v>848.564</v>
+        <v>400.04</v>
       </c>
       <c r="C210">
-        <v>538</v>
+        <v>277</v>
       </c>
       <c r="D210">
         <v>17</v>
@@ -4829,13 +5405,13 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46142.17708333334</v>
+        <v>46144.17708333334</v>
       </c>
       <c r="B211">
-        <v>868.607</v>
+        <v>418.064</v>
       </c>
       <c r="C211">
-        <v>563</v>
+        <v>302</v>
       </c>
       <c r="D211">
         <v>18</v>
@@ -4846,13 +5422,13 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46142.1875</v>
+        <v>46144.1875</v>
       </c>
       <c r="B212">
-        <v>891.778</v>
+        <v>436.469</v>
       </c>
       <c r="C212">
-        <v>592</v>
+        <v>336</v>
       </c>
       <c r="D212">
         <v>19</v>
@@ -4863,13 +5439,13 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46142.19791666666</v>
+        <v>46144.19791666666</v>
       </c>
       <c r="B213">
-        <v>910.2329999999999</v>
+        <v>454.05</v>
       </c>
       <c r="C213">
-        <v>606</v>
+        <v>361</v>
       </c>
       <c r="D213">
         <v>20</v>
@@ -4880,13 +5456,13 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46142.20833333334</v>
+        <v>46144.20833333334</v>
       </c>
       <c r="B214">
-        <v>971.033</v>
+        <v>485.903</v>
       </c>
       <c r="C214">
-        <v>623</v>
+        <v>406</v>
       </c>
       <c r="D214">
         <v>21</v>
@@ -4897,13 +5473,13 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46142.21875</v>
+        <v>46144.21875</v>
       </c>
       <c r="B215">
-        <v>996.926</v>
+        <v>489.119</v>
       </c>
       <c r="C215">
-        <v>627</v>
+        <v>404</v>
       </c>
       <c r="D215">
         <v>22</v>
@@ -4914,13 +5490,13 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46142.22916666666</v>
+        <v>46144.22916666666</v>
       </c>
       <c r="B216">
-        <v>1022.417</v>
+        <v>494.769</v>
       </c>
       <c r="C216">
-        <v>641</v>
+        <v>388</v>
       </c>
       <c r="D216">
         <v>23</v>
@@ -4931,13 +5507,13 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46142.23958333334</v>
+        <v>46144.23958333334</v>
       </c>
       <c r="B217">
-        <v>1045.328</v>
+        <v>500.894</v>
       </c>
       <c r="C217">
-        <v>674</v>
+        <v>391</v>
       </c>
       <c r="D217">
         <v>24</v>
@@ -4948,13 +5524,13 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46142.25</v>
+        <v>46144.25</v>
       </c>
       <c r="B218">
-        <v>1119.208</v>
+        <v>512.787</v>
       </c>
       <c r="C218">
-        <v>672</v>
+        <v>383</v>
       </c>
       <c r="D218">
         <v>25</v>
@@ -4965,13 +5541,13 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46142.26041666666</v>
+        <v>46144.26041666666</v>
       </c>
       <c r="B219">
-        <v>1142.173</v>
+        <v>506.717</v>
       </c>
       <c r="C219">
-        <v>686</v>
+        <v>371</v>
       </c>
       <c r="D219">
         <v>26</v>
@@ -4982,13 +5558,13 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46142.27083333334</v>
+        <v>46144.27083333334</v>
       </c>
       <c r="B220">
-        <v>1160.553</v>
+        <v>501.829</v>
       </c>
       <c r="C220">
-        <v>713</v>
+        <v>350</v>
       </c>
       <c r="D220">
         <v>27</v>
@@ -4999,13 +5575,13 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46142.28125</v>
+        <v>46144.28125</v>
       </c>
       <c r="B221">
-        <v>1164.352</v>
+        <v>494.943</v>
       </c>
       <c r="C221">
-        <v>723</v>
+        <v>335</v>
       </c>
       <c r="D221">
         <v>28</v>
@@ -5016,13 +5592,13 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46142.29166666666</v>
+        <v>46144.29166666666</v>
       </c>
       <c r="B222">
-        <v>1215.261</v>
+        <v>494.188</v>
       </c>
       <c r="C222">
-        <v>710</v>
+        <v>329</v>
       </c>
       <c r="D222">
         <v>29</v>
@@ -5033,13 +5609,13 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46142.30208333334</v>
+        <v>46144.30208333334</v>
       </c>
       <c r="B223">
-        <v>1213.192</v>
+        <v>466.67</v>
       </c>
       <c r="C223">
-        <v>683</v>
+        <v>296</v>
       </c>
       <c r="D223">
         <v>30</v>
@@ -5050,13 +5626,13 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46142.3125</v>
+        <v>46144.3125</v>
       </c>
       <c r="B224">
-        <v>1210.118</v>
+        <v>448.283</v>
       </c>
       <c r="C224">
-        <v>628</v>
+        <v>256</v>
       </c>
       <c r="D224">
         <v>31</v>
@@ -5067,13 +5643,13 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46142.32291666666</v>
+        <v>46144.32291666666</v>
       </c>
       <c r="B225">
-        <v>1220.582</v>
+        <v>425.188</v>
       </c>
       <c r="C225">
-        <v>605</v>
+        <v>211</v>
       </c>
       <c r="D225">
         <v>32</v>
@@ -5084,13 +5660,13 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46142.33333333334</v>
+        <v>46144.33333333334</v>
       </c>
       <c r="B226">
-        <v>1116.184</v>
+        <v>410.483</v>
       </c>
       <c r="C226">
-        <v>609</v>
+        <v>184</v>
       </c>
       <c r="D226">
         <v>33</v>
@@ -5101,13 +5677,13 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46142.34375</v>
+        <v>46144.34375</v>
       </c>
       <c r="B227">
-        <v>1119.482</v>
+        <v>400.578</v>
       </c>
       <c r="C227">
-        <v>626</v>
+        <v>178</v>
       </c>
       <c r="D227">
         <v>34</v>
@@ -5118,13 +5694,13 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46142.35416666666</v>
+        <v>46144.35416666666</v>
       </c>
       <c r="B228">
-        <v>1134.834</v>
+        <v>395.201</v>
       </c>
       <c r="C228">
-        <v>677</v>
+        <v>184</v>
       </c>
       <c r="D228">
         <v>35</v>
@@ -5135,13 +5711,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46142.36458333334</v>
+        <v>46144.36458333334</v>
       </c>
       <c r="B229">
-        <v>1142.694</v>
+        <v>389.635</v>
       </c>
       <c r="C229">
-        <v>767</v>
+        <v>167</v>
       </c>
       <c r="D229">
         <v>36</v>
@@ -5152,13 +5728,13 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46142.375</v>
+        <v>46144.375</v>
       </c>
       <c r="B230">
-        <v>1318.648</v>
+        <v>439.254</v>
       </c>
       <c r="C230">
-        <v>867</v>
+        <v>177</v>
       </c>
       <c r="D230">
         <v>37</v>
@@ -5169,13 +5745,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46142.38541666666</v>
+        <v>46144.38541666666</v>
       </c>
       <c r="B231">
-        <v>1331.289</v>
+        <v>431.31</v>
       </c>
       <c r="C231">
-        <v>975</v>
+        <v>204</v>
       </c>
       <c r="D231">
         <v>38</v>
@@ -5186,13 +5762,13 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46142.39583333334</v>
+        <v>46144.39583333334</v>
       </c>
       <c r="B232">
-        <v>1343.271</v>
+        <v>389.802</v>
       </c>
       <c r="C232">
-        <v>1142</v>
+        <v>247</v>
       </c>
       <c r="D232">
         <v>39</v>
@@ -5203,13 +5779,13 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46142.40625</v>
+        <v>46144.40625</v>
       </c>
       <c r="B233">
-        <v>1318.529</v>
+        <v>390.304</v>
       </c>
       <c r="C233">
-        <v>1198</v>
+        <v>261</v>
       </c>
       <c r="D233">
         <v>40</v>
@@ -5220,13 +5796,13 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46142.41666666666</v>
+        <v>46144.41666666666</v>
       </c>
       <c r="B234">
-        <v>1369.836</v>
+        <v>414.845</v>
       </c>
       <c r="C234">
-        <v>1279</v>
+        <v>247</v>
       </c>
       <c r="D234">
         <v>41</v>
@@ -5237,13 +5813,13 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46142.42708333334</v>
+        <v>46144.42708333334</v>
       </c>
       <c r="B235">
-        <v>1345.14</v>
+        <v>432.394</v>
       </c>
       <c r="C235">
-        <v>1396</v>
+        <v>226</v>
       </c>
       <c r="D235">
         <v>42</v>
@@ -5254,13 +5830,13 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46142.4375</v>
+        <v>46144.4375</v>
       </c>
       <c r="B236">
-        <v>1387.805</v>
+        <v>436.048</v>
       </c>
       <c r="C236">
-        <v>1409</v>
+        <v>220</v>
       </c>
       <c r="D236">
         <v>43</v>
@@ -5271,13 +5847,13 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46142.44791666666</v>
+        <v>46144.44791666666</v>
       </c>
       <c r="B237">
-        <v>1416.536</v>
+        <v>441.078</v>
       </c>
       <c r="C237">
-        <v>1402</v>
+        <v>227</v>
       </c>
       <c r="D237">
         <v>44</v>
@@ -5288,13 +5864,13 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46142.45833333334</v>
+        <v>46144.45833333334</v>
       </c>
       <c r="B238">
-        <v>1494.563</v>
+        <v>426.277</v>
       </c>
       <c r="C238">
-        <v>1470</v>
+        <v>234</v>
       </c>
       <c r="D238">
         <v>45</v>
@@ -5305,13 +5881,13 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46142.46875</v>
+        <v>46144.46875</v>
       </c>
       <c r="B239">
-        <v>1513.067</v>
+        <v>434.08</v>
       </c>
       <c r="C239">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="D239">
         <v>46</v>
@@ -5322,13 +5898,13 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46142.47916666666</v>
+        <v>46144.47916666666</v>
       </c>
       <c r="B240">
-        <v>1535.332</v>
+        <v>463.706</v>
       </c>
       <c r="C240">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="D240">
         <v>47</v>
@@ -5339,13 +5915,13 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46142.48958333334</v>
+        <v>46144.48958333334</v>
       </c>
       <c r="B241">
-        <v>1553.759</v>
+        <v>483.496</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="D241">
         <v>48</v>
@@ -5356,13 +5932,13 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46142.5</v>
+        <v>46144.5</v>
       </c>
       <c r="B242">
-        <v>1585.976</v>
+        <v>480.085</v>
       </c>
       <c r="C242">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="D242">
         <v>49</v>
@@ -5373,13 +5949,13 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46142.51041666666</v>
+        <v>46144.51041666666</v>
       </c>
       <c r="B243">
-        <v>1610.747</v>
+        <v>491.936</v>
       </c>
       <c r="C243">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="D243">
         <v>50</v>
@@ -5390,13 +5966,13 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46142.52083333334</v>
+        <v>46144.52083333334</v>
       </c>
       <c r="B244">
-        <v>1587.508</v>
+        <v>505.181</v>
       </c>
       <c r="C244">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="D244">
         <v>51</v>
@@ -5407,13 +5983,13 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46142.53125</v>
+        <v>46144.53125</v>
       </c>
       <c r="B245">
-        <v>1609.954</v>
+        <v>520.053</v>
       </c>
       <c r="C245">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="D245">
         <v>52</v>
@@ -5424,13 +6000,13 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46142.54166666666</v>
+        <v>46144.54166666666</v>
       </c>
       <c r="B246">
-        <v>1615.319</v>
+        <v>532.427</v>
       </c>
       <c r="C246">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="D246">
         <v>53</v>
@@ -5441,13 +6017,13 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46142.55208333334</v>
+        <v>46144.55208333334</v>
       </c>
       <c r="B247">
-        <v>1623.051</v>
+        <v>562.074</v>
       </c>
       <c r="C247">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="D247">
         <v>54</v>
@@ -5458,13 +6034,13 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46142.5625</v>
+        <v>46144.5625</v>
       </c>
       <c r="B248">
-        <v>1629.591</v>
+        <v>584.187</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="D248">
         <v>55</v>
@@ -5475,13 +6051,13 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46142.57291666666</v>
+        <v>46144.57291666666</v>
       </c>
       <c r="B249">
-        <v>1690.212</v>
+        <v>604.777</v>
       </c>
       <c r="C249">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="D249">
         <v>56</v>
@@ -5492,13 +6068,13 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46142.58333333334</v>
+        <v>46144.58333333334</v>
       </c>
       <c r="B250">
-        <v>1691.257</v>
+        <v>629.694</v>
       </c>
       <c r="C250">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="D250">
         <v>57</v>
@@ -5509,13 +6085,13 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46142.59375</v>
+        <v>46144.59375</v>
       </c>
       <c r="B251">
-        <v>1684.456</v>
+        <v>644.5940000000001</v>
       </c>
       <c r="C251">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="D251">
         <v>58</v>
@@ -5526,13 +6102,13 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46142.60416666666</v>
+        <v>46144.60416666666</v>
       </c>
       <c r="B252">
-        <v>1730.248</v>
+        <v>657.562</v>
       </c>
       <c r="C252">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="D252">
         <v>59</v>
@@ -5543,13 +6119,13 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46142.61458333334</v>
+        <v>46144.61458333334</v>
       </c>
       <c r="B253">
-        <v>1667.491</v>
+        <v>669.721</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="D253">
         <v>60</v>
@@ -5560,13 +6136,13 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46142.625</v>
+        <v>46144.625</v>
       </c>
       <c r="B254">
-        <v>1651.491</v>
+        <v>699.797</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="D254">
         <v>61</v>
@@ -5577,13 +6153,13 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46142.63541666666</v>
+        <v>46144.63541666666</v>
       </c>
       <c r="B255">
-        <v>1639.549</v>
+        <v>697.461</v>
       </c>
       <c r="C255">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="D255">
         <v>62</v>
@@ -5594,13 +6170,13 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46142.64583333334</v>
+        <v>46144.64583333334</v>
       </c>
       <c r="B256">
-        <v>1678.808</v>
+        <v>697.5309999999999</v>
       </c>
       <c r="C256">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="D256">
         <v>63</v>
@@ -5611,13 +6187,13 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46142.65625</v>
+        <v>46144.65625</v>
       </c>
       <c r="B257">
-        <v>1664.533</v>
+        <v>697.808</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="D257">
         <v>64</v>
@@ -5628,13 +6204,13 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46142.66666666666</v>
+        <v>46144.66666666666</v>
       </c>
       <c r="B258">
-        <v>1596.839</v>
+        <v>598.196</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="D258">
         <v>65</v>
@@ -5645,13 +6221,13 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46142.67708333334</v>
+        <v>46144.67708333334</v>
       </c>
       <c r="B259">
-        <v>1561.902</v>
+        <v>593.64</v>
       </c>
       <c r="C259">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="D259">
         <v>66</v>
@@ -5662,13 +6238,13 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46142.6875</v>
+        <v>46144.6875</v>
       </c>
       <c r="B260">
-        <v>1523.067</v>
+        <v>588.54</v>
       </c>
       <c r="C260">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="D260">
         <v>67</v>
@@ -5679,13 +6255,13 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46142.69791666666</v>
+        <v>46144.69791666666</v>
       </c>
       <c r="B261">
-        <v>1481.622</v>
+        <v>583.206</v>
       </c>
       <c r="C261">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -5696,13 +6272,13 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46142.70833333334</v>
+        <v>46144.70833333334</v>
       </c>
       <c r="B262">
-        <v>1202.378</v>
+        <v>580.489</v>
       </c>
       <c r="C262">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="D262">
         <v>69</v>
@@ -5713,13 +6289,13 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46142.71875</v>
+        <v>46144.71875</v>
       </c>
       <c r="B263">
-        <v>1140.683</v>
+        <v>561.557</v>
       </c>
       <c r="C263">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="D263">
         <v>70</v>
@@ -5730,13 +6306,13 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46142.72916666666</v>
+        <v>46144.72916666666</v>
       </c>
       <c r="B264">
-        <v>1082.644</v>
+        <v>543.02</v>
       </c>
       <c r="C264">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="D264">
         <v>71</v>
@@ -5747,13 +6323,13 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46142.73958333334</v>
+        <v>46144.73958333334</v>
       </c>
       <c r="B265">
-        <v>1026.684</v>
+        <v>525.8579999999999</v>
       </c>
       <c r="C265">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="D265">
         <v>72</v>
@@ -5764,13 +6340,13 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46142.75</v>
+        <v>46144.75</v>
       </c>
       <c r="B266">
-        <v>934.331</v>
+        <v>497.468</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="D266">
         <v>73</v>
@@ -5781,13 +6357,13 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46142.76041666666</v>
+        <v>46144.76041666666</v>
       </c>
       <c r="B267">
-        <v>873.372</v>
+        <v>475.4</v>
       </c>
       <c r="C267">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="D267">
         <v>74</v>
@@ -5798,13 +6374,13 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46142.77083333334</v>
+        <v>46144.77083333334</v>
       </c>
       <c r="B268">
-        <v>814.657</v>
+        <v>453.722</v>
       </c>
       <c r="C268">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="D268">
         <v>75</v>
@@ -5815,13 +6391,13 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46142.78125</v>
+        <v>46144.78125</v>
       </c>
       <c r="B269">
-        <v>755.008</v>
+        <v>433.357</v>
       </c>
       <c r="C269">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="D269">
         <v>76</v>
@@ -5832,13 +6408,13 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46142.79166666666</v>
+        <v>46144.79166666666</v>
       </c>
       <c r="B270">
-        <v>684.558</v>
+        <v>414.863</v>
       </c>
       <c r="C270">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="D270">
         <v>77</v>
@@ -5849,13 +6425,13 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46142.80208333334</v>
+        <v>46144.80208333334</v>
       </c>
       <c r="B271">
-        <v>645.986</v>
+        <v>406.643</v>
       </c>
       <c r="C271">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="D271">
         <v>78</v>
@@ -5866,13 +6442,13 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46142.8125</v>
+        <v>46144.8125</v>
       </c>
       <c r="B272">
-        <v>608.806</v>
+        <v>399.155</v>
       </c>
       <c r="C272">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="D272">
         <v>79</v>
@@ -5883,13 +6459,13 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46142.82291666666</v>
+        <v>46144.82291666666</v>
       </c>
       <c r="B273">
-        <v>571.515</v>
+        <v>392.612</v>
       </c>
       <c r="C273">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="D273">
         <v>80</v>
@@ -5900,13 +6476,13 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46142.83333333334</v>
+        <v>46144.83333333334</v>
       </c>
       <c r="B274">
-        <v>515.564</v>
+        <v>405.378</v>
       </c>
       <c r="C274">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="D274">
         <v>81</v>
@@ -5917,13 +6493,13 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46142.84375</v>
+        <v>46144.84375</v>
       </c>
       <c r="B275">
-        <v>494.889</v>
+        <v>400.436</v>
       </c>
       <c r="C275">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="D275">
         <v>82</v>
@@ -5934,13 +6510,13 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46142.85416666666</v>
+        <v>46144.85416666666</v>
       </c>
       <c r="B276">
-        <v>474.77</v>
+        <v>395.875</v>
       </c>
       <c r="C276">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="D276">
         <v>83</v>
@@ -5951,13 +6527,13 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46142.86458333334</v>
+        <v>46144.86458333334</v>
       </c>
       <c r="B277">
-        <v>454.56</v>
+        <v>390.298</v>
       </c>
       <c r="C277">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="D277">
         <v>84</v>
@@ -5968,13 +6544,13 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46142.875</v>
+        <v>46144.875</v>
       </c>
       <c r="B278">
-        <v>448.509</v>
+        <v>390.071</v>
       </c>
       <c r="C278">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="D278">
         <v>85</v>
@@ -5985,13 +6561,13 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46142.88541666666</v>
+        <v>46144.88541666666</v>
       </c>
       <c r="B279">
-        <v>445.173</v>
+        <v>392.027</v>
       </c>
       <c r="C279">
-        <v>0</v>
+        <v>452</v>
       </c>
       <c r="D279">
         <v>86</v>
@@ -6002,13 +6578,13 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46142.89583333334</v>
+        <v>46144.89583333334</v>
       </c>
       <c r="B280">
-        <v>442.81</v>
+        <v>394.767</v>
       </c>
       <c r="C280">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="D280">
         <v>87</v>
@@ -6019,13 +6595,13 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46142.90625</v>
+        <v>46144.90625</v>
       </c>
       <c r="B281">
-        <v>429.088</v>
+        <v>397.527</v>
       </c>
       <c r="C281">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="D281">
         <v>88</v>
@@ -6036,13 +6612,13 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46142.91666666666</v>
+        <v>46144.91666666666</v>
       </c>
       <c r="B282">
-        <v>448.858</v>
+        <v>406.994</v>
       </c>
       <c r="C282">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="D282">
         <v>89</v>
@@ -6053,13 +6629,13 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46142.92708333334</v>
+        <v>46144.92708333334</v>
       </c>
       <c r="B283">
-        <v>469.044</v>
+        <v>415.246</v>
       </c>
       <c r="C283">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="D283">
         <v>90</v>
@@ -6070,13 +6646,13 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46142.9375</v>
+        <v>46144.9375</v>
       </c>
       <c r="B284">
-        <v>489.697</v>
+        <v>425.787</v>
       </c>
       <c r="C284">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="D284">
         <v>91</v>
@@ -6087,13 +6663,13 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46142.94791666666</v>
+        <v>46144.94791666666</v>
       </c>
       <c r="B285">
-        <v>509.745</v>
+        <v>435.688</v>
       </c>
       <c r="C285">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="D285">
         <v>92</v>
@@ -6104,13 +6680,13 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="2">
-        <v>46142.95833333334</v>
+        <v>46144.95833333334</v>
       </c>
       <c r="B286">
-        <v>0</v>
+        <v>395.144</v>
       </c>
       <c r="C286">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="D286">
         <v>93</v>
@@ -6121,13 +6697,13 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="2">
-        <v>46142.96875</v>
+        <v>46144.96875</v>
       </c>
       <c r="B287">
-        <v>0</v>
+        <v>410.152</v>
       </c>
       <c r="C287">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="D287">
         <v>94</v>
@@ -6138,13 +6714,13 @@
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="2">
-        <v>46142.97916666666</v>
+        <v>46144.97916666666</v>
       </c>
       <c r="B288">
-        <v>0</v>
+        <v>423.146</v>
       </c>
       <c r="C288">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="D288">
         <v>95</v>
@@ -6155,19 +6731,3283 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="2">
-        <v>46142.98958333334</v>
+        <v>46144.98958333334</v>
       </c>
       <c r="B289">
-        <v>0</v>
+        <v>437.293</v>
       </c>
       <c r="C289">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="D289">
         <v>96</v>
       </c>
       <c r="E289" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46145</v>
+      </c>
+      <c r="B290">
+        <v>426.414</v>
+      </c>
+      <c r="C290">
+        <v>367</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46145.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>447.362</v>
+      </c>
+      <c r="C291">
+        <v>370</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46145.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>471.742</v>
+      </c>
+      <c r="C292">
+        <v>364</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46145.03125</v>
+      </c>
+      <c r="B293">
+        <v>491.669</v>
+      </c>
+      <c r="C293">
+        <v>366</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46145.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>508.34</v>
+      </c>
+      <c r="C294">
+        <v>378</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46145.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>550.475</v>
+      </c>
+      <c r="C295">
+        <v>409</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46145.0625</v>
+      </c>
+      <c r="B296">
+        <v>580.9400000000001</v>
+      </c>
+      <c r="C296">
+        <v>442</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46145.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>619.338</v>
+      </c>
+      <c r="C297">
+        <v>467</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46145.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>657.232</v>
+      </c>
+      <c r="C298">
+        <v>479</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46145.09375</v>
+      </c>
+      <c r="B299">
+        <v>703.506</v>
+      </c>
+      <c r="C299">
+        <v>497</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46145.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>737.8440000000001</v>
+      </c>
+      <c r="C300">
+        <v>528</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46145.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>779.024</v>
+      </c>
+      <c r="C301">
+        <v>587</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46145.125</v>
+      </c>
+      <c r="B302">
+        <v>817.7</v>
+      </c>
+      <c r="C302">
+        <v>618</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46145.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>837.847</v>
+      </c>
+      <c r="C303">
+        <v>640</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46145.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>856.865</v>
+      </c>
+      <c r="C304">
+        <v>682</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46145.15625</v>
+      </c>
+      <c r="B305">
+        <v>873.285</v>
+      </c>
+      <c r="C305">
+        <v>740</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46145.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>908.752</v>
+      </c>
+      <c r="C306">
+        <v>792</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46145.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>916.04</v>
+      </c>
+      <c r="C307">
+        <v>839</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46145.1875</v>
+      </c>
+      <c r="B308">
+        <v>921.525</v>
+      </c>
+      <c r="C308">
+        <v>869</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46145.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>937.221</v>
+      </c>
+      <c r="C309">
+        <v>891</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46145.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>968.8440000000001</v>
+      </c>
+      <c r="C310">
+        <v>938</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46145.21875</v>
+      </c>
+      <c r="B311">
+        <v>979.3390000000001</v>
+      </c>
+      <c r="C311">
+        <v>976</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46145.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>983.303</v>
+      </c>
+      <c r="C312">
+        <v>996</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46145.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>993.451</v>
+      </c>
+      <c r="C313">
+        <v>991</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46145.25</v>
+      </c>
+      <c r="B314">
+        <v>1001.058</v>
+      </c>
+      <c r="C314">
+        <v>942</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46145.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>992.658</v>
+      </c>
+      <c r="C315">
+        <v>878</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46145.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>974.793</v>
+      </c>
+      <c r="C316">
+        <v>802</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46145.28125</v>
+      </c>
+      <c r="B317">
+        <v>972.3</v>
+      </c>
+      <c r="C317">
+        <v>690</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46145.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>955.4059999999999</v>
+      </c>
+      <c r="C318">
+        <v>579</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46145.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>914.048</v>
+      </c>
+      <c r="C319">
+        <v>488</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46145.3125</v>
+      </c>
+      <c r="B320">
+        <v>878.848</v>
+      </c>
+      <c r="C320">
+        <v>441</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46145.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>828.925</v>
+      </c>
+      <c r="C321">
+        <v>399</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46145.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>836.333</v>
+      </c>
+      <c r="C322">
+        <v>428</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46145.34375</v>
+      </c>
+      <c r="B323">
+        <v>861.999</v>
+      </c>
+      <c r="C323">
+        <v>528</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46145.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>897.938</v>
+      </c>
+      <c r="C324">
+        <v>630</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46145.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>920.577</v>
+      </c>
+      <c r="C325">
+        <v>700</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46145.375</v>
+      </c>
+      <c r="B326">
+        <v>1121.256</v>
+      </c>
+      <c r="C326">
+        <v>734</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46145.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>1127.352</v>
+      </c>
+      <c r="C327">
+        <v>724</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46145.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>1132.849</v>
+      </c>
+      <c r="C328">
+        <v>719</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46145.40625</v>
+      </c>
+      <c r="B329">
+        <v>1095.427</v>
+      </c>
+      <c r="C329">
+        <v>673</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46145.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>1050.003</v>
+      </c>
+      <c r="C330">
+        <v>601</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46145.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>1045.849</v>
+      </c>
+      <c r="C331">
+        <v>576</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46145.4375</v>
+      </c>
+      <c r="B332">
+        <v>1041.948</v>
+      </c>
+      <c r="C332">
+        <v>554</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46145.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>997.025</v>
+      </c>
+      <c r="C333">
+        <v>506</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46145.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>1025.23</v>
+      </c>
+      <c r="C334">
+        <v>482</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46145.46875</v>
+      </c>
+      <c r="B335">
+        <v>972.605</v>
+      </c>
+      <c r="C335">
+        <v>428</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46145.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>957.8200000000001</v>
+      </c>
+      <c r="C336">
+        <v>417</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46145.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>944.837</v>
+      </c>
+      <c r="C337">
+        <v>389</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46145.5</v>
+      </c>
+      <c r="B338">
+        <v>924.836</v>
+      </c>
+      <c r="C338">
+        <v>405</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46145.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>912.092</v>
+      </c>
+      <c r="C339">
+        <v>388</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46145.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>899.021</v>
+      </c>
+      <c r="C340">
+        <v>323</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46145.53125</v>
+      </c>
+      <c r="B341">
+        <v>886.409</v>
+      </c>
+      <c r="C341">
+        <v>329</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46145.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>720.391</v>
+      </c>
+      <c r="C342">
+        <v>310</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46145.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>705.318</v>
+      </c>
+      <c r="C343">
+        <v>269</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46145.5625</v>
+      </c>
+      <c r="B344">
+        <v>699.3150000000001</v>
+      </c>
+      <c r="C344">
+        <v>275</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46145.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>692.77</v>
+      </c>
+      <c r="C345">
+        <v>282</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46145.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>832.991</v>
+      </c>
+      <c r="C346">
+        <v>313</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46145.59375</v>
+      </c>
+      <c r="B347">
+        <v>827.9160000000001</v>
+      </c>
+      <c r="C347">
+        <v>332</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46145.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>822.174</v>
+      </c>
+      <c r="C348">
+        <v>376</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46145.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>816.1130000000001</v>
+      </c>
+      <c r="C349">
+        <v>388</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46145.625</v>
+      </c>
+      <c r="B350">
+        <v>822.3049999999999</v>
+      </c>
+      <c r="C350">
+        <v>445</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46145.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>812.607</v>
+      </c>
+      <c r="C351">
+        <v>454</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46145.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>803.894</v>
+      </c>
+      <c r="C352">
+        <v>477</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46145.65625</v>
+      </c>
+      <c r="B353">
+        <v>795.413</v>
+      </c>
+      <c r="C353">
+        <v>478</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46145.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>663.693</v>
+      </c>
+      <c r="C354">
+        <v>482</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46145.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>667.136</v>
+      </c>
+      <c r="C355">
+        <v>416</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46145.6875</v>
+      </c>
+      <c r="B356">
+        <v>680.797</v>
+      </c>
+      <c r="C356">
+        <v>443</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46145.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>666.1609999999999</v>
+      </c>
+      <c r="C357">
+        <v>401</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46145.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>629.923</v>
+      </c>
+      <c r="C358">
+        <v>353</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46145.71875</v>
+      </c>
+      <c r="B359">
+        <v>596.835</v>
+      </c>
+      <c r="C359">
+        <v>279</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46145.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>562.845</v>
+      </c>
+      <c r="C360">
+        <v>273</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46145.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>530.29</v>
+      </c>
+      <c r="C361">
+        <v>267</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46145.75</v>
+      </c>
+      <c r="B362">
+        <v>488.936</v>
+      </c>
+      <c r="C362">
+        <v>214</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46145.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>466.712</v>
+      </c>
+      <c r="C363">
+        <v>176</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46145.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>445.789</v>
+      </c>
+      <c r="C364">
+        <v>121</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46145.78125</v>
+      </c>
+      <c r="B365">
+        <v>426.638</v>
+      </c>
+      <c r="C365">
+        <v>89</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46145.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>405.967</v>
+      </c>
+      <c r="C366">
+        <v>51</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46145.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>390.296</v>
+      </c>
+      <c r="C367">
+        <v>30</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46145.8125</v>
+      </c>
+      <c r="B368">
+        <v>375.258</v>
+      </c>
+      <c r="C368">
+        <v>21</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46145.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>360.462</v>
+      </c>
+      <c r="C369">
+        <v>24</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46145.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>329.989</v>
+      </c>
+      <c r="C370">
+        <v>30</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46145.84375</v>
+      </c>
+      <c r="B371">
+        <v>307.857</v>
+      </c>
+      <c r="C371">
+        <v>26</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46145.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>288.637</v>
+      </c>
+      <c r="C372">
+        <v>13</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46145.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>269.785</v>
+      </c>
+      <c r="C373">
+        <v>9</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46145.875</v>
+      </c>
+      <c r="B374">
+        <v>245.785</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46145.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>235.922</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46145.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>227.971</v>
+      </c>
+      <c r="C376">
+        <v>9</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46145.90625</v>
+      </c>
+      <c r="B377">
+        <v>219.642</v>
+      </c>
+      <c r="C377">
+        <v>15</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46145.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>218.919</v>
+      </c>
+      <c r="C378">
+        <v>12</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46145.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>228.507</v>
+      </c>
+      <c r="C379">
+        <v>13</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46145.9375</v>
+      </c>
+      <c r="B380">
+        <v>238.834</v>
+      </c>
+      <c r="C380">
+        <v>17</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46145.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>248.452</v>
+      </c>
+      <c r="C381">
+        <v>30</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46145.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>228.525</v>
+      </c>
+      <c r="C382">
+        <v>61</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46145.96875</v>
+      </c>
+      <c r="B383">
+        <v>257.063</v>
+      </c>
+      <c r="C383">
+        <v>119</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46145.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>283.817</v>
+      </c>
+      <c r="C384">
+        <v>156</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46145.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>303.87</v>
+      </c>
+      <c r="C385">
+        <v>180</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B386">
+        <v>321.179</v>
+      </c>
+      <c r="C386">
+        <v>226</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46146.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>358.975</v>
+      </c>
+      <c r="C387">
+        <v>302</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46146.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>400.4</v>
+      </c>
+      <c r="C388">
+        <v>380</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46146.03125</v>
+      </c>
+      <c r="B389">
+        <v>435.715</v>
+      </c>
+      <c r="C389">
+        <v>421</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2">
+        <v>46146.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>523.473</v>
+      </c>
+      <c r="C390">
+        <v>473</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2">
+        <v>46146.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>576.629</v>
+      </c>
+      <c r="C391">
+        <v>560</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2">
+        <v>46146.0625</v>
+      </c>
+      <c r="B392">
+        <v>633.7809999999999</v>
+      </c>
+      <c r="C392">
+        <v>646</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2">
+        <v>46146.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>686.773</v>
+      </c>
+      <c r="C393">
+        <v>692</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2">
+        <v>46146.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>765.367</v>
+      </c>
+      <c r="C394">
+        <v>741</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2">
+        <v>46146.09375</v>
+      </c>
+      <c r="B395">
+        <v>809.1420000000001</v>
+      </c>
+      <c r="C395">
+        <v>761</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2">
+        <v>46146.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>854.982</v>
+      </c>
+      <c r="C396">
+        <v>782</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2">
+        <v>46146.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>901.0700000000001</v>
+      </c>
+      <c r="C397">
+        <v>769</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2">
+        <v>46146.125</v>
+      </c>
+      <c r="B398">
+        <v>933.098</v>
+      </c>
+      <c r="C398">
+        <v>790</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2">
+        <v>46146.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>940.434</v>
+      </c>
+      <c r="C399">
+        <v>818</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2">
+        <v>46146.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>950.9829999999999</v>
+      </c>
+      <c r="C400">
+        <v>871</v>
+      </c>
+      <c r="D400">
+        <v>15</v>
+      </c>
+      <c r="E400" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2">
+        <v>46146.15625</v>
+      </c>
+      <c r="B401">
+        <v>960.503</v>
+      </c>
+      <c r="C401">
+        <v>947</v>
+      </c>
+      <c r="D401">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2">
+        <v>46146.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>987.227</v>
+      </c>
+      <c r="C402">
+        <v>1011</v>
+      </c>
+      <c r="D402">
+        <v>17</v>
+      </c>
+      <c r="E402" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2">
+        <v>46146.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>975.657</v>
+      </c>
+      <c r="C403">
+        <v>1043</v>
+      </c>
+      <c r="D403">
+        <v>18</v>
+      </c>
+      <c r="E403" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2">
+        <v>46146.1875</v>
+      </c>
+      <c r="B404">
+        <v>973.208</v>
+      </c>
+      <c r="C404">
+        <v>1052</v>
+      </c>
+      <c r="D404">
+        <v>19</v>
+      </c>
+      <c r="E404" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2">
+        <v>46146.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>970.766</v>
+      </c>
+      <c r="C405">
+        <v>1066</v>
+      </c>
+      <c r="D405">
+        <v>20</v>
+      </c>
+      <c r="E405" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2">
+        <v>46146.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>983.554</v>
+      </c>
+      <c r="C406">
+        <v>1080</v>
+      </c>
+      <c r="D406">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2">
+        <v>46146.21875</v>
+      </c>
+      <c r="B407">
+        <v>966.086</v>
+      </c>
+      <c r="C407">
+        <v>1104</v>
+      </c>
+      <c r="D407">
+        <v>22</v>
+      </c>
+      <c r="E407" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2">
+        <v>46146.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>949.351</v>
+      </c>
+      <c r="C408">
+        <v>1120</v>
+      </c>
+      <c r="D408">
+        <v>23</v>
+      </c>
+      <c r="E408" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2">
+        <v>46146.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>936.811</v>
+      </c>
+      <c r="C409">
+        <v>1125</v>
+      </c>
+      <c r="D409">
+        <v>24</v>
+      </c>
+      <c r="E409" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2">
+        <v>46146.25</v>
+      </c>
+      <c r="B410">
+        <v>874.3579999999999</v>
+      </c>
+      <c r="C410">
+        <v>1060</v>
+      </c>
+      <c r="D410">
+        <v>25</v>
+      </c>
+      <c r="E410" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2">
+        <v>46146.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>829.378</v>
+      </c>
+      <c r="C411">
+        <v>970</v>
+      </c>
+      <c r="D411">
+        <v>26</v>
+      </c>
+      <c r="E411" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2">
+        <v>46146.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>790.652</v>
+      </c>
+      <c r="C412">
+        <v>909</v>
+      </c>
+      <c r="D412">
+        <v>27</v>
+      </c>
+      <c r="E412" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2">
+        <v>46146.28125</v>
+      </c>
+      <c r="B413">
+        <v>761.8579999999999</v>
+      </c>
+      <c r="C413">
+        <v>838</v>
+      </c>
+      <c r="D413">
+        <v>28</v>
+      </c>
+      <c r="E413" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2">
+        <v>46146.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>710.475</v>
+      </c>
+      <c r="C414">
+        <v>739</v>
+      </c>
+      <c r="D414">
+        <v>29</v>
+      </c>
+      <c r="E414" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2">
+        <v>46146.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>648.1319999999999</v>
+      </c>
+      <c r="C415">
+        <v>624</v>
+      </c>
+      <c r="D415">
+        <v>30</v>
+      </c>
+      <c r="E415" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2">
+        <v>46146.3125</v>
+      </c>
+      <c r="B416">
+        <v>594.109</v>
+      </c>
+      <c r="C416">
+        <v>495</v>
+      </c>
+      <c r="D416">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2">
+        <v>46146.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>538.867</v>
+      </c>
+      <c r="C417">
+        <v>370</v>
+      </c>
+      <c r="D417">
+        <v>32</v>
+      </c>
+      <c r="E417" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2">
+        <v>46146.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>526.653</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
+      </c>
+      <c r="D418">
+        <v>33</v>
+      </c>
+      <c r="E418" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2">
+        <v>46146.34375</v>
+      </c>
+      <c r="B419">
+        <v>511.289</v>
+      </c>
+      <c r="C419">
+        <v>0</v>
+      </c>
+      <c r="D419">
+        <v>34</v>
+      </c>
+      <c r="E419" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2">
+        <v>46146.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>492.434</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+      <c r="D420">
+        <v>35</v>
+      </c>
+      <c r="E420" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2">
+        <v>46146.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>484.004</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+      <c r="D421">
+        <v>36</v>
+      </c>
+      <c r="E421" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2">
+        <v>46146.375</v>
+      </c>
+      <c r="B422">
+        <v>581.164</v>
+      </c>
+      <c r="C422">
+        <v>0</v>
+      </c>
+      <c r="D422">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2">
+        <v>46146.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>624.288</v>
+      </c>
+      <c r="C423">
+        <v>0</v>
+      </c>
+      <c r="D423">
+        <v>38</v>
+      </c>
+      <c r="E423" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2">
+        <v>46146.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>668.321</v>
+      </c>
+      <c r="C424">
+        <v>0</v>
+      </c>
+      <c r="D424">
+        <v>39</v>
+      </c>
+      <c r="E424" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2">
+        <v>46146.40625</v>
+      </c>
+      <c r="B425">
+        <v>711.7430000000001</v>
+      </c>
+      <c r="C425">
+        <v>0</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2">
+        <v>46146.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>741.652</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
+      </c>
+      <c r="D426">
+        <v>41</v>
+      </c>
+      <c r="E426" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="2">
+        <v>46146.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>766.6849999999999</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
+      </c>
+      <c r="D427">
+        <v>42</v>
+      </c>
+      <c r="E427" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="2">
+        <v>46146.4375</v>
+      </c>
+      <c r="B428">
+        <v>790.359</v>
+      </c>
+      <c r="C428">
+        <v>0</v>
+      </c>
+      <c r="D428">
+        <v>43</v>
+      </c>
+      <c r="E428" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="2">
+        <v>46146.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>813.653</v>
+      </c>
+      <c r="C429">
+        <v>0</v>
+      </c>
+      <c r="D429">
+        <v>44</v>
+      </c>
+      <c r="E429" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="2">
+        <v>46146.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>833.396</v>
+      </c>
+      <c r="C430">
+        <v>0</v>
+      </c>
+      <c r="D430">
+        <v>45</v>
+      </c>
+      <c r="E430" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="2">
+        <v>46146.46875</v>
+      </c>
+      <c r="B431">
+        <v>852.876</v>
+      </c>
+      <c r="C431">
+        <v>0</v>
+      </c>
+      <c r="D431">
+        <v>46</v>
+      </c>
+      <c r="E431" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="2">
+        <v>46146.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>870.932</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+      <c r="D432">
+        <v>47</v>
+      </c>
+      <c r="E432" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="2">
+        <v>46146.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>889.84</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
+      </c>
+      <c r="D433">
+        <v>48</v>
+      </c>
+      <c r="E433" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="2">
+        <v>46146.5</v>
+      </c>
+      <c r="B434">
+        <v>888.986</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
+      </c>
+      <c r="D434">
+        <v>49</v>
+      </c>
+      <c r="E434" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="2">
+        <v>46146.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>897.708</v>
+      </c>
+      <c r="C435">
+        <v>0</v>
+      </c>
+      <c r="D435">
+        <v>50</v>
+      </c>
+      <c r="E435" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="2">
+        <v>46146.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>906.01</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+      <c r="D436">
+        <v>51</v>
+      </c>
+      <c r="E436" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="2">
+        <v>46146.53125</v>
+      </c>
+      <c r="B437">
+        <v>914.174</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+      <c r="D437">
+        <v>52</v>
+      </c>
+      <c r="E437" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="2">
+        <v>46146.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>933.086</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438">
+        <v>53</v>
+      </c>
+      <c r="E438" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="2">
+        <v>46146.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>932.346</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+      <c r="D439">
+        <v>54</v>
+      </c>
+      <c r="E439" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="2">
+        <v>46146.5625</v>
+      </c>
+      <c r="B440">
+        <v>930.4109999999999</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440">
+        <v>55</v>
+      </c>
+      <c r="E440" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="2">
+        <v>46146.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>928.7190000000001</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441">
+        <v>56</v>
+      </c>
+      <c r="E441" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="2">
+        <v>46146.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>935.6559999999999</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442">
+        <v>57</v>
+      </c>
+      <c r="E442" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="2">
+        <v>46146.59375</v>
+      </c>
+      <c r="B443">
+        <v>922.064</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+      <c r="D443">
+        <v>58</v>
+      </c>
+      <c r="E443" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="2">
+        <v>46146.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>909.5700000000001</v>
+      </c>
+      <c r="C444">
+        <v>0</v>
+      </c>
+      <c r="D444">
+        <v>59</v>
+      </c>
+      <c r="E444" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="2">
+        <v>46146.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>896.622</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445">
+        <v>60</v>
+      </c>
+      <c r="E445" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="2">
+        <v>46146.625</v>
+      </c>
+      <c r="B446">
+        <v>861.654</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446">
+        <v>61</v>
+      </c>
+      <c r="E446" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="2">
+        <v>46146.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>838.954</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+      <c r="D447">
+        <v>62</v>
+      </c>
+      <c r="E447" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="2">
+        <v>46146.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>816.558</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+      <c r="D448">
+        <v>63</v>
+      </c>
+      <c r="E448" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="2">
+        <v>46146.65625</v>
+      </c>
+      <c r="B449">
+        <v>793.851</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+      <c r="D449">
+        <v>64</v>
+      </c>
+      <c r="E449" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="2">
+        <v>46146.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>670.649</v>
+      </c>
+      <c r="C450">
+        <v>0</v>
+      </c>
+      <c r="D450">
+        <v>65</v>
+      </c>
+      <c r="E450" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="2">
+        <v>46146.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>637.075</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+      <c r="D451">
+        <v>66</v>
+      </c>
+      <c r="E451" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="2">
+        <v>46146.6875</v>
+      </c>
+      <c r="B452">
+        <v>602.746</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+      <c r="D452">
+        <v>67</v>
+      </c>
+      <c r="E452" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="2">
+        <v>46146.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>568.256</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+      <c r="D453">
+        <v>68</v>
+      </c>
+      <c r="E453" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="2">
+        <v>46146.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>521.7329999999999</v>
+      </c>
+      <c r="C454">
+        <v>0</v>
+      </c>
+      <c r="D454">
+        <v>69</v>
+      </c>
+      <c r="E454" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="2">
+        <v>46146.71875</v>
+      </c>
+      <c r="B455">
+        <v>486.272</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+      <c r="D455">
+        <v>70</v>
+      </c>
+      <c r="E455" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="2">
+        <v>46146.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>452.48</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456">
+        <v>71</v>
+      </c>
+      <c r="E456" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="2">
+        <v>46146.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>419.509</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+      <c r="D457">
+        <v>72</v>
+      </c>
+      <c r="E457" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="2">
+        <v>46146.75</v>
+      </c>
+      <c r="B458">
+        <v>384.43</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458">
+        <v>73</v>
+      </c>
+      <c r="E458" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="2">
+        <v>46146.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>367.768</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459">
+        <v>74</v>
+      </c>
+      <c r="E459" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="2">
+        <v>46146.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>352.286</v>
+      </c>
+      <c r="C460">
+        <v>0</v>
+      </c>
+      <c r="D460">
+        <v>75</v>
+      </c>
+      <c r="E460" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="2">
+        <v>46146.78125</v>
+      </c>
+      <c r="B461">
+        <v>336.974</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461">
+        <v>76</v>
+      </c>
+      <c r="E461" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="2">
+        <v>46146.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>288.111</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462">
+        <v>77</v>
+      </c>
+      <c r="E462" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="2">
+        <v>46146.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>283.442</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463">
+        <v>78</v>
+      </c>
+      <c r="E463" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="2">
+        <v>46146.8125</v>
+      </c>
+      <c r="B464">
+        <v>279.81</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464">
+        <v>79</v>
+      </c>
+      <c r="E464" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="2">
+        <v>46146.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>297.538</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465">
+        <v>80</v>
+      </c>
+      <c r="E465" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="2">
+        <v>46146.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>278.591</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466">
+        <v>81</v>
+      </c>
+      <c r="E466" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="2">
+        <v>46146.84375</v>
+      </c>
+      <c r="B467">
+        <v>268.529</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467">
+        <v>82</v>
+      </c>
+      <c r="E467" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="2">
+        <v>46146.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>258.671</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468">
+        <v>83</v>
+      </c>
+      <c r="E468" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="2">
+        <v>46146.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>227.964</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469">
+        <v>84</v>
+      </c>
+      <c r="E469" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="2">
+        <v>46146.875</v>
+      </c>
+      <c r="B470">
+        <v>236.234</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+      <c r="D470">
+        <v>85</v>
+      </c>
+      <c r="E470" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="2">
+        <v>46146.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>230.014</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>86</v>
+      </c>
+      <c r="E471" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="2">
+        <v>46146.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>222.607</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>87</v>
+      </c>
+      <c r="E472" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="2">
+        <v>46146.90625</v>
+      </c>
+      <c r="B473">
+        <v>194.154</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473">
+        <v>88</v>
+      </c>
+      <c r="E473" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="2">
+        <v>46146.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>200.394</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>89</v>
+      </c>
+      <c r="E474" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="2">
+        <v>46146.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>196.854</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475">
+        <v>90</v>
+      </c>
+      <c r="E475" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="2">
+        <v>46146.9375</v>
+      </c>
+      <c r="B476">
+        <v>193.225</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476">
+        <v>91</v>
+      </c>
+      <c r="E476" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="2">
+        <v>46146.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>190.135</v>
+      </c>
+      <c r="C477">
+        <v>0</v>
+      </c>
+      <c r="D477">
+        <v>92</v>
+      </c>
+      <c r="E477" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" s="2">
+        <v>46146.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478">
+        <v>93</v>
+      </c>
+      <c r="E478" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" s="2">
+        <v>46146.96875</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479">
+        <v>94</v>
+      </c>
+      <c r="E479" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" s="2">
+        <v>46146.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480">
+        <v>95</v>
+      </c>
+      <c r="E480" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" s="2">
+        <v>46146.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481">
+        <v>96</v>
+      </c>
+      <c r="E481" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>05.05.20261</t>
-  </si>
-  <si>
-    <t>05.05.20262</t>
-  </si>
-  <si>
-    <t>05.05.20263</t>
-  </si>
-  <si>
-    <t>05.05.20264</t>
-  </si>
-  <si>
-    <t>05.05.20265</t>
-  </si>
-  <si>
-    <t>05.05.20266</t>
-  </si>
-  <si>
-    <t>05.05.20267</t>
-  </si>
-  <si>
-    <t>05.05.20268</t>
-  </si>
-  <si>
-    <t>05.05.20269</t>
-  </si>
-  <si>
-    <t>05.05.202610</t>
-  </si>
-  <si>
-    <t>05.05.202611</t>
-  </si>
-  <si>
-    <t>05.05.202612</t>
-  </si>
-  <si>
-    <t>05.05.202613</t>
-  </si>
-  <si>
-    <t>05.05.202614</t>
-  </si>
-  <si>
-    <t>05.05.202615</t>
-  </si>
-  <si>
-    <t>05.05.202616</t>
-  </si>
-  <si>
-    <t>05.05.202617</t>
-  </si>
-  <si>
-    <t>05.05.202618</t>
-  </si>
-  <si>
-    <t>05.05.202619</t>
-  </si>
-  <si>
-    <t>05.05.202620</t>
-  </si>
-  <si>
-    <t>05.05.202621</t>
-  </si>
-  <si>
-    <t>05.05.202622</t>
-  </si>
-  <si>
-    <t>05.05.202623</t>
-  </si>
-  <si>
-    <t>05.05.202624</t>
-  </si>
-  <si>
-    <t>05.05.202625</t>
-  </si>
-  <si>
-    <t>05.05.202626</t>
-  </si>
-  <si>
-    <t>05.05.202627</t>
-  </si>
-  <si>
-    <t>05.05.202628</t>
-  </si>
-  <si>
-    <t>05.05.202629</t>
-  </si>
-  <si>
-    <t>05.05.202630</t>
-  </si>
-  <si>
-    <t>05.05.202631</t>
-  </si>
-  <si>
-    <t>05.05.202632</t>
-  </si>
-  <si>
-    <t>05.05.202633</t>
-  </si>
-  <si>
-    <t>05.05.202634</t>
-  </si>
-  <si>
-    <t>05.05.202635</t>
-  </si>
-  <si>
-    <t>05.05.202636</t>
-  </si>
-  <si>
-    <t>05.05.202637</t>
-  </si>
-  <si>
-    <t>05.05.202638</t>
-  </si>
-  <si>
-    <t>05.05.202639</t>
-  </si>
-  <si>
-    <t>05.05.202640</t>
-  </si>
-  <si>
-    <t>05.05.202641</t>
-  </si>
-  <si>
-    <t>05.05.202642</t>
-  </si>
-  <si>
-    <t>05.05.202643</t>
-  </si>
-  <si>
-    <t>05.05.202644</t>
-  </si>
-  <si>
-    <t>05.05.202645</t>
-  </si>
-  <si>
-    <t>05.05.202646</t>
-  </si>
-  <si>
-    <t>05.05.202647</t>
-  </si>
-  <si>
-    <t>05.05.202648</t>
-  </si>
-  <si>
-    <t>05.05.202649</t>
-  </si>
-  <si>
-    <t>05.05.202650</t>
-  </si>
-  <si>
-    <t>05.05.202651</t>
-  </si>
-  <si>
-    <t>05.05.202652</t>
-  </si>
-  <si>
-    <t>05.05.202653</t>
-  </si>
-  <si>
-    <t>05.05.202654</t>
-  </si>
-  <si>
-    <t>05.05.202655</t>
-  </si>
-  <si>
-    <t>05.05.202656</t>
-  </si>
-  <si>
-    <t>05.05.202657</t>
-  </si>
-  <si>
-    <t>05.05.202658</t>
-  </si>
-  <si>
-    <t>05.05.202659</t>
-  </si>
-  <si>
-    <t>05.05.202660</t>
-  </si>
-  <si>
-    <t>05.05.202661</t>
-  </si>
-  <si>
-    <t>05.05.202662</t>
-  </si>
-  <si>
-    <t>05.05.202663</t>
-  </si>
-  <si>
-    <t>05.05.202664</t>
-  </si>
-  <si>
-    <t>05.05.202665</t>
-  </si>
-  <si>
-    <t>05.05.202666</t>
-  </si>
-  <si>
-    <t>05.05.202667</t>
-  </si>
-  <si>
-    <t>05.05.202668</t>
-  </si>
-  <si>
-    <t>05.05.202669</t>
-  </si>
-  <si>
-    <t>05.05.202670</t>
-  </si>
-  <si>
-    <t>05.05.202671</t>
-  </si>
-  <si>
-    <t>05.05.202672</t>
-  </si>
-  <si>
-    <t>05.05.202673</t>
-  </si>
-  <si>
-    <t>05.05.202674</t>
-  </si>
-  <si>
-    <t>05.05.202675</t>
-  </si>
-  <si>
-    <t>05.05.202676</t>
-  </si>
-  <si>
-    <t>05.05.202677</t>
-  </si>
-  <si>
-    <t>05.05.202678</t>
-  </si>
-  <si>
-    <t>05.05.202679</t>
-  </si>
-  <si>
-    <t>05.05.202680</t>
-  </si>
-  <si>
-    <t>05.05.202681</t>
-  </si>
-  <si>
-    <t>05.05.202682</t>
-  </si>
-  <si>
-    <t>05.05.202683</t>
-  </si>
-  <si>
-    <t>05.05.202684</t>
-  </si>
-  <si>
-    <t>05.05.202685</t>
-  </si>
-  <si>
-    <t>05.05.202686</t>
-  </si>
-  <si>
-    <t>05.05.202687</t>
-  </si>
-  <si>
-    <t>05.05.202688</t>
-  </si>
-  <si>
-    <t>05.05.202689</t>
-  </si>
-  <si>
-    <t>05.05.202690</t>
-  </si>
-  <si>
-    <t>05.05.202691</t>
-  </si>
-  <si>
-    <t>05.05.202692</t>
-  </si>
-  <si>
-    <t>05.05.202693</t>
-  </si>
-  <si>
-    <t>05.05.202694</t>
-  </si>
-  <si>
-    <t>05.05.202695</t>
-  </si>
-  <si>
-    <t>05.05.202696</t>
-  </si>
-  <si>
-    <t>06.05.20261</t>
-  </si>
-  <si>
-    <t>06.05.20262</t>
-  </si>
-  <si>
-    <t>06.05.20263</t>
-  </si>
-  <si>
-    <t>06.05.20264</t>
-  </si>
-  <si>
-    <t>06.05.20265</t>
-  </si>
-  <si>
-    <t>06.05.20266</t>
-  </si>
-  <si>
-    <t>06.05.20267</t>
-  </si>
-  <si>
-    <t>06.05.20268</t>
-  </si>
-  <si>
-    <t>06.05.20269</t>
-  </si>
-  <si>
-    <t>06.05.202610</t>
-  </si>
-  <si>
-    <t>06.05.202611</t>
-  </si>
-  <si>
-    <t>06.05.202612</t>
-  </si>
-  <si>
-    <t>06.05.202613</t>
-  </si>
-  <si>
-    <t>06.05.202614</t>
-  </si>
-  <si>
-    <t>06.05.202615</t>
-  </si>
-  <si>
-    <t>06.05.202616</t>
-  </si>
-  <si>
-    <t>06.05.202617</t>
-  </si>
-  <si>
-    <t>06.05.202618</t>
-  </si>
-  <si>
-    <t>06.05.202619</t>
-  </si>
-  <si>
-    <t>06.05.202620</t>
-  </si>
-  <si>
-    <t>06.05.202621</t>
-  </si>
-  <si>
-    <t>06.05.202622</t>
-  </si>
-  <si>
-    <t>06.05.202623</t>
-  </si>
-  <si>
-    <t>06.05.202624</t>
-  </si>
-  <si>
-    <t>06.05.202625</t>
-  </si>
-  <si>
-    <t>06.05.202626</t>
-  </si>
-  <si>
-    <t>06.05.202627</t>
-  </si>
-  <si>
-    <t>06.05.202628</t>
-  </si>
-  <si>
-    <t>06.05.202629</t>
-  </si>
-  <si>
-    <t>06.05.202630</t>
-  </si>
-  <si>
-    <t>06.05.202631</t>
-  </si>
-  <si>
-    <t>06.05.202632</t>
-  </si>
-  <si>
-    <t>06.05.202633</t>
-  </si>
-  <si>
-    <t>06.05.202634</t>
-  </si>
-  <si>
-    <t>06.05.202635</t>
-  </si>
-  <si>
-    <t>06.05.202636</t>
-  </si>
-  <si>
-    <t>06.05.202637</t>
-  </si>
-  <si>
-    <t>06.05.202638</t>
-  </si>
-  <si>
-    <t>06.05.202639</t>
-  </si>
-  <si>
-    <t>06.05.202640</t>
-  </si>
-  <si>
-    <t>06.05.202641</t>
-  </si>
-  <si>
-    <t>06.05.202642</t>
-  </si>
-  <si>
-    <t>06.05.202643</t>
-  </si>
-  <si>
-    <t>06.05.202644</t>
-  </si>
-  <si>
-    <t>06.05.202645</t>
-  </si>
-  <si>
-    <t>06.05.202646</t>
-  </si>
-  <si>
-    <t>06.05.202647</t>
-  </si>
-  <si>
-    <t>06.05.202648</t>
-  </si>
-  <si>
-    <t>06.05.202649</t>
-  </si>
-  <si>
-    <t>06.05.202650</t>
-  </si>
-  <si>
-    <t>06.05.202651</t>
-  </si>
-  <si>
-    <t>06.05.202652</t>
-  </si>
-  <si>
-    <t>06.05.202653</t>
-  </si>
-  <si>
-    <t>06.05.202654</t>
-  </si>
-  <si>
-    <t>06.05.202655</t>
-  </si>
-  <si>
-    <t>06.05.202656</t>
-  </si>
-  <si>
-    <t>06.05.202657</t>
-  </si>
-  <si>
-    <t>06.05.202658</t>
-  </si>
-  <si>
-    <t>06.05.202659</t>
-  </si>
-  <si>
-    <t>06.05.202660</t>
-  </si>
-  <si>
-    <t>06.05.202661</t>
-  </si>
-  <si>
-    <t>06.05.202662</t>
-  </si>
-  <si>
-    <t>06.05.202663</t>
-  </si>
-  <si>
-    <t>06.05.202664</t>
-  </si>
-  <si>
-    <t>06.05.202665</t>
-  </si>
-  <si>
-    <t>06.05.202666</t>
-  </si>
-  <si>
-    <t>06.05.202667</t>
-  </si>
-  <si>
-    <t>06.05.202668</t>
-  </si>
-  <si>
-    <t>06.05.202669</t>
-  </si>
-  <si>
-    <t>06.05.202670</t>
-  </si>
-  <si>
-    <t>06.05.202671</t>
-  </si>
-  <si>
-    <t>06.05.202672</t>
-  </si>
-  <si>
-    <t>06.05.202673</t>
-  </si>
-  <si>
-    <t>06.05.202674</t>
-  </si>
-  <si>
-    <t>06.05.202675</t>
-  </si>
-  <si>
-    <t>06.05.202676</t>
-  </si>
-  <si>
-    <t>06.05.202677</t>
-  </si>
-  <si>
-    <t>06.05.202678</t>
-  </si>
-  <si>
-    <t>06.05.202679</t>
-  </si>
-  <si>
-    <t>06.05.202680</t>
-  </si>
-  <si>
-    <t>06.05.202681</t>
-  </si>
-  <si>
-    <t>06.05.202682</t>
-  </si>
-  <si>
-    <t>06.05.202683</t>
-  </si>
-  <si>
-    <t>06.05.202684</t>
-  </si>
-  <si>
-    <t>06.05.202685</t>
-  </si>
-  <si>
-    <t>06.05.202686</t>
-  </si>
-  <si>
-    <t>06.05.202687</t>
-  </si>
-  <si>
-    <t>06.05.202688</t>
-  </si>
-  <si>
-    <t>06.05.202689</t>
-  </si>
-  <si>
-    <t>06.05.202690</t>
-  </si>
-  <si>
-    <t>06.05.202691</t>
-  </si>
-  <si>
-    <t>06.05.202692</t>
-  </si>
-  <si>
-    <t>06.05.202693</t>
-  </si>
-  <si>
-    <t>06.05.202694</t>
-  </si>
-  <si>
-    <t>06.05.202695</t>
-  </si>
-  <si>
-    <t>06.05.202696</t>
+    <t>07.05.20261</t>
+  </si>
+  <si>
+    <t>07.05.20262</t>
+  </si>
+  <si>
+    <t>07.05.20263</t>
+  </si>
+  <si>
+    <t>07.05.20264</t>
+  </si>
+  <si>
+    <t>07.05.20265</t>
+  </si>
+  <si>
+    <t>07.05.20266</t>
+  </si>
+  <si>
+    <t>07.05.20267</t>
+  </si>
+  <si>
+    <t>07.05.20268</t>
+  </si>
+  <si>
+    <t>07.05.20269</t>
+  </si>
+  <si>
+    <t>07.05.202610</t>
+  </si>
+  <si>
+    <t>07.05.202611</t>
+  </si>
+  <si>
+    <t>07.05.202612</t>
+  </si>
+  <si>
+    <t>07.05.202613</t>
+  </si>
+  <si>
+    <t>07.05.202614</t>
+  </si>
+  <si>
+    <t>07.05.202615</t>
+  </si>
+  <si>
+    <t>07.05.202616</t>
+  </si>
+  <si>
+    <t>07.05.202617</t>
+  </si>
+  <si>
+    <t>07.05.202618</t>
+  </si>
+  <si>
+    <t>07.05.202619</t>
+  </si>
+  <si>
+    <t>07.05.202620</t>
+  </si>
+  <si>
+    <t>07.05.202621</t>
+  </si>
+  <si>
+    <t>07.05.202622</t>
+  </si>
+  <si>
+    <t>07.05.202623</t>
+  </si>
+  <si>
+    <t>07.05.202624</t>
+  </si>
+  <si>
+    <t>07.05.202625</t>
+  </si>
+  <si>
+    <t>07.05.202626</t>
+  </si>
+  <si>
+    <t>07.05.202627</t>
+  </si>
+  <si>
+    <t>07.05.202628</t>
+  </si>
+  <si>
+    <t>07.05.202629</t>
+  </si>
+  <si>
+    <t>07.05.202630</t>
+  </si>
+  <si>
+    <t>07.05.202631</t>
+  </si>
+  <si>
+    <t>07.05.202632</t>
+  </si>
+  <si>
+    <t>07.05.202633</t>
+  </si>
+  <si>
+    <t>07.05.202634</t>
+  </si>
+  <si>
+    <t>07.05.202635</t>
+  </si>
+  <si>
+    <t>07.05.202636</t>
+  </si>
+  <si>
+    <t>07.05.202637</t>
+  </si>
+  <si>
+    <t>07.05.202638</t>
+  </si>
+  <si>
+    <t>07.05.202639</t>
+  </si>
+  <si>
+    <t>07.05.202640</t>
+  </si>
+  <si>
+    <t>07.05.202641</t>
+  </si>
+  <si>
+    <t>07.05.202642</t>
+  </si>
+  <si>
+    <t>07.05.202643</t>
+  </si>
+  <si>
+    <t>07.05.202644</t>
+  </si>
+  <si>
+    <t>07.05.202645</t>
+  </si>
+  <si>
+    <t>07.05.202646</t>
+  </si>
+  <si>
+    <t>07.05.202647</t>
+  </si>
+  <si>
+    <t>07.05.202648</t>
+  </si>
+  <si>
+    <t>07.05.202649</t>
+  </si>
+  <si>
+    <t>07.05.202650</t>
+  </si>
+  <si>
+    <t>07.05.202651</t>
+  </si>
+  <si>
+    <t>07.05.202652</t>
+  </si>
+  <si>
+    <t>07.05.202653</t>
+  </si>
+  <si>
+    <t>07.05.202654</t>
+  </si>
+  <si>
+    <t>07.05.202655</t>
+  </si>
+  <si>
+    <t>07.05.202656</t>
+  </si>
+  <si>
+    <t>07.05.202657</t>
+  </si>
+  <si>
+    <t>07.05.202658</t>
+  </si>
+  <si>
+    <t>07.05.202659</t>
+  </si>
+  <si>
+    <t>07.05.202660</t>
+  </si>
+  <si>
+    <t>07.05.202661</t>
+  </si>
+  <si>
+    <t>07.05.202662</t>
+  </si>
+  <si>
+    <t>07.05.202663</t>
+  </si>
+  <si>
+    <t>07.05.202664</t>
+  </si>
+  <si>
+    <t>07.05.202665</t>
+  </si>
+  <si>
+    <t>07.05.202666</t>
+  </si>
+  <si>
+    <t>07.05.202667</t>
+  </si>
+  <si>
+    <t>07.05.202668</t>
+  </si>
+  <si>
+    <t>07.05.202669</t>
+  </si>
+  <si>
+    <t>07.05.202670</t>
+  </si>
+  <si>
+    <t>07.05.202671</t>
+  </si>
+  <si>
+    <t>07.05.202672</t>
+  </si>
+  <si>
+    <t>07.05.202673</t>
+  </si>
+  <si>
+    <t>07.05.202674</t>
+  </si>
+  <si>
+    <t>07.05.202675</t>
+  </si>
+  <si>
+    <t>07.05.202676</t>
+  </si>
+  <si>
+    <t>07.05.202677</t>
+  </si>
+  <si>
+    <t>07.05.202678</t>
+  </si>
+  <si>
+    <t>07.05.202679</t>
+  </si>
+  <si>
+    <t>07.05.202680</t>
+  </si>
+  <si>
+    <t>07.05.202681</t>
+  </si>
+  <si>
+    <t>07.05.202682</t>
+  </si>
+  <si>
+    <t>07.05.202683</t>
+  </si>
+  <si>
+    <t>07.05.202684</t>
+  </si>
+  <si>
+    <t>07.05.202685</t>
+  </si>
+  <si>
+    <t>07.05.202686</t>
+  </si>
+  <si>
+    <t>07.05.202687</t>
+  </si>
+  <si>
+    <t>07.05.202688</t>
+  </si>
+  <si>
+    <t>07.05.202689</t>
+  </si>
+  <si>
+    <t>07.05.202690</t>
+  </si>
+  <si>
+    <t>07.05.202691</t>
+  </si>
+  <si>
+    <t>07.05.202692</t>
+  </si>
+  <si>
+    <t>07.05.202693</t>
+  </si>
+  <si>
+    <t>07.05.202694</t>
+  </si>
+  <si>
+    <t>07.05.202695</t>
+  </si>
+  <si>
+    <t>07.05.202696</t>
+  </si>
+  <si>
+    <t>08.05.20261</t>
+  </si>
+  <si>
+    <t>08.05.20262</t>
+  </si>
+  <si>
+    <t>08.05.20263</t>
+  </si>
+  <si>
+    <t>08.05.20264</t>
+  </si>
+  <si>
+    <t>08.05.20265</t>
+  </si>
+  <si>
+    <t>08.05.20266</t>
+  </si>
+  <si>
+    <t>08.05.20267</t>
+  </si>
+  <si>
+    <t>08.05.20268</t>
+  </si>
+  <si>
+    <t>08.05.20269</t>
+  </si>
+  <si>
+    <t>08.05.202610</t>
+  </si>
+  <si>
+    <t>08.05.202611</t>
+  </si>
+  <si>
+    <t>08.05.202612</t>
+  </si>
+  <si>
+    <t>08.05.202613</t>
+  </si>
+  <si>
+    <t>08.05.202614</t>
+  </si>
+  <si>
+    <t>08.05.202615</t>
+  </si>
+  <si>
+    <t>08.05.202616</t>
+  </si>
+  <si>
+    <t>08.05.202617</t>
+  </si>
+  <si>
+    <t>08.05.202618</t>
+  </si>
+  <si>
+    <t>08.05.202619</t>
+  </si>
+  <si>
+    <t>08.05.202620</t>
+  </si>
+  <si>
+    <t>08.05.202621</t>
+  </si>
+  <si>
+    <t>08.05.202622</t>
+  </si>
+  <si>
+    <t>08.05.202623</t>
+  </si>
+  <si>
+    <t>08.05.202624</t>
+  </si>
+  <si>
+    <t>08.05.202625</t>
+  </si>
+  <si>
+    <t>08.05.202626</t>
+  </si>
+  <si>
+    <t>08.05.202627</t>
+  </si>
+  <si>
+    <t>08.05.202628</t>
+  </si>
+  <si>
+    <t>08.05.202629</t>
+  </si>
+  <si>
+    <t>08.05.202630</t>
+  </si>
+  <si>
+    <t>08.05.202631</t>
+  </si>
+  <si>
+    <t>08.05.202632</t>
+  </si>
+  <si>
+    <t>08.05.202633</t>
+  </si>
+  <si>
+    <t>08.05.202634</t>
+  </si>
+  <si>
+    <t>08.05.202635</t>
+  </si>
+  <si>
+    <t>08.05.202636</t>
+  </si>
+  <si>
+    <t>08.05.202637</t>
+  </si>
+  <si>
+    <t>08.05.202638</t>
+  </si>
+  <si>
+    <t>08.05.202639</t>
+  </si>
+  <si>
+    <t>08.05.202640</t>
+  </si>
+  <si>
+    <t>08.05.202641</t>
+  </si>
+  <si>
+    <t>08.05.202642</t>
+  </si>
+  <si>
+    <t>08.05.202643</t>
+  </si>
+  <si>
+    <t>08.05.202644</t>
+  </si>
+  <si>
+    <t>08.05.202645</t>
+  </si>
+  <si>
+    <t>08.05.202646</t>
+  </si>
+  <si>
+    <t>08.05.202647</t>
+  </si>
+  <si>
+    <t>08.05.202648</t>
+  </si>
+  <si>
+    <t>08.05.202649</t>
+  </si>
+  <si>
+    <t>08.05.202650</t>
+  </si>
+  <si>
+    <t>08.05.202651</t>
+  </si>
+  <si>
+    <t>08.05.202652</t>
+  </si>
+  <si>
+    <t>08.05.202653</t>
+  </si>
+  <si>
+    <t>08.05.202654</t>
+  </si>
+  <si>
+    <t>08.05.202655</t>
+  </si>
+  <si>
+    <t>08.05.202656</t>
+  </si>
+  <si>
+    <t>08.05.202657</t>
+  </si>
+  <si>
+    <t>08.05.202658</t>
+  </si>
+  <si>
+    <t>08.05.202659</t>
+  </si>
+  <si>
+    <t>08.05.202660</t>
+  </si>
+  <si>
+    <t>08.05.202661</t>
+  </si>
+  <si>
+    <t>08.05.202662</t>
+  </si>
+  <si>
+    <t>08.05.202663</t>
+  </si>
+  <si>
+    <t>08.05.202664</t>
+  </si>
+  <si>
+    <t>08.05.202665</t>
+  </si>
+  <si>
+    <t>08.05.202666</t>
+  </si>
+  <si>
+    <t>08.05.202667</t>
+  </si>
+  <si>
+    <t>08.05.202668</t>
+  </si>
+  <si>
+    <t>08.05.202669</t>
+  </si>
+  <si>
+    <t>08.05.202670</t>
+  </si>
+  <si>
+    <t>08.05.202671</t>
+  </si>
+  <si>
+    <t>08.05.202672</t>
+  </si>
+  <si>
+    <t>08.05.202673</t>
+  </si>
+  <si>
+    <t>08.05.202674</t>
+  </si>
+  <si>
+    <t>08.05.202675</t>
+  </si>
+  <si>
+    <t>08.05.202676</t>
+  </si>
+  <si>
+    <t>08.05.202677</t>
+  </si>
+  <si>
+    <t>08.05.202678</t>
+  </si>
+  <si>
+    <t>08.05.202679</t>
+  </si>
+  <si>
+    <t>08.05.202680</t>
+  </si>
+  <si>
+    <t>08.05.202681</t>
+  </si>
+  <si>
+    <t>08.05.202682</t>
+  </si>
+  <si>
+    <t>08.05.202683</t>
+  </si>
+  <si>
+    <t>08.05.202684</t>
+  </si>
+  <si>
+    <t>08.05.202685</t>
+  </si>
+  <si>
+    <t>08.05.202686</t>
+  </si>
+  <si>
+    <t>08.05.202687</t>
+  </si>
+  <si>
+    <t>08.05.202688</t>
+  </si>
+  <si>
+    <t>08.05.202689</t>
+  </si>
+  <si>
+    <t>08.05.202690</t>
+  </si>
+  <si>
+    <t>08.05.202691</t>
+  </si>
+  <si>
+    <t>08.05.202692</t>
+  </si>
+  <si>
+    <t>08.05.202693</t>
+  </si>
+  <si>
+    <t>08.05.202694</t>
+  </si>
+  <si>
+    <t>08.05.202695</t>
+  </si>
+  <si>
+    <t>08.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B2">
-        <v>127.794</v>
+        <v>762.05</v>
       </c>
       <c r="C2">
-        <v>106</v>
+        <v>840</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46147.01041666666</v>
+        <v>46149.01041666666</v>
       </c>
       <c r="B3">
-        <v>124.51</v>
+        <v>747.8579999999999</v>
       </c>
       <c r="C3">
-        <v>114</v>
+        <v>839</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46147.02083333334</v>
+        <v>46149.02083333334</v>
       </c>
       <c r="B4">
-        <v>121.084</v>
+        <v>739.557</v>
       </c>
       <c r="C4">
-        <v>118</v>
+        <v>838</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46147.03125</v>
+        <v>46149.03125</v>
       </c>
       <c r="B5">
-        <v>117.803</v>
+        <v>730.7190000000001</v>
       </c>
       <c r="C5">
-        <v>116</v>
+        <v>868</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46147.04166666666</v>
+        <v>46149.04166666666</v>
       </c>
       <c r="B6">
-        <v>114.065</v>
+        <v>733.5549999999999</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>876</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46147.05208333334</v>
+        <v>46149.05208333334</v>
       </c>
       <c r="B7">
-        <v>111.981</v>
+        <v>720.004</v>
       </c>
       <c r="C7">
-        <v>90</v>
+        <v>879</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46147.0625</v>
+        <v>46149.0625</v>
       </c>
       <c r="B8">
-        <v>110.078</v>
+        <v>713.748</v>
       </c>
       <c r="C8">
-        <v>78</v>
+        <v>869</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46147.07291666666</v>
+        <v>46149.07291666666</v>
       </c>
       <c r="B9">
-        <v>106.885</v>
+        <v>709.947</v>
       </c>
       <c r="C9">
-        <v>69</v>
+        <v>850</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46147.08333333334</v>
+        <v>46149.08333333334</v>
       </c>
       <c r="B10">
-        <v>104.71</v>
+        <v>703.2859999999999</v>
       </c>
       <c r="C10">
-        <v>64</v>
+        <v>833</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46147.09375</v>
+        <v>46149.09375</v>
       </c>
       <c r="B11">
-        <v>105.173</v>
+        <v>695.318</v>
       </c>
       <c r="C11">
-        <v>58</v>
+        <v>810</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46147.10416666666</v>
+        <v>46149.10416666666</v>
       </c>
       <c r="B12">
-        <v>105.727</v>
+        <v>695.545</v>
       </c>
       <c r="C12">
-        <v>52</v>
+        <v>809</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46147.11458333334</v>
+        <v>46149.11458333334</v>
       </c>
       <c r="B13">
-        <v>106.929</v>
+        <v>691.683</v>
       </c>
       <c r="C13">
-        <v>39</v>
+        <v>794</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46147.125</v>
+        <v>46149.125</v>
       </c>
       <c r="B14">
-        <v>107.953</v>
+        <v>650.5170000000001</v>
       </c>
       <c r="C14">
-        <v>33</v>
+        <v>790</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46147.13541666666</v>
+        <v>46149.13541666666</v>
       </c>
       <c r="B15">
-        <v>110.087</v>
+        <v>650.144</v>
       </c>
       <c r="C15">
-        <v>28</v>
+        <v>809</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46147.14583333334</v>
+        <v>46149.14583333334</v>
       </c>
       <c r="B16">
-        <v>112.812</v>
+        <v>645.091</v>
       </c>
       <c r="C16">
-        <v>26</v>
+        <v>832</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46147.15625</v>
+        <v>46149.15625</v>
       </c>
       <c r="B17">
-        <v>114.82</v>
+        <v>639.264</v>
       </c>
       <c r="C17">
-        <v>20</v>
+        <v>846</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46147.16666666666</v>
+        <v>46149.16666666666</v>
       </c>
       <c r="B18">
-        <v>121.934</v>
+        <v>638.8150000000001</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46147.17708333334</v>
+        <v>46149.17708333334</v>
       </c>
       <c r="B19">
-        <v>123.691</v>
+        <v>632.873</v>
       </c>
       <c r="C19">
-        <v>17</v>
+        <v>853</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46147.1875</v>
+        <v>46149.1875</v>
       </c>
       <c r="B20">
-        <v>125.039</v>
+        <v>634.465</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>840</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46147.19791666666</v>
+        <v>46149.19791666666</v>
       </c>
       <c r="B21">
-        <v>126.337</v>
+        <v>633.998</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>815</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46147.20833333334</v>
+        <v>46149.20833333334</v>
       </c>
       <c r="B22">
-        <v>123.044</v>
+        <v>631.864</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>800</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46147.21875</v>
+        <v>46149.21875</v>
       </c>
       <c r="B23">
-        <v>123.559</v>
+        <v>630.146</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>783</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46147.22916666666</v>
+        <v>46149.22916666666</v>
       </c>
       <c r="B24">
-        <v>119.486</v>
+        <v>632.739</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>786</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46147.23958333334</v>
+        <v>46149.23958333334</v>
       </c>
       <c r="B25">
-        <v>118.089</v>
+        <v>633.35</v>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>791</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46147.25</v>
+        <v>46149.25</v>
       </c>
       <c r="B26">
-        <v>122.942</v>
+        <v>618.395</v>
       </c>
       <c r="C26">
-        <v>19</v>
+        <v>788</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46147.26041666666</v>
+        <v>46149.26041666666</v>
       </c>
       <c r="B27">
-        <v>121.107</v>
+        <v>603.55</v>
       </c>
       <c r="C27">
-        <v>23</v>
+        <v>765</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46147.27083333334</v>
+        <v>46149.27083333334</v>
       </c>
       <c r="B28">
-        <v>116.135</v>
+        <v>590.179</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46147.28125</v>
+        <v>46149.28125</v>
       </c>
       <c r="B29">
-        <v>113.106</v>
+        <v>579.24</v>
       </c>
       <c r="C29">
-        <v>24</v>
+        <v>613</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46147.29166666666</v>
+        <v>46149.29166666666</v>
       </c>
       <c r="B30">
-        <v>116.921</v>
+        <v>590.823</v>
       </c>
       <c r="C30">
-        <v>21</v>
+        <v>544</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46147.30208333334</v>
+        <v>46149.30208333334</v>
       </c>
       <c r="B31">
-        <v>108.964</v>
+        <v>575.269</v>
       </c>
       <c r="C31">
-        <v>13</v>
+        <v>490</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46147.3125</v>
+        <v>46149.3125</v>
       </c>
       <c r="B32">
-        <v>106.559</v>
+        <v>561.073</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>449</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46147.32291666666</v>
+        <v>46149.32291666666</v>
       </c>
       <c r="B33">
-        <v>109.95</v>
+        <v>546.39</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46147.33333333334</v>
+        <v>46149.33333333334</v>
       </c>
       <c r="B34">
-        <v>106.867</v>
+        <v>639.1180000000001</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46147.34375</v>
+        <v>46149.34375</v>
       </c>
       <c r="B35">
-        <v>104.47</v>
+        <v>651.03</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46147.35416666666</v>
+        <v>46149.35416666666</v>
       </c>
       <c r="B36">
-        <v>113.855</v>
+        <v>664.809</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46147.36458333334</v>
+        <v>46149.36458333334</v>
       </c>
       <c r="B37">
-        <v>111.506</v>
+        <v>679.72</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46147.375</v>
+        <v>46149.375</v>
       </c>
       <c r="B38">
-        <v>112.342</v>
+        <v>636.4880000000001</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46147.38541666666</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="B39">
-        <v>113.781</v>
+        <v>668.408</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46147.39583333334</v>
+        <v>46149.39583333334</v>
       </c>
       <c r="B40">
-        <v>115.183</v>
+        <v>700.657</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46147.40625</v>
+        <v>46149.40625</v>
       </c>
       <c r="B41">
-        <v>117.22</v>
+        <v>733.45</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46147.41666666666</v>
+        <v>46149.41666666666</v>
       </c>
       <c r="B42">
-        <v>122.957</v>
+        <v>732.1130000000001</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>774</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46147.42708333334</v>
+        <v>46149.42708333334</v>
       </c>
       <c r="B43">
-        <v>126.069</v>
+        <v>768.008</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46147.4375</v>
+        <v>46149.4375</v>
       </c>
       <c r="B44">
-        <v>129.021</v>
+        <v>803.207</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46147.44791666666</v>
+        <v>46149.44791666666</v>
       </c>
       <c r="B45">
-        <v>132.034</v>
+        <v>839.126</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46147.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="B46">
-        <v>137.825</v>
+        <v>886.426</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>935</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46147.46875</v>
+        <v>46149.46875</v>
       </c>
       <c r="B47">
-        <v>141.585</v>
+        <v>915.842</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46147.47916666666</v>
+        <v>46149.47916666666</v>
       </c>
       <c r="B48">
-        <v>145.799</v>
+        <v>944.466</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1014</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46147.48958333334</v>
+        <v>46149.48958333334</v>
       </c>
       <c r="B49">
-        <v>149.82</v>
+        <v>973.4299999999999</v>
       </c>
       <c r="C49">
-        <v>8</v>
+        <v>1046</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46147.5</v>
+        <v>46149.5</v>
       </c>
       <c r="B50">
-        <v>152.765</v>
+        <v>998.478</v>
       </c>
       <c r="C50">
-        <v>20</v>
+        <v>1081</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46147.51041666666</v>
+        <v>46149.51041666666</v>
       </c>
       <c r="B51">
-        <v>157.993</v>
+        <v>1010.347</v>
       </c>
       <c r="C51">
-        <v>44</v>
+        <v>1089</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46147.52083333334</v>
+        <v>46149.52083333334</v>
       </c>
       <c r="B52">
-        <v>163.732</v>
+        <v>1020.493</v>
       </c>
       <c r="C52">
-        <v>60</v>
+        <v>1106</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46147.53125</v>
+        <v>46149.53125</v>
       </c>
       <c r="B53">
-        <v>168.753</v>
+        <v>1030.382</v>
       </c>
       <c r="C53">
-        <v>92</v>
+        <v>1123</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46147.54166666666</v>
+        <v>46149.54166666666</v>
       </c>
       <c r="B54">
-        <v>178.376</v>
+        <v>1073.36</v>
       </c>
       <c r="C54">
-        <v>118</v>
+        <v>1141</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46147.55208333334</v>
+        <v>46149.55208333334</v>
       </c>
       <c r="B55">
-        <v>185.801</v>
+        <v>1082.236</v>
       </c>
       <c r="C55">
-        <v>134</v>
+        <v>1152</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46147.5625</v>
+        <v>46149.5625</v>
       </c>
       <c r="B56">
-        <v>193.661</v>
+        <v>1090.039</v>
       </c>
       <c r="C56">
-        <v>153</v>
+        <v>1189</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46147.57291666666</v>
+        <v>46149.57291666666</v>
       </c>
       <c r="B57">
-        <v>201.156</v>
+        <v>1097.666</v>
       </c>
       <c r="C57">
-        <v>170</v>
+        <v>1245</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46147.58333333334</v>
+        <v>46149.58333333334</v>
       </c>
       <c r="B58">
-        <v>217.933</v>
+        <v>1120.911</v>
       </c>
       <c r="C58">
-        <v>201</v>
+        <v>1256</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46147.59375</v>
+        <v>46149.59375</v>
       </c>
       <c r="B59">
-        <v>225.846</v>
+        <v>1126.245</v>
       </c>
       <c r="C59">
-        <v>212</v>
+        <v>1303</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46147.60416666666</v>
+        <v>46149.60416666666</v>
       </c>
       <c r="B60">
-        <v>234.185</v>
+        <v>1131.495</v>
       </c>
       <c r="C60">
-        <v>225</v>
+        <v>1300</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46147.61458333334</v>
+        <v>46149.61458333334</v>
       </c>
       <c r="B61">
-        <v>242.177</v>
+        <v>1135.786</v>
       </c>
       <c r="C61">
-        <v>237</v>
+        <v>1302</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46147.625</v>
+        <v>46149.625</v>
       </c>
       <c r="B62">
-        <v>224.669</v>
+        <v>1102.027</v>
       </c>
       <c r="C62">
-        <v>243</v>
+        <v>1300</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46147.63541666666</v>
+        <v>46149.63541666666</v>
       </c>
       <c r="B63">
-        <v>232.404</v>
+        <v>1111.02</v>
       </c>
       <c r="C63">
-        <v>276</v>
+        <v>1312</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46147.64583333334</v>
+        <v>46149.64583333334</v>
       </c>
       <c r="B64">
-        <v>239.73</v>
+        <v>1118.524</v>
       </c>
       <c r="C64">
-        <v>296</v>
+        <v>1328</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46147.65625</v>
+        <v>46149.65625</v>
       </c>
       <c r="B65">
-        <v>246.878</v>
+        <v>1125.911</v>
       </c>
       <c r="C65">
-        <v>321</v>
+        <v>1340</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46147.66666666666</v>
+        <v>46149.66666666666</v>
       </c>
       <c r="B66">
-        <v>278.154</v>
+        <v>1130.993</v>
       </c>
       <c r="C66">
-        <v>358</v>
+        <v>1350</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46147.67708333334</v>
+        <v>46149.67708333334</v>
       </c>
       <c r="B67">
-        <v>294.036</v>
+        <v>1141.256</v>
       </c>
       <c r="C67">
-        <v>405</v>
+        <v>1356</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46147.6875</v>
+        <v>46149.6875</v>
       </c>
       <c r="B68">
-        <v>309.626</v>
+        <v>1151.208</v>
       </c>
       <c r="C68">
-        <v>417</v>
+        <v>1391</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46147.69791666666</v>
+        <v>46149.69791666666</v>
       </c>
       <c r="B69">
-        <v>326.54</v>
+        <v>1160.287</v>
       </c>
       <c r="C69">
-        <v>395</v>
+        <v>1444</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46147.70833333334</v>
+        <v>46149.70833333334</v>
       </c>
       <c r="B70">
-        <v>365.925</v>
+        <v>1156.753</v>
       </c>
       <c r="C70">
-        <v>435</v>
+        <v>1491</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46147.71875</v>
+        <v>46149.71875</v>
       </c>
       <c r="B71">
-        <v>398.561</v>
+        <v>1165.437</v>
       </c>
       <c r="C71">
-        <v>499</v>
+        <v>1495</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46147.72916666666</v>
+        <v>46149.72916666666</v>
       </c>
       <c r="B72">
-        <v>431.232</v>
+        <v>1175.581</v>
       </c>
       <c r="C72">
-        <v>498</v>
+        <v>1476</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46147.73958333334</v>
+        <v>46149.73958333334</v>
       </c>
       <c r="B73">
-        <v>464.94</v>
+        <v>1186.285</v>
       </c>
       <c r="C73">
-        <v>542</v>
+        <v>1468</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46147.75</v>
+        <v>46149.75</v>
       </c>
       <c r="B74">
-        <v>509.18</v>
+        <v>1205.854</v>
       </c>
       <c r="C74">
-        <v>597</v>
+        <v>1426</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46147.76041666666</v>
+        <v>46149.76041666666</v>
       </c>
       <c r="B75">
-        <v>557.495</v>
+        <v>1227.032</v>
       </c>
       <c r="C75">
-        <v>655</v>
+        <v>1445</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46147.77083333334</v>
+        <v>46149.77083333334</v>
       </c>
       <c r="B76">
-        <v>599.109</v>
+        <v>1250.289</v>
       </c>
       <c r="C76">
-        <v>688</v>
+        <v>1444</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46147.78125</v>
+        <v>46149.78125</v>
       </c>
       <c r="B77">
-        <v>641.176</v>
+        <v>1270.113</v>
       </c>
       <c r="C77">
-        <v>739</v>
+        <v>1470</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46147.79166666666</v>
+        <v>46149.79166666666</v>
       </c>
       <c r="B78">
-        <v>616.149</v>
+        <v>1245.008</v>
       </c>
       <c r="C78">
-        <v>814</v>
+        <v>1546</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46147.80208333334</v>
+        <v>46149.80208333334</v>
       </c>
       <c r="B79">
-        <v>647.125</v>
+        <v>1274.221</v>
       </c>
       <c r="C79">
-        <v>904</v>
+        <v>1596</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46147.8125</v>
+        <v>46149.8125</v>
       </c>
       <c r="B80">
-        <v>679.58</v>
+        <v>1303.75</v>
       </c>
       <c r="C80">
-        <v>983</v>
+        <v>1612</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46147.82291666666</v>
+        <v>46149.82291666666</v>
       </c>
       <c r="B81">
-        <v>715.471</v>
+        <v>1330.78</v>
       </c>
       <c r="C81">
-        <v>1033</v>
+        <v>1585</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46147.83333333334</v>
+        <v>46149.83333333334</v>
       </c>
       <c r="B82">
-        <v>716.193</v>
+        <v>1382.785</v>
       </c>
       <c r="C82">
-        <v>1112</v>
+        <v>1590</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46147.84375</v>
+        <v>46149.84375</v>
       </c>
       <c r="B83">
-        <v>735.692</v>
+        <v>1387.861</v>
       </c>
       <c r="C83">
-        <v>1154</v>
+        <v>1593</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46147.85416666666</v>
+        <v>46149.85416666666</v>
       </c>
       <c r="B84">
-        <v>755.599</v>
+        <v>1391.948</v>
       </c>
       <c r="C84">
-        <v>1189</v>
+        <v>1582</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46147.86458333334</v>
+        <v>46149.86458333334</v>
       </c>
       <c r="B85">
-        <v>774.275</v>
+        <v>1396.8</v>
       </c>
       <c r="C85">
-        <v>1216</v>
+        <v>1534</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46147.875</v>
+        <v>46149.875</v>
       </c>
       <c r="B86">
-        <v>783.145</v>
+        <v>1366.305</v>
       </c>
       <c r="C86">
-        <v>1226</v>
+        <v>1516</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46147.88541666666</v>
+        <v>46149.88541666666</v>
       </c>
       <c r="B87">
-        <v>787.203</v>
+        <v>1354.51</v>
       </c>
       <c r="C87">
-        <v>1239</v>
+        <v>1486</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46147.89583333334</v>
+        <v>46149.89583333334</v>
       </c>
       <c r="B88">
-        <v>790.992</v>
+        <v>1341.969</v>
       </c>
       <c r="C88">
-        <v>1183</v>
+        <v>1449</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46147.90625</v>
+        <v>46149.90625</v>
       </c>
       <c r="B89">
-        <v>793.563</v>
+        <v>1328.238</v>
       </c>
       <c r="C89">
-        <v>1140</v>
+        <v>1426</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46147.91666666666</v>
+        <v>46149.91666666666</v>
       </c>
       <c r="B90">
-        <v>848.452</v>
+        <v>1328.933</v>
       </c>
       <c r="C90">
-        <v>1114</v>
+        <v>1435</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46147.92708333334</v>
+        <v>46149.92708333334</v>
       </c>
       <c r="B91">
-        <v>839.7190000000001</v>
+        <v>1308.96</v>
       </c>
       <c r="C91">
-        <v>1091</v>
+        <v>1460</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46147.9375</v>
+        <v>46149.9375</v>
       </c>
       <c r="B92">
-        <v>832.0549999999999</v>
+        <v>1288.348</v>
       </c>
       <c r="C92">
-        <v>1063</v>
+        <v>1441</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46147.94791666666</v>
+        <v>46149.94791666666</v>
       </c>
       <c r="B93">
-        <v>823.154</v>
+        <v>1266.628</v>
       </c>
       <c r="C93">
-        <v>1012</v>
+        <v>1393</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46147.95833333334</v>
+        <v>46149.95833333334</v>
       </c>
       <c r="B94">
-        <v>804.077</v>
+        <v>1232.427</v>
       </c>
       <c r="C94">
-        <v>987</v>
+        <v>1315</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46147.96875</v>
+        <v>46149.96875</v>
       </c>
       <c r="B95">
-        <v>778.775</v>
+        <v>1200.547</v>
       </c>
       <c r="C95">
-        <v>971</v>
+        <v>1242</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46147.97916666666</v>
+        <v>46149.97916666666</v>
       </c>
       <c r="B96">
-        <v>760.081</v>
+        <v>1173.06</v>
       </c>
       <c r="C96">
-        <v>958</v>
+        <v>1228</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46147.98958333334</v>
+        <v>46149.98958333334</v>
       </c>
       <c r="B97">
-        <v>740.923</v>
+        <v>1139.233</v>
       </c>
       <c r="C97">
-        <v>948</v>
+        <v>1225</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B98">
-        <v>782.6</v>
+        <v>1128.219</v>
       </c>
       <c r="C98">
-        <v>922</v>
+        <v>1233</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B99">
-        <v>750.5599999999999</v>
+        <v>1103.223</v>
       </c>
       <c r="C99">
-        <v>914</v>
+        <v>1227</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B100">
-        <v>731.287</v>
+        <v>1076.002</v>
       </c>
       <c r="C100">
-        <v>881</v>
+        <v>1244</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B101">
-        <v>706.922</v>
+        <v>1055.529</v>
       </c>
       <c r="C101">
-        <v>818</v>
+        <v>1218</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B102">
-        <v>637.643</v>
+        <v>1035.284</v>
       </c>
       <c r="C102">
-        <v>732</v>
+        <v>1211</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B103">
-        <v>603.902</v>
+        <v>1025.564</v>
       </c>
       <c r="C103">
-        <v>655</v>
+        <v>1213</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B104">
-        <v>580.249</v>
+        <v>1005.742</v>
       </c>
       <c r="C104">
-        <v>589</v>
+        <v>1203</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B105">
-        <v>558.985</v>
+        <v>991.107</v>
       </c>
       <c r="C105">
-        <v>533</v>
+        <v>1169</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B106">
-        <v>519.23</v>
+        <v>963.066</v>
       </c>
       <c r="C106">
-        <v>482</v>
+        <v>1163</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B107">
-        <v>487.589</v>
+        <v>953.102</v>
       </c>
       <c r="C107">
-        <v>430</v>
+        <v>1142</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B108">
-        <v>468.55</v>
+        <v>957.638</v>
       </c>
       <c r="C108">
-        <v>393</v>
+        <v>1089</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B109">
-        <v>444.037</v>
+        <v>938.829</v>
       </c>
       <c r="C109">
-        <v>370</v>
+        <v>1005</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B110">
-        <v>443.371</v>
+        <v>898.919</v>
       </c>
       <c r="C110">
-        <v>360</v>
+        <v>947</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B111">
-        <v>425.783</v>
+        <v>874.433</v>
       </c>
       <c r="C111">
-        <v>327</v>
+        <v>901</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B112">
-        <v>413.582</v>
+        <v>853.569</v>
       </c>
       <c r="C112">
-        <v>304</v>
+        <v>856</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B113">
-        <v>395.002</v>
+        <v>828.7190000000001</v>
       </c>
       <c r="C113">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B114">
-        <v>334.312</v>
+        <v>725.808</v>
       </c>
       <c r="C114">
-        <v>281</v>
+        <v>894</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B115">
-        <v>320.263</v>
+        <v>705.97</v>
       </c>
       <c r="C115">
-        <v>259</v>
+        <v>888</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B116">
-        <v>307.128</v>
+        <v>683.84</v>
       </c>
       <c r="C116">
-        <v>241</v>
+        <v>884</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B117">
-        <v>294.25</v>
+        <v>658.9829999999999</v>
       </c>
       <c r="C117">
-        <v>240</v>
+        <v>859</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B118">
-        <v>274.426</v>
+        <v>610.22</v>
       </c>
       <c r="C118">
-        <v>233</v>
+        <v>791</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B119">
-        <v>263.078</v>
+        <v>603.42</v>
       </c>
       <c r="C119">
-        <v>225</v>
+        <v>727</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B120">
-        <v>256.936</v>
+        <v>588.58</v>
       </c>
       <c r="C120">
-        <v>207</v>
+        <v>681</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B121">
-        <v>249.909</v>
+        <v>576.699</v>
       </c>
       <c r="C121">
-        <v>194</v>
+        <v>645</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B122">
-        <v>238.905</v>
+        <v>512.752</v>
       </c>
       <c r="C122">
-        <v>190</v>
+        <v>575</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B123">
-        <v>237.743</v>
+        <v>510.174</v>
       </c>
       <c r="C123">
-        <v>176</v>
+        <v>522</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B124">
-        <v>233.729</v>
+        <v>524.353</v>
       </c>
       <c r="C124">
-        <v>158</v>
+        <v>480</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B125">
-        <v>232.179</v>
+        <v>518.778</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B126">
-        <v>236.659</v>
+        <v>446.075</v>
       </c>
       <c r="C126">
-        <v>139</v>
+        <v>373</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B127">
-        <v>234.812</v>
+        <v>430.238</v>
       </c>
       <c r="C127">
-        <v>120</v>
+        <v>322</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B128">
-        <v>233.834</v>
+        <v>409.691</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B129">
-        <v>239.047</v>
+        <v>396.414</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B130">
-        <v>300.224</v>
+        <v>405.968</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B131">
-        <v>303.863</v>
+        <v>392.106</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B132">
-        <v>318.007</v>
+        <v>384.164</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B133">
-        <v>313.134</v>
+        <v>375.771</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B134">
-        <v>345.72</v>
+        <v>379.921</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B135">
-        <v>372.873</v>
+        <v>379.085</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B136">
-        <v>399.491</v>
+        <v>378.58</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B137">
-        <v>426.29</v>
+        <v>377.693</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B138">
-        <v>434.392</v>
+        <v>384.565</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B139">
-        <v>458.299</v>
+        <v>396.72</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B140">
-        <v>481.282</v>
+        <v>408.144</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B141">
-        <v>503.735</v>
+        <v>419.41</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B142">
-        <v>544.563</v>
+        <v>432.76</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B143">
-        <v>560.078</v>
+        <v>441.251</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B144">
-        <v>575.821</v>
+        <v>450.268</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B145">
-        <v>592.349</v>
+        <v>459.733</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B146">
-        <v>594.5309999999999</v>
+        <v>478.332</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B147">
-        <v>602.684</v>
+        <v>485.135</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B148">
-        <v>610.708</v>
+        <v>491.605</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B149">
-        <v>618.492</v>
+        <v>498.903</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B150">
-        <v>622.478</v>
+        <v>511.014</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B151">
-        <v>624.4930000000001</v>
+        <v>517.292</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B152">
-        <v>626.129</v>
+        <v>521.86</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B153">
-        <v>628.698</v>
+        <v>526.9930000000001</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B154">
-        <v>649.298</v>
+        <v>524.653</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B155">
-        <v>653.508</v>
+        <v>532.766</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B156">
-        <v>657.486</v>
+        <v>540.204</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B157">
-        <v>661.277</v>
+        <v>549.728</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B158">
-        <v>668.0170000000001</v>
+        <v>554.545</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B159">
-        <v>675.697</v>
+        <v>559.178</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B160">
-        <v>683.78</v>
+        <v>564.417</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B161">
-        <v>691.801</v>
+        <v>568.955</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B162">
-        <v>750.998</v>
+        <v>509.336</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B163">
-        <v>760.914</v>
+        <v>510.897</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B164">
-        <v>770.251</v>
+        <v>513.307</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B165">
-        <v>778.332</v>
+        <v>516.074</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B166">
-        <v>762.087</v>
+        <v>515.9299999999999</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B167">
-        <v>776.933</v>
+        <v>514.064</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B168">
-        <v>792.0890000000001</v>
+        <v>512.515</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B169">
-        <v>805.84</v>
+        <v>511.612</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B170">
-        <v>834.356</v>
+        <v>502.257</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B171">
-        <v>863.265</v>
+        <v>508.437</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B172">
-        <v>893.154</v>
+        <v>516.023</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B173">
-        <v>923.309</v>
+        <v>522.876</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B174">
-        <v>951.201</v>
+        <v>535.347</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B175">
-        <v>974.909</v>
+        <v>540.175</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B176">
-        <v>1001.251</v>
+        <v>545.4829999999999</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B177">
-        <v>1024.676</v>
+        <v>550.277</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B178">
-        <v>1059.86</v>
+        <v>568.159</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B179">
-        <v>1069.276</v>
+        <v>561.001</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B180">
-        <v>1077.697</v>
+        <v>553.962</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B181">
-        <v>1085.675</v>
+        <v>546.873</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B182">
-        <v>1093.885</v>
+        <v>516.223</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B183">
-        <v>1094.099</v>
+        <v>503.182</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B184">
-        <v>1093.667</v>
+        <v>485.545</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B185">
-        <v>1094.016</v>
+        <v>471.292</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B186">
-        <v>1066.746</v>
+        <v>450.85</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B187">
-        <v>1063.407</v>
+        <v>442.259</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B188">
-        <v>1062.067</v>
+        <v>428.21</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B189">
-        <v>1060.107</v>
+        <v>443.51</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.05.20261</t>
-  </si>
-  <si>
-    <t>07.05.20262</t>
-  </si>
-  <si>
-    <t>07.05.20263</t>
-  </si>
-  <si>
-    <t>07.05.20264</t>
-  </si>
-  <si>
-    <t>07.05.20265</t>
-  </si>
-  <si>
-    <t>07.05.20266</t>
-  </si>
-  <si>
-    <t>07.05.20267</t>
-  </si>
-  <si>
-    <t>07.05.20268</t>
-  </si>
-  <si>
-    <t>07.05.20269</t>
-  </si>
-  <si>
-    <t>07.05.202610</t>
-  </si>
-  <si>
-    <t>07.05.202611</t>
-  </si>
-  <si>
-    <t>07.05.202612</t>
-  </si>
-  <si>
-    <t>07.05.202613</t>
-  </si>
-  <si>
-    <t>07.05.202614</t>
-  </si>
-  <si>
-    <t>07.05.202615</t>
-  </si>
-  <si>
-    <t>07.05.202616</t>
-  </si>
-  <si>
-    <t>07.05.202617</t>
-  </si>
-  <si>
-    <t>07.05.202618</t>
-  </si>
-  <si>
-    <t>07.05.202619</t>
-  </si>
-  <si>
-    <t>07.05.202620</t>
-  </si>
-  <si>
-    <t>07.05.202621</t>
-  </si>
-  <si>
-    <t>07.05.202622</t>
-  </si>
-  <si>
-    <t>07.05.202623</t>
-  </si>
-  <si>
-    <t>07.05.202624</t>
-  </si>
-  <si>
-    <t>07.05.202625</t>
-  </si>
-  <si>
-    <t>07.05.202626</t>
-  </si>
-  <si>
-    <t>07.05.202627</t>
-  </si>
-  <si>
-    <t>07.05.202628</t>
-  </si>
-  <si>
-    <t>07.05.202629</t>
-  </si>
-  <si>
-    <t>07.05.202630</t>
-  </si>
-  <si>
-    <t>07.05.202631</t>
-  </si>
-  <si>
-    <t>07.05.202632</t>
-  </si>
-  <si>
-    <t>07.05.202633</t>
-  </si>
-  <si>
-    <t>07.05.202634</t>
-  </si>
-  <si>
-    <t>07.05.202635</t>
-  </si>
-  <si>
-    <t>07.05.202636</t>
-  </si>
-  <si>
-    <t>07.05.202637</t>
-  </si>
-  <si>
-    <t>07.05.202638</t>
-  </si>
-  <si>
-    <t>07.05.202639</t>
-  </si>
-  <si>
-    <t>07.05.202640</t>
-  </si>
-  <si>
-    <t>07.05.202641</t>
-  </si>
-  <si>
-    <t>07.05.202642</t>
-  </si>
-  <si>
-    <t>07.05.202643</t>
-  </si>
-  <si>
-    <t>07.05.202644</t>
-  </si>
-  <si>
-    <t>07.05.202645</t>
-  </si>
-  <si>
-    <t>07.05.202646</t>
-  </si>
-  <si>
-    <t>07.05.202647</t>
-  </si>
-  <si>
-    <t>07.05.202648</t>
-  </si>
-  <si>
-    <t>07.05.202649</t>
-  </si>
-  <si>
-    <t>07.05.202650</t>
-  </si>
-  <si>
-    <t>07.05.202651</t>
-  </si>
-  <si>
-    <t>07.05.202652</t>
-  </si>
-  <si>
-    <t>07.05.202653</t>
-  </si>
-  <si>
-    <t>07.05.202654</t>
-  </si>
-  <si>
-    <t>07.05.202655</t>
-  </si>
-  <si>
-    <t>07.05.202656</t>
-  </si>
-  <si>
-    <t>07.05.202657</t>
-  </si>
-  <si>
-    <t>07.05.202658</t>
-  </si>
-  <si>
-    <t>07.05.202659</t>
-  </si>
-  <si>
-    <t>07.05.202660</t>
-  </si>
-  <si>
-    <t>07.05.202661</t>
-  </si>
-  <si>
-    <t>07.05.202662</t>
-  </si>
-  <si>
-    <t>07.05.202663</t>
-  </si>
-  <si>
-    <t>07.05.202664</t>
-  </si>
-  <si>
-    <t>07.05.202665</t>
-  </si>
-  <si>
-    <t>07.05.202666</t>
-  </si>
-  <si>
-    <t>07.05.202667</t>
-  </si>
-  <si>
-    <t>07.05.202668</t>
-  </si>
-  <si>
-    <t>07.05.202669</t>
-  </si>
-  <si>
-    <t>07.05.202670</t>
-  </si>
-  <si>
-    <t>07.05.202671</t>
-  </si>
-  <si>
-    <t>07.05.202672</t>
-  </si>
-  <si>
-    <t>07.05.202673</t>
-  </si>
-  <si>
-    <t>07.05.202674</t>
-  </si>
-  <si>
-    <t>07.05.202675</t>
-  </si>
-  <si>
-    <t>07.05.202676</t>
-  </si>
-  <si>
-    <t>07.05.202677</t>
-  </si>
-  <si>
-    <t>07.05.202678</t>
-  </si>
-  <si>
-    <t>07.05.202679</t>
-  </si>
-  <si>
-    <t>07.05.202680</t>
-  </si>
-  <si>
-    <t>07.05.202681</t>
-  </si>
-  <si>
-    <t>07.05.202682</t>
-  </si>
-  <si>
-    <t>07.05.202683</t>
-  </si>
-  <si>
-    <t>07.05.202684</t>
-  </si>
-  <si>
-    <t>07.05.202685</t>
-  </si>
-  <si>
-    <t>07.05.202686</t>
-  </si>
-  <si>
-    <t>07.05.202687</t>
-  </si>
-  <si>
-    <t>07.05.202688</t>
-  </si>
-  <si>
-    <t>07.05.202689</t>
-  </si>
-  <si>
-    <t>07.05.202690</t>
-  </si>
-  <si>
-    <t>07.05.202691</t>
-  </si>
-  <si>
-    <t>07.05.202692</t>
-  </si>
-  <si>
-    <t>07.05.202693</t>
-  </si>
-  <si>
-    <t>07.05.202694</t>
-  </si>
-  <si>
-    <t>07.05.202695</t>
-  </si>
-  <si>
-    <t>07.05.202696</t>
-  </si>
-  <si>
-    <t>08.05.20261</t>
-  </si>
-  <si>
-    <t>08.05.20262</t>
-  </si>
-  <si>
-    <t>08.05.20263</t>
-  </si>
-  <si>
-    <t>08.05.20264</t>
-  </si>
-  <si>
-    <t>08.05.20265</t>
-  </si>
-  <si>
-    <t>08.05.20266</t>
-  </si>
-  <si>
-    <t>08.05.20267</t>
-  </si>
-  <si>
-    <t>08.05.20268</t>
-  </si>
-  <si>
-    <t>08.05.20269</t>
-  </si>
-  <si>
-    <t>08.05.202610</t>
-  </si>
-  <si>
-    <t>08.05.202611</t>
-  </si>
-  <si>
-    <t>08.05.202612</t>
-  </si>
-  <si>
-    <t>08.05.202613</t>
-  </si>
-  <si>
-    <t>08.05.202614</t>
-  </si>
-  <si>
-    <t>08.05.202615</t>
-  </si>
-  <si>
-    <t>08.05.202616</t>
-  </si>
-  <si>
-    <t>08.05.202617</t>
-  </si>
-  <si>
-    <t>08.05.202618</t>
-  </si>
-  <si>
-    <t>08.05.202619</t>
-  </si>
-  <si>
-    <t>08.05.202620</t>
-  </si>
-  <si>
-    <t>08.05.202621</t>
-  </si>
-  <si>
-    <t>08.05.202622</t>
-  </si>
-  <si>
-    <t>08.05.202623</t>
-  </si>
-  <si>
-    <t>08.05.202624</t>
-  </si>
-  <si>
-    <t>08.05.202625</t>
-  </si>
-  <si>
-    <t>08.05.202626</t>
-  </si>
-  <si>
-    <t>08.05.202627</t>
-  </si>
-  <si>
-    <t>08.05.202628</t>
-  </si>
-  <si>
-    <t>08.05.202629</t>
-  </si>
-  <si>
-    <t>08.05.202630</t>
-  </si>
-  <si>
-    <t>08.05.202631</t>
-  </si>
-  <si>
-    <t>08.05.202632</t>
-  </si>
-  <si>
-    <t>08.05.202633</t>
-  </si>
-  <si>
-    <t>08.05.202634</t>
-  </si>
-  <si>
-    <t>08.05.202635</t>
-  </si>
-  <si>
-    <t>08.05.202636</t>
-  </si>
-  <si>
-    <t>08.05.202637</t>
-  </si>
-  <si>
-    <t>08.05.202638</t>
-  </si>
-  <si>
-    <t>08.05.202639</t>
-  </si>
-  <si>
-    <t>08.05.202640</t>
-  </si>
-  <si>
-    <t>08.05.202641</t>
-  </si>
-  <si>
-    <t>08.05.202642</t>
-  </si>
-  <si>
-    <t>08.05.202643</t>
-  </si>
-  <si>
-    <t>08.05.202644</t>
-  </si>
-  <si>
-    <t>08.05.202645</t>
-  </si>
-  <si>
-    <t>08.05.202646</t>
-  </si>
-  <si>
-    <t>08.05.202647</t>
-  </si>
-  <si>
-    <t>08.05.202648</t>
-  </si>
-  <si>
-    <t>08.05.202649</t>
-  </si>
-  <si>
-    <t>08.05.202650</t>
-  </si>
-  <si>
-    <t>08.05.202651</t>
-  </si>
-  <si>
-    <t>08.05.202652</t>
-  </si>
-  <si>
-    <t>08.05.202653</t>
-  </si>
-  <si>
-    <t>08.05.202654</t>
-  </si>
-  <si>
-    <t>08.05.202655</t>
-  </si>
-  <si>
-    <t>08.05.202656</t>
-  </si>
-  <si>
-    <t>08.05.202657</t>
-  </si>
-  <si>
-    <t>08.05.202658</t>
-  </si>
-  <si>
-    <t>08.05.202659</t>
-  </si>
-  <si>
-    <t>08.05.202660</t>
-  </si>
-  <si>
-    <t>08.05.202661</t>
-  </si>
-  <si>
-    <t>08.05.202662</t>
-  </si>
-  <si>
-    <t>08.05.202663</t>
-  </si>
-  <si>
-    <t>08.05.202664</t>
-  </si>
-  <si>
-    <t>08.05.202665</t>
-  </si>
-  <si>
-    <t>08.05.202666</t>
-  </si>
-  <si>
-    <t>08.05.202667</t>
-  </si>
-  <si>
-    <t>08.05.202668</t>
-  </si>
-  <si>
-    <t>08.05.202669</t>
-  </si>
-  <si>
-    <t>08.05.202670</t>
-  </si>
-  <si>
-    <t>08.05.202671</t>
-  </si>
-  <si>
-    <t>08.05.202672</t>
-  </si>
-  <si>
-    <t>08.05.202673</t>
-  </si>
-  <si>
-    <t>08.05.202674</t>
-  </si>
-  <si>
-    <t>08.05.202675</t>
-  </si>
-  <si>
-    <t>08.05.202676</t>
-  </si>
-  <si>
-    <t>08.05.202677</t>
-  </si>
-  <si>
-    <t>08.05.202678</t>
-  </si>
-  <si>
-    <t>08.05.202679</t>
-  </si>
-  <si>
-    <t>08.05.202680</t>
-  </si>
-  <si>
-    <t>08.05.202681</t>
-  </si>
-  <si>
-    <t>08.05.202682</t>
-  </si>
-  <si>
-    <t>08.05.202683</t>
-  </si>
-  <si>
-    <t>08.05.202684</t>
-  </si>
-  <si>
-    <t>08.05.202685</t>
-  </si>
-  <si>
-    <t>08.05.202686</t>
-  </si>
-  <si>
-    <t>08.05.202687</t>
-  </si>
-  <si>
-    <t>08.05.202688</t>
-  </si>
-  <si>
-    <t>08.05.202689</t>
-  </si>
-  <si>
-    <t>08.05.202690</t>
-  </si>
-  <si>
-    <t>08.05.202691</t>
-  </si>
-  <si>
-    <t>08.05.202692</t>
-  </si>
-  <si>
-    <t>08.05.202693</t>
-  </si>
-  <si>
-    <t>08.05.202694</t>
-  </si>
-  <si>
-    <t>08.05.202695</t>
-  </si>
-  <si>
-    <t>08.05.202696</t>
+    <t>11.05.20261</t>
+  </si>
+  <si>
+    <t>11.05.20262</t>
+  </si>
+  <si>
+    <t>11.05.20263</t>
+  </si>
+  <si>
+    <t>11.05.20264</t>
+  </si>
+  <si>
+    <t>11.05.20265</t>
+  </si>
+  <si>
+    <t>11.05.20266</t>
+  </si>
+  <si>
+    <t>11.05.20267</t>
+  </si>
+  <si>
+    <t>11.05.20268</t>
+  </si>
+  <si>
+    <t>11.05.20269</t>
+  </si>
+  <si>
+    <t>11.05.202610</t>
+  </si>
+  <si>
+    <t>11.05.202611</t>
+  </si>
+  <si>
+    <t>11.05.202612</t>
+  </si>
+  <si>
+    <t>11.05.202613</t>
+  </si>
+  <si>
+    <t>11.05.202614</t>
+  </si>
+  <si>
+    <t>11.05.202615</t>
+  </si>
+  <si>
+    <t>11.05.202616</t>
+  </si>
+  <si>
+    <t>11.05.202617</t>
+  </si>
+  <si>
+    <t>11.05.202618</t>
+  </si>
+  <si>
+    <t>11.05.202619</t>
+  </si>
+  <si>
+    <t>11.05.202620</t>
+  </si>
+  <si>
+    <t>11.05.202621</t>
+  </si>
+  <si>
+    <t>11.05.202622</t>
+  </si>
+  <si>
+    <t>11.05.202623</t>
+  </si>
+  <si>
+    <t>11.05.202624</t>
+  </si>
+  <si>
+    <t>11.05.202625</t>
+  </si>
+  <si>
+    <t>11.05.202626</t>
+  </si>
+  <si>
+    <t>11.05.202627</t>
+  </si>
+  <si>
+    <t>11.05.202628</t>
+  </si>
+  <si>
+    <t>11.05.202629</t>
+  </si>
+  <si>
+    <t>11.05.202630</t>
+  </si>
+  <si>
+    <t>11.05.202631</t>
+  </si>
+  <si>
+    <t>11.05.202632</t>
+  </si>
+  <si>
+    <t>11.05.202633</t>
+  </si>
+  <si>
+    <t>11.05.202634</t>
+  </si>
+  <si>
+    <t>11.05.202635</t>
+  </si>
+  <si>
+    <t>11.05.202636</t>
+  </si>
+  <si>
+    <t>11.05.202637</t>
+  </si>
+  <si>
+    <t>11.05.202638</t>
+  </si>
+  <si>
+    <t>11.05.202639</t>
+  </si>
+  <si>
+    <t>11.05.202640</t>
+  </si>
+  <si>
+    <t>11.05.202641</t>
+  </si>
+  <si>
+    <t>11.05.202642</t>
+  </si>
+  <si>
+    <t>11.05.202643</t>
+  </si>
+  <si>
+    <t>11.05.202644</t>
+  </si>
+  <si>
+    <t>11.05.202645</t>
+  </si>
+  <si>
+    <t>11.05.202646</t>
+  </si>
+  <si>
+    <t>11.05.202647</t>
+  </si>
+  <si>
+    <t>11.05.202648</t>
+  </si>
+  <si>
+    <t>11.05.202649</t>
+  </si>
+  <si>
+    <t>11.05.202650</t>
+  </si>
+  <si>
+    <t>11.05.202651</t>
+  </si>
+  <si>
+    <t>11.05.202652</t>
+  </si>
+  <si>
+    <t>11.05.202653</t>
+  </si>
+  <si>
+    <t>11.05.202654</t>
+  </si>
+  <si>
+    <t>11.05.202655</t>
+  </si>
+  <si>
+    <t>11.05.202656</t>
+  </si>
+  <si>
+    <t>11.05.202657</t>
+  </si>
+  <si>
+    <t>11.05.202658</t>
+  </si>
+  <si>
+    <t>11.05.202659</t>
+  </si>
+  <si>
+    <t>11.05.202660</t>
+  </si>
+  <si>
+    <t>11.05.202661</t>
+  </si>
+  <si>
+    <t>11.05.202662</t>
+  </si>
+  <si>
+    <t>11.05.202663</t>
+  </si>
+  <si>
+    <t>11.05.202664</t>
+  </si>
+  <si>
+    <t>11.05.202665</t>
+  </si>
+  <si>
+    <t>11.05.202666</t>
+  </si>
+  <si>
+    <t>11.05.202667</t>
+  </si>
+  <si>
+    <t>11.05.202668</t>
+  </si>
+  <si>
+    <t>11.05.202669</t>
+  </si>
+  <si>
+    <t>11.05.202670</t>
+  </si>
+  <si>
+    <t>11.05.202671</t>
+  </si>
+  <si>
+    <t>11.05.202672</t>
+  </si>
+  <si>
+    <t>11.05.202673</t>
+  </si>
+  <si>
+    <t>11.05.202674</t>
+  </si>
+  <si>
+    <t>11.05.202675</t>
+  </si>
+  <si>
+    <t>11.05.202676</t>
+  </si>
+  <si>
+    <t>11.05.202677</t>
+  </si>
+  <si>
+    <t>11.05.202678</t>
+  </si>
+  <si>
+    <t>11.05.202679</t>
+  </si>
+  <si>
+    <t>11.05.202680</t>
+  </si>
+  <si>
+    <t>11.05.202681</t>
+  </si>
+  <si>
+    <t>11.05.202682</t>
+  </si>
+  <si>
+    <t>11.05.202683</t>
+  </si>
+  <si>
+    <t>11.05.202684</t>
+  </si>
+  <si>
+    <t>11.05.202685</t>
+  </si>
+  <si>
+    <t>11.05.202686</t>
+  </si>
+  <si>
+    <t>11.05.202687</t>
+  </si>
+  <si>
+    <t>11.05.202688</t>
+  </si>
+  <si>
+    <t>11.05.202689</t>
+  </si>
+  <si>
+    <t>11.05.202690</t>
+  </si>
+  <si>
+    <t>11.05.202691</t>
+  </si>
+  <si>
+    <t>11.05.202692</t>
+  </si>
+  <si>
+    <t>11.05.202693</t>
+  </si>
+  <si>
+    <t>11.05.202694</t>
+  </si>
+  <si>
+    <t>11.05.202695</t>
+  </si>
+  <si>
+    <t>11.05.202696</t>
+  </si>
+  <si>
+    <t>12.05.20261</t>
+  </si>
+  <si>
+    <t>12.05.20262</t>
+  </si>
+  <si>
+    <t>12.05.20263</t>
+  </si>
+  <si>
+    <t>12.05.20264</t>
+  </si>
+  <si>
+    <t>12.05.20265</t>
+  </si>
+  <si>
+    <t>12.05.20266</t>
+  </si>
+  <si>
+    <t>12.05.20267</t>
+  </si>
+  <si>
+    <t>12.05.20268</t>
+  </si>
+  <si>
+    <t>12.05.20269</t>
+  </si>
+  <si>
+    <t>12.05.202610</t>
+  </si>
+  <si>
+    <t>12.05.202611</t>
+  </si>
+  <si>
+    <t>12.05.202612</t>
+  </si>
+  <si>
+    <t>12.05.202613</t>
+  </si>
+  <si>
+    <t>12.05.202614</t>
+  </si>
+  <si>
+    <t>12.05.202615</t>
+  </si>
+  <si>
+    <t>12.05.202616</t>
+  </si>
+  <si>
+    <t>12.05.202617</t>
+  </si>
+  <si>
+    <t>12.05.202618</t>
+  </si>
+  <si>
+    <t>12.05.202619</t>
+  </si>
+  <si>
+    <t>12.05.202620</t>
+  </si>
+  <si>
+    <t>12.05.202621</t>
+  </si>
+  <si>
+    <t>12.05.202622</t>
+  </si>
+  <si>
+    <t>12.05.202623</t>
+  </si>
+  <si>
+    <t>12.05.202624</t>
+  </si>
+  <si>
+    <t>12.05.202625</t>
+  </si>
+  <si>
+    <t>12.05.202626</t>
+  </si>
+  <si>
+    <t>12.05.202627</t>
+  </si>
+  <si>
+    <t>12.05.202628</t>
+  </si>
+  <si>
+    <t>12.05.202629</t>
+  </si>
+  <si>
+    <t>12.05.202630</t>
+  </si>
+  <si>
+    <t>12.05.202631</t>
+  </si>
+  <si>
+    <t>12.05.202632</t>
+  </si>
+  <si>
+    <t>12.05.202633</t>
+  </si>
+  <si>
+    <t>12.05.202634</t>
+  </si>
+  <si>
+    <t>12.05.202635</t>
+  </si>
+  <si>
+    <t>12.05.202636</t>
+  </si>
+  <si>
+    <t>12.05.202637</t>
+  </si>
+  <si>
+    <t>12.05.202638</t>
+  </si>
+  <si>
+    <t>12.05.202639</t>
+  </si>
+  <si>
+    <t>12.05.202640</t>
+  </si>
+  <si>
+    <t>12.05.202641</t>
+  </si>
+  <si>
+    <t>12.05.202642</t>
+  </si>
+  <si>
+    <t>12.05.202643</t>
+  </si>
+  <si>
+    <t>12.05.202644</t>
+  </si>
+  <si>
+    <t>12.05.202645</t>
+  </si>
+  <si>
+    <t>12.05.202646</t>
+  </si>
+  <si>
+    <t>12.05.202647</t>
+  </si>
+  <si>
+    <t>12.05.202648</t>
+  </si>
+  <si>
+    <t>12.05.202649</t>
+  </si>
+  <si>
+    <t>12.05.202650</t>
+  </si>
+  <si>
+    <t>12.05.202651</t>
+  </si>
+  <si>
+    <t>12.05.202652</t>
+  </si>
+  <si>
+    <t>12.05.202653</t>
+  </si>
+  <si>
+    <t>12.05.202654</t>
+  </si>
+  <si>
+    <t>12.05.202655</t>
+  </si>
+  <si>
+    <t>12.05.202656</t>
+  </si>
+  <si>
+    <t>12.05.202657</t>
+  </si>
+  <si>
+    <t>12.05.202658</t>
+  </si>
+  <si>
+    <t>12.05.202659</t>
+  </si>
+  <si>
+    <t>12.05.202660</t>
+  </si>
+  <si>
+    <t>12.05.202661</t>
+  </si>
+  <si>
+    <t>12.05.202662</t>
+  </si>
+  <si>
+    <t>12.05.202663</t>
+  </si>
+  <si>
+    <t>12.05.202664</t>
+  </si>
+  <si>
+    <t>12.05.202665</t>
+  </si>
+  <si>
+    <t>12.05.202666</t>
+  </si>
+  <si>
+    <t>12.05.202667</t>
+  </si>
+  <si>
+    <t>12.05.202668</t>
+  </si>
+  <si>
+    <t>12.05.202669</t>
+  </si>
+  <si>
+    <t>12.05.202670</t>
+  </si>
+  <si>
+    <t>12.05.202671</t>
+  </si>
+  <si>
+    <t>12.05.202672</t>
+  </si>
+  <si>
+    <t>12.05.202673</t>
+  </si>
+  <si>
+    <t>12.05.202674</t>
+  </si>
+  <si>
+    <t>12.05.202675</t>
+  </si>
+  <si>
+    <t>12.05.202676</t>
+  </si>
+  <si>
+    <t>12.05.202677</t>
+  </si>
+  <si>
+    <t>12.05.202678</t>
+  </si>
+  <si>
+    <t>12.05.202679</t>
+  </si>
+  <si>
+    <t>12.05.202680</t>
+  </si>
+  <si>
+    <t>12.05.202681</t>
+  </si>
+  <si>
+    <t>12.05.202682</t>
+  </si>
+  <si>
+    <t>12.05.202683</t>
+  </si>
+  <si>
+    <t>12.05.202684</t>
+  </si>
+  <si>
+    <t>12.05.202685</t>
+  </si>
+  <si>
+    <t>12.05.202686</t>
+  </si>
+  <si>
+    <t>12.05.202687</t>
+  </si>
+  <si>
+    <t>12.05.202688</t>
+  </si>
+  <si>
+    <t>12.05.202689</t>
+  </si>
+  <si>
+    <t>12.05.202690</t>
+  </si>
+  <si>
+    <t>12.05.202691</t>
+  </si>
+  <si>
+    <t>12.05.202692</t>
+  </si>
+  <si>
+    <t>12.05.202693</t>
+  </si>
+  <si>
+    <t>12.05.202694</t>
+  </si>
+  <si>
+    <t>12.05.202695</t>
+  </si>
+  <si>
+    <t>12.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B2">
-        <v>762.05</v>
+        <v>130.332</v>
       </c>
       <c r="C2">
-        <v>840</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46149.01041666666</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
-        <v>747.8579999999999</v>
+        <v>130.352</v>
       </c>
       <c r="C3">
-        <v>839</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46149.02083333334</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
-        <v>739.557</v>
+        <v>130.671</v>
       </c>
       <c r="C4">
-        <v>838</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46149.03125</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
-        <v>730.7190000000001</v>
+        <v>130.81</v>
       </c>
       <c r="C5">
-        <v>868</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46149.04166666666</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
-        <v>733.5549999999999</v>
+        <v>129.903</v>
       </c>
       <c r="C6">
-        <v>876</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46149.05208333334</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
-        <v>720.004</v>
+        <v>128.473</v>
       </c>
       <c r="C7">
-        <v>879</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46149.0625</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
-        <v>713.748</v>
+        <v>127.035</v>
       </c>
       <c r="C8">
-        <v>869</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46149.07291666666</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
-        <v>709.947</v>
+        <v>125.456</v>
       </c>
       <c r="C9">
-        <v>850</v>
+        <v>23</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46149.08333333334</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
-        <v>703.2859999999999</v>
+        <v>112.252</v>
       </c>
       <c r="C10">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46149.09375</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
-        <v>695.318</v>
+        <v>112.257</v>
       </c>
       <c r="C11">
-        <v>810</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46149.10416666666</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
-        <v>695.545</v>
+        <v>112.884</v>
       </c>
       <c r="C12">
-        <v>809</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46149.11458333334</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>691.683</v>
+        <v>113.472</v>
       </c>
       <c r="C13">
-        <v>794</v>
+        <v>20</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46149.125</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>650.5170000000001</v>
+        <v>116.366</v>
       </c>
       <c r="C14">
-        <v>790</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46149.13541666666</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>650.144</v>
+        <v>119.211</v>
       </c>
       <c r="C15">
-        <v>809</v>
+        <v>29</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46149.14583333334</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>645.091</v>
+        <v>122.09</v>
       </c>
       <c r="C16">
-        <v>832</v>
+        <v>38</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46149.15625</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>639.264</v>
+        <v>125.275</v>
       </c>
       <c r="C17">
-        <v>846</v>
+        <v>42</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46149.16666666666</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>638.8150000000001</v>
+        <v>128.958</v>
       </c>
       <c r="C18">
-        <v>852</v>
+        <v>51</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46149.17708333334</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>632.873</v>
+        <v>135.368</v>
       </c>
       <c r="C19">
-        <v>853</v>
+        <v>65</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46149.1875</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>634.465</v>
+        <v>139.99</v>
       </c>
       <c r="C20">
-        <v>840</v>
+        <v>77</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46149.19791666666</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>633.998</v>
+        <v>146.63</v>
       </c>
       <c r="C21">
-        <v>815</v>
+        <v>85</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46149.20833333334</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>631.864</v>
+        <v>161.679</v>
       </c>
       <c r="C22">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46149.21875</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>630.146</v>
+        <v>172.446</v>
       </c>
       <c r="C23">
-        <v>783</v>
+        <v>128</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46149.22916666666</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>632.739</v>
+        <v>184.133</v>
       </c>
       <c r="C24">
-        <v>786</v>
+        <v>157</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46149.23958333334</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>633.35</v>
+        <v>195.863</v>
       </c>
       <c r="C25">
-        <v>791</v>
+        <v>173</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46149.25</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>618.395</v>
+        <v>184.073</v>
       </c>
       <c r="C26">
-        <v>788</v>
+        <v>177</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46149.26041666666</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>603.55</v>
+        <v>194.949</v>
       </c>
       <c r="C27">
-        <v>765</v>
+        <v>197</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46149.27083333334</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>590.179</v>
+        <v>207.406</v>
       </c>
       <c r="C28">
-        <v>692</v>
+        <v>195</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46149.28125</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>579.24</v>
+        <v>217.963</v>
       </c>
       <c r="C29">
-        <v>613</v>
+        <v>180</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46149.29166666666</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>590.823</v>
+        <v>223.207</v>
       </c>
       <c r="C30">
-        <v>544</v>
+        <v>164</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46149.30208333334</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>575.269</v>
+        <v>226.249</v>
       </c>
       <c r="C31">
-        <v>490</v>
+        <v>146</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46149.3125</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>561.073</v>
+        <v>228.391</v>
       </c>
       <c r="C32">
-        <v>449</v>
+        <v>138</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46149.32291666666</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>546.39</v>
+        <v>228.891</v>
       </c>
       <c r="C33">
-        <v>413</v>
+        <v>132</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46149.33333333334</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>639.1180000000001</v>
+        <v>241.616</v>
       </c>
       <c r="C34">
-        <v>391</v>
+        <v>144</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46149.34375</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>651.03</v>
+        <v>247.111</v>
       </c>
       <c r="C35">
-        <v>392</v>
+        <v>169</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46149.35416666666</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>664.809</v>
+        <v>260.222</v>
       </c>
       <c r="C36">
-        <v>399</v>
+        <v>201</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46149.36458333334</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>679.72</v>
+        <v>267.281</v>
       </c>
       <c r="C37">
-        <v>431</v>
+        <v>224</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46149.375</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>636.4880000000001</v>
+        <v>340.494</v>
       </c>
       <c r="C38">
-        <v>482</v>
+        <v>251</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46149.38541666666</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>668.408</v>
+        <v>365.54</v>
       </c>
       <c r="C39">
-        <v>543</v>
+        <v>274</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46149.39583333334</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>700.657</v>
+        <v>389.794</v>
       </c>
       <c r="C40">
-        <v>603</v>
+        <v>284</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46149.40625</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>733.45</v>
+        <v>413.845</v>
       </c>
       <c r="C41">
-        <v>695</v>
+        <v>297</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46149.41666666666</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>732.1130000000001</v>
+        <v>424.131</v>
       </c>
       <c r="C42">
-        <v>774</v>
+        <v>322</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46149.42708333334</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>768.008</v>
+        <v>454.116</v>
       </c>
       <c r="C43">
-        <v>818</v>
+        <v>350</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46149.4375</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>803.207</v>
+        <v>483.236</v>
       </c>
       <c r="C44">
-        <v>865</v>
+        <v>376</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46149.44791666666</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>839.126</v>
+        <v>512.643</v>
       </c>
       <c r="C45">
-        <v>915</v>
+        <v>415</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46149.45833333334</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>886.426</v>
+        <v>540.408</v>
       </c>
       <c r="C46">
-        <v>935</v>
+        <v>449</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46149.46875</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>915.842</v>
+        <v>570.808</v>
       </c>
       <c r="C47">
-        <v>969</v>
+        <v>490</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46149.47916666666</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>944.466</v>
+        <v>600.515</v>
       </c>
       <c r="C48">
-        <v>1014</v>
+        <v>508</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46149.48958333334</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>973.4299999999999</v>
+        <v>630.097</v>
       </c>
       <c r="C49">
-        <v>1046</v>
+        <v>529</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46149.5</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>998.478</v>
+        <v>698.88</v>
       </c>
       <c r="C50">
-        <v>1081</v>
+        <v>559</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46149.51041666666</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>1010.347</v>
+        <v>737.718</v>
       </c>
       <c r="C51">
-        <v>1089</v>
+        <v>599</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46149.52083333334</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>1020.493</v>
+        <v>777.216</v>
       </c>
       <c r="C52">
-        <v>1106</v>
+        <v>648</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46149.53125</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>1030.382</v>
+        <v>818.133</v>
       </c>
       <c r="C53">
-        <v>1123</v>
+        <v>718</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46149.54166666666</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>1073.36</v>
+        <v>883.697</v>
       </c>
       <c r="C54">
-        <v>1141</v>
+        <v>775</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46149.55208333334</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>1082.236</v>
+        <v>929.708</v>
       </c>
       <c r="C55">
-        <v>1152</v>
+        <v>835</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46149.5625</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>1090.039</v>
+        <v>974.356</v>
       </c>
       <c r="C56">
-        <v>1189</v>
+        <v>905</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46149.57291666666</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>1097.666</v>
+        <v>1019.87</v>
       </c>
       <c r="C57">
-        <v>1245</v>
+        <v>985</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46149.58333333334</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>1120.911</v>
+        <v>1098.039</v>
       </c>
       <c r="C58">
-        <v>1256</v>
+        <v>1055</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46149.59375</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>1126.245</v>
+        <v>1138.043</v>
       </c>
       <c r="C59">
-        <v>1303</v>
+        <v>1121</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46149.60416666666</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>1131.495</v>
+        <v>1177.11</v>
       </c>
       <c r="C60">
-        <v>1300</v>
+        <v>1171</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46149.61458333334</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>1135.786</v>
+        <v>1218.53</v>
       </c>
       <c r="C61">
-        <v>1302</v>
+        <v>1233</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46149.625</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>1102.027</v>
+        <v>1298.2</v>
       </c>
       <c r="C62">
-        <v>1300</v>
+        <v>1383</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46149.63541666666</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>1111.02</v>
+        <v>1327.065</v>
       </c>
       <c r="C63">
-        <v>1312</v>
+        <v>1476</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46149.64583333334</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>1118.524</v>
+        <v>1356.838</v>
       </c>
       <c r="C64">
-        <v>1328</v>
+        <v>1555</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46149.65625</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>1125.911</v>
+        <v>1383.577</v>
       </c>
       <c r="C65">
-        <v>1340</v>
+        <v>1591</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46149.66666666666</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>1130.993</v>
+        <v>1387.656</v>
       </c>
       <c r="C66">
-        <v>1350</v>
+        <v>1668</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46149.67708333334</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>1141.256</v>
+        <v>1387.816</v>
       </c>
       <c r="C67">
-        <v>1356</v>
+        <v>1707</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46149.6875</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>1151.208</v>
+        <v>1388.871</v>
       </c>
       <c r="C68">
-        <v>1391</v>
+        <v>1696</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46149.69791666666</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>1160.287</v>
+        <v>1389.424</v>
       </c>
       <c r="C69">
-        <v>1444</v>
+        <v>1649</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46149.70833333334</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>1156.753</v>
+        <v>1446.241</v>
       </c>
       <c r="C70">
-        <v>1491</v>
+        <v>1626</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46149.71875</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>1165.437</v>
+        <v>1444.349</v>
       </c>
       <c r="C71">
-        <v>1495</v>
+        <v>1651</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46149.72916666666</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>1175.581</v>
+        <v>1441.196</v>
       </c>
       <c r="C72">
-        <v>1476</v>
+        <v>1678</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46149.73958333334</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>1186.285</v>
+        <v>1440.542</v>
       </c>
       <c r="C73">
-        <v>1468</v>
+        <v>1667</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46149.75</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>1205.854</v>
+        <v>1452.502</v>
       </c>
       <c r="C74">
-        <v>1426</v>
+        <v>1754</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46149.76041666666</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>1227.032</v>
+        <v>1469.295</v>
       </c>
       <c r="C75">
-        <v>1445</v>
+        <v>1718</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46149.77083333334</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>1250.289</v>
+        <v>1484.072</v>
       </c>
       <c r="C76">
-        <v>1444</v>
+        <v>1728</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46149.78125</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>1270.113</v>
+        <v>1502.072</v>
       </c>
       <c r="C77">
-        <v>1470</v>
+        <v>1780</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46149.79166666666</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>1245.008</v>
+        <v>1537.951</v>
       </c>
       <c r="C78">
-        <v>1546</v>
+        <v>1786</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46149.80208333334</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>1274.221</v>
+        <v>1566.247</v>
       </c>
       <c r="C79">
-        <v>1596</v>
+        <v>1840</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46149.8125</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>1303.75</v>
+        <v>1590.751</v>
       </c>
       <c r="C80">
-        <v>1612</v>
+        <v>1880</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46149.82291666666</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>1330.78</v>
+        <v>1614.623</v>
       </c>
       <c r="C81">
-        <v>1585</v>
+        <v>1937</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46149.83333333334</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>1382.785</v>
+        <v>1693.584</v>
       </c>
       <c r="C82">
-        <v>1590</v>
+        <v>1924</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46149.84375</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>1387.861</v>
+        <v>1711.131</v>
       </c>
       <c r="C83">
-        <v>1593</v>
+        <v>1939</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46149.85416666666</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>1391.948</v>
+        <v>1729.709</v>
       </c>
       <c r="C84">
-        <v>1582</v>
+        <v>1953</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46149.86458333334</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>1396.8</v>
+        <v>1748.139</v>
       </c>
       <c r="C85">
-        <v>1534</v>
+        <v>1991</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46149.875</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>1366.305</v>
+        <v>1765.897</v>
       </c>
       <c r="C86">
-        <v>1516</v>
+        <v>2020</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46149.88541666666</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>1354.51</v>
+        <v>1767.159</v>
       </c>
       <c r="C87">
-        <v>1486</v>
+        <v>2050</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46149.89583333334</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>1341.969</v>
+        <v>1769.011</v>
       </c>
       <c r="C88">
-        <v>1449</v>
+        <v>2107</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46149.90625</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>1328.238</v>
+        <v>1769.947</v>
       </c>
       <c r="C89">
-        <v>1426</v>
+        <v>2103</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46149.91666666666</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>1328.933</v>
+        <v>1777.055</v>
       </c>
       <c r="C90">
-        <v>1435</v>
+        <v>2091</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46149.92708333334</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>1308.96</v>
+        <v>1778.638</v>
       </c>
       <c r="C91">
-        <v>1460</v>
+        <v>2050</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46149.9375</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
-        <v>1288.348</v>
+        <v>1780.721</v>
       </c>
       <c r="C92">
-        <v>1441</v>
+        <v>2042</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46149.94791666666</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>1266.628</v>
+        <v>1783.516</v>
       </c>
       <c r="C93">
-        <v>1393</v>
+        <v>2003</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46149.95833333334</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
-        <v>1232.427</v>
+        <v>1843.986</v>
       </c>
       <c r="C94">
-        <v>1315</v>
+        <v>2043</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46149.96875</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
-        <v>1200.547</v>
+        <v>1832.334</v>
       </c>
       <c r="C95">
-        <v>1242</v>
+        <v>2030</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46149.97916666666</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
-        <v>1173.06</v>
+        <v>1819.501</v>
       </c>
       <c r="C96">
-        <v>1228</v>
+        <v>2021</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46149.98958333334</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
-        <v>1139.233</v>
+        <v>1810.982</v>
       </c>
       <c r="C97">
-        <v>1225</v>
+        <v>2003</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B98">
-        <v>1128.219</v>
+        <v>1771.932</v>
       </c>
       <c r="C98">
-        <v>1233</v>
+        <v>1958</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B99">
-        <v>1103.223</v>
+        <v>1751.182</v>
       </c>
       <c r="C99">
-        <v>1227</v>
+        <v>1919</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B100">
-        <v>1076.002</v>
+        <v>1714.042</v>
       </c>
       <c r="C100">
-        <v>1244</v>
+        <v>1885</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B101">
-        <v>1055.529</v>
+        <v>1688.671</v>
       </c>
       <c r="C101">
-        <v>1218</v>
+        <v>1863</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B102">
-        <v>1035.284</v>
+        <v>1622.899</v>
       </c>
       <c r="C102">
-        <v>1211</v>
+        <v>1828</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B103">
-        <v>1025.564</v>
+        <v>1584.565</v>
       </c>
       <c r="C103">
-        <v>1213</v>
+        <v>1804</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B104">
-        <v>1005.742</v>
+        <v>1543.412</v>
       </c>
       <c r="C104">
-        <v>1203</v>
+        <v>1759</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B105">
-        <v>991.107</v>
+        <v>1513.14</v>
       </c>
       <c r="C105">
-        <v>1169</v>
+        <v>1711</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46150.08333333334</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B106">
-        <v>963.066</v>
+        <v>1444.737</v>
       </c>
       <c r="C106">
-        <v>1163</v>
+        <v>1652</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B107">
-        <v>953.102</v>
+        <v>1408.098</v>
       </c>
       <c r="C107">
-        <v>1142</v>
+        <v>1604</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46150.10416666666</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B108">
-        <v>957.638</v>
+        <v>1373.897</v>
       </c>
       <c r="C108">
-        <v>1089</v>
+        <v>1502</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46150.11458333334</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B109">
-        <v>938.829</v>
+        <v>1341.622</v>
       </c>
       <c r="C109">
-        <v>1005</v>
+        <v>1442</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B110">
-        <v>898.919</v>
+        <v>1266.748</v>
       </c>
       <c r="C110">
-        <v>947</v>
+        <v>1307</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46150.13541666666</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B111">
-        <v>874.433</v>
+        <v>1229.519</v>
       </c>
       <c r="C111">
-        <v>901</v>
+        <v>1239</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46150.14583333334</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B112">
-        <v>853.569</v>
+        <v>1186.962</v>
       </c>
       <c r="C112">
-        <v>856</v>
+        <v>1153</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B113">
-        <v>828.7190000000001</v>
+        <v>1142.421</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46150.16666666666</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B114">
-        <v>725.808</v>
+        <v>1122.598</v>
       </c>
       <c r="C114">
-        <v>894</v>
+        <v>910</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46150.17708333334</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B115">
-        <v>705.97</v>
+        <v>1073.779</v>
       </c>
       <c r="C115">
-        <v>888</v>
+        <v>814</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B116">
-        <v>683.84</v>
+        <v>1018.752</v>
       </c>
       <c r="C116">
-        <v>884</v>
+        <v>750</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46150.19791666666</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B117">
-        <v>658.9829999999999</v>
+        <v>965.311</v>
       </c>
       <c r="C117">
-        <v>859</v>
+        <v>699</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46150.20833333334</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B118">
-        <v>610.22</v>
+        <v>870.058</v>
       </c>
       <c r="C118">
-        <v>791</v>
+        <v>636</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B119">
-        <v>603.42</v>
+        <v>813.076</v>
       </c>
       <c r="C119">
-        <v>727</v>
+        <v>528</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46150.22916666666</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B120">
-        <v>588.58</v>
+        <v>781.1130000000001</v>
       </c>
       <c r="C120">
-        <v>681</v>
+        <v>469</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46150.23958333334</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B121">
-        <v>576.699</v>
+        <v>746.236</v>
       </c>
       <c r="C121">
-        <v>645</v>
+        <v>417</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B122">
-        <v>512.752</v>
+        <v>688.596</v>
       </c>
       <c r="C122">
-        <v>575</v>
+        <v>356</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46150.26041666666</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B123">
-        <v>510.174</v>
+        <v>656.061</v>
       </c>
       <c r="C123">
-        <v>522</v>
+        <v>302</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46150.27083333334</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B124">
-        <v>524.353</v>
+        <v>624.674</v>
       </c>
       <c r="C124">
-        <v>480</v>
+        <v>356</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B125">
-        <v>518.778</v>
+        <v>591.022</v>
       </c>
       <c r="C125">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46150.29166666666</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B126">
-        <v>446.075</v>
+        <v>530.841</v>
       </c>
       <c r="C126">
-        <v>373</v>
+        <v>442</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46150.30208333334</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B127">
-        <v>430.238</v>
+        <v>513.6130000000001</v>
       </c>
       <c r="C127">
-        <v>322</v>
+        <v>429</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B128">
-        <v>409.691</v>
+        <v>469.495</v>
       </c>
       <c r="C128">
-        <v>278</v>
+        <v>440</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46150.32291666666</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B129">
-        <v>396.414</v>
+        <v>460.553</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46150.33333333334</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B130">
-        <v>405.968</v>
+        <v>441.822</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B131">
-        <v>392.106</v>
+        <v>450.078</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46150.35416666666</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B132">
-        <v>384.164</v>
+        <v>432.415</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46150.36458333334</v>
+        <v>46154.36458333334</v>
       </c>
       <c r="B133">
-        <v>375.771</v>
+        <v>409.886</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46150.375</v>
+        <v>46154.375</v>
       </c>
       <c r="B134">
-        <v>379.921</v>
+        <v>468.282</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46150.38541666666</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="B135">
-        <v>379.085</v>
+        <v>462.117</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46150.39583333334</v>
+        <v>46154.39583333334</v>
       </c>
       <c r="B136">
-        <v>378.58</v>
+        <v>457.774</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46150.40625</v>
+        <v>46154.40625</v>
       </c>
       <c r="B137">
-        <v>377.693</v>
+        <v>451.082</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46150.41666666666</v>
+        <v>46154.41666666666</v>
       </c>
       <c r="B138">
-        <v>384.565</v>
+        <v>439.625</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46150.42708333334</v>
+        <v>46154.42708333334</v>
       </c>
       <c r="B139">
-        <v>396.72</v>
+        <v>441.053</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46150.4375</v>
+        <v>46154.4375</v>
       </c>
       <c r="B140">
-        <v>408.144</v>
+        <v>442.328</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46150.44791666666</v>
+        <v>46154.44791666666</v>
       </c>
       <c r="B141">
-        <v>419.41</v>
+        <v>445.59</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46150.45833333334</v>
+        <v>46154.45833333334</v>
       </c>
       <c r="B142">
-        <v>432.76</v>
+        <v>414.994</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46150.46875</v>
+        <v>46154.46875</v>
       </c>
       <c r="B143">
-        <v>441.251</v>
+        <v>425.045</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46150.47916666666</v>
+        <v>46154.47916666666</v>
       </c>
       <c r="B144">
-        <v>450.268</v>
+        <v>434.314</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46150.48958333334</v>
+        <v>46154.48958333334</v>
       </c>
       <c r="B145">
-        <v>459.733</v>
+        <v>442.498</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46150.5</v>
+        <v>46154.5</v>
       </c>
       <c r="B146">
-        <v>478.332</v>
+        <v>458.33</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46150.51041666666</v>
+        <v>46154.51041666666</v>
       </c>
       <c r="B147">
-        <v>485.135</v>
+        <v>469.996</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46150.52083333334</v>
+        <v>46154.52083333334</v>
       </c>
       <c r="B148">
-        <v>491.605</v>
+        <v>483.167</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46150.53125</v>
+        <v>46154.53125</v>
       </c>
       <c r="B149">
-        <v>498.903</v>
+        <v>498.348</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46150.54166666666</v>
+        <v>46154.54166666666</v>
       </c>
       <c r="B150">
-        <v>511.014</v>
+        <v>515.377</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46150.55208333334</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="B151">
-        <v>517.292</v>
+        <v>537.6420000000001</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46150.5625</v>
+        <v>46154.5625</v>
       </c>
       <c r="B152">
-        <v>521.86</v>
+        <v>557.335</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46150.57291666666</v>
+        <v>46154.57291666666</v>
       </c>
       <c r="B153">
-        <v>526.9930000000001</v>
+        <v>574.833</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46150.58333333334</v>
+        <v>46154.58333333334</v>
       </c>
       <c r="B154">
-        <v>524.653</v>
+        <v>651.165</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46150.59375</v>
+        <v>46154.59375</v>
       </c>
       <c r="B155">
-        <v>532.766</v>
+        <v>663.1660000000001</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46150.60416666666</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B156">
-        <v>540.204</v>
+        <v>674.6180000000001</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46150.61458333334</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="B157">
-        <v>549.728</v>
+        <v>685.9690000000001</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46150.625</v>
+        <v>46154.625</v>
       </c>
       <c r="B158">
-        <v>554.545</v>
+        <v>647.934</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46150.63541666666</v>
+        <v>46154.63541666666</v>
       </c>
       <c r="B159">
-        <v>559.178</v>
+        <v>638.01</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46150.64583333334</v>
+        <v>46154.64583333334</v>
       </c>
       <c r="B160">
-        <v>564.417</v>
+        <v>628.692</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46150.65625</v>
+        <v>46154.65625</v>
       </c>
       <c r="B161">
-        <v>568.955</v>
+        <v>617.827</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46150.66666666666</v>
+        <v>46154.66666666666</v>
       </c>
       <c r="B162">
-        <v>509.336</v>
+        <v>594.9640000000001</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46150.67708333334</v>
+        <v>46154.67708333334</v>
       </c>
       <c r="B163">
-        <v>510.897</v>
+        <v>574.833</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46150.6875</v>
+        <v>46154.6875</v>
       </c>
       <c r="B164">
-        <v>513.307</v>
+        <v>556.796</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46150.69791666666</v>
+        <v>46154.69791666666</v>
       </c>
       <c r="B165">
-        <v>516.074</v>
+        <v>540.894</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46150.70833333334</v>
+        <v>46154.70833333334</v>
       </c>
       <c r="B166">
-        <v>515.9299999999999</v>
+        <v>499.05</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46150.71875</v>
+        <v>46154.71875</v>
       </c>
       <c r="B167">
-        <v>514.064</v>
+        <v>494.184</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46150.72916666666</v>
+        <v>46154.72916666666</v>
       </c>
       <c r="B168">
-        <v>512.515</v>
+        <v>490.37</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46150.73958333334</v>
+        <v>46154.73958333334</v>
       </c>
       <c r="B169">
-        <v>511.612</v>
+        <v>484.916</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46150.75</v>
+        <v>46154.75</v>
       </c>
       <c r="B170">
-        <v>502.257</v>
+        <v>496.24</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46150.76041666666</v>
+        <v>46154.76041666666</v>
       </c>
       <c r="B171">
-        <v>508.437</v>
+        <v>506.987</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46150.77083333334</v>
+        <v>46154.77083333334</v>
       </c>
       <c r="B172">
-        <v>516.023</v>
+        <v>521.224</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46150.78125</v>
+        <v>46154.78125</v>
       </c>
       <c r="B173">
-        <v>522.876</v>
+        <v>537.224</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46150.79166666666</v>
+        <v>46154.79166666666</v>
       </c>
       <c r="B174">
-        <v>535.347</v>
+        <v>459.371</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46150.80208333334</v>
+        <v>46154.80208333334</v>
       </c>
       <c r="B175">
-        <v>540.175</v>
+        <v>469.003</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46150.8125</v>
+        <v>46154.8125</v>
       </c>
       <c r="B176">
-        <v>545.4829999999999</v>
+        <v>479.97</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46150.82291666666</v>
+        <v>46154.82291666666</v>
       </c>
       <c r="B177">
-        <v>550.277</v>
+        <v>504.874</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46150.83333333334</v>
+        <v>46154.83333333334</v>
       </c>
       <c r="B178">
-        <v>568.159</v>
+        <v>561.684</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46150.84375</v>
+        <v>46154.84375</v>
       </c>
       <c r="B179">
-        <v>561.001</v>
+        <v>583.133</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46150.85416666666</v>
+        <v>46154.85416666666</v>
       </c>
       <c r="B180">
-        <v>553.962</v>
+        <v>599.796</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46150.86458333334</v>
+        <v>46154.86458333334</v>
       </c>
       <c r="B181">
-        <v>546.873</v>
+        <v>604.559</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46150.875</v>
+        <v>46154.875</v>
       </c>
       <c r="B182">
-        <v>516.223</v>
+        <v>655.6079999999999</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46150.88541666666</v>
+        <v>46154.88541666666</v>
       </c>
       <c r="B183">
-        <v>503.182</v>
+        <v>670.912</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46150.89583333334</v>
+        <v>46154.89583333334</v>
       </c>
       <c r="B184">
-        <v>485.545</v>
+        <v>696.563</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46150.90625</v>
+        <v>46154.90625</v>
       </c>
       <c r="B185">
-        <v>471.292</v>
+        <v>728.0309999999999</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46150.91666666666</v>
+        <v>46154.91666666666</v>
       </c>
       <c r="B186">
-        <v>450.85</v>
+        <v>758.484</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46150.92708333334</v>
+        <v>46154.92708333334</v>
       </c>
       <c r="B187">
-        <v>442.259</v>
+        <v>773.376</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46150.9375</v>
+        <v>46154.9375</v>
       </c>
       <c r="B188">
-        <v>428.21</v>
+        <v>796.628</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46150.94791666666</v>
+        <v>46154.94791666666</v>
       </c>
       <c r="B189">
-        <v>443.51</v>
+        <v>818.764</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46150.95833333334</v>
+        <v>46154.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46150.96875</v>
+        <v>46154.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46150.97916666666</v>
+        <v>46154.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46150.98958333334</v>
+        <v>46154.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.05.20261</t>
-  </si>
-  <si>
-    <t>11.05.20262</t>
-  </si>
-  <si>
-    <t>11.05.20263</t>
-  </si>
-  <si>
-    <t>11.05.20264</t>
-  </si>
-  <si>
-    <t>11.05.20265</t>
-  </si>
-  <si>
-    <t>11.05.20266</t>
-  </si>
-  <si>
-    <t>11.05.20267</t>
-  </si>
-  <si>
-    <t>11.05.20268</t>
-  </si>
-  <si>
-    <t>11.05.20269</t>
-  </si>
-  <si>
-    <t>11.05.202610</t>
-  </si>
-  <si>
-    <t>11.05.202611</t>
-  </si>
-  <si>
-    <t>11.05.202612</t>
-  </si>
-  <si>
-    <t>11.05.202613</t>
-  </si>
-  <si>
-    <t>11.05.202614</t>
-  </si>
-  <si>
-    <t>11.05.202615</t>
-  </si>
-  <si>
-    <t>11.05.202616</t>
-  </si>
-  <si>
-    <t>11.05.202617</t>
-  </si>
-  <si>
-    <t>11.05.202618</t>
-  </si>
-  <si>
-    <t>11.05.202619</t>
-  </si>
-  <si>
-    <t>11.05.202620</t>
-  </si>
-  <si>
-    <t>11.05.202621</t>
-  </si>
-  <si>
-    <t>11.05.202622</t>
-  </si>
-  <si>
-    <t>11.05.202623</t>
-  </si>
-  <si>
-    <t>11.05.202624</t>
-  </si>
-  <si>
-    <t>11.05.202625</t>
-  </si>
-  <si>
-    <t>11.05.202626</t>
-  </si>
-  <si>
-    <t>11.05.202627</t>
-  </si>
-  <si>
-    <t>11.05.202628</t>
-  </si>
-  <si>
-    <t>11.05.202629</t>
-  </si>
-  <si>
-    <t>11.05.202630</t>
-  </si>
-  <si>
-    <t>11.05.202631</t>
-  </si>
-  <si>
-    <t>11.05.202632</t>
-  </si>
-  <si>
-    <t>11.05.202633</t>
-  </si>
-  <si>
-    <t>11.05.202634</t>
-  </si>
-  <si>
-    <t>11.05.202635</t>
-  </si>
-  <si>
-    <t>11.05.202636</t>
-  </si>
-  <si>
-    <t>11.05.202637</t>
-  </si>
-  <si>
-    <t>11.05.202638</t>
-  </si>
-  <si>
-    <t>11.05.202639</t>
-  </si>
-  <si>
-    <t>11.05.202640</t>
-  </si>
-  <si>
-    <t>11.05.202641</t>
-  </si>
-  <si>
-    <t>11.05.202642</t>
-  </si>
-  <si>
-    <t>11.05.202643</t>
-  </si>
-  <si>
-    <t>11.05.202644</t>
-  </si>
-  <si>
-    <t>11.05.202645</t>
-  </si>
-  <si>
-    <t>11.05.202646</t>
-  </si>
-  <si>
-    <t>11.05.202647</t>
-  </si>
-  <si>
-    <t>11.05.202648</t>
-  </si>
-  <si>
-    <t>11.05.202649</t>
-  </si>
-  <si>
-    <t>11.05.202650</t>
-  </si>
-  <si>
-    <t>11.05.202651</t>
-  </si>
-  <si>
-    <t>11.05.202652</t>
-  </si>
-  <si>
-    <t>11.05.202653</t>
-  </si>
-  <si>
-    <t>11.05.202654</t>
-  </si>
-  <si>
-    <t>11.05.202655</t>
-  </si>
-  <si>
-    <t>11.05.202656</t>
-  </si>
-  <si>
-    <t>11.05.202657</t>
-  </si>
-  <si>
-    <t>11.05.202658</t>
-  </si>
-  <si>
-    <t>11.05.202659</t>
-  </si>
-  <si>
-    <t>11.05.202660</t>
-  </si>
-  <si>
-    <t>11.05.202661</t>
-  </si>
-  <si>
-    <t>11.05.202662</t>
-  </si>
-  <si>
-    <t>11.05.202663</t>
-  </si>
-  <si>
-    <t>11.05.202664</t>
-  </si>
-  <si>
-    <t>11.05.202665</t>
-  </si>
-  <si>
-    <t>11.05.202666</t>
-  </si>
-  <si>
-    <t>11.05.202667</t>
-  </si>
-  <si>
-    <t>11.05.202668</t>
-  </si>
-  <si>
-    <t>11.05.202669</t>
-  </si>
-  <si>
-    <t>11.05.202670</t>
-  </si>
-  <si>
-    <t>11.05.202671</t>
-  </si>
-  <si>
-    <t>11.05.202672</t>
-  </si>
-  <si>
-    <t>11.05.202673</t>
-  </si>
-  <si>
-    <t>11.05.202674</t>
-  </si>
-  <si>
-    <t>11.05.202675</t>
-  </si>
-  <si>
-    <t>11.05.202676</t>
-  </si>
-  <si>
-    <t>11.05.202677</t>
-  </si>
-  <si>
-    <t>11.05.202678</t>
-  </si>
-  <si>
-    <t>11.05.202679</t>
-  </si>
-  <si>
-    <t>11.05.202680</t>
-  </si>
-  <si>
-    <t>11.05.202681</t>
-  </si>
-  <si>
-    <t>11.05.202682</t>
-  </si>
-  <si>
-    <t>11.05.202683</t>
-  </si>
-  <si>
-    <t>11.05.202684</t>
-  </si>
-  <si>
-    <t>11.05.202685</t>
-  </si>
-  <si>
-    <t>11.05.202686</t>
-  </si>
-  <si>
-    <t>11.05.202687</t>
-  </si>
-  <si>
-    <t>11.05.202688</t>
-  </si>
-  <si>
-    <t>11.05.202689</t>
-  </si>
-  <si>
-    <t>11.05.202690</t>
-  </si>
-  <si>
-    <t>11.05.202691</t>
-  </si>
-  <si>
-    <t>11.05.202692</t>
-  </si>
-  <si>
-    <t>11.05.202693</t>
-  </si>
-  <si>
-    <t>11.05.202694</t>
-  </si>
-  <si>
-    <t>11.05.202695</t>
-  </si>
-  <si>
-    <t>11.05.202696</t>
-  </si>
-  <si>
-    <t>12.05.20261</t>
-  </si>
-  <si>
-    <t>12.05.20262</t>
-  </si>
-  <si>
-    <t>12.05.20263</t>
-  </si>
-  <si>
-    <t>12.05.20264</t>
-  </si>
-  <si>
-    <t>12.05.20265</t>
-  </si>
-  <si>
-    <t>12.05.20266</t>
-  </si>
-  <si>
-    <t>12.05.20267</t>
-  </si>
-  <si>
-    <t>12.05.20268</t>
-  </si>
-  <si>
-    <t>12.05.20269</t>
-  </si>
-  <si>
-    <t>12.05.202610</t>
-  </si>
-  <si>
-    <t>12.05.202611</t>
-  </si>
-  <si>
-    <t>12.05.202612</t>
-  </si>
-  <si>
-    <t>12.05.202613</t>
-  </si>
-  <si>
-    <t>12.05.202614</t>
-  </si>
-  <si>
-    <t>12.05.202615</t>
-  </si>
-  <si>
-    <t>12.05.202616</t>
-  </si>
-  <si>
-    <t>12.05.202617</t>
-  </si>
-  <si>
-    <t>12.05.202618</t>
-  </si>
-  <si>
-    <t>12.05.202619</t>
-  </si>
-  <si>
-    <t>12.05.202620</t>
-  </si>
-  <si>
-    <t>12.05.202621</t>
-  </si>
-  <si>
-    <t>12.05.202622</t>
-  </si>
-  <si>
-    <t>12.05.202623</t>
-  </si>
-  <si>
-    <t>12.05.202624</t>
-  </si>
-  <si>
-    <t>12.05.202625</t>
-  </si>
-  <si>
-    <t>12.05.202626</t>
-  </si>
-  <si>
-    <t>12.05.202627</t>
-  </si>
-  <si>
-    <t>12.05.202628</t>
-  </si>
-  <si>
-    <t>12.05.202629</t>
-  </si>
-  <si>
-    <t>12.05.202630</t>
-  </si>
-  <si>
-    <t>12.05.202631</t>
-  </si>
-  <si>
-    <t>12.05.202632</t>
-  </si>
-  <si>
-    <t>12.05.202633</t>
-  </si>
-  <si>
-    <t>12.05.202634</t>
-  </si>
-  <si>
-    <t>12.05.202635</t>
-  </si>
-  <si>
-    <t>12.05.202636</t>
-  </si>
-  <si>
-    <t>12.05.202637</t>
-  </si>
-  <si>
-    <t>12.05.202638</t>
-  </si>
-  <si>
-    <t>12.05.202639</t>
-  </si>
-  <si>
-    <t>12.05.202640</t>
-  </si>
-  <si>
-    <t>12.05.202641</t>
-  </si>
-  <si>
-    <t>12.05.202642</t>
-  </si>
-  <si>
-    <t>12.05.202643</t>
-  </si>
-  <si>
-    <t>12.05.202644</t>
-  </si>
-  <si>
-    <t>12.05.202645</t>
-  </si>
-  <si>
-    <t>12.05.202646</t>
-  </si>
-  <si>
-    <t>12.05.202647</t>
-  </si>
-  <si>
-    <t>12.05.202648</t>
-  </si>
-  <si>
-    <t>12.05.202649</t>
-  </si>
-  <si>
-    <t>12.05.202650</t>
-  </si>
-  <si>
-    <t>12.05.202651</t>
-  </si>
-  <si>
-    <t>12.05.202652</t>
-  </si>
-  <si>
-    <t>12.05.202653</t>
-  </si>
-  <si>
-    <t>12.05.202654</t>
-  </si>
-  <si>
-    <t>12.05.202655</t>
-  </si>
-  <si>
-    <t>12.05.202656</t>
-  </si>
-  <si>
-    <t>12.05.202657</t>
-  </si>
-  <si>
-    <t>12.05.202658</t>
-  </si>
-  <si>
-    <t>12.05.202659</t>
-  </si>
-  <si>
-    <t>12.05.202660</t>
-  </si>
-  <si>
-    <t>12.05.202661</t>
-  </si>
-  <si>
-    <t>12.05.202662</t>
-  </si>
-  <si>
-    <t>12.05.202663</t>
-  </si>
-  <si>
-    <t>12.05.202664</t>
-  </si>
-  <si>
-    <t>12.05.202665</t>
-  </si>
-  <si>
-    <t>12.05.202666</t>
-  </si>
-  <si>
-    <t>12.05.202667</t>
-  </si>
-  <si>
-    <t>12.05.202668</t>
-  </si>
-  <si>
-    <t>12.05.202669</t>
-  </si>
-  <si>
-    <t>12.05.202670</t>
-  </si>
-  <si>
-    <t>12.05.202671</t>
-  </si>
-  <si>
-    <t>12.05.202672</t>
-  </si>
-  <si>
-    <t>12.05.202673</t>
-  </si>
-  <si>
-    <t>12.05.202674</t>
-  </si>
-  <si>
-    <t>12.05.202675</t>
-  </si>
-  <si>
-    <t>12.05.202676</t>
-  </si>
-  <si>
-    <t>12.05.202677</t>
-  </si>
-  <si>
-    <t>12.05.202678</t>
-  </si>
-  <si>
-    <t>12.05.202679</t>
-  </si>
-  <si>
-    <t>12.05.202680</t>
-  </si>
-  <si>
-    <t>12.05.202681</t>
-  </si>
-  <si>
-    <t>12.05.202682</t>
-  </si>
-  <si>
-    <t>12.05.202683</t>
-  </si>
-  <si>
-    <t>12.05.202684</t>
-  </si>
-  <si>
-    <t>12.05.202685</t>
-  </si>
-  <si>
-    <t>12.05.202686</t>
-  </si>
-  <si>
-    <t>12.05.202687</t>
-  </si>
-  <si>
-    <t>12.05.202688</t>
-  </si>
-  <si>
-    <t>12.05.202689</t>
-  </si>
-  <si>
-    <t>12.05.202690</t>
-  </si>
-  <si>
-    <t>12.05.202691</t>
-  </si>
-  <si>
-    <t>12.05.202692</t>
-  </si>
-  <si>
-    <t>12.05.202693</t>
-  </si>
-  <si>
-    <t>12.05.202694</t>
-  </si>
-  <si>
-    <t>12.05.202695</t>
-  </si>
-  <si>
-    <t>12.05.202696</t>
+    <t>13.05.20261</t>
+  </si>
+  <si>
+    <t>13.05.20262</t>
+  </si>
+  <si>
+    <t>13.05.20263</t>
+  </si>
+  <si>
+    <t>13.05.20264</t>
+  </si>
+  <si>
+    <t>13.05.20265</t>
+  </si>
+  <si>
+    <t>13.05.20266</t>
+  </si>
+  <si>
+    <t>13.05.20267</t>
+  </si>
+  <si>
+    <t>13.05.20268</t>
+  </si>
+  <si>
+    <t>13.05.20269</t>
+  </si>
+  <si>
+    <t>13.05.202610</t>
+  </si>
+  <si>
+    <t>13.05.202611</t>
+  </si>
+  <si>
+    <t>13.05.202612</t>
+  </si>
+  <si>
+    <t>13.05.202613</t>
+  </si>
+  <si>
+    <t>13.05.202614</t>
+  </si>
+  <si>
+    <t>13.05.202615</t>
+  </si>
+  <si>
+    <t>13.05.202616</t>
+  </si>
+  <si>
+    <t>13.05.202617</t>
+  </si>
+  <si>
+    <t>13.05.202618</t>
+  </si>
+  <si>
+    <t>13.05.202619</t>
+  </si>
+  <si>
+    <t>13.05.202620</t>
+  </si>
+  <si>
+    <t>13.05.202621</t>
+  </si>
+  <si>
+    <t>13.05.202622</t>
+  </si>
+  <si>
+    <t>13.05.202623</t>
+  </si>
+  <si>
+    <t>13.05.202624</t>
+  </si>
+  <si>
+    <t>13.05.202625</t>
+  </si>
+  <si>
+    <t>13.05.202626</t>
+  </si>
+  <si>
+    <t>13.05.202627</t>
+  </si>
+  <si>
+    <t>13.05.202628</t>
+  </si>
+  <si>
+    <t>13.05.202629</t>
+  </si>
+  <si>
+    <t>13.05.202630</t>
+  </si>
+  <si>
+    <t>13.05.202631</t>
+  </si>
+  <si>
+    <t>13.05.202632</t>
+  </si>
+  <si>
+    <t>13.05.202633</t>
+  </si>
+  <si>
+    <t>13.05.202634</t>
+  </si>
+  <si>
+    <t>13.05.202635</t>
+  </si>
+  <si>
+    <t>13.05.202636</t>
+  </si>
+  <si>
+    <t>13.05.202637</t>
+  </si>
+  <si>
+    <t>13.05.202638</t>
+  </si>
+  <si>
+    <t>13.05.202639</t>
+  </si>
+  <si>
+    <t>13.05.202640</t>
+  </si>
+  <si>
+    <t>13.05.202641</t>
+  </si>
+  <si>
+    <t>13.05.202642</t>
+  </si>
+  <si>
+    <t>13.05.202643</t>
+  </si>
+  <si>
+    <t>13.05.202644</t>
+  </si>
+  <si>
+    <t>13.05.202645</t>
+  </si>
+  <si>
+    <t>13.05.202646</t>
+  </si>
+  <si>
+    <t>13.05.202647</t>
+  </si>
+  <si>
+    <t>13.05.202648</t>
+  </si>
+  <si>
+    <t>13.05.202649</t>
+  </si>
+  <si>
+    <t>13.05.202650</t>
+  </si>
+  <si>
+    <t>13.05.202651</t>
+  </si>
+  <si>
+    <t>13.05.202652</t>
+  </si>
+  <si>
+    <t>13.05.202653</t>
+  </si>
+  <si>
+    <t>13.05.202654</t>
+  </si>
+  <si>
+    <t>13.05.202655</t>
+  </si>
+  <si>
+    <t>13.05.202656</t>
+  </si>
+  <si>
+    <t>13.05.202657</t>
+  </si>
+  <si>
+    <t>13.05.202658</t>
+  </si>
+  <si>
+    <t>13.05.202659</t>
+  </si>
+  <si>
+    <t>13.05.202660</t>
+  </si>
+  <si>
+    <t>13.05.202661</t>
+  </si>
+  <si>
+    <t>13.05.202662</t>
+  </si>
+  <si>
+    <t>13.05.202663</t>
+  </si>
+  <si>
+    <t>13.05.202664</t>
+  </si>
+  <si>
+    <t>13.05.202665</t>
+  </si>
+  <si>
+    <t>13.05.202666</t>
+  </si>
+  <si>
+    <t>13.05.202667</t>
+  </si>
+  <si>
+    <t>13.05.202668</t>
+  </si>
+  <si>
+    <t>13.05.202669</t>
+  </si>
+  <si>
+    <t>13.05.202670</t>
+  </si>
+  <si>
+    <t>13.05.202671</t>
+  </si>
+  <si>
+    <t>13.05.202672</t>
+  </si>
+  <si>
+    <t>13.05.202673</t>
+  </si>
+  <si>
+    <t>13.05.202674</t>
+  </si>
+  <si>
+    <t>13.05.202675</t>
+  </si>
+  <si>
+    <t>13.05.202676</t>
+  </si>
+  <si>
+    <t>13.05.202677</t>
+  </si>
+  <si>
+    <t>13.05.202678</t>
+  </si>
+  <si>
+    <t>13.05.202679</t>
+  </si>
+  <si>
+    <t>13.05.202680</t>
+  </si>
+  <si>
+    <t>13.05.202681</t>
+  </si>
+  <si>
+    <t>13.05.202682</t>
+  </si>
+  <si>
+    <t>13.05.202683</t>
+  </si>
+  <si>
+    <t>13.05.202684</t>
+  </si>
+  <si>
+    <t>13.05.202685</t>
+  </si>
+  <si>
+    <t>13.05.202686</t>
+  </si>
+  <si>
+    <t>13.05.202687</t>
+  </si>
+  <si>
+    <t>13.05.202688</t>
+  </si>
+  <si>
+    <t>13.05.202689</t>
+  </si>
+  <si>
+    <t>13.05.202690</t>
+  </si>
+  <si>
+    <t>13.05.202691</t>
+  </si>
+  <si>
+    <t>13.05.202692</t>
+  </si>
+  <si>
+    <t>13.05.202693</t>
+  </si>
+  <si>
+    <t>13.05.202694</t>
+  </si>
+  <si>
+    <t>13.05.202695</t>
+  </si>
+  <si>
+    <t>13.05.202696</t>
+  </si>
+  <si>
+    <t>14.05.20261</t>
+  </si>
+  <si>
+    <t>14.05.20262</t>
+  </si>
+  <si>
+    <t>14.05.20263</t>
+  </si>
+  <si>
+    <t>14.05.20264</t>
+  </si>
+  <si>
+    <t>14.05.20265</t>
+  </si>
+  <si>
+    <t>14.05.20266</t>
+  </si>
+  <si>
+    <t>14.05.20267</t>
+  </si>
+  <si>
+    <t>14.05.20268</t>
+  </si>
+  <si>
+    <t>14.05.20269</t>
+  </si>
+  <si>
+    <t>14.05.202610</t>
+  </si>
+  <si>
+    <t>14.05.202611</t>
+  </si>
+  <si>
+    <t>14.05.202612</t>
+  </si>
+  <si>
+    <t>14.05.202613</t>
+  </si>
+  <si>
+    <t>14.05.202614</t>
+  </si>
+  <si>
+    <t>14.05.202615</t>
+  </si>
+  <si>
+    <t>14.05.202616</t>
+  </si>
+  <si>
+    <t>14.05.202617</t>
+  </si>
+  <si>
+    <t>14.05.202618</t>
+  </si>
+  <si>
+    <t>14.05.202619</t>
+  </si>
+  <si>
+    <t>14.05.202620</t>
+  </si>
+  <si>
+    <t>14.05.202621</t>
+  </si>
+  <si>
+    <t>14.05.202622</t>
+  </si>
+  <si>
+    <t>14.05.202623</t>
+  </si>
+  <si>
+    <t>14.05.202624</t>
+  </si>
+  <si>
+    <t>14.05.202625</t>
+  </si>
+  <si>
+    <t>14.05.202626</t>
+  </si>
+  <si>
+    <t>14.05.202627</t>
+  </si>
+  <si>
+    <t>14.05.202628</t>
+  </si>
+  <si>
+    <t>14.05.202629</t>
+  </si>
+  <si>
+    <t>14.05.202630</t>
+  </si>
+  <si>
+    <t>14.05.202631</t>
+  </si>
+  <si>
+    <t>14.05.202632</t>
+  </si>
+  <si>
+    <t>14.05.202633</t>
+  </si>
+  <si>
+    <t>14.05.202634</t>
+  </si>
+  <si>
+    <t>14.05.202635</t>
+  </si>
+  <si>
+    <t>14.05.202636</t>
+  </si>
+  <si>
+    <t>14.05.202637</t>
+  </si>
+  <si>
+    <t>14.05.202638</t>
+  </si>
+  <si>
+    <t>14.05.202639</t>
+  </si>
+  <si>
+    <t>14.05.202640</t>
+  </si>
+  <si>
+    <t>14.05.202641</t>
+  </si>
+  <si>
+    <t>14.05.202642</t>
+  </si>
+  <si>
+    <t>14.05.202643</t>
+  </si>
+  <si>
+    <t>14.05.202644</t>
+  </si>
+  <si>
+    <t>14.05.202645</t>
+  </si>
+  <si>
+    <t>14.05.202646</t>
+  </si>
+  <si>
+    <t>14.05.202647</t>
+  </si>
+  <si>
+    <t>14.05.202648</t>
+  </si>
+  <si>
+    <t>14.05.202649</t>
+  </si>
+  <si>
+    <t>14.05.202650</t>
+  </si>
+  <si>
+    <t>14.05.202651</t>
+  </si>
+  <si>
+    <t>14.05.202652</t>
+  </si>
+  <si>
+    <t>14.05.202653</t>
+  </si>
+  <si>
+    <t>14.05.202654</t>
+  </si>
+  <si>
+    <t>14.05.202655</t>
+  </si>
+  <si>
+    <t>14.05.202656</t>
+  </si>
+  <si>
+    <t>14.05.202657</t>
+  </si>
+  <si>
+    <t>14.05.202658</t>
+  </si>
+  <si>
+    <t>14.05.202659</t>
+  </si>
+  <si>
+    <t>14.05.202660</t>
+  </si>
+  <si>
+    <t>14.05.202661</t>
+  </si>
+  <si>
+    <t>14.05.202662</t>
+  </si>
+  <si>
+    <t>14.05.202663</t>
+  </si>
+  <si>
+    <t>14.05.202664</t>
+  </si>
+  <si>
+    <t>14.05.202665</t>
+  </si>
+  <si>
+    <t>14.05.202666</t>
+  </si>
+  <si>
+    <t>14.05.202667</t>
+  </si>
+  <si>
+    <t>14.05.202668</t>
+  </si>
+  <si>
+    <t>14.05.202669</t>
+  </si>
+  <si>
+    <t>14.05.202670</t>
+  </si>
+  <si>
+    <t>14.05.202671</t>
+  </si>
+  <si>
+    <t>14.05.202672</t>
+  </si>
+  <si>
+    <t>14.05.202673</t>
+  </si>
+  <si>
+    <t>14.05.202674</t>
+  </si>
+  <si>
+    <t>14.05.202675</t>
+  </si>
+  <si>
+    <t>14.05.202676</t>
+  </si>
+  <si>
+    <t>14.05.202677</t>
+  </si>
+  <si>
+    <t>14.05.202678</t>
+  </si>
+  <si>
+    <t>14.05.202679</t>
+  </si>
+  <si>
+    <t>14.05.202680</t>
+  </si>
+  <si>
+    <t>14.05.202681</t>
+  </si>
+  <si>
+    <t>14.05.202682</t>
+  </si>
+  <si>
+    <t>14.05.202683</t>
+  </si>
+  <si>
+    <t>14.05.202684</t>
+  </si>
+  <si>
+    <t>14.05.202685</t>
+  </si>
+  <si>
+    <t>14.05.202686</t>
+  </si>
+  <si>
+    <t>14.05.202687</t>
+  </si>
+  <si>
+    <t>14.05.202688</t>
+  </si>
+  <si>
+    <t>14.05.202689</t>
+  </si>
+  <si>
+    <t>14.05.202690</t>
+  </si>
+  <si>
+    <t>14.05.202691</t>
+  </si>
+  <si>
+    <t>14.05.202692</t>
+  </si>
+  <si>
+    <t>14.05.202693</t>
+  </si>
+  <si>
+    <t>14.05.202694</t>
+  </si>
+  <si>
+    <t>14.05.202695</t>
+  </si>
+  <si>
+    <t>14.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
-        <v>130.332</v>
+        <v>1514.13</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>1560</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
-        <v>130.352</v>
+        <v>1515.061</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>1572</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
-        <v>130.671</v>
+        <v>1524.795</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>1548</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
-        <v>130.81</v>
+        <v>1587.942</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1489</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>129.903</v>
+        <v>1534.096</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>1445</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>128.473</v>
+        <v>1554.276</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>1410</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>127.035</v>
+        <v>1567.674</v>
       </c>
       <c r="C8">
-        <v>18</v>
+        <v>1413</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>125.456</v>
+        <v>1577.159</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>1380</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>112.252</v>
+        <v>1534.106</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1345</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>112.257</v>
+        <v>1534.661</v>
       </c>
       <c r="C11">
-        <v>21</v>
+        <v>1334</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>112.884</v>
+        <v>1516.831</v>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>1347</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>113.472</v>
+        <v>1496.469</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>1361</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>116.366</v>
+        <v>1492.012</v>
       </c>
       <c r="C14">
-        <v>24</v>
+        <v>1388</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>119.211</v>
+        <v>1498.614</v>
       </c>
       <c r="C15">
-        <v>29</v>
+        <v>1474</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>122.09</v>
+        <v>1518.435</v>
       </c>
       <c r="C16">
-        <v>38</v>
+        <v>1509</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>125.275</v>
+        <v>1489.71</v>
       </c>
       <c r="C17">
-        <v>42</v>
+        <v>1470</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>128.958</v>
+        <v>1458.967</v>
       </c>
       <c r="C18">
-        <v>51</v>
+        <v>1450</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>135.368</v>
+        <v>1471.633</v>
       </c>
       <c r="C19">
-        <v>65</v>
+        <v>1422</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>139.99</v>
+        <v>1496.239</v>
       </c>
       <c r="C20">
-        <v>77</v>
+        <v>1405</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>146.63</v>
+        <v>1499.005</v>
       </c>
       <c r="C21">
-        <v>85</v>
+        <v>1446</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>161.679</v>
+        <v>1510.375</v>
       </c>
       <c r="C22">
-        <v>107</v>
+        <v>1437</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>172.446</v>
+        <v>1539.779</v>
       </c>
       <c r="C23">
-        <v>128</v>
+        <v>1452</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>184.133</v>
+        <v>1567.268</v>
       </c>
       <c r="C24">
-        <v>157</v>
+        <v>1459</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>195.863</v>
+        <v>1585.051</v>
       </c>
       <c r="C25">
-        <v>173</v>
+        <v>1495</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>184.073</v>
+        <v>1554.619</v>
       </c>
       <c r="C26">
-        <v>177</v>
+        <v>1524</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>194.949</v>
+        <v>1573.037</v>
       </c>
       <c r="C27">
-        <v>197</v>
+        <v>1569</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>207.406</v>
+        <v>1606.125</v>
       </c>
       <c r="C28">
-        <v>195</v>
+        <v>1597</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>217.963</v>
+        <v>1634.351</v>
       </c>
       <c r="C29">
-        <v>180</v>
+        <v>1668</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>223.207</v>
+        <v>1677.919</v>
       </c>
       <c r="C30">
-        <v>164</v>
+        <v>1689</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>226.249</v>
+        <v>1695.033</v>
       </c>
       <c r="C31">
-        <v>146</v>
+        <v>1761</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>228.391</v>
+        <v>1713.155</v>
       </c>
       <c r="C32">
-        <v>138</v>
+        <v>1825</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>228.891</v>
+        <v>1727.28</v>
       </c>
       <c r="C33">
-        <v>132</v>
+        <v>1822</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>241.616</v>
+        <v>1754.489</v>
       </c>
       <c r="C34">
-        <v>144</v>
+        <v>1820</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>247.111</v>
+        <v>1751.634</v>
       </c>
       <c r="C35">
-        <v>169</v>
+        <v>1788</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>260.222</v>
+        <v>1768.254</v>
       </c>
       <c r="C36">
-        <v>201</v>
+        <v>1799</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>267.281</v>
+        <v>1772.681</v>
       </c>
       <c r="C37">
-        <v>224</v>
+        <v>1873</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>340.494</v>
+        <v>1755.138</v>
       </c>
       <c r="C38">
-        <v>251</v>
+        <v>2022</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>365.54</v>
+        <v>1766.358</v>
       </c>
       <c r="C39">
-        <v>274</v>
+        <v>2075</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>389.794</v>
+        <v>1781.007</v>
       </c>
       <c r="C40">
-        <v>284</v>
+        <v>2097</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>413.845</v>
+        <v>1795.969</v>
       </c>
       <c r="C41">
-        <v>297</v>
+        <v>2066</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>424.131</v>
+        <v>1825.392</v>
       </c>
       <c r="C42">
-        <v>322</v>
+        <v>2102</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>454.116</v>
+        <v>1847.688</v>
       </c>
       <c r="C43">
-        <v>350</v>
+        <v>2104</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>483.236</v>
+        <v>1867.773</v>
       </c>
       <c r="C44">
-        <v>376</v>
+        <v>2188</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>512.643</v>
+        <v>1887.089</v>
       </c>
       <c r="C45">
-        <v>415</v>
+        <v>2189</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>540.408</v>
+        <v>1992.724</v>
       </c>
       <c r="C46">
-        <v>449</v>
+        <v>2227</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>570.808</v>
+        <v>1992.904</v>
       </c>
       <c r="C47">
-        <v>490</v>
+        <v>2312</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>600.515</v>
+        <v>1991.211</v>
       </c>
       <c r="C48">
-        <v>508</v>
+        <v>2338</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>630.097</v>
+        <v>1988.345</v>
       </c>
       <c r="C49">
-        <v>529</v>
+        <v>2345</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>698.88</v>
+        <v>1983.107</v>
       </c>
       <c r="C50">
-        <v>559</v>
+        <v>2361</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>737.718</v>
+        <v>1976.124</v>
       </c>
       <c r="C51">
-        <v>599</v>
+        <v>2393</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>777.216</v>
+        <v>1967.59</v>
       </c>
       <c r="C52">
-        <v>648</v>
+        <v>2388</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>818.133</v>
+        <v>1961.448</v>
       </c>
       <c r="C53">
-        <v>718</v>
+        <v>2313</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>883.697</v>
+        <v>1944.922</v>
       </c>
       <c r="C54">
-        <v>775</v>
+        <v>2257</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>929.708</v>
+        <v>1940.154</v>
       </c>
       <c r="C55">
-        <v>835</v>
+        <v>2266</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>974.356</v>
+        <v>1936.239</v>
       </c>
       <c r="C56">
-        <v>905</v>
+        <v>2293</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>1019.87</v>
+        <v>1930.641</v>
       </c>
       <c r="C57">
-        <v>985</v>
+        <v>2270</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>1098.039</v>
+        <v>1792.393</v>
       </c>
       <c r="C58">
-        <v>1055</v>
+        <v>2165</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>1138.043</v>
+        <v>1792.031</v>
       </c>
       <c r="C59">
-        <v>1121</v>
+        <v>2129</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>1177.11</v>
+        <v>1792.058</v>
       </c>
       <c r="C60">
-        <v>1171</v>
+        <v>2151</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>1218.53</v>
+        <v>1790.385</v>
       </c>
       <c r="C61">
-        <v>1233</v>
+        <v>2149</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>1298.2</v>
+        <v>1748.898</v>
       </c>
       <c r="C62">
-        <v>1383</v>
+        <v>2215</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>1327.065</v>
+        <v>1731.857</v>
       </c>
       <c r="C63">
-        <v>1476</v>
+        <v>2225</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>1356.838</v>
+        <v>1714.094</v>
       </c>
       <c r="C64">
-        <v>1555</v>
+        <v>2159</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>1383.577</v>
+        <v>1694.718</v>
       </c>
       <c r="C65">
-        <v>1591</v>
+        <v>2127</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>1387.656</v>
+        <v>1660.219</v>
       </c>
       <c r="C66">
-        <v>1668</v>
+        <v>2043</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>1387.816</v>
+        <v>1630.865</v>
       </c>
       <c r="C67">
-        <v>1707</v>
+        <v>1947</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>1388.871</v>
+        <v>1596.048</v>
       </c>
       <c r="C68">
-        <v>1696</v>
+        <v>1864</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>1389.424</v>
+        <v>1564.751</v>
       </c>
       <c r="C69">
-        <v>1649</v>
+        <v>1759</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>1446.241</v>
+        <v>1512.377</v>
       </c>
       <c r="C70">
-        <v>1626</v>
+        <v>1666</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>1444.349</v>
+        <v>1458.714</v>
       </c>
       <c r="C71">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>1441.196</v>
+        <v>1406.566</v>
       </c>
       <c r="C72">
-        <v>1678</v>
+        <v>1642</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>1440.542</v>
+        <v>1350.205</v>
       </c>
       <c r="C73">
-        <v>1667</v>
+        <v>1516</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>1452.502</v>
+        <v>1145.099</v>
       </c>
       <c r="C74">
-        <v>1754</v>
+        <v>1414</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>1469.295</v>
+        <v>1079.028</v>
       </c>
       <c r="C75">
-        <v>1718</v>
+        <v>1356</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>1484.072</v>
+        <v>1014.477</v>
       </c>
       <c r="C76">
-        <v>1728</v>
+        <v>1322</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>1502.072</v>
+        <v>947.792</v>
       </c>
       <c r="C77">
-        <v>1780</v>
+        <v>1267</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>1537.951</v>
+        <v>851.813</v>
       </c>
       <c r="C78">
-        <v>1786</v>
+        <v>1225</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>1566.247</v>
+        <v>824.486</v>
       </c>
       <c r="C79">
-        <v>1840</v>
+        <v>1173</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>1590.751</v>
+        <v>796.572</v>
       </c>
       <c r="C80">
-        <v>1880</v>
+        <v>1201</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>1614.623</v>
+        <v>771.203</v>
       </c>
       <c r="C81">
-        <v>1937</v>
+        <v>1170</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>1693.584</v>
+        <v>748.548</v>
       </c>
       <c r="C82">
-        <v>1924</v>
+        <v>1142</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>1711.131</v>
+        <v>744.351</v>
       </c>
       <c r="C83">
-        <v>1939</v>
+        <v>1197</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>1729.709</v>
+        <v>737.604</v>
       </c>
       <c r="C84">
-        <v>1953</v>
+        <v>1229</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>1748.139</v>
+        <v>730.006</v>
       </c>
       <c r="C85">
-        <v>1991</v>
+        <v>1247</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>1765.897</v>
+        <v>721.509</v>
       </c>
       <c r="C86">
-        <v>2020</v>
+        <v>1216</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>1767.159</v>
+        <v>719.472</v>
       </c>
       <c r="C87">
-        <v>2050</v>
+        <v>1181</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>1769.011</v>
+        <v>716.616</v>
       </c>
       <c r="C88">
-        <v>2107</v>
+        <v>1131</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>1769.947</v>
+        <v>715.165</v>
       </c>
       <c r="C89">
-        <v>2103</v>
+        <v>1047</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>1777.055</v>
+        <v>714.871</v>
       </c>
       <c r="C90">
-        <v>2091</v>
+        <v>983</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>1778.638</v>
+        <v>711.456</v>
       </c>
       <c r="C91">
-        <v>2050</v>
+        <v>999</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
-        <v>1780.721</v>
+        <v>710.492</v>
       </c>
       <c r="C92">
-        <v>2042</v>
+        <v>1039</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
-        <v>1783.516</v>
+        <v>708.744</v>
       </c>
       <c r="C93">
-        <v>2003</v>
+        <v>1044</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
-        <v>1843.986</v>
+        <v>841.873</v>
       </c>
       <c r="C94">
-        <v>2043</v>
+        <v>1040</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
-        <v>1832.334</v>
+        <v>817.362</v>
       </c>
       <c r="C95">
-        <v>2030</v>
+        <v>996</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
-        <v>1819.501</v>
+        <v>810.7140000000001</v>
       </c>
       <c r="C96">
-        <v>2021</v>
+        <v>932</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
-        <v>1810.982</v>
+        <v>803.0309999999999</v>
       </c>
       <c r="C97">
-        <v>2003</v>
+        <v>895</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
-        <v>1771.932</v>
+        <v>850.961</v>
       </c>
       <c r="C98">
-        <v>1958</v>
+        <v>846</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
-        <v>1751.182</v>
+        <v>851.946</v>
       </c>
       <c r="C99">
-        <v>1919</v>
+        <v>836</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
-        <v>1714.042</v>
+        <v>842.08</v>
       </c>
       <c r="C100">
-        <v>1885</v>
+        <v>876</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
-        <v>1688.671</v>
+        <v>831.447</v>
       </c>
       <c r="C101">
-        <v>1863</v>
+        <v>881</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
-        <v>1622.899</v>
+        <v>821.532</v>
       </c>
       <c r="C102">
-        <v>1828</v>
+        <v>863</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
-        <v>1584.565</v>
+        <v>811.2809999999999</v>
       </c>
       <c r="C103">
-        <v>1804</v>
+        <v>825</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
-        <v>1543.412</v>
+        <v>793.987</v>
       </c>
       <c r="C104">
-        <v>1759</v>
+        <v>817</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
-        <v>1513.14</v>
+        <v>789.751</v>
       </c>
       <c r="C105">
-        <v>1711</v>
+        <v>841</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
-        <v>1444.737</v>
+        <v>801.353</v>
       </c>
       <c r="C106">
-        <v>1652</v>
+        <v>853</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
-        <v>1408.098</v>
+        <v>792.157</v>
       </c>
       <c r="C107">
-        <v>1604</v>
+        <v>857</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
-        <v>1373.897</v>
+        <v>779.986</v>
       </c>
       <c r="C108">
-        <v>1502</v>
+        <v>847</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
-        <v>1341.622</v>
+        <v>779.905</v>
       </c>
       <c r="C109">
-        <v>1442</v>
+        <v>840</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
-        <v>1266.748</v>
+        <v>743.831</v>
       </c>
       <c r="C110">
-        <v>1307</v>
+        <v>848</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
-        <v>1229.519</v>
+        <v>744.289</v>
       </c>
       <c r="C111">
-        <v>1239</v>
+        <v>842</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
-        <v>1186.962</v>
+        <v>746.659</v>
       </c>
       <c r="C112">
-        <v>1153</v>
+        <v>829</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
-        <v>1142.421</v>
+        <v>750.821</v>
       </c>
       <c r="C113">
-        <v>1050</v>
+        <v>827</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
-        <v>1122.598</v>
+        <v>766.516</v>
       </c>
       <c r="C114">
-        <v>910</v>
+        <v>803</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
-        <v>1073.779</v>
+        <v>748.886</v>
       </c>
       <c r="C115">
-        <v>814</v>
+        <v>787</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
-        <v>1018.752</v>
+        <v>737.21</v>
       </c>
       <c r="C116">
-        <v>750</v>
+        <v>776</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
-        <v>965.311</v>
+        <v>717.085</v>
       </c>
       <c r="C117">
-        <v>699</v>
+        <v>785</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>870.058</v>
+        <v>682.6559999999999</v>
       </c>
       <c r="C118">
-        <v>636</v>
+        <v>787</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>813.076</v>
+        <v>659.782</v>
       </c>
       <c r="C119">
-        <v>528</v>
+        <v>778</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
-        <v>781.1130000000001</v>
+        <v>638.905</v>
       </c>
       <c r="C120">
-        <v>469</v>
+        <v>749</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>746.236</v>
+        <v>623.833</v>
       </c>
       <c r="C121">
-        <v>417</v>
+        <v>705</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>688.596</v>
+        <v>593.729</v>
       </c>
       <c r="C122">
-        <v>356</v>
+        <v>660</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>656.061</v>
+        <v>566.782</v>
       </c>
       <c r="C123">
-        <v>302</v>
+        <v>638</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>624.674</v>
+        <v>545.8680000000001</v>
       </c>
       <c r="C124">
-        <v>356</v>
+        <v>603</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>591.022</v>
+        <v>526.865</v>
       </c>
       <c r="C125">
-        <v>415</v>
+        <v>561</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>530.841</v>
+        <v>485.906</v>
       </c>
       <c r="C126">
-        <v>442</v>
+        <v>522</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>513.6130000000001</v>
+        <v>471.932</v>
       </c>
       <c r="C127">
-        <v>429</v>
+        <v>496</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>469.495</v>
+        <v>441.799</v>
       </c>
       <c r="C128">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>460.553</v>
+        <v>421.953</v>
       </c>
       <c r="C129">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>441.822</v>
+        <v>431.464</v>
       </c>
       <c r="C130">
-        <v>323</v>
+        <v>447</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>450.078</v>
+        <v>418.926</v>
       </c>
       <c r="C131">
-        <v>273</v>
+        <v>420</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>432.415</v>
+        <v>407.484</v>
       </c>
       <c r="C132">
-        <v>245</v>
+        <v>401</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>409.886</v>
+        <v>397.45</v>
       </c>
       <c r="C133">
-        <v>221</v>
+        <v>376</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>468.282</v>
+        <v>393.706</v>
       </c>
       <c r="C134">
-        <v>209</v>
+        <v>357</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>462.117</v>
+        <v>384.827</v>
       </c>
       <c r="C135">
-        <v>176</v>
+        <v>339</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>457.774</v>
+        <v>375.519</v>
       </c>
       <c r="C136">
-        <v>172</v>
+        <v>330</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>451.082</v>
+        <v>366.706</v>
       </c>
       <c r="C137">
-        <v>163</v>
+        <v>310</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>439.625</v>
+        <v>321.559</v>
       </c>
       <c r="C138">
-        <v>172</v>
+        <v>312</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>441.053</v>
+        <v>314.462</v>
       </c>
       <c r="C139">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
-        <v>442.328</v>
+        <v>308.366</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
-        <v>445.59</v>
+        <v>302.297</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
-        <v>414.994</v>
+        <v>292.48</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
-        <v>425.045</v>
+        <v>290.736</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
-        <v>434.314</v>
+        <v>287.638</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
-        <v>442.498</v>
+        <v>285.027</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
-        <v>458.33</v>
+        <v>281.955</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
-        <v>469.996</v>
+        <v>283.506</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
-        <v>483.167</v>
+        <v>281.405</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
-        <v>498.348</v>
+        <v>279.851</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
-        <v>515.377</v>
+        <v>280.353</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
-        <v>537.6420000000001</v>
+        <v>281.242</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
-        <v>557.335</v>
+        <v>282.407</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
-        <v>574.833</v>
+        <v>283.453</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
-        <v>651.165</v>
+        <v>297.324</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
-        <v>663.1660000000001</v>
+        <v>298.037</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
-        <v>674.6180000000001</v>
+        <v>300.221</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
-        <v>685.9690000000001</v>
+        <v>301.145</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
-        <v>647.934</v>
+        <v>286.167</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
-        <v>638.01</v>
+        <v>284.396</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
-        <v>628.692</v>
+        <v>281.992</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
-        <v>617.827</v>
+        <v>279.394</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
-        <v>594.9640000000001</v>
+        <v>270.462</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
-        <v>574.833</v>
+        <v>260.252</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
-        <v>556.796</v>
+        <v>250.38</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
-        <v>540.894</v>
+        <v>241.314</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
-        <v>499.05</v>
+        <v>229.08</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
-        <v>494.184</v>
+        <v>219.544</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
-        <v>490.37</v>
+        <v>208.15</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
-        <v>484.916</v>
+        <v>198.242</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
-        <v>496.24</v>
+        <v>161.252</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
-        <v>506.987</v>
+        <v>159.013</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
-        <v>521.224</v>
+        <v>157.204</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
-        <v>537.224</v>
+        <v>156.221</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
-        <v>459.371</v>
+        <v>158.86</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
-        <v>469.003</v>
+        <v>163.381</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
-        <v>479.97</v>
+        <v>168.92</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
-        <v>504.874</v>
+        <v>192.402</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
-        <v>561.684</v>
+        <v>180.375</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
-        <v>583.133</v>
+        <v>202.573</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
-        <v>599.796</v>
+        <v>206.589</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
-        <v>604.559</v>
+        <v>211.398</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
-        <v>655.6079999999999</v>
+        <v>217.831</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
-        <v>670.912</v>
+        <v>223.268</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
-        <v>696.563</v>
+        <v>227.715</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
-        <v>728.0309999999999</v>
+        <v>232.507</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
-        <v>758.484</v>
+        <v>207.682</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
-        <v>773.376</v>
+        <v>211.453</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
-        <v>796.628</v>
+        <v>215.4</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
-        <v>818.764</v>
+        <v>219.97</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.05.20261</t>
-  </si>
-  <si>
-    <t>13.05.20262</t>
-  </si>
-  <si>
-    <t>13.05.20263</t>
-  </si>
-  <si>
-    <t>13.05.20264</t>
-  </si>
-  <si>
-    <t>13.05.20265</t>
-  </si>
-  <si>
-    <t>13.05.20266</t>
-  </si>
-  <si>
-    <t>13.05.20267</t>
-  </si>
-  <si>
-    <t>13.05.20268</t>
-  </si>
-  <si>
-    <t>13.05.20269</t>
-  </si>
-  <si>
-    <t>13.05.202610</t>
-  </si>
-  <si>
-    <t>13.05.202611</t>
-  </si>
-  <si>
-    <t>13.05.202612</t>
-  </si>
-  <si>
-    <t>13.05.202613</t>
-  </si>
-  <si>
-    <t>13.05.202614</t>
-  </si>
-  <si>
-    <t>13.05.202615</t>
-  </si>
-  <si>
-    <t>13.05.202616</t>
-  </si>
-  <si>
-    <t>13.05.202617</t>
-  </si>
-  <si>
-    <t>13.05.202618</t>
-  </si>
-  <si>
-    <t>13.05.202619</t>
-  </si>
-  <si>
-    <t>13.05.202620</t>
-  </si>
-  <si>
-    <t>13.05.202621</t>
-  </si>
-  <si>
-    <t>13.05.202622</t>
-  </si>
-  <si>
-    <t>13.05.202623</t>
-  </si>
-  <si>
-    <t>13.05.202624</t>
-  </si>
-  <si>
-    <t>13.05.202625</t>
-  </si>
-  <si>
-    <t>13.05.202626</t>
-  </si>
-  <si>
-    <t>13.05.202627</t>
-  </si>
-  <si>
-    <t>13.05.202628</t>
-  </si>
-  <si>
-    <t>13.05.202629</t>
-  </si>
-  <si>
-    <t>13.05.202630</t>
-  </si>
-  <si>
-    <t>13.05.202631</t>
-  </si>
-  <si>
-    <t>13.05.202632</t>
-  </si>
-  <si>
-    <t>13.05.202633</t>
-  </si>
-  <si>
-    <t>13.05.202634</t>
-  </si>
-  <si>
-    <t>13.05.202635</t>
-  </si>
-  <si>
-    <t>13.05.202636</t>
-  </si>
-  <si>
-    <t>13.05.202637</t>
-  </si>
-  <si>
-    <t>13.05.202638</t>
-  </si>
-  <si>
-    <t>13.05.202639</t>
-  </si>
-  <si>
-    <t>13.05.202640</t>
-  </si>
-  <si>
-    <t>13.05.202641</t>
-  </si>
-  <si>
-    <t>13.05.202642</t>
-  </si>
-  <si>
-    <t>13.05.202643</t>
-  </si>
-  <si>
-    <t>13.05.202644</t>
-  </si>
-  <si>
-    <t>13.05.202645</t>
-  </si>
-  <si>
-    <t>13.05.202646</t>
-  </si>
-  <si>
-    <t>13.05.202647</t>
-  </si>
-  <si>
-    <t>13.05.202648</t>
-  </si>
-  <si>
-    <t>13.05.202649</t>
-  </si>
-  <si>
-    <t>13.05.202650</t>
-  </si>
-  <si>
-    <t>13.05.202651</t>
-  </si>
-  <si>
-    <t>13.05.202652</t>
-  </si>
-  <si>
-    <t>13.05.202653</t>
-  </si>
-  <si>
-    <t>13.05.202654</t>
-  </si>
-  <si>
-    <t>13.05.202655</t>
-  </si>
-  <si>
-    <t>13.05.202656</t>
-  </si>
-  <si>
-    <t>13.05.202657</t>
-  </si>
-  <si>
-    <t>13.05.202658</t>
-  </si>
-  <si>
-    <t>13.05.202659</t>
-  </si>
-  <si>
-    <t>13.05.202660</t>
-  </si>
-  <si>
-    <t>13.05.202661</t>
-  </si>
-  <si>
-    <t>13.05.202662</t>
-  </si>
-  <si>
-    <t>13.05.202663</t>
-  </si>
-  <si>
-    <t>13.05.202664</t>
-  </si>
-  <si>
-    <t>13.05.202665</t>
-  </si>
-  <si>
-    <t>13.05.202666</t>
-  </si>
-  <si>
-    <t>13.05.202667</t>
-  </si>
-  <si>
-    <t>13.05.202668</t>
-  </si>
-  <si>
-    <t>13.05.202669</t>
-  </si>
-  <si>
-    <t>13.05.202670</t>
-  </si>
-  <si>
-    <t>13.05.202671</t>
-  </si>
-  <si>
-    <t>13.05.202672</t>
-  </si>
-  <si>
-    <t>13.05.202673</t>
-  </si>
-  <si>
-    <t>13.05.202674</t>
-  </si>
-  <si>
-    <t>13.05.202675</t>
-  </si>
-  <si>
-    <t>13.05.202676</t>
-  </si>
-  <si>
-    <t>13.05.202677</t>
-  </si>
-  <si>
-    <t>13.05.202678</t>
-  </si>
-  <si>
-    <t>13.05.202679</t>
-  </si>
-  <si>
-    <t>13.05.202680</t>
-  </si>
-  <si>
-    <t>13.05.202681</t>
-  </si>
-  <si>
-    <t>13.05.202682</t>
-  </si>
-  <si>
-    <t>13.05.202683</t>
-  </si>
-  <si>
-    <t>13.05.202684</t>
-  </si>
-  <si>
-    <t>13.05.202685</t>
-  </si>
-  <si>
-    <t>13.05.202686</t>
-  </si>
-  <si>
-    <t>13.05.202687</t>
-  </si>
-  <si>
-    <t>13.05.202688</t>
-  </si>
-  <si>
-    <t>13.05.202689</t>
-  </si>
-  <si>
-    <t>13.05.202690</t>
-  </si>
-  <si>
-    <t>13.05.202691</t>
-  </si>
-  <si>
-    <t>13.05.202692</t>
-  </si>
-  <si>
-    <t>13.05.202693</t>
-  </si>
-  <si>
-    <t>13.05.202694</t>
-  </si>
-  <si>
-    <t>13.05.202695</t>
-  </si>
-  <si>
-    <t>13.05.202696</t>
-  </si>
-  <si>
     <t>14.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>14.05.202696</t>
+  </si>
+  <si>
+    <t>15.05.20261</t>
+  </si>
+  <si>
+    <t>15.05.20262</t>
+  </si>
+  <si>
+    <t>15.05.20263</t>
+  </si>
+  <si>
+    <t>15.05.20264</t>
+  </si>
+  <si>
+    <t>15.05.20265</t>
+  </si>
+  <si>
+    <t>15.05.20266</t>
+  </si>
+  <si>
+    <t>15.05.20267</t>
+  </si>
+  <si>
+    <t>15.05.20268</t>
+  </si>
+  <si>
+    <t>15.05.20269</t>
+  </si>
+  <si>
+    <t>15.05.202610</t>
+  </si>
+  <si>
+    <t>15.05.202611</t>
+  </si>
+  <si>
+    <t>15.05.202612</t>
+  </si>
+  <si>
+    <t>15.05.202613</t>
+  </si>
+  <si>
+    <t>15.05.202614</t>
+  </si>
+  <si>
+    <t>15.05.202615</t>
+  </si>
+  <si>
+    <t>15.05.202616</t>
+  </si>
+  <si>
+    <t>15.05.202617</t>
+  </si>
+  <si>
+    <t>15.05.202618</t>
+  </si>
+  <si>
+    <t>15.05.202619</t>
+  </si>
+  <si>
+    <t>15.05.202620</t>
+  </si>
+  <si>
+    <t>15.05.202621</t>
+  </si>
+  <si>
+    <t>15.05.202622</t>
+  </si>
+  <si>
+    <t>15.05.202623</t>
+  </si>
+  <si>
+    <t>15.05.202624</t>
+  </si>
+  <si>
+    <t>15.05.202625</t>
+  </si>
+  <si>
+    <t>15.05.202626</t>
+  </si>
+  <si>
+    <t>15.05.202627</t>
+  </si>
+  <si>
+    <t>15.05.202628</t>
+  </si>
+  <si>
+    <t>15.05.202629</t>
+  </si>
+  <si>
+    <t>15.05.202630</t>
+  </si>
+  <si>
+    <t>15.05.202631</t>
+  </si>
+  <si>
+    <t>15.05.202632</t>
+  </si>
+  <si>
+    <t>15.05.202633</t>
+  </si>
+  <si>
+    <t>15.05.202634</t>
+  </si>
+  <si>
+    <t>15.05.202635</t>
+  </si>
+  <si>
+    <t>15.05.202636</t>
+  </si>
+  <si>
+    <t>15.05.202637</t>
+  </si>
+  <si>
+    <t>15.05.202638</t>
+  </si>
+  <si>
+    <t>15.05.202639</t>
+  </si>
+  <si>
+    <t>15.05.202640</t>
+  </si>
+  <si>
+    <t>15.05.202641</t>
+  </si>
+  <si>
+    <t>15.05.202642</t>
+  </si>
+  <si>
+    <t>15.05.202643</t>
+  </si>
+  <si>
+    <t>15.05.202644</t>
+  </si>
+  <si>
+    <t>15.05.202645</t>
+  </si>
+  <si>
+    <t>15.05.202646</t>
+  </si>
+  <si>
+    <t>15.05.202647</t>
+  </si>
+  <si>
+    <t>15.05.202648</t>
+  </si>
+  <si>
+    <t>15.05.202649</t>
+  </si>
+  <si>
+    <t>15.05.202650</t>
+  </si>
+  <si>
+    <t>15.05.202651</t>
+  </si>
+  <si>
+    <t>15.05.202652</t>
+  </si>
+  <si>
+    <t>15.05.202653</t>
+  </si>
+  <si>
+    <t>15.05.202654</t>
+  </si>
+  <si>
+    <t>15.05.202655</t>
+  </si>
+  <si>
+    <t>15.05.202656</t>
+  </si>
+  <si>
+    <t>15.05.202657</t>
+  </si>
+  <si>
+    <t>15.05.202658</t>
+  </si>
+  <si>
+    <t>15.05.202659</t>
+  </si>
+  <si>
+    <t>15.05.202660</t>
+  </si>
+  <si>
+    <t>15.05.202661</t>
+  </si>
+  <si>
+    <t>15.05.202662</t>
+  </si>
+  <si>
+    <t>15.05.202663</t>
+  </si>
+  <si>
+    <t>15.05.202664</t>
+  </si>
+  <si>
+    <t>15.05.202665</t>
+  </si>
+  <si>
+    <t>15.05.202666</t>
+  </si>
+  <si>
+    <t>15.05.202667</t>
+  </si>
+  <si>
+    <t>15.05.202668</t>
+  </si>
+  <si>
+    <t>15.05.202669</t>
+  </si>
+  <si>
+    <t>15.05.202670</t>
+  </si>
+  <si>
+    <t>15.05.202671</t>
+  </si>
+  <si>
+    <t>15.05.202672</t>
+  </si>
+  <si>
+    <t>15.05.202673</t>
+  </si>
+  <si>
+    <t>15.05.202674</t>
+  </si>
+  <si>
+    <t>15.05.202675</t>
+  </si>
+  <si>
+    <t>15.05.202676</t>
+  </si>
+  <si>
+    <t>15.05.202677</t>
+  </si>
+  <si>
+    <t>15.05.202678</t>
+  </si>
+  <si>
+    <t>15.05.202679</t>
+  </si>
+  <si>
+    <t>15.05.202680</t>
+  </si>
+  <si>
+    <t>15.05.202681</t>
+  </si>
+  <si>
+    <t>15.05.202682</t>
+  </si>
+  <si>
+    <t>15.05.202683</t>
+  </si>
+  <si>
+    <t>15.05.202684</t>
+  </si>
+  <si>
+    <t>15.05.202685</t>
+  </si>
+  <si>
+    <t>15.05.202686</t>
+  </si>
+  <si>
+    <t>15.05.202687</t>
+  </si>
+  <si>
+    <t>15.05.202688</t>
+  </si>
+  <si>
+    <t>15.05.202689</t>
+  </si>
+  <si>
+    <t>15.05.202690</t>
+  </si>
+  <si>
+    <t>15.05.202691</t>
+  </si>
+  <si>
+    <t>15.05.202692</t>
+  </si>
+  <si>
+    <t>15.05.202693</t>
+  </si>
+  <si>
+    <t>15.05.202694</t>
+  </si>
+  <si>
+    <t>15.05.202695</t>
+  </si>
+  <si>
+    <t>15.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B2">
-        <v>1514.13</v>
+        <v>850.961</v>
       </c>
       <c r="C2">
-        <v>1560</v>
+        <v>846</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B3">
-        <v>1515.061</v>
+        <v>851.946</v>
       </c>
       <c r="C3">
-        <v>1572</v>
+        <v>836</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B4">
-        <v>1524.795</v>
+        <v>842.08</v>
       </c>
       <c r="C4">
-        <v>1548</v>
+        <v>876</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B5">
-        <v>1587.942</v>
+        <v>831.447</v>
       </c>
       <c r="C5">
-        <v>1489</v>
+        <v>881</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B6">
-        <v>1534.096</v>
+        <v>821.532</v>
       </c>
       <c r="C6">
-        <v>1445</v>
+        <v>863</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B7">
-        <v>1554.276</v>
+        <v>811.2809999999999</v>
       </c>
       <c r="C7">
-        <v>1410</v>
+        <v>825</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B8">
-        <v>1567.674</v>
+        <v>793.987</v>
       </c>
       <c r="C8">
-        <v>1413</v>
+        <v>817</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B9">
-        <v>1577.159</v>
+        <v>789.751</v>
       </c>
       <c r="C9">
-        <v>1380</v>
+        <v>841</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B10">
-        <v>1534.106</v>
+        <v>801.353</v>
       </c>
       <c r="C10">
-        <v>1345</v>
+        <v>853</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B11">
-        <v>1534.661</v>
+        <v>792.157</v>
       </c>
       <c r="C11">
-        <v>1334</v>
+        <v>857</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B12">
-        <v>1516.831</v>
+        <v>779.986</v>
       </c>
       <c r="C12">
-        <v>1347</v>
+        <v>847</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B13">
-        <v>1496.469</v>
+        <v>779.905</v>
       </c>
       <c r="C13">
-        <v>1361</v>
+        <v>840</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B14">
-        <v>1492.012</v>
+        <v>743.831</v>
       </c>
       <c r="C14">
-        <v>1388</v>
+        <v>848</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B15">
-        <v>1498.614</v>
+        <v>744.289</v>
       </c>
       <c r="C15">
-        <v>1474</v>
+        <v>842</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B16">
-        <v>1518.435</v>
+        <v>746.659</v>
       </c>
       <c r="C16">
-        <v>1509</v>
+        <v>829</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B17">
-        <v>1489.71</v>
+        <v>750.821</v>
       </c>
       <c r="C17">
-        <v>1470</v>
+        <v>827</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B18">
-        <v>1458.967</v>
+        <v>766.516</v>
       </c>
       <c r="C18">
-        <v>1450</v>
+        <v>803</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B19">
-        <v>1471.633</v>
+        <v>748.886</v>
       </c>
       <c r="C19">
-        <v>1422</v>
+        <v>787</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B20">
-        <v>1496.239</v>
+        <v>737.21</v>
       </c>
       <c r="C20">
-        <v>1405</v>
+        <v>776</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B21">
-        <v>1499.005</v>
+        <v>717.085</v>
       </c>
       <c r="C21">
-        <v>1446</v>
+        <v>785</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B22">
-        <v>1510.375</v>
+        <v>682.6559999999999</v>
       </c>
       <c r="C22">
-        <v>1437</v>
+        <v>787</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B23">
-        <v>1539.779</v>
+        <v>659.782</v>
       </c>
       <c r="C23">
-        <v>1452</v>
+        <v>778</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B24">
-        <v>1567.268</v>
+        <v>638.905</v>
       </c>
       <c r="C24">
-        <v>1459</v>
+        <v>749</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B25">
-        <v>1585.051</v>
+        <v>623.833</v>
       </c>
       <c r="C25">
-        <v>1495</v>
+        <v>705</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B26">
-        <v>1554.619</v>
+        <v>593.729</v>
       </c>
       <c r="C26">
-        <v>1524</v>
+        <v>660</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B27">
-        <v>1573.037</v>
+        <v>566.782</v>
       </c>
       <c r="C27">
-        <v>1569</v>
+        <v>638</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B28">
-        <v>1606.125</v>
+        <v>545.8680000000001</v>
       </c>
       <c r="C28">
-        <v>1597</v>
+        <v>603</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B29">
-        <v>1634.351</v>
+        <v>526.865</v>
       </c>
       <c r="C29">
-        <v>1668</v>
+        <v>561</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B30">
-        <v>1677.919</v>
+        <v>485.906</v>
       </c>
       <c r="C30">
-        <v>1689</v>
+        <v>522</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B31">
-        <v>1695.033</v>
+        <v>471.932</v>
       </c>
       <c r="C31">
-        <v>1761</v>
+        <v>496</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B32">
-        <v>1713.155</v>
+        <v>441.799</v>
       </c>
       <c r="C32">
-        <v>1825</v>
+        <v>463</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B33">
-        <v>1727.28</v>
+        <v>421.953</v>
       </c>
       <c r="C33">
-        <v>1822</v>
+        <v>449</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B34">
-        <v>1754.489</v>
+        <v>431.464</v>
       </c>
       <c r="C34">
-        <v>1820</v>
+        <v>447</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B35">
-        <v>1751.634</v>
+        <v>418.926</v>
       </c>
       <c r="C35">
-        <v>1788</v>
+        <v>420</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B36">
-        <v>1768.254</v>
+        <v>407.484</v>
       </c>
       <c r="C36">
-        <v>1799</v>
+        <v>401</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B37">
-        <v>1772.681</v>
+        <v>397.45</v>
       </c>
       <c r="C37">
-        <v>1873</v>
+        <v>376</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B38">
-        <v>1755.138</v>
+        <v>393.706</v>
       </c>
       <c r="C38">
-        <v>2022</v>
+        <v>357</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B39">
-        <v>1766.358</v>
+        <v>384.827</v>
       </c>
       <c r="C39">
-        <v>2075</v>
+        <v>339</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B40">
-        <v>1781.007</v>
+        <v>375.519</v>
       </c>
       <c r="C40">
-        <v>2097</v>
+        <v>330</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B41">
-        <v>1795.969</v>
+        <v>366.706</v>
       </c>
       <c r="C41">
-        <v>2066</v>
+        <v>310</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B42">
-        <v>1825.392</v>
+        <v>321.559</v>
       </c>
       <c r="C42">
-        <v>2102</v>
+        <v>312</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B43">
-        <v>1847.688</v>
+        <v>314.462</v>
       </c>
       <c r="C43">
-        <v>2104</v>
+        <v>322</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B44">
-        <v>1867.773</v>
+        <v>308.366</v>
       </c>
       <c r="C44">
-        <v>2188</v>
+        <v>365</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B45">
-        <v>1887.089</v>
+        <v>302.297</v>
       </c>
       <c r="C45">
-        <v>2189</v>
+        <v>383</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B46">
-        <v>1992.724</v>
+        <v>292.48</v>
       </c>
       <c r="C46">
-        <v>2227</v>
+        <v>366</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B47">
-        <v>1992.904</v>
+        <v>290.736</v>
       </c>
       <c r="C47">
-        <v>2312</v>
+        <v>349</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B48">
-        <v>1991.211</v>
+        <v>287.638</v>
       </c>
       <c r="C48">
-        <v>2338</v>
+        <v>336</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B49">
-        <v>1988.345</v>
+        <v>285.027</v>
       </c>
       <c r="C49">
-        <v>2345</v>
+        <v>358</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B50">
-        <v>1983.107</v>
+        <v>281.955</v>
       </c>
       <c r="C50">
-        <v>2361</v>
+        <v>378</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B51">
-        <v>1976.124</v>
+        <v>283.506</v>
       </c>
       <c r="C51">
-        <v>2393</v>
+        <v>393</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B52">
-        <v>1967.59</v>
+        <v>281.405</v>
       </c>
       <c r="C52">
-        <v>2388</v>
+        <v>382</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B53">
-        <v>1961.448</v>
+        <v>279.851</v>
       </c>
       <c r="C53">
-        <v>2313</v>
+        <v>370</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B54">
-        <v>1944.922</v>
+        <v>280.353</v>
       </c>
       <c r="C54">
-        <v>2257</v>
+        <v>342</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B55">
-        <v>1940.154</v>
+        <v>281.242</v>
       </c>
       <c r="C55">
-        <v>2266</v>
+        <v>340</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B56">
-        <v>1936.239</v>
+        <v>282.407</v>
       </c>
       <c r="C56">
-        <v>2293</v>
+        <v>358</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B57">
-        <v>1930.641</v>
+        <v>283.453</v>
       </c>
       <c r="C57">
-        <v>2270</v>
+        <v>359</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B58">
-        <v>1792.393</v>
+        <v>297.324</v>
       </c>
       <c r="C58">
-        <v>2165</v>
+        <v>403</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B59">
-        <v>1792.031</v>
+        <v>298.037</v>
       </c>
       <c r="C59">
-        <v>2129</v>
+        <v>406</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B60">
-        <v>1792.058</v>
+        <v>300.221</v>
       </c>
       <c r="C60">
-        <v>2151</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B61">
-        <v>1790.385</v>
+        <v>301.145</v>
       </c>
       <c r="C61">
-        <v>2149</v>
+        <v>391</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B62">
-        <v>1748.898</v>
+        <v>286.167</v>
       </c>
       <c r="C62">
-        <v>2215</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B63">
-        <v>1731.857</v>
+        <v>284.396</v>
       </c>
       <c r="C63">
-        <v>2225</v>
+        <v>361</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B64">
-        <v>1714.094</v>
+        <v>281.992</v>
       </c>
       <c r="C64">
-        <v>2159</v>
+        <v>351</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B65">
-        <v>1694.718</v>
+        <v>279.394</v>
       </c>
       <c r="C65">
-        <v>2127</v>
+        <v>340</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B66">
-        <v>1660.219</v>
+        <v>270.462</v>
       </c>
       <c r="C66">
-        <v>2043</v>
+        <v>282</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B67">
-        <v>1630.865</v>
+        <v>260.252</v>
       </c>
       <c r="C67">
-        <v>1947</v>
+        <v>285</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B68">
-        <v>1596.048</v>
+        <v>250.38</v>
       </c>
       <c r="C68">
-        <v>1864</v>
+        <v>268</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B69">
-        <v>1564.751</v>
+        <v>241.314</v>
       </c>
       <c r="C69">
-        <v>1759</v>
+        <v>259</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B70">
-        <v>1512.377</v>
+        <v>229.08</v>
       </c>
       <c r="C70">
-        <v>1666</v>
+        <v>225</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B71">
-        <v>1458.714</v>
+        <v>219.544</v>
       </c>
       <c r="C71">
-        <v>1649</v>
+        <v>190</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B72">
-        <v>1406.566</v>
+        <v>208.15</v>
       </c>
       <c r="C72">
-        <v>1642</v>
+        <v>167</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B73">
-        <v>1350.205</v>
+        <v>198.242</v>
       </c>
       <c r="C73">
-        <v>1516</v>
+        <v>141</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B74">
-        <v>1145.099</v>
+        <v>161.252</v>
       </c>
       <c r="C74">
-        <v>1414</v>
+        <v>115</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B75">
-        <v>1079.028</v>
+        <v>159.013</v>
       </c>
       <c r="C75">
-        <v>1356</v>
+        <v>90</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B76">
-        <v>1014.477</v>
+        <v>157.204</v>
       </c>
       <c r="C76">
-        <v>1322</v>
+        <v>68</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B77">
-        <v>947.792</v>
+        <v>156.221</v>
       </c>
       <c r="C77">
-        <v>1267</v>
+        <v>57</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B78">
-        <v>851.813</v>
+        <v>158.86</v>
       </c>
       <c r="C78">
-        <v>1225</v>
+        <v>55</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B79">
-        <v>824.486</v>
+        <v>163.381</v>
       </c>
       <c r="C79">
-        <v>1173</v>
+        <v>60</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B80">
-        <v>796.572</v>
+        <v>168.92</v>
       </c>
       <c r="C80">
-        <v>1201</v>
+        <v>57</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B81">
-        <v>771.203</v>
+        <v>192.402</v>
       </c>
       <c r="C81">
-        <v>1170</v>
+        <v>62</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B82">
-        <v>748.548</v>
+        <v>180.375</v>
       </c>
       <c r="C82">
-        <v>1142</v>
+        <v>65</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B83">
-        <v>744.351</v>
+        <v>202.573</v>
       </c>
       <c r="C83">
-        <v>1197</v>
+        <v>73</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B84">
-        <v>737.604</v>
+        <v>206.589</v>
       </c>
       <c r="C84">
-        <v>1229</v>
+        <v>79</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B85">
-        <v>730.006</v>
+        <v>211.398</v>
       </c>
       <c r="C85">
-        <v>1247</v>
+        <v>91</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B86">
-        <v>721.509</v>
+        <v>217.831</v>
       </c>
       <c r="C86">
-        <v>1216</v>
+        <v>106</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B87">
-        <v>719.472</v>
+        <v>223.268</v>
       </c>
       <c r="C87">
-        <v>1181</v>
+        <v>109</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B88">
-        <v>716.616</v>
+        <v>227.715</v>
       </c>
       <c r="C88">
-        <v>1131</v>
+        <v>110</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B89">
-        <v>715.165</v>
+        <v>232.507</v>
       </c>
       <c r="C89">
-        <v>1047</v>
+        <v>117</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B90">
-        <v>714.871</v>
+        <v>207.682</v>
       </c>
       <c r="C90">
-        <v>983</v>
+        <v>130</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B91">
-        <v>711.456</v>
+        <v>211.453</v>
       </c>
       <c r="C91">
-        <v>999</v>
+        <v>156</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B92">
-        <v>710.492</v>
+        <v>215.4</v>
       </c>
       <c r="C92">
-        <v>1039</v>
+        <v>177</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B93">
-        <v>708.744</v>
+        <v>219.97</v>
       </c>
       <c r="C93">
-        <v>1044</v>
+        <v>189</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B94">
-        <v>841.873</v>
+        <v>225.124</v>
       </c>
       <c r="C94">
-        <v>1040</v>
+        <v>201</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B95">
-        <v>817.362</v>
+        <v>229.075</v>
       </c>
       <c r="C95">
-        <v>996</v>
+        <v>202</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B96">
-        <v>810.7140000000001</v>
+        <v>233.319</v>
       </c>
       <c r="C96">
-        <v>932</v>
+        <v>207</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B97">
-        <v>803.0309999999999</v>
+        <v>238.129</v>
       </c>
       <c r="C97">
-        <v>895</v>
+        <v>222</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B98">
-        <v>850.961</v>
+        <v>222.986</v>
       </c>
       <c r="C98">
-        <v>846</v>
+        <v>229</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46156.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B99">
-        <v>851.946</v>
+        <v>230.688</v>
       </c>
       <c r="C99">
-        <v>836</v>
+        <v>241</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46156.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B100">
-        <v>842.08</v>
+        <v>237.596</v>
       </c>
       <c r="C100">
-        <v>876</v>
+        <v>255</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46156.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B101">
-        <v>831.447</v>
+        <v>242.19</v>
       </c>
       <c r="C101">
-        <v>881</v>
+        <v>286</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46156.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B102">
-        <v>821.532</v>
+        <v>276.714</v>
       </c>
       <c r="C102">
-        <v>863</v>
+        <v>301</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46156.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B103">
-        <v>811.2809999999999</v>
+        <v>283.335</v>
       </c>
       <c r="C103">
-        <v>825</v>
+        <v>304</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46156.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B104">
-        <v>793.987</v>
+        <v>288.709</v>
       </c>
       <c r="C104">
-        <v>817</v>
+        <v>311</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46156.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B105">
-        <v>789.751</v>
+        <v>299.508</v>
       </c>
       <c r="C105">
-        <v>841</v>
+        <v>308</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46156.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B106">
-        <v>801.353</v>
+        <v>313.95</v>
       </c>
       <c r="C106">
-        <v>853</v>
+        <v>306</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46156.09375</v>
+        <v>46157.09375</v>
       </c>
       <c r="B107">
-        <v>792.157</v>
+        <v>326.004</v>
       </c>
       <c r="C107">
-        <v>857</v>
+        <v>323</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46156.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B108">
-        <v>779.986</v>
+        <v>340.298</v>
       </c>
       <c r="C108">
-        <v>847</v>
+        <v>352</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46156.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B109">
-        <v>779.905</v>
+        <v>348.449</v>
       </c>
       <c r="C109">
-        <v>840</v>
+        <v>375</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46156.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B110">
-        <v>743.831</v>
+        <v>353.975</v>
       </c>
       <c r="C110">
-        <v>848</v>
+        <v>391</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46156.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B111">
-        <v>744.289</v>
+        <v>354.969</v>
       </c>
       <c r="C111">
-        <v>842</v>
+        <v>409</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46156.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B112">
-        <v>746.659</v>
+        <v>351.276</v>
       </c>
       <c r="C112">
-        <v>829</v>
+        <v>416</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46156.15625</v>
+        <v>46157.15625</v>
       </c>
       <c r="B113">
-        <v>750.821</v>
+        <v>361.81</v>
       </c>
       <c r="C113">
-        <v>827</v>
+        <v>430</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46156.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B114">
-        <v>766.516</v>
+        <v>346.455</v>
       </c>
       <c r="C114">
-        <v>803</v>
+        <v>468</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46156.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B115">
-        <v>748.886</v>
+        <v>345.357</v>
       </c>
       <c r="C115">
-        <v>787</v>
+        <v>472</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46156.1875</v>
+        <v>46157.1875</v>
       </c>
       <c r="B116">
-        <v>737.21</v>
+        <v>347.186</v>
       </c>
       <c r="C116">
-        <v>776</v>
+        <v>448</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46156.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B117">
-        <v>717.085</v>
+        <v>356.172</v>
       </c>
       <c r="C117">
-        <v>785</v>
+        <v>436</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46156.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B118">
-        <v>682.6559999999999</v>
+        <v>333.547</v>
       </c>
       <c r="C118">
-        <v>787</v>
+        <v>421</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46156.21875</v>
+        <v>46157.21875</v>
       </c>
       <c r="B119">
-        <v>659.782</v>
+        <v>326.877</v>
       </c>
       <c r="C119">
-        <v>778</v>
+        <v>394</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46156.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B120">
-        <v>638.905</v>
+        <v>328.628</v>
       </c>
       <c r="C120">
-        <v>749</v>
+        <v>359</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46156.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B121">
-        <v>623.833</v>
+        <v>320.927</v>
       </c>
       <c r="C121">
-        <v>705</v>
+        <v>329</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46156.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B122">
-        <v>593.729</v>
+        <v>303.678</v>
       </c>
       <c r="C122">
-        <v>660</v>
+        <v>279</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46156.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B123">
-        <v>566.782</v>
+        <v>293.056</v>
       </c>
       <c r="C123">
-        <v>638</v>
+        <v>246</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46156.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B124">
-        <v>545.8680000000001</v>
+        <v>284.244</v>
       </c>
       <c r="C124">
-        <v>603</v>
+        <v>223</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46156.28125</v>
+        <v>46157.28125</v>
       </c>
       <c r="B125">
-        <v>526.865</v>
+        <v>275.382</v>
       </c>
       <c r="C125">
-        <v>561</v>
+        <v>194</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46156.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B126">
-        <v>485.906</v>
+        <v>257.059</v>
       </c>
       <c r="C126">
-        <v>522</v>
+        <v>157</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46156.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B127">
-        <v>471.932</v>
+        <v>238.345</v>
       </c>
       <c r="C127">
-        <v>496</v>
+        <v>131</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46156.3125</v>
+        <v>46157.3125</v>
       </c>
       <c r="B128">
-        <v>441.799</v>
+        <v>228.704</v>
       </c>
       <c r="C128">
-        <v>463</v>
+        <v>98</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46156.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B129">
-        <v>421.953</v>
+        <v>214.243</v>
       </c>
       <c r="C129">
-        <v>449</v>
+        <v>73</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46156.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B130">
-        <v>431.464</v>
+        <v>229.026</v>
       </c>
       <c r="C130">
-        <v>447</v>
+        <v>64</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46156.34375</v>
+        <v>46157.34375</v>
       </c>
       <c r="B131">
-        <v>418.926</v>
+        <v>226.48</v>
       </c>
       <c r="C131">
-        <v>420</v>
+        <v>66</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46156.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B132">
-        <v>407.484</v>
+        <v>223.826</v>
       </c>
       <c r="C132">
-        <v>401</v>
+        <v>63</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46156.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B133">
-        <v>397.45</v>
+        <v>221.355</v>
       </c>
       <c r="C133">
-        <v>376</v>
+        <v>61</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46156.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B134">
-        <v>393.706</v>
+        <v>204.523</v>
       </c>
       <c r="C134">
-        <v>357</v>
+        <v>66</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46156.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B135">
-        <v>384.827</v>
+        <v>210.767</v>
       </c>
       <c r="C135">
-        <v>339</v>
+        <v>63</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46156.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B136">
-        <v>375.519</v>
+        <v>215.808</v>
       </c>
       <c r="C136">
-        <v>330</v>
+        <v>58</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46156.40625</v>
+        <v>46157.40625</v>
       </c>
       <c r="B137">
-        <v>366.706</v>
+        <v>221.519</v>
       </c>
       <c r="C137">
-        <v>310</v>
+        <v>59</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46156.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B138">
-        <v>321.559</v>
+        <v>231.147</v>
       </c>
       <c r="C138">
-        <v>312</v>
+        <v>53</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46156.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B139">
-        <v>314.462</v>
+        <v>239.129</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46156.4375</v>
+        <v>46157.4375</v>
       </c>
       <c r="B140">
-        <v>308.366</v>
+        <v>250.918</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46156.44791666666</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B141">
-        <v>302.297</v>
+        <v>260.606</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46156.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B142">
-        <v>292.48</v>
+        <v>275.241</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46156.46875</v>
+        <v>46157.46875</v>
       </c>
       <c r="B143">
-        <v>290.736</v>
+        <v>287.181</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46156.47916666666</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B144">
-        <v>287.638</v>
+        <v>302.018</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46156.48958333334</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B145">
-        <v>285.027</v>
+        <v>317.543</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46156.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B146">
-        <v>281.955</v>
+        <v>348.313</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46156.51041666666</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B147">
-        <v>283.506</v>
+        <v>375.099</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46156.52083333334</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B148">
-        <v>281.405</v>
+        <v>403.187</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46156.53125</v>
+        <v>46157.53125</v>
       </c>
       <c r="B149">
-        <v>279.851</v>
+        <v>430.833</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46156.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B150">
-        <v>280.353</v>
+        <v>482.566</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46156.55208333334</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B151">
-        <v>281.242</v>
+        <v>526.181</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46156.5625</v>
+        <v>46157.5625</v>
       </c>
       <c r="B152">
-        <v>282.407</v>
+        <v>568.566</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46156.57291666666</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B153">
-        <v>283.453</v>
+        <v>611.28</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46156.58333333334</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B154">
-        <v>297.324</v>
+        <v>682.7670000000001</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46156.59375</v>
+        <v>46157.59375</v>
       </c>
       <c r="B155">
-        <v>298.037</v>
+        <v>733.467</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46156.60416666666</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B156">
-        <v>300.221</v>
+        <v>782.672</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46156.61458333334</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B157">
-        <v>301.145</v>
+        <v>831.625</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46156.625</v>
+        <v>46157.625</v>
       </c>
       <c r="B158">
-        <v>286.167</v>
+        <v>900.1319999999999</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46156.63541666666</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B159">
-        <v>284.396</v>
+        <v>949.564</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46156.64583333334</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B160">
-        <v>281.992</v>
+        <v>993.9589999999999</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46156.65625</v>
+        <v>46157.65625</v>
       </c>
       <c r="B161">
-        <v>279.394</v>
+        <v>1037.369</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46156.66666666666</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B162">
-        <v>270.462</v>
+        <v>1093.285</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46156.67708333334</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B163">
-        <v>260.252</v>
+        <v>1131.188</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46156.6875</v>
+        <v>46157.6875</v>
       </c>
       <c r="B164">
-        <v>250.38</v>
+        <v>1168.437</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46156.69791666666</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B165">
-        <v>241.314</v>
+        <v>1207.48</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46156.70833333334</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B166">
-        <v>229.08</v>
+        <v>1256.398</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46156.71875</v>
+        <v>46157.71875</v>
       </c>
       <c r="B167">
-        <v>219.544</v>
+        <v>1279.469</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46156.72916666666</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B168">
-        <v>208.15</v>
+        <v>1303.068</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46156.73958333334</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B169">
-        <v>198.242</v>
+        <v>1330.042</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46156.75</v>
+        <v>46157.75</v>
       </c>
       <c r="B170">
-        <v>161.252</v>
+        <v>1374.92</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46156.76041666666</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B171">
-        <v>159.013</v>
+        <v>1407.143</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46156.77083333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B172">
-        <v>157.204</v>
+        <v>1444.749</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46156.78125</v>
+        <v>46157.78125</v>
       </c>
       <c r="B173">
-        <v>156.221</v>
+        <v>1480.185</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46156.79166666666</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B174">
-        <v>158.86</v>
+        <v>1489.991</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46156.80208333334</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B175">
-        <v>163.381</v>
+        <v>1518.608</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46156.8125</v>
+        <v>46157.8125</v>
       </c>
       <c r="B176">
-        <v>168.92</v>
+        <v>1547.712</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46156.82291666666</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B177">
-        <v>192.402</v>
+        <v>1579.435</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46156.83333333334</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B178">
-        <v>180.375</v>
+        <v>1650.331</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46156.84375</v>
+        <v>46157.84375</v>
       </c>
       <c r="B179">
-        <v>202.573</v>
+        <v>1661.088</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46156.85416666666</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B180">
-        <v>206.589</v>
+        <v>1668.145</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46156.86458333334</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B181">
-        <v>211.398</v>
+        <v>1674.912</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46156.875</v>
+        <v>46157.875</v>
       </c>
       <c r="B182">
-        <v>217.831</v>
+        <v>1680.104</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46156.88541666666</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B183">
-        <v>223.268</v>
+        <v>1679.039</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46156.89583333334</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B184">
-        <v>227.715</v>
+        <v>1679.32</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46156.90625</v>
+        <v>46157.90625</v>
       </c>
       <c r="B185">
-        <v>232.507</v>
+        <v>1678.328</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46156.91666666666</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B186">
-        <v>207.682</v>
+        <v>1671.927</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46156.92708333334</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B187">
-        <v>211.453</v>
+        <v>1661.971</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46156.9375</v>
+        <v>46157.9375</v>
       </c>
       <c r="B188">
-        <v>215.4</v>
+        <v>1649.49</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46156.94791666666</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B189">
-        <v>219.97</v>
+        <v>1636.378</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46156.95833333334</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46156.96875</v>
+        <v>46157.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46156.97916666666</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46156.98958333334</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.05.20261</t>
-  </si>
-  <si>
-    <t>14.05.20262</t>
-  </si>
-  <si>
-    <t>14.05.20263</t>
-  </si>
-  <si>
-    <t>14.05.20264</t>
-  </si>
-  <si>
-    <t>14.05.20265</t>
-  </si>
-  <si>
-    <t>14.05.20266</t>
-  </si>
-  <si>
-    <t>14.05.20267</t>
-  </si>
-  <si>
-    <t>14.05.20268</t>
-  </si>
-  <si>
-    <t>14.05.20269</t>
-  </si>
-  <si>
-    <t>14.05.202610</t>
-  </si>
-  <si>
-    <t>14.05.202611</t>
-  </si>
-  <si>
-    <t>14.05.202612</t>
-  </si>
-  <si>
-    <t>14.05.202613</t>
-  </si>
-  <si>
-    <t>14.05.202614</t>
-  </si>
-  <si>
-    <t>14.05.202615</t>
-  </si>
-  <si>
-    <t>14.05.202616</t>
-  </si>
-  <si>
-    <t>14.05.202617</t>
-  </si>
-  <si>
-    <t>14.05.202618</t>
-  </si>
-  <si>
-    <t>14.05.202619</t>
-  </si>
-  <si>
-    <t>14.05.202620</t>
-  </si>
-  <si>
-    <t>14.05.202621</t>
-  </si>
-  <si>
-    <t>14.05.202622</t>
-  </si>
-  <si>
-    <t>14.05.202623</t>
-  </si>
-  <si>
-    <t>14.05.202624</t>
-  </si>
-  <si>
-    <t>14.05.202625</t>
-  </si>
-  <si>
-    <t>14.05.202626</t>
-  </si>
-  <si>
-    <t>14.05.202627</t>
-  </si>
-  <si>
-    <t>14.05.202628</t>
-  </si>
-  <si>
-    <t>14.05.202629</t>
-  </si>
-  <si>
-    <t>14.05.202630</t>
-  </si>
-  <si>
-    <t>14.05.202631</t>
-  </si>
-  <si>
-    <t>14.05.202632</t>
-  </si>
-  <si>
-    <t>14.05.202633</t>
-  </si>
-  <si>
-    <t>14.05.202634</t>
-  </si>
-  <si>
-    <t>14.05.202635</t>
-  </si>
-  <si>
-    <t>14.05.202636</t>
-  </si>
-  <si>
-    <t>14.05.202637</t>
-  </si>
-  <si>
-    <t>14.05.202638</t>
-  </si>
-  <si>
-    <t>14.05.202639</t>
-  </si>
-  <si>
-    <t>14.05.202640</t>
-  </si>
-  <si>
-    <t>14.05.202641</t>
-  </si>
-  <si>
-    <t>14.05.202642</t>
-  </si>
-  <si>
-    <t>14.05.202643</t>
-  </si>
-  <si>
-    <t>14.05.202644</t>
-  </si>
-  <si>
-    <t>14.05.202645</t>
-  </si>
-  <si>
-    <t>14.05.202646</t>
-  </si>
-  <si>
-    <t>14.05.202647</t>
-  </si>
-  <si>
-    <t>14.05.202648</t>
-  </si>
-  <si>
-    <t>14.05.202649</t>
-  </si>
-  <si>
-    <t>14.05.202650</t>
-  </si>
-  <si>
-    <t>14.05.202651</t>
-  </si>
-  <si>
-    <t>14.05.202652</t>
-  </si>
-  <si>
-    <t>14.05.202653</t>
-  </si>
-  <si>
-    <t>14.05.202654</t>
-  </si>
-  <si>
-    <t>14.05.202655</t>
-  </si>
-  <si>
-    <t>14.05.202656</t>
-  </si>
-  <si>
-    <t>14.05.202657</t>
-  </si>
-  <si>
-    <t>14.05.202658</t>
-  </si>
-  <si>
-    <t>14.05.202659</t>
-  </si>
-  <si>
-    <t>14.05.202660</t>
-  </si>
-  <si>
-    <t>14.05.202661</t>
-  </si>
-  <si>
-    <t>14.05.202662</t>
-  </si>
-  <si>
-    <t>14.05.202663</t>
-  </si>
-  <si>
-    <t>14.05.202664</t>
-  </si>
-  <si>
-    <t>14.05.202665</t>
-  </si>
-  <si>
-    <t>14.05.202666</t>
-  </si>
-  <si>
-    <t>14.05.202667</t>
-  </si>
-  <si>
-    <t>14.05.202668</t>
-  </si>
-  <si>
-    <t>14.05.202669</t>
-  </si>
-  <si>
-    <t>14.05.202670</t>
-  </si>
-  <si>
-    <t>14.05.202671</t>
-  </si>
-  <si>
-    <t>14.05.202672</t>
-  </si>
-  <si>
-    <t>14.05.202673</t>
-  </si>
-  <si>
-    <t>14.05.202674</t>
-  </si>
-  <si>
-    <t>14.05.202675</t>
-  </si>
-  <si>
-    <t>14.05.202676</t>
-  </si>
-  <si>
-    <t>14.05.202677</t>
-  </si>
-  <si>
-    <t>14.05.202678</t>
-  </si>
-  <si>
-    <t>14.05.202679</t>
-  </si>
-  <si>
-    <t>14.05.202680</t>
-  </si>
-  <si>
-    <t>14.05.202681</t>
-  </si>
-  <si>
-    <t>14.05.202682</t>
-  </si>
-  <si>
-    <t>14.05.202683</t>
-  </si>
-  <si>
-    <t>14.05.202684</t>
-  </si>
-  <si>
-    <t>14.05.202685</t>
-  </si>
-  <si>
-    <t>14.05.202686</t>
-  </si>
-  <si>
-    <t>14.05.202687</t>
-  </si>
-  <si>
-    <t>14.05.202688</t>
-  </si>
-  <si>
-    <t>14.05.202689</t>
-  </si>
-  <si>
-    <t>14.05.202690</t>
-  </si>
-  <si>
-    <t>14.05.202691</t>
-  </si>
-  <si>
-    <t>14.05.202692</t>
-  </si>
-  <si>
-    <t>14.05.202693</t>
-  </si>
-  <si>
-    <t>14.05.202694</t>
-  </si>
-  <si>
-    <t>14.05.202695</t>
-  </si>
-  <si>
-    <t>14.05.202696</t>
-  </si>
-  <si>
-    <t>15.05.20261</t>
-  </si>
-  <si>
-    <t>15.05.20262</t>
-  </si>
-  <si>
-    <t>15.05.20263</t>
-  </si>
-  <si>
-    <t>15.05.20264</t>
-  </si>
-  <si>
-    <t>15.05.20265</t>
-  </si>
-  <si>
-    <t>15.05.20266</t>
-  </si>
-  <si>
-    <t>15.05.20267</t>
-  </si>
-  <si>
-    <t>15.05.20268</t>
-  </si>
-  <si>
-    <t>15.05.20269</t>
-  </si>
-  <si>
-    <t>15.05.202610</t>
-  </si>
-  <si>
-    <t>15.05.202611</t>
-  </si>
-  <si>
-    <t>15.05.202612</t>
-  </si>
-  <si>
-    <t>15.05.202613</t>
-  </si>
-  <si>
-    <t>15.05.202614</t>
-  </si>
-  <si>
-    <t>15.05.202615</t>
-  </si>
-  <si>
-    <t>15.05.202616</t>
-  </si>
-  <si>
-    <t>15.05.202617</t>
-  </si>
-  <si>
-    <t>15.05.202618</t>
-  </si>
-  <si>
-    <t>15.05.202619</t>
-  </si>
-  <si>
-    <t>15.05.202620</t>
-  </si>
-  <si>
-    <t>15.05.202621</t>
-  </si>
-  <si>
-    <t>15.05.202622</t>
-  </si>
-  <si>
-    <t>15.05.202623</t>
-  </si>
-  <si>
-    <t>15.05.202624</t>
-  </si>
-  <si>
-    <t>15.05.202625</t>
-  </si>
-  <si>
-    <t>15.05.202626</t>
-  </si>
-  <si>
-    <t>15.05.202627</t>
-  </si>
-  <si>
-    <t>15.05.202628</t>
-  </si>
-  <si>
-    <t>15.05.202629</t>
-  </si>
-  <si>
-    <t>15.05.202630</t>
-  </si>
-  <si>
-    <t>15.05.202631</t>
-  </si>
-  <si>
-    <t>15.05.202632</t>
-  </si>
-  <si>
-    <t>15.05.202633</t>
-  </si>
-  <si>
-    <t>15.05.202634</t>
-  </si>
-  <si>
-    <t>15.05.202635</t>
-  </si>
-  <si>
-    <t>15.05.202636</t>
-  </si>
-  <si>
-    <t>15.05.202637</t>
-  </si>
-  <si>
-    <t>15.05.202638</t>
-  </si>
-  <si>
-    <t>15.05.202639</t>
-  </si>
-  <si>
-    <t>15.05.202640</t>
-  </si>
-  <si>
-    <t>15.05.202641</t>
-  </si>
-  <si>
-    <t>15.05.202642</t>
-  </si>
-  <si>
-    <t>15.05.202643</t>
-  </si>
-  <si>
-    <t>15.05.202644</t>
-  </si>
-  <si>
-    <t>15.05.202645</t>
-  </si>
-  <si>
-    <t>15.05.202646</t>
-  </si>
-  <si>
-    <t>15.05.202647</t>
-  </si>
-  <si>
-    <t>15.05.202648</t>
-  </si>
-  <si>
-    <t>15.05.202649</t>
-  </si>
-  <si>
-    <t>15.05.202650</t>
-  </si>
-  <si>
-    <t>15.05.202651</t>
-  </si>
-  <si>
-    <t>15.05.202652</t>
-  </si>
-  <si>
-    <t>15.05.202653</t>
-  </si>
-  <si>
-    <t>15.05.202654</t>
-  </si>
-  <si>
-    <t>15.05.202655</t>
-  </si>
-  <si>
-    <t>15.05.202656</t>
-  </si>
-  <si>
-    <t>15.05.202657</t>
-  </si>
-  <si>
-    <t>15.05.202658</t>
-  </si>
-  <si>
-    <t>15.05.202659</t>
-  </si>
-  <si>
-    <t>15.05.202660</t>
-  </si>
-  <si>
-    <t>15.05.202661</t>
-  </si>
-  <si>
-    <t>15.05.202662</t>
-  </si>
-  <si>
-    <t>15.05.202663</t>
-  </si>
-  <si>
-    <t>15.05.202664</t>
-  </si>
-  <si>
-    <t>15.05.202665</t>
-  </si>
-  <si>
-    <t>15.05.202666</t>
-  </si>
-  <si>
-    <t>15.05.202667</t>
-  </si>
-  <si>
-    <t>15.05.202668</t>
-  </si>
-  <si>
-    <t>15.05.202669</t>
-  </si>
-  <si>
-    <t>15.05.202670</t>
-  </si>
-  <si>
-    <t>15.05.202671</t>
-  </si>
-  <si>
-    <t>15.05.202672</t>
-  </si>
-  <si>
-    <t>15.05.202673</t>
-  </si>
-  <si>
-    <t>15.05.202674</t>
-  </si>
-  <si>
-    <t>15.05.202675</t>
-  </si>
-  <si>
-    <t>15.05.202676</t>
-  </si>
-  <si>
-    <t>15.05.202677</t>
-  </si>
-  <si>
-    <t>15.05.202678</t>
-  </si>
-  <si>
-    <t>15.05.202679</t>
-  </si>
-  <si>
-    <t>15.05.202680</t>
-  </si>
-  <si>
-    <t>15.05.202681</t>
-  </si>
-  <si>
-    <t>15.05.202682</t>
-  </si>
-  <si>
-    <t>15.05.202683</t>
-  </si>
-  <si>
-    <t>15.05.202684</t>
-  </si>
-  <si>
-    <t>15.05.202685</t>
-  </si>
-  <si>
-    <t>15.05.202686</t>
-  </si>
-  <si>
-    <t>15.05.202687</t>
-  </si>
-  <si>
-    <t>15.05.202688</t>
-  </si>
-  <si>
-    <t>15.05.202689</t>
-  </si>
-  <si>
-    <t>15.05.202690</t>
-  </si>
-  <si>
-    <t>15.05.202691</t>
-  </si>
-  <si>
-    <t>15.05.202692</t>
-  </si>
-  <si>
-    <t>15.05.202693</t>
-  </si>
-  <si>
-    <t>15.05.202694</t>
-  </si>
-  <si>
-    <t>15.05.202695</t>
-  </si>
-  <si>
-    <t>15.05.202696</t>
+    <t>20.05.20261</t>
+  </si>
+  <si>
+    <t>20.05.20262</t>
+  </si>
+  <si>
+    <t>20.05.20263</t>
+  </si>
+  <si>
+    <t>20.05.20264</t>
+  </si>
+  <si>
+    <t>20.05.20265</t>
+  </si>
+  <si>
+    <t>20.05.20266</t>
+  </si>
+  <si>
+    <t>20.05.20267</t>
+  </si>
+  <si>
+    <t>20.05.20268</t>
+  </si>
+  <si>
+    <t>20.05.20269</t>
+  </si>
+  <si>
+    <t>20.05.202610</t>
+  </si>
+  <si>
+    <t>20.05.202611</t>
+  </si>
+  <si>
+    <t>20.05.202612</t>
+  </si>
+  <si>
+    <t>20.05.202613</t>
+  </si>
+  <si>
+    <t>20.05.202614</t>
+  </si>
+  <si>
+    <t>20.05.202615</t>
+  </si>
+  <si>
+    <t>20.05.202616</t>
+  </si>
+  <si>
+    <t>20.05.202617</t>
+  </si>
+  <si>
+    <t>20.05.202618</t>
+  </si>
+  <si>
+    <t>20.05.202619</t>
+  </si>
+  <si>
+    <t>20.05.202620</t>
+  </si>
+  <si>
+    <t>20.05.202621</t>
+  </si>
+  <si>
+    <t>20.05.202622</t>
+  </si>
+  <si>
+    <t>20.05.202623</t>
+  </si>
+  <si>
+    <t>20.05.202624</t>
+  </si>
+  <si>
+    <t>20.05.202625</t>
+  </si>
+  <si>
+    <t>20.05.202626</t>
+  </si>
+  <si>
+    <t>20.05.202627</t>
+  </si>
+  <si>
+    <t>20.05.202628</t>
+  </si>
+  <si>
+    <t>20.05.202629</t>
+  </si>
+  <si>
+    <t>20.05.202630</t>
+  </si>
+  <si>
+    <t>20.05.202631</t>
+  </si>
+  <si>
+    <t>20.05.202632</t>
+  </si>
+  <si>
+    <t>20.05.202633</t>
+  </si>
+  <si>
+    <t>20.05.202634</t>
+  </si>
+  <si>
+    <t>20.05.202635</t>
+  </si>
+  <si>
+    <t>20.05.202636</t>
+  </si>
+  <si>
+    <t>20.05.202637</t>
+  </si>
+  <si>
+    <t>20.05.202638</t>
+  </si>
+  <si>
+    <t>20.05.202639</t>
+  </si>
+  <si>
+    <t>20.05.202640</t>
+  </si>
+  <si>
+    <t>20.05.202641</t>
+  </si>
+  <si>
+    <t>20.05.202642</t>
+  </si>
+  <si>
+    <t>20.05.202643</t>
+  </si>
+  <si>
+    <t>20.05.202644</t>
+  </si>
+  <si>
+    <t>20.05.202645</t>
+  </si>
+  <si>
+    <t>20.05.202646</t>
+  </si>
+  <si>
+    <t>20.05.202647</t>
+  </si>
+  <si>
+    <t>20.05.202648</t>
+  </si>
+  <si>
+    <t>20.05.202649</t>
+  </si>
+  <si>
+    <t>20.05.202650</t>
+  </si>
+  <si>
+    <t>20.05.202651</t>
+  </si>
+  <si>
+    <t>20.05.202652</t>
+  </si>
+  <si>
+    <t>20.05.202653</t>
+  </si>
+  <si>
+    <t>20.05.202654</t>
+  </si>
+  <si>
+    <t>20.05.202655</t>
+  </si>
+  <si>
+    <t>20.05.202656</t>
+  </si>
+  <si>
+    <t>20.05.202657</t>
+  </si>
+  <si>
+    <t>20.05.202658</t>
+  </si>
+  <si>
+    <t>20.05.202659</t>
+  </si>
+  <si>
+    <t>20.05.202660</t>
+  </si>
+  <si>
+    <t>20.05.202661</t>
+  </si>
+  <si>
+    <t>20.05.202662</t>
+  </si>
+  <si>
+    <t>20.05.202663</t>
+  </si>
+  <si>
+    <t>20.05.202664</t>
+  </si>
+  <si>
+    <t>20.05.202665</t>
+  </si>
+  <si>
+    <t>20.05.202666</t>
+  </si>
+  <si>
+    <t>20.05.202667</t>
+  </si>
+  <si>
+    <t>20.05.202668</t>
+  </si>
+  <si>
+    <t>20.05.202669</t>
+  </si>
+  <si>
+    <t>20.05.202670</t>
+  </si>
+  <si>
+    <t>20.05.202671</t>
+  </si>
+  <si>
+    <t>20.05.202672</t>
+  </si>
+  <si>
+    <t>20.05.202673</t>
+  </si>
+  <si>
+    <t>20.05.202674</t>
+  </si>
+  <si>
+    <t>20.05.202675</t>
+  </si>
+  <si>
+    <t>20.05.202676</t>
+  </si>
+  <si>
+    <t>20.05.202677</t>
+  </si>
+  <si>
+    <t>20.05.202678</t>
+  </si>
+  <si>
+    <t>20.05.202679</t>
+  </si>
+  <si>
+    <t>20.05.202680</t>
+  </si>
+  <si>
+    <t>20.05.202681</t>
+  </si>
+  <si>
+    <t>20.05.202682</t>
+  </si>
+  <si>
+    <t>20.05.202683</t>
+  </si>
+  <si>
+    <t>20.05.202684</t>
+  </si>
+  <si>
+    <t>20.05.202685</t>
+  </si>
+  <si>
+    <t>20.05.202686</t>
+  </si>
+  <si>
+    <t>20.05.202687</t>
+  </si>
+  <si>
+    <t>20.05.202688</t>
+  </si>
+  <si>
+    <t>20.05.202689</t>
+  </si>
+  <si>
+    <t>20.05.202690</t>
+  </si>
+  <si>
+    <t>20.05.202691</t>
+  </si>
+  <si>
+    <t>20.05.202692</t>
+  </si>
+  <si>
+    <t>20.05.202693</t>
+  </si>
+  <si>
+    <t>20.05.202694</t>
+  </si>
+  <si>
+    <t>20.05.202695</t>
+  </si>
+  <si>
+    <t>20.05.202696</t>
+  </si>
+  <si>
+    <t>21.05.20261</t>
+  </si>
+  <si>
+    <t>21.05.20262</t>
+  </si>
+  <si>
+    <t>21.05.20263</t>
+  </si>
+  <si>
+    <t>21.05.20264</t>
+  </si>
+  <si>
+    <t>21.05.20265</t>
+  </si>
+  <si>
+    <t>21.05.20266</t>
+  </si>
+  <si>
+    <t>21.05.20267</t>
+  </si>
+  <si>
+    <t>21.05.20268</t>
+  </si>
+  <si>
+    <t>21.05.20269</t>
+  </si>
+  <si>
+    <t>21.05.202610</t>
+  </si>
+  <si>
+    <t>21.05.202611</t>
+  </si>
+  <si>
+    <t>21.05.202612</t>
+  </si>
+  <si>
+    <t>21.05.202613</t>
+  </si>
+  <si>
+    <t>21.05.202614</t>
+  </si>
+  <si>
+    <t>21.05.202615</t>
+  </si>
+  <si>
+    <t>21.05.202616</t>
+  </si>
+  <si>
+    <t>21.05.202617</t>
+  </si>
+  <si>
+    <t>21.05.202618</t>
+  </si>
+  <si>
+    <t>21.05.202619</t>
+  </si>
+  <si>
+    <t>21.05.202620</t>
+  </si>
+  <si>
+    <t>21.05.202621</t>
+  </si>
+  <si>
+    <t>21.05.202622</t>
+  </si>
+  <si>
+    <t>21.05.202623</t>
+  </si>
+  <si>
+    <t>21.05.202624</t>
+  </si>
+  <si>
+    <t>21.05.202625</t>
+  </si>
+  <si>
+    <t>21.05.202626</t>
+  </si>
+  <si>
+    <t>21.05.202627</t>
+  </si>
+  <si>
+    <t>21.05.202628</t>
+  </si>
+  <si>
+    <t>21.05.202629</t>
+  </si>
+  <si>
+    <t>21.05.202630</t>
+  </si>
+  <si>
+    <t>21.05.202631</t>
+  </si>
+  <si>
+    <t>21.05.202632</t>
+  </si>
+  <si>
+    <t>21.05.202633</t>
+  </si>
+  <si>
+    <t>21.05.202634</t>
+  </si>
+  <si>
+    <t>21.05.202635</t>
+  </si>
+  <si>
+    <t>21.05.202636</t>
+  </si>
+  <si>
+    <t>21.05.202637</t>
+  </si>
+  <si>
+    <t>21.05.202638</t>
+  </si>
+  <si>
+    <t>21.05.202639</t>
+  </si>
+  <si>
+    <t>21.05.202640</t>
+  </si>
+  <si>
+    <t>21.05.202641</t>
+  </si>
+  <si>
+    <t>21.05.202642</t>
+  </si>
+  <si>
+    <t>21.05.202643</t>
+  </si>
+  <si>
+    <t>21.05.202644</t>
+  </si>
+  <si>
+    <t>21.05.202645</t>
+  </si>
+  <si>
+    <t>21.05.202646</t>
+  </si>
+  <si>
+    <t>21.05.202647</t>
+  </si>
+  <si>
+    <t>21.05.202648</t>
+  </si>
+  <si>
+    <t>21.05.202649</t>
+  </si>
+  <si>
+    <t>21.05.202650</t>
+  </si>
+  <si>
+    <t>21.05.202651</t>
+  </si>
+  <si>
+    <t>21.05.202652</t>
+  </si>
+  <si>
+    <t>21.05.202653</t>
+  </si>
+  <si>
+    <t>21.05.202654</t>
+  </si>
+  <si>
+    <t>21.05.202655</t>
+  </si>
+  <si>
+    <t>21.05.202656</t>
+  </si>
+  <si>
+    <t>21.05.202657</t>
+  </si>
+  <si>
+    <t>21.05.202658</t>
+  </si>
+  <si>
+    <t>21.05.202659</t>
+  </si>
+  <si>
+    <t>21.05.202660</t>
+  </si>
+  <si>
+    <t>21.05.202661</t>
+  </si>
+  <si>
+    <t>21.05.202662</t>
+  </si>
+  <si>
+    <t>21.05.202663</t>
+  </si>
+  <si>
+    <t>21.05.202664</t>
+  </si>
+  <si>
+    <t>21.05.202665</t>
+  </si>
+  <si>
+    <t>21.05.202666</t>
+  </si>
+  <si>
+    <t>21.05.202667</t>
+  </si>
+  <si>
+    <t>21.05.202668</t>
+  </si>
+  <si>
+    <t>21.05.202669</t>
+  </si>
+  <si>
+    <t>21.05.202670</t>
+  </si>
+  <si>
+    <t>21.05.202671</t>
+  </si>
+  <si>
+    <t>21.05.202672</t>
+  </si>
+  <si>
+    <t>21.05.202673</t>
+  </si>
+  <si>
+    <t>21.05.202674</t>
+  </si>
+  <si>
+    <t>21.05.202675</t>
+  </si>
+  <si>
+    <t>21.05.202676</t>
+  </si>
+  <si>
+    <t>21.05.202677</t>
+  </si>
+  <si>
+    <t>21.05.202678</t>
+  </si>
+  <si>
+    <t>21.05.202679</t>
+  </si>
+  <si>
+    <t>21.05.202680</t>
+  </si>
+  <si>
+    <t>21.05.202681</t>
+  </si>
+  <si>
+    <t>21.05.202682</t>
+  </si>
+  <si>
+    <t>21.05.202683</t>
+  </si>
+  <si>
+    <t>21.05.202684</t>
+  </si>
+  <si>
+    <t>21.05.202685</t>
+  </si>
+  <si>
+    <t>21.05.202686</t>
+  </si>
+  <si>
+    <t>21.05.202687</t>
+  </si>
+  <si>
+    <t>21.05.202688</t>
+  </si>
+  <si>
+    <t>21.05.202689</t>
+  </si>
+  <si>
+    <t>21.05.202690</t>
+  </si>
+  <si>
+    <t>21.05.202691</t>
+  </si>
+  <si>
+    <t>21.05.202692</t>
+  </si>
+  <si>
+    <t>21.05.202693</t>
+  </si>
+  <si>
+    <t>21.05.202694</t>
+  </si>
+  <si>
+    <t>21.05.202695</t>
+  </si>
+  <si>
+    <t>21.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B2">
-        <v>850.961</v>
+        <v>1129.64</v>
       </c>
       <c r="C2">
-        <v>846</v>
+        <v>1302</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46156.01041666666</v>
+        <v>46162.01041666666</v>
       </c>
       <c r="B3">
-        <v>851.946</v>
+        <v>1167.958</v>
       </c>
       <c r="C3">
-        <v>836</v>
+        <v>1283</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46156.02083333334</v>
+        <v>46162.02083333334</v>
       </c>
       <c r="B4">
-        <v>842.08</v>
+        <v>1201.558</v>
       </c>
       <c r="C4">
-        <v>876</v>
+        <v>1263</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46156.03125</v>
+        <v>46162.03125</v>
       </c>
       <c r="B5">
-        <v>831.447</v>
+        <v>1242.202</v>
       </c>
       <c r="C5">
-        <v>881</v>
+        <v>1277</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46156.04166666666</v>
+        <v>46162.04166666666</v>
       </c>
       <c r="B6">
-        <v>821.532</v>
+        <v>1268.558</v>
       </c>
       <c r="C6">
-        <v>863</v>
+        <v>1289</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46156.05208333334</v>
+        <v>46162.05208333334</v>
       </c>
       <c r="B7">
-        <v>811.2809999999999</v>
+        <v>1310.456</v>
       </c>
       <c r="C7">
-        <v>825</v>
+        <v>1293</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46156.0625</v>
+        <v>46162.0625</v>
       </c>
       <c r="B8">
-        <v>793.987</v>
+        <v>1349.938</v>
       </c>
       <c r="C8">
-        <v>817</v>
+        <v>1316</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46156.07291666666</v>
+        <v>46162.07291666666</v>
       </c>
       <c r="B9">
-        <v>789.751</v>
+        <v>1368.7</v>
       </c>
       <c r="C9">
-        <v>841</v>
+        <v>1346</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46156.08333333334</v>
+        <v>46162.08333333334</v>
       </c>
       <c r="B10">
-        <v>801.353</v>
+        <v>1332.897</v>
       </c>
       <c r="C10">
-        <v>853</v>
+        <v>1396</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46156.09375</v>
+        <v>46162.09375</v>
       </c>
       <c r="B11">
-        <v>792.157</v>
+        <v>1359.917</v>
       </c>
       <c r="C11">
-        <v>857</v>
+        <v>1442</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46156.10416666666</v>
+        <v>46162.10416666666</v>
       </c>
       <c r="B12">
-        <v>779.986</v>
+        <v>1387.488</v>
       </c>
       <c r="C12">
-        <v>847</v>
+        <v>1499</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46156.11458333334</v>
+        <v>46162.11458333334</v>
       </c>
       <c r="B13">
-        <v>779.905</v>
+        <v>1416.43</v>
       </c>
       <c r="C13">
-        <v>840</v>
+        <v>1555</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46156.125</v>
+        <v>46162.125</v>
       </c>
       <c r="B14">
-        <v>743.831</v>
+        <v>1452.704</v>
       </c>
       <c r="C14">
-        <v>848</v>
+        <v>1612</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46156.13541666666</v>
+        <v>46162.13541666666</v>
       </c>
       <c r="B15">
-        <v>744.289</v>
+        <v>1467.688</v>
       </c>
       <c r="C15">
-        <v>842</v>
+        <v>1672</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46156.14583333334</v>
+        <v>46162.14583333334</v>
       </c>
       <c r="B16">
-        <v>746.659</v>
+        <v>1488.706</v>
       </c>
       <c r="C16">
-        <v>829</v>
+        <v>1734</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46156.15625</v>
+        <v>46162.15625</v>
       </c>
       <c r="B17">
-        <v>750.821</v>
+        <v>1520.647</v>
       </c>
       <c r="C17">
-        <v>827</v>
+        <v>1756</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46156.16666666666</v>
+        <v>46162.16666666666</v>
       </c>
       <c r="B18">
-        <v>766.516</v>
+        <v>1613.367</v>
       </c>
       <c r="C18">
-        <v>803</v>
+        <v>1794</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46156.17708333334</v>
+        <v>46162.17708333334</v>
       </c>
       <c r="B19">
-        <v>748.886</v>
+        <v>1637.57</v>
       </c>
       <c r="C19">
-        <v>787</v>
+        <v>1854</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46156.1875</v>
+        <v>46162.1875</v>
       </c>
       <c r="B20">
-        <v>737.21</v>
+        <v>1660.04</v>
       </c>
       <c r="C20">
-        <v>776</v>
+        <v>1902</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46156.19791666666</v>
+        <v>46162.19791666666</v>
       </c>
       <c r="B21">
-        <v>717.085</v>
+        <v>1683.581</v>
       </c>
       <c r="C21">
-        <v>785</v>
+        <v>1958</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46156.20833333334</v>
+        <v>46162.20833333334</v>
       </c>
       <c r="B22">
-        <v>682.6559999999999</v>
+        <v>1735.004</v>
       </c>
       <c r="C22">
-        <v>787</v>
+        <v>2006</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46156.21875</v>
+        <v>46162.21875</v>
       </c>
       <c r="B23">
-        <v>659.782</v>
+        <v>1731.651</v>
       </c>
       <c r="C23">
-        <v>778</v>
+        <v>1998</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46156.22916666666</v>
+        <v>46162.22916666666</v>
       </c>
       <c r="B24">
-        <v>638.905</v>
+        <v>1728.585</v>
       </c>
       <c r="C24">
-        <v>749</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46156.23958333334</v>
+        <v>46162.23958333334</v>
       </c>
       <c r="B25">
-        <v>623.833</v>
+        <v>1738.854</v>
       </c>
       <c r="C25">
-        <v>705</v>
+        <v>1983</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46156.25</v>
+        <v>46162.25</v>
       </c>
       <c r="B26">
-        <v>593.729</v>
+        <v>1753.739</v>
       </c>
       <c r="C26">
-        <v>660</v>
+        <v>1978</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46156.26041666666</v>
+        <v>46162.26041666666</v>
       </c>
       <c r="B27">
-        <v>566.782</v>
+        <v>1753.659</v>
       </c>
       <c r="C27">
-        <v>638</v>
+        <v>1963</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46156.27083333334</v>
+        <v>46162.27083333334</v>
       </c>
       <c r="B28">
-        <v>545.8680000000001</v>
+        <v>1754.425</v>
       </c>
       <c r="C28">
-        <v>603</v>
+        <v>1899</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46156.28125</v>
+        <v>46162.28125</v>
       </c>
       <c r="B29">
-        <v>526.865</v>
+        <v>1758.572</v>
       </c>
       <c r="C29">
-        <v>561</v>
+        <v>1840</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46156.29166666666</v>
+        <v>46162.29166666666</v>
       </c>
       <c r="B30">
-        <v>485.906</v>
+        <v>1744.419</v>
       </c>
       <c r="C30">
-        <v>522</v>
+        <v>1779</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46156.30208333334</v>
+        <v>46162.30208333334</v>
       </c>
       <c r="B31">
-        <v>471.932</v>
+        <v>1748.146</v>
       </c>
       <c r="C31">
-        <v>496</v>
+        <v>1751</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46156.3125</v>
+        <v>46162.3125</v>
       </c>
       <c r="B32">
-        <v>441.799</v>
+        <v>1768.214</v>
       </c>
       <c r="C32">
-        <v>463</v>
+        <v>1742</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46156.32291666666</v>
+        <v>46162.32291666666</v>
       </c>
       <c r="B33">
-        <v>421.953</v>
+        <v>1779.365</v>
       </c>
       <c r="C33">
-        <v>449</v>
+        <v>1748</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46156.33333333334</v>
+        <v>46162.33333333334</v>
       </c>
       <c r="B34">
-        <v>431.464</v>
+        <v>1785.14</v>
       </c>
       <c r="C34">
-        <v>447</v>
+        <v>1714</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46156.34375</v>
+        <v>46162.34375</v>
       </c>
       <c r="B35">
-        <v>418.926</v>
+        <v>1795.802</v>
       </c>
       <c r="C35">
-        <v>420</v>
+        <v>1732</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46156.35416666666</v>
+        <v>46162.35416666666</v>
       </c>
       <c r="B36">
-        <v>407.484</v>
+        <v>1820.914</v>
       </c>
       <c r="C36">
-        <v>401</v>
+        <v>1731</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46156.36458333334</v>
+        <v>46162.36458333334</v>
       </c>
       <c r="B37">
-        <v>397.45</v>
+        <v>1838.863</v>
       </c>
       <c r="C37">
-        <v>376</v>
+        <v>1759</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46156.375</v>
+        <v>46162.375</v>
       </c>
       <c r="B38">
-        <v>393.706</v>
+        <v>1911.31</v>
       </c>
       <c r="C38">
-        <v>357</v>
+        <v>1813</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46156.38541666666</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="B39">
-        <v>384.827</v>
+        <v>1922.162</v>
       </c>
       <c r="C39">
-        <v>339</v>
+        <v>1873</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46156.39583333334</v>
+        <v>46162.39583333334</v>
       </c>
       <c r="B40">
-        <v>375.519</v>
+        <v>1934.724</v>
       </c>
       <c r="C40">
-        <v>330</v>
+        <v>1938</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46156.40625</v>
+        <v>46162.40625</v>
       </c>
       <c r="B41">
-        <v>366.706</v>
+        <v>1943.48</v>
       </c>
       <c r="C41">
-        <v>310</v>
+        <v>1968</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46156.41666666666</v>
+        <v>46162.41666666666</v>
       </c>
       <c r="B42">
-        <v>321.559</v>
+        <v>1968.803</v>
       </c>
       <c r="C42">
-        <v>312</v>
+        <v>2026</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46156.42708333334</v>
+        <v>46162.42708333334</v>
       </c>
       <c r="B43">
-        <v>314.462</v>
+        <v>1974.4</v>
       </c>
       <c r="C43">
-        <v>322</v>
+        <v>2054</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46156.4375</v>
+        <v>46162.4375</v>
       </c>
       <c r="B44">
-        <v>308.366</v>
+        <v>1983.251</v>
       </c>
       <c r="C44">
-        <v>365</v>
+        <v>2057</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46156.44791666666</v>
+        <v>46162.44791666666</v>
       </c>
       <c r="B45">
-        <v>302.297</v>
+        <v>1990.01</v>
       </c>
       <c r="C45">
-        <v>383</v>
+        <v>2048</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46156.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="B46">
-        <v>292.48</v>
+        <v>2001.364</v>
       </c>
       <c r="C46">
-        <v>366</v>
+        <v>1998</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46156.46875</v>
+        <v>46162.46875</v>
       </c>
       <c r="B47">
-        <v>290.736</v>
+        <v>1997.443</v>
       </c>
       <c r="C47">
-        <v>349</v>
+        <v>2020</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46156.47916666666</v>
+        <v>46162.47916666666</v>
       </c>
       <c r="B48">
-        <v>287.638</v>
+        <v>1993.376</v>
       </c>
       <c r="C48">
-        <v>336</v>
+        <v>2017</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46156.48958333334</v>
+        <v>46162.48958333334</v>
       </c>
       <c r="B49">
-        <v>285.027</v>
+        <v>1989.152</v>
       </c>
       <c r="C49">
-        <v>358</v>
+        <v>2027</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46156.5</v>
+        <v>46162.5</v>
       </c>
       <c r="B50">
-        <v>281.955</v>
+        <v>1959.322</v>
       </c>
       <c r="C50">
-        <v>378</v>
+        <v>2009</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46156.51041666666</v>
+        <v>46162.51041666666</v>
       </c>
       <c r="B51">
-        <v>283.506</v>
+        <v>1941.208</v>
       </c>
       <c r="C51">
-        <v>393</v>
+        <v>1952</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46156.52083333334</v>
+        <v>46162.52083333334</v>
       </c>
       <c r="B52">
-        <v>281.405</v>
+        <v>1924.931</v>
       </c>
       <c r="C52">
-        <v>382</v>
+        <v>1906</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46156.53125</v>
+        <v>46162.53125</v>
       </c>
       <c r="B53">
-        <v>279.851</v>
+        <v>1908.047</v>
       </c>
       <c r="C53">
-        <v>370</v>
+        <v>1868</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46156.54166666666</v>
+        <v>46162.54166666666</v>
       </c>
       <c r="B54">
-        <v>280.353</v>
+        <v>1925.643</v>
       </c>
       <c r="C54">
-        <v>342</v>
+        <v>1839</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46156.55208333334</v>
+        <v>46162.55208333334</v>
       </c>
       <c r="B55">
-        <v>281.242</v>
+        <v>1909.724</v>
       </c>
       <c r="C55">
-        <v>340</v>
+        <v>1842</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46156.5625</v>
+        <v>46162.5625</v>
       </c>
       <c r="B56">
-        <v>282.407</v>
+        <v>1893.499</v>
       </c>
       <c r="C56">
-        <v>358</v>
+        <v>1865</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46156.57291666666</v>
+        <v>46162.57291666666</v>
       </c>
       <c r="B57">
-        <v>283.453</v>
+        <v>1877.917</v>
       </c>
       <c r="C57">
-        <v>359</v>
+        <v>1880</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46156.58333333334</v>
+        <v>46162.58333333334</v>
       </c>
       <c r="B58">
-        <v>297.324</v>
+        <v>1866.439</v>
       </c>
       <c r="C58">
-        <v>403</v>
+        <v>1933</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46156.59375</v>
+        <v>46162.59375</v>
       </c>
       <c r="B59">
-        <v>298.037</v>
+        <v>1841.737</v>
       </c>
       <c r="C59">
-        <v>406</v>
+        <v>1986</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46156.60416666666</v>
+        <v>46162.60416666666</v>
       </c>
       <c r="B60">
-        <v>300.221</v>
+        <v>1816.365</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>2014</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46156.61458333334</v>
+        <v>46162.61458333334</v>
       </c>
       <c r="B61">
-        <v>301.145</v>
+        <v>1793.937</v>
       </c>
       <c r="C61">
-        <v>391</v>
+        <v>2058</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46156.625</v>
+        <v>46162.625</v>
       </c>
       <c r="B62">
-        <v>286.167</v>
+        <v>1754.083</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>2051</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46156.63541666666</v>
+        <v>46162.63541666666</v>
       </c>
       <c r="B63">
-        <v>284.396</v>
+        <v>1726.862</v>
       </c>
       <c r="C63">
-        <v>361</v>
+        <v>2000</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46156.64583333334</v>
+        <v>46162.64583333334</v>
       </c>
       <c r="B64">
-        <v>281.992</v>
+        <v>1698.727</v>
       </c>
       <c r="C64">
-        <v>351</v>
+        <v>2045</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46156.65625</v>
+        <v>46162.65625</v>
       </c>
       <c r="B65">
-        <v>279.394</v>
+        <v>1671.19</v>
       </c>
       <c r="C65">
-        <v>340</v>
+        <v>2037</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46156.66666666666</v>
+        <v>46162.66666666666</v>
       </c>
       <c r="B66">
-        <v>270.462</v>
+        <v>1542.963</v>
       </c>
       <c r="C66">
-        <v>282</v>
+        <v>2128</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46156.67708333334</v>
+        <v>46162.67708333334</v>
       </c>
       <c r="B67">
-        <v>260.252</v>
+        <v>1523.353</v>
       </c>
       <c r="C67">
-        <v>285</v>
+        <v>2114</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46156.6875</v>
+        <v>46162.6875</v>
       </c>
       <c r="B68">
-        <v>250.38</v>
+        <v>1503.867</v>
       </c>
       <c r="C68">
-        <v>268</v>
+        <v>2169</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46156.69791666666</v>
+        <v>46162.69791666666</v>
       </c>
       <c r="B69">
-        <v>241.314</v>
+        <v>1483.878</v>
       </c>
       <c r="C69">
-        <v>259</v>
+        <v>2138</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46156.70833333334</v>
+        <v>46162.70833333334</v>
       </c>
       <c r="B70">
-        <v>229.08</v>
+        <v>1426.847</v>
       </c>
       <c r="C70">
-        <v>225</v>
+        <v>2174</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46156.71875</v>
+        <v>46162.71875</v>
       </c>
       <c r="B71">
-        <v>219.544</v>
+        <v>1398.01</v>
       </c>
       <c r="C71">
-        <v>190</v>
+        <v>2222</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46156.72916666666</v>
+        <v>46162.72916666666</v>
       </c>
       <c r="B72">
-        <v>208.15</v>
+        <v>1370.595</v>
       </c>
       <c r="C72">
-        <v>167</v>
+        <v>2226</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46156.73958333334</v>
+        <v>46162.73958333334</v>
       </c>
       <c r="B73">
-        <v>198.242</v>
+        <v>1344.172</v>
       </c>
       <c r="C73">
-        <v>141</v>
+        <v>2216</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46156.75</v>
+        <v>46162.75</v>
       </c>
       <c r="B74">
-        <v>161.252</v>
+        <v>1335.305</v>
       </c>
       <c r="C74">
-        <v>115</v>
+        <v>2210</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46156.76041666666</v>
+        <v>46162.76041666666</v>
       </c>
       <c r="B75">
-        <v>159.013</v>
+        <v>1331.903</v>
       </c>
       <c r="C75">
-        <v>90</v>
+        <v>2245</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46156.77083333334</v>
+        <v>46162.77083333334</v>
       </c>
       <c r="B76">
-        <v>157.204</v>
+        <v>1328.172</v>
       </c>
       <c r="C76">
-        <v>68</v>
+        <v>2236</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46156.78125</v>
+        <v>46162.78125</v>
       </c>
       <c r="B77">
-        <v>156.221</v>
+        <v>1320.086</v>
       </c>
       <c r="C77">
-        <v>57</v>
+        <v>2222</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46156.79166666666</v>
+        <v>46162.79166666666</v>
       </c>
       <c r="B78">
-        <v>158.86</v>
+        <v>1340.229</v>
       </c>
       <c r="C78">
-        <v>55</v>
+        <v>2233</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46156.80208333334</v>
+        <v>46162.80208333334</v>
       </c>
       <c r="B79">
-        <v>163.381</v>
+        <v>1358.072</v>
       </c>
       <c r="C79">
-        <v>60</v>
+        <v>2240</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46156.8125</v>
+        <v>46162.8125</v>
       </c>
       <c r="B80">
-        <v>168.92</v>
+        <v>1375.873</v>
       </c>
       <c r="C80">
-        <v>57</v>
+        <v>2163</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46156.82291666666</v>
+        <v>46162.82291666666</v>
       </c>
       <c r="B81">
-        <v>192.402</v>
+        <v>1391.265</v>
       </c>
       <c r="C81">
-        <v>62</v>
+        <v>2102</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46156.83333333334</v>
+        <v>46162.83333333334</v>
       </c>
       <c r="B82">
-        <v>180.375</v>
+        <v>1406.429</v>
       </c>
       <c r="C82">
-        <v>65</v>
+        <v>2076</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46156.84375</v>
+        <v>46162.84375</v>
       </c>
       <c r="B83">
-        <v>202.573</v>
+        <v>1424.4</v>
       </c>
       <c r="C83">
-        <v>73</v>
+        <v>2072</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46156.85416666666</v>
+        <v>46162.85416666666</v>
       </c>
       <c r="B84">
-        <v>206.589</v>
+        <v>1443.657</v>
       </c>
       <c r="C84">
-        <v>79</v>
+        <v>2089</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46156.86458333334</v>
+        <v>46162.86458333334</v>
       </c>
       <c r="B85">
-        <v>211.398</v>
+        <v>1464.84</v>
       </c>
       <c r="C85">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46156.875</v>
+        <v>46162.875</v>
       </c>
       <c r="B86">
-        <v>217.831</v>
+        <v>1498.522</v>
       </c>
       <c r="C86">
-        <v>106</v>
+        <v>2124</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46156.88541666666</v>
+        <v>46162.88541666666</v>
       </c>
       <c r="B87">
-        <v>223.268</v>
+        <v>1516.046</v>
       </c>
       <c r="C87">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46156.89583333334</v>
+        <v>46162.89583333334</v>
       </c>
       <c r="B88">
-        <v>227.715</v>
+        <v>1536.581</v>
       </c>
       <c r="C88">
-        <v>110</v>
+        <v>2143</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46156.90625</v>
+        <v>46162.90625</v>
       </c>
       <c r="B89">
-        <v>232.507</v>
+        <v>1558.249</v>
       </c>
       <c r="C89">
-        <v>117</v>
+        <v>2137</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46156.91666666666</v>
+        <v>46162.91666666666</v>
       </c>
       <c r="B90">
-        <v>207.682</v>
+        <v>1589.975</v>
       </c>
       <c r="C90">
-        <v>130</v>
+        <v>2128</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46156.92708333334</v>
+        <v>46162.92708333334</v>
       </c>
       <c r="B91">
-        <v>211.453</v>
+        <v>1608.573</v>
       </c>
       <c r="C91">
-        <v>156</v>
+        <v>2122</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46156.9375</v>
+        <v>46162.9375</v>
       </c>
       <c r="B92">
-        <v>215.4</v>
+        <v>1629.277</v>
       </c>
       <c r="C92">
-        <v>177</v>
+        <v>2133</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46156.94791666666</v>
+        <v>46162.94791666666</v>
       </c>
       <c r="B93">
-        <v>219.97</v>
+        <v>1651.253</v>
       </c>
       <c r="C93">
-        <v>189</v>
+        <v>2115</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46156.95833333334</v>
+        <v>46162.95833333334</v>
       </c>
       <c r="B94">
-        <v>225.124</v>
+        <v>1825.457</v>
       </c>
       <c r="C94">
-        <v>201</v>
+        <v>2143</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46156.96875</v>
+        <v>46162.96875</v>
       </c>
       <c r="B95">
-        <v>229.075</v>
+        <v>1858.346</v>
       </c>
       <c r="C95">
-        <v>202</v>
+        <v>2173</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46156.97916666666</v>
+        <v>46162.97916666666</v>
       </c>
       <c r="B96">
-        <v>233.319</v>
+        <v>1879.475</v>
       </c>
       <c r="C96">
-        <v>207</v>
+        <v>2186</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46156.98958333334</v>
+        <v>46162.98958333334</v>
       </c>
       <c r="B97">
-        <v>238.129</v>
+        <v>1912.949</v>
       </c>
       <c r="C97">
-        <v>222</v>
+        <v>2196</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B98">
-        <v>222.986</v>
+        <v>2011.594</v>
       </c>
       <c r="C98">
-        <v>229</v>
+        <v>2186</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B99">
-        <v>230.688</v>
+        <v>2014.513</v>
       </c>
       <c r="C99">
-        <v>241</v>
+        <v>2176</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B100">
-        <v>237.596</v>
+        <v>2021.993</v>
       </c>
       <c r="C100">
-        <v>255</v>
+        <v>2208</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B101">
-        <v>242.19</v>
+        <v>2038.267</v>
       </c>
       <c r="C101">
-        <v>286</v>
+        <v>2202</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B102">
-        <v>276.714</v>
+        <v>2082.547</v>
       </c>
       <c r="C102">
-        <v>301</v>
+        <v>2250</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B103">
-        <v>283.335</v>
+        <v>2102.276</v>
       </c>
       <c r="C103">
-        <v>304</v>
+        <v>2300</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B104">
-        <v>288.709</v>
+        <v>2116.323</v>
       </c>
       <c r="C104">
-        <v>311</v>
+        <v>2336</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B105">
-        <v>299.508</v>
+        <v>2125.058</v>
       </c>
       <c r="C105">
-        <v>308</v>
+        <v>2354</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B106">
-        <v>313.95</v>
+        <v>2100.509</v>
       </c>
       <c r="C106">
-        <v>306</v>
+        <v>2366</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B107">
-        <v>326.004</v>
+        <v>2114.928</v>
       </c>
       <c r="C107">
-        <v>323</v>
+        <v>2324</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B108">
-        <v>340.298</v>
+        <v>2121.844</v>
       </c>
       <c r="C108">
-        <v>352</v>
+        <v>2284</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B109">
-        <v>348.449</v>
+        <v>2125.094</v>
       </c>
       <c r="C109">
-        <v>375</v>
+        <v>2285</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B110">
-        <v>353.975</v>
+        <v>2119.449</v>
       </c>
       <c r="C110">
-        <v>391</v>
+        <v>2252</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B111">
-        <v>354.969</v>
+        <v>2132.258</v>
       </c>
       <c r="C111">
-        <v>409</v>
+        <v>2251</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B112">
-        <v>351.276</v>
+        <v>2135.947</v>
       </c>
       <c r="C112">
-        <v>416</v>
+        <v>2264</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B113">
-        <v>361.81</v>
+        <v>2137.335</v>
       </c>
       <c r="C113">
-        <v>430</v>
+        <v>2278</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B114">
-        <v>346.455</v>
+        <v>2125.63</v>
       </c>
       <c r="C114">
-        <v>468</v>
+        <v>2267</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B115">
-        <v>345.357</v>
+        <v>2132.514</v>
       </c>
       <c r="C115">
-        <v>472</v>
+        <v>2252</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B116">
-        <v>347.186</v>
+        <v>2127.748</v>
       </c>
       <c r="C116">
-        <v>448</v>
+        <v>2216</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B117">
-        <v>356.172</v>
+        <v>2121.565</v>
       </c>
       <c r="C117">
-        <v>436</v>
+        <v>2250</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B118">
-        <v>333.547</v>
+        <v>2178.735</v>
       </c>
       <c r="C118">
-        <v>421</v>
+        <v>2258</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B119">
-        <v>326.877</v>
+        <v>2176.146</v>
       </c>
       <c r="C119">
-        <v>394</v>
+        <v>2246</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B120">
-        <v>328.628</v>
+        <v>2173.474</v>
       </c>
       <c r="C120">
-        <v>359</v>
+        <v>2199</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B121">
-        <v>320.927</v>
+        <v>2167.727</v>
       </c>
       <c r="C121">
-        <v>329</v>
+        <v>2161</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B122">
-        <v>303.678</v>
+        <v>2164.497</v>
       </c>
       <c r="C122">
-        <v>279</v>
+        <v>2063</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B123">
-        <v>293.056</v>
+        <v>2177.459</v>
       </c>
       <c r="C123">
-        <v>246</v>
+        <v>2013</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B124">
-        <v>284.244</v>
+        <v>2195.562</v>
       </c>
       <c r="C124">
-        <v>223</v>
+        <v>2003</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B125">
-        <v>275.382</v>
+        <v>2220.964</v>
       </c>
       <c r="C125">
-        <v>194</v>
+        <v>1993</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B126">
-        <v>257.059</v>
+        <v>2213.556</v>
       </c>
       <c r="C126">
-        <v>157</v>
+        <v>1966</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B127">
-        <v>238.345</v>
+        <v>2208.366</v>
       </c>
       <c r="C127">
-        <v>131</v>
+        <v>1931</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B128">
-        <v>228.704</v>
+        <v>2205.51</v>
       </c>
       <c r="C128">
-        <v>98</v>
+        <v>1911</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B129">
-        <v>214.243</v>
+        <v>2207.71</v>
       </c>
       <c r="C129">
-        <v>73</v>
+        <v>1901</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B130">
-        <v>229.026</v>
+        <v>2166.95</v>
       </c>
       <c r="C130">
-        <v>64</v>
+        <v>1936</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B131">
-        <v>226.48</v>
+        <v>2151.582</v>
       </c>
       <c r="C131">
-        <v>66</v>
+        <v>1898</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B132">
-        <v>223.826</v>
+        <v>2122.157</v>
       </c>
       <c r="C132">
-        <v>63</v>
+        <v>1809</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B133">
-        <v>221.355</v>
+        <v>2107.632</v>
       </c>
       <c r="C133">
-        <v>61</v>
+        <v>1702</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B134">
-        <v>204.523</v>
+        <v>2008.521</v>
       </c>
       <c r="C134">
-        <v>66</v>
+        <v>1727</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B135">
-        <v>210.767</v>
+        <v>1988.378</v>
       </c>
       <c r="C135">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B136">
-        <v>215.808</v>
+        <v>1968.003</v>
       </c>
       <c r="C136">
-        <v>58</v>
+        <v>1772</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B137">
-        <v>221.519</v>
+        <v>1949.559</v>
       </c>
       <c r="C137">
-        <v>59</v>
+        <v>1682</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B138">
-        <v>231.147</v>
+        <v>1995.077</v>
       </c>
       <c r="C138">
-        <v>53</v>
+        <v>1622</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B139">
-        <v>239.129</v>
+        <v>1974.716</v>
       </c>
       <c r="C139">
-        <v>56</v>
+        <v>1555</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B140">
-        <v>250.918</v>
+        <v>1957.036</v>
       </c>
       <c r="C140">
-        <v>62</v>
+        <v>1550</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B141">
-        <v>260.606</v>
+        <v>1940.504</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1561</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B142">
-        <v>275.241</v>
+        <v>1819.321</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1545</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B143">
-        <v>287.181</v>
+        <v>1801.815</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1539</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3402,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B144">
-        <v>302.018</v>
+        <v>1784.579</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1599</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3419,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B145">
-        <v>317.543</v>
+        <v>1765.999</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1597</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +3436,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B146">
-        <v>348.313</v>
+        <v>1730.827</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1546</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B147">
-        <v>375.099</v>
+        <v>1703.079</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1522</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +3470,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B148">
-        <v>403.187</v>
+        <v>1675.186</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1480</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B149">
-        <v>430.833</v>
+        <v>1646.007</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B150">
-        <v>482.566</v>
+        <v>1586.548</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B151">
-        <v>526.181</v>
+        <v>1563.061</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B152">
-        <v>568.566</v>
+        <v>1539.32</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B153">
-        <v>611.28</v>
+        <v>1511.519</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B154">
-        <v>682.7670000000001</v>
+        <v>1513.295</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B155">
-        <v>733.467</v>
+        <v>1492.574</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B156">
-        <v>782.672</v>
+        <v>1472.17</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B157">
-        <v>831.625</v>
+        <v>1451.834</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B158">
-        <v>900.1319999999999</v>
+        <v>1478.755</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B159">
-        <v>949.564</v>
+        <v>1457.184</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B160">
-        <v>993.9589999999999</v>
+        <v>1436.075</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B161">
-        <v>1037.369</v>
+        <v>1416.53</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B162">
-        <v>1093.285</v>
+        <v>1391.006</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B163">
-        <v>1131.188</v>
+        <v>1382.72</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B164">
-        <v>1168.437</v>
+        <v>1377.459</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B165">
-        <v>1207.48</v>
+        <v>1371.863</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B166">
-        <v>1256.398</v>
+        <v>1353.84</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B167">
-        <v>1279.469</v>
+        <v>1345.745</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B168">
-        <v>1303.068</v>
+        <v>1336.994</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B169">
-        <v>1330.042</v>
+        <v>1328.238</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B170">
-        <v>1374.92</v>
+        <v>1310.1</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B171">
-        <v>1407.143</v>
+        <v>1296.716</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B172">
-        <v>1444.749</v>
+        <v>1285.568</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B173">
-        <v>1480.185</v>
+        <v>1271.845</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B174">
-        <v>1489.991</v>
+        <v>1255.245</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B175">
-        <v>1518.608</v>
+        <v>1240.48</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B176">
-        <v>1547.712</v>
+        <v>1226.82</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B177">
-        <v>1579.435</v>
+        <v>1211.221</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B178">
-        <v>1650.331</v>
+        <v>1165.87</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B179">
-        <v>1661.088</v>
+        <v>1150.827</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B180">
-        <v>1668.145</v>
+        <v>1135.978</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B181">
-        <v>1674.912</v>
+        <v>1120.161</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B182">
-        <v>1680.104</v>
+        <v>1093.194</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B183">
-        <v>1679.039</v>
+        <v>1075.387</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B184">
-        <v>1679.32</v>
+        <v>1059.155</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B185">
-        <v>1678.328</v>
+        <v>1042.227</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B186">
-        <v>1671.927</v>
+        <v>1010.275</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B187">
-        <v>1661.971</v>
+        <v>992.931</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B188">
-        <v>1649.49</v>
+        <v>975.061</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B189">
-        <v>1636.378</v>
+        <v>958.145</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.05.20261</t>
-  </si>
-  <si>
-    <t>20.05.20262</t>
-  </si>
-  <si>
-    <t>20.05.20263</t>
-  </si>
-  <si>
-    <t>20.05.20264</t>
-  </si>
-  <si>
-    <t>20.05.20265</t>
-  </si>
-  <si>
-    <t>20.05.20266</t>
-  </si>
-  <si>
-    <t>20.05.20267</t>
-  </si>
-  <si>
-    <t>20.05.20268</t>
-  </si>
-  <si>
-    <t>20.05.20269</t>
-  </si>
-  <si>
-    <t>20.05.202610</t>
-  </si>
-  <si>
-    <t>20.05.202611</t>
-  </si>
-  <si>
-    <t>20.05.202612</t>
-  </si>
-  <si>
-    <t>20.05.202613</t>
-  </si>
-  <si>
-    <t>20.05.202614</t>
-  </si>
-  <si>
-    <t>20.05.202615</t>
-  </si>
-  <si>
-    <t>20.05.202616</t>
-  </si>
-  <si>
-    <t>20.05.202617</t>
-  </si>
-  <si>
-    <t>20.05.202618</t>
-  </si>
-  <si>
-    <t>20.05.202619</t>
-  </si>
-  <si>
-    <t>20.05.202620</t>
-  </si>
-  <si>
-    <t>20.05.202621</t>
-  </si>
-  <si>
-    <t>20.05.202622</t>
-  </si>
-  <si>
-    <t>20.05.202623</t>
-  </si>
-  <si>
-    <t>20.05.202624</t>
-  </si>
-  <si>
-    <t>20.05.202625</t>
-  </si>
-  <si>
-    <t>20.05.202626</t>
-  </si>
-  <si>
-    <t>20.05.202627</t>
-  </si>
-  <si>
-    <t>20.05.202628</t>
-  </si>
-  <si>
-    <t>20.05.202629</t>
-  </si>
-  <si>
-    <t>20.05.202630</t>
-  </si>
-  <si>
-    <t>20.05.202631</t>
-  </si>
-  <si>
-    <t>20.05.202632</t>
-  </si>
-  <si>
-    <t>20.05.202633</t>
-  </si>
-  <si>
-    <t>20.05.202634</t>
-  </si>
-  <si>
-    <t>20.05.202635</t>
-  </si>
-  <si>
-    <t>20.05.202636</t>
-  </si>
-  <si>
-    <t>20.05.202637</t>
-  </si>
-  <si>
-    <t>20.05.202638</t>
-  </si>
-  <si>
-    <t>20.05.202639</t>
-  </si>
-  <si>
-    <t>20.05.202640</t>
-  </si>
-  <si>
-    <t>20.05.202641</t>
-  </si>
-  <si>
-    <t>20.05.202642</t>
-  </si>
-  <si>
-    <t>20.05.202643</t>
-  </si>
-  <si>
-    <t>20.05.202644</t>
-  </si>
-  <si>
-    <t>20.05.202645</t>
-  </si>
-  <si>
-    <t>20.05.202646</t>
-  </si>
-  <si>
-    <t>20.05.202647</t>
-  </si>
-  <si>
-    <t>20.05.202648</t>
-  </si>
-  <si>
-    <t>20.05.202649</t>
-  </si>
-  <si>
-    <t>20.05.202650</t>
-  </si>
-  <si>
-    <t>20.05.202651</t>
-  </si>
-  <si>
-    <t>20.05.202652</t>
-  </si>
-  <si>
-    <t>20.05.202653</t>
-  </si>
-  <si>
-    <t>20.05.202654</t>
-  </si>
-  <si>
-    <t>20.05.202655</t>
-  </si>
-  <si>
-    <t>20.05.202656</t>
-  </si>
-  <si>
-    <t>20.05.202657</t>
-  </si>
-  <si>
-    <t>20.05.202658</t>
-  </si>
-  <si>
-    <t>20.05.202659</t>
-  </si>
-  <si>
-    <t>20.05.202660</t>
-  </si>
-  <si>
-    <t>20.05.202661</t>
-  </si>
-  <si>
-    <t>20.05.202662</t>
-  </si>
-  <si>
-    <t>20.05.202663</t>
-  </si>
-  <si>
-    <t>20.05.202664</t>
-  </si>
-  <si>
-    <t>20.05.202665</t>
-  </si>
-  <si>
-    <t>20.05.202666</t>
-  </si>
-  <si>
-    <t>20.05.202667</t>
-  </si>
-  <si>
-    <t>20.05.202668</t>
-  </si>
-  <si>
-    <t>20.05.202669</t>
-  </si>
-  <si>
-    <t>20.05.202670</t>
-  </si>
-  <si>
-    <t>20.05.202671</t>
-  </si>
-  <si>
-    <t>20.05.202672</t>
-  </si>
-  <si>
-    <t>20.05.202673</t>
-  </si>
-  <si>
-    <t>20.05.202674</t>
-  </si>
-  <si>
-    <t>20.05.202675</t>
-  </si>
-  <si>
-    <t>20.05.202676</t>
-  </si>
-  <si>
-    <t>20.05.202677</t>
-  </si>
-  <si>
-    <t>20.05.202678</t>
-  </si>
-  <si>
-    <t>20.05.202679</t>
-  </si>
-  <si>
-    <t>20.05.202680</t>
-  </si>
-  <si>
-    <t>20.05.202681</t>
-  </si>
-  <si>
-    <t>20.05.202682</t>
-  </si>
-  <si>
-    <t>20.05.202683</t>
-  </si>
-  <si>
-    <t>20.05.202684</t>
-  </si>
-  <si>
-    <t>20.05.202685</t>
-  </si>
-  <si>
-    <t>20.05.202686</t>
-  </si>
-  <si>
-    <t>20.05.202687</t>
-  </si>
-  <si>
-    <t>20.05.202688</t>
-  </si>
-  <si>
-    <t>20.05.202689</t>
-  </si>
-  <si>
-    <t>20.05.202690</t>
-  </si>
-  <si>
-    <t>20.05.202691</t>
-  </si>
-  <si>
-    <t>20.05.202692</t>
-  </si>
-  <si>
-    <t>20.05.202693</t>
-  </si>
-  <si>
-    <t>20.05.202694</t>
-  </si>
-  <si>
-    <t>20.05.202695</t>
-  </si>
-  <si>
-    <t>20.05.202696</t>
-  </si>
-  <si>
     <t>21.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>21.05.202696</t>
+  </si>
+  <si>
+    <t>22.05.20261</t>
+  </si>
+  <si>
+    <t>22.05.20262</t>
+  </si>
+  <si>
+    <t>22.05.20263</t>
+  </si>
+  <si>
+    <t>22.05.20264</t>
+  </si>
+  <si>
+    <t>22.05.20265</t>
+  </si>
+  <si>
+    <t>22.05.20266</t>
+  </si>
+  <si>
+    <t>22.05.20267</t>
+  </si>
+  <si>
+    <t>22.05.20268</t>
+  </si>
+  <si>
+    <t>22.05.20269</t>
+  </si>
+  <si>
+    <t>22.05.202610</t>
+  </si>
+  <si>
+    <t>22.05.202611</t>
+  </si>
+  <si>
+    <t>22.05.202612</t>
+  </si>
+  <si>
+    <t>22.05.202613</t>
+  </si>
+  <si>
+    <t>22.05.202614</t>
+  </si>
+  <si>
+    <t>22.05.202615</t>
+  </si>
+  <si>
+    <t>22.05.202616</t>
+  </si>
+  <si>
+    <t>22.05.202617</t>
+  </si>
+  <si>
+    <t>22.05.202618</t>
+  </si>
+  <si>
+    <t>22.05.202619</t>
+  </si>
+  <si>
+    <t>22.05.202620</t>
+  </si>
+  <si>
+    <t>22.05.202621</t>
+  </si>
+  <si>
+    <t>22.05.202622</t>
+  </si>
+  <si>
+    <t>22.05.202623</t>
+  </si>
+  <si>
+    <t>22.05.202624</t>
+  </si>
+  <si>
+    <t>22.05.202625</t>
+  </si>
+  <si>
+    <t>22.05.202626</t>
+  </si>
+  <si>
+    <t>22.05.202627</t>
+  </si>
+  <si>
+    <t>22.05.202628</t>
+  </si>
+  <si>
+    <t>22.05.202629</t>
+  </si>
+  <si>
+    <t>22.05.202630</t>
+  </si>
+  <si>
+    <t>22.05.202631</t>
+  </si>
+  <si>
+    <t>22.05.202632</t>
+  </si>
+  <si>
+    <t>22.05.202633</t>
+  </si>
+  <si>
+    <t>22.05.202634</t>
+  </si>
+  <si>
+    <t>22.05.202635</t>
+  </si>
+  <si>
+    <t>22.05.202636</t>
+  </si>
+  <si>
+    <t>22.05.202637</t>
+  </si>
+  <si>
+    <t>22.05.202638</t>
+  </si>
+  <si>
+    <t>22.05.202639</t>
+  </si>
+  <si>
+    <t>22.05.202640</t>
+  </si>
+  <si>
+    <t>22.05.202641</t>
+  </si>
+  <si>
+    <t>22.05.202642</t>
+  </si>
+  <si>
+    <t>22.05.202643</t>
+  </si>
+  <si>
+    <t>22.05.202644</t>
+  </si>
+  <si>
+    <t>22.05.202645</t>
+  </si>
+  <si>
+    <t>22.05.202646</t>
+  </si>
+  <si>
+    <t>22.05.202647</t>
+  </si>
+  <si>
+    <t>22.05.202648</t>
+  </si>
+  <si>
+    <t>22.05.202649</t>
+  </si>
+  <si>
+    <t>22.05.202650</t>
+  </si>
+  <si>
+    <t>22.05.202651</t>
+  </si>
+  <si>
+    <t>22.05.202652</t>
+  </si>
+  <si>
+    <t>22.05.202653</t>
+  </si>
+  <si>
+    <t>22.05.202654</t>
+  </si>
+  <si>
+    <t>22.05.202655</t>
+  </si>
+  <si>
+    <t>22.05.202656</t>
+  </si>
+  <si>
+    <t>22.05.202657</t>
+  </si>
+  <si>
+    <t>22.05.202658</t>
+  </si>
+  <si>
+    <t>22.05.202659</t>
+  </si>
+  <si>
+    <t>22.05.202660</t>
+  </si>
+  <si>
+    <t>22.05.202661</t>
+  </si>
+  <si>
+    <t>22.05.202662</t>
+  </si>
+  <si>
+    <t>22.05.202663</t>
+  </si>
+  <si>
+    <t>22.05.202664</t>
+  </si>
+  <si>
+    <t>22.05.202665</t>
+  </si>
+  <si>
+    <t>22.05.202666</t>
+  </si>
+  <si>
+    <t>22.05.202667</t>
+  </si>
+  <si>
+    <t>22.05.202668</t>
+  </si>
+  <si>
+    <t>22.05.202669</t>
+  </si>
+  <si>
+    <t>22.05.202670</t>
+  </si>
+  <si>
+    <t>22.05.202671</t>
+  </si>
+  <si>
+    <t>22.05.202672</t>
+  </si>
+  <si>
+    <t>22.05.202673</t>
+  </si>
+  <si>
+    <t>22.05.202674</t>
+  </si>
+  <si>
+    <t>22.05.202675</t>
+  </si>
+  <si>
+    <t>22.05.202676</t>
+  </si>
+  <si>
+    <t>22.05.202677</t>
+  </si>
+  <si>
+    <t>22.05.202678</t>
+  </si>
+  <si>
+    <t>22.05.202679</t>
+  </si>
+  <si>
+    <t>22.05.202680</t>
+  </si>
+  <si>
+    <t>22.05.202681</t>
+  </si>
+  <si>
+    <t>22.05.202682</t>
+  </si>
+  <si>
+    <t>22.05.202683</t>
+  </si>
+  <si>
+    <t>22.05.202684</t>
+  </si>
+  <si>
+    <t>22.05.202685</t>
+  </si>
+  <si>
+    <t>22.05.202686</t>
+  </si>
+  <si>
+    <t>22.05.202687</t>
+  </si>
+  <si>
+    <t>22.05.202688</t>
+  </si>
+  <si>
+    <t>22.05.202689</t>
+  </si>
+  <si>
+    <t>22.05.202690</t>
+  </si>
+  <si>
+    <t>22.05.202691</t>
+  </si>
+  <si>
+    <t>22.05.202692</t>
+  </si>
+  <si>
+    <t>22.05.202693</t>
+  </si>
+  <si>
+    <t>22.05.202694</t>
+  </si>
+  <si>
+    <t>22.05.202695</t>
+  </si>
+  <si>
+    <t>22.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B2">
-        <v>1129.64</v>
+        <v>2011.594</v>
       </c>
       <c r="C2">
-        <v>1302</v>
+        <v>2186</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46162.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
-        <v>1167.958</v>
+        <v>2014.513</v>
       </c>
       <c r="C3">
-        <v>1283</v>
+        <v>2176</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46162.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
-        <v>1201.558</v>
+        <v>2021.993</v>
       </c>
       <c r="C4">
-        <v>1263</v>
+        <v>2208</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46162.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
-        <v>1242.202</v>
+        <v>2038.267</v>
       </c>
       <c r="C5">
-        <v>1277</v>
+        <v>2202</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46162.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
-        <v>1268.558</v>
+        <v>2082.547</v>
       </c>
       <c r="C6">
-        <v>1289</v>
+        <v>2250</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46162.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
-        <v>1310.456</v>
+        <v>2102.276</v>
       </c>
       <c r="C7">
-        <v>1293</v>
+        <v>2300</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46162.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
-        <v>1349.938</v>
+        <v>2116.323</v>
       </c>
       <c r="C8">
-        <v>1316</v>
+        <v>2336</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46162.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
-        <v>1368.7</v>
+        <v>2125.058</v>
       </c>
       <c r="C9">
-        <v>1346</v>
+        <v>2354</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46162.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
-        <v>1332.897</v>
+        <v>2100.509</v>
       </c>
       <c r="C10">
-        <v>1396</v>
+        <v>2366</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46162.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
-        <v>1359.917</v>
+        <v>2114.928</v>
       </c>
       <c r="C11">
-        <v>1442</v>
+        <v>2324</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46162.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
-        <v>1387.488</v>
+        <v>2121.844</v>
       </c>
       <c r="C12">
-        <v>1499</v>
+        <v>2284</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46162.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
-        <v>1416.43</v>
+        <v>2125.094</v>
       </c>
       <c r="C13">
-        <v>1555</v>
+        <v>2285</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46162.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
-        <v>1452.704</v>
+        <v>2119.449</v>
       </c>
       <c r="C14">
-        <v>1612</v>
+        <v>2252</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46162.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
-        <v>1467.688</v>
+        <v>2132.258</v>
       </c>
       <c r="C15">
-        <v>1672</v>
+        <v>2251</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46162.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
-        <v>1488.706</v>
+        <v>2135.947</v>
       </c>
       <c r="C16">
-        <v>1734</v>
+        <v>2264</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46162.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
-        <v>1520.647</v>
+        <v>2137.335</v>
       </c>
       <c r="C17">
-        <v>1756</v>
+        <v>2278</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46162.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
-        <v>1613.367</v>
+        <v>2125.63</v>
       </c>
       <c r="C18">
-        <v>1794</v>
+        <v>2267</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46162.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>1637.57</v>
+        <v>2132.514</v>
       </c>
       <c r="C19">
-        <v>1854</v>
+        <v>2252</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46162.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
-        <v>1660.04</v>
+        <v>2127.748</v>
       </c>
       <c r="C20">
-        <v>1902</v>
+        <v>2216</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46162.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>1683.581</v>
+        <v>2121.565</v>
       </c>
       <c r="C21">
-        <v>1958</v>
+        <v>2250</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46162.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>1735.004</v>
+        <v>2178.735</v>
       </c>
       <c r="C22">
-        <v>2006</v>
+        <v>2258</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46162.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>1731.651</v>
+        <v>2176.146</v>
       </c>
       <c r="C23">
-        <v>1998</v>
+        <v>2246</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46162.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>1728.585</v>
+        <v>2173.474</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2199</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46162.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>1738.854</v>
+        <v>2167.727</v>
       </c>
       <c r="C25">
-        <v>1983</v>
+        <v>2161</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46162.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>1753.739</v>
+        <v>2164.497</v>
       </c>
       <c r="C26">
-        <v>1978</v>
+        <v>2063</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46162.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>1753.659</v>
+        <v>2177.459</v>
       </c>
       <c r="C27">
-        <v>1963</v>
+        <v>2013</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46162.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>1754.425</v>
+        <v>2195.562</v>
       </c>
       <c r="C28">
-        <v>1899</v>
+        <v>2003</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46162.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>1758.572</v>
+        <v>2220.964</v>
       </c>
       <c r="C29">
-        <v>1840</v>
+        <v>1993</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46162.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>1744.419</v>
+        <v>2213.556</v>
       </c>
       <c r="C30">
-        <v>1779</v>
+        <v>1966</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46162.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>1748.146</v>
+        <v>2208.366</v>
       </c>
       <c r="C31">
-        <v>1751</v>
+        <v>1931</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46162.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>1768.214</v>
+        <v>2205.51</v>
       </c>
       <c r="C32">
-        <v>1742</v>
+        <v>1911</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46162.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>1779.365</v>
+        <v>2207.71</v>
       </c>
       <c r="C33">
-        <v>1748</v>
+        <v>1901</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46162.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>1785.14</v>
+        <v>2166.95</v>
       </c>
       <c r="C34">
-        <v>1714</v>
+        <v>1936</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46162.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>1795.802</v>
+        <v>2151.582</v>
       </c>
       <c r="C35">
-        <v>1732</v>
+        <v>1898</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46162.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>1820.914</v>
+        <v>2122.157</v>
       </c>
       <c r="C36">
-        <v>1731</v>
+        <v>1809</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46162.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>1838.863</v>
+        <v>2107.632</v>
       </c>
       <c r="C37">
-        <v>1759</v>
+        <v>1702</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46162.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>1911.31</v>
+        <v>2008.521</v>
       </c>
       <c r="C38">
-        <v>1813</v>
+        <v>1727</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46162.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>1922.162</v>
+        <v>1988.378</v>
       </c>
       <c r="C39">
-        <v>1873</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46162.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>1934.724</v>
+        <v>1968.003</v>
       </c>
       <c r="C40">
-        <v>1938</v>
+        <v>1772</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46162.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>1943.48</v>
+        <v>1949.559</v>
       </c>
       <c r="C41">
-        <v>1968</v>
+        <v>1682</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46162.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>1968.803</v>
+        <v>1995.077</v>
       </c>
       <c r="C42">
-        <v>2026</v>
+        <v>1622</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46162.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>1974.4</v>
+        <v>1974.716</v>
       </c>
       <c r="C43">
-        <v>2054</v>
+        <v>1555</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46162.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>1983.251</v>
+        <v>1957.036</v>
       </c>
       <c r="C44">
-        <v>2057</v>
+        <v>1550</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46162.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>1990.01</v>
+        <v>1940.504</v>
       </c>
       <c r="C45">
-        <v>2048</v>
+        <v>1561</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46162.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>2001.364</v>
+        <v>1819.321</v>
       </c>
       <c r="C46">
-        <v>1998</v>
+        <v>1545</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46162.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>1997.443</v>
+        <v>1801.815</v>
       </c>
       <c r="C47">
-        <v>2020</v>
+        <v>1539</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46162.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>1993.376</v>
+        <v>1784.579</v>
       </c>
       <c r="C48">
-        <v>2017</v>
+        <v>1599</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46162.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>1989.152</v>
+        <v>1765.999</v>
       </c>
       <c r="C49">
-        <v>2027</v>
+        <v>1597</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46162.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
-        <v>1959.322</v>
+        <v>1730.827</v>
       </c>
       <c r="C50">
-        <v>2009</v>
+        <v>1546</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46162.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>1941.208</v>
+        <v>1703.079</v>
       </c>
       <c r="C51">
-        <v>1952</v>
+        <v>1522</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46162.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>1924.931</v>
+        <v>1675.186</v>
       </c>
       <c r="C52">
-        <v>1906</v>
+        <v>1480</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46162.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>1908.047</v>
+        <v>1646.007</v>
       </c>
       <c r="C53">
-        <v>1868</v>
+        <v>1365</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46162.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
-        <v>1925.643</v>
+        <v>1586.548</v>
       </c>
       <c r="C54">
-        <v>1839</v>
+        <v>1306</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46162.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B55">
-        <v>1909.724</v>
+        <v>1563.061</v>
       </c>
       <c r="C55">
-        <v>1842</v>
+        <v>1222</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46162.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B56">
-        <v>1893.499</v>
+        <v>1539.32</v>
       </c>
       <c r="C56">
-        <v>1865</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46162.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B57">
-        <v>1877.917</v>
+        <v>1511.519</v>
       </c>
       <c r="C57">
-        <v>1880</v>
+        <v>1219</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46162.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B58">
-        <v>1866.439</v>
+        <v>1513.295</v>
       </c>
       <c r="C58">
-        <v>1933</v>
+        <v>1319</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46162.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B59">
-        <v>1841.737</v>
+        <v>1492.574</v>
       </c>
       <c r="C59">
-        <v>1986</v>
+        <v>1446</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46162.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B60">
-        <v>1816.365</v>
+        <v>1472.17</v>
       </c>
       <c r="C60">
-        <v>2014</v>
+        <v>1557</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46162.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B61">
-        <v>1793.937</v>
+        <v>1451.834</v>
       </c>
       <c r="C61">
-        <v>2058</v>
+        <v>1699</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46162.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B62">
-        <v>1754.083</v>
+        <v>1478.755</v>
       </c>
       <c r="C62">
-        <v>2051</v>
+        <v>1664</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46162.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B63">
-        <v>1726.862</v>
+        <v>1457.184</v>
       </c>
       <c r="C63">
-        <v>2000</v>
+        <v>1577</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46162.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B64">
-        <v>1698.727</v>
+        <v>1436.075</v>
       </c>
       <c r="C64">
-        <v>2045</v>
+        <v>1484</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46162.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B65">
-        <v>1671.19</v>
+        <v>1416.53</v>
       </c>
       <c r="C65">
-        <v>2037</v>
+        <v>1389</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46162.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B66">
-        <v>1542.963</v>
+        <v>1391.006</v>
       </c>
       <c r="C66">
-        <v>2128</v>
+        <v>1564</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46162.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B67">
-        <v>1523.353</v>
+        <v>1382.72</v>
       </c>
       <c r="C67">
-        <v>2114</v>
+        <v>1617</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46162.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B68">
-        <v>1503.867</v>
+        <v>1377.459</v>
       </c>
       <c r="C68">
-        <v>2169</v>
+        <v>1675</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46162.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B69">
-        <v>1483.878</v>
+        <v>1371.863</v>
       </c>
       <c r="C69">
-        <v>2138</v>
+        <v>1687</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46162.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B70">
-        <v>1426.847</v>
+        <v>1353.84</v>
       </c>
       <c r="C70">
-        <v>2174</v>
+        <v>1683</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46162.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B71">
-        <v>1398.01</v>
+        <v>1345.745</v>
       </c>
       <c r="C71">
-        <v>2222</v>
+        <v>1634</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46162.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B72">
-        <v>1370.595</v>
+        <v>1336.994</v>
       </c>
       <c r="C72">
-        <v>2226</v>
+        <v>1609</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46162.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B73">
-        <v>1344.172</v>
+        <v>1328.238</v>
       </c>
       <c r="C73">
-        <v>2216</v>
+        <v>1599</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46162.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B74">
-        <v>1335.305</v>
+        <v>1310.1</v>
       </c>
       <c r="C74">
-        <v>2210</v>
+        <v>1619</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46162.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B75">
-        <v>1331.903</v>
+        <v>1296.716</v>
       </c>
       <c r="C75">
-        <v>2245</v>
+        <v>1637</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46162.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B76">
-        <v>1328.172</v>
+        <v>1285.568</v>
       </c>
       <c r="C76">
-        <v>2236</v>
+        <v>1622</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46162.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B77">
-        <v>1320.086</v>
+        <v>1271.845</v>
       </c>
       <c r="C77">
-        <v>2222</v>
+        <v>1603</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46162.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B78">
-        <v>1340.229</v>
+        <v>1255.245</v>
       </c>
       <c r="C78">
-        <v>2233</v>
+        <v>1551</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46162.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B79">
-        <v>1358.072</v>
+        <v>1240.48</v>
       </c>
       <c r="C79">
-        <v>2240</v>
+        <v>1519</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46162.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B80">
-        <v>1375.873</v>
+        <v>1226.82</v>
       </c>
       <c r="C80">
-        <v>2163</v>
+        <v>1497</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46162.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B81">
-        <v>1391.265</v>
+        <v>1211.221</v>
       </c>
       <c r="C81">
-        <v>2102</v>
+        <v>1507</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46162.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B82">
-        <v>1406.429</v>
+        <v>1165.87</v>
       </c>
       <c r="C82">
-        <v>2076</v>
+        <v>1437</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46162.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B83">
-        <v>1424.4</v>
+        <v>1150.827</v>
       </c>
       <c r="C83">
-        <v>2072</v>
+        <v>1390</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46162.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B84">
-        <v>1443.657</v>
+        <v>1135.978</v>
       </c>
       <c r="C84">
-        <v>2089</v>
+        <v>1397</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46162.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B85">
-        <v>1464.84</v>
+        <v>1120.161</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1396</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46162.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B86">
-        <v>1498.522</v>
+        <v>1093.194</v>
       </c>
       <c r="C86">
-        <v>2124</v>
+        <v>1341</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46162.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B87">
-        <v>1516.046</v>
+        <v>1075.387</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1319</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46162.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B88">
-        <v>1536.581</v>
+        <v>1059.155</v>
       </c>
       <c r="C88">
-        <v>2143</v>
+        <v>1284</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46162.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B89">
-        <v>1558.249</v>
+        <v>1042.227</v>
       </c>
       <c r="C89">
-        <v>2137</v>
+        <v>1301</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46162.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B90">
-        <v>1589.975</v>
+        <v>1010.275</v>
       </c>
       <c r="C90">
-        <v>2128</v>
+        <v>1296</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46162.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B91">
-        <v>1608.573</v>
+        <v>992.931</v>
       </c>
       <c r="C91">
-        <v>2122</v>
+        <v>1262</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46162.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B92">
-        <v>1629.277</v>
+        <v>975.061</v>
       </c>
       <c r="C92">
-        <v>2133</v>
+        <v>1199</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46162.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B93">
-        <v>1651.253</v>
+        <v>958.145</v>
       </c>
       <c r="C93">
-        <v>2115</v>
+        <v>1132</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46162.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B94">
-        <v>1825.457</v>
+        <v>945.765</v>
       </c>
       <c r="C94">
-        <v>2143</v>
+        <v>1102</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46162.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B95">
-        <v>1858.346</v>
+        <v>950.021</v>
       </c>
       <c r="C95">
-        <v>2173</v>
+        <v>1066</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46162.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B96">
-        <v>1879.475</v>
+        <v>923.399</v>
       </c>
       <c r="C96">
-        <v>2186</v>
+        <v>1012</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46162.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B97">
-        <v>1912.949</v>
+        <v>901.6950000000001</v>
       </c>
       <c r="C97">
-        <v>2196</v>
+        <v>971</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98">
-        <v>2011.594</v>
+        <v>881.374</v>
       </c>
       <c r="C98">
-        <v>2186</v>
+        <v>941</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B99">
-        <v>2014.513</v>
+        <v>870.271</v>
       </c>
       <c r="C99">
-        <v>2176</v>
+        <v>921</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B100">
-        <v>2021.993</v>
+        <v>851.846</v>
       </c>
       <c r="C100">
-        <v>2208</v>
+        <v>881</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B101">
-        <v>2038.267</v>
+        <v>839.737</v>
       </c>
       <c r="C101">
-        <v>2202</v>
+        <v>872</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B102">
-        <v>2082.547</v>
+        <v>807.894</v>
       </c>
       <c r="C102">
-        <v>2250</v>
+        <v>864</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B103">
-        <v>2102.276</v>
+        <v>809.749</v>
       </c>
       <c r="C103">
-        <v>2300</v>
+        <v>871</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B104">
-        <v>2116.323</v>
+        <v>801.558</v>
       </c>
       <c r="C104">
-        <v>2336</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B105">
-        <v>2125.058</v>
+        <v>807.412</v>
       </c>
       <c r="C105">
-        <v>2354</v>
+        <v>870</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B106">
-        <v>2100.509</v>
+        <v>800.36</v>
       </c>
       <c r="C106">
-        <v>2366</v>
+        <v>881</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B107">
-        <v>2114.928</v>
+        <v>809.723</v>
       </c>
       <c r="C107">
-        <v>2324</v>
+        <v>879</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B108">
-        <v>2121.844</v>
+        <v>808.6660000000001</v>
       </c>
       <c r="C108">
-        <v>2284</v>
+        <v>878</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B109">
-        <v>2125.094</v>
+        <v>812.662</v>
       </c>
       <c r="C109">
-        <v>2285</v>
+        <v>867</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B110">
-        <v>2119.449</v>
+        <v>817.691</v>
       </c>
       <c r="C110">
-        <v>2252</v>
+        <v>870</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B111">
-        <v>2132.258</v>
+        <v>823.0549999999999</v>
       </c>
       <c r="C111">
-        <v>2251</v>
+        <v>869</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B112">
-        <v>2135.947</v>
+        <v>825.125</v>
       </c>
       <c r="C112">
-        <v>2264</v>
+        <v>837</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B113">
-        <v>2137.335</v>
+        <v>834.793</v>
       </c>
       <c r="C113">
-        <v>2278</v>
+        <v>832</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B114">
-        <v>2125.63</v>
+        <v>804.628</v>
       </c>
       <c r="C114">
-        <v>2267</v>
+        <v>818</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B115">
-        <v>2132.514</v>
+        <v>811.3869999999999</v>
       </c>
       <c r="C115">
-        <v>2252</v>
+        <v>804</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B116">
-        <v>2127.748</v>
+        <v>817.679</v>
       </c>
       <c r="C116">
-        <v>2216</v>
+        <v>798</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B117">
-        <v>2121.565</v>
+        <v>830.405</v>
       </c>
       <c r="C117">
-        <v>2250</v>
+        <v>784</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B118">
-        <v>2178.735</v>
+        <v>831.578</v>
       </c>
       <c r="C118">
-        <v>2258</v>
+        <v>773</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B119">
-        <v>2176.146</v>
+        <v>833.5</v>
       </c>
       <c r="C119">
-        <v>2246</v>
+        <v>755</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B120">
-        <v>2173.474</v>
+        <v>836.212</v>
       </c>
       <c r="C120">
-        <v>2199</v>
+        <v>714</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B121">
-        <v>2167.727</v>
+        <v>837.139</v>
       </c>
       <c r="C121">
-        <v>2161</v>
+        <v>680</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B122">
-        <v>2164.497</v>
+        <v>825.7619999999999</v>
       </c>
       <c r="C122">
-        <v>2063</v>
+        <v>692</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B123">
-        <v>2177.459</v>
+        <v>826.002</v>
       </c>
       <c r="C123">
-        <v>2013</v>
+        <v>685</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B124">
-        <v>2195.562</v>
+        <v>818.394</v>
       </c>
       <c r="C124">
-        <v>2003</v>
+        <v>692</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B125">
-        <v>2220.964</v>
+        <v>815.753</v>
       </c>
       <c r="C125">
-        <v>1993</v>
+        <v>707</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B126">
-        <v>2213.556</v>
+        <v>808.288</v>
       </c>
       <c r="C126">
-        <v>1966</v>
+        <v>705</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B127">
-        <v>2208.366</v>
+        <v>811.279</v>
       </c>
       <c r="C127">
-        <v>1931</v>
+        <v>669</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B128">
-        <v>2205.51</v>
+        <v>805.973</v>
       </c>
       <c r="C128">
-        <v>1911</v>
+        <v>649</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B129">
-        <v>2207.71</v>
+        <v>784.494</v>
       </c>
       <c r="C129">
-        <v>1901</v>
+        <v>635</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B130">
-        <v>2166.95</v>
+        <v>733.323</v>
       </c>
       <c r="C130">
-        <v>1936</v>
+        <v>629</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B131">
-        <v>2151.582</v>
+        <v>732.0549999999999</v>
       </c>
       <c r="C131">
-        <v>1898</v>
+        <v>635</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B132">
-        <v>2122.157</v>
+        <v>715.103</v>
       </c>
       <c r="C132">
-        <v>1809</v>
+        <v>612</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B133">
-        <v>2107.632</v>
+        <v>713.745</v>
       </c>
       <c r="C133">
-        <v>1702</v>
+        <v>607</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B134">
-        <v>2008.521</v>
+        <v>728.112</v>
       </c>
       <c r="C134">
-        <v>1727</v>
+        <v>600</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B135">
-        <v>1988.378</v>
+        <v>718.299</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B136">
-        <v>1968.003</v>
+        <v>708.554</v>
       </c>
       <c r="C136">
-        <v>1772</v>
+        <v>569</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B137">
-        <v>1949.559</v>
+        <v>699.423</v>
       </c>
       <c r="C137">
-        <v>1682</v>
+        <v>560</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B138">
-        <v>1995.077</v>
+        <v>747.523</v>
       </c>
       <c r="C138">
-        <v>1622</v>
+        <v>551</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B139">
-        <v>1974.716</v>
+        <v>739.575</v>
       </c>
       <c r="C139">
-        <v>1555</v>
+        <v>539</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B140">
-        <v>1957.036</v>
+        <v>732.17</v>
       </c>
       <c r="C140">
-        <v>1550</v>
+        <v>516</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B141">
-        <v>1940.504</v>
+        <v>725.133</v>
       </c>
       <c r="C141">
-        <v>1561</v>
+        <v>506</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B142">
-        <v>1819.321</v>
+        <v>729.981</v>
       </c>
       <c r="C142">
-        <v>1545</v>
+        <v>527</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B143">
-        <v>1801.815</v>
+        <v>727.908</v>
       </c>
       <c r="C143">
-        <v>1539</v>
+        <v>512</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3402,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B144">
-        <v>1784.579</v>
+        <v>687.395</v>
       </c>
       <c r="C144">
-        <v>1599</v>
+        <v>492</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3419,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B145">
-        <v>1765.999</v>
+        <v>681.1900000000001</v>
       </c>
       <c r="C145">
-        <v>1597</v>
+        <v>478</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +3436,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B146">
-        <v>1730.827</v>
+        <v>675.616</v>
       </c>
       <c r="C146">
-        <v>1546</v>
+        <v>464</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B147">
-        <v>1703.079</v>
+        <v>668.851</v>
       </c>
       <c r="C147">
-        <v>1522</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +3470,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B148">
-        <v>1675.186</v>
+        <v>662.078</v>
       </c>
       <c r="C148">
-        <v>1480</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B149">
-        <v>1646.007</v>
+        <v>655.849</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B150">
-        <v>1586.548</v>
+        <v>647.7569999999999</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B151">
-        <v>1563.061</v>
+        <v>636.329</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B152">
-        <v>1539.32</v>
+        <v>613.67</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B153">
-        <v>1511.519</v>
+        <v>590.326</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B154">
-        <v>1513.295</v>
+        <v>609.354</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B155">
-        <v>1492.574</v>
+        <v>598.149</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B156">
-        <v>1472.17</v>
+        <v>584.995</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B157">
-        <v>1451.834</v>
+        <v>604.95</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B158">
-        <v>1478.755</v>
+        <v>584.232</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B159">
-        <v>1457.184</v>
+        <v>571.936</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B160">
-        <v>1436.075</v>
+        <v>562.206</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B161">
-        <v>1416.53</v>
+        <v>551.4589999999999</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B162">
-        <v>1391.006</v>
+        <v>540.091</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B163">
-        <v>1382.72</v>
+        <v>531.514</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B164">
-        <v>1377.459</v>
+        <v>523.713</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B165">
-        <v>1371.863</v>
+        <v>513.831</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B166">
-        <v>1353.84</v>
+        <v>498.973</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B167">
-        <v>1345.745</v>
+        <v>495.552</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B168">
-        <v>1336.994</v>
+        <v>492.963</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B169">
-        <v>1328.238</v>
+        <v>487.806</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B170">
-        <v>1310.1</v>
+        <v>472.674</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B171">
-        <v>1296.716</v>
+        <v>475.666</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B172">
-        <v>1285.568</v>
+        <v>477.614</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B173">
-        <v>1271.845</v>
+        <v>479.918</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B174">
-        <v>1255.245</v>
+        <v>454.593</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B175">
-        <v>1240.48</v>
+        <v>464.329</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B176">
-        <v>1226.82</v>
+        <v>475.979</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B177">
-        <v>1211.221</v>
+        <v>507.899</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B178">
-        <v>1165.87</v>
+        <v>544.415</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B179">
-        <v>1150.827</v>
+        <v>553.9160000000001</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B180">
-        <v>1135.978</v>
+        <v>563.788</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B181">
-        <v>1120.161</v>
+        <v>574.63</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B182">
-        <v>1093.194</v>
+        <v>610.204</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B183">
-        <v>1075.387</v>
+        <v>602.856</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B184">
-        <v>1059.155</v>
+        <v>613.211</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B185">
-        <v>1042.227</v>
+        <v>623.426</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B186">
-        <v>1010.275</v>
+        <v>691.136</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B187">
-        <v>992.931</v>
+        <v>702.423</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B188">
-        <v>975.061</v>
+        <v>716.958</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B189">
-        <v>958.145</v>
+        <v>728.6130000000001</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.05.20261</t>
-  </si>
-  <si>
-    <t>21.05.20262</t>
-  </si>
-  <si>
-    <t>21.05.20263</t>
-  </si>
-  <si>
-    <t>21.05.20264</t>
-  </si>
-  <si>
-    <t>21.05.20265</t>
-  </si>
-  <si>
-    <t>21.05.20266</t>
-  </si>
-  <si>
-    <t>21.05.20267</t>
-  </si>
-  <si>
-    <t>21.05.20268</t>
-  </si>
-  <si>
-    <t>21.05.20269</t>
-  </si>
-  <si>
-    <t>21.05.202610</t>
-  </si>
-  <si>
-    <t>21.05.202611</t>
-  </si>
-  <si>
-    <t>21.05.202612</t>
-  </si>
-  <si>
-    <t>21.05.202613</t>
-  </si>
-  <si>
-    <t>21.05.202614</t>
-  </si>
-  <si>
-    <t>21.05.202615</t>
-  </si>
-  <si>
-    <t>21.05.202616</t>
-  </si>
-  <si>
-    <t>21.05.202617</t>
-  </si>
-  <si>
-    <t>21.05.202618</t>
-  </si>
-  <si>
-    <t>21.05.202619</t>
-  </si>
-  <si>
-    <t>21.05.202620</t>
-  </si>
-  <si>
-    <t>21.05.202621</t>
-  </si>
-  <si>
-    <t>21.05.202622</t>
-  </si>
-  <si>
-    <t>21.05.202623</t>
-  </si>
-  <si>
-    <t>21.05.202624</t>
-  </si>
-  <si>
-    <t>21.05.202625</t>
-  </si>
-  <si>
-    <t>21.05.202626</t>
-  </si>
-  <si>
-    <t>21.05.202627</t>
-  </si>
-  <si>
-    <t>21.05.202628</t>
-  </si>
-  <si>
-    <t>21.05.202629</t>
-  </si>
-  <si>
-    <t>21.05.202630</t>
-  </si>
-  <si>
-    <t>21.05.202631</t>
-  </si>
-  <si>
-    <t>21.05.202632</t>
-  </si>
-  <si>
-    <t>21.05.202633</t>
-  </si>
-  <si>
-    <t>21.05.202634</t>
-  </si>
-  <si>
-    <t>21.05.202635</t>
-  </si>
-  <si>
-    <t>21.05.202636</t>
-  </si>
-  <si>
-    <t>21.05.202637</t>
-  </si>
-  <si>
-    <t>21.05.202638</t>
-  </si>
-  <si>
-    <t>21.05.202639</t>
-  </si>
-  <si>
-    <t>21.05.202640</t>
-  </si>
-  <si>
-    <t>21.05.202641</t>
-  </si>
-  <si>
-    <t>21.05.202642</t>
-  </si>
-  <si>
-    <t>21.05.202643</t>
-  </si>
-  <si>
-    <t>21.05.202644</t>
-  </si>
-  <si>
-    <t>21.05.202645</t>
-  </si>
-  <si>
-    <t>21.05.202646</t>
-  </si>
-  <si>
-    <t>21.05.202647</t>
-  </si>
-  <si>
-    <t>21.05.202648</t>
-  </si>
-  <si>
-    <t>21.05.202649</t>
-  </si>
-  <si>
-    <t>21.05.202650</t>
-  </si>
-  <si>
-    <t>21.05.202651</t>
-  </si>
-  <si>
-    <t>21.05.202652</t>
-  </si>
-  <si>
-    <t>21.05.202653</t>
-  </si>
-  <si>
-    <t>21.05.202654</t>
-  </si>
-  <si>
-    <t>21.05.202655</t>
-  </si>
-  <si>
-    <t>21.05.202656</t>
-  </si>
-  <si>
-    <t>21.05.202657</t>
-  </si>
-  <si>
-    <t>21.05.202658</t>
-  </si>
-  <si>
-    <t>21.05.202659</t>
-  </si>
-  <si>
-    <t>21.05.202660</t>
-  </si>
-  <si>
-    <t>21.05.202661</t>
-  </si>
-  <si>
-    <t>21.05.202662</t>
-  </si>
-  <si>
-    <t>21.05.202663</t>
-  </si>
-  <si>
-    <t>21.05.202664</t>
-  </si>
-  <si>
-    <t>21.05.202665</t>
-  </si>
-  <si>
-    <t>21.05.202666</t>
-  </si>
-  <si>
-    <t>21.05.202667</t>
-  </si>
-  <si>
-    <t>21.05.202668</t>
-  </si>
-  <si>
-    <t>21.05.202669</t>
-  </si>
-  <si>
-    <t>21.05.202670</t>
-  </si>
-  <si>
-    <t>21.05.202671</t>
-  </si>
-  <si>
-    <t>21.05.202672</t>
-  </si>
-  <si>
-    <t>21.05.202673</t>
-  </si>
-  <si>
-    <t>21.05.202674</t>
-  </si>
-  <si>
-    <t>21.05.202675</t>
-  </si>
-  <si>
-    <t>21.05.202676</t>
-  </si>
-  <si>
-    <t>21.05.202677</t>
-  </si>
-  <si>
-    <t>21.05.202678</t>
-  </si>
-  <si>
-    <t>21.05.202679</t>
-  </si>
-  <si>
-    <t>21.05.202680</t>
-  </si>
-  <si>
-    <t>21.05.202681</t>
-  </si>
-  <si>
-    <t>21.05.202682</t>
-  </si>
-  <si>
-    <t>21.05.202683</t>
-  </si>
-  <si>
-    <t>21.05.202684</t>
-  </si>
-  <si>
-    <t>21.05.202685</t>
-  </si>
-  <si>
-    <t>21.05.202686</t>
-  </si>
-  <si>
-    <t>21.05.202687</t>
-  </si>
-  <si>
-    <t>21.05.202688</t>
-  </si>
-  <si>
-    <t>21.05.202689</t>
-  </si>
-  <si>
-    <t>21.05.202690</t>
-  </si>
-  <si>
-    <t>21.05.202691</t>
-  </si>
-  <si>
-    <t>21.05.202692</t>
-  </si>
-  <si>
-    <t>21.05.202693</t>
-  </si>
-  <si>
-    <t>21.05.202694</t>
-  </si>
-  <si>
-    <t>21.05.202695</t>
-  </si>
-  <si>
-    <t>21.05.202696</t>
-  </si>
-  <si>
     <t>22.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,870 @@
   </si>
   <si>
     <t>22.05.202696</t>
+  </si>
+  <si>
+    <t>23.05.20261</t>
+  </si>
+  <si>
+    <t>23.05.20262</t>
+  </si>
+  <si>
+    <t>23.05.20263</t>
+  </si>
+  <si>
+    <t>23.05.20264</t>
+  </si>
+  <si>
+    <t>23.05.20265</t>
+  </si>
+  <si>
+    <t>23.05.20266</t>
+  </si>
+  <si>
+    <t>23.05.20267</t>
+  </si>
+  <si>
+    <t>23.05.20268</t>
+  </si>
+  <si>
+    <t>23.05.20269</t>
+  </si>
+  <si>
+    <t>23.05.202610</t>
+  </si>
+  <si>
+    <t>23.05.202611</t>
+  </si>
+  <si>
+    <t>23.05.202612</t>
+  </si>
+  <si>
+    <t>23.05.202613</t>
+  </si>
+  <si>
+    <t>23.05.202614</t>
+  </si>
+  <si>
+    <t>23.05.202615</t>
+  </si>
+  <si>
+    <t>23.05.202616</t>
+  </si>
+  <si>
+    <t>23.05.202617</t>
+  </si>
+  <si>
+    <t>23.05.202618</t>
+  </si>
+  <si>
+    <t>23.05.202619</t>
+  </si>
+  <si>
+    <t>23.05.202620</t>
+  </si>
+  <si>
+    <t>23.05.202621</t>
+  </si>
+  <si>
+    <t>23.05.202622</t>
+  </si>
+  <si>
+    <t>23.05.202623</t>
+  </si>
+  <si>
+    <t>23.05.202624</t>
+  </si>
+  <si>
+    <t>23.05.202625</t>
+  </si>
+  <si>
+    <t>23.05.202626</t>
+  </si>
+  <si>
+    <t>23.05.202627</t>
+  </si>
+  <si>
+    <t>23.05.202628</t>
+  </si>
+  <si>
+    <t>23.05.202629</t>
+  </si>
+  <si>
+    <t>23.05.202630</t>
+  </si>
+  <si>
+    <t>23.05.202631</t>
+  </si>
+  <si>
+    <t>23.05.202632</t>
+  </si>
+  <si>
+    <t>23.05.202633</t>
+  </si>
+  <si>
+    <t>23.05.202634</t>
+  </si>
+  <si>
+    <t>23.05.202635</t>
+  </si>
+  <si>
+    <t>23.05.202636</t>
+  </si>
+  <si>
+    <t>23.05.202637</t>
+  </si>
+  <si>
+    <t>23.05.202638</t>
+  </si>
+  <si>
+    <t>23.05.202639</t>
+  </si>
+  <si>
+    <t>23.05.202640</t>
+  </si>
+  <si>
+    <t>23.05.202641</t>
+  </si>
+  <si>
+    <t>23.05.202642</t>
+  </si>
+  <si>
+    <t>23.05.202643</t>
+  </si>
+  <si>
+    <t>23.05.202644</t>
+  </si>
+  <si>
+    <t>23.05.202645</t>
+  </si>
+  <si>
+    <t>23.05.202646</t>
+  </si>
+  <si>
+    <t>23.05.202647</t>
+  </si>
+  <si>
+    <t>23.05.202648</t>
+  </si>
+  <si>
+    <t>23.05.202649</t>
+  </si>
+  <si>
+    <t>23.05.202650</t>
+  </si>
+  <si>
+    <t>23.05.202651</t>
+  </si>
+  <si>
+    <t>23.05.202652</t>
+  </si>
+  <si>
+    <t>23.05.202653</t>
+  </si>
+  <si>
+    <t>23.05.202654</t>
+  </si>
+  <si>
+    <t>23.05.202655</t>
+  </si>
+  <si>
+    <t>23.05.202656</t>
+  </si>
+  <si>
+    <t>23.05.202657</t>
+  </si>
+  <si>
+    <t>23.05.202658</t>
+  </si>
+  <si>
+    <t>23.05.202659</t>
+  </si>
+  <si>
+    <t>23.05.202660</t>
+  </si>
+  <si>
+    <t>23.05.202661</t>
+  </si>
+  <si>
+    <t>23.05.202662</t>
+  </si>
+  <si>
+    <t>23.05.202663</t>
+  </si>
+  <si>
+    <t>23.05.202664</t>
+  </si>
+  <si>
+    <t>23.05.202665</t>
+  </si>
+  <si>
+    <t>23.05.202666</t>
+  </si>
+  <si>
+    <t>23.05.202667</t>
+  </si>
+  <si>
+    <t>23.05.202668</t>
+  </si>
+  <si>
+    <t>23.05.202669</t>
+  </si>
+  <si>
+    <t>23.05.202670</t>
+  </si>
+  <si>
+    <t>23.05.202671</t>
+  </si>
+  <si>
+    <t>23.05.202672</t>
+  </si>
+  <si>
+    <t>23.05.202673</t>
+  </si>
+  <si>
+    <t>23.05.202674</t>
+  </si>
+  <si>
+    <t>23.05.202675</t>
+  </si>
+  <si>
+    <t>23.05.202676</t>
+  </si>
+  <si>
+    <t>23.05.202677</t>
+  </si>
+  <si>
+    <t>23.05.202678</t>
+  </si>
+  <si>
+    <t>23.05.202679</t>
+  </si>
+  <si>
+    <t>23.05.202680</t>
+  </si>
+  <si>
+    <t>23.05.202681</t>
+  </si>
+  <si>
+    <t>23.05.202682</t>
+  </si>
+  <si>
+    <t>23.05.202683</t>
+  </si>
+  <si>
+    <t>23.05.202684</t>
+  </si>
+  <si>
+    <t>23.05.202685</t>
+  </si>
+  <si>
+    <t>23.05.202686</t>
+  </si>
+  <si>
+    <t>23.05.202687</t>
+  </si>
+  <si>
+    <t>23.05.202688</t>
+  </si>
+  <si>
+    <t>23.05.202689</t>
+  </si>
+  <si>
+    <t>23.05.202690</t>
+  </si>
+  <si>
+    <t>23.05.202691</t>
+  </si>
+  <si>
+    <t>23.05.202692</t>
+  </si>
+  <si>
+    <t>23.05.202693</t>
+  </si>
+  <si>
+    <t>23.05.202694</t>
+  </si>
+  <si>
+    <t>23.05.202695</t>
+  </si>
+  <si>
+    <t>23.05.202696</t>
+  </si>
+  <si>
+    <t>24.05.20261</t>
+  </si>
+  <si>
+    <t>24.05.20262</t>
+  </si>
+  <si>
+    <t>24.05.20263</t>
+  </si>
+  <si>
+    <t>24.05.20264</t>
+  </si>
+  <si>
+    <t>24.05.20265</t>
+  </si>
+  <si>
+    <t>24.05.20266</t>
+  </si>
+  <si>
+    <t>24.05.20267</t>
+  </si>
+  <si>
+    <t>24.05.20268</t>
+  </si>
+  <si>
+    <t>24.05.20269</t>
+  </si>
+  <si>
+    <t>24.05.202610</t>
+  </si>
+  <si>
+    <t>24.05.202611</t>
+  </si>
+  <si>
+    <t>24.05.202612</t>
+  </si>
+  <si>
+    <t>24.05.202613</t>
+  </si>
+  <si>
+    <t>24.05.202614</t>
+  </si>
+  <si>
+    <t>24.05.202615</t>
+  </si>
+  <si>
+    <t>24.05.202616</t>
+  </si>
+  <si>
+    <t>24.05.202617</t>
+  </si>
+  <si>
+    <t>24.05.202618</t>
+  </si>
+  <si>
+    <t>24.05.202619</t>
+  </si>
+  <si>
+    <t>24.05.202620</t>
+  </si>
+  <si>
+    <t>24.05.202621</t>
+  </si>
+  <si>
+    <t>24.05.202622</t>
+  </si>
+  <si>
+    <t>24.05.202623</t>
+  </si>
+  <si>
+    <t>24.05.202624</t>
+  </si>
+  <si>
+    <t>24.05.202625</t>
+  </si>
+  <si>
+    <t>24.05.202626</t>
+  </si>
+  <si>
+    <t>24.05.202627</t>
+  </si>
+  <si>
+    <t>24.05.202628</t>
+  </si>
+  <si>
+    <t>24.05.202629</t>
+  </si>
+  <si>
+    <t>24.05.202630</t>
+  </si>
+  <si>
+    <t>24.05.202631</t>
+  </si>
+  <si>
+    <t>24.05.202632</t>
+  </si>
+  <si>
+    <t>24.05.202633</t>
+  </si>
+  <si>
+    <t>24.05.202634</t>
+  </si>
+  <si>
+    <t>24.05.202635</t>
+  </si>
+  <si>
+    <t>24.05.202636</t>
+  </si>
+  <si>
+    <t>24.05.202637</t>
+  </si>
+  <si>
+    <t>24.05.202638</t>
+  </si>
+  <si>
+    <t>24.05.202639</t>
+  </si>
+  <si>
+    <t>24.05.202640</t>
+  </si>
+  <si>
+    <t>24.05.202641</t>
+  </si>
+  <si>
+    <t>24.05.202642</t>
+  </si>
+  <si>
+    <t>24.05.202643</t>
+  </si>
+  <si>
+    <t>24.05.202644</t>
+  </si>
+  <si>
+    <t>24.05.202645</t>
+  </si>
+  <si>
+    <t>24.05.202646</t>
+  </si>
+  <si>
+    <t>24.05.202647</t>
+  </si>
+  <si>
+    <t>24.05.202648</t>
+  </si>
+  <si>
+    <t>24.05.202649</t>
+  </si>
+  <si>
+    <t>24.05.202650</t>
+  </si>
+  <si>
+    <t>24.05.202651</t>
+  </si>
+  <si>
+    <t>24.05.202652</t>
+  </si>
+  <si>
+    <t>24.05.202653</t>
+  </si>
+  <si>
+    <t>24.05.202654</t>
+  </si>
+  <si>
+    <t>24.05.202655</t>
+  </si>
+  <si>
+    <t>24.05.202656</t>
+  </si>
+  <si>
+    <t>24.05.202657</t>
+  </si>
+  <si>
+    <t>24.05.202658</t>
+  </si>
+  <si>
+    <t>24.05.202659</t>
+  </si>
+  <si>
+    <t>24.05.202660</t>
+  </si>
+  <si>
+    <t>24.05.202661</t>
+  </si>
+  <si>
+    <t>24.05.202662</t>
+  </si>
+  <si>
+    <t>24.05.202663</t>
+  </si>
+  <si>
+    <t>24.05.202664</t>
+  </si>
+  <si>
+    <t>24.05.202665</t>
+  </si>
+  <si>
+    <t>24.05.202666</t>
+  </si>
+  <si>
+    <t>24.05.202667</t>
+  </si>
+  <si>
+    <t>24.05.202668</t>
+  </si>
+  <si>
+    <t>24.05.202669</t>
+  </si>
+  <si>
+    <t>24.05.202670</t>
+  </si>
+  <si>
+    <t>24.05.202671</t>
+  </si>
+  <si>
+    <t>24.05.202672</t>
+  </si>
+  <si>
+    <t>24.05.202673</t>
+  </si>
+  <si>
+    <t>24.05.202674</t>
+  </si>
+  <si>
+    <t>24.05.202675</t>
+  </si>
+  <si>
+    <t>24.05.202676</t>
+  </si>
+  <si>
+    <t>24.05.202677</t>
+  </si>
+  <si>
+    <t>24.05.202678</t>
+  </si>
+  <si>
+    <t>24.05.202679</t>
+  </si>
+  <si>
+    <t>24.05.202680</t>
+  </si>
+  <si>
+    <t>24.05.202681</t>
+  </si>
+  <si>
+    <t>24.05.202682</t>
+  </si>
+  <si>
+    <t>24.05.202683</t>
+  </si>
+  <si>
+    <t>24.05.202684</t>
+  </si>
+  <si>
+    <t>24.05.202685</t>
+  </si>
+  <si>
+    <t>24.05.202686</t>
+  </si>
+  <si>
+    <t>24.05.202687</t>
+  </si>
+  <si>
+    <t>24.05.202688</t>
+  </si>
+  <si>
+    <t>24.05.202689</t>
+  </si>
+  <si>
+    <t>24.05.202690</t>
+  </si>
+  <si>
+    <t>24.05.202691</t>
+  </si>
+  <si>
+    <t>24.05.202692</t>
+  </si>
+  <si>
+    <t>24.05.202693</t>
+  </si>
+  <si>
+    <t>24.05.202694</t>
+  </si>
+  <si>
+    <t>24.05.202695</t>
+  </si>
+  <si>
+    <t>24.05.202696</t>
+  </si>
+  <si>
+    <t>25.05.20261</t>
+  </si>
+  <si>
+    <t>25.05.20262</t>
+  </si>
+  <si>
+    <t>25.05.20263</t>
+  </si>
+  <si>
+    <t>25.05.20264</t>
+  </si>
+  <si>
+    <t>25.05.20265</t>
+  </si>
+  <si>
+    <t>25.05.20266</t>
+  </si>
+  <si>
+    <t>25.05.20267</t>
+  </si>
+  <si>
+    <t>25.05.20268</t>
+  </si>
+  <si>
+    <t>25.05.20269</t>
+  </si>
+  <si>
+    <t>25.05.202610</t>
+  </si>
+  <si>
+    <t>25.05.202611</t>
+  </si>
+  <si>
+    <t>25.05.202612</t>
+  </si>
+  <si>
+    <t>25.05.202613</t>
+  </si>
+  <si>
+    <t>25.05.202614</t>
+  </si>
+  <si>
+    <t>25.05.202615</t>
+  </si>
+  <si>
+    <t>25.05.202616</t>
+  </si>
+  <si>
+    <t>25.05.202617</t>
+  </si>
+  <si>
+    <t>25.05.202618</t>
+  </si>
+  <si>
+    <t>25.05.202619</t>
+  </si>
+  <si>
+    <t>25.05.202620</t>
+  </si>
+  <si>
+    <t>25.05.202621</t>
+  </si>
+  <si>
+    <t>25.05.202622</t>
+  </si>
+  <si>
+    <t>25.05.202623</t>
+  </si>
+  <si>
+    <t>25.05.202624</t>
+  </si>
+  <si>
+    <t>25.05.202625</t>
+  </si>
+  <si>
+    <t>25.05.202626</t>
+  </si>
+  <si>
+    <t>25.05.202627</t>
+  </si>
+  <si>
+    <t>25.05.202628</t>
+  </si>
+  <si>
+    <t>25.05.202629</t>
+  </si>
+  <si>
+    <t>25.05.202630</t>
+  </si>
+  <si>
+    <t>25.05.202631</t>
+  </si>
+  <si>
+    <t>25.05.202632</t>
+  </si>
+  <si>
+    <t>25.05.202633</t>
+  </si>
+  <si>
+    <t>25.05.202634</t>
+  </si>
+  <si>
+    <t>25.05.202635</t>
+  </si>
+  <si>
+    <t>25.05.202636</t>
+  </si>
+  <si>
+    <t>25.05.202637</t>
+  </si>
+  <si>
+    <t>25.05.202638</t>
+  </si>
+  <si>
+    <t>25.05.202639</t>
+  </si>
+  <si>
+    <t>25.05.202640</t>
+  </si>
+  <si>
+    <t>25.05.202641</t>
+  </si>
+  <si>
+    <t>25.05.202642</t>
+  </si>
+  <si>
+    <t>25.05.202643</t>
+  </si>
+  <si>
+    <t>25.05.202644</t>
+  </si>
+  <si>
+    <t>25.05.202645</t>
+  </si>
+  <si>
+    <t>25.05.202646</t>
+  </si>
+  <si>
+    <t>25.05.202647</t>
+  </si>
+  <si>
+    <t>25.05.202648</t>
+  </si>
+  <si>
+    <t>25.05.202649</t>
+  </si>
+  <si>
+    <t>25.05.202650</t>
+  </si>
+  <si>
+    <t>25.05.202651</t>
+  </si>
+  <si>
+    <t>25.05.202652</t>
+  </si>
+  <si>
+    <t>25.05.202653</t>
+  </si>
+  <si>
+    <t>25.05.202654</t>
+  </si>
+  <si>
+    <t>25.05.202655</t>
+  </si>
+  <si>
+    <t>25.05.202656</t>
+  </si>
+  <si>
+    <t>25.05.202657</t>
+  </si>
+  <si>
+    <t>25.05.202658</t>
+  </si>
+  <si>
+    <t>25.05.202659</t>
+  </si>
+  <si>
+    <t>25.05.202660</t>
+  </si>
+  <si>
+    <t>25.05.202661</t>
+  </si>
+  <si>
+    <t>25.05.202662</t>
+  </si>
+  <si>
+    <t>25.05.202663</t>
+  </si>
+  <si>
+    <t>25.05.202664</t>
+  </si>
+  <si>
+    <t>25.05.202665</t>
+  </si>
+  <si>
+    <t>25.05.202666</t>
+  </si>
+  <si>
+    <t>25.05.202667</t>
+  </si>
+  <si>
+    <t>25.05.202668</t>
+  </si>
+  <si>
+    <t>25.05.202669</t>
+  </si>
+  <si>
+    <t>25.05.202670</t>
+  </si>
+  <si>
+    <t>25.05.202671</t>
+  </si>
+  <si>
+    <t>25.05.202672</t>
+  </si>
+  <si>
+    <t>25.05.202673</t>
+  </si>
+  <si>
+    <t>25.05.202674</t>
+  </si>
+  <si>
+    <t>25.05.202675</t>
+  </si>
+  <si>
+    <t>25.05.202676</t>
+  </si>
+  <si>
+    <t>25.05.202677</t>
+  </si>
+  <si>
+    <t>25.05.202678</t>
+  </si>
+  <si>
+    <t>25.05.202679</t>
+  </si>
+  <si>
+    <t>25.05.202680</t>
+  </si>
+  <si>
+    <t>25.05.202681</t>
+  </si>
+  <si>
+    <t>25.05.202682</t>
+  </si>
+  <si>
+    <t>25.05.202683</t>
+  </si>
+  <si>
+    <t>25.05.202684</t>
+  </si>
+  <si>
+    <t>25.05.202685</t>
+  </si>
+  <si>
+    <t>25.05.202686</t>
+  </si>
+  <si>
+    <t>25.05.202687</t>
+  </si>
+  <si>
+    <t>25.05.202688</t>
+  </si>
+  <si>
+    <t>25.05.202689</t>
+  </si>
+  <si>
+    <t>25.05.202690</t>
+  </si>
+  <si>
+    <t>25.05.202691</t>
+  </si>
+  <si>
+    <t>25.05.202692</t>
+  </si>
+  <si>
+    <t>25.05.202693</t>
+  </si>
+  <si>
+    <t>25.05.202694</t>
+  </si>
+  <si>
+    <t>25.05.202695</t>
+  </si>
+  <si>
+    <t>25.05.202696</t>
   </si>
 </sst>
 </file>
@@ -966,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -988,13 +1564,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
-        <v>2011.594</v>
+        <v>881.374</v>
       </c>
       <c r="C2">
-        <v>2186</v>
+        <v>941</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1581,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
-        <v>2014.513</v>
+        <v>870.271</v>
       </c>
       <c r="C3">
-        <v>2176</v>
+        <v>921</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1598,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
-        <v>2021.993</v>
+        <v>851.846</v>
       </c>
       <c r="C4">
-        <v>2208</v>
+        <v>881</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1615,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
-        <v>2038.267</v>
+        <v>839.737</v>
       </c>
       <c r="C5">
-        <v>2202</v>
+        <v>872</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1632,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
-        <v>2082.547</v>
+        <v>807.894</v>
       </c>
       <c r="C6">
-        <v>2250</v>
+        <v>864</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1649,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
-        <v>2102.276</v>
+        <v>809.749</v>
       </c>
       <c r="C7">
-        <v>2300</v>
+        <v>871</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1666,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
-        <v>2116.323</v>
+        <v>801.558</v>
       </c>
       <c r="C8">
-        <v>2336</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1683,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
-        <v>2125.058</v>
+        <v>807.412</v>
       </c>
       <c r="C9">
-        <v>2354</v>
+        <v>870</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1700,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
-        <v>2100.509</v>
+        <v>800.36</v>
       </c>
       <c r="C10">
-        <v>2366</v>
+        <v>881</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1717,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
-        <v>2114.928</v>
+        <v>809.723</v>
       </c>
       <c r="C11">
-        <v>2324</v>
+        <v>879</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1734,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
-        <v>2121.844</v>
+        <v>808.6660000000001</v>
       </c>
       <c r="C12">
-        <v>2284</v>
+        <v>878</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1751,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>2125.094</v>
+        <v>812.662</v>
       </c>
       <c r="C13">
-        <v>2285</v>
+        <v>867</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1768,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>2119.449</v>
+        <v>817.691</v>
       </c>
       <c r="C14">
-        <v>2252</v>
+        <v>870</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1785,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
-        <v>2132.258</v>
+        <v>823.0549999999999</v>
       </c>
       <c r="C15">
-        <v>2251</v>
+        <v>869</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1802,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>2135.947</v>
+        <v>825.125</v>
       </c>
       <c r="C16">
-        <v>2264</v>
+        <v>837</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1819,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>2137.335</v>
+        <v>834.793</v>
       </c>
       <c r="C17">
-        <v>2278</v>
+        <v>832</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1836,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>2125.63</v>
+        <v>804.628</v>
       </c>
       <c r="C18">
-        <v>2267</v>
+        <v>818</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1853,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>2132.514</v>
+        <v>811.3869999999999</v>
       </c>
       <c r="C19">
-        <v>2252</v>
+        <v>804</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1870,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>2127.748</v>
+        <v>817.679</v>
       </c>
       <c r="C20">
-        <v>2216</v>
+        <v>798</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1887,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>2121.565</v>
+        <v>830.405</v>
       </c>
       <c r="C21">
-        <v>2250</v>
+        <v>784</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1904,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>2178.735</v>
+        <v>831.578</v>
       </c>
       <c r="C22">
-        <v>2258</v>
+        <v>773</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1921,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>2176.146</v>
+        <v>833.5</v>
       </c>
       <c r="C23">
-        <v>2246</v>
+        <v>755</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1938,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>2173.474</v>
+        <v>836.212</v>
       </c>
       <c r="C24">
-        <v>2199</v>
+        <v>714</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1955,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>2167.727</v>
+        <v>837.139</v>
       </c>
       <c r="C25">
-        <v>2161</v>
+        <v>680</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1972,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>2164.497</v>
+        <v>825.7619999999999</v>
       </c>
       <c r="C26">
-        <v>2063</v>
+        <v>692</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1989,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>2177.459</v>
+        <v>826.002</v>
       </c>
       <c r="C27">
-        <v>2013</v>
+        <v>685</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +2006,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>2195.562</v>
+        <v>818.394</v>
       </c>
       <c r="C28">
-        <v>2003</v>
+        <v>692</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +2023,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>2220.964</v>
+        <v>815.753</v>
       </c>
       <c r="C29">
-        <v>1993</v>
+        <v>707</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +2040,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>2213.556</v>
+        <v>808.288</v>
       </c>
       <c r="C30">
-        <v>1966</v>
+        <v>705</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +2057,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>2208.366</v>
+        <v>811.279</v>
       </c>
       <c r="C31">
-        <v>1931</v>
+        <v>669</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +2074,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>2205.51</v>
+        <v>805.973</v>
       </c>
       <c r="C32">
-        <v>1911</v>
+        <v>649</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +2091,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>2207.71</v>
+        <v>784.494</v>
       </c>
       <c r="C33">
-        <v>1901</v>
+        <v>635</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +2108,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>2166.95</v>
+        <v>733.323</v>
       </c>
       <c r="C34">
-        <v>1936</v>
+        <v>629</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +2125,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>2151.582</v>
+        <v>732.0549999999999</v>
       </c>
       <c r="C35">
-        <v>1898</v>
+        <v>635</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +2142,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>2122.157</v>
+        <v>715.103</v>
       </c>
       <c r="C36">
-        <v>1809</v>
+        <v>612</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +2159,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>2107.632</v>
+        <v>713.745</v>
       </c>
       <c r="C37">
-        <v>1702</v>
+        <v>607</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +2176,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>2008.521</v>
+        <v>728.112</v>
       </c>
       <c r="C38">
-        <v>1727</v>
+        <v>600</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +2193,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>1988.378</v>
+        <v>718.299</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +2210,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>1968.003</v>
+        <v>708.554</v>
       </c>
       <c r="C40">
-        <v>1772</v>
+        <v>569</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +2227,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>1949.559</v>
+        <v>699.423</v>
       </c>
       <c r="C41">
-        <v>1682</v>
+        <v>560</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +2244,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>1995.077</v>
+        <v>747.523</v>
       </c>
       <c r="C42">
-        <v>1622</v>
+        <v>551</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +2261,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>1974.716</v>
+        <v>739.575</v>
       </c>
       <c r="C43">
-        <v>1555</v>
+        <v>539</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +2278,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>1957.036</v>
+        <v>732.17</v>
       </c>
       <c r="C44">
-        <v>1550</v>
+        <v>516</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +2295,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>1940.504</v>
+        <v>725.133</v>
       </c>
       <c r="C45">
-        <v>1561</v>
+        <v>506</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +2312,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>1819.321</v>
+        <v>729.981</v>
       </c>
       <c r="C46">
-        <v>1545</v>
+        <v>527</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +2329,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>1801.815</v>
+        <v>727.908</v>
       </c>
       <c r="C47">
-        <v>1539</v>
+        <v>512</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +2346,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>1784.579</v>
+        <v>687.395</v>
       </c>
       <c r="C48">
-        <v>1599</v>
+        <v>492</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +2363,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>1765.999</v>
+        <v>681.1900000000001</v>
       </c>
       <c r="C49">
-        <v>1597</v>
+        <v>478</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +2380,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
-        <v>1730.827</v>
+        <v>675.616</v>
       </c>
       <c r="C50">
-        <v>1546</v>
+        <v>464</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +2397,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>1703.079</v>
+        <v>668.851</v>
       </c>
       <c r="C51">
-        <v>1522</v>
+        <v>469</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +2414,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>1675.186</v>
+        <v>662.078</v>
       </c>
       <c r="C52">
-        <v>1480</v>
+        <v>445</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +2431,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>1646.007</v>
+        <v>655.849</v>
       </c>
       <c r="C53">
-        <v>1365</v>
+        <v>457</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +2448,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B54">
-        <v>1586.548</v>
+        <v>647.7569999999999</v>
       </c>
       <c r="C54">
-        <v>1306</v>
+        <v>455</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +2465,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B55">
-        <v>1563.061</v>
+        <v>636.329</v>
       </c>
       <c r="C55">
-        <v>1222</v>
+        <v>447</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +2482,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B56">
-        <v>1539.32</v>
+        <v>613.67</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +2499,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B57">
-        <v>1511.519</v>
+        <v>590.326</v>
       </c>
       <c r="C57">
-        <v>1219</v>
+        <v>442</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +2516,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B58">
-        <v>1513.295</v>
+        <v>609.354</v>
       </c>
       <c r="C58">
-        <v>1319</v>
+        <v>407</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +2533,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B59">
-        <v>1492.574</v>
+        <v>598.149</v>
       </c>
       <c r="C59">
-        <v>1446</v>
+        <v>425</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +2550,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B60">
-        <v>1472.17</v>
+        <v>584.995</v>
       </c>
       <c r="C60">
-        <v>1557</v>
+        <v>447</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +2567,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B61">
-        <v>1451.834</v>
+        <v>604.95</v>
       </c>
       <c r="C61">
-        <v>1699</v>
+        <v>469</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2584,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B62">
-        <v>1478.755</v>
+        <v>584.232</v>
       </c>
       <c r="C62">
-        <v>1664</v>
+        <v>538</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2601,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B63">
-        <v>1457.184</v>
+        <v>571.936</v>
       </c>
       <c r="C63">
-        <v>1577</v>
+        <v>558</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2618,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B64">
-        <v>1436.075</v>
+        <v>562.206</v>
       </c>
       <c r="C64">
-        <v>1484</v>
+        <v>514</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2635,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B65">
-        <v>1416.53</v>
+        <v>551.4589999999999</v>
       </c>
       <c r="C65">
-        <v>1389</v>
+        <v>504</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2652,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B66">
-        <v>1391.006</v>
+        <v>540.091</v>
       </c>
       <c r="C66">
-        <v>1564</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2669,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B67">
-        <v>1382.72</v>
+        <v>531.514</v>
       </c>
       <c r="C67">
-        <v>1617</v>
+        <v>545</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2686,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B68">
-        <v>1377.459</v>
+        <v>523.713</v>
       </c>
       <c r="C68">
-        <v>1675</v>
+        <v>589</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2703,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B69">
-        <v>1371.863</v>
+        <v>513.831</v>
       </c>
       <c r="C69">
-        <v>1687</v>
+        <v>597</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2720,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B70">
-        <v>1353.84</v>
+        <v>498.973</v>
       </c>
       <c r="C70">
-        <v>1683</v>
+        <v>585</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2737,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B71">
-        <v>1345.745</v>
+        <v>495.552</v>
       </c>
       <c r="C71">
-        <v>1634</v>
+        <v>558</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2754,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B72">
-        <v>1336.994</v>
+        <v>492.963</v>
       </c>
       <c r="C72">
-        <v>1609</v>
+        <v>541</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2771,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B73">
-        <v>1328.238</v>
+        <v>487.806</v>
       </c>
       <c r="C73">
-        <v>1599</v>
+        <v>557</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2788,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B74">
-        <v>1310.1</v>
+        <v>472.674</v>
       </c>
       <c r="C74">
-        <v>1619</v>
+        <v>554</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2805,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B75">
-        <v>1296.716</v>
+        <v>475.666</v>
       </c>
       <c r="C75">
-        <v>1637</v>
+        <v>555</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2822,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B76">
-        <v>1285.568</v>
+        <v>477.614</v>
       </c>
       <c r="C76">
-        <v>1622</v>
+        <v>573</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2839,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B77">
-        <v>1271.845</v>
+        <v>479.918</v>
       </c>
       <c r="C77">
-        <v>1603</v>
+        <v>572</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2856,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B78">
-        <v>1255.245</v>
+        <v>454.593</v>
       </c>
       <c r="C78">
-        <v>1551</v>
+        <v>532</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2873,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B79">
-        <v>1240.48</v>
+        <v>464.329</v>
       </c>
       <c r="C79">
-        <v>1519</v>
+        <v>489</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2890,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B80">
-        <v>1226.82</v>
+        <v>475.979</v>
       </c>
       <c r="C80">
-        <v>1497</v>
+        <v>404</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2907,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B81">
-        <v>1211.221</v>
+        <v>507.899</v>
       </c>
       <c r="C81">
-        <v>1507</v>
+        <v>423</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2924,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B82">
-        <v>1165.87</v>
+        <v>544.415</v>
       </c>
       <c r="C82">
-        <v>1437</v>
+        <v>491</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2941,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B83">
-        <v>1150.827</v>
+        <v>553.9160000000001</v>
       </c>
       <c r="C83">
-        <v>1390</v>
+        <v>552</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2958,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B84">
-        <v>1135.978</v>
+        <v>563.788</v>
       </c>
       <c r="C84">
-        <v>1397</v>
+        <v>566</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2975,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B85">
-        <v>1120.161</v>
+        <v>574.63</v>
       </c>
       <c r="C85">
-        <v>1396</v>
+        <v>632</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2992,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B86">
-        <v>1093.194</v>
+        <v>610.204</v>
       </c>
       <c r="C86">
-        <v>1341</v>
+        <v>713</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +3009,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B87">
-        <v>1075.387</v>
+        <v>602.856</v>
       </c>
       <c r="C87">
-        <v>1319</v>
+        <v>805</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +3026,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B88">
-        <v>1059.155</v>
+        <v>613.211</v>
       </c>
       <c r="C88">
-        <v>1284</v>
+        <v>861</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +3043,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B89">
-        <v>1042.227</v>
+        <v>623.426</v>
       </c>
       <c r="C89">
-        <v>1301</v>
+        <v>853</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +3060,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B90">
-        <v>1010.275</v>
+        <v>691.136</v>
       </c>
       <c r="C90">
-        <v>1296</v>
+        <v>881</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +3077,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B91">
-        <v>992.931</v>
+        <v>702.423</v>
       </c>
       <c r="C91">
-        <v>1262</v>
+        <v>887</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +3094,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B92">
-        <v>975.061</v>
+        <v>716.958</v>
       </c>
       <c r="C92">
-        <v>1199</v>
+        <v>871</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +3111,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B93">
-        <v>958.145</v>
+        <v>728.6130000000001</v>
       </c>
       <c r="C93">
-        <v>1132</v>
+        <v>837</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +3128,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B94">
-        <v>945.765</v>
+        <v>874.689</v>
       </c>
       <c r="C94">
-        <v>1102</v>
+        <v>762</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +3145,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B95">
-        <v>950.021</v>
+        <v>892.675</v>
       </c>
       <c r="C95">
-        <v>1066</v>
+        <v>765</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +3162,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B96">
-        <v>923.399</v>
+        <v>903.136</v>
       </c>
       <c r="C96">
-        <v>1012</v>
+        <v>754</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +3179,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B97">
-        <v>901.6950000000001</v>
+        <v>924.58</v>
       </c>
       <c r="C97">
-        <v>971</v>
+        <v>780</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +3196,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B98">
-        <v>881.374</v>
+        <v>1005.26</v>
       </c>
       <c r="C98">
-        <v>941</v>
+        <v>782</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +3213,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46164.01041666666</v>
+        <v>46165.01041666666</v>
       </c>
       <c r="B99">
-        <v>870.271</v>
+        <v>1014.823</v>
       </c>
       <c r="C99">
-        <v>921</v>
+        <v>808</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +3230,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46164.02083333334</v>
+        <v>46165.02083333334</v>
       </c>
       <c r="B100">
-        <v>851.846</v>
+        <v>1023.4</v>
       </c>
       <c r="C100">
-        <v>881</v>
+        <v>825</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +3247,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46164.03125</v>
+        <v>46165.03125</v>
       </c>
       <c r="B101">
-        <v>839.737</v>
+        <v>1041.1</v>
       </c>
       <c r="C101">
-        <v>872</v>
+        <v>831</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +3264,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46164.04166666666</v>
+        <v>46165.04166666666</v>
       </c>
       <c r="B102">
-        <v>807.894</v>
+        <v>1014.016</v>
       </c>
       <c r="C102">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +3281,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46164.05208333334</v>
+        <v>46165.05208333334</v>
       </c>
       <c r="B103">
-        <v>809.749</v>
+        <v>1034.534</v>
       </c>
       <c r="C103">
-        <v>871</v>
+        <v>912</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +3298,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46164.0625</v>
+        <v>46165.0625</v>
       </c>
       <c r="B104">
-        <v>801.558</v>
+        <v>1050.692</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>964</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +3315,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46164.07291666666</v>
+        <v>46165.07291666666</v>
       </c>
       <c r="B105">
-        <v>807.412</v>
+        <v>1068.324</v>
       </c>
       <c r="C105">
-        <v>870</v>
+        <v>1035</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +3332,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46164.08333333334</v>
+        <v>46165.08333333334</v>
       </c>
       <c r="B106">
-        <v>800.36</v>
+        <v>1062.373</v>
       </c>
       <c r="C106">
-        <v>881</v>
+        <v>1085</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +3349,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46164.09375</v>
+        <v>46165.09375</v>
       </c>
       <c r="B107">
-        <v>809.723</v>
+        <v>1090.579</v>
       </c>
       <c r="C107">
-        <v>879</v>
+        <v>1100</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +3366,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46164.10416666666</v>
+        <v>46165.10416666666</v>
       </c>
       <c r="B108">
-        <v>808.6660000000001</v>
+        <v>1119.71</v>
       </c>
       <c r="C108">
-        <v>878</v>
+        <v>1074</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +3383,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46164.11458333334</v>
+        <v>46165.11458333334</v>
       </c>
       <c r="B109">
-        <v>812.662</v>
+        <v>1153.053</v>
       </c>
       <c r="C109">
-        <v>867</v>
+        <v>1091</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +3400,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46164.125</v>
+        <v>46165.125</v>
       </c>
       <c r="B110">
-        <v>817.691</v>
+        <v>1211.782</v>
       </c>
       <c r="C110">
-        <v>870</v>
+        <v>1172</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +3417,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46164.13541666666</v>
+        <v>46165.13541666666</v>
       </c>
       <c r="B111">
-        <v>823.0549999999999</v>
+        <v>1245.818</v>
       </c>
       <c r="C111">
-        <v>869</v>
+        <v>1226</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +3434,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46164.14583333334</v>
+        <v>46165.14583333334</v>
       </c>
       <c r="B112">
-        <v>825.125</v>
+        <v>1268.145</v>
       </c>
       <c r="C112">
-        <v>837</v>
+        <v>1314</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +3451,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46164.15625</v>
+        <v>46165.15625</v>
       </c>
       <c r="B113">
-        <v>834.793</v>
+        <v>1295.316</v>
       </c>
       <c r="C113">
-        <v>832</v>
+        <v>1305</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +3468,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46164.16666666666</v>
+        <v>46165.16666666666</v>
       </c>
       <c r="B114">
-        <v>804.628</v>
+        <v>1321.817</v>
       </c>
       <c r="C114">
-        <v>818</v>
+        <v>1290</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +3485,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46164.17708333334</v>
+        <v>46165.17708333334</v>
       </c>
       <c r="B115">
-        <v>811.3869999999999</v>
+        <v>1335.956</v>
       </c>
       <c r="C115">
-        <v>804</v>
+        <v>1302</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +3502,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46164.1875</v>
+        <v>46165.1875</v>
       </c>
       <c r="B116">
-        <v>817.679</v>
+        <v>1351.104</v>
       </c>
       <c r="C116">
-        <v>798</v>
+        <v>1325</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +3519,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46164.19791666666</v>
+        <v>46165.19791666666</v>
       </c>
       <c r="B117">
-        <v>830.405</v>
+        <v>1367.269</v>
       </c>
       <c r="C117">
-        <v>784</v>
+        <v>1364</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +3536,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46164.20833333334</v>
+        <v>46165.20833333334</v>
       </c>
       <c r="B118">
-        <v>831.578</v>
+        <v>1378.171</v>
       </c>
       <c r="C118">
-        <v>773</v>
+        <v>1368</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +3553,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46164.21875</v>
+        <v>46165.21875</v>
       </c>
       <c r="B119">
-        <v>833.5</v>
+        <v>1388.138</v>
       </c>
       <c r="C119">
-        <v>755</v>
+        <v>1419</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +3570,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46164.22916666666</v>
+        <v>46165.22916666666</v>
       </c>
       <c r="B120">
-        <v>836.212</v>
+        <v>1402.342</v>
       </c>
       <c r="C120">
-        <v>714</v>
+        <v>1474</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3587,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46164.23958333334</v>
+        <v>46165.23958333334</v>
       </c>
       <c r="B121">
-        <v>837.139</v>
+        <v>1417.348</v>
       </c>
       <c r="C121">
-        <v>680</v>
+        <v>1483</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3604,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46164.25</v>
+        <v>46165.25</v>
       </c>
       <c r="B122">
-        <v>825.7619999999999</v>
+        <v>1436.155</v>
       </c>
       <c r="C122">
-        <v>692</v>
+        <v>1450</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3621,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46164.26041666666</v>
+        <v>46165.26041666666</v>
       </c>
       <c r="B123">
-        <v>826.002</v>
+        <v>1442.421</v>
       </c>
       <c r="C123">
-        <v>685</v>
+        <v>1396</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3638,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46164.27083333334</v>
+        <v>46165.27083333334</v>
       </c>
       <c r="B124">
-        <v>818.394</v>
+        <v>1440.607</v>
       </c>
       <c r="C124">
-        <v>692</v>
+        <v>1368</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3655,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46164.28125</v>
+        <v>46165.28125</v>
       </c>
       <c r="B125">
-        <v>815.753</v>
+        <v>1433.659</v>
       </c>
       <c r="C125">
-        <v>707</v>
+        <v>1307</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3672,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46164.29166666666</v>
+        <v>46165.29166666666</v>
       </c>
       <c r="B126">
-        <v>808.288</v>
+        <v>1447.357</v>
       </c>
       <c r="C126">
-        <v>705</v>
+        <v>1241</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3689,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46164.30208333334</v>
+        <v>46165.30208333334</v>
       </c>
       <c r="B127">
-        <v>811.279</v>
+        <v>1448.532</v>
       </c>
       <c r="C127">
-        <v>669</v>
+        <v>1213</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3706,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46164.3125</v>
+        <v>46165.3125</v>
       </c>
       <c r="B128">
-        <v>805.973</v>
+        <v>1462.889</v>
       </c>
       <c r="C128">
-        <v>649</v>
+        <v>1186</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3723,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46164.32291666666</v>
+        <v>46165.32291666666</v>
       </c>
       <c r="B129">
-        <v>784.494</v>
+        <v>1459.802</v>
       </c>
       <c r="C129">
-        <v>635</v>
+        <v>1166</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3740,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46164.33333333334</v>
+        <v>46165.33333333334</v>
       </c>
       <c r="B130">
-        <v>733.323</v>
+        <v>1390.097</v>
       </c>
       <c r="C130">
-        <v>629</v>
+        <v>1139</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3757,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46164.34375</v>
+        <v>46165.34375</v>
       </c>
       <c r="B131">
-        <v>732.0549999999999</v>
+        <v>1393.275</v>
       </c>
       <c r="C131">
-        <v>635</v>
+        <v>1140</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3774,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46164.35416666666</v>
+        <v>46165.35416666666</v>
       </c>
       <c r="B132">
-        <v>715.103</v>
+        <v>1443.277</v>
       </c>
       <c r="C132">
-        <v>612</v>
+        <v>1106</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3791,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46164.36458333334</v>
+        <v>46165.36458333334</v>
       </c>
       <c r="B133">
-        <v>713.745</v>
+        <v>1455.669</v>
       </c>
       <c r="C133">
-        <v>607</v>
+        <v>1089</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3808,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46164.375</v>
+        <v>46165.375</v>
       </c>
       <c r="B134">
-        <v>728.112</v>
+        <v>1552.646</v>
       </c>
       <c r="C134">
-        <v>600</v>
+        <v>1072</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3825,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46164.38541666666</v>
+        <v>46165.38541666666</v>
       </c>
       <c r="B135">
-        <v>718.299</v>
+        <v>1560.789</v>
       </c>
       <c r="C135">
-        <v>583</v>
+        <v>1040</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3842,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46164.39583333334</v>
+        <v>46165.39583333334</v>
       </c>
       <c r="B136">
-        <v>708.554</v>
+        <v>1462.031</v>
       </c>
       <c r="C136">
-        <v>569</v>
+        <v>973</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3859,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46164.40625</v>
+        <v>46165.40625</v>
       </c>
       <c r="B137">
-        <v>699.423</v>
+        <v>1376.318</v>
       </c>
       <c r="C137">
-        <v>560</v>
+        <v>945</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3876,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46164.41666666666</v>
+        <v>46165.41666666666</v>
       </c>
       <c r="B138">
-        <v>747.523</v>
+        <v>1433.506</v>
       </c>
       <c r="C138">
-        <v>551</v>
+        <v>956</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3893,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46164.42708333334</v>
+        <v>46165.42708333334</v>
       </c>
       <c r="B139">
-        <v>739.575</v>
+        <v>1446.222</v>
       </c>
       <c r="C139">
-        <v>539</v>
+        <v>939</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3910,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46164.4375</v>
+        <v>46165.4375</v>
       </c>
       <c r="B140">
-        <v>732.17</v>
+        <v>1459.502</v>
       </c>
       <c r="C140">
-        <v>516</v>
+        <v>946</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3927,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46164.44791666666</v>
+        <v>46165.44791666666</v>
       </c>
       <c r="B141">
-        <v>725.133</v>
+        <v>1472.017</v>
       </c>
       <c r="C141">
-        <v>506</v>
+        <v>981</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3944,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46164.45833333334</v>
+        <v>46165.45833333334</v>
       </c>
       <c r="B142">
-        <v>729.981</v>
+        <v>1592.588</v>
       </c>
       <c r="C142">
-        <v>527</v>
+        <v>1078</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3961,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46164.46875</v>
+        <v>46165.46875</v>
       </c>
       <c r="B143">
-        <v>727.908</v>
+        <v>1618.126</v>
       </c>
       <c r="C143">
-        <v>512</v>
+        <v>1126</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3978,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46164.47916666666</v>
+        <v>46165.47916666666</v>
       </c>
       <c r="B144">
-        <v>687.395</v>
+        <v>1599.148</v>
       </c>
       <c r="C144">
-        <v>492</v>
+        <v>1142</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3995,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46164.48958333334</v>
+        <v>46165.48958333334</v>
       </c>
       <c r="B145">
-        <v>681.1900000000001</v>
+        <v>1605.431</v>
       </c>
       <c r="C145">
-        <v>478</v>
+        <v>1177</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +4012,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46164.5</v>
+        <v>46165.5</v>
       </c>
       <c r="B146">
-        <v>675.616</v>
+        <v>1687.281</v>
       </c>
       <c r="C146">
-        <v>464</v>
+        <v>1178</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +4029,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46164.51041666666</v>
+        <v>46165.51041666666</v>
       </c>
       <c r="B147">
-        <v>668.851</v>
+        <v>1687.06</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1184</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +4046,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46164.52083333334</v>
+        <v>46165.52083333334</v>
       </c>
       <c r="B148">
-        <v>662.078</v>
+        <v>1684.973</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1204</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,13 +4063,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46164.53125</v>
+        <v>46165.53125</v>
       </c>
       <c r="B149">
-        <v>655.849</v>
+        <v>1682.822</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3504,13 +4080,13 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46164.54166666666</v>
+        <v>46165.54166666666</v>
       </c>
       <c r="B150">
-        <v>647.7569999999999</v>
+        <v>1686.313</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1251</v>
       </c>
       <c r="D150">
         <v>53</v>
@@ -3521,13 +4097,13 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46164.55208333334</v>
+        <v>46165.55208333334</v>
       </c>
       <c r="B151">
-        <v>636.329</v>
+        <v>1704.312</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>1304</v>
       </c>
       <c r="D151">
         <v>54</v>
@@ -3538,13 +4114,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46164.5625</v>
+        <v>46165.5625</v>
       </c>
       <c r="B152">
-        <v>613.67</v>
+        <v>1703.017</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>1326</v>
       </c>
       <c r="D152">
         <v>55</v>
@@ -3555,13 +4131,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46164.57291666666</v>
+        <v>46165.57291666666</v>
       </c>
       <c r="B153">
-        <v>590.326</v>
+        <v>1722.712</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="D153">
         <v>56</v>
@@ -3572,13 +4148,13 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46164.58333333334</v>
+        <v>46165.58333333334</v>
       </c>
       <c r="B154">
-        <v>609.354</v>
+        <v>1573.111</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>1351</v>
       </c>
       <c r="D154">
         <v>57</v>
@@ -3589,13 +4165,13 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46164.59375</v>
+        <v>46165.59375</v>
       </c>
       <c r="B155">
-        <v>598.149</v>
+        <v>1586.404</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>1395</v>
       </c>
       <c r="D155">
         <v>58</v>
@@ -3606,13 +4182,13 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46164.60416666666</v>
+        <v>46165.60416666666</v>
       </c>
       <c r="B156">
-        <v>584.995</v>
+        <v>1604.046</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>1421</v>
       </c>
       <c r="D156">
         <v>59</v>
@@ -3623,13 +4199,13 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46164.61458333334</v>
+        <v>46165.61458333334</v>
       </c>
       <c r="B157">
-        <v>604.95</v>
+        <v>1623.386</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="D157">
         <v>60</v>
@@ -3640,13 +4216,13 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46164.625</v>
+        <v>46165.625</v>
       </c>
       <c r="B158">
-        <v>584.232</v>
+        <v>1631.812</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="D158">
         <v>61</v>
@@ -3657,13 +4233,13 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46164.63541666666</v>
+        <v>46165.63541666666</v>
       </c>
       <c r="B159">
-        <v>571.936</v>
+        <v>1621.41</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>1585</v>
       </c>
       <c r="D159">
         <v>62</v>
@@ -3674,13 +4250,13 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46164.64583333334</v>
+        <v>46165.64583333334</v>
       </c>
       <c r="B160">
-        <v>562.206</v>
+        <v>1605.91</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>1644</v>
       </c>
       <c r="D160">
         <v>63</v>
@@ -3691,13 +4267,13 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46164.65625</v>
+        <v>46165.65625</v>
       </c>
       <c r="B161">
-        <v>551.4589999999999</v>
+        <v>1592.291</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>1718</v>
       </c>
       <c r="D161">
         <v>64</v>
@@ -3708,13 +4284,13 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46164.66666666666</v>
+        <v>46165.66666666666</v>
       </c>
       <c r="B162">
-        <v>540.091</v>
+        <v>1571.464</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>1755</v>
       </c>
       <c r="D162">
         <v>65</v>
@@ -3725,13 +4301,13 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46164.67708333334</v>
+        <v>46165.67708333334</v>
       </c>
       <c r="B163">
-        <v>531.514</v>
+        <v>1583.898</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>1764</v>
       </c>
       <c r="D163">
         <v>66</v>
@@ -3742,13 +4318,13 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46164.6875</v>
+        <v>46165.6875</v>
       </c>
       <c r="B164">
-        <v>523.713</v>
+        <v>1597.577</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>1811</v>
       </c>
       <c r="D164">
         <v>67</v>
@@ -3759,13 +4335,13 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46164.69791666666</v>
+        <v>46165.69791666666</v>
       </c>
       <c r="B165">
-        <v>513.831</v>
+        <v>1737.044</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>1873</v>
       </c>
       <c r="D165">
         <v>68</v>
@@ -3776,13 +4352,13 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46164.70833333334</v>
+        <v>46165.70833333334</v>
       </c>
       <c r="B166">
-        <v>498.973</v>
+        <v>1690.283</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>1870</v>
       </c>
       <c r="D166">
         <v>69</v>
@@ -3793,13 +4369,13 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46164.71875</v>
+        <v>46165.71875</v>
       </c>
       <c r="B167">
-        <v>495.552</v>
+        <v>1784.509</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>1823</v>
       </c>
       <c r="D167">
         <v>70</v>
@@ -3810,13 +4386,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46164.72916666666</v>
+        <v>46165.72916666666</v>
       </c>
       <c r="B168">
-        <v>492.963</v>
+        <v>1784.414</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1803</v>
       </c>
       <c r="D168">
         <v>71</v>
@@ -3827,13 +4403,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46164.73958333334</v>
+        <v>46165.73958333334</v>
       </c>
       <c r="B169">
-        <v>487.806</v>
+        <v>1780.55</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1795</v>
       </c>
       <c r="D169">
         <v>72</v>
@@ -3844,13 +4420,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46164.75</v>
+        <v>46165.75</v>
       </c>
       <c r="B170">
-        <v>472.674</v>
+        <v>1796.571</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1790</v>
       </c>
       <c r="D170">
         <v>73</v>
@@ -3861,13 +4437,13 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46164.76041666666</v>
+        <v>46165.76041666666</v>
       </c>
       <c r="B171">
-        <v>475.666</v>
+        <v>1816.266</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1754</v>
       </c>
       <c r="D171">
         <v>74</v>
@@ -3878,13 +4454,13 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46164.77083333334</v>
+        <v>46165.77083333334</v>
       </c>
       <c r="B172">
-        <v>477.614</v>
+        <v>1833.886</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1741</v>
       </c>
       <c r="D172">
         <v>75</v>
@@ -3895,13 +4471,13 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46164.78125</v>
+        <v>46165.78125</v>
       </c>
       <c r="B173">
-        <v>479.918</v>
+        <v>1851.523</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1729</v>
       </c>
       <c r="D173">
         <v>76</v>
@@ -3912,13 +4488,13 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46164.79166666666</v>
+        <v>46165.79166666666</v>
       </c>
       <c r="B174">
-        <v>454.593</v>
+        <v>1828.73</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>1887</v>
       </c>
       <c r="D174">
         <v>77</v>
@@ -3929,13 +4505,13 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46164.80208333334</v>
+        <v>46165.80208333334</v>
       </c>
       <c r="B175">
-        <v>464.329</v>
+        <v>1849.967</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>2078</v>
       </c>
       <c r="D175">
         <v>78</v>
@@ -3946,13 +4522,13 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46164.8125</v>
+        <v>46165.8125</v>
       </c>
       <c r="B176">
-        <v>475.979</v>
+        <v>1870.452</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>2136</v>
       </c>
       <c r="D176">
         <v>79</v>
@@ -3963,13 +4539,13 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46164.82291666666</v>
+        <v>46165.82291666666</v>
       </c>
       <c r="B177">
-        <v>507.899</v>
+        <v>1893.761</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="D177">
         <v>80</v>
@@ -3980,13 +4556,13 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46164.83333333334</v>
+        <v>46165.83333333334</v>
       </c>
       <c r="B178">
-        <v>544.415</v>
+        <v>1917.308</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>2019</v>
       </c>
       <c r="D178">
         <v>81</v>
@@ -3997,13 +4573,13 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46164.84375</v>
+        <v>46165.84375</v>
       </c>
       <c r="B179">
-        <v>553.9160000000001</v>
+        <v>1923.207</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1977</v>
       </c>
       <c r="D179">
         <v>82</v>
@@ -4014,13 +4590,13 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46164.85416666666</v>
+        <v>46165.85416666666</v>
       </c>
       <c r="B180">
-        <v>563.788</v>
+        <v>1931.507</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>1962</v>
       </c>
       <c r="D180">
         <v>83</v>
@@ -4031,13 +4607,13 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46164.86458333334</v>
+        <v>46165.86458333334</v>
       </c>
       <c r="B181">
-        <v>574.63</v>
+        <v>1937.334</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>1685</v>
       </c>
       <c r="D181">
         <v>84</v>
@@ -4048,13 +4624,13 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46164.875</v>
+        <v>46165.875</v>
       </c>
       <c r="B182">
-        <v>610.204</v>
+        <v>1933.713</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1556</v>
       </c>
       <c r="D182">
         <v>85</v>
@@ -4065,13 +4641,13 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46164.88541666666</v>
+        <v>46165.88541666666</v>
       </c>
       <c r="B183">
-        <v>602.856</v>
+        <v>1931.651</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1636</v>
       </c>
       <c r="D183">
         <v>86</v>
@@ -4082,13 +4658,13 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46164.89583333334</v>
+        <v>46165.89583333334</v>
       </c>
       <c r="B184">
-        <v>613.211</v>
+        <v>1930.939</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>1588</v>
       </c>
       <c r="D184">
         <v>87</v>
@@ -4099,13 +4675,13 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46164.90625</v>
+        <v>46165.90625</v>
       </c>
       <c r="B185">
-        <v>623.426</v>
+        <v>1929.865</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="D185">
         <v>88</v>
@@ -4116,13 +4692,13 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46164.91666666666</v>
+        <v>46165.91666666666</v>
       </c>
       <c r="B186">
-        <v>691.136</v>
+        <v>1920.425</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>1205</v>
       </c>
       <c r="D186">
         <v>89</v>
@@ -4133,13 +4709,13 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46164.92708333334</v>
+        <v>46165.92708333334</v>
       </c>
       <c r="B187">
-        <v>702.423</v>
+        <v>1911.124</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>976</v>
       </c>
       <c r="D187">
         <v>90</v>
@@ -4150,13 +4726,13 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46164.9375</v>
+        <v>46165.9375</v>
       </c>
       <c r="B188">
-        <v>716.958</v>
+        <v>1900.57</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="D188">
         <v>91</v>
@@ -4167,13 +4743,13 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46164.94791666666</v>
+        <v>46165.94791666666</v>
       </c>
       <c r="B189">
-        <v>728.6130000000001</v>
+        <v>1889.233</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="D189">
         <v>92</v>
@@ -4184,13 +4760,13 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46164.95833333334</v>
+        <v>46165.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>1864.418</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="D190">
         <v>93</v>
@@ -4201,13 +4777,13 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46164.96875</v>
+        <v>46165.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>1855.041</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="D191">
         <v>94</v>
@@ -4218,13 +4794,13 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46164.97916666666</v>
+        <v>46165.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>1855.074</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="D192">
         <v>95</v>
@@ -4235,19 +4811,3283 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46164.98958333334</v>
+        <v>46165.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>1859.566</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1088</v>
       </c>
       <c r="D193">
         <v>96</v>
       </c>
       <c r="E193" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B194">
+        <v>1811.416</v>
+      </c>
+      <c r="C194">
+        <v>1309</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46166.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>1812.31</v>
+      </c>
+      <c r="C195">
+        <v>1446</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46166.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>1795.297</v>
+      </c>
+      <c r="C196">
+        <v>1606</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46166.03125</v>
+      </c>
+      <c r="B197">
+        <v>1789.074</v>
+      </c>
+      <c r="C197">
+        <v>1658</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46166.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>1811.43</v>
+      </c>
+      <c r="C198">
+        <v>1713</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46166.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>1798.459</v>
+      </c>
+      <c r="C199">
+        <v>1773</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46166.0625</v>
+      </c>
+      <c r="B200">
+        <v>1807.366</v>
+      </c>
+      <c r="C200">
+        <v>1812</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46166.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>1823.262</v>
+      </c>
+      <c r="C201">
+        <v>1818</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46166.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>1868.083</v>
+      </c>
+      <c r="C202">
+        <v>1840</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46166.09375</v>
+      </c>
+      <c r="B203">
+        <v>1861.821</v>
+      </c>
+      <c r="C203">
+        <v>1842</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46166.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1852.286</v>
+      </c>
+      <c r="C204">
+        <v>1834</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46166.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>1852.235</v>
+      </c>
+      <c r="C205">
+        <v>1840</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46166.125</v>
+      </c>
+      <c r="B206">
+        <v>1871.336</v>
+      </c>
+      <c r="C206">
+        <v>1907</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46166.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>1853.976</v>
+      </c>
+      <c r="C207">
+        <v>1914</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46166.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>1853.129</v>
+      </c>
+      <c r="C208">
+        <v>1902</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46166.15625</v>
+      </c>
+      <c r="B209">
+        <v>1857.906</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46166.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>1852.42</v>
+      </c>
+      <c r="C210">
+        <v>1890</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46166.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>1852.241</v>
+      </c>
+      <c r="C211">
+        <v>1866</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46166.1875</v>
+      </c>
+      <c r="B212">
+        <v>1866.713</v>
+      </c>
+      <c r="C212">
+        <v>1819</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46166.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>1867.878</v>
+      </c>
+      <c r="C213">
+        <v>1748</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46166.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>1847.79</v>
+      </c>
+      <c r="C214">
+        <v>1681</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46166.21875</v>
+      </c>
+      <c r="B215">
+        <v>1838.216</v>
+      </c>
+      <c r="C215">
+        <v>1612</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46166.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>1819.556</v>
+      </c>
+      <c r="C216">
+        <v>1572</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46166.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>1799.798</v>
+      </c>
+      <c r="C217">
+        <v>1523</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46166.25</v>
+      </c>
+      <c r="B218">
+        <v>1705.345</v>
+      </c>
+      <c r="C218">
+        <v>1475</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46166.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>1643.878</v>
+      </c>
+      <c r="C219">
+        <v>1369</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46166.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>1575.116</v>
+      </c>
+      <c r="C220">
+        <v>1271</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46166.28125</v>
+      </c>
+      <c r="B221">
+        <v>1501.346</v>
+      </c>
+      <c r="C221">
+        <v>1176</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46166.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>1447.393</v>
+      </c>
+      <c r="C222">
+        <v>1136</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46166.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>1403.698</v>
+      </c>
+      <c r="C223">
+        <v>1139</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46166.3125</v>
+      </c>
+      <c r="B224">
+        <v>1329.458</v>
+      </c>
+      <c r="C224">
+        <v>1148</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46166.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>1287.761</v>
+      </c>
+      <c r="C225">
+        <v>1163</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46166.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1309.43</v>
+      </c>
+      <c r="C226">
+        <v>1168</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46166.34375</v>
+      </c>
+      <c r="B227">
+        <v>1280.33</v>
+      </c>
+      <c r="C227">
+        <v>1155</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46166.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>1263.9</v>
+      </c>
+      <c r="C228">
+        <v>1109</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46166.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>1188.658</v>
+      </c>
+      <c r="C229">
+        <v>1089</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46166.375</v>
+      </c>
+      <c r="B230">
+        <v>1207.933</v>
+      </c>
+      <c r="C230">
+        <v>1060</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46166.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>1124.693</v>
+      </c>
+      <c r="C231">
+        <v>1026</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46166.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>1134.112</v>
+      </c>
+      <c r="C232">
+        <v>1015</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46166.40625</v>
+      </c>
+      <c r="B233">
+        <v>1142.163</v>
+      </c>
+      <c r="C233">
+        <v>1059</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46166.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>1277.805</v>
+      </c>
+      <c r="C234">
+        <v>1223</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46166.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>1302.72</v>
+      </c>
+      <c r="C235">
+        <v>1218</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46166.4375</v>
+      </c>
+      <c r="B236">
+        <v>1324.892</v>
+      </c>
+      <c r="C236">
+        <v>1195</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46166.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>1347.3</v>
+      </c>
+      <c r="C237">
+        <v>1176</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46166.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>1372.49</v>
+      </c>
+      <c r="C238">
+        <v>1146</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46166.46875</v>
+      </c>
+      <c r="B239">
+        <v>1376.019</v>
+      </c>
+      <c r="C239">
+        <v>1153</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46166.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>1378.4</v>
+      </c>
+      <c r="C240">
+        <v>1170</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46166.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>1382.179</v>
+      </c>
+      <c r="C241">
+        <v>1289</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46166.5</v>
+      </c>
+      <c r="B242">
+        <v>1445.733</v>
+      </c>
+      <c r="C242">
+        <v>1278</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46166.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>1434.368</v>
+      </c>
+      <c r="C243">
+        <v>1332</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46166.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>1423.547</v>
+      </c>
+      <c r="C244">
+        <v>1425</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46166.53125</v>
+      </c>
+      <c r="B245">
+        <v>1412.871</v>
+      </c>
+      <c r="C245">
+        <v>1516</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46166.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>1396.142</v>
+      </c>
+      <c r="C246">
+        <v>1594</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46166.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>1384.446</v>
+      </c>
+      <c r="C247">
+        <v>1584</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46166.5625</v>
+      </c>
+      <c r="B248">
+        <v>1374.341</v>
+      </c>
+      <c r="C248">
+        <v>1544</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46166.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>1363.109</v>
+      </c>
+      <c r="C249">
+        <v>1555</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46166.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>1361.022</v>
+      </c>
+      <c r="C250">
+        <v>1552</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46166.59375</v>
+      </c>
+      <c r="B251">
+        <v>1368.292</v>
+      </c>
+      <c r="C251">
+        <v>1546</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46166.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>1376.391</v>
+      </c>
+      <c r="C252">
+        <v>1542</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46166.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>1384.176</v>
+      </c>
+      <c r="C253">
+        <v>1517</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46166.625</v>
+      </c>
+      <c r="B254">
+        <v>1337.034</v>
+      </c>
+      <c r="C254">
+        <v>1485</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46166.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>1343.922</v>
+      </c>
+      <c r="C255">
+        <v>1470</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46166.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>1348.116</v>
+      </c>
+      <c r="C256">
+        <v>1452</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46166.65625</v>
+      </c>
+      <c r="B257">
+        <v>1353.883</v>
+      </c>
+      <c r="C257">
+        <v>1430</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46166.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1355.016</v>
+      </c>
+      <c r="C258">
+        <v>1422</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46166.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1343.574</v>
+      </c>
+      <c r="C259">
+        <v>1405</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46166.6875</v>
+      </c>
+      <c r="B260">
+        <v>1333.14</v>
+      </c>
+      <c r="C260">
+        <v>1357</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46166.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>1323.646</v>
+      </c>
+      <c r="C261">
+        <v>1330</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46166.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>1211.828</v>
+      </c>
+      <c r="C262">
+        <v>1241</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46166.71875</v>
+      </c>
+      <c r="B263">
+        <v>1278.969</v>
+      </c>
+      <c r="C263">
+        <v>1232</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46166.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>1303.341</v>
+      </c>
+      <c r="C264">
+        <v>1180</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46166.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>1268.978</v>
+      </c>
+      <c r="C265">
+        <v>1153</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46166.75</v>
+      </c>
+      <c r="B266">
+        <v>1225.878</v>
+      </c>
+      <c r="C266">
+        <v>1061</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46166.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>1208.091</v>
+      </c>
+      <c r="C267">
+        <v>975</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46166.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>1189.307</v>
+      </c>
+      <c r="C268">
+        <v>883</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46166.78125</v>
+      </c>
+      <c r="B269">
+        <v>1171.866</v>
+      </c>
+      <c r="C269">
+        <v>814</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46166.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>1149.454</v>
+      </c>
+      <c r="C270">
+        <v>772</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46166.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>1158.611</v>
+      </c>
+      <c r="C271">
+        <v>760</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46166.8125</v>
+      </c>
+      <c r="B272">
+        <v>1167.332</v>
+      </c>
+      <c r="C272">
+        <v>746</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46166.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>1174.411</v>
+      </c>
+      <c r="C273">
+        <v>729</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46166.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>1176.692</v>
+      </c>
+      <c r="C274">
+        <v>741</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46166.84375</v>
+      </c>
+      <c r="B275">
+        <v>1186.614</v>
+      </c>
+      <c r="C275">
+        <v>750</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46166.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>1194.013</v>
+      </c>
+      <c r="C276">
+        <v>775</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46166.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>1201.818</v>
+      </c>
+      <c r="C277">
+        <v>805</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46166.875</v>
+      </c>
+      <c r="B278">
+        <v>1208.013</v>
+      </c>
+      <c r="C278">
+        <v>854</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46166.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>1204.207</v>
+      </c>
+      <c r="C279">
+        <v>883</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46166.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>1201.757</v>
+      </c>
+      <c r="C280">
+        <v>936</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46166.90625</v>
+      </c>
+      <c r="B281">
+        <v>1198.726</v>
+      </c>
+      <c r="C281">
+        <v>959</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46166.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>1186.353</v>
+      </c>
+      <c r="C282">
+        <v>968</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46166.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>1180.509</v>
+      </c>
+      <c r="C283">
+        <v>954</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46166.9375</v>
+      </c>
+      <c r="B284">
+        <v>1175.46</v>
+      </c>
+      <c r="C284">
+        <v>951</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46166.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>1166.416</v>
+      </c>
+      <c r="C285">
+        <v>931</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46166.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>1096.828</v>
+      </c>
+      <c r="C286">
+        <v>922</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46166.96875</v>
+      </c>
+      <c r="B287">
+        <v>1081.381</v>
+      </c>
+      <c r="C287">
+        <v>911</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46166.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>1064.218</v>
+      </c>
+      <c r="C288">
+        <v>874</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46166.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>1054.274</v>
+      </c>
+      <c r="C289">
+        <v>844</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B290">
+        <v>972.653</v>
+      </c>
+      <c r="C290">
+        <v>791</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46167.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>960.2619999999999</v>
+      </c>
+      <c r="C291">
+        <v>768</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46167.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>947.4160000000001</v>
+      </c>
+      <c r="C292">
+        <v>751</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46167.03125</v>
+      </c>
+      <c r="B293">
+        <v>930.179</v>
+      </c>
+      <c r="C293">
+        <v>738</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46167.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>933.896</v>
+      </c>
+      <c r="C294">
+        <v>725</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46167.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>916.247</v>
+      </c>
+      <c r="C295">
+        <v>711</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46167.0625</v>
+      </c>
+      <c r="B296">
+        <v>896.357</v>
+      </c>
+      <c r="C296">
+        <v>705</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46167.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>877.948</v>
+      </c>
+      <c r="C297">
+        <v>706</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46167.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>836.875</v>
+      </c>
+      <c r="C298">
+        <v>721</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46167.09375</v>
+      </c>
+      <c r="B299">
+        <v>824.187</v>
+      </c>
+      <c r="C299">
+        <v>759</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46167.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>816.197</v>
+      </c>
+      <c r="C300">
+        <v>839</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46167.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>791.1660000000001</v>
+      </c>
+      <c r="C301">
+        <v>938</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46167.125</v>
+      </c>
+      <c r="B302">
+        <v>788.485</v>
+      </c>
+      <c r="C302">
+        <v>933</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46167.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>786.563</v>
+      </c>
+      <c r="C303">
+        <v>929</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46167.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>783.505</v>
+      </c>
+      <c r="C304">
+        <v>896</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46167.15625</v>
+      </c>
+      <c r="B305">
+        <v>792.538</v>
+      </c>
+      <c r="C305">
+        <v>856</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46167.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>864.225</v>
+      </c>
+      <c r="C306">
+        <v>810</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46167.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>859.821</v>
+      </c>
+      <c r="C307">
+        <v>740</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46167.1875</v>
+      </c>
+      <c r="B308">
+        <v>853.453</v>
+      </c>
+      <c r="C308">
+        <v>701</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46167.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>829.51</v>
+      </c>
+      <c r="C309">
+        <v>685</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46167.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>812.091</v>
+      </c>
+      <c r="C310">
+        <v>688</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46167.21875</v>
+      </c>
+      <c r="B311">
+        <v>787.864</v>
+      </c>
+      <c r="C311">
+        <v>722</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46167.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>758.96</v>
+      </c>
+      <c r="C312">
+        <v>732</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46167.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>721.144</v>
+      </c>
+      <c r="C313">
+        <v>708</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46167.25</v>
+      </c>
+      <c r="B314">
+        <v>666.047</v>
+      </c>
+      <c r="C314">
+        <v>666</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46167.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>625.374</v>
+      </c>
+      <c r="C315">
+        <v>617</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46167.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>594.192</v>
+      </c>
+      <c r="C316">
+        <v>558</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46167.28125</v>
+      </c>
+      <c r="B317">
+        <v>552.171</v>
+      </c>
+      <c r="C317">
+        <v>504</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46167.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>518.33</v>
+      </c>
+      <c r="C318">
+        <v>441</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46167.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>470.288</v>
+      </c>
+      <c r="C319">
+        <v>366</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46167.3125</v>
+      </c>
+      <c r="B320">
+        <v>420.938</v>
+      </c>
+      <c r="C320">
+        <v>310</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46167.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>375.583</v>
+      </c>
+      <c r="C321">
+        <v>283</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46167.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>372.912</v>
+      </c>
+      <c r="C322">
+        <v>244</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46167.34375</v>
+      </c>
+      <c r="B323">
+        <v>367.143</v>
+      </c>
+      <c r="C323">
+        <v>225</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46167.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>358.106</v>
+      </c>
+      <c r="C324">
+        <v>236</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46167.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>350.828</v>
+      </c>
+      <c r="C325">
+        <v>237</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46167.375</v>
+      </c>
+      <c r="B326">
+        <v>357.36</v>
+      </c>
+      <c r="C326">
+        <v>242</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46167.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>368.321</v>
+      </c>
+      <c r="C327">
+        <v>265</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46167.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>356.227</v>
+      </c>
+      <c r="C328">
+        <v>278</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46167.40625</v>
+      </c>
+      <c r="B329">
+        <v>360.337</v>
+      </c>
+      <c r="C329">
+        <v>274</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46167.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>356.952</v>
+      </c>
+      <c r="C330">
+        <v>304</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46167.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>365.662</v>
+      </c>
+      <c r="C331">
+        <v>347</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46167.4375</v>
+      </c>
+      <c r="B332">
+        <v>374.362</v>
+      </c>
+      <c r="C332">
+        <v>365</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46167.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>383.482</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46167.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>451.893</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46167.46875</v>
+      </c>
+      <c r="B335">
+        <v>462.935</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46167.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>473.369</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46167.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>485.059</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46167.5</v>
+      </c>
+      <c r="B338">
+        <v>501.682</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46167.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>506.619</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46167.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>511.974</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46167.53125</v>
+      </c>
+      <c r="B341">
+        <v>516.7329999999999</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46167.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>482.299</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46167.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>501.074</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46167.5625</v>
+      </c>
+      <c r="B344">
+        <v>494.035</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46167.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>489.221</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46167.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>504.458</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46167.59375</v>
+      </c>
+      <c r="B347">
+        <v>509.158</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46167.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>515.256</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46167.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>521.371</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46167.625</v>
+      </c>
+      <c r="B350">
+        <v>533.936</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46167.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>550.569</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46167.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>567.665</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46167.65625</v>
+      </c>
+      <c r="B353">
+        <v>585.254</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46167.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>561.723</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46167.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>575.25</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46167.6875</v>
+      </c>
+      <c r="B356">
+        <v>589.428</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46167.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>604.336</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46167.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>620.523</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46167.71875</v>
+      </c>
+      <c r="B359">
+        <v>629.793</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46167.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>638.202</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46167.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>646.609</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46167.75</v>
+      </c>
+      <c r="B362">
+        <v>673.963</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46167.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>693.61</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46167.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>712.08</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46167.78125</v>
+      </c>
+      <c r="B365">
+        <v>730.58</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46167.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>753.274</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46167.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>769.639</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46167.8125</v>
+      </c>
+      <c r="B368">
+        <v>781.79</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46167.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>795.009</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46167.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>820.181</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46167.84375</v>
+      </c>
+      <c r="B371">
+        <v>836.045</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46167.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>853.657</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46167.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>873.353</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46167.875</v>
+      </c>
+      <c r="B374">
+        <v>905.3339999999999</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46167.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>931.5700000000001</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46167.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>956.045</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46167.90625</v>
+      </c>
+      <c r="B377">
+        <v>982.253</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46167.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>1008.207</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46167.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>1028.843</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46167.9375</v>
+      </c>
+      <c r="B380">
+        <v>1047.814</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46167.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>1068.919</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46167.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46167.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46167.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46167.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.05.20261</t>
-  </si>
-  <si>
-    <t>25.05.20262</t>
-  </si>
-  <si>
-    <t>25.05.20263</t>
-  </si>
-  <si>
-    <t>25.05.20264</t>
-  </si>
-  <si>
-    <t>25.05.20265</t>
-  </si>
-  <si>
-    <t>25.05.20266</t>
-  </si>
-  <si>
-    <t>25.05.20267</t>
-  </si>
-  <si>
-    <t>25.05.20268</t>
-  </si>
-  <si>
-    <t>25.05.20269</t>
-  </si>
-  <si>
-    <t>25.05.202610</t>
-  </si>
-  <si>
-    <t>25.05.202611</t>
-  </si>
-  <si>
-    <t>25.05.202612</t>
-  </si>
-  <si>
-    <t>25.05.202613</t>
-  </si>
-  <si>
-    <t>25.05.202614</t>
-  </si>
-  <si>
-    <t>25.05.202615</t>
-  </si>
-  <si>
-    <t>25.05.202616</t>
-  </si>
-  <si>
-    <t>25.05.202617</t>
-  </si>
-  <si>
-    <t>25.05.202618</t>
-  </si>
-  <si>
-    <t>25.05.202619</t>
-  </si>
-  <si>
-    <t>25.05.202620</t>
-  </si>
-  <si>
-    <t>25.05.202621</t>
-  </si>
-  <si>
-    <t>25.05.202622</t>
-  </si>
-  <si>
-    <t>25.05.202623</t>
-  </si>
-  <si>
-    <t>25.05.202624</t>
-  </si>
-  <si>
-    <t>25.05.202625</t>
-  </si>
-  <si>
-    <t>25.05.202626</t>
-  </si>
-  <si>
-    <t>25.05.202627</t>
-  </si>
-  <si>
-    <t>25.05.202628</t>
-  </si>
-  <si>
-    <t>25.05.202629</t>
-  </si>
-  <si>
-    <t>25.05.202630</t>
-  </si>
-  <si>
-    <t>25.05.202631</t>
-  </si>
-  <si>
-    <t>25.05.202632</t>
-  </si>
-  <si>
-    <t>25.05.202633</t>
-  </si>
-  <si>
-    <t>25.05.202634</t>
-  </si>
-  <si>
-    <t>25.05.202635</t>
-  </si>
-  <si>
-    <t>25.05.202636</t>
-  </si>
-  <si>
-    <t>25.05.202637</t>
-  </si>
-  <si>
-    <t>25.05.202638</t>
-  </si>
-  <si>
-    <t>25.05.202639</t>
-  </si>
-  <si>
-    <t>25.05.202640</t>
-  </si>
-  <si>
-    <t>25.05.202641</t>
-  </si>
-  <si>
-    <t>25.05.202642</t>
-  </si>
-  <si>
-    <t>25.05.202643</t>
-  </si>
-  <si>
-    <t>25.05.202644</t>
-  </si>
-  <si>
-    <t>25.05.202645</t>
-  </si>
-  <si>
-    <t>25.05.202646</t>
-  </si>
-  <si>
-    <t>25.05.202647</t>
-  </si>
-  <si>
-    <t>25.05.202648</t>
-  </si>
-  <si>
-    <t>25.05.202649</t>
-  </si>
-  <si>
-    <t>25.05.202650</t>
-  </si>
-  <si>
-    <t>25.05.202651</t>
-  </si>
-  <si>
-    <t>25.05.202652</t>
-  </si>
-  <si>
-    <t>25.05.202653</t>
-  </si>
-  <si>
-    <t>25.05.202654</t>
-  </si>
-  <si>
-    <t>25.05.202655</t>
-  </si>
-  <si>
-    <t>25.05.202656</t>
-  </si>
-  <si>
-    <t>25.05.202657</t>
-  </si>
-  <si>
-    <t>25.05.202658</t>
-  </si>
-  <si>
-    <t>25.05.202659</t>
-  </si>
-  <si>
-    <t>25.05.202660</t>
-  </si>
-  <si>
-    <t>25.05.202661</t>
-  </si>
-  <si>
-    <t>25.05.202662</t>
-  </si>
-  <si>
-    <t>25.05.202663</t>
-  </si>
-  <si>
-    <t>25.05.202664</t>
-  </si>
-  <si>
-    <t>25.05.202665</t>
-  </si>
-  <si>
-    <t>25.05.202666</t>
-  </si>
-  <si>
-    <t>25.05.202667</t>
-  </si>
-  <si>
-    <t>25.05.202668</t>
-  </si>
-  <si>
-    <t>25.05.202669</t>
-  </si>
-  <si>
-    <t>25.05.202670</t>
-  </si>
-  <si>
-    <t>25.05.202671</t>
-  </si>
-  <si>
-    <t>25.05.202672</t>
-  </si>
-  <si>
-    <t>25.05.202673</t>
-  </si>
-  <si>
-    <t>25.05.202674</t>
-  </si>
-  <si>
-    <t>25.05.202675</t>
-  </si>
-  <si>
-    <t>25.05.202676</t>
-  </si>
-  <si>
-    <t>25.05.202677</t>
-  </si>
-  <si>
-    <t>25.05.202678</t>
-  </si>
-  <si>
-    <t>25.05.202679</t>
-  </si>
-  <si>
-    <t>25.05.202680</t>
-  </si>
-  <si>
-    <t>25.05.202681</t>
-  </si>
-  <si>
-    <t>25.05.202682</t>
-  </si>
-  <si>
-    <t>25.05.202683</t>
-  </si>
-  <si>
-    <t>25.05.202684</t>
-  </si>
-  <si>
-    <t>25.05.202685</t>
-  </si>
-  <si>
-    <t>25.05.202686</t>
-  </si>
-  <si>
-    <t>25.05.202687</t>
-  </si>
-  <si>
-    <t>25.05.202688</t>
-  </si>
-  <si>
-    <t>25.05.202689</t>
-  </si>
-  <si>
-    <t>25.05.202690</t>
-  </si>
-  <si>
-    <t>25.05.202691</t>
-  </si>
-  <si>
-    <t>25.05.202692</t>
-  </si>
-  <si>
-    <t>25.05.202693</t>
-  </si>
-  <si>
-    <t>25.05.202694</t>
-  </si>
-  <si>
-    <t>25.05.202695</t>
-  </si>
-  <si>
-    <t>25.05.202696</t>
-  </si>
-  <si>
     <t>26.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>26.05.202696</t>
+  </si>
+  <si>
+    <t>27.05.20261</t>
+  </si>
+  <si>
+    <t>27.05.20262</t>
+  </si>
+  <si>
+    <t>27.05.20263</t>
+  </si>
+  <si>
+    <t>27.05.20264</t>
+  </si>
+  <si>
+    <t>27.05.20265</t>
+  </si>
+  <si>
+    <t>27.05.20266</t>
+  </si>
+  <si>
+    <t>27.05.20267</t>
+  </si>
+  <si>
+    <t>27.05.20268</t>
+  </si>
+  <si>
+    <t>27.05.20269</t>
+  </si>
+  <si>
+    <t>27.05.202610</t>
+  </si>
+  <si>
+    <t>27.05.202611</t>
+  </si>
+  <si>
+    <t>27.05.202612</t>
+  </si>
+  <si>
+    <t>27.05.202613</t>
+  </si>
+  <si>
+    <t>27.05.202614</t>
+  </si>
+  <si>
+    <t>27.05.202615</t>
+  </si>
+  <si>
+    <t>27.05.202616</t>
+  </si>
+  <si>
+    <t>27.05.202617</t>
+  </si>
+  <si>
+    <t>27.05.202618</t>
+  </si>
+  <si>
+    <t>27.05.202619</t>
+  </si>
+  <si>
+    <t>27.05.202620</t>
+  </si>
+  <si>
+    <t>27.05.202621</t>
+  </si>
+  <si>
+    <t>27.05.202622</t>
+  </si>
+  <si>
+    <t>27.05.202623</t>
+  </si>
+  <si>
+    <t>27.05.202624</t>
+  </si>
+  <si>
+    <t>27.05.202625</t>
+  </si>
+  <si>
+    <t>27.05.202626</t>
+  </si>
+  <si>
+    <t>27.05.202627</t>
+  </si>
+  <si>
+    <t>27.05.202628</t>
+  </si>
+  <si>
+    <t>27.05.202629</t>
+  </si>
+  <si>
+    <t>27.05.202630</t>
+  </si>
+  <si>
+    <t>27.05.202631</t>
+  </si>
+  <si>
+    <t>27.05.202632</t>
+  </si>
+  <si>
+    <t>27.05.202633</t>
+  </si>
+  <si>
+    <t>27.05.202634</t>
+  </si>
+  <si>
+    <t>27.05.202635</t>
+  </si>
+  <si>
+    <t>27.05.202636</t>
+  </si>
+  <si>
+    <t>27.05.202637</t>
+  </si>
+  <si>
+    <t>27.05.202638</t>
+  </si>
+  <si>
+    <t>27.05.202639</t>
+  </si>
+  <si>
+    <t>27.05.202640</t>
+  </si>
+  <si>
+    <t>27.05.202641</t>
+  </si>
+  <si>
+    <t>27.05.202642</t>
+  </si>
+  <si>
+    <t>27.05.202643</t>
+  </si>
+  <si>
+    <t>27.05.202644</t>
+  </si>
+  <si>
+    <t>27.05.202645</t>
+  </si>
+  <si>
+    <t>27.05.202646</t>
+  </si>
+  <si>
+    <t>27.05.202647</t>
+  </si>
+  <si>
+    <t>27.05.202648</t>
+  </si>
+  <si>
+    <t>27.05.202649</t>
+  </si>
+  <si>
+    <t>27.05.202650</t>
+  </si>
+  <si>
+    <t>27.05.202651</t>
+  </si>
+  <si>
+    <t>27.05.202652</t>
+  </si>
+  <si>
+    <t>27.05.202653</t>
+  </si>
+  <si>
+    <t>27.05.202654</t>
+  </si>
+  <si>
+    <t>27.05.202655</t>
+  </si>
+  <si>
+    <t>27.05.202656</t>
+  </si>
+  <si>
+    <t>27.05.202657</t>
+  </si>
+  <si>
+    <t>27.05.202658</t>
+  </si>
+  <si>
+    <t>27.05.202659</t>
+  </si>
+  <si>
+    <t>27.05.202660</t>
+  </si>
+  <si>
+    <t>27.05.202661</t>
+  </si>
+  <si>
+    <t>27.05.202662</t>
+  </si>
+  <si>
+    <t>27.05.202663</t>
+  </si>
+  <si>
+    <t>27.05.202664</t>
+  </si>
+  <si>
+    <t>27.05.202665</t>
+  </si>
+  <si>
+    <t>27.05.202666</t>
+  </si>
+  <si>
+    <t>27.05.202667</t>
+  </si>
+  <si>
+    <t>27.05.202668</t>
+  </si>
+  <si>
+    <t>27.05.202669</t>
+  </si>
+  <si>
+    <t>27.05.202670</t>
+  </si>
+  <si>
+    <t>27.05.202671</t>
+  </si>
+  <si>
+    <t>27.05.202672</t>
+  </si>
+  <si>
+    <t>27.05.202673</t>
+  </si>
+  <si>
+    <t>27.05.202674</t>
+  </si>
+  <si>
+    <t>27.05.202675</t>
+  </si>
+  <si>
+    <t>27.05.202676</t>
+  </si>
+  <si>
+    <t>27.05.202677</t>
+  </si>
+  <si>
+    <t>27.05.202678</t>
+  </si>
+  <si>
+    <t>27.05.202679</t>
+  </si>
+  <si>
+    <t>27.05.202680</t>
+  </si>
+  <si>
+    <t>27.05.202681</t>
+  </si>
+  <si>
+    <t>27.05.202682</t>
+  </si>
+  <si>
+    <t>27.05.202683</t>
+  </si>
+  <si>
+    <t>27.05.202684</t>
+  </si>
+  <si>
+    <t>27.05.202685</t>
+  </si>
+  <si>
+    <t>27.05.202686</t>
+  </si>
+  <si>
+    <t>27.05.202687</t>
+  </si>
+  <si>
+    <t>27.05.202688</t>
+  </si>
+  <si>
+    <t>27.05.202689</t>
+  </si>
+  <si>
+    <t>27.05.202690</t>
+  </si>
+  <si>
+    <t>27.05.202691</t>
+  </si>
+  <si>
+    <t>27.05.202692</t>
+  </si>
+  <si>
+    <t>27.05.202693</t>
+  </si>
+  <si>
+    <t>27.05.202694</t>
+  </si>
+  <si>
+    <t>27.05.202695</t>
+  </si>
+  <si>
+    <t>27.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
-        <v>972.653</v>
+        <v>1120.118</v>
       </c>
       <c r="C2">
-        <v>791</v>
+        <v>1250</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
-        <v>960.2619999999999</v>
+        <v>1160.955</v>
       </c>
       <c r="C3">
-        <v>768</v>
+        <v>1321</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
-        <v>947.4160000000001</v>
+        <v>1196.695</v>
       </c>
       <c r="C4">
-        <v>751</v>
+        <v>1383</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
-        <v>930.179</v>
+        <v>1233.087</v>
       </c>
       <c r="C5">
-        <v>738</v>
+        <v>1430</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
-        <v>933.896</v>
+        <v>1314.219</v>
       </c>
       <c r="C6">
-        <v>725</v>
+        <v>1487</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
-        <v>916.247</v>
+        <v>1329.801</v>
       </c>
       <c r="C7">
-        <v>711</v>
+        <v>1548</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
-        <v>896.357</v>
+        <v>1353.694</v>
       </c>
       <c r="C8">
-        <v>705</v>
+        <v>1618</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
-        <v>877.948</v>
+        <v>1376.095</v>
       </c>
       <c r="C9">
-        <v>706</v>
+        <v>1694</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
-        <v>836.875</v>
+        <v>1398.617</v>
       </c>
       <c r="C10">
-        <v>721</v>
+        <v>1768</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
-        <v>824.187</v>
+        <v>1421.584</v>
       </c>
       <c r="C11">
-        <v>759</v>
+        <v>1812</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
-        <v>816.197</v>
+        <v>1434.341</v>
       </c>
       <c r="C12">
-        <v>839</v>
+        <v>1850</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
-        <v>791.1660000000001</v>
+        <v>1462.321</v>
       </c>
       <c r="C13">
-        <v>938</v>
+        <v>1856</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
-        <v>788.485</v>
+        <v>1502.288</v>
       </c>
       <c r="C14">
-        <v>933</v>
+        <v>1888</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
-        <v>786.563</v>
+        <v>1524.347</v>
       </c>
       <c r="C15">
-        <v>929</v>
+        <v>1944</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
-        <v>783.505</v>
+        <v>1536.819</v>
       </c>
       <c r="C16">
-        <v>896</v>
+        <v>1971</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
-        <v>792.538</v>
+        <v>1558.759</v>
       </c>
       <c r="C17">
-        <v>856</v>
+        <v>1965</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>864.225</v>
+        <v>1554.042</v>
       </c>
       <c r="C18">
-        <v>810</v>
+        <v>1954</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>859.821</v>
+        <v>1569.379</v>
       </c>
       <c r="C19">
-        <v>740</v>
+        <v>1953</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>853.453</v>
+        <v>1582.75</v>
       </c>
       <c r="C20">
-        <v>701</v>
+        <v>1945</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
-        <v>829.51</v>
+        <v>1602.65</v>
       </c>
       <c r="C21">
-        <v>685</v>
+        <v>1936</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>812.091</v>
+        <v>1584.713</v>
       </c>
       <c r="C22">
-        <v>688</v>
+        <v>1900</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>787.864</v>
+        <v>1557.816</v>
       </c>
       <c r="C23">
-        <v>722</v>
+        <v>1857</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>758.96</v>
+        <v>1532.091</v>
       </c>
       <c r="C24">
-        <v>732</v>
+        <v>1846</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
-        <v>721.144</v>
+        <v>1504.972</v>
       </c>
       <c r="C25">
-        <v>708</v>
+        <v>1758</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
-        <v>666.047</v>
+        <v>1415.558</v>
       </c>
       <c r="C26">
-        <v>666</v>
+        <v>1635</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>625.374</v>
+        <v>1367.098</v>
       </c>
       <c r="C27">
-        <v>617</v>
+        <v>1543</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>594.192</v>
+        <v>1301.627</v>
       </c>
       <c r="C28">
-        <v>558</v>
+        <v>1431</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>552.171</v>
+        <v>1236.599</v>
       </c>
       <c r="C29">
-        <v>504</v>
+        <v>1255</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>518.33</v>
+        <v>1129.476</v>
       </c>
       <c r="C30">
-        <v>441</v>
+        <v>1032</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>470.288</v>
+        <v>1058.591</v>
       </c>
       <c r="C31">
-        <v>366</v>
+        <v>792</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>420.938</v>
+        <v>993.784</v>
       </c>
       <c r="C32">
-        <v>310</v>
+        <v>649</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>375.583</v>
+        <v>937.283</v>
       </c>
       <c r="C33">
-        <v>283</v>
+        <v>535</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>372.912</v>
+        <v>844.943</v>
       </c>
       <c r="C34">
-        <v>244</v>
+        <v>495</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>367.143</v>
+        <v>828.136</v>
       </c>
       <c r="C35">
-        <v>225</v>
+        <v>496</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>358.106</v>
+        <v>803.448</v>
       </c>
       <c r="C36">
-        <v>236</v>
+        <v>516</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>350.828</v>
+        <v>784.869</v>
       </c>
       <c r="C37">
-        <v>237</v>
+        <v>497</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>357.36</v>
+        <v>813.218</v>
       </c>
       <c r="C38">
-        <v>242</v>
+        <v>504</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>368.321</v>
+        <v>812.7670000000001</v>
       </c>
       <c r="C39">
-        <v>265</v>
+        <v>522</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>356.227</v>
+        <v>808.965</v>
       </c>
       <c r="C40">
-        <v>278</v>
+        <v>526</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>360.337</v>
+        <v>806.551</v>
       </c>
       <c r="C41">
-        <v>274</v>
+        <v>555</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
-        <v>356.952</v>
+        <v>802.873</v>
       </c>
       <c r="C42">
-        <v>304</v>
+        <v>549</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>365.662</v>
+        <v>800.97</v>
       </c>
       <c r="C43">
-        <v>347</v>
+        <v>515</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>374.362</v>
+        <v>747.328</v>
       </c>
       <c r="C44">
-        <v>365</v>
+        <v>474</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
-        <v>383.482</v>
+        <v>745.619</v>
       </c>
       <c r="C45">
-        <v>377</v>
+        <v>494</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>451.893</v>
+        <v>753.667</v>
       </c>
       <c r="C46">
-        <v>369</v>
+        <v>536</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>462.935</v>
+        <v>754.921</v>
       </c>
       <c r="C47">
-        <v>375</v>
+        <v>544</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>473.369</v>
+        <v>756.567</v>
       </c>
       <c r="C48">
-        <v>371</v>
+        <v>574</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>485.059</v>
+        <v>758.197</v>
       </c>
       <c r="C49">
-        <v>353</v>
+        <v>578</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>501.682</v>
+        <v>766.8390000000001</v>
       </c>
       <c r="C50">
-        <v>357</v>
+        <v>644</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>506.619</v>
+        <v>763.717</v>
       </c>
       <c r="C51">
-        <v>327</v>
+        <v>650</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>511.974</v>
+        <v>762.74</v>
       </c>
       <c r="C52">
-        <v>329</v>
+        <v>658</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>516.7329999999999</v>
+        <v>760.05</v>
       </c>
       <c r="C53">
-        <v>332</v>
+        <v>688</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>482.299</v>
+        <v>763.246</v>
       </c>
       <c r="C54">
-        <v>329</v>
+        <v>685</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>501.074</v>
+        <v>759.234</v>
       </c>
       <c r="C55">
-        <v>355</v>
+        <v>664</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>494.035</v>
+        <v>801.323</v>
       </c>
       <c r="C56">
-        <v>389</v>
+        <v>678</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>489.221</v>
+        <v>797.653</v>
       </c>
       <c r="C57">
-        <v>409</v>
+        <v>686</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>504.458</v>
+        <v>759.356</v>
       </c>
       <c r="C58">
-        <v>415</v>
+        <v>650</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>509.158</v>
+        <v>799.001</v>
       </c>
       <c r="C59">
-        <v>432</v>
+        <v>658</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>515.256</v>
+        <v>790.748</v>
       </c>
       <c r="C60">
-        <v>380</v>
+        <v>685</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>521.371</v>
+        <v>740.2910000000001</v>
       </c>
       <c r="C61">
-        <v>372</v>
+        <v>698</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>533.936</v>
+        <v>719.247</v>
       </c>
       <c r="C62">
-        <v>385</v>
+        <v>693</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>550.569</v>
+        <v>709.186</v>
       </c>
       <c r="C63">
-        <v>437</v>
+        <v>673</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>567.665</v>
+        <v>698.943</v>
       </c>
       <c r="C64">
-        <v>447</v>
+        <v>690</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>585.254</v>
+        <v>691.0119999999999</v>
       </c>
       <c r="C65">
-        <v>450</v>
+        <v>683</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>561.723</v>
+        <v>667.586</v>
       </c>
       <c r="C66">
-        <v>491</v>
+        <v>699</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>575.25</v>
+        <v>684.222</v>
       </c>
       <c r="C67">
-        <v>507</v>
+        <v>752</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>589.428</v>
+        <v>662.734</v>
       </c>
       <c r="C68">
-        <v>580</v>
+        <v>745</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>604.336</v>
+        <v>639.027</v>
       </c>
       <c r="C69">
-        <v>497</v>
+        <v>738</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
-        <v>620.523</v>
+        <v>570.564</v>
       </c>
       <c r="C70">
-        <v>477</v>
+        <v>737</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>629.793</v>
+        <v>563.033</v>
       </c>
       <c r="C71">
-        <v>493</v>
+        <v>775</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>638.202</v>
+        <v>555.946</v>
       </c>
       <c r="C72">
-        <v>666</v>
+        <v>849</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>646.609</v>
+        <v>550.1</v>
       </c>
       <c r="C73">
-        <v>781</v>
+        <v>931</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>673.963</v>
+        <v>560.678</v>
       </c>
       <c r="C74">
-        <v>881</v>
+        <v>977</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>693.61</v>
+        <v>599.047</v>
       </c>
       <c r="C75">
-        <v>849</v>
+        <v>992</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>712.08</v>
+        <v>639.148</v>
       </c>
       <c r="C76">
-        <v>797</v>
+        <v>1000</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>730.58</v>
+        <v>679.217</v>
       </c>
       <c r="C77">
-        <v>785</v>
+        <v>1019</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>753.274</v>
+        <v>763.313</v>
       </c>
       <c r="C78">
-        <v>725</v>
+        <v>1059</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>769.639</v>
+        <v>821.378</v>
       </c>
       <c r="C79">
-        <v>680</v>
+        <v>1151</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
-        <v>781.79</v>
+        <v>883.564</v>
       </c>
       <c r="C80">
-        <v>726</v>
+        <v>1249</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>795.009</v>
+        <v>950.752</v>
       </c>
       <c r="C81">
-        <v>764</v>
+        <v>1356</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>820.181</v>
+        <v>1032.125</v>
       </c>
       <c r="C82">
-        <v>784</v>
+        <v>1417</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
-        <v>836.045</v>
+        <v>1085.591</v>
       </c>
       <c r="C83">
-        <v>791</v>
+        <v>1444</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
-        <v>853.657</v>
+        <v>1136.153</v>
       </c>
       <c r="C84">
-        <v>802</v>
+        <v>1466</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
-        <v>873.353</v>
+        <v>1189.243</v>
       </c>
       <c r="C85">
-        <v>790</v>
+        <v>1459</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
-        <v>905.3339999999999</v>
+        <v>1256.529</v>
       </c>
       <c r="C86">
-        <v>784</v>
+        <v>1471</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
-        <v>931.5700000000001</v>
+        <v>1299.035</v>
       </c>
       <c r="C87">
-        <v>799</v>
+        <v>1478</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
-        <v>956.045</v>
+        <v>1341.269</v>
       </c>
       <c r="C88">
-        <v>790</v>
+        <v>1495</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
-        <v>982.253</v>
+        <v>1381.938</v>
       </c>
       <c r="C89">
-        <v>797</v>
+        <v>1487</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
-        <v>1008.207</v>
+        <v>1395.934</v>
       </c>
       <c r="C90">
-        <v>848</v>
+        <v>1421</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
-        <v>1028.843</v>
+        <v>1399.102</v>
       </c>
       <c r="C91">
-        <v>883</v>
+        <v>1355</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
-        <v>1047.814</v>
+        <v>1397.987</v>
       </c>
       <c r="C92">
-        <v>945</v>
+        <v>1281</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
-        <v>1068.919</v>
+        <v>1392.711</v>
       </c>
       <c r="C93">
-        <v>993</v>
+        <v>1208</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>1034.835</v>
+        <v>1278.774</v>
       </c>
       <c r="C94">
-        <v>1026</v>
+        <v>1207</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
-        <v>1059.54</v>
+        <v>1248.323</v>
       </c>
       <c r="C95">
-        <v>1076</v>
+        <v>1169</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
-        <v>1073.375</v>
+        <v>1216.169</v>
       </c>
       <c r="C96">
-        <v>1158</v>
+        <v>1129</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B97">
-        <v>1103.701</v>
+        <v>1182.172</v>
       </c>
       <c r="C97">
-        <v>1215</v>
+        <v>1113</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B98">
-        <v>1120.118</v>
+        <v>968.177</v>
       </c>
       <c r="C98">
-        <v>1250</v>
+        <v>1077</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B99">
-        <v>1160.955</v>
+        <v>925.954</v>
       </c>
       <c r="C99">
-        <v>1321</v>
+        <v>1033</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B100">
-        <v>1196.695</v>
+        <v>886.772</v>
       </c>
       <c r="C100">
-        <v>1383</v>
+        <v>960</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B101">
-        <v>1233.087</v>
+        <v>846.275</v>
       </c>
       <c r="C101">
-        <v>1430</v>
+        <v>885</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B102">
-        <v>1314.219</v>
+        <v>790.985</v>
       </c>
       <c r="C102">
-        <v>1487</v>
+        <v>825</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B103">
-        <v>1329.801</v>
+        <v>756.944</v>
       </c>
       <c r="C103">
-        <v>1548</v>
+        <v>788</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B104">
-        <v>1353.694</v>
+        <v>732.716</v>
       </c>
       <c r="C104">
-        <v>1618</v>
+        <v>732</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B105">
-        <v>1376.095</v>
+        <v>704.546</v>
       </c>
       <c r="C105">
-        <v>1694</v>
+        <v>674</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B106">
-        <v>1398.617</v>
+        <v>669.766</v>
       </c>
       <c r="C106">
-        <v>1768</v>
+        <v>640</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B107">
-        <v>1421.584</v>
+        <v>649.48</v>
       </c>
       <c r="C107">
-        <v>1812</v>
+        <v>609</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B108">
-        <v>1434.341</v>
+        <v>631.688</v>
       </c>
       <c r="C108">
-        <v>1850</v>
+        <v>581</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B109">
-        <v>1462.321</v>
+        <v>609.175</v>
       </c>
       <c r="C109">
-        <v>1856</v>
+        <v>543</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B110">
-        <v>1502.288</v>
+        <v>590.461</v>
       </c>
       <c r="C110">
-        <v>1888</v>
+        <v>536</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B111">
-        <v>1524.347</v>
+        <v>569.0170000000001</v>
       </c>
       <c r="C111">
-        <v>1944</v>
+        <v>517</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B112">
-        <v>1536.819</v>
+        <v>553.9059999999999</v>
       </c>
       <c r="C112">
-        <v>1971</v>
+        <v>474</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B113">
-        <v>1558.759</v>
+        <v>533.85</v>
       </c>
       <c r="C113">
-        <v>1965</v>
+        <v>463</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B114">
-        <v>1554.042</v>
+        <v>493.472</v>
       </c>
       <c r="C114">
-        <v>1954</v>
+        <v>445</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B115">
-        <v>1569.379</v>
+        <v>469.636</v>
       </c>
       <c r="C115">
-        <v>1953</v>
+        <v>408</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B116">
-        <v>1582.75</v>
+        <v>448.506</v>
       </c>
       <c r="C116">
-        <v>1945</v>
+        <v>374</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B117">
-        <v>1602.65</v>
+        <v>429.713</v>
       </c>
       <c r="C117">
-        <v>1936</v>
+        <v>350</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B118">
-        <v>1584.713</v>
+        <v>397.968</v>
       </c>
       <c r="C118">
-        <v>1900</v>
+        <v>339</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B119">
-        <v>1557.816</v>
+        <v>381.267</v>
       </c>
       <c r="C119">
-        <v>1857</v>
+        <v>314</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B120">
-        <v>1532.091</v>
+        <v>363.79</v>
       </c>
       <c r="C120">
-        <v>1846</v>
+        <v>279</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B121">
-        <v>1504.972</v>
+        <v>345.808</v>
       </c>
       <c r="C121">
-        <v>1758</v>
+        <v>246</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B122">
-        <v>1415.558</v>
+        <v>301.359</v>
       </c>
       <c r="C122">
-        <v>1635</v>
+        <v>206</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B123">
-        <v>1367.098</v>
+        <v>284.643</v>
       </c>
       <c r="C123">
-        <v>1543</v>
+        <v>165</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B124">
-        <v>1301.627</v>
+        <v>271.301</v>
       </c>
       <c r="C124">
-        <v>1431</v>
+        <v>150</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B125">
-        <v>1236.599</v>
+        <v>254.307</v>
       </c>
       <c r="C125">
-        <v>1255</v>
+        <v>123</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B126">
-        <v>1129.476</v>
+        <v>234.511</v>
       </c>
       <c r="C126">
-        <v>1032</v>
+        <v>96</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B127">
-        <v>1058.591</v>
+        <v>214.131</v>
       </c>
       <c r="C127">
-        <v>792</v>
+        <v>69</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B128">
-        <v>993.784</v>
+        <v>198.09</v>
       </c>
       <c r="C128">
-        <v>649</v>
+        <v>50</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B129">
-        <v>937.283</v>
+        <v>181.058</v>
       </c>
       <c r="C129">
-        <v>535</v>
+        <v>39</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B130">
-        <v>844.943</v>
+        <v>159.833</v>
       </c>
       <c r="C130">
-        <v>495</v>
+        <v>38</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B131">
-        <v>828.136</v>
+        <v>160.638</v>
       </c>
       <c r="C131">
-        <v>496</v>
+        <v>35</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B132">
-        <v>803.448</v>
+        <v>158.173</v>
       </c>
       <c r="C132">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B133">
-        <v>784.869</v>
+        <v>154.113</v>
       </c>
       <c r="C133">
-        <v>497</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B134">
-        <v>813.218</v>
+        <v>163.42</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B135">
-        <v>812.7670000000001</v>
+        <v>169.288</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B136">
-        <v>808.965</v>
+        <v>170.347</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B137">
-        <v>806.551</v>
+        <v>166.869</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B138">
-        <v>802.873</v>
+        <v>171.866</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B139">
-        <v>800.97</v>
+        <v>179.219</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B140">
-        <v>747.328</v>
+        <v>186.23</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B141">
-        <v>745.619</v>
+        <v>193.822</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B142">
-        <v>753.667</v>
+        <v>210.769</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B143">
-        <v>754.921</v>
+        <v>225.097</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B144">
-        <v>756.567</v>
+        <v>241.448</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B145">
-        <v>758.197</v>
+        <v>256.327</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B146">
-        <v>766.8390000000001</v>
+        <v>283.902</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B147">
-        <v>763.717</v>
+        <v>304.168</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B148">
-        <v>762.74</v>
+        <v>325.373</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B149">
-        <v>760.05</v>
+        <v>345.138</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B150">
-        <v>763.246</v>
+        <v>374.558</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B151">
-        <v>759.234</v>
+        <v>397.244</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B152">
-        <v>801.323</v>
+        <v>420.209</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B153">
-        <v>797.653</v>
+        <v>442.292</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B154">
-        <v>759.356</v>
+        <v>486.002</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B155">
-        <v>799.001</v>
+        <v>508.528</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B156">
-        <v>790.748</v>
+        <v>532.088</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B157">
-        <v>740.2910000000001</v>
+        <v>557.99</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B158">
-        <v>719.247</v>
+        <v>594.5170000000001</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B159">
-        <v>709.186</v>
+        <v>621.851</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B160">
-        <v>698.943</v>
+        <v>646.076</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B161">
-        <v>691.0119999999999</v>
+        <v>671.899</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B162">
-        <v>667.586</v>
+        <v>692.5839999999999</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B163">
-        <v>684.222</v>
+        <v>703.879</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B164">
-        <v>662.734</v>
+        <v>715.573</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B165">
-        <v>639.027</v>
+        <v>727.829</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B166">
-        <v>570.564</v>
+        <v>742.475</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B167">
-        <v>563.033</v>
+        <v>747.4450000000001</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B168">
-        <v>555.946</v>
+        <v>753.2140000000001</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B169">
-        <v>550.1</v>
+        <v>758.707</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B170">
-        <v>560.678</v>
+        <v>783.022</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B171">
-        <v>599.047</v>
+        <v>807.098</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B172">
-        <v>639.148</v>
+        <v>832.646</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B173">
-        <v>679.217</v>
+        <v>861.077</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B174">
-        <v>763.313</v>
+        <v>881.183</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B175">
-        <v>821.378</v>
+        <v>916.026</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B176">
-        <v>883.564</v>
+        <v>951.373</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B177">
-        <v>950.752</v>
+        <v>984.893</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B178">
-        <v>1032.125</v>
+        <v>1032.365</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B179">
-        <v>1085.591</v>
+        <v>1055.294</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B180">
-        <v>1136.153</v>
+        <v>1074.92</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B181">
-        <v>1189.243</v>
+        <v>1098.592</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B182">
-        <v>1256.529</v>
+        <v>1125.574</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B183">
-        <v>1299.035</v>
+        <v>1142.988</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B184">
-        <v>1341.269</v>
+        <v>1158.963</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B185">
-        <v>1381.938</v>
+        <v>1171.542</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B186">
-        <v>1395.934</v>
+        <v>1173.933</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B187">
-        <v>1399.102</v>
+        <v>1167.589</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B188">
-        <v>1397.987</v>
+        <v>1167.561</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B189">
-        <v>1392.711</v>
+        <v>1165.584</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>26.05.20261</t>
-  </si>
-  <si>
-    <t>26.05.20262</t>
-  </si>
-  <si>
-    <t>26.05.20263</t>
-  </si>
-  <si>
-    <t>26.05.20264</t>
-  </si>
-  <si>
-    <t>26.05.20265</t>
-  </si>
-  <si>
-    <t>26.05.20266</t>
-  </si>
-  <si>
-    <t>26.05.20267</t>
-  </si>
-  <si>
-    <t>26.05.20268</t>
-  </si>
-  <si>
-    <t>26.05.20269</t>
-  </si>
-  <si>
-    <t>26.05.202610</t>
-  </si>
-  <si>
-    <t>26.05.202611</t>
-  </si>
-  <si>
-    <t>26.05.202612</t>
-  </si>
-  <si>
-    <t>26.05.202613</t>
-  </si>
-  <si>
-    <t>26.05.202614</t>
-  </si>
-  <si>
-    <t>26.05.202615</t>
-  </si>
-  <si>
-    <t>26.05.202616</t>
-  </si>
-  <si>
-    <t>26.05.202617</t>
-  </si>
-  <si>
-    <t>26.05.202618</t>
-  </si>
-  <si>
-    <t>26.05.202619</t>
-  </si>
-  <si>
-    <t>26.05.202620</t>
-  </si>
-  <si>
-    <t>26.05.202621</t>
-  </si>
-  <si>
-    <t>26.05.202622</t>
-  </si>
-  <si>
-    <t>26.05.202623</t>
-  </si>
-  <si>
-    <t>26.05.202624</t>
-  </si>
-  <si>
-    <t>26.05.202625</t>
-  </si>
-  <si>
-    <t>26.05.202626</t>
-  </si>
-  <si>
-    <t>26.05.202627</t>
-  </si>
-  <si>
-    <t>26.05.202628</t>
-  </si>
-  <si>
-    <t>26.05.202629</t>
-  </si>
-  <si>
-    <t>26.05.202630</t>
-  </si>
-  <si>
-    <t>26.05.202631</t>
-  </si>
-  <si>
-    <t>26.05.202632</t>
-  </si>
-  <si>
-    <t>26.05.202633</t>
-  </si>
-  <si>
-    <t>26.05.202634</t>
-  </si>
-  <si>
-    <t>26.05.202635</t>
-  </si>
-  <si>
-    <t>26.05.202636</t>
-  </si>
-  <si>
-    <t>26.05.202637</t>
-  </si>
-  <si>
-    <t>26.05.202638</t>
-  </si>
-  <si>
-    <t>26.05.202639</t>
-  </si>
-  <si>
-    <t>26.05.202640</t>
-  </si>
-  <si>
-    <t>26.05.202641</t>
-  </si>
-  <si>
-    <t>26.05.202642</t>
-  </si>
-  <si>
-    <t>26.05.202643</t>
-  </si>
-  <si>
-    <t>26.05.202644</t>
-  </si>
-  <si>
-    <t>26.05.202645</t>
-  </si>
-  <si>
-    <t>26.05.202646</t>
-  </si>
-  <si>
-    <t>26.05.202647</t>
-  </si>
-  <si>
-    <t>26.05.202648</t>
-  </si>
-  <si>
-    <t>26.05.202649</t>
-  </si>
-  <si>
-    <t>26.05.202650</t>
-  </si>
-  <si>
-    <t>26.05.202651</t>
-  </si>
-  <si>
-    <t>26.05.202652</t>
-  </si>
-  <si>
-    <t>26.05.202653</t>
-  </si>
-  <si>
-    <t>26.05.202654</t>
-  </si>
-  <si>
-    <t>26.05.202655</t>
-  </si>
-  <si>
-    <t>26.05.202656</t>
-  </si>
-  <si>
-    <t>26.05.202657</t>
-  </si>
-  <si>
-    <t>26.05.202658</t>
-  </si>
-  <si>
-    <t>26.05.202659</t>
-  </si>
-  <si>
-    <t>26.05.202660</t>
-  </si>
-  <si>
-    <t>26.05.202661</t>
-  </si>
-  <si>
-    <t>26.05.202662</t>
-  </si>
-  <si>
-    <t>26.05.202663</t>
-  </si>
-  <si>
-    <t>26.05.202664</t>
-  </si>
-  <si>
-    <t>26.05.202665</t>
-  </si>
-  <si>
-    <t>26.05.202666</t>
-  </si>
-  <si>
-    <t>26.05.202667</t>
-  </si>
-  <si>
-    <t>26.05.202668</t>
-  </si>
-  <si>
-    <t>26.05.202669</t>
-  </si>
-  <si>
-    <t>26.05.202670</t>
-  </si>
-  <si>
-    <t>26.05.202671</t>
-  </si>
-  <si>
-    <t>26.05.202672</t>
-  </si>
-  <si>
-    <t>26.05.202673</t>
-  </si>
-  <si>
-    <t>26.05.202674</t>
-  </si>
-  <si>
-    <t>26.05.202675</t>
-  </si>
-  <si>
-    <t>26.05.202676</t>
-  </si>
-  <si>
-    <t>26.05.202677</t>
-  </si>
-  <si>
-    <t>26.05.202678</t>
-  </si>
-  <si>
-    <t>26.05.202679</t>
-  </si>
-  <si>
-    <t>26.05.202680</t>
-  </si>
-  <si>
-    <t>26.05.202681</t>
-  </si>
-  <si>
-    <t>26.05.202682</t>
-  </si>
-  <si>
-    <t>26.05.202683</t>
-  </si>
-  <si>
-    <t>26.05.202684</t>
-  </si>
-  <si>
-    <t>26.05.202685</t>
-  </si>
-  <si>
-    <t>26.05.202686</t>
-  </si>
-  <si>
-    <t>26.05.202687</t>
-  </si>
-  <si>
-    <t>26.05.202688</t>
-  </si>
-  <si>
-    <t>26.05.202689</t>
-  </si>
-  <si>
-    <t>26.05.202690</t>
-  </si>
-  <si>
-    <t>26.05.202691</t>
-  </si>
-  <si>
-    <t>26.05.202692</t>
-  </si>
-  <si>
-    <t>26.05.202693</t>
-  </si>
-  <si>
-    <t>26.05.202694</t>
-  </si>
-  <si>
-    <t>26.05.202695</t>
-  </si>
-  <si>
-    <t>26.05.202696</t>
-  </si>
-  <si>
     <t>27.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>27.05.202696</t>
+  </si>
+  <si>
+    <t>28.05.20261</t>
+  </si>
+  <si>
+    <t>28.05.20262</t>
+  </si>
+  <si>
+    <t>28.05.20263</t>
+  </si>
+  <si>
+    <t>28.05.20264</t>
+  </si>
+  <si>
+    <t>28.05.20265</t>
+  </si>
+  <si>
+    <t>28.05.20266</t>
+  </si>
+  <si>
+    <t>28.05.20267</t>
+  </si>
+  <si>
+    <t>28.05.20268</t>
+  </si>
+  <si>
+    <t>28.05.20269</t>
+  </si>
+  <si>
+    <t>28.05.202610</t>
+  </si>
+  <si>
+    <t>28.05.202611</t>
+  </si>
+  <si>
+    <t>28.05.202612</t>
+  </si>
+  <si>
+    <t>28.05.202613</t>
+  </si>
+  <si>
+    <t>28.05.202614</t>
+  </si>
+  <si>
+    <t>28.05.202615</t>
+  </si>
+  <si>
+    <t>28.05.202616</t>
+  </si>
+  <si>
+    <t>28.05.202617</t>
+  </si>
+  <si>
+    <t>28.05.202618</t>
+  </si>
+  <si>
+    <t>28.05.202619</t>
+  </si>
+  <si>
+    <t>28.05.202620</t>
+  </si>
+  <si>
+    <t>28.05.202621</t>
+  </si>
+  <si>
+    <t>28.05.202622</t>
+  </si>
+  <si>
+    <t>28.05.202623</t>
+  </si>
+  <si>
+    <t>28.05.202624</t>
+  </si>
+  <si>
+    <t>28.05.202625</t>
+  </si>
+  <si>
+    <t>28.05.202626</t>
+  </si>
+  <si>
+    <t>28.05.202627</t>
+  </si>
+  <si>
+    <t>28.05.202628</t>
+  </si>
+  <si>
+    <t>28.05.202629</t>
+  </si>
+  <si>
+    <t>28.05.202630</t>
+  </si>
+  <si>
+    <t>28.05.202631</t>
+  </si>
+  <si>
+    <t>28.05.202632</t>
+  </si>
+  <si>
+    <t>28.05.202633</t>
+  </si>
+  <si>
+    <t>28.05.202634</t>
+  </si>
+  <si>
+    <t>28.05.202635</t>
+  </si>
+  <si>
+    <t>28.05.202636</t>
+  </si>
+  <si>
+    <t>28.05.202637</t>
+  </si>
+  <si>
+    <t>28.05.202638</t>
+  </si>
+  <si>
+    <t>28.05.202639</t>
+  </si>
+  <si>
+    <t>28.05.202640</t>
+  </si>
+  <si>
+    <t>28.05.202641</t>
+  </si>
+  <si>
+    <t>28.05.202642</t>
+  </si>
+  <si>
+    <t>28.05.202643</t>
+  </si>
+  <si>
+    <t>28.05.202644</t>
+  </si>
+  <si>
+    <t>28.05.202645</t>
+  </si>
+  <si>
+    <t>28.05.202646</t>
+  </si>
+  <si>
+    <t>28.05.202647</t>
+  </si>
+  <si>
+    <t>28.05.202648</t>
+  </si>
+  <si>
+    <t>28.05.202649</t>
+  </si>
+  <si>
+    <t>28.05.202650</t>
+  </si>
+  <si>
+    <t>28.05.202651</t>
+  </si>
+  <si>
+    <t>28.05.202652</t>
+  </si>
+  <si>
+    <t>28.05.202653</t>
+  </si>
+  <si>
+    <t>28.05.202654</t>
+  </si>
+  <si>
+    <t>28.05.202655</t>
+  </si>
+  <si>
+    <t>28.05.202656</t>
+  </si>
+  <si>
+    <t>28.05.202657</t>
+  </si>
+  <si>
+    <t>28.05.202658</t>
+  </si>
+  <si>
+    <t>28.05.202659</t>
+  </si>
+  <si>
+    <t>28.05.202660</t>
+  </si>
+  <si>
+    <t>28.05.202661</t>
+  </si>
+  <si>
+    <t>28.05.202662</t>
+  </si>
+  <si>
+    <t>28.05.202663</t>
+  </si>
+  <si>
+    <t>28.05.202664</t>
+  </si>
+  <si>
+    <t>28.05.202665</t>
+  </si>
+  <si>
+    <t>28.05.202666</t>
+  </si>
+  <si>
+    <t>28.05.202667</t>
+  </si>
+  <si>
+    <t>28.05.202668</t>
+  </si>
+  <si>
+    <t>28.05.202669</t>
+  </si>
+  <si>
+    <t>28.05.202670</t>
+  </si>
+  <si>
+    <t>28.05.202671</t>
+  </si>
+  <si>
+    <t>28.05.202672</t>
+  </si>
+  <si>
+    <t>28.05.202673</t>
+  </si>
+  <si>
+    <t>28.05.202674</t>
+  </si>
+  <si>
+    <t>28.05.202675</t>
+  </si>
+  <si>
+    <t>28.05.202676</t>
+  </si>
+  <si>
+    <t>28.05.202677</t>
+  </si>
+  <si>
+    <t>28.05.202678</t>
+  </si>
+  <si>
+    <t>28.05.202679</t>
+  </si>
+  <si>
+    <t>28.05.202680</t>
+  </si>
+  <si>
+    <t>28.05.202681</t>
+  </si>
+  <si>
+    <t>28.05.202682</t>
+  </si>
+  <si>
+    <t>28.05.202683</t>
+  </si>
+  <si>
+    <t>28.05.202684</t>
+  </si>
+  <si>
+    <t>28.05.202685</t>
+  </si>
+  <si>
+    <t>28.05.202686</t>
+  </si>
+  <si>
+    <t>28.05.202687</t>
+  </si>
+  <si>
+    <t>28.05.202688</t>
+  </si>
+  <si>
+    <t>28.05.202689</t>
+  </si>
+  <si>
+    <t>28.05.202690</t>
+  </si>
+  <si>
+    <t>28.05.202691</t>
+  </si>
+  <si>
+    <t>28.05.202692</t>
+  </si>
+  <si>
+    <t>28.05.202693</t>
+  </si>
+  <si>
+    <t>28.05.202694</t>
+  </si>
+  <si>
+    <t>28.05.202695</t>
+  </si>
+  <si>
+    <t>28.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
-        <v>1120.118</v>
+        <v>968.177</v>
       </c>
       <c r="C2">
-        <v>1250</v>
+        <v>1077</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
-        <v>1160.955</v>
+        <v>925.954</v>
       </c>
       <c r="C3">
-        <v>1321</v>
+        <v>1033</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
-        <v>1196.695</v>
+        <v>886.772</v>
       </c>
       <c r="C4">
-        <v>1383</v>
+        <v>960</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
-        <v>1233.087</v>
+        <v>846.275</v>
       </c>
       <c r="C5">
-        <v>1430</v>
+        <v>885</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
-        <v>1314.219</v>
+        <v>790.985</v>
       </c>
       <c r="C6">
-        <v>1487</v>
+        <v>825</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
-        <v>1329.801</v>
+        <v>756.944</v>
       </c>
       <c r="C7">
-        <v>1548</v>
+        <v>788</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
-        <v>1353.694</v>
+        <v>732.716</v>
       </c>
       <c r="C8">
-        <v>1618</v>
+        <v>732</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
-        <v>1376.095</v>
+        <v>704.546</v>
       </c>
       <c r="C9">
-        <v>1694</v>
+        <v>674</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
-        <v>1398.617</v>
+        <v>669.766</v>
       </c>
       <c r="C10">
-        <v>1768</v>
+        <v>640</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
-        <v>1421.584</v>
+        <v>649.48</v>
       </c>
       <c r="C11">
-        <v>1812</v>
+        <v>609</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
-        <v>1434.341</v>
+        <v>631.688</v>
       </c>
       <c r="C12">
-        <v>1850</v>
+        <v>581</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
-        <v>1462.321</v>
+        <v>609.175</v>
       </c>
       <c r="C13">
-        <v>1856</v>
+        <v>543</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
-        <v>1502.288</v>
+        <v>590.461</v>
       </c>
       <c r="C14">
-        <v>1888</v>
+        <v>536</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
-        <v>1524.347</v>
+        <v>569.0170000000001</v>
       </c>
       <c r="C15">
-        <v>1944</v>
+        <v>517</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>1536.819</v>
+        <v>553.9059999999999</v>
       </c>
       <c r="C16">
-        <v>1971</v>
+        <v>474</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>1558.759</v>
+        <v>533.85</v>
       </c>
       <c r="C17">
-        <v>1965</v>
+        <v>463</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
-        <v>1554.042</v>
+        <v>493.472</v>
       </c>
       <c r="C18">
-        <v>1954</v>
+        <v>445</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>1569.379</v>
+        <v>469.636</v>
       </c>
       <c r="C19">
-        <v>1953</v>
+        <v>408</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>1582.75</v>
+        <v>448.506</v>
       </c>
       <c r="C20">
-        <v>1945</v>
+        <v>374</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>1602.65</v>
+        <v>429.713</v>
       </c>
       <c r="C21">
-        <v>1936</v>
+        <v>350</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>1584.713</v>
+        <v>397.968</v>
       </c>
       <c r="C22">
-        <v>1900</v>
+        <v>339</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>1557.816</v>
+        <v>381.267</v>
       </c>
       <c r="C23">
-        <v>1857</v>
+        <v>314</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>1532.091</v>
+        <v>363.79</v>
       </c>
       <c r="C24">
-        <v>1846</v>
+        <v>279</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>1504.972</v>
+        <v>345.808</v>
       </c>
       <c r="C25">
-        <v>1758</v>
+        <v>246</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>1415.558</v>
+        <v>301.359</v>
       </c>
       <c r="C26">
-        <v>1635</v>
+        <v>206</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>1367.098</v>
+        <v>284.643</v>
       </c>
       <c r="C27">
-        <v>1543</v>
+        <v>165</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>1301.627</v>
+        <v>271.301</v>
       </c>
       <c r="C28">
-        <v>1431</v>
+        <v>150</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>1236.599</v>
+        <v>254.307</v>
       </c>
       <c r="C29">
-        <v>1255</v>
+        <v>123</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>1129.476</v>
+        <v>234.511</v>
       </c>
       <c r="C30">
-        <v>1032</v>
+        <v>96</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>1058.591</v>
+        <v>214.131</v>
       </c>
       <c r="C31">
-        <v>792</v>
+        <v>69</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>993.784</v>
+        <v>198.09</v>
       </c>
       <c r="C32">
-        <v>649</v>
+        <v>50</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>937.283</v>
+        <v>181.058</v>
       </c>
       <c r="C33">
-        <v>535</v>
+        <v>39</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>844.943</v>
+        <v>159.833</v>
       </c>
       <c r="C34">
-        <v>495</v>
+        <v>38</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>828.136</v>
+        <v>160.638</v>
       </c>
       <c r="C35">
-        <v>496</v>
+        <v>35</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>803.448</v>
+        <v>158.173</v>
       </c>
       <c r="C36">
-        <v>516</v>
+        <v>27</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>784.869</v>
+        <v>154.113</v>
       </c>
       <c r="C37">
-        <v>497</v>
+        <v>24</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>813.218</v>
+        <v>163.42</v>
       </c>
       <c r="C38">
-        <v>504</v>
+        <v>26</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>812.7670000000001</v>
+        <v>169.288</v>
       </c>
       <c r="C39">
-        <v>522</v>
+        <v>29</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>808.965</v>
+        <v>170.347</v>
       </c>
       <c r="C40">
-        <v>526</v>
+        <v>25</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>806.551</v>
+        <v>166.869</v>
       </c>
       <c r="C41">
-        <v>555</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>802.873</v>
+        <v>171.866</v>
       </c>
       <c r="C42">
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>800.97</v>
+        <v>179.219</v>
       </c>
       <c r="C43">
-        <v>515</v>
+        <v>34</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>747.328</v>
+        <v>186.23</v>
       </c>
       <c r="C44">
-        <v>474</v>
+        <v>39</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>745.619</v>
+        <v>193.822</v>
       </c>
       <c r="C45">
-        <v>494</v>
+        <v>50</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>753.667</v>
+        <v>210.769</v>
       </c>
       <c r="C46">
-        <v>536</v>
+        <v>71</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>754.921</v>
+        <v>225.097</v>
       </c>
       <c r="C47">
-        <v>544</v>
+        <v>97</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>756.567</v>
+        <v>241.448</v>
       </c>
       <c r="C48">
-        <v>574</v>
+        <v>128</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>758.197</v>
+        <v>256.327</v>
       </c>
       <c r="C49">
-        <v>578</v>
+        <v>160</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>766.8390000000001</v>
+        <v>283.902</v>
       </c>
       <c r="C50">
-        <v>644</v>
+        <v>188</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>763.717</v>
+        <v>304.168</v>
       </c>
       <c r="C51">
-        <v>650</v>
+        <v>217</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>762.74</v>
+        <v>325.373</v>
       </c>
       <c r="C52">
-        <v>658</v>
+        <v>241</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>760.05</v>
+        <v>345.138</v>
       </c>
       <c r="C53">
-        <v>688</v>
+        <v>278</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>763.246</v>
+        <v>374.558</v>
       </c>
       <c r="C54">
-        <v>685</v>
+        <v>316</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>759.234</v>
+        <v>397.244</v>
       </c>
       <c r="C55">
-        <v>664</v>
+        <v>343</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>801.323</v>
+        <v>420.209</v>
       </c>
       <c r="C56">
-        <v>678</v>
+        <v>364</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>797.653</v>
+        <v>442.292</v>
       </c>
       <c r="C57">
-        <v>686</v>
+        <v>378</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>759.356</v>
+        <v>486.002</v>
       </c>
       <c r="C58">
-        <v>650</v>
+        <v>422</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>799.001</v>
+        <v>508.528</v>
       </c>
       <c r="C59">
-        <v>658</v>
+        <v>466</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>790.748</v>
+        <v>532.088</v>
       </c>
       <c r="C60">
-        <v>685</v>
+        <v>505</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>740.2910000000001</v>
+        <v>557.99</v>
       </c>
       <c r="C61">
-        <v>698</v>
+        <v>538</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>719.247</v>
+        <v>594.5170000000001</v>
       </c>
       <c r="C62">
-        <v>693</v>
+        <v>598</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>709.186</v>
+        <v>621.851</v>
       </c>
       <c r="C63">
-        <v>673</v>
+        <v>652</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>698.943</v>
+        <v>646.076</v>
       </c>
       <c r="C64">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>691.0119999999999</v>
+        <v>671.899</v>
       </c>
       <c r="C65">
-        <v>683</v>
+        <v>758</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>667.586</v>
+        <v>692.5839999999999</v>
       </c>
       <c r="C66">
-        <v>699</v>
+        <v>801</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>684.222</v>
+        <v>703.879</v>
       </c>
       <c r="C67">
-        <v>752</v>
+        <v>813</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>662.734</v>
+        <v>715.573</v>
       </c>
       <c r="C68">
-        <v>745</v>
+        <v>821</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>639.027</v>
+        <v>727.829</v>
       </c>
       <c r="C69">
-        <v>738</v>
+        <v>851</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>570.564</v>
+        <v>742.475</v>
       </c>
       <c r="C70">
-        <v>737</v>
+        <v>856</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>563.033</v>
+        <v>747.4450000000001</v>
       </c>
       <c r="C71">
-        <v>775</v>
+        <v>857</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>555.946</v>
+        <v>753.2140000000001</v>
       </c>
       <c r="C72">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>550.1</v>
+        <v>758.707</v>
       </c>
       <c r="C73">
-        <v>931</v>
+        <v>820</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>560.678</v>
+        <v>783.022</v>
       </c>
       <c r="C74">
-        <v>977</v>
+        <v>796</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>599.047</v>
+        <v>807.098</v>
       </c>
       <c r="C75">
-        <v>992</v>
+        <v>805</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>639.148</v>
+        <v>832.646</v>
       </c>
       <c r="C76">
-        <v>1000</v>
+        <v>840</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>679.217</v>
+        <v>861.077</v>
       </c>
       <c r="C77">
-        <v>1019</v>
+        <v>876</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>763.313</v>
+        <v>881.183</v>
       </c>
       <c r="C78">
-        <v>1059</v>
+        <v>905</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>821.378</v>
+        <v>916.026</v>
       </c>
       <c r="C79">
-        <v>1151</v>
+        <v>919</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>883.564</v>
+        <v>951.373</v>
       </c>
       <c r="C80">
-        <v>1249</v>
+        <v>928</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>950.752</v>
+        <v>984.893</v>
       </c>
       <c r="C81">
-        <v>1356</v>
+        <v>990</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>1032.125</v>
+        <v>1032.365</v>
       </c>
       <c r="C82">
-        <v>1417</v>
+        <v>1037</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>1085.591</v>
+        <v>1055.294</v>
       </c>
       <c r="C83">
-        <v>1444</v>
+        <v>1068</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>1136.153</v>
+        <v>1074.92</v>
       </c>
       <c r="C84">
-        <v>1466</v>
+        <v>1107</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>1189.243</v>
+        <v>1098.592</v>
       </c>
       <c r="C85">
-        <v>1459</v>
+        <v>1145</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>1256.529</v>
+        <v>1125.574</v>
       </c>
       <c r="C86">
-        <v>1471</v>
+        <v>1163</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
-        <v>1299.035</v>
+        <v>1142.988</v>
       </c>
       <c r="C87">
-        <v>1478</v>
+        <v>1133</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>1341.269</v>
+        <v>1158.963</v>
       </c>
       <c r="C88">
-        <v>1495</v>
+        <v>1143</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>1381.938</v>
+        <v>1171.542</v>
       </c>
       <c r="C89">
-        <v>1487</v>
+        <v>1241</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
-        <v>1395.934</v>
+        <v>1173.933</v>
       </c>
       <c r="C90">
-        <v>1421</v>
+        <v>1323</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
-        <v>1399.102</v>
+        <v>1167.589</v>
       </c>
       <c r="C91">
-        <v>1355</v>
+        <v>1446</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
-        <v>1397.987</v>
+        <v>1167.561</v>
       </c>
       <c r="C92">
-        <v>1281</v>
+        <v>1443</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
-        <v>1392.711</v>
+        <v>1165.584</v>
       </c>
       <c r="C93">
-        <v>1208</v>
+        <v>1353</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>1278.774</v>
+        <v>1102.103</v>
       </c>
       <c r="C94">
-        <v>1207</v>
+        <v>1275</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
-        <v>1248.323</v>
+        <v>1107.912</v>
       </c>
       <c r="C95">
-        <v>1169</v>
+        <v>1358</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
-        <v>1216.169</v>
+        <v>1104.848</v>
       </c>
       <c r="C96">
-        <v>1129</v>
+        <v>1396</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
-        <v>1182.172</v>
+        <v>1091.355</v>
       </c>
       <c r="C97">
-        <v>1113</v>
+        <v>1385</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>968.177</v>
+        <v>1145.311</v>
       </c>
       <c r="C98">
-        <v>1077</v>
+        <v>1288</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
-        <v>925.954</v>
+        <v>1123.122</v>
       </c>
       <c r="C99">
-        <v>1033</v>
+        <v>1229</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
-        <v>886.772</v>
+        <v>1116.171</v>
       </c>
       <c r="C100">
-        <v>960</v>
+        <v>1087</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
-        <v>846.275</v>
+        <v>1108.729</v>
       </c>
       <c r="C101">
-        <v>885</v>
+        <v>966</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
-        <v>790.985</v>
+        <v>1124.744</v>
       </c>
       <c r="C102">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
-        <v>756.944</v>
+        <v>1136.86</v>
       </c>
       <c r="C103">
-        <v>788</v>
+        <v>626</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
-        <v>732.716</v>
+        <v>1153.913</v>
       </c>
       <c r="C104">
-        <v>732</v>
+        <v>529</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
-        <v>704.546</v>
+        <v>1155.775</v>
       </c>
       <c r="C105">
-        <v>674</v>
+        <v>568</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
-        <v>669.766</v>
+        <v>1132.338</v>
       </c>
       <c r="C106">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
-        <v>649.48</v>
+        <v>1122.575</v>
       </c>
       <c r="C107">
-        <v>609</v>
+        <v>534</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
-        <v>631.688</v>
+        <v>1127.766</v>
       </c>
       <c r="C108">
-        <v>581</v>
+        <v>393</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
-        <v>609.175</v>
+        <v>1133.853</v>
       </c>
       <c r="C109">
-        <v>543</v>
+        <v>372</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
-        <v>590.461</v>
+        <v>1117.217</v>
       </c>
       <c r="C110">
-        <v>536</v>
+        <v>382</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
-        <v>569.0170000000001</v>
+        <v>1111.369</v>
       </c>
       <c r="C111">
-        <v>517</v>
+        <v>443</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
-        <v>553.9059999999999</v>
+        <v>1099.843</v>
       </c>
       <c r="C112">
-        <v>474</v>
+        <v>521</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
-        <v>533.85</v>
+        <v>1085.726</v>
       </c>
       <c r="C113">
-        <v>463</v>
+        <v>553</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
-        <v>493.472</v>
+        <v>1111.567</v>
       </c>
       <c r="C114">
-        <v>445</v>
+        <v>638</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
-        <v>469.636</v>
+        <v>1093.644</v>
       </c>
       <c r="C115">
-        <v>408</v>
+        <v>736</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
-        <v>448.506</v>
+        <v>1075.779</v>
       </c>
       <c r="C116">
-        <v>374</v>
+        <v>826</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
-        <v>429.713</v>
+        <v>1058.034</v>
       </c>
       <c r="C117">
-        <v>350</v>
+        <v>871</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>397.968</v>
+        <v>1097.86</v>
       </c>
       <c r="C118">
-        <v>339</v>
+        <v>950</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>381.267</v>
+        <v>1084.866</v>
       </c>
       <c r="C119">
-        <v>314</v>
+        <v>967</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>363.79</v>
+        <v>1067.601</v>
       </c>
       <c r="C120">
-        <v>279</v>
+        <v>831</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>345.808</v>
+        <v>1060.729</v>
       </c>
       <c r="C121">
-        <v>246</v>
+        <v>833</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>301.359</v>
+        <v>1042.536</v>
       </c>
       <c r="C122">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>284.643</v>
+        <v>1001.511</v>
       </c>
       <c r="C123">
-        <v>165</v>
+        <v>776</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>271.301</v>
+        <v>979.593</v>
       </c>
       <c r="C124">
-        <v>150</v>
+        <v>802</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>254.307</v>
+        <v>952.644</v>
       </c>
       <c r="C125">
-        <v>123</v>
+        <v>746</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>234.511</v>
+        <v>918.862</v>
       </c>
       <c r="C126">
-        <v>96</v>
+        <v>692</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>214.131</v>
+        <v>915.29</v>
       </c>
       <c r="C127">
-        <v>69</v>
+        <v>693</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>198.09</v>
+        <v>918.626</v>
       </c>
       <c r="C128">
-        <v>50</v>
+        <v>742</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>181.058</v>
+        <v>922.864</v>
       </c>
       <c r="C129">
-        <v>39</v>
+        <v>765</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>159.833</v>
+        <v>870.261</v>
       </c>
       <c r="C130">
-        <v>38</v>
+        <v>669</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>160.638</v>
+        <v>864.173</v>
       </c>
       <c r="C131">
-        <v>35</v>
+        <v>605</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>158.173</v>
+        <v>890.585</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
-        <v>154.113</v>
+        <v>883.152</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
-        <v>163.42</v>
+        <v>1044.111</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
-        <v>169.288</v>
+        <v>1051.657</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
-        <v>170.347</v>
+        <v>1054.17</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
-        <v>166.869</v>
+        <v>1055.901</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
-        <v>171.866</v>
+        <v>976.917</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
-        <v>179.219</v>
+        <v>973.501</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
-        <v>186.23</v>
+        <v>969.021</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
-        <v>193.822</v>
+        <v>962.736</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
-        <v>210.769</v>
+        <v>974.122</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
-        <v>225.097</v>
+        <v>954.162</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
-        <v>241.448</v>
+        <v>876.26</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
-        <v>256.327</v>
+        <v>857.999</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
-        <v>283.902</v>
+        <v>868.049</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
-        <v>304.168</v>
+        <v>860.923</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
-        <v>325.373</v>
+        <v>856.353</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
-        <v>345.138</v>
+        <v>852.186</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
-        <v>374.558</v>
+        <v>878.2190000000001</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
-        <v>397.244</v>
+        <v>882.754</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
-        <v>420.209</v>
+        <v>888.447</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
-        <v>442.292</v>
+        <v>894.586</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
-        <v>486.002</v>
+        <v>912.5700000000001</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
-        <v>508.528</v>
+        <v>913.051</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
-        <v>532.088</v>
+        <v>915.259</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
-        <v>557.99</v>
+        <v>915.321</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
-        <v>594.5170000000001</v>
+        <v>956.386</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
-        <v>621.851</v>
+        <v>953.712</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
-        <v>646.076</v>
+        <v>1003.502</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
-        <v>671.899</v>
+        <v>999.491</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
-        <v>692.5839999999999</v>
+        <v>927.549</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
-        <v>703.879</v>
+        <v>934.987</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
-        <v>715.573</v>
+        <v>944.985</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
-        <v>727.829</v>
+        <v>953.644</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
-        <v>742.475</v>
+        <v>915.097</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
-        <v>747.4450000000001</v>
+        <v>927.851</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
-        <v>753.2140000000001</v>
+        <v>940.785</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
-        <v>758.707</v>
+        <v>953.522</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
-        <v>783.022</v>
+        <v>964.107</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
-        <v>807.098</v>
+        <v>968.4299999999999</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
-        <v>832.646</v>
+        <v>971.021</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
-        <v>861.077</v>
+        <v>972.691</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
-        <v>881.183</v>
+        <v>1013.818</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
-        <v>916.026</v>
+        <v>1006.628</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
-        <v>951.373</v>
+        <v>998.481</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
-        <v>984.893</v>
+        <v>987.854</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
-        <v>1032.365</v>
+        <v>970.533</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
-        <v>1055.294</v>
+        <v>952.837</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
-        <v>1074.92</v>
+        <v>931.707</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
-        <v>1098.592</v>
+        <v>910.35</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
-        <v>1125.574</v>
+        <v>848.825</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
-        <v>1142.988</v>
+        <v>848.266</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
-        <v>1158.963</v>
+        <v>845.915</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
-        <v>1171.542</v>
+        <v>845.731</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
-        <v>1173.933</v>
+        <v>842.111</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
-        <v>1167.589</v>
+        <v>843.746</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
-        <v>1167.561</v>
+        <v>845.639</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
-        <v>1165.584</v>
+        <v>852.399</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>27.05.20261</t>
-  </si>
-  <si>
-    <t>27.05.20262</t>
-  </si>
-  <si>
-    <t>27.05.20263</t>
-  </si>
-  <si>
-    <t>27.05.20264</t>
-  </si>
-  <si>
-    <t>27.05.20265</t>
-  </si>
-  <si>
-    <t>27.05.20266</t>
-  </si>
-  <si>
-    <t>27.05.20267</t>
-  </si>
-  <si>
-    <t>27.05.20268</t>
-  </si>
-  <si>
-    <t>27.05.20269</t>
-  </si>
-  <si>
-    <t>27.05.202610</t>
-  </si>
-  <si>
-    <t>27.05.202611</t>
-  </si>
-  <si>
-    <t>27.05.202612</t>
-  </si>
-  <si>
-    <t>27.05.202613</t>
-  </si>
-  <si>
-    <t>27.05.202614</t>
-  </si>
-  <si>
-    <t>27.05.202615</t>
-  </si>
-  <si>
-    <t>27.05.202616</t>
-  </si>
-  <si>
-    <t>27.05.202617</t>
-  </si>
-  <si>
-    <t>27.05.202618</t>
-  </si>
-  <si>
-    <t>27.05.202619</t>
-  </si>
-  <si>
-    <t>27.05.202620</t>
-  </si>
-  <si>
-    <t>27.05.202621</t>
-  </si>
-  <si>
-    <t>27.05.202622</t>
-  </si>
-  <si>
-    <t>27.05.202623</t>
-  </si>
-  <si>
-    <t>27.05.202624</t>
-  </si>
-  <si>
-    <t>27.05.202625</t>
-  </si>
-  <si>
-    <t>27.05.202626</t>
-  </si>
-  <si>
-    <t>27.05.202627</t>
-  </si>
-  <si>
-    <t>27.05.202628</t>
-  </si>
-  <si>
-    <t>27.05.202629</t>
-  </si>
-  <si>
-    <t>27.05.202630</t>
-  </si>
-  <si>
-    <t>27.05.202631</t>
-  </si>
-  <si>
-    <t>27.05.202632</t>
-  </si>
-  <si>
-    <t>27.05.202633</t>
-  </si>
-  <si>
-    <t>27.05.202634</t>
-  </si>
-  <si>
-    <t>27.05.202635</t>
-  </si>
-  <si>
-    <t>27.05.202636</t>
-  </si>
-  <si>
-    <t>27.05.202637</t>
-  </si>
-  <si>
-    <t>27.05.202638</t>
-  </si>
-  <si>
-    <t>27.05.202639</t>
-  </si>
-  <si>
-    <t>27.05.202640</t>
-  </si>
-  <si>
-    <t>27.05.202641</t>
-  </si>
-  <si>
-    <t>27.05.202642</t>
-  </si>
-  <si>
-    <t>27.05.202643</t>
-  </si>
-  <si>
-    <t>27.05.202644</t>
-  </si>
-  <si>
-    <t>27.05.202645</t>
-  </si>
-  <si>
-    <t>27.05.202646</t>
-  </si>
-  <si>
-    <t>27.05.202647</t>
-  </si>
-  <si>
-    <t>27.05.202648</t>
-  </si>
-  <si>
-    <t>27.05.202649</t>
-  </si>
-  <si>
-    <t>27.05.202650</t>
-  </si>
-  <si>
-    <t>27.05.202651</t>
-  </si>
-  <si>
-    <t>27.05.202652</t>
-  </si>
-  <si>
-    <t>27.05.202653</t>
-  </si>
-  <si>
-    <t>27.05.202654</t>
-  </si>
-  <si>
-    <t>27.05.202655</t>
-  </si>
-  <si>
-    <t>27.05.202656</t>
-  </si>
-  <si>
-    <t>27.05.202657</t>
-  </si>
-  <si>
-    <t>27.05.202658</t>
-  </si>
-  <si>
-    <t>27.05.202659</t>
-  </si>
-  <si>
-    <t>27.05.202660</t>
-  </si>
-  <si>
-    <t>27.05.202661</t>
-  </si>
-  <si>
-    <t>27.05.202662</t>
-  </si>
-  <si>
-    <t>27.05.202663</t>
-  </si>
-  <si>
-    <t>27.05.202664</t>
-  </si>
-  <si>
-    <t>27.05.202665</t>
-  </si>
-  <si>
-    <t>27.05.202666</t>
-  </si>
-  <si>
-    <t>27.05.202667</t>
-  </si>
-  <si>
-    <t>27.05.202668</t>
-  </si>
-  <si>
-    <t>27.05.202669</t>
-  </si>
-  <si>
-    <t>27.05.202670</t>
-  </si>
-  <si>
-    <t>27.05.202671</t>
-  </si>
-  <si>
-    <t>27.05.202672</t>
-  </si>
-  <si>
-    <t>27.05.202673</t>
-  </si>
-  <si>
-    <t>27.05.202674</t>
-  </si>
-  <si>
-    <t>27.05.202675</t>
-  </si>
-  <si>
-    <t>27.05.202676</t>
-  </si>
-  <si>
-    <t>27.05.202677</t>
-  </si>
-  <si>
-    <t>27.05.202678</t>
-  </si>
-  <si>
-    <t>27.05.202679</t>
-  </si>
-  <si>
-    <t>27.05.202680</t>
-  </si>
-  <si>
-    <t>27.05.202681</t>
-  </si>
-  <si>
-    <t>27.05.202682</t>
-  </si>
-  <si>
-    <t>27.05.202683</t>
-  </si>
-  <si>
-    <t>27.05.202684</t>
-  </si>
-  <si>
-    <t>27.05.202685</t>
-  </si>
-  <si>
-    <t>27.05.202686</t>
-  </si>
-  <si>
-    <t>27.05.202687</t>
-  </si>
-  <si>
-    <t>27.05.202688</t>
-  </si>
-  <si>
-    <t>27.05.202689</t>
-  </si>
-  <si>
-    <t>27.05.202690</t>
-  </si>
-  <si>
-    <t>27.05.202691</t>
-  </si>
-  <si>
-    <t>27.05.202692</t>
-  </si>
-  <si>
-    <t>27.05.202693</t>
-  </si>
-  <si>
-    <t>27.05.202694</t>
-  </si>
-  <si>
-    <t>27.05.202695</t>
-  </si>
-  <si>
-    <t>27.05.202696</t>
-  </si>
-  <si>
     <t>28.05.20261</t>
   </si>
   <si>
@@ -605,6 +317,294 @@
   </si>
   <si>
     <t>28.05.202696</t>
+  </si>
+  <si>
+    <t>29.05.20261</t>
+  </si>
+  <si>
+    <t>29.05.20262</t>
+  </si>
+  <si>
+    <t>29.05.20263</t>
+  </si>
+  <si>
+    <t>29.05.20264</t>
+  </si>
+  <si>
+    <t>29.05.20265</t>
+  </si>
+  <si>
+    <t>29.05.20266</t>
+  </si>
+  <si>
+    <t>29.05.20267</t>
+  </si>
+  <si>
+    <t>29.05.20268</t>
+  </si>
+  <si>
+    <t>29.05.20269</t>
+  </si>
+  <si>
+    <t>29.05.202610</t>
+  </si>
+  <si>
+    <t>29.05.202611</t>
+  </si>
+  <si>
+    <t>29.05.202612</t>
+  </si>
+  <si>
+    <t>29.05.202613</t>
+  </si>
+  <si>
+    <t>29.05.202614</t>
+  </si>
+  <si>
+    <t>29.05.202615</t>
+  </si>
+  <si>
+    <t>29.05.202616</t>
+  </si>
+  <si>
+    <t>29.05.202617</t>
+  </si>
+  <si>
+    <t>29.05.202618</t>
+  </si>
+  <si>
+    <t>29.05.202619</t>
+  </si>
+  <si>
+    <t>29.05.202620</t>
+  </si>
+  <si>
+    <t>29.05.202621</t>
+  </si>
+  <si>
+    <t>29.05.202622</t>
+  </si>
+  <si>
+    <t>29.05.202623</t>
+  </si>
+  <si>
+    <t>29.05.202624</t>
+  </si>
+  <si>
+    <t>29.05.202625</t>
+  </si>
+  <si>
+    <t>29.05.202626</t>
+  </si>
+  <si>
+    <t>29.05.202627</t>
+  </si>
+  <si>
+    <t>29.05.202628</t>
+  </si>
+  <si>
+    <t>29.05.202629</t>
+  </si>
+  <si>
+    <t>29.05.202630</t>
+  </si>
+  <si>
+    <t>29.05.202631</t>
+  </si>
+  <si>
+    <t>29.05.202632</t>
+  </si>
+  <si>
+    <t>29.05.202633</t>
+  </si>
+  <si>
+    <t>29.05.202634</t>
+  </si>
+  <si>
+    <t>29.05.202635</t>
+  </si>
+  <si>
+    <t>29.05.202636</t>
+  </si>
+  <si>
+    <t>29.05.202637</t>
+  </si>
+  <si>
+    <t>29.05.202638</t>
+  </si>
+  <si>
+    <t>29.05.202639</t>
+  </si>
+  <si>
+    <t>29.05.202640</t>
+  </si>
+  <si>
+    <t>29.05.202641</t>
+  </si>
+  <si>
+    <t>29.05.202642</t>
+  </si>
+  <si>
+    <t>29.05.202643</t>
+  </si>
+  <si>
+    <t>29.05.202644</t>
+  </si>
+  <si>
+    <t>29.05.202645</t>
+  </si>
+  <si>
+    <t>29.05.202646</t>
+  </si>
+  <si>
+    <t>29.05.202647</t>
+  </si>
+  <si>
+    <t>29.05.202648</t>
+  </si>
+  <si>
+    <t>29.05.202649</t>
+  </si>
+  <si>
+    <t>29.05.202650</t>
+  </si>
+  <si>
+    <t>29.05.202651</t>
+  </si>
+  <si>
+    <t>29.05.202652</t>
+  </si>
+  <si>
+    <t>29.05.202653</t>
+  </si>
+  <si>
+    <t>29.05.202654</t>
+  </si>
+  <si>
+    <t>29.05.202655</t>
+  </si>
+  <si>
+    <t>29.05.202656</t>
+  </si>
+  <si>
+    <t>29.05.202657</t>
+  </si>
+  <si>
+    <t>29.05.202658</t>
+  </si>
+  <si>
+    <t>29.05.202659</t>
+  </si>
+  <si>
+    <t>29.05.202660</t>
+  </si>
+  <si>
+    <t>29.05.202661</t>
+  </si>
+  <si>
+    <t>29.05.202662</t>
+  </si>
+  <si>
+    <t>29.05.202663</t>
+  </si>
+  <si>
+    <t>29.05.202664</t>
+  </si>
+  <si>
+    <t>29.05.202665</t>
+  </si>
+  <si>
+    <t>29.05.202666</t>
+  </si>
+  <si>
+    <t>29.05.202667</t>
+  </si>
+  <si>
+    <t>29.05.202668</t>
+  </si>
+  <si>
+    <t>29.05.202669</t>
+  </si>
+  <si>
+    <t>29.05.202670</t>
+  </si>
+  <si>
+    <t>29.05.202671</t>
+  </si>
+  <si>
+    <t>29.05.202672</t>
+  </si>
+  <si>
+    <t>29.05.202673</t>
+  </si>
+  <si>
+    <t>29.05.202674</t>
+  </si>
+  <si>
+    <t>29.05.202675</t>
+  </si>
+  <si>
+    <t>29.05.202676</t>
+  </si>
+  <si>
+    <t>29.05.202677</t>
+  </si>
+  <si>
+    <t>29.05.202678</t>
+  </si>
+  <si>
+    <t>29.05.202679</t>
+  </si>
+  <si>
+    <t>29.05.202680</t>
+  </si>
+  <si>
+    <t>29.05.202681</t>
+  </si>
+  <si>
+    <t>29.05.202682</t>
+  </si>
+  <si>
+    <t>29.05.202683</t>
+  </si>
+  <si>
+    <t>29.05.202684</t>
+  </si>
+  <si>
+    <t>29.05.202685</t>
+  </si>
+  <si>
+    <t>29.05.202686</t>
+  </si>
+  <si>
+    <t>29.05.202687</t>
+  </si>
+  <si>
+    <t>29.05.202688</t>
+  </si>
+  <si>
+    <t>29.05.202689</t>
+  </si>
+  <si>
+    <t>29.05.202690</t>
+  </si>
+  <si>
+    <t>29.05.202691</t>
+  </si>
+  <si>
+    <t>29.05.202692</t>
+  </si>
+  <si>
+    <t>29.05.202693</t>
+  </si>
+  <si>
+    <t>29.05.202694</t>
+  </si>
+  <si>
+    <t>29.05.202695</t>
+  </si>
+  <si>
+    <t>29.05.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
-        <v>968.177</v>
+        <v>1145.311</v>
       </c>
       <c r="C2">
-        <v>1077</v>
+        <v>1288</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
-        <v>925.954</v>
+        <v>1123.122</v>
       </c>
       <c r="C3">
-        <v>1033</v>
+        <v>1229</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
-        <v>886.772</v>
+        <v>1116.171</v>
       </c>
       <c r="C4">
-        <v>960</v>
+        <v>1087</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
-        <v>846.275</v>
+        <v>1108.729</v>
       </c>
       <c r="C5">
-        <v>885</v>
+        <v>966</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
-        <v>790.985</v>
+        <v>1124.744</v>
       </c>
       <c r="C6">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
-        <v>756.944</v>
+        <v>1136.86</v>
       </c>
       <c r="C7">
-        <v>788</v>
+        <v>626</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
-        <v>732.716</v>
+        <v>1153.913</v>
       </c>
       <c r="C8">
-        <v>732</v>
+        <v>529</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
-        <v>704.546</v>
+        <v>1155.775</v>
       </c>
       <c r="C9">
-        <v>674</v>
+        <v>568</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
-        <v>669.766</v>
+        <v>1132.338</v>
       </c>
       <c r="C10">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
-        <v>649.48</v>
+        <v>1122.575</v>
       </c>
       <c r="C11">
-        <v>609</v>
+        <v>534</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
-        <v>631.688</v>
+        <v>1127.766</v>
       </c>
       <c r="C12">
-        <v>581</v>
+        <v>393</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
-        <v>609.175</v>
+        <v>1133.853</v>
       </c>
       <c r="C13">
-        <v>543</v>
+        <v>372</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>590.461</v>
+        <v>1117.217</v>
       </c>
       <c r="C14">
-        <v>536</v>
+        <v>382</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
-        <v>569.0170000000001</v>
+        <v>1111.369</v>
       </c>
       <c r="C15">
-        <v>517</v>
+        <v>443</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>553.9059999999999</v>
+        <v>1099.843</v>
       </c>
       <c r="C16">
-        <v>474</v>
+        <v>521</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>533.85</v>
+        <v>1085.726</v>
       </c>
       <c r="C17">
-        <v>463</v>
+        <v>553</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>493.472</v>
+        <v>1111.567</v>
       </c>
       <c r="C18">
-        <v>445</v>
+        <v>638</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>469.636</v>
+        <v>1093.644</v>
       </c>
       <c r="C19">
-        <v>408</v>
+        <v>736</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>448.506</v>
+        <v>1075.779</v>
       </c>
       <c r="C20">
-        <v>374</v>
+        <v>826</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>429.713</v>
+        <v>1058.034</v>
       </c>
       <c r="C21">
-        <v>350</v>
+        <v>871</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>397.968</v>
+        <v>1097.86</v>
       </c>
       <c r="C22">
-        <v>339</v>
+        <v>950</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>381.267</v>
+        <v>1084.866</v>
       </c>
       <c r="C23">
-        <v>314</v>
+        <v>967</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>363.79</v>
+        <v>1067.601</v>
       </c>
       <c r="C24">
-        <v>279</v>
+        <v>831</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>345.808</v>
+        <v>1060.729</v>
       </c>
       <c r="C25">
-        <v>246</v>
+        <v>833</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>301.359</v>
+        <v>1042.536</v>
       </c>
       <c r="C26">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>284.643</v>
+        <v>1001.511</v>
       </c>
       <c r="C27">
-        <v>165</v>
+        <v>776</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>271.301</v>
+        <v>979.593</v>
       </c>
       <c r="C28">
-        <v>150</v>
+        <v>802</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>254.307</v>
+        <v>952.644</v>
       </c>
       <c r="C29">
-        <v>123</v>
+        <v>746</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>234.511</v>
+        <v>918.862</v>
       </c>
       <c r="C30">
-        <v>96</v>
+        <v>692</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>214.131</v>
+        <v>915.29</v>
       </c>
       <c r="C31">
-        <v>69</v>
+        <v>693</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>198.09</v>
+        <v>918.626</v>
       </c>
       <c r="C32">
-        <v>50</v>
+        <v>742</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>181.058</v>
+        <v>922.864</v>
       </c>
       <c r="C33">
-        <v>39</v>
+        <v>765</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>159.833</v>
+        <v>870.261</v>
       </c>
       <c r="C34">
-        <v>38</v>
+        <v>669</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>160.638</v>
+        <v>864.173</v>
       </c>
       <c r="C35">
-        <v>35</v>
+        <v>605</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>158.173</v>
+        <v>890.585</v>
       </c>
       <c r="C36">
-        <v>27</v>
+        <v>539</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>154.113</v>
+        <v>883.152</v>
       </c>
       <c r="C37">
-        <v>24</v>
+        <v>502</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>163.42</v>
+        <v>1044.111</v>
       </c>
       <c r="C38">
-        <v>26</v>
+        <v>514</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>169.288</v>
+        <v>1051.657</v>
       </c>
       <c r="C39">
-        <v>29</v>
+        <v>539</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>170.347</v>
+        <v>1054.17</v>
       </c>
       <c r="C40">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>166.869</v>
+        <v>1055.901</v>
       </c>
       <c r="C41">
-        <v>28</v>
+        <v>559</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>171.866</v>
+        <v>976.917</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>179.219</v>
+        <v>973.501</v>
       </c>
       <c r="C43">
-        <v>34</v>
+        <v>427</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>186.23</v>
+        <v>969.021</v>
       </c>
       <c r="C44">
-        <v>39</v>
+        <v>425</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>193.822</v>
+        <v>962.736</v>
       </c>
       <c r="C45">
-        <v>50</v>
+        <v>434</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>210.769</v>
+        <v>974.122</v>
       </c>
       <c r="C46">
-        <v>71</v>
+        <v>465</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>225.097</v>
+        <v>954.162</v>
       </c>
       <c r="C47">
-        <v>97</v>
+        <v>486</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>241.448</v>
+        <v>876.26</v>
       </c>
       <c r="C48">
-        <v>128</v>
+        <v>499</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>256.327</v>
+        <v>857.999</v>
       </c>
       <c r="C49">
-        <v>160</v>
+        <v>509</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>283.902</v>
+        <v>868.049</v>
       </c>
       <c r="C50">
-        <v>188</v>
+        <v>521</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>304.168</v>
+        <v>860.923</v>
       </c>
       <c r="C51">
-        <v>217</v>
+        <v>503</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>325.373</v>
+        <v>856.353</v>
       </c>
       <c r="C52">
-        <v>241</v>
+        <v>497</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>345.138</v>
+        <v>852.186</v>
       </c>
       <c r="C53">
-        <v>278</v>
+        <v>474</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>374.558</v>
+        <v>878.2190000000001</v>
       </c>
       <c r="C54">
-        <v>316</v>
+        <v>464</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>397.244</v>
+        <v>882.754</v>
       </c>
       <c r="C55">
-        <v>343</v>
+        <v>493</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>420.209</v>
+        <v>888.447</v>
       </c>
       <c r="C56">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>442.292</v>
+        <v>894.586</v>
       </c>
       <c r="C57">
-        <v>378</v>
+        <v>482</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>486.002</v>
+        <v>912.5700000000001</v>
       </c>
       <c r="C58">
-        <v>422</v>
+        <v>488</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>508.528</v>
+        <v>913.051</v>
       </c>
       <c r="C59">
-        <v>466</v>
+        <v>512</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>532.088</v>
+        <v>915.259</v>
       </c>
       <c r="C60">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>557.99</v>
+        <v>915.321</v>
       </c>
       <c r="C61">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>594.5170000000001</v>
+        <v>956.386</v>
       </c>
       <c r="C62">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>621.851</v>
+        <v>953.712</v>
       </c>
       <c r="C63">
-        <v>652</v>
+        <v>601</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>646.076</v>
+        <v>1003.502</v>
       </c>
       <c r="C64">
-        <v>700</v>
+        <v>604</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>671.899</v>
+        <v>999.491</v>
       </c>
       <c r="C65">
-        <v>758</v>
+        <v>618</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>692.5839999999999</v>
+        <v>927.549</v>
       </c>
       <c r="C66">
-        <v>801</v>
+        <v>621</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>703.879</v>
+        <v>934.987</v>
       </c>
       <c r="C67">
-        <v>813</v>
+        <v>586</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>715.573</v>
+        <v>944.985</v>
       </c>
       <c r="C68">
-        <v>821</v>
+        <v>577</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>727.829</v>
+        <v>953.644</v>
       </c>
       <c r="C69">
-        <v>851</v>
+        <v>618</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>742.475</v>
+        <v>915.097</v>
       </c>
       <c r="C70">
-        <v>856</v>
+        <v>660</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>747.4450000000001</v>
+        <v>927.851</v>
       </c>
       <c r="C71">
-        <v>857</v>
+        <v>699</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>753.2140000000001</v>
+        <v>940.785</v>
       </c>
       <c r="C72">
-        <v>845</v>
+        <v>716</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>758.707</v>
+        <v>953.522</v>
       </c>
       <c r="C73">
-        <v>820</v>
+        <v>644</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>783.022</v>
+        <v>964.107</v>
       </c>
       <c r="C74">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>807.098</v>
+        <v>968.4299999999999</v>
       </c>
       <c r="C75">
-        <v>805</v>
+        <v>747</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>832.646</v>
+        <v>971.021</v>
       </c>
       <c r="C76">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>861.077</v>
+        <v>972.691</v>
       </c>
       <c r="C77">
-        <v>876</v>
+        <v>856</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>881.183</v>
+        <v>1013.818</v>
       </c>
       <c r="C78">
         <v>905</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>916.026</v>
+        <v>1006.628</v>
       </c>
       <c r="C79">
-        <v>919</v>
+        <v>1000</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>951.373</v>
+        <v>998.481</v>
       </c>
       <c r="C80">
-        <v>928</v>
+        <v>1073</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>984.893</v>
+        <v>987.854</v>
       </c>
       <c r="C81">
-        <v>990</v>
+        <v>1039</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>1032.365</v>
+        <v>970.533</v>
       </c>
       <c r="C82">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>1055.294</v>
+        <v>952.837</v>
       </c>
       <c r="C83">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>1074.92</v>
+        <v>931.707</v>
       </c>
       <c r="C84">
-        <v>1107</v>
+        <v>1131</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>1098.592</v>
+        <v>910.35</v>
       </c>
       <c r="C85">
-        <v>1145</v>
+        <v>1199</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>1125.574</v>
+        <v>848.825</v>
       </c>
       <c r="C86">
-        <v>1163</v>
+        <v>1285</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>1142.988</v>
+        <v>848.266</v>
       </c>
       <c r="C87">
-        <v>1133</v>
+        <v>1306</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
-        <v>1158.963</v>
+        <v>845.915</v>
       </c>
       <c r="C88">
-        <v>1143</v>
+        <v>1269</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>1171.542</v>
+        <v>845.731</v>
       </c>
       <c r="C89">
-        <v>1241</v>
+        <v>1175</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>1173.933</v>
+        <v>842.111</v>
       </c>
       <c r="C90">
-        <v>1323</v>
+        <v>1194</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>1167.589</v>
+        <v>843.746</v>
       </c>
       <c r="C91">
-        <v>1446</v>
+        <v>1202</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
-        <v>1167.561</v>
+        <v>845.639</v>
       </c>
       <c r="C92">
-        <v>1443</v>
+        <v>1225</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
-        <v>1165.584</v>
+        <v>852.399</v>
       </c>
       <c r="C93">
-        <v>1353</v>
+        <v>1173</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
-        <v>1102.103</v>
+        <v>951.077</v>
       </c>
       <c r="C94">
-        <v>1275</v>
+        <v>1031</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
-        <v>1107.912</v>
+        <v>956.926</v>
       </c>
       <c r="C95">
-        <v>1358</v>
+        <v>942</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
-        <v>1104.848</v>
+        <v>942.524</v>
       </c>
       <c r="C96">
-        <v>1396</v>
+        <v>810</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
-        <v>1091.355</v>
+        <v>942.952</v>
       </c>
       <c r="C97">
-        <v>1385</v>
+        <v>741</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
-        <v>1145.311</v>
+        <v>940.735</v>
       </c>
       <c r="C98">
-        <v>1288</v>
+        <v>652</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
-        <v>1123.122</v>
+        <v>922.115</v>
       </c>
       <c r="C99">
-        <v>1229</v>
+        <v>612</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
-        <v>1116.171</v>
+        <v>896.678</v>
       </c>
       <c r="C100">
-        <v>1087</v>
+        <v>603</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
-        <v>1108.729</v>
+        <v>880.107</v>
       </c>
       <c r="C101">
-        <v>966</v>
+        <v>615</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
-        <v>1124.744</v>
+        <v>850.032</v>
       </c>
       <c r="C102">
-        <v>850</v>
+        <v>661</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
-        <v>1136.86</v>
+        <v>851.812</v>
       </c>
       <c r="C103">
-        <v>626</v>
+        <v>693</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
-        <v>1153.913</v>
+        <v>848.515</v>
       </c>
       <c r="C104">
-        <v>529</v>
+        <v>752</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
-        <v>1155.775</v>
+        <v>847.87</v>
       </c>
       <c r="C105">
-        <v>568</v>
+        <v>819</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
-        <v>1132.338</v>
+        <v>847.55</v>
       </c>
       <c r="C106">
-        <v>635</v>
+        <v>859</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
-        <v>1122.575</v>
+        <v>861.245</v>
       </c>
       <c r="C107">
-        <v>534</v>
+        <v>941</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
-        <v>1127.766</v>
+        <v>875.669</v>
       </c>
       <c r="C108">
-        <v>393</v>
+        <v>990</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
-        <v>1133.853</v>
+        <v>905.244</v>
       </c>
       <c r="C109">
-        <v>372</v>
+        <v>1036</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
-        <v>1117.217</v>
+        <v>941.001</v>
       </c>
       <c r="C110">
-        <v>382</v>
+        <v>1045</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
-        <v>1111.369</v>
+        <v>970.492</v>
       </c>
       <c r="C111">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
-        <v>1099.843</v>
+        <v>987.1130000000001</v>
       </c>
       <c r="C112">
-        <v>521</v>
+        <v>1025</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
-        <v>1085.726</v>
+        <v>1004.18</v>
       </c>
       <c r="C113">
-        <v>553</v>
+        <v>1005</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
-        <v>1111.567</v>
+        <v>1048.057</v>
       </c>
       <c r="C114">
-        <v>638</v>
+        <v>970</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
-        <v>1093.644</v>
+        <v>1063.948</v>
       </c>
       <c r="C115">
-        <v>736</v>
+        <v>974</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
-        <v>1075.779</v>
+        <v>1075.113</v>
       </c>
       <c r="C116">
-        <v>826</v>
+        <v>1044</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>1058.034</v>
+        <v>1082.456</v>
       </c>
       <c r="C117">
-        <v>871</v>
+        <v>1052</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>1097.86</v>
+        <v>1085.848</v>
       </c>
       <c r="C118">
-        <v>950</v>
+        <v>1042</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>1084.866</v>
+        <v>1073.242</v>
       </c>
       <c r="C119">
-        <v>967</v>
+        <v>1031</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>1067.601</v>
+        <v>1062.672</v>
       </c>
       <c r="C120">
-        <v>831</v>
+        <v>1057</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>1060.729</v>
+        <v>1053.064</v>
       </c>
       <c r="C121">
-        <v>833</v>
+        <v>1059</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>1042.536</v>
+        <v>1029.939</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>1063</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>1001.511</v>
+        <v>979.907</v>
       </c>
       <c r="C123">
-        <v>776</v>
+        <v>972</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>979.593</v>
+        <v>935.568</v>
       </c>
       <c r="C124">
-        <v>802</v>
+        <v>892</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>952.644</v>
+        <v>895.271</v>
       </c>
       <c r="C125">
-        <v>746</v>
+        <v>864</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>918.862</v>
+        <v>881.612</v>
       </c>
       <c r="C126">
-        <v>692</v>
+        <v>812</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>915.29</v>
+        <v>885.614</v>
       </c>
       <c r="C127">
-        <v>693</v>
+        <v>791</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>918.626</v>
+        <v>890.519</v>
       </c>
       <c r="C128">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>922.864</v>
+        <v>899.0650000000001</v>
       </c>
       <c r="C129">
-        <v>765</v>
+        <v>691</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>870.261</v>
+        <v>916.687</v>
       </c>
       <c r="C130">
-        <v>669</v>
+        <v>690</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>864.173</v>
+        <v>943.788</v>
       </c>
       <c r="C131">
-        <v>605</v>
+        <v>725</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>890.585</v>
+        <v>971.8200000000001</v>
       </c>
       <c r="C132">
-        <v>539</v>
+        <v>744</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
-        <v>883.152</v>
+        <v>1004.072</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
-        <v>1044.111</v>
+        <v>1125.688</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
-        <v>1051.657</v>
+        <v>1161.654</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
-        <v>1054.17</v>
+        <v>1197.062</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
-        <v>1055.901</v>
+        <v>1232.957</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
-        <v>976.917</v>
+        <v>1352.951</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
-        <v>973.501</v>
+        <v>1394.104</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
-        <v>969.021</v>
+        <v>1436.909</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
-        <v>962.736</v>
+        <v>1477.779</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
-        <v>974.122</v>
+        <v>1528.587</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -3385,10 +3385,10 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
-        <v>954.162</v>
+        <v>1554.609</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -3402,10 +3402,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
-        <v>876.26</v>
+        <v>1577.678</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
-        <v>857.999</v>
+        <v>1598.411</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
-        <v>868.049</v>
+        <v>1580.333</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
-        <v>860.923</v>
+        <v>1599.826</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -3470,10 +3470,10 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
-        <v>856.353</v>
+        <v>1619.63</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -3487,10 +3487,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
-        <v>852.186</v>
+        <v>1638.402</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
-        <v>878.2190000000001</v>
+        <v>1606.43</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
-        <v>882.754</v>
+        <v>1597.345</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
-        <v>888.447</v>
+        <v>1588.115</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
-        <v>894.586</v>
+        <v>1577.401</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
-        <v>912.5700000000001</v>
+        <v>1573.094</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
-        <v>913.051</v>
+        <v>1544.475</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
-        <v>915.259</v>
+        <v>1515.642</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
-        <v>915.321</v>
+        <v>1486.99</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
-        <v>956.386</v>
+        <v>1473.462</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
-        <v>953.712</v>
+        <v>1437.031</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
-        <v>1003.502</v>
+        <v>1401.151</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
-        <v>999.491</v>
+        <v>1361.086</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
-        <v>927.549</v>
+        <v>1230.863</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
-        <v>934.987</v>
+        <v>1202.179</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
-        <v>944.985</v>
+        <v>1174.575</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
-        <v>953.644</v>
+        <v>1149.54</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
-        <v>915.097</v>
+        <v>1094.509</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
-        <v>927.851</v>
+        <v>1043.154</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
-        <v>940.785</v>
+        <v>994.076</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
-        <v>953.522</v>
+        <v>947.4880000000001</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
-        <v>964.107</v>
+        <v>887.542</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
-        <v>968.4299999999999</v>
+        <v>864.98</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
-        <v>971.021</v>
+        <v>844.538</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
-        <v>972.691</v>
+        <v>825.651</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
-        <v>1013.818</v>
+        <v>796.273</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
-        <v>1006.628</v>
+        <v>793.112</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
-        <v>998.481</v>
+        <v>786.64</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
-        <v>987.854</v>
+        <v>780.309</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
-        <v>970.533</v>
+        <v>764.907</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
-        <v>952.837</v>
+        <v>747.316</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
-        <v>931.707</v>
+        <v>732.135</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
-        <v>910.35</v>
+        <v>712.827</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
-        <v>848.825</v>
+        <v>678.509</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
-        <v>848.266</v>
+        <v>660.641</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
-        <v>845.915</v>
+        <v>645.8440000000001</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
-        <v>845.731</v>
+        <v>627.514</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
-        <v>842.111</v>
+        <v>608.4640000000001</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
-        <v>843.746</v>
+        <v>585.35</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
-        <v>845.639</v>
+        <v>563.232</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
-        <v>852.399</v>
+        <v>542.976</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -31,580 +31,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.06.20261</t>
-  </si>
-  <si>
-    <t>03.06.20262</t>
-  </si>
-  <si>
-    <t>03.06.20263</t>
-  </si>
-  <si>
-    <t>03.06.20264</t>
-  </si>
-  <si>
-    <t>03.06.20265</t>
-  </si>
-  <si>
-    <t>03.06.20266</t>
-  </si>
-  <si>
-    <t>03.06.20267</t>
-  </si>
-  <si>
-    <t>03.06.20268</t>
-  </si>
-  <si>
-    <t>03.06.20269</t>
-  </si>
-  <si>
-    <t>03.06.202610</t>
-  </si>
-  <si>
-    <t>03.06.202611</t>
-  </si>
-  <si>
-    <t>03.06.202612</t>
-  </si>
-  <si>
-    <t>03.06.202613</t>
-  </si>
-  <si>
-    <t>03.06.202614</t>
-  </si>
-  <si>
-    <t>03.06.202615</t>
-  </si>
-  <si>
-    <t>03.06.202616</t>
-  </si>
-  <si>
-    <t>03.06.202617</t>
-  </si>
-  <si>
-    <t>03.06.202618</t>
-  </si>
-  <si>
-    <t>03.06.202619</t>
-  </si>
-  <si>
-    <t>03.06.202620</t>
-  </si>
-  <si>
-    <t>03.06.202621</t>
-  </si>
-  <si>
-    <t>03.06.202622</t>
-  </si>
-  <si>
-    <t>03.06.202623</t>
-  </si>
-  <si>
-    <t>03.06.202624</t>
-  </si>
-  <si>
-    <t>03.06.202625</t>
-  </si>
-  <si>
-    <t>03.06.202626</t>
-  </si>
-  <si>
-    <t>03.06.202627</t>
-  </si>
-  <si>
-    <t>03.06.202628</t>
-  </si>
-  <si>
-    <t>03.06.202629</t>
-  </si>
-  <si>
-    <t>03.06.202630</t>
-  </si>
-  <si>
-    <t>03.06.202631</t>
-  </si>
-  <si>
-    <t>03.06.202632</t>
-  </si>
-  <si>
-    <t>03.06.202633</t>
-  </si>
-  <si>
-    <t>03.06.202634</t>
-  </si>
-  <si>
-    <t>03.06.202635</t>
-  </si>
-  <si>
-    <t>03.06.202636</t>
-  </si>
-  <si>
-    <t>03.06.202637</t>
-  </si>
-  <si>
-    <t>03.06.202638</t>
-  </si>
-  <si>
-    <t>03.06.202639</t>
-  </si>
-  <si>
-    <t>03.06.202640</t>
-  </si>
-  <si>
-    <t>03.06.202641</t>
-  </si>
-  <si>
-    <t>03.06.202642</t>
-  </si>
-  <si>
-    <t>03.06.202643</t>
-  </si>
-  <si>
-    <t>03.06.202644</t>
-  </si>
-  <si>
-    <t>03.06.202645</t>
-  </si>
-  <si>
-    <t>03.06.202646</t>
-  </si>
-  <si>
-    <t>03.06.202647</t>
-  </si>
-  <si>
-    <t>03.06.202648</t>
-  </si>
-  <si>
-    <t>03.06.202649</t>
-  </si>
-  <si>
-    <t>03.06.202650</t>
-  </si>
-  <si>
-    <t>03.06.202651</t>
-  </si>
-  <si>
-    <t>03.06.202652</t>
-  </si>
-  <si>
-    <t>03.06.202653</t>
-  </si>
-  <si>
-    <t>03.06.202654</t>
-  </si>
-  <si>
-    <t>03.06.202655</t>
-  </si>
-  <si>
-    <t>03.06.202656</t>
-  </si>
-  <si>
-    <t>03.06.202657</t>
-  </si>
-  <si>
-    <t>03.06.202658</t>
-  </si>
-  <si>
-    <t>03.06.202659</t>
-  </si>
-  <si>
-    <t>03.06.202660</t>
-  </si>
-  <si>
-    <t>03.06.202661</t>
-  </si>
-  <si>
-    <t>03.06.202662</t>
-  </si>
-  <si>
-    <t>03.06.202663</t>
-  </si>
-  <si>
-    <t>03.06.202664</t>
-  </si>
-  <si>
-    <t>03.06.202665</t>
-  </si>
-  <si>
-    <t>03.06.202666</t>
-  </si>
-  <si>
-    <t>03.06.202667</t>
-  </si>
-  <si>
-    <t>03.06.202668</t>
-  </si>
-  <si>
-    <t>03.06.202669</t>
-  </si>
-  <si>
-    <t>03.06.202670</t>
-  </si>
-  <si>
-    <t>03.06.202671</t>
-  </si>
-  <si>
-    <t>03.06.202672</t>
-  </si>
-  <si>
-    <t>03.06.202673</t>
-  </si>
-  <si>
-    <t>03.06.202674</t>
-  </si>
-  <si>
-    <t>03.06.202675</t>
-  </si>
-  <si>
-    <t>03.06.202676</t>
-  </si>
-  <si>
-    <t>03.06.202677</t>
-  </si>
-  <si>
-    <t>03.06.202678</t>
-  </si>
-  <si>
-    <t>03.06.202679</t>
-  </si>
-  <si>
-    <t>03.06.202680</t>
-  </si>
-  <si>
-    <t>03.06.202681</t>
-  </si>
-  <si>
-    <t>03.06.202682</t>
-  </si>
-  <si>
-    <t>03.06.202683</t>
-  </si>
-  <si>
-    <t>03.06.202684</t>
-  </si>
-  <si>
-    <t>03.06.202685</t>
-  </si>
-  <si>
-    <t>03.06.202686</t>
-  </si>
-  <si>
-    <t>03.06.202687</t>
-  </si>
-  <si>
-    <t>03.06.202688</t>
-  </si>
-  <si>
-    <t>03.06.202689</t>
-  </si>
-  <si>
-    <t>03.06.202690</t>
-  </si>
-  <si>
-    <t>03.06.202691</t>
-  </si>
-  <si>
-    <t>03.06.202692</t>
-  </si>
-  <si>
-    <t>03.06.202693</t>
-  </si>
-  <si>
-    <t>03.06.202694</t>
-  </si>
-  <si>
-    <t>03.06.202695</t>
-  </si>
-  <si>
-    <t>03.06.202696</t>
-  </si>
-  <si>
-    <t>04.06.20261</t>
-  </si>
-  <si>
-    <t>04.06.20262</t>
-  </si>
-  <si>
-    <t>04.06.20263</t>
-  </si>
-  <si>
-    <t>04.06.20264</t>
-  </si>
-  <si>
-    <t>04.06.20265</t>
-  </si>
-  <si>
-    <t>04.06.20266</t>
-  </si>
-  <si>
-    <t>04.06.20267</t>
-  </si>
-  <si>
-    <t>04.06.20268</t>
-  </si>
-  <si>
-    <t>04.06.20269</t>
-  </si>
-  <si>
-    <t>04.06.202610</t>
-  </si>
-  <si>
-    <t>04.06.202611</t>
-  </si>
-  <si>
-    <t>04.06.202612</t>
-  </si>
-  <si>
-    <t>04.06.202613</t>
-  </si>
-  <si>
-    <t>04.06.202614</t>
-  </si>
-  <si>
-    <t>04.06.202615</t>
-  </si>
-  <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>04.06.202624</t>
-  </si>
-  <si>
-    <t>04.06.202625</t>
-  </si>
-  <si>
-    <t>04.06.202626</t>
-  </si>
-  <si>
-    <t>04.06.202627</t>
-  </si>
-  <si>
-    <t>04.06.202628</t>
-  </si>
-  <si>
-    <t>04.06.202629</t>
-  </si>
-  <si>
-    <t>04.06.202630</t>
-  </si>
-  <si>
-    <t>04.06.202631</t>
-  </si>
-  <si>
-    <t>04.06.202632</t>
-  </si>
-  <si>
-    <t>04.06.202633</t>
-  </si>
-  <si>
-    <t>04.06.202634</t>
-  </si>
-  <si>
-    <t>04.06.202635</t>
-  </si>
-  <si>
-    <t>04.06.202636</t>
-  </si>
-  <si>
-    <t>04.06.202637</t>
-  </si>
-  <si>
-    <t>04.06.202638</t>
-  </si>
-  <si>
-    <t>04.06.202639</t>
-  </si>
-  <si>
-    <t>04.06.202640</t>
-  </si>
-  <si>
-    <t>04.06.202641</t>
-  </si>
-  <si>
-    <t>04.06.202642</t>
-  </si>
-  <si>
-    <t>04.06.202643</t>
-  </si>
-  <si>
-    <t>04.06.202644</t>
-  </si>
-  <si>
-    <t>04.06.202645</t>
-  </si>
-  <si>
-    <t>04.06.202646</t>
-  </si>
-  <si>
-    <t>04.06.202647</t>
-  </si>
-  <si>
-    <t>04.06.202648</t>
-  </si>
-  <si>
-    <t>04.06.202649</t>
-  </si>
-  <si>
-    <t>04.06.202650</t>
-  </si>
-  <si>
-    <t>04.06.202651</t>
-  </si>
-  <si>
-    <t>04.06.202652</t>
-  </si>
-  <si>
-    <t>04.06.202653</t>
-  </si>
-  <si>
-    <t>04.06.202654</t>
-  </si>
-  <si>
-    <t>04.06.202655</t>
-  </si>
-  <si>
-    <t>04.06.202656</t>
-  </si>
-  <si>
-    <t>04.06.202657</t>
-  </si>
-  <si>
-    <t>04.06.202658</t>
-  </si>
-  <si>
-    <t>04.06.202659</t>
-  </si>
-  <si>
-    <t>04.06.202660</t>
-  </si>
-  <si>
-    <t>04.06.202661</t>
-  </si>
-  <si>
-    <t>04.06.202662</t>
-  </si>
-  <si>
-    <t>04.06.202663</t>
-  </si>
-  <si>
-    <t>04.06.202664</t>
-  </si>
-  <si>
-    <t>04.06.202665</t>
-  </si>
-  <si>
-    <t>04.06.202666</t>
-  </si>
-  <si>
-    <t>04.06.202667</t>
-  </si>
-  <si>
-    <t>04.06.202668</t>
-  </si>
-  <si>
-    <t>04.06.202669</t>
-  </si>
-  <si>
-    <t>04.06.202670</t>
-  </si>
-  <si>
-    <t>04.06.202671</t>
-  </si>
-  <si>
-    <t>04.06.202672</t>
-  </si>
-  <si>
-    <t>04.06.202673</t>
-  </si>
-  <si>
-    <t>04.06.202674</t>
-  </si>
-  <si>
-    <t>04.06.202675</t>
-  </si>
-  <si>
-    <t>04.06.202676</t>
-  </si>
-  <si>
-    <t>04.06.202677</t>
-  </si>
-  <si>
-    <t>04.06.202678</t>
-  </si>
-  <si>
-    <t>04.06.202679</t>
-  </si>
-  <si>
-    <t>04.06.202680</t>
-  </si>
-  <si>
-    <t>04.06.202681</t>
-  </si>
-  <si>
-    <t>04.06.202682</t>
-  </si>
-  <si>
-    <t>04.06.202683</t>
-  </si>
-  <si>
-    <t>04.06.202684</t>
-  </si>
-  <si>
-    <t>04.06.202685</t>
-  </si>
-  <si>
-    <t>04.06.202686</t>
-  </si>
-  <si>
-    <t>04.06.202687</t>
-  </si>
-  <si>
-    <t>04.06.202688</t>
-  </si>
-  <si>
-    <t>04.06.202689</t>
-  </si>
-  <si>
-    <t>04.06.202690</t>
-  </si>
-  <si>
-    <t>04.06.202691</t>
-  </si>
-  <si>
-    <t>04.06.202692</t>
-  </si>
-  <si>
-    <t>04.06.202693</t>
-  </si>
-  <si>
-    <t>04.06.202694</t>
-  </si>
-  <si>
-    <t>04.06.202695</t>
-  </si>
-  <si>
-    <t>04.06.202696</t>
+    <t>11.06.20261</t>
+  </si>
+  <si>
+    <t>11.06.20262</t>
+  </si>
+  <si>
+    <t>11.06.20263</t>
+  </si>
+  <si>
+    <t>11.06.20264</t>
+  </si>
+  <si>
+    <t>11.06.20265</t>
+  </si>
+  <si>
+    <t>11.06.20266</t>
+  </si>
+  <si>
+    <t>11.06.20267</t>
+  </si>
+  <si>
+    <t>11.06.20268</t>
+  </si>
+  <si>
+    <t>11.06.20269</t>
+  </si>
+  <si>
+    <t>11.06.202610</t>
+  </si>
+  <si>
+    <t>11.06.202611</t>
+  </si>
+  <si>
+    <t>11.06.202612</t>
+  </si>
+  <si>
+    <t>11.06.202613</t>
+  </si>
+  <si>
+    <t>11.06.202614</t>
+  </si>
+  <si>
+    <t>11.06.202615</t>
+  </si>
+  <si>
+    <t>11.06.202616</t>
+  </si>
+  <si>
+    <t>11.06.202617</t>
+  </si>
+  <si>
+    <t>11.06.202618</t>
+  </si>
+  <si>
+    <t>11.06.202619</t>
+  </si>
+  <si>
+    <t>11.06.202620</t>
+  </si>
+  <si>
+    <t>11.06.202621</t>
+  </si>
+  <si>
+    <t>11.06.202622</t>
+  </si>
+  <si>
+    <t>11.06.202623</t>
+  </si>
+  <si>
+    <t>11.06.202624</t>
+  </si>
+  <si>
+    <t>11.06.202625</t>
+  </si>
+  <si>
+    <t>11.06.202626</t>
+  </si>
+  <si>
+    <t>11.06.202627</t>
+  </si>
+  <si>
+    <t>11.06.202628</t>
+  </si>
+  <si>
+    <t>11.06.202629</t>
+  </si>
+  <si>
+    <t>11.06.202630</t>
+  </si>
+  <si>
+    <t>11.06.202631</t>
+  </si>
+  <si>
+    <t>11.06.202632</t>
+  </si>
+  <si>
+    <t>11.06.202633</t>
+  </si>
+  <si>
+    <t>11.06.202634</t>
+  </si>
+  <si>
+    <t>11.06.202635</t>
+  </si>
+  <si>
+    <t>11.06.202636</t>
+  </si>
+  <si>
+    <t>11.06.202637</t>
+  </si>
+  <si>
+    <t>11.06.202638</t>
+  </si>
+  <si>
+    <t>11.06.202639</t>
+  </si>
+  <si>
+    <t>11.06.202640</t>
+  </si>
+  <si>
+    <t>11.06.202641</t>
+  </si>
+  <si>
+    <t>11.06.202642</t>
+  </si>
+  <si>
+    <t>11.06.202643</t>
+  </si>
+  <si>
+    <t>11.06.202644</t>
+  </si>
+  <si>
+    <t>11.06.202645</t>
+  </si>
+  <si>
+    <t>11.06.202646</t>
+  </si>
+  <si>
+    <t>11.06.202647</t>
+  </si>
+  <si>
+    <t>11.06.202648</t>
+  </si>
+  <si>
+    <t>11.06.202649</t>
+  </si>
+  <si>
+    <t>11.06.202650</t>
+  </si>
+  <si>
+    <t>11.06.202651</t>
+  </si>
+  <si>
+    <t>11.06.202652</t>
+  </si>
+  <si>
+    <t>11.06.202653</t>
+  </si>
+  <si>
+    <t>11.06.202654</t>
+  </si>
+  <si>
+    <t>11.06.202655</t>
+  </si>
+  <si>
+    <t>11.06.202656</t>
+  </si>
+  <si>
+    <t>11.06.202657</t>
+  </si>
+  <si>
+    <t>11.06.202658</t>
+  </si>
+  <si>
+    <t>11.06.202659</t>
+  </si>
+  <si>
+    <t>11.06.202660</t>
+  </si>
+  <si>
+    <t>11.06.202661</t>
+  </si>
+  <si>
+    <t>11.06.202662</t>
+  </si>
+  <si>
+    <t>11.06.202663</t>
+  </si>
+  <si>
+    <t>11.06.202664</t>
+  </si>
+  <si>
+    <t>11.06.202665</t>
+  </si>
+  <si>
+    <t>11.06.202666</t>
+  </si>
+  <si>
+    <t>11.06.202667</t>
+  </si>
+  <si>
+    <t>11.06.202668</t>
+  </si>
+  <si>
+    <t>11.06.202669</t>
+  </si>
+  <si>
+    <t>11.06.202670</t>
+  </si>
+  <si>
+    <t>11.06.202671</t>
+  </si>
+  <si>
+    <t>11.06.202672</t>
+  </si>
+  <si>
+    <t>11.06.202673</t>
+  </si>
+  <si>
+    <t>11.06.202674</t>
+  </si>
+  <si>
+    <t>11.06.202675</t>
+  </si>
+  <si>
+    <t>11.06.202676</t>
+  </si>
+  <si>
+    <t>11.06.202677</t>
+  </si>
+  <si>
+    <t>11.06.202678</t>
+  </si>
+  <si>
+    <t>11.06.202679</t>
+  </si>
+  <si>
+    <t>11.06.202680</t>
+  </si>
+  <si>
+    <t>11.06.202681</t>
+  </si>
+  <si>
+    <t>11.06.202682</t>
+  </si>
+  <si>
+    <t>11.06.202683</t>
+  </si>
+  <si>
+    <t>11.06.202684</t>
+  </si>
+  <si>
+    <t>11.06.202685</t>
+  </si>
+  <si>
+    <t>11.06.202686</t>
+  </si>
+  <si>
+    <t>11.06.202687</t>
+  </si>
+  <si>
+    <t>11.06.202688</t>
+  </si>
+  <si>
+    <t>11.06.202689</t>
+  </si>
+  <si>
+    <t>11.06.202690</t>
+  </si>
+  <si>
+    <t>11.06.202691</t>
+  </si>
+  <si>
+    <t>11.06.202692</t>
+  </si>
+  <si>
+    <t>11.06.202693</t>
+  </si>
+  <si>
+    <t>11.06.202694</t>
+  </si>
+  <si>
+    <t>11.06.202695</t>
+  </si>
+  <si>
+    <t>11.06.202696</t>
+  </si>
+  <si>
+    <t>12.06.20261</t>
+  </si>
+  <si>
+    <t>12.06.20262</t>
+  </si>
+  <si>
+    <t>12.06.20263</t>
+  </si>
+  <si>
+    <t>12.06.20264</t>
+  </si>
+  <si>
+    <t>12.06.20265</t>
+  </si>
+  <si>
+    <t>12.06.20266</t>
+  </si>
+  <si>
+    <t>12.06.20267</t>
+  </si>
+  <si>
+    <t>12.06.20268</t>
+  </si>
+  <si>
+    <t>12.06.20269</t>
+  </si>
+  <si>
+    <t>12.06.202610</t>
+  </si>
+  <si>
+    <t>12.06.202611</t>
+  </si>
+  <si>
+    <t>12.06.202612</t>
+  </si>
+  <si>
+    <t>12.06.202613</t>
+  </si>
+  <si>
+    <t>12.06.202614</t>
+  </si>
+  <si>
+    <t>12.06.202615</t>
+  </si>
+  <si>
+    <t>12.06.202616</t>
+  </si>
+  <si>
+    <t>12.06.202617</t>
+  </si>
+  <si>
+    <t>12.06.202618</t>
+  </si>
+  <si>
+    <t>12.06.202619</t>
+  </si>
+  <si>
+    <t>12.06.202620</t>
+  </si>
+  <si>
+    <t>12.06.202621</t>
+  </si>
+  <si>
+    <t>12.06.202622</t>
+  </si>
+  <si>
+    <t>12.06.202623</t>
+  </si>
+  <si>
+    <t>12.06.202624</t>
+  </si>
+  <si>
+    <t>12.06.202625</t>
+  </si>
+  <si>
+    <t>12.06.202626</t>
+  </si>
+  <si>
+    <t>12.06.202627</t>
+  </si>
+  <si>
+    <t>12.06.202628</t>
+  </si>
+  <si>
+    <t>12.06.202629</t>
+  </si>
+  <si>
+    <t>12.06.202630</t>
+  </si>
+  <si>
+    <t>12.06.202631</t>
+  </si>
+  <si>
+    <t>12.06.202632</t>
+  </si>
+  <si>
+    <t>12.06.202633</t>
+  </si>
+  <si>
+    <t>12.06.202634</t>
+  </si>
+  <si>
+    <t>12.06.202635</t>
+  </si>
+  <si>
+    <t>12.06.202636</t>
+  </si>
+  <si>
+    <t>12.06.202637</t>
+  </si>
+  <si>
+    <t>12.06.202638</t>
+  </si>
+  <si>
+    <t>12.06.202639</t>
+  </si>
+  <si>
+    <t>12.06.202640</t>
+  </si>
+  <si>
+    <t>12.06.202641</t>
+  </si>
+  <si>
+    <t>12.06.202642</t>
+  </si>
+  <si>
+    <t>12.06.202643</t>
+  </si>
+  <si>
+    <t>12.06.202644</t>
+  </si>
+  <si>
+    <t>12.06.202645</t>
+  </si>
+  <si>
+    <t>12.06.202646</t>
+  </si>
+  <si>
+    <t>12.06.202647</t>
+  </si>
+  <si>
+    <t>12.06.202648</t>
+  </si>
+  <si>
+    <t>12.06.202649</t>
+  </si>
+  <si>
+    <t>12.06.202650</t>
+  </si>
+  <si>
+    <t>12.06.202651</t>
+  </si>
+  <si>
+    <t>12.06.202652</t>
+  </si>
+  <si>
+    <t>12.06.202653</t>
+  </si>
+  <si>
+    <t>12.06.202654</t>
+  </si>
+  <si>
+    <t>12.06.202655</t>
+  </si>
+  <si>
+    <t>12.06.202656</t>
+  </si>
+  <si>
+    <t>12.06.202657</t>
+  </si>
+  <si>
+    <t>12.06.202658</t>
+  </si>
+  <si>
+    <t>12.06.202659</t>
+  </si>
+  <si>
+    <t>12.06.202660</t>
+  </si>
+  <si>
+    <t>12.06.202661</t>
+  </si>
+  <si>
+    <t>12.06.202662</t>
+  </si>
+  <si>
+    <t>12.06.202663</t>
+  </si>
+  <si>
+    <t>12.06.202664</t>
+  </si>
+  <si>
+    <t>12.06.202665</t>
+  </si>
+  <si>
+    <t>12.06.202666</t>
+  </si>
+  <si>
+    <t>12.06.202667</t>
+  </si>
+  <si>
+    <t>12.06.202668</t>
+  </si>
+  <si>
+    <t>12.06.202669</t>
+  </si>
+  <si>
+    <t>12.06.202670</t>
+  </si>
+  <si>
+    <t>12.06.202671</t>
+  </si>
+  <si>
+    <t>12.06.202672</t>
+  </si>
+  <si>
+    <t>12.06.202673</t>
+  </si>
+  <si>
+    <t>12.06.202674</t>
+  </si>
+  <si>
+    <t>12.06.202675</t>
+  </si>
+  <si>
+    <t>12.06.202676</t>
+  </si>
+  <si>
+    <t>12.06.202677</t>
+  </si>
+  <si>
+    <t>12.06.202678</t>
+  </si>
+  <si>
+    <t>12.06.202679</t>
+  </si>
+  <si>
+    <t>12.06.202680</t>
+  </si>
+  <si>
+    <t>12.06.202681</t>
+  </si>
+  <si>
+    <t>12.06.202682</t>
+  </si>
+  <si>
+    <t>12.06.202683</t>
+  </si>
+  <si>
+    <t>12.06.202684</t>
+  </si>
+  <si>
+    <t>12.06.202685</t>
+  </si>
+  <si>
+    <t>12.06.202686</t>
+  </si>
+  <si>
+    <t>12.06.202687</t>
+  </si>
+  <si>
+    <t>12.06.202688</t>
+  </si>
+  <si>
+    <t>12.06.202689</t>
+  </si>
+  <si>
+    <t>12.06.202690</t>
+  </si>
+  <si>
+    <t>12.06.202691</t>
+  </si>
+  <si>
+    <t>12.06.202692</t>
+  </si>
+  <si>
+    <t>12.06.202693</t>
+  </si>
+  <si>
+    <t>12.06.202694</t>
+  </si>
+  <si>
+    <t>12.06.202695</t>
+  </si>
+  <si>
+    <t>12.06.202696</t>
   </si>
 </sst>
 </file>
@@ -988,13 +988,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2">
-        <v>506.237</v>
+        <v>304.164</v>
       </c>
       <c r="C2">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +1005,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46176.01041666666</v>
+        <v>46184.01041666666</v>
       </c>
       <c r="B3">
-        <v>482.218</v>
+        <v>296.175</v>
       </c>
       <c r="C3">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1022,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46176.02083333334</v>
+        <v>46184.02083333334</v>
       </c>
       <c r="B4">
-        <v>458.811</v>
+        <v>289.947</v>
       </c>
       <c r="C4">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1039,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46176.03125</v>
+        <v>46184.03125</v>
       </c>
       <c r="B5">
-        <v>433.199</v>
+        <v>283.344</v>
       </c>
       <c r="C5">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46176.04166666666</v>
+        <v>46184.04166666666</v>
       </c>
       <c r="B6">
-        <v>440.053</v>
+        <v>271.068</v>
       </c>
       <c r="C6">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46176.05208333334</v>
+        <v>46184.05208333334</v>
       </c>
       <c r="B7">
-        <v>397.051</v>
+        <v>263.915</v>
       </c>
       <c r="C7">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1090,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46176.0625</v>
+        <v>46184.0625</v>
       </c>
       <c r="B8">
-        <v>359.298</v>
+        <v>259.375</v>
       </c>
       <c r="C8">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1107,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46176.07291666666</v>
+        <v>46184.07291666666</v>
       </c>
       <c r="B9">
-        <v>322.379</v>
+        <v>249.585</v>
       </c>
       <c r="C9">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1124,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46176.08333333334</v>
+        <v>46184.08333333334</v>
       </c>
       <c r="B10">
-        <v>315.47</v>
+        <v>240.685</v>
       </c>
       <c r="C10">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1141,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46176.09375</v>
+        <v>46184.09375</v>
       </c>
       <c r="B11">
-        <v>293.418</v>
+        <v>236.178</v>
       </c>
       <c r="C11">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46176.10416666666</v>
+        <v>46184.10416666666</v>
       </c>
       <c r="B12">
-        <v>275.588</v>
+        <v>231.565</v>
       </c>
       <c r="C12">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1175,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46176.11458333334</v>
+        <v>46184.11458333334</v>
       </c>
       <c r="B13">
-        <v>253.44</v>
+        <v>227.616</v>
       </c>
       <c r="C13">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46176.125</v>
+        <v>46184.125</v>
       </c>
       <c r="B14">
-        <v>235.122</v>
+        <v>222.289</v>
       </c>
       <c r="C14">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46176.13541666666</v>
+        <v>46184.13541666666</v>
       </c>
       <c r="B15">
-        <v>225.416</v>
+        <v>219.92</v>
       </c>
       <c r="C15">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46176.14583333334</v>
+        <v>46184.14583333334</v>
       </c>
       <c r="B16">
-        <v>213.319</v>
+        <v>219.032</v>
       </c>
       <c r="C16">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1243,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46176.15625</v>
+        <v>46184.15625</v>
       </c>
       <c r="B17">
-        <v>201.61</v>
+        <v>218.24</v>
       </c>
       <c r="C17">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46176.16666666666</v>
+        <v>46184.16666666666</v>
       </c>
       <c r="B18">
-        <v>185.821</v>
+        <v>215.198</v>
       </c>
       <c r="C18">
-        <v>148</v>
+        <v>66</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46176.17708333334</v>
+        <v>46184.17708333334</v>
       </c>
       <c r="B19">
-        <v>176.531</v>
+        <v>214.625</v>
       </c>
       <c r="C19">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46176.1875</v>
+        <v>46184.1875</v>
       </c>
       <c r="B20">
-        <v>166.472</v>
+        <v>218.137</v>
       </c>
       <c r="C20">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1311,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46176.19791666666</v>
+        <v>46184.19791666666</v>
       </c>
       <c r="B21">
-        <v>158.317</v>
+        <v>220.278</v>
       </c>
       <c r="C21">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1328,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46176.20833333334</v>
+        <v>46184.20833333334</v>
       </c>
       <c r="B22">
-        <v>149.194</v>
+        <v>216.401</v>
       </c>
       <c r="C22">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46176.21875</v>
+        <v>46184.21875</v>
       </c>
       <c r="B23">
-        <v>143.187</v>
+        <v>233.163</v>
       </c>
       <c r="C23">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1362,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46176.22916666666</v>
+        <v>46184.22916666666</v>
       </c>
       <c r="B24">
-        <v>135.599</v>
+        <v>239.651</v>
       </c>
       <c r="C24">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46176.23958333334</v>
+        <v>46184.23958333334</v>
       </c>
       <c r="B25">
-        <v>128.961</v>
+        <v>248.624</v>
       </c>
       <c r="C25">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46176.25</v>
+        <v>46184.25</v>
       </c>
       <c r="B26">
-        <v>114.24</v>
+        <v>251.695</v>
       </c>
       <c r="C26">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46176.26041666666</v>
+        <v>46184.26041666666</v>
       </c>
       <c r="B27">
-        <v>108.126</v>
+        <v>251.806</v>
       </c>
       <c r="C27">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46176.27083333334</v>
+        <v>46184.27083333334</v>
       </c>
       <c r="B28">
-        <v>104.276</v>
+        <v>254.844</v>
       </c>
       <c r="C28">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1447,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46176.28125</v>
+        <v>46184.28125</v>
       </c>
       <c r="B29">
-        <v>103.001</v>
+        <v>256.473</v>
       </c>
       <c r="C29">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46176.29166666666</v>
+        <v>46184.29166666666</v>
       </c>
       <c r="B30">
-        <v>105.169</v>
+        <v>268.411</v>
       </c>
       <c r="C30">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1481,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46176.30208333334</v>
+        <v>46184.30208333334</v>
       </c>
       <c r="B31">
-        <v>104.629</v>
+        <v>257.673</v>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46176.3125</v>
+        <v>46184.3125</v>
       </c>
       <c r="B32">
-        <v>106.448</v>
+        <v>245.403</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46176.32291666666</v>
+        <v>46184.32291666666</v>
       </c>
       <c r="B33">
-        <v>105.89</v>
+        <v>234.413</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46176.33333333334</v>
+        <v>46184.33333333334</v>
       </c>
       <c r="B34">
-        <v>104.555</v>
+        <v>230.953</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46176.34375</v>
+        <v>46184.34375</v>
       </c>
       <c r="B35">
-        <v>106.968</v>
+        <v>237.122</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46176.35416666666</v>
+        <v>46184.35416666666</v>
       </c>
       <c r="B36">
-        <v>105.514</v>
+        <v>188.809</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46176.36458333334</v>
+        <v>46184.36458333334</v>
       </c>
       <c r="B37">
-        <v>105.989</v>
+        <v>192.752</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46176.375</v>
+        <v>46184.375</v>
       </c>
       <c r="B38">
-        <v>112.314</v>
+        <v>202.683</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46176.38541666666</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="B39">
-        <v>114.048</v>
+        <v>215.166</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1634,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46176.39583333334</v>
+        <v>46184.39583333334</v>
       </c>
       <c r="B40">
-        <v>115.763</v>
+        <v>228.528</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1651,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46176.40625</v>
+        <v>46184.40625</v>
       </c>
       <c r="B41">
-        <v>117.868</v>
+        <v>241.602</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46176.41666666666</v>
+        <v>46184.41666666666</v>
       </c>
       <c r="B42">
-        <v>129.211</v>
+        <v>254.804</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1685,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46176.42708333334</v>
+        <v>46184.42708333334</v>
       </c>
       <c r="B43">
-        <v>133.885</v>
+        <v>272.677</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46176.4375</v>
+        <v>46184.4375</v>
       </c>
       <c r="B44">
-        <v>139.005</v>
+        <v>291.472</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46176.44791666666</v>
+        <v>46184.44791666666</v>
       </c>
       <c r="B45">
-        <v>144.313</v>
+        <v>312.756</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46176.45833333334</v>
+        <v>46184.45833333334</v>
       </c>
       <c r="B46">
-        <v>160.708</v>
+        <v>339.02</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46176.46875</v>
+        <v>46184.46875</v>
       </c>
       <c r="B47">
-        <v>168.678</v>
+        <v>365.599</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46176.47916666666</v>
+        <v>46184.47916666666</v>
       </c>
       <c r="B48">
-        <v>177.214</v>
+        <v>391.191</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46176.48958333334</v>
+        <v>46184.48958333334</v>
       </c>
       <c r="B49">
-        <v>185.968</v>
+        <v>413.696</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1804,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46176.5</v>
+        <v>46184.5</v>
       </c>
       <c r="B50">
-        <v>188.495</v>
+        <v>449.001</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46176.51041666666</v>
+        <v>46184.51041666666</v>
       </c>
       <c r="B51">
-        <v>196.124</v>
+        <v>469.895</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46176.52083333334</v>
+        <v>46184.52083333334</v>
       </c>
       <c r="B52">
-        <v>203.585</v>
+        <v>490.829</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46176.53125</v>
+        <v>46184.53125</v>
       </c>
       <c r="B53">
-        <v>210.698</v>
+        <v>512.216</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46176.54166666666</v>
+        <v>46184.54166666666</v>
       </c>
       <c r="B54">
-        <v>217.937</v>
+        <v>548.338</v>
       </c>
       <c r="C54">
-        <v>6</v>
+        <v>276</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46176.55208333334</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="B55">
-        <v>226.669</v>
+        <v>576.894</v>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>297</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46176.5625</v>
+        <v>46184.5625</v>
       </c>
       <c r="B56">
-        <v>234.936</v>
+        <v>605.405</v>
       </c>
       <c r="C56">
-        <v>24</v>
+        <v>316</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1923,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46176.57291666666</v>
+        <v>46184.57291666666</v>
       </c>
       <c r="B57">
-        <v>243.295</v>
+        <v>633.038</v>
       </c>
       <c r="C57">
-        <v>33</v>
+        <v>349</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46176.58333333334</v>
+        <v>46184.58333333334</v>
       </c>
       <c r="B58">
-        <v>250.349</v>
+        <v>680.976</v>
       </c>
       <c r="C58">
-        <v>47</v>
+        <v>395</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1957,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46176.59375</v>
+        <v>46184.59375</v>
       </c>
       <c r="B59">
-        <v>255.498</v>
+        <v>714.383</v>
       </c>
       <c r="C59">
-        <v>66</v>
+        <v>447</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46176.60416666666</v>
+        <v>46184.60416666666</v>
       </c>
       <c r="B60">
-        <v>260.762</v>
+        <v>748.169</v>
       </c>
       <c r="C60">
-        <v>73</v>
+        <v>504</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46176.61458333334</v>
+        <v>46184.61458333334</v>
       </c>
       <c r="B61">
-        <v>265.785</v>
+        <v>780.2569999999999</v>
       </c>
       <c r="C61">
-        <v>90</v>
+        <v>542</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +2008,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46176.625</v>
+        <v>46184.625</v>
       </c>
       <c r="B62">
-        <v>273.192</v>
+        <v>824.872</v>
       </c>
       <c r="C62">
-        <v>114</v>
+        <v>550</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2025,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46176.63541666666</v>
+        <v>46184.63541666666</v>
       </c>
       <c r="B63">
-        <v>281.313</v>
+        <v>847.1849999999999</v>
       </c>
       <c r="C63">
-        <v>126</v>
+        <v>510</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46176.64583333334</v>
+        <v>46184.64583333334</v>
       </c>
       <c r="B64">
-        <v>289.76</v>
+        <v>867.973</v>
       </c>
       <c r="C64">
-        <v>133</v>
+        <v>525</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46176.65625</v>
+        <v>46184.65625</v>
       </c>
       <c r="B65">
-        <v>298.07</v>
+        <v>888.471</v>
       </c>
       <c r="C65">
-        <v>141</v>
+        <v>533</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2076,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46176.66666666666</v>
+        <v>46184.66666666666</v>
       </c>
       <c r="B66">
-        <v>322.211</v>
+        <v>896.322</v>
       </c>
       <c r="C66">
-        <v>159</v>
+        <v>555</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2093,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46176.67708333334</v>
+        <v>46184.67708333334</v>
       </c>
       <c r="B67">
-        <v>333.294</v>
+        <v>899.116</v>
       </c>
       <c r="C67">
-        <v>196</v>
+        <v>600</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46176.6875</v>
+        <v>46184.6875</v>
       </c>
       <c r="B68">
-        <v>344.542</v>
+        <v>902.624</v>
       </c>
       <c r="C68">
-        <v>231</v>
+        <v>611</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46176.69791666666</v>
+        <v>46184.69791666666</v>
       </c>
       <c r="B69">
-        <v>355.767</v>
+        <v>904.947</v>
       </c>
       <c r="C69">
-        <v>267</v>
+        <v>612</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2144,13 +2144,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46176.70833333334</v>
+        <v>46184.70833333334</v>
       </c>
       <c r="B70">
-        <v>381.306</v>
+        <v>936.3099999999999</v>
       </c>
       <c r="C70">
-        <v>288</v>
+        <v>601</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46176.71875</v>
+        <v>46184.71875</v>
       </c>
       <c r="B71">
-        <v>402.276</v>
+        <v>931.438</v>
       </c>
       <c r="C71">
-        <v>295</v>
+        <v>623</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2178,13 +2178,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46176.72916666666</v>
+        <v>46184.72916666666</v>
       </c>
       <c r="B72">
-        <v>420.686</v>
+        <v>925.6319999999999</v>
       </c>
       <c r="C72">
-        <v>302</v>
+        <v>614</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2195,13 +2195,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46176.73958333334</v>
+        <v>46184.73958333334</v>
       </c>
       <c r="B73">
-        <v>439.531</v>
+        <v>920.958</v>
       </c>
       <c r="C73">
-        <v>309</v>
+        <v>613</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2212,13 +2212,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46176.75</v>
+        <v>46184.75</v>
       </c>
       <c r="B74">
-        <v>478.905</v>
+        <v>879.237</v>
       </c>
       <c r="C74">
-        <v>347</v>
+        <v>570</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46176.76041666666</v>
+        <v>46184.76041666666</v>
       </c>
       <c r="B75">
-        <v>497.362</v>
+        <v>873.848</v>
       </c>
       <c r="C75">
-        <v>397</v>
+        <v>578</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2246,13 +2246,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46176.77083333334</v>
+        <v>46184.77083333334</v>
       </c>
       <c r="B76">
-        <v>516.66</v>
+        <v>867.617</v>
       </c>
       <c r="C76">
-        <v>417</v>
+        <v>619</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2263,13 +2263,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46176.78125</v>
+        <v>46184.78125</v>
       </c>
       <c r="B77">
-        <v>538.093</v>
+        <v>863.269</v>
       </c>
       <c r="C77">
-        <v>415</v>
+        <v>708</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46176.79166666666</v>
+        <v>46184.79166666666</v>
       </c>
       <c r="B78">
-        <v>571.682</v>
+        <v>783.879</v>
       </c>
       <c r="C78">
-        <v>433</v>
+        <v>762</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46176.80208333334</v>
+        <v>46184.80208333334</v>
       </c>
       <c r="B79">
-        <v>602.39</v>
+        <v>796.9</v>
       </c>
       <c r="C79">
-        <v>465</v>
+        <v>857</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2314,13 +2314,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46176.8125</v>
+        <v>46184.8125</v>
       </c>
       <c r="B80">
-        <v>633.6079999999999</v>
+        <v>810.337</v>
       </c>
       <c r="C80">
-        <v>497</v>
+        <v>902</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46176.82291666666</v>
+        <v>46184.82291666666</v>
       </c>
       <c r="B81">
-        <v>664.222</v>
+        <v>821.698</v>
       </c>
       <c r="C81">
-        <v>520</v>
+        <v>920</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46176.83333333334</v>
+        <v>46184.83333333334</v>
       </c>
       <c r="B82">
-        <v>701.096</v>
+        <v>807.9109999999999</v>
       </c>
       <c r="C82">
-        <v>530</v>
+        <v>952</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46176.84375</v>
+        <v>46184.84375</v>
       </c>
       <c r="B83">
-        <v>719.1319999999999</v>
+        <v>806.4589999999999</v>
       </c>
       <c r="C83">
-        <v>537</v>
+        <v>1016</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2382,13 +2382,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46176.85416666666</v>
+        <v>46184.85416666666</v>
       </c>
       <c r="B84">
-        <v>737.6420000000001</v>
+        <v>804.912</v>
       </c>
       <c r="C84">
-        <v>524</v>
+        <v>1050</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46176.86458333334</v>
+        <v>46184.86458333334</v>
       </c>
       <c r="B85">
-        <v>755.994</v>
+        <v>802.6369999999999</v>
       </c>
       <c r="C85">
-        <v>502</v>
+        <v>1021</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46176.875</v>
+        <v>46184.875</v>
       </c>
       <c r="B86">
-        <v>777.736</v>
+        <v>806.769</v>
       </c>
       <c r="C86">
-        <v>487</v>
+        <v>1017</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2433,13 +2433,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46176.88541666666</v>
+        <v>46184.88541666666</v>
       </c>
       <c r="B87">
-        <v>783.054</v>
+        <v>796.4</v>
       </c>
       <c r="C87">
-        <v>470</v>
+        <v>990</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2450,13 +2450,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46176.89583333334</v>
+        <v>46184.89583333334</v>
       </c>
       <c r="B88">
-        <v>787.794</v>
+        <v>786.835</v>
       </c>
       <c r="C88">
-        <v>446</v>
+        <v>972</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46176.90625</v>
+        <v>46184.90625</v>
       </c>
       <c r="B89">
-        <v>794.101</v>
+        <v>774.966</v>
       </c>
       <c r="C89">
-        <v>440</v>
+        <v>943</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2484,13 +2484,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46176.91666666666</v>
+        <v>46184.91666666666</v>
       </c>
       <c r="B90">
-        <v>759.388</v>
+        <v>746.567</v>
       </c>
       <c r="C90">
-        <v>438</v>
+        <v>914</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2501,13 +2501,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46176.92708333334</v>
+        <v>46184.92708333334</v>
       </c>
       <c r="B91">
-        <v>765.044</v>
+        <v>733.268</v>
       </c>
       <c r="C91">
-        <v>439</v>
+        <v>855</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2518,13 +2518,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46176.9375</v>
+        <v>46184.9375</v>
       </c>
       <c r="B92">
-        <v>771.395</v>
+        <v>718.529</v>
       </c>
       <c r="C92">
-        <v>448</v>
+        <v>807</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2535,13 +2535,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46176.94791666666</v>
+        <v>46184.94791666666</v>
       </c>
       <c r="B93">
-        <v>775.663</v>
+        <v>706.04</v>
       </c>
       <c r="C93">
-        <v>465</v>
+        <v>751</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46176.95833333334</v>
+        <v>46184.95833333334</v>
       </c>
       <c r="B94">
-        <v>701.3339999999999</v>
+        <v>742.333</v>
       </c>
       <c r="C94">
-        <v>481</v>
+        <v>696</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2569,13 +2569,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46176.96875</v>
+        <v>46184.96875</v>
       </c>
       <c r="B95">
-        <v>695.2859999999999</v>
+        <v>731.263</v>
       </c>
       <c r="C95">
-        <v>514</v>
+        <v>670</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46176.97916666666</v>
+        <v>46184.97916666666</v>
       </c>
       <c r="B96">
-        <v>695.04</v>
+        <v>720.138</v>
       </c>
       <c r="C96">
-        <v>522</v>
+        <v>659</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2603,13 +2603,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46176.98958333334</v>
+        <v>46184.98958333334</v>
       </c>
       <c r="B97">
-        <v>696.341</v>
+        <v>708.011</v>
       </c>
       <c r="C97">
-        <v>528</v>
+        <v>639</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2620,13 +2620,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B98">
-        <v>573.957</v>
+        <v>703.268</v>
       </c>
       <c r="C98">
-        <v>544</v>
+        <v>640</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2637,13 +2637,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46177.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B99">
-        <v>580.322</v>
+        <v>691.595</v>
       </c>
       <c r="C99">
-        <v>567</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46177.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B100">
-        <v>586.721</v>
+        <v>672.953</v>
       </c>
       <c r="C100">
-        <v>576</v>
+        <v>635</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2671,13 +2671,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46177.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B101">
-        <v>593.133</v>
+        <v>667.522</v>
       </c>
       <c r="C101">
-        <v>572</v>
+        <v>634</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2688,13 +2688,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46177.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B102">
-        <v>580.388</v>
+        <v>622.746</v>
       </c>
       <c r="C102">
-        <v>565</v>
+        <v>605</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46177.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B103">
-        <v>582.825</v>
+        <v>603.11</v>
       </c>
       <c r="C103">
-        <v>561</v>
+        <v>607</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46177.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B104">
-        <v>591.736</v>
+        <v>584.78</v>
       </c>
       <c r="C104">
-        <v>573</v>
+        <v>619</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2739,13 +2739,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46177.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B105">
-        <v>591.377</v>
+        <v>581.83</v>
       </c>
       <c r="C105">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46177.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B106">
-        <v>579.801</v>
+        <v>556.008</v>
       </c>
       <c r="C106">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2773,13 +2773,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46177.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B107">
-        <v>568.703</v>
+        <v>536.2859999999999</v>
       </c>
       <c r="C107">
-        <v>544</v>
+        <v>588</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2790,13 +2790,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46177.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B108">
-        <v>577.098</v>
+        <v>513.354</v>
       </c>
       <c r="C108">
-        <v>517</v>
+        <v>570</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46177.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B109">
-        <v>564.994</v>
+        <v>495.133</v>
       </c>
       <c r="C109">
-        <v>505</v>
+        <v>540</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46177.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B110">
-        <v>547.073</v>
+        <v>463.779</v>
       </c>
       <c r="C110">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46177.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B111">
-        <v>532.958</v>
+        <v>451.973</v>
       </c>
       <c r="C111">
-        <v>486</v>
+        <v>517</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2858,13 +2858,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46177.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B112">
-        <v>519.7859999999999</v>
+        <v>441.703</v>
       </c>
       <c r="C112">
-        <v>467</v>
+        <v>516</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2875,13 +2875,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46177.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B113">
-        <v>506.617</v>
+        <v>422.315</v>
       </c>
       <c r="C113">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2892,13 +2892,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46177.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B114">
-        <v>505.913</v>
+        <v>388.295</v>
       </c>
       <c r="C114">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46177.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B115">
-        <v>501.362</v>
+        <v>373.879</v>
       </c>
       <c r="C115">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2926,13 +2926,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46177.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B116">
-        <v>493.364</v>
+        <v>376.052</v>
       </c>
       <c r="C116">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2943,13 +2943,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46177.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B117">
-        <v>491.132</v>
+        <v>363.785</v>
       </c>
       <c r="C117">
-        <v>383</v>
+        <v>452</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46177.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B118">
-        <v>494.939</v>
+        <v>346.099</v>
       </c>
       <c r="C118">
-        <v>390</v>
+        <v>446</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46177.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B119">
-        <v>489.744</v>
+        <v>334.848</v>
       </c>
       <c r="C119">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2994,13 +2994,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46177.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B120">
-        <v>481.944</v>
+        <v>326.408</v>
       </c>
       <c r="C120">
-        <v>443</v>
+        <v>324</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3011,13 +3011,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46177.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B121">
-        <v>477.853</v>
+        <v>322.237</v>
       </c>
       <c r="C121">
-        <v>470</v>
+        <v>326</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3028,13 +3028,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46177.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B122">
-        <v>490.004</v>
+        <v>327.94</v>
       </c>
       <c r="C122">
-        <v>502</v>
+        <v>324</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3045,13 +3045,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46177.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B123">
-        <v>483.749</v>
+        <v>311.471</v>
       </c>
       <c r="C123">
-        <v>501</v>
+        <v>332</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46177.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B124">
-        <v>483.905</v>
+        <v>301.59</v>
       </c>
       <c r="C124">
-        <v>485</v>
+        <v>363</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46177.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B125">
-        <v>483.233</v>
+        <v>292.085</v>
       </c>
       <c r="C125">
-        <v>488</v>
+        <v>410</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46177.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B126">
-        <v>480.023</v>
+        <v>277.456</v>
       </c>
       <c r="C126">
-        <v>521</v>
+        <v>445</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46177.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B127">
-        <v>494.665</v>
+        <v>269.403</v>
       </c>
       <c r="C127">
-        <v>540</v>
+        <v>460</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3130,13 +3130,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46177.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B128">
-        <v>499.05</v>
+        <v>263.254</v>
       </c>
       <c r="C128">
-        <v>563</v>
+        <v>524</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3147,13 +3147,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46177.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B129">
-        <v>510.486</v>
+        <v>258.446</v>
       </c>
       <c r="C129">
-        <v>593</v>
+        <v>556</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46177.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B130">
-        <v>553.504</v>
+        <v>244.041</v>
       </c>
       <c r="C130">
-        <v>616</v>
+        <v>585</v>
       </c>
       <c r="D130">
         <v>33</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46177.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B131">
-        <v>576.552</v>
+        <v>250.211</v>
       </c>
       <c r="C131">
-        <v>663</v>
+        <v>626</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3198,13 +3198,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46177.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B132">
-        <v>590.276</v>
+        <v>269.267</v>
       </c>
       <c r="C132">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46177.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B133">
-        <v>607.206</v>
+        <v>274.716</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3232,13 +3232,13 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46177.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B134">
-        <v>645.242</v>
+        <v>330.354</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="D134">
         <v>37</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46177.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B135">
-        <v>662.793</v>
+        <v>340.926</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46177.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B136">
-        <v>680.601</v>
+        <v>350.881</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46177.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B137">
-        <v>699.21</v>
+        <v>360.345</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46177.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B138">
-        <v>734.557</v>
+        <v>332.263</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3317,13 +3317,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46177.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B139">
-        <v>754.569</v>
+        <v>350.576</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3334,13 +3334,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46177.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B140">
-        <v>774.042</v>
+        <v>369.884</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46177.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B141">
-        <v>794.173</v>
+        <v>390.023</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="D141">
         <v>44</v>
@@ -3368,13 +3368,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46177.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B142">
-        <v>800.2140000000001</v>
+        <v>416.32</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="D142">
         <v>45</v>
@@ -3385,13 +3385,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46177.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B143">
-        <v>811.231</v>
+        <v>442.182</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="D143">
         <v>46</v>
@@ -3402,13 +3402,13 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46177.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B144">
-        <v>822.2140000000001</v>
+        <v>467.256</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>763</v>
       </c>
       <c r="D144">
         <v>47</v>
@@ -3419,13 +3419,13 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46177.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B145">
-        <v>832.716</v>
+        <v>492.503</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="D145">
         <v>48</v>
@@ -3436,13 +3436,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46177.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B146">
-        <v>830.189</v>
+        <v>583.2670000000001</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>807</v>
       </c>
       <c r="D146">
         <v>49</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46177.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B147">
-        <v>826.351</v>
+        <v>620.328</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="D147">
         <v>50</v>
@@ -3470,13 +3470,13 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46177.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B148">
-        <v>822.903</v>
+        <v>656.048</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>887</v>
       </c>
       <c r="D148">
         <v>51</v>
@@ -3487,13 +3487,13 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46177.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B149">
-        <v>819.444</v>
+        <v>695.883</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>943</v>
       </c>
       <c r="D149">
         <v>52</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46177.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B150">
-        <v>817.314</v>
+        <v>756.11</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -3521,10 +3521,10 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46177.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B151">
-        <v>813.107</v>
+        <v>802.866</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46177.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B152">
-        <v>808.92</v>
+        <v>849.521</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46177.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B153">
-        <v>803.784</v>
+        <v>896.886</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46177.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B154">
-        <v>802.5119999999999</v>
+        <v>991.41</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46177.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B155">
-        <v>792.671</v>
+        <v>1025.834</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46177.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B156">
-        <v>783.497</v>
+        <v>1058.283</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -3623,10 +3623,10 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46177.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B157">
-        <v>774.096</v>
+        <v>1092.029</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46177.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B158">
-        <v>695.598</v>
+        <v>1147.673</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46177.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B159">
-        <v>685.323</v>
+        <v>1188.13</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46177.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B160">
-        <v>674.674</v>
+        <v>1226.492</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3691,10 +3691,10 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46177.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B161">
-        <v>664.551</v>
+        <v>1262.901</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3708,10 +3708,10 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46177.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B162">
-        <v>639.171</v>
+        <v>1230.626</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46177.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B163">
-        <v>617.861</v>
+        <v>1268.032</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46177.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B164">
-        <v>597.2329999999999</v>
+        <v>1307.478</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46177.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B165">
-        <v>576.429</v>
+        <v>1345.105</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46177.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B166">
-        <v>547.366</v>
+        <v>1384.322</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46177.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B167">
-        <v>530.425</v>
+        <v>1406.188</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46177.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B168">
-        <v>513.706</v>
+        <v>1428.982</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3827,10 +3827,10 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46177.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B169">
-        <v>496.927</v>
+        <v>1452.674</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46177.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B170">
-        <v>478.039</v>
+        <v>1479.041</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46177.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B171">
-        <v>467.691</v>
+        <v>1494.595</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46177.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B172">
-        <v>456.794</v>
+        <v>1509.484</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46177.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B173">
-        <v>446.479</v>
+        <v>1524.774</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46177.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B174">
-        <v>440.241</v>
+        <v>1566.269</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46177.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B175">
-        <v>440.838</v>
+        <v>1587.253</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46177.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B176">
-        <v>443.81</v>
+        <v>1606.463</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46177.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B177">
-        <v>445.481</v>
+        <v>1626.694</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46177.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B178">
-        <v>454.23</v>
+        <v>1580.59</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3997,10 +3997,10 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46177.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B179">
-        <v>456.266</v>
+        <v>1601.322</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -4014,10 +4014,10 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46177.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B180">
-        <v>458.788</v>
+        <v>1618.817</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46177.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B181">
-        <v>459.012</v>
+        <v>1636.85</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46177.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B182">
-        <v>454.972</v>
+        <v>1659.634</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46177.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B183">
-        <v>447.289</v>
+        <v>1671.946</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46177.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B184">
-        <v>438.961</v>
+        <v>1685.606</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4099,10 +4099,10 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46177.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B185">
-        <v>430.47</v>
+        <v>1696.322</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46177.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B186">
-        <v>416.252</v>
+        <v>1701.162</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46177.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B187">
-        <v>409.697</v>
+        <v>1705.016</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46177.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B188">
-        <v>402.893</v>
+        <v>1707.337</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46177.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B189">
-        <v>397.423</v>
+        <v>1710.318</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46177.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46177.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46177.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46177.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Wind_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Wind_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,580 +31,568 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.06.20261</t>
-  </si>
-  <si>
-    <t>11.06.20262</t>
-  </si>
-  <si>
-    <t>11.06.20263</t>
-  </si>
-  <si>
-    <t>11.06.20264</t>
-  </si>
-  <si>
-    <t>11.06.20265</t>
-  </si>
-  <si>
-    <t>11.06.20266</t>
-  </si>
-  <si>
-    <t>11.06.20267</t>
-  </si>
-  <si>
-    <t>11.06.20268</t>
-  </si>
-  <si>
-    <t>11.06.20269</t>
-  </si>
-  <si>
-    <t>11.06.202610</t>
-  </si>
-  <si>
-    <t>11.06.202611</t>
-  </si>
-  <si>
-    <t>11.06.202612</t>
-  </si>
-  <si>
-    <t>11.06.202613</t>
-  </si>
-  <si>
-    <t>11.06.202614</t>
-  </si>
-  <si>
-    <t>11.06.202615</t>
-  </si>
-  <si>
-    <t>11.06.202616</t>
-  </si>
-  <si>
-    <t>11.06.202617</t>
-  </si>
-  <si>
-    <t>11.06.202618</t>
-  </si>
-  <si>
-    <t>11.06.202619</t>
-  </si>
-  <si>
-    <t>11.06.202620</t>
-  </si>
-  <si>
-    <t>11.06.202621</t>
-  </si>
-  <si>
-    <t>11.06.202622</t>
-  </si>
-  <si>
-    <t>11.06.202623</t>
-  </si>
-  <si>
-    <t>11.06.202624</t>
-  </si>
-  <si>
-    <t>11.06.202625</t>
-  </si>
-  <si>
-    <t>11.06.202626</t>
-  </si>
-  <si>
-    <t>11.06.202627</t>
-  </si>
-  <si>
-    <t>11.06.202628</t>
-  </si>
-  <si>
-    <t>11.06.202629</t>
-  </si>
-  <si>
-    <t>11.06.202630</t>
-  </si>
-  <si>
-    <t>11.06.202631</t>
-  </si>
-  <si>
-    <t>11.06.202632</t>
-  </si>
-  <si>
-    <t>11.06.202633</t>
-  </si>
-  <si>
-    <t>11.06.202634</t>
-  </si>
-  <si>
-    <t>11.06.202635</t>
-  </si>
-  <si>
-    <t>11.06.202636</t>
-  </si>
-  <si>
-    <t>11.06.202637</t>
-  </si>
-  <si>
-    <t>11.06.202638</t>
-  </si>
-  <si>
-    <t>11.06.202639</t>
-  </si>
-  <si>
-    <t>11.06.202640</t>
-  </si>
-  <si>
-    <t>11.06.202641</t>
-  </si>
-  <si>
-    <t>11.06.202642</t>
-  </si>
-  <si>
-    <t>11.06.202643</t>
-  </si>
-  <si>
-    <t>11.06.202644</t>
-  </si>
-  <si>
-    <t>11.06.202645</t>
-  </si>
-  <si>
-    <t>11.06.202646</t>
-  </si>
-  <si>
-    <t>11.06.202647</t>
-  </si>
-  <si>
-    <t>11.06.202648</t>
-  </si>
-  <si>
-    <t>11.06.202649</t>
-  </si>
-  <si>
-    <t>11.06.202650</t>
-  </si>
-  <si>
-    <t>11.06.202651</t>
-  </si>
-  <si>
-    <t>11.06.202652</t>
-  </si>
-  <si>
-    <t>11.06.202653</t>
-  </si>
-  <si>
-    <t>11.06.202654</t>
-  </si>
-  <si>
-    <t>11.06.202655</t>
-  </si>
-  <si>
-    <t>11.06.202656</t>
-  </si>
-  <si>
-    <t>11.06.202657</t>
-  </si>
-  <si>
-    <t>11.06.202658</t>
-  </si>
-  <si>
-    <t>11.06.202659</t>
-  </si>
-  <si>
-    <t>11.06.202660</t>
-  </si>
-  <si>
-    <t>11.06.202661</t>
-  </si>
-  <si>
-    <t>11.06.202662</t>
-  </si>
-  <si>
-    <t>11.06.202663</t>
-  </si>
-  <si>
-    <t>11.06.202664</t>
-  </si>
-  <si>
-    <t>11.06.202665</t>
-  </si>
-  <si>
-    <t>11.06.202666</t>
-  </si>
-  <si>
-    <t>11.06.202667</t>
-  </si>
-  <si>
-    <t>11.06.202668</t>
-  </si>
-  <si>
-    <t>11.06.202669</t>
-  </si>
-  <si>
-    <t>11.06.202670</t>
-  </si>
-  <si>
-    <t>11.06.202671</t>
-  </si>
-  <si>
-    <t>11.06.202672</t>
-  </si>
-  <si>
-    <t>11.06.202673</t>
-  </si>
-  <si>
-    <t>11.06.202674</t>
-  </si>
-  <si>
-    <t>11.06.202675</t>
-  </si>
-  <si>
-    <t>11.06.202676</t>
-  </si>
-  <si>
-    <t>11.06.202677</t>
-  </si>
-  <si>
-    <t>11.06.202678</t>
-  </si>
-  <si>
-    <t>11.06.202679</t>
-  </si>
-  <si>
-    <t>11.06.202680</t>
-  </si>
-  <si>
-    <t>11.06.202681</t>
-  </si>
-  <si>
-    <t>11.06.202682</t>
-  </si>
-  <si>
-    <t>11.06.202683</t>
-  </si>
-  <si>
-    <t>11.06.202684</t>
-  </si>
-  <si>
-    <t>11.06.202685</t>
-  </si>
-  <si>
-    <t>11.06.202686</t>
-  </si>
-  <si>
-    <t>11.06.202687</t>
-  </si>
-  <si>
-    <t>11.06.202688</t>
-  </si>
-  <si>
-    <t>11.06.202689</t>
-  </si>
-  <si>
-    <t>11.06.202690</t>
-  </si>
-  <si>
-    <t>11.06.202691</t>
-  </si>
-  <si>
-    <t>11.06.202692</t>
-  </si>
-  <si>
-    <t>11.06.202693</t>
-  </si>
-  <si>
-    <t>11.06.202694</t>
-  </si>
-  <si>
-    <t>11.06.202695</t>
-  </si>
-  <si>
-    <t>11.06.202696</t>
-  </si>
-  <si>
-    <t>12.06.20261</t>
-  </si>
-  <si>
-    <t>12.06.20262</t>
-  </si>
-  <si>
-    <t>12.06.20263</t>
-  </si>
-  <si>
-    <t>12.06.20264</t>
-  </si>
-  <si>
-    <t>12.06.20265</t>
-  </si>
-  <si>
-    <t>12.06.20266</t>
-  </si>
-  <si>
-    <t>12.06.20267</t>
-  </si>
-  <si>
-    <t>12.06.20268</t>
-  </si>
-  <si>
-    <t>12.06.20269</t>
-  </si>
-  <si>
-    <t>12.06.202610</t>
-  </si>
-  <si>
-    <t>12.06.202611</t>
-  </si>
-  <si>
-    <t>12.06.202612</t>
-  </si>
-  <si>
-    <t>12.06.202613</t>
-  </si>
-  <si>
-    <t>12.06.202614</t>
-  </si>
-  <si>
-    <t>12.06.202615</t>
-  </si>
-  <si>
-    <t>12.06.202616</t>
-  </si>
-  <si>
-    <t>12.06.202617</t>
-  </si>
-  <si>
-    <t>12.06.202618</t>
-  </si>
-  <si>
-    <t>12.06.202619</t>
-  </si>
-  <si>
-    <t>12.06.202620</t>
-  </si>
-  <si>
-    <t>12.06.202621</t>
-  </si>
-  <si>
-    <t>12.06.202622</t>
-  </si>
-  <si>
-    <t>12.06.202623</t>
-  </si>
-  <si>
-    <t>12.06.202624</t>
-  </si>
-  <si>
-    <t>12.06.202625</t>
-  </si>
-  <si>
-    <t>12.06.202626</t>
-  </si>
-  <si>
-    <t>12.06.202627</t>
-  </si>
-  <si>
-    <t>12.06.202628</t>
-  </si>
-  <si>
-    <t>12.06.202629</t>
-  </si>
-  <si>
-    <t>12.06.202630</t>
-  </si>
-  <si>
-    <t>12.06.202631</t>
-  </si>
-  <si>
-    <t>12.06.202632</t>
-  </si>
-  <si>
-    <t>12.06.202633</t>
-  </si>
-  <si>
-    <t>12.06.202634</t>
-  </si>
-  <si>
-    <t>12.06.202635</t>
-  </si>
-  <si>
-    <t>12.06.202636</t>
-  </si>
-  <si>
-    <t>12.06.202637</t>
-  </si>
-  <si>
-    <t>12.06.202638</t>
-  </si>
-  <si>
-    <t>12.06.202639</t>
-  </si>
-  <si>
-    <t>12.06.202640</t>
-  </si>
-  <si>
-    <t>12.06.202641</t>
-  </si>
-  <si>
-    <t>12.06.202642</t>
-  </si>
-  <si>
-    <t>12.06.202643</t>
-  </si>
-  <si>
-    <t>12.06.202644</t>
-  </si>
-  <si>
-    <t>12.06.202645</t>
-  </si>
-  <si>
-    <t>12.06.202646</t>
-  </si>
-  <si>
-    <t>12.06.202647</t>
-  </si>
-  <si>
-    <t>12.06.202648</t>
-  </si>
-  <si>
-    <t>12.06.202649</t>
-  </si>
-  <si>
-    <t>12.06.202650</t>
-  </si>
-  <si>
-    <t>12.06.202651</t>
-  </si>
-  <si>
-    <t>12.06.202652</t>
-  </si>
-  <si>
-    <t>12.06.202653</t>
-  </si>
-  <si>
-    <t>12.06.202654</t>
-  </si>
-  <si>
-    <t>12.06.202655</t>
-  </si>
-  <si>
-    <t>12.06.202656</t>
-  </si>
-  <si>
-    <t>12.06.202657</t>
-  </si>
-  <si>
-    <t>12.06.202658</t>
-  </si>
-  <si>
-    <t>12.06.202659</t>
-  </si>
-  <si>
-    <t>12.06.202660</t>
-  </si>
-  <si>
-    <t>12.06.202661</t>
-  </si>
-  <si>
-    <t>12.06.202662</t>
-  </si>
-  <si>
-    <t>12.06.202663</t>
-  </si>
-  <si>
-    <t>12.06.202664</t>
-  </si>
-  <si>
-    <t>12.06.202665</t>
-  </si>
-  <si>
-    <t>12.06.202666</t>
-  </si>
-  <si>
-    <t>12.06.202667</t>
-  </si>
-  <si>
-    <t>12.06.202668</t>
-  </si>
-  <si>
-    <t>12.06.202669</t>
-  </si>
-  <si>
-    <t>12.06.202670</t>
-  </si>
-  <si>
-    <t>12.06.202671</t>
-  </si>
-  <si>
-    <t>12.06.202672</t>
-  </si>
-  <si>
-    <t>12.06.202673</t>
-  </si>
-  <si>
-    <t>12.06.202674</t>
-  </si>
-  <si>
-    <t>12.06.202675</t>
-  </si>
-  <si>
-    <t>12.06.202676</t>
-  </si>
-  <si>
-    <t>12.06.202677</t>
-  </si>
-  <si>
-    <t>12.06.202678</t>
-  </si>
-  <si>
-    <t>12.06.202679</t>
-  </si>
-  <si>
-    <t>12.06.202680</t>
-  </si>
-  <si>
-    <t>12.06.202681</t>
-  </si>
-  <si>
-    <t>12.06.202682</t>
-  </si>
-  <si>
-    <t>12.06.202683</t>
-  </si>
-  <si>
-    <t>12.06.202684</t>
-  </si>
-  <si>
-    <t>12.06.202685</t>
-  </si>
-  <si>
-    <t>12.06.202686</t>
-  </si>
-  <si>
-    <t>12.06.202687</t>
-  </si>
-  <si>
-    <t>12.06.202688</t>
-  </si>
-  <si>
-    <t>12.06.202689</t>
-  </si>
-  <si>
-    <t>12.06.202690</t>
-  </si>
-  <si>
-    <t>12.06.202691</t>
-  </si>
-  <si>
-    <t>12.06.202692</t>
-  </si>
-  <si>
-    <t>12.06.202693</t>
-  </si>
-  <si>
-    <t>12.06.202694</t>
-  </si>
-  <si>
-    <t>12.06.202695</t>
-  </si>
-  <si>
-    <t>12.06.202696</t>
+    <t>09.07.20261</t>
+  </si>
+  <si>
+    <t>09.07.20262</t>
+  </si>
+  <si>
+    <t>09.07.20263</t>
+  </si>
+  <si>
+    <t>09.07.20264</t>
+  </si>
+  <si>
+    <t>09.07.20265</t>
+  </si>
+  <si>
+    <t>09.07.20266</t>
+  </si>
+  <si>
+    <t>09.07.20267</t>
+  </si>
+  <si>
+    <t>09.07.20268</t>
+  </si>
+  <si>
+    <t>09.07.20269</t>
+  </si>
+  <si>
+    <t>09.07.202610</t>
+  </si>
+  <si>
+    <t>09.07.202611</t>
+  </si>
+  <si>
+    <t>09.07.202612</t>
+  </si>
+  <si>
+    <t>09.07.202613</t>
+  </si>
+  <si>
+    <t>09.07.202614</t>
+  </si>
+  <si>
+    <t>09.07.202615</t>
+  </si>
+  <si>
+    <t>09.07.202616</t>
+  </si>
+  <si>
+    <t>09.07.202617</t>
+  </si>
+  <si>
+    <t>09.07.202618</t>
+  </si>
+  <si>
+    <t>09.07.202619</t>
+  </si>
+  <si>
+    <t>09.07.202620</t>
+  </si>
+  <si>
+    <t>09.07.202621</t>
+  </si>
+  <si>
+    <t>09.07.202622</t>
+  </si>
+  <si>
+    <t>09.07.202623</t>
+  </si>
+  <si>
+    <t>09.07.202624</t>
+  </si>
+  <si>
+    <t>09.07.202625</t>
+  </si>
+  <si>
+    <t>09.07.202626</t>
+  </si>
+  <si>
+    <t>09.07.202627</t>
+  </si>
+  <si>
+    <t>09.07.202628</t>
+  </si>
+  <si>
+    <t>09.07.202629</t>
+  </si>
+  <si>
+    <t>09.07.202630</t>
+  </si>
+  <si>
+    <t>09.07.202631</t>
+  </si>
+  <si>
+    <t>09.07.202632</t>
+  </si>
+  <si>
+    <t>09.07.202633</t>
+  </si>
+  <si>
+    <t>09.07.202634</t>
+  </si>
+  <si>
+    <t>09.07.202635</t>
+  </si>
+  <si>
+    <t>09.07.202636</t>
+  </si>
+  <si>
+    <t>09.07.202637</t>
+  </si>
+  <si>
+    <t>09.07.202638</t>
+  </si>
+  <si>
+    <t>09.07.202639</t>
+  </si>
+  <si>
+    <t>09.07.202640</t>
+  </si>
+  <si>
+    <t>09.07.202641</t>
+  </si>
+  <si>
+    <t>09.07.202642</t>
+  </si>
+  <si>
+    <t>09.07.202643</t>
+  </si>
+  <si>
+    <t>09.07.202644</t>
+  </si>
+  <si>
+    <t>09.07.202645</t>
+  </si>
+  <si>
+    <t>09.07.202646</t>
+  </si>
+  <si>
+    <t>09.07.202647</t>
+  </si>
+  <si>
+    <t>09.07.202648</t>
+  </si>
+  <si>
+    <t>09.07.202649</t>
+  </si>
+  <si>
+    <t>09.07.202650</t>
+  </si>
+  <si>
+    <t>09.07.202651</t>
+  </si>
+  <si>
+    <t>09.07.202652</t>
+  </si>
+  <si>
+    <t>09.07.202653</t>
+  </si>
+  <si>
+    <t>09.07.202654</t>
+  </si>
+  <si>
+    <t>09.07.202655</t>
+  </si>
+  <si>
+    <t>09.07.202656</t>
+  </si>
+  <si>
+    <t>09.07.202657</t>
+  </si>
+  <si>
+    <t>09.07.202658</t>
+  </si>
+  <si>
+    <t>09.07.202659</t>
+  </si>
+  <si>
+    <t>09.07.202660</t>
+  </si>
+  <si>
+    <t>09.07.202661</t>
+  </si>
+  <si>
+    <t>09.07.202662</t>
+  </si>
+  <si>
+    <t>09.07.202663</t>
+  </si>
+  <si>
+    <t>09.07.202664</t>
+  </si>
+  <si>
+    <t>09.07.202665</t>
+  </si>
+  <si>
+    <t>09.07.202666</t>
+  </si>
+  <si>
+    <t>09.07.202667</t>
+  </si>
+  <si>
+    <t>09.07.202668</t>
+  </si>
+  <si>
+    <t>09.07.202669</t>
+  </si>
+  <si>
+    <t>09.07.202670</t>
+  </si>
+  <si>
+    <t>09.07.202671</t>
+  </si>
+  <si>
+    <t>09.07.202672</t>
+  </si>
+  <si>
+    <t>09.07.202673</t>
+  </si>
+  <si>
+    <t>09.07.202674</t>
+  </si>
+  <si>
+    <t>09.07.202675</t>
+  </si>
+  <si>
+    <t>09.07.202676</t>
+  </si>
+  <si>
+    <t>09.07.202677</t>
+  </si>
+  <si>
+    <t>09.07.202678</t>
+  </si>
+  <si>
+    <t>09.07.202679</t>
+  </si>
+  <si>
+    <t>09.07.202680</t>
+  </si>
+  <si>
+    <t>09.07.202681</t>
+  </si>
+  <si>
+    <t>09.07.202682</t>
+  </si>
+  <si>
+    <t>09.07.202683</t>
+  </si>
+  <si>
+    <t>09.07.202684</t>
+  </si>
+  <si>
+    <t>09.07.202685</t>
+  </si>
+  <si>
+    <t>09.07.202686</t>
+  </si>
+  <si>
+    <t>09.07.202687</t>
+  </si>
+  <si>
+    <t>09.07.202688</t>
+  </si>
+  <si>
+    <t>09.07.202689</t>
+  </si>
+  <si>
+    <t>09.07.202690</t>
+  </si>
+  <si>
+    <t>09.07.202691</t>
+  </si>
+  <si>
+    <t>09.07.202692</t>
+  </si>
+  <si>
+    <t>09.07.202693</t>
+  </si>
+  <si>
+    <t>09.07.202694</t>
+  </si>
+  <si>
+    <t>09.07.202695</t>
+  </si>
+  <si>
+    <t>09.07.202696</t>
+  </si>
+  <si>
+    <t>10.07.20261</t>
+  </si>
+  <si>
+    <t>10.07.20262</t>
+  </si>
+  <si>
+    <t>10.07.20263</t>
+  </si>
+  <si>
+    <t>10.07.20264</t>
+  </si>
+  <si>
+    <t>10.07.20265</t>
+  </si>
+  <si>
+    <t>10.07.20266</t>
+  </si>
+  <si>
+    <t>10.07.20267</t>
+  </si>
+  <si>
+    <t>10.07.20268</t>
+  </si>
+  <si>
+    <t>10.07.20269</t>
+  </si>
+  <si>
+    <t>10.07.202610</t>
+  </si>
+  <si>
+    <t>10.07.202611</t>
+  </si>
+  <si>
+    <t>10.07.202612</t>
+  </si>
+  <si>
+    <t>10.07.202613</t>
+  </si>
+  <si>
+    <t>10.07.202614</t>
+  </si>
+  <si>
+    <t>10.07.202615</t>
+  </si>
+  <si>
+    <t>10.07.202616</t>
+  </si>
+  <si>
+    <t>10.07.202617</t>
+  </si>
+  <si>
+    <t>10.07.202618</t>
+  </si>
+  <si>
+    <t>10.07.202619</t>
+  </si>
+  <si>
+    <t>10.07.202620</t>
+  </si>
+  <si>
+    <t>10.07.202621</t>
+  </si>
+  <si>
+    <t>10.07.202622</t>
+  </si>
+  <si>
+    <t>10.07.202623</t>
+  </si>
+  <si>
+    <t>10.07.202624</t>
+  </si>
+  <si>
+    <t>10.07.202625</t>
+  </si>
+  <si>
+    <t>10.07.202626</t>
+  </si>
+  <si>
+    <t>10.07.202627</t>
+  </si>
+  <si>
+    <t>10.07.202628</t>
+  </si>
+  <si>
+    <t>10.07.202629</t>
+  </si>
+  <si>
+    <t>10.07.202630</t>
+  </si>
+  <si>
+    <t>10.07.202631</t>
+  </si>
+  <si>
+    <t>10.07.202632</t>
+  </si>
+  <si>
+    <t>10.07.202633</t>
+  </si>
+  <si>
+    <t>10.07.202634</t>
+  </si>
+  <si>
+    <t>10.07.202635</t>
+  </si>
+  <si>
+    <t>10.07.202636</t>
+  </si>
+  <si>
+    <t>10.07.202637</t>
+  </si>
+  <si>
+    <t>10.07.202638</t>
+  </si>
+  <si>
+    <t>10.07.202639</t>
+  </si>
+  <si>
+    <t>10.07.202640</t>
+  </si>
+  <si>
+    <t>10.07.202641</t>
+  </si>
+  <si>
+    <t>10.07.202642</t>
+  </si>
+  <si>
+    <t>10.07.202643</t>
+  </si>
+  <si>
+    <t>10.07.202644</t>
+  </si>
+  <si>
+    <t>10.07.202645</t>
+  </si>
+  <si>
+    <t>10.07.202646</t>
+  </si>
+  <si>
+    <t>10.07.202647</t>
+  </si>
+  <si>
+    <t>10.07.202648</t>
+  </si>
+  <si>
+    <t>10.07.202649</t>
+  </si>
+  <si>
+    <t>10.07.202650</t>
+  </si>
+  <si>
+    <t>10.07.202651</t>
+  </si>
+  <si>
+    <t>10.07.202652</t>
+  </si>
+  <si>
+    <t>10.07.202653</t>
+  </si>
+  <si>
+    <t>10.07.202654</t>
+  </si>
+  <si>
+    <t>10.07.202655</t>
+  </si>
+  <si>
+    <t>10.07.202656</t>
+  </si>
+  <si>
+    <t>10.07.202657</t>
+  </si>
+  <si>
+    <t>10.07.202658</t>
+  </si>
+  <si>
+    <t>10.07.202659</t>
+  </si>
+  <si>
+    <t>10.07.202660</t>
+  </si>
+  <si>
+    <t>10.07.202661</t>
+  </si>
+  <si>
+    <t>10.07.202662</t>
+  </si>
+  <si>
+    <t>10.07.202663</t>
+  </si>
+  <si>
+    <t>10.07.202664</t>
+  </si>
+  <si>
+    <t>10.07.202665</t>
+  </si>
+  <si>
+    <t>10.07.202666</t>
+  </si>
+  <si>
+    <t>10.07.202667</t>
+  </si>
+  <si>
+    <t>10.07.202668</t>
+  </si>
+  <si>
+    <t>10.07.202669</t>
+  </si>
+  <si>
+    <t>10.07.202670</t>
+  </si>
+  <si>
+    <t>10.07.202671</t>
+  </si>
+  <si>
+    <t>10.07.202672</t>
+  </si>
+  <si>
+    <t>10.07.202673</t>
+  </si>
+  <si>
+    <t>10.07.202674</t>
+  </si>
+  <si>
+    <t>10.07.202675</t>
+  </si>
+  <si>
+    <t>10.07.202676</t>
+  </si>
+  <si>
+    <t>10.07.202677</t>
+  </si>
+  <si>
+    <t>10.07.202678</t>
+  </si>
+  <si>
+    <t>10.07.202679</t>
+  </si>
+  <si>
+    <t>10.07.202680</t>
+  </si>
+  <si>
+    <t>10.07.202681</t>
+  </si>
+  <si>
+    <t>10.07.202682</t>
+  </si>
+  <si>
+    <t>10.07.202683</t>
+  </si>
+  <si>
+    <t>10.07.202684</t>
+  </si>
+  <si>
+    <t>10.07.202685</t>
+  </si>
+  <si>
+    <t>10.07.202686</t>
+  </si>
+  <si>
+    <t>10.07.202687</t>
+  </si>
+  <si>
+    <t>10.07.202688</t>
+  </si>
+  <si>
+    <t>10.07.202689</t>
+  </si>
+  <si>
+    <t>10.07.202690</t>
+  </si>
+  <si>
+    <t>10.07.202691</t>
+  </si>
+  <si>
+    <t>10.07.202692</t>
   </si>
 </sst>
 </file>
@@ -966,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -988,13 +976,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46184</v>
+        <v>46212</v>
       </c>
       <c r="B2">
-        <v>304.164</v>
+        <v>375.925</v>
       </c>
       <c r="C2">
-        <v>158</v>
+        <v>265</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1005,13 +993,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46184.01041666666</v>
+        <v>46212.01041666666</v>
       </c>
       <c r="B3">
-        <v>296.175</v>
+        <v>385.464</v>
       </c>
       <c r="C3">
-        <v>137</v>
+        <v>301</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1022,13 +1010,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46184.02083333334</v>
+        <v>46212.02083333334</v>
       </c>
       <c r="B4">
-        <v>289.947</v>
+        <v>387.673</v>
       </c>
       <c r="C4">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1039,13 +1027,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46184.03125</v>
+        <v>46212.03125</v>
       </c>
       <c r="B5">
-        <v>283.344</v>
+        <v>394.835</v>
       </c>
       <c r="C5">
-        <v>121</v>
+        <v>357</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1056,13 +1044,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46184.04166666666</v>
+        <v>46212.04166666666</v>
       </c>
       <c r="B6">
-        <v>271.068</v>
+        <v>434.103</v>
       </c>
       <c r="C6">
-        <v>112</v>
+        <v>450</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1073,13 +1061,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46184.05208333334</v>
+        <v>46212.05208333334</v>
       </c>
       <c r="B7">
-        <v>263.915</v>
+        <v>447.04</v>
       </c>
       <c r="C7">
-        <v>114</v>
+        <v>547</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1090,13 +1078,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46184.0625</v>
+        <v>46212.0625</v>
       </c>
       <c r="B8">
-        <v>259.375</v>
+        <v>458.686</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1107,13 +1095,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46184.07291666666</v>
+        <v>46212.07291666666</v>
       </c>
       <c r="B9">
-        <v>249.585</v>
+        <v>467.992</v>
       </c>
       <c r="C9">
-        <v>113</v>
+        <v>609</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1124,13 +1112,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46184.08333333334</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B10">
-        <v>240.685</v>
+        <v>504.782</v>
       </c>
       <c r="C10">
-        <v>112</v>
+        <v>607</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1141,13 +1129,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46184.09375</v>
+        <v>46212.09375</v>
       </c>
       <c r="B11">
-        <v>236.178</v>
+        <v>518.854</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1158,13 +1146,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46184.10416666666</v>
+        <v>46212.10416666666</v>
       </c>
       <c r="B12">
-        <v>231.565</v>
+        <v>530.929</v>
       </c>
       <c r="C12">
-        <v>105</v>
+        <v>702</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1175,13 +1163,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46184.11458333334</v>
+        <v>46212.11458333334</v>
       </c>
       <c r="B13">
-        <v>227.616</v>
+        <v>534.287</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>741</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1192,13 +1180,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46184.125</v>
+        <v>46212.125</v>
       </c>
       <c r="B14">
-        <v>222.289</v>
+        <v>591.0650000000001</v>
       </c>
       <c r="C14">
-        <v>104</v>
+        <v>774</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1209,13 +1197,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46184.13541666666</v>
+        <v>46212.13541666666</v>
       </c>
       <c r="B15">
-        <v>219.92</v>
+        <v>590.437</v>
       </c>
       <c r="C15">
-        <v>105</v>
+        <v>793</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1226,13 +1214,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46184.14583333334</v>
+        <v>46212.14583333334</v>
       </c>
       <c r="B16">
-        <v>219.032</v>
+        <v>591.345</v>
       </c>
       <c r="C16">
-        <v>92</v>
+        <v>810</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1243,13 +1231,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46184.15625</v>
+        <v>46212.15625</v>
       </c>
       <c r="B17">
-        <v>218.24</v>
+        <v>598.146</v>
       </c>
       <c r="C17">
-        <v>78</v>
+        <v>824</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1260,13 +1248,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46184.16666666666</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B18">
-        <v>215.198</v>
+        <v>653.026</v>
       </c>
       <c r="C18">
-        <v>66</v>
+        <v>885</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1277,13 +1265,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46184.17708333334</v>
+        <v>46212.17708333334</v>
       </c>
       <c r="B19">
-        <v>214.625</v>
+        <v>659.284</v>
       </c>
       <c r="C19">
-        <v>70</v>
+        <v>862</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1294,13 +1282,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46184.1875</v>
+        <v>46212.1875</v>
       </c>
       <c r="B20">
-        <v>218.137</v>
+        <v>662.063</v>
       </c>
       <c r="C20">
-        <v>79</v>
+        <v>823</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1311,13 +1299,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46184.19791666666</v>
+        <v>46212.19791666666</v>
       </c>
       <c r="B21">
-        <v>220.278</v>
+        <v>660.631</v>
       </c>
       <c r="C21">
-        <v>83</v>
+        <v>781</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1328,13 +1316,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46184.20833333334</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B22">
-        <v>216.401</v>
+        <v>652.5359999999999</v>
       </c>
       <c r="C22">
-        <v>81</v>
+        <v>751</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1345,13 +1333,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46184.21875</v>
+        <v>46212.21875</v>
       </c>
       <c r="B23">
-        <v>233.163</v>
+        <v>637.586</v>
       </c>
       <c r="C23">
-        <v>74</v>
+        <v>719</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1362,13 +1350,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46184.22916666666</v>
+        <v>46212.22916666666</v>
       </c>
       <c r="B24">
-        <v>239.651</v>
+        <v>619.3099999999999</v>
       </c>
       <c r="C24">
-        <v>80</v>
+        <v>696</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1379,13 +1367,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46184.23958333334</v>
+        <v>46212.23958333334</v>
       </c>
       <c r="B25">
-        <v>248.624</v>
+        <v>607.696</v>
       </c>
       <c r="C25">
-        <v>95</v>
+        <v>673</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1396,13 +1384,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46184.25</v>
+        <v>46212.25</v>
       </c>
       <c r="B26">
-        <v>251.695</v>
+        <v>600.59</v>
       </c>
       <c r="C26">
-        <v>110</v>
+        <v>623</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1413,13 +1401,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46184.26041666666</v>
+        <v>46212.26041666666</v>
       </c>
       <c r="B27">
-        <v>251.806</v>
+        <v>561.872</v>
       </c>
       <c r="C27">
-        <v>112</v>
+        <v>562</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1430,13 +1418,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46184.27083333334</v>
+        <v>46212.27083333334</v>
       </c>
       <c r="B28">
-        <v>254.844</v>
+        <v>528.174</v>
       </c>
       <c r="C28">
-        <v>123</v>
+        <v>481</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1447,13 +1435,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46184.28125</v>
+        <v>46212.28125</v>
       </c>
       <c r="B29">
-        <v>256.473</v>
+        <v>491.39</v>
       </c>
       <c r="C29">
-        <v>116</v>
+        <v>427</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1464,13 +1452,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46184.29166666666</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B30">
-        <v>268.411</v>
+        <v>464.975</v>
       </c>
       <c r="C30">
-        <v>86</v>
+        <v>400</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1481,13 +1469,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46184.30208333334</v>
+        <v>46212.30208333334</v>
       </c>
       <c r="B31">
-        <v>257.673</v>
+        <v>439.244</v>
       </c>
       <c r="C31">
-        <v>72</v>
+        <v>368</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1498,13 +1486,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46184.3125</v>
+        <v>46212.3125</v>
       </c>
       <c r="B32">
-        <v>245.403</v>
+        <v>416.287</v>
       </c>
       <c r="C32">
-        <v>62</v>
+        <v>350</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1515,13 +1503,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46184.32291666666</v>
+        <v>46212.32291666666</v>
       </c>
       <c r="B33">
-        <v>234.413</v>
+        <v>392.472</v>
       </c>
       <c r="C33">
-        <v>63</v>
+        <v>309</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1532,13 +1520,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46184.33333333334</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B34">
-        <v>230.953</v>
+        <v>373.742</v>
       </c>
       <c r="C34">
-        <v>55</v>
+        <v>291</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1549,13 +1537,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46184.34375</v>
+        <v>46212.34375</v>
       </c>
       <c r="B35">
-        <v>237.122</v>
+        <v>366.944</v>
       </c>
       <c r="C35">
-        <v>51</v>
+        <v>278</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1566,13 +1554,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46184.35416666666</v>
+        <v>46212.35416666666</v>
       </c>
       <c r="B36">
-        <v>188.809</v>
+        <v>367.788</v>
       </c>
       <c r="C36">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1583,13 +1571,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46184.36458333334</v>
+        <v>46212.36458333334</v>
       </c>
       <c r="B37">
-        <v>192.752</v>
+        <v>347.217</v>
       </c>
       <c r="C37">
-        <v>46</v>
+        <v>232</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1600,13 +1588,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46184.375</v>
+        <v>46212.375</v>
       </c>
       <c r="B38">
-        <v>202.683</v>
+        <v>326.899</v>
       </c>
       <c r="C38">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1617,13 +1605,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46184.38541666666</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="B39">
-        <v>215.166</v>
+        <v>318.91</v>
       </c>
       <c r="C39">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1634,13 +1622,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46184.39583333334</v>
+        <v>46212.39583333334</v>
       </c>
       <c r="B40">
-        <v>228.528</v>
+        <v>310.238</v>
       </c>
       <c r="C40">
-        <v>82</v>
+        <v>218</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1651,13 +1639,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46184.40625</v>
+        <v>46212.40625</v>
       </c>
       <c r="B41">
-        <v>241.602</v>
+        <v>302.25</v>
       </c>
       <c r="C41">
-        <v>107</v>
+        <v>206</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1668,13 +1656,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46184.41666666666</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B42">
-        <v>254.804</v>
+        <v>242.528</v>
       </c>
       <c r="C42">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1685,13 +1673,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46184.42708333334</v>
+        <v>46212.42708333334</v>
       </c>
       <c r="B43">
-        <v>272.677</v>
+        <v>237.83</v>
       </c>
       <c r="C43">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1702,13 +1690,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46184.4375</v>
+        <v>46212.4375</v>
       </c>
       <c r="B44">
-        <v>291.472</v>
+        <v>231.673</v>
       </c>
       <c r="C44">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1719,13 +1707,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46184.44791666666</v>
+        <v>46212.44791666666</v>
       </c>
       <c r="B45">
-        <v>312.756</v>
+        <v>225.34</v>
       </c>
       <c r="C45">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1736,13 +1724,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46184.45833333334</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B46">
-        <v>339.02</v>
+        <v>217.207</v>
       </c>
       <c r="C46">
-        <v>184</v>
+        <v>117</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1753,13 +1741,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46184.46875</v>
+        <v>46212.46875</v>
       </c>
       <c r="B47">
-        <v>365.599</v>
+        <v>212.452</v>
       </c>
       <c r="C47">
-        <v>177</v>
+        <v>92</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1770,13 +1758,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46184.47916666666</v>
+        <v>46212.47916666666</v>
       </c>
       <c r="B48">
-        <v>391.191</v>
+        <v>209.077</v>
       </c>
       <c r="C48">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1787,13 +1775,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46184.48958333334</v>
+        <v>46212.48958333334</v>
       </c>
       <c r="B49">
-        <v>413.696</v>
+        <v>204.096</v>
       </c>
       <c r="C49">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1804,13 +1792,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46184.5</v>
+        <v>46212.5</v>
       </c>
       <c r="B50">
-        <v>449.001</v>
+        <v>201.129</v>
       </c>
       <c r="C50">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1821,13 +1809,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46184.51041666666</v>
+        <v>46212.51041666666</v>
       </c>
       <c r="B51">
-        <v>469.895</v>
+        <v>200.026</v>
       </c>
       <c r="C51">
-        <v>182</v>
+        <v>61</v>
       </c>
       <c r="D51">
         <v>50</v>
@@ -1838,13 +1826,13 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46184.52083333334</v>
+        <v>46212.52083333334</v>
       </c>
       <c r="B52">
-        <v>490.829</v>
+        <v>198.762</v>
       </c>
       <c r="C52">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="D52">
         <v>51</v>
@@ -1855,13 +1843,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46184.53125</v>
+        <v>46212.53125</v>
       </c>
       <c r="B53">
-        <v>512.216</v>
+        <v>197.955</v>
       </c>
       <c r="C53">
-        <v>257</v>
+        <v>54</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -1872,13 +1860,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46184.54166666666</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B54">
-        <v>548.338</v>
+        <v>199.863</v>
       </c>
       <c r="C54">
-        <v>276</v>
+        <v>54</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1889,13 +1877,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46184.55208333334</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="B55">
-        <v>576.894</v>
+        <v>200.66</v>
       </c>
       <c r="C55">
-        <v>297</v>
+        <v>67</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1906,13 +1894,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46184.5625</v>
+        <v>46212.5625</v>
       </c>
       <c r="B56">
-        <v>605.405</v>
+        <v>201.078</v>
       </c>
       <c r="C56">
-        <v>316</v>
+        <v>68</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1923,13 +1911,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46184.57291666666</v>
+        <v>46212.57291666666</v>
       </c>
       <c r="B57">
-        <v>633.038</v>
+        <v>202.081</v>
       </c>
       <c r="C57">
-        <v>349</v>
+        <v>75</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1940,13 +1928,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46184.58333333334</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B58">
-        <v>680.976</v>
+        <v>205.193</v>
       </c>
       <c r="C58">
-        <v>395</v>
+        <v>75</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1957,13 +1945,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46184.59375</v>
+        <v>46212.59375</v>
       </c>
       <c r="B59">
-        <v>714.383</v>
+        <v>207.42</v>
       </c>
       <c r="C59">
-        <v>447</v>
+        <v>119</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1974,13 +1962,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46184.60416666666</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="B60">
-        <v>748.169</v>
+        <v>210.04</v>
       </c>
       <c r="C60">
-        <v>504</v>
+        <v>228</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1991,13 +1979,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46184.61458333334</v>
+        <v>46212.61458333334</v>
       </c>
       <c r="B61">
-        <v>780.2569999999999</v>
+        <v>213.004</v>
       </c>
       <c r="C61">
-        <v>542</v>
+        <v>267</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -2008,13 +1996,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46184.625</v>
+        <v>46212.625</v>
       </c>
       <c r="B62">
-        <v>824.872</v>
+        <v>220.235</v>
       </c>
       <c r="C62">
-        <v>550</v>
+        <v>305</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -2025,13 +2013,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46184.63541666666</v>
+        <v>46212.63541666666</v>
       </c>
       <c r="B63">
-        <v>847.1849999999999</v>
+        <v>222.144</v>
       </c>
       <c r="C63">
-        <v>510</v>
+        <v>297</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2042,13 +2030,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46184.64583333334</v>
+        <v>46212.64583333334</v>
       </c>
       <c r="B64">
-        <v>867.973</v>
+        <v>225.722</v>
       </c>
       <c r="C64">
-        <v>525</v>
+        <v>273</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2059,13 +2047,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46184.65625</v>
+        <v>46212.65625</v>
       </c>
       <c r="B65">
-        <v>888.471</v>
+        <v>229.236</v>
       </c>
       <c r="C65">
-        <v>533</v>
+        <v>261</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -2076,13 +2064,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46184.66666666666</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="B66">
-        <v>896.322</v>
+        <v>228.419</v>
       </c>
       <c r="C66">
-        <v>555</v>
+        <v>273</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2093,13 +2081,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46184.67708333334</v>
+        <v>46212.67708333334</v>
       </c>
       <c r="B67">
-        <v>899.116</v>
+        <v>231.238</v>
       </c>
       <c